--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R69875673269444fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Ra5a3ef9629cf47b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Rf78ec5972e6c4e2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R4e1ac54991c64d54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R7004b990cad54fa8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9e7ec641311149cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R623b14e734884736"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Ra3fc694566e74908"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R321c0c0bae554346"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R7addb0bb97924c53"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -439,7 +439,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 14:57 JST</x:v>
+        <x:v>2026-06-23 15:16 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -487,7 +487,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build includes the US-051 native local Source Analysis default plus ProjectPanel source-analysis AX identifiers, the US-047 Command Palette stale-search-field fix, the US-045 preview renderer duration fix, and the US-056 native Candidate Swap AX/testability fix. Focused ProjectAnalysisRunnerTests passed 5/0, focused Project readiness/goal tests passed 6/0, focused Agent job/readiness tests passed 13/0, focused Codex App Server/Command Palette tests passed 14/0, swift build --target VideoOSStudio passed, build_and_run.sh --verify rebuilt/applied the app, git diff --check passed on focused changed files, and full swift test previously executed 229 tests with 0 failures.</x:v>
+        <x:v>Latest code build includes the US-052 ProjectPanel compile/review identifiers plus roughCutCompileActivity label fix, the US-051 native local Source Analysis default, the US-047 Command Palette stale-search-field fix, the US-045 preview renderer duration fix, and the US-056 native Candidate Swap AX/testability fix. Focused ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests passed 16/0; focused Project readiness/goal tests passed 6/0; focused Agent job/readiness tests passed 13/0; focused Codex App Server/Command Palette tests passed 14/0; swift build --target VideoOSStudio passed; build_and_run.sh --verify rebuilt/applied the app; git diff --check passed on focused changed files; and full swift test previously executed 229 tests with 0 failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-051 native loop verified the ProjectPanel Source Analysis button on a disposable one-source project. The panel showed ready / 1 source / 0 skipped and a local command with all skip flags plus --concurrency 1 --no-cache; clicking Run Source Analysis changed the button to Analyzing Sources and completed with Local analysis completed for 1 sources. Artifacts had assets=1, segments=1, indexDocuments=2, no appraiser_frames, and no source_map due skip-media-link; the disposable project was removed afterward. The prior US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
+        <x:v>Latest US-052 native loop verified ProjectPanel Compile Rough Cut and Apply Review Patch on a disposable project. Compile Rough Cut completed with Rough cut compiled and timeline.json is ready plus exact preview / 50s timeline; Apply Review Patch completed with Review patch applied and timeline.json was recompiled. Artifacts showed timeline version=2, markerCount=6, US-052 smoke marker present, indexDocuments=253, library ready, assets=2, segments=2, mediaReady=true, and ragReady=true. The disposable project was removed and Refresh Projects removed it from the shelf. The prior US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest native checks used computer-use element targeting instead of coordinate-only probing: ProjectPanel.RunSourceAnalysisButton and ProjectPanel.SourceAnalysisCommandLine were visible on the disposable project, the button executed local analysis, and Refresh Projects removed the disposable project from the shelf afterward. Prior Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Settings, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks remain recorded in Test Log.</x:v>
+        <x:v>Latest native checks used computer-use element targeting: ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine were visible. During rough-cut compile, only the Rough Cut button showed Compiling Rough Cut; during review patch compile, only Apply Review Patch showed Applying Review Patch. Prior Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Settings, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks remain recorded in Test Log.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1912,19 +1912,19 @@
         <x:v>As a native Studio operator, I can compile a rough cut from canonical planning artifacts, or apply review_patch.json through the deterministic compiler.</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>ProjectPanel, command palette, and menu call compileSelectedProjectRoughCut or compileSelectedProjectWithReviewPatch; core runner validates readiness, invokes scripts/compile-timeline.ts, refreshes timeline state, and rebuilds the project index after success.</x:v>
+        <x:v>ProjectPanel, command palette, and menu call compileSelectedProjectRoughCut or compileSelectedProjectWithReviewPatch; core runner validates readiness, invokes scripts/compile-timeline.ts, refreshes timeline state, and rebuilds the project index after success. ProjectPanel exposes stable Rough Cut / Review Patch identifiers and tracks the active compile activity so only the button for the running action shows a progress label.</x:v>
       </x:c>
       <x:c r="E53" s="26" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/ProjectInspectorViews.swift:302-323; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1614-1631,2073-2110; apps/macos-studio/Sources/VideoOSStudioCore/ProjectRoughCutCompileRunner.swift; apps/macos-studio/Sources/VideoOSStudioCLI/main.swift:790-837,2380-2391</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/ProjectInspectorViews.swift:268-328; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:15-20,176-183,1690-1714,2204-2240; apps/macos-studio/Sources/VideoOSStudioCore/ProjectRoughCutCompileRunner.swift; apps/macos-studio/Sources/VideoOSStudioCLI/main.swift:790-837,2380-2391</x:v>
       </x:c>
       <x:c r="F53" s="26" t="str">
-        <x:v>Run ProjectRoughCutCompileRunnerTests and ReviewPatchDocumentTests; run compile-plan on existing projects; run compile-run and --review-patch on an outputs smoke project; confirm timeline, preview manifest, marker, and index refresh.</x:v>
+        <x:v>Run ProjectRoughCutCompileRunnerTests and ReviewPatchDocumentTests; run compile-plan on existing projects; run compile-run and --review-patch on an outputs smoke project; click native Compile Rough Cut and Apply Review Patch on a disposable project; confirm timeline, preview manifest, marker, and index refresh.</x:v>
       </x:c>
       <x:c r="G53" s="26" t="str">
-        <x:v>Runtime contract pass; UI click pending</x:v>
+        <x:v>Native compile/review patch pass</x:v>
       </x:c>
       <x:c r="H53" s="11" t="str">
-        <x:v>Existing ax1 and fumoto projects plan as ready to recompile. outputs/us052-compile-smoke compiled with skip-preview, wrote timeline.json, rebuilt 253 SQLite documents, then applied review_patch.json through --review-patch with Patch applied 1/1 ops, version 1-&gt;2, marker count 6, and the smoke marker persisted. Native ProjectPanel button click remains pending.</x:v>
+        <x:v>Existing ax1 and fumoto projects plan as ready to recompile. outputs/us052-compile-smoke compiled with skip-preview, wrote timeline.json, rebuilt 253 SQLite documents, then applied review_patch.json through --review-patch with Patch applied 1/1 ops, version 1-&gt;2, marker count 6, and the smoke marker persisted. Latest native pass copied that smoke fixture to projects/us052-native-compile-smoke, reset timeline.json to v001, clicked ProjectPanel.CompileRoughCutButton, observed only the Rough Cut button change to Compiling Rough Cut while ProjectPanel.ApplyReviewPatchButton stayed labeled Apply Review Patch, and completed with Rough cut compiled and timeline.json is ready plus exact preview. Clicking Apply Review Patch then showed only Applying Review Patch, command line included --patch review_patch.json, completed with Review patch applied and timeline.json was recompiled, timeline version=2, markerCount=6, US-052 smoke marker visible at frame 12, indexDocuments=253, library-status ready, and the disposable project was removed after Refresh Projects.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="48" customHeight="1">
@@ -3088,7 +3088,7 @@
         <x:v>Marked each macOS story with Core tests pass / UI pending or runtime pending instead of claiming Pass; next loop should run native manual/automation passes story by story and promote statuses only with evidence.</x:v>
       </x:c>
       <x:c r="H27" s="26" t="str">
-        <x:v>Current evidence: swift test passed 223 tests; build/run verify passed in the latest Viewer loop; US-045 has runtime/AVKit first-frame and latest-output evidence with visual confirmation pending, US-046 has project-switch runtime plus ProjectInitializer creation/failure contract tests but NSOpenPanel creation remains unpromoted, US-047 has native Command Palette keyboard/top-bar pass, US-048 has native Agent panel Check/Start/Stop lifecycle pass, US-049 has native read-only Status job plus approval prompt/rejection gate pass while approved write remains intentionally pending, US-050 has native Project tab readiness/action queue plus Copy-to-pasteboard pass while destructive Open/Start &amp; Run actions remain pending, US-051 has native local Source Analysis click evidence on a disposable one-source project, and US-053 has marker/waveform CLI coverage after the MP4 waveform fix. Remaining macOS stories are explicitly not complete.</x:v>
+        <x:v>Current evidence: swift test passed 223 tests; build/run verify passed in the latest Viewer loop; US-045 has runtime/AVKit first-frame and latest-output evidence with visual confirmation pending, US-046 has project-switch runtime plus ProjectInitializer creation/failure contract tests but NSOpenPanel creation remains unpromoted, US-047 has native Command Palette keyboard/top-bar pass, US-048 has native Agent panel Check/Start/Stop lifecycle pass, US-049 has native read-only Status job plus approval prompt/rejection gate pass while approved write remains intentionally pending, US-050 has native Project tab readiness/action queue plus Copy-to-pasteboard pass while destructive Open/Start &amp; Run actions remain pending, US-051 has native local Source Analysis click evidence on a disposable one-source project, US-052 has native Compile Rough Cut and Apply Review Patch click evidence on a disposable project plus marker/index/library verification, and US-053 has marker/waveform CLI coverage after the MP4 waveform fix. Remaining macOS stories are explicitly not complete.</x:v>
       </x:c>
       <x:c r="I27" s="11" t="str">
         <x:v>Open</x:v>
@@ -8485,23 +8485,43 @@
       </x:c>
     </x:row>
     <x:row r="216" ht="48" customHeight="1">
-      <x:c r="A216" s="12" t="str">
+      <x:c r="A216" s="10" t="str">
         <x:v>TL-215</x:v>
       </x:c>
-      <x:c r="B216" s="27" t="str">
+      <x:c r="B216" s="26" t="str">
         <x:v>US-051</x:v>
       </x:c>
-      <x:c r="C216" s="27" t="str">
+      <x:c r="C216" s="26" t="str">
         <x:v>Native local Source Analysis button</x:v>
       </x:c>
-      <x:c r="D216" s="27" t="str">
+      <x:c r="D216" s="26" t="str">
         <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
       </x:c>
-      <x:c r="E216" s="27" t="str">
+      <x:c r="E216" s="26" t="str">
         <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
       </x:c>
-      <x:c r="F216" s="13" t="str">
+      <x:c r="F216" s="11" t="str">
         <x:v>Native local analysis pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" ht="48" customHeight="1">
+      <x:c r="A217" s="12" t="str">
+        <x:v>TL-216</x:v>
+      </x:c>
+      <x:c r="B217" s="27" t="str">
+        <x:v>US-052</x:v>
+      </x:c>
+      <x:c r="C217" s="27" t="str">
+        <x:v>Native Rough Cut and Review Patch buttons</x:v>
+      </x:c>
+      <x:c r="D217" s="27" t="str">
+        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
+      </x:c>
+      <x:c r="E217" s="27" t="str">
+        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
+      </x:c>
+      <x:c r="F217" s="13" t="str">
+        <x:v>Native compile/review patch pass</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8930,10 +8950,10 @@
         <x:v>macOS Rough cut compile runner</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/ProjectInspectorViews.swift:302-323; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1614-1631,2073-2110; apps/macos-studio/Sources/VideoOSStudioCore/ProjectRoughCutCompileRunner.swift; apps/macos-studio/Sources/VideoOSStudioCLI/main.swift:790-837,2380-2391</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/ProjectInspectorViews.swift:268-328; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:15-20,176-183,1690-1714,2204-2240; apps/macos-studio/Sources/VideoOSStudioCore/ProjectRoughCutCompileRunner.swift; apps/macos-studio/Sources/VideoOSStudioCLI/main.swift:790-837,2380-2391</x:v>
       </x:c>
       <x:c r="C38" s="11" t="str">
-        <x:v>Rough cut compile and review_patch compile readiness, command generation, deterministic compiler invocation, timeline refresh, preview manifest regeneration, and post-compile SQLite index rebuild.</x:v>
+        <x:v>Rough cut compile and review_patch compile readiness, stable ProjectPanel compile/review identifiers, active compile activity tracking so progress labels do not cross-contaminate actions, command generation, deterministic compiler invocation, timeline refresh, preview manifest regeneration, and post-compile SQLite index rebuild.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="48" customHeight="1">

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9e7ec641311149cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R623b14e734884736"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Ra3fc694566e74908"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R321c0c0bae554346"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R7addb0bb97924c53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R50147e2fa6254f2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rc2bf5d19799b42cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R9808efb36a2d4adb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="Rd4207f5829704230"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R3d5e50cad6614dca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -439,7 +439,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 15:16 JST</x:v>
+        <x:v>2026-06-23 15:32 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -487,7 +487,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build includes the US-052 ProjectPanel compile/review identifiers plus roughCutCompileActivity label fix, the US-051 native local Source Analysis default, the US-047 Command Palette stale-search-field fix, the US-045 preview renderer duration fix, and the US-056 native Candidate Swap AX/testability fix. Focused ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests passed 16/0; focused Project readiness/goal tests passed 6/0; focused Agent job/readiness tests passed 13/0; focused Codex App Server/Command Palette tests passed 14/0; swift build --target VideoOSStudio passed; build_and_run.sh --verify rebuilt/applied the app; git diff --check passed on focused changed files; and full swift test previously executed 229 tests with 0 failures.</x:v>
+        <x:v>Latest code build includes the US-053 Timeline/Feedback AX identifiers, the US-052 ProjectPanel compile/review identifiers plus roughCutCompileActivity label fix, the US-051 native local Source Analysis default, the US-047 Command Palette stale-search-field fix, the US-045 preview renderer duration fix, and the US-056 native Candidate Swap AX/testability fix. Focused TimelineDocument, ProjectAudioTimelineMap, ProjectAudioWaveformMap, StudioFeedbackSession, and CandidateBrowserDataSource tests passed 24/0; swift build --target VideoOSStudio passed; build_and_run.sh --verify rebuilt/applied the app from the repo root; git diff --check passed; and full swift test previously executed 229 tests with 0 failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-052 native loop verified ProjectPanel Compile Rough Cut and Apply Review Patch on a disposable project. Compile Rough Cut completed with Rough cut compiled and timeline.json is ready plus exact preview / 50s timeline; Apply Review Patch completed with Review patch applied and timeline.json was recompiled. Artifacts showed timeline version=2, markerCount=6, US-052 smoke marker present, indexDocuments=253, library ready, assets=2, segments=2, mediaReady=true, and ragReady=true. The disposable project was removed and Refresh Projects removed it from the shelf. The prior US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
+        <x:v>Latest US-053 native loop verified Timeline marker/clip/audio cue identifiers and context menu actions on ax1-participant-voices-20260401. Native right-click Approve/Reject updated FeedbackStatus counts, Swap opened CandidateSwap.Title, Search opened Search Footage, and Discard returned all pending/approved/rejected/swapped counts to 0. CLI checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. The prior US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest native checks used computer-use element targeting: ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine were visible. During rough-cut compile, only the Rough Cut button showed Compiling Rough Cut; during review patch compile, only Apply Review Patch showed Applying Review Patch. Prior Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Settings, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks remain recorded in Test Log.</x:v>
+        <x:v>Latest native checks used computer-use element targeting: Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.Marker.*, Timeline.AudioCue.*, Timeline.ContextMenu.Approve/Reject/Swap/SearchReplacement, CandidateSwap.Title, Search Footage sheet, FeedbackStatus.PendingCount, and FeedbackStatus.DiscardButton. Prior ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Settings, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks remain recorded in Test Log.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1938,19 +1938,19 @@
         <x:v>As a native Studio editor, I can inspect timeline tracks, markers, waveform/audio cues, scrub the playhead, select clips, and open approve/reject/swap/search actions from clips.</x:v>
       </x:c>
       <x:c r="D54" s="26" t="str">
-        <x:v>TimelinePanel renders ruler, markers, tracks, waveform overlay, cues, selected/changed highlights, playhead scrub gesture, and context menu operations.</x:v>
+        <x:v>TimelinePanel renders ruler, markers, tracks, waveform overlay, cues, selected/changed highlights, playhead scrub gesture, context menu operations, and stable AX identifiers for timeline clips, markers, audio cues, waveforms, context menu commands, and feedback status.</x:v>
       </x:c>
       <x:c r="E54" s="26" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/TimelineViews.swift:6-565; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:686-718,873-966; apps/macos-studio/Sources/VideoOSStudioCore/ProjectAudioWaveformMap.swift:1-240; apps/macos-studio/Sources/VideoOSStudioCLI/main.swift:1370-1478</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/TimelineViews.swift:6-594; apps/macos-studio/Sources/VideoOSStudio/FeedbackStatusBar.swift:4-76; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:686-718,873-966; apps/macos-studio/Sources/VideoOSStudioCore/ProjectAudioWaveformMap.swift:1-240; apps/macos-studio/Sources/VideoOSStudioCLI/main.swift:1370-1478</x:v>
       </x:c>
       <x:c r="F54" s="26" t="str">
-        <x:v>Use native app to scrub/select/context-click clips and confirm Viewer/Inspector/playhead sync; run timeline/audio map tests and CLI marker/waveform/monitor checks; relaunch and scan logs for AVAudioFile MP4 errors.</x:v>
+        <x:v>Use native app to scrub/select/context-click clips and confirm Viewer/Inspector/playhead sync; run timeline/audio map tests and CLI marker/waveform checks; relaunch and scan logs for AVAudioFile MP4 errors.</x:v>
       </x:c>
       <x:c r="G54" s="26" t="str">
-        <x:v>Core/CLI pass after MP4 waveform fix; native context menu pending</x:v>
+        <x:v>Native timeline/context menu pass</x:v>
       </x:c>
       <x:c r="H54" s="11" t="str">
-        <x:v>Timeline selection and Viewer sync are exercised through monitor-status and the Viewer fix path. TimelineDocument, audio map, waveform, and feedback session tests pass; ax1 reports 5 beat markers, 0 audio cues for that fixture, and 7 A1 waveform overlays extracted from real MP4 through the AVAssetReader path without AVAudioFile 2003334207 relaunch logs. Native right-click approve/reject/swap/search context menu still needs a reliable UI/manual pass.</x:v>
+        <x:v>TimelineDocument, audio map, waveform, candidate browser, and feedback session tests pass. On VideoOSStudio PID 32295, AX exposed Timeline.Marker.*, Timeline.Clip.*, Timeline.AudioCue.*, context menu command IDs, and FeedbackStatus.* controls for ax1-participant-voices-20260401. CLI returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 normalized peaks from source_map.local_source_path. Native right-click on CLP_0001 exposed Approve/Reject/Swap/Search/Remove; Approve changed status to 1 approved, Reject on CLP_0002 changed status to 1 changes pending / 1 approved / 1 rejected, Swap opened CandidateSwap.Title for CLP_0001, Search opened the Search Footage sheet, and Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. A 10m unified log scan after relaunch returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="48" customHeight="1">
@@ -3088,7 +3088,7 @@
         <x:v>Marked each macOS story with Core tests pass / UI pending or runtime pending instead of claiming Pass; next loop should run native manual/automation passes story by story and promote statuses only with evidence.</x:v>
       </x:c>
       <x:c r="H27" s="26" t="str">
-        <x:v>Current evidence: swift test passed 223 tests; build/run verify passed in the latest Viewer loop; US-045 has runtime/AVKit first-frame and latest-output evidence with visual confirmation pending, US-046 has project-switch runtime plus ProjectInitializer creation/failure contract tests but NSOpenPanel creation remains unpromoted, US-047 has native Command Palette keyboard/top-bar pass, US-048 has native Agent panel Check/Start/Stop lifecycle pass, US-049 has native read-only Status job plus approval prompt/rejection gate pass while approved write remains intentionally pending, US-050 has native Project tab readiness/action queue plus Copy-to-pasteboard pass while destructive Open/Start &amp; Run actions remain pending, US-051 has native local Source Analysis click evidence on a disposable one-source project, US-052 has native Compile Rough Cut and Apply Review Patch click evidence on a disposable project plus marker/index/library verification, and US-053 has marker/waveform CLI coverage after the MP4 waveform fix. Remaining macOS stories are explicitly not complete.</x:v>
+        <x:v>Current evidence: swift test passed 223 tests; build/run verify passed in the latest Viewer loop; US-045 has runtime/AVKit first-frame and latest-output evidence with visual confirmation pending, US-046 has project-switch runtime plus ProjectInitializer creation/failure contract tests but NSOpenPanel creation remains unpromoted, US-047 has native Command Palette keyboard/top-bar pass, US-048 has native Agent panel Check/Start/Stop lifecycle pass, US-049 has native read-only Status job plus approval prompt/rejection gate pass while approved write remains intentionally pending, US-050 has native Project tab readiness/action queue plus Copy-to-pasteboard pass while destructive Open/Start &amp; Run actions remain pending, US-051 has native local Source Analysis click evidence on a disposable one-source project, US-052 has native Compile Rough Cut and Apply Review Patch click evidence on a disposable project plus marker/index/library verification, and US-053 has native timeline marker/audio/waveform/context-menu approve/reject/swap/search evidence. Remaining macOS stories are explicitly not complete.</x:v>
       </x:c>
       <x:c r="I27" s="11" t="str">
         <x:v>Open</x:v>
@@ -3407,7 +3407,7 @@
         <x:v>Route mov/mp4/m4v waveform extraction through AVAssetReader with float32 PCM output, keep the existing AVAudioFile path for audio files, and fall back to AVAssetReader if AVAudioFile throws.</x:v>
       </x:c>
       <x:c r="H38" s="26" t="str">
-        <x:v>ProjectAudioWaveformMapTests passed; audio-waveform ax1-participant-voices-20260401 8 returned 7 A1 overlays with peaks from source_map.local_source_path; app relaunch PID 99420 produced no AVAudioFile/2003334207 log matches while AVKit still logged seek 14.880, ReadyForPlayback, and Did enqueue first frame; full swift test passed 192 tests.</x:v>
+        <x:v>ProjectAudioWaveformMapTests passed; audio-waveform ax1-participant-voices-20260401 8 returned 7 A1 overlays with peaks from source_map.local_source_path; app relaunch PID 99420 produced no AVAudioFile/2003334207 log matches while AVKit still logged seek 14.880, ReadyForPlayback, and Did enqueue first frame; latest native US-053 relaunch PID 32295 plus 10m log scan again returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
       </x:c>
       <x:c r="I38" s="11" t="str">
         <x:v>Fixed</x:v>
@@ -8505,23 +8505,43 @@
       </x:c>
     </x:row>
     <x:row r="217" ht="48" customHeight="1">
-      <x:c r="A217" s="12" t="str">
+      <x:c r="A217" s="10" t="str">
         <x:v>TL-216</x:v>
       </x:c>
-      <x:c r="B217" s="27" t="str">
+      <x:c r="B217" s="26" t="str">
         <x:v>US-052</x:v>
       </x:c>
-      <x:c r="C217" s="27" t="str">
+      <x:c r="C217" s="26" t="str">
         <x:v>Native Rough Cut and Review Patch buttons</x:v>
       </x:c>
-      <x:c r="D217" s="27" t="str">
+      <x:c r="D217" s="26" t="str">
         <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
       </x:c>
-      <x:c r="E217" s="27" t="str">
+      <x:c r="E217" s="26" t="str">
         <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
-      <x:c r="F217" s="13" t="str">
+      <x:c r="F217" s="11" t="str">
         <x:v>Native compile/review patch pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" ht="48" customHeight="1">
+      <x:c r="A218" s="12" t="str">
+        <x:v>TL-217</x:v>
+      </x:c>
+      <x:c r="B218" s="27" t="str">
+        <x:v>US-053</x:v>
+      </x:c>
+      <x:c r="C218" s="27" t="str">
+        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
+      </x:c>
+      <x:c r="D218" s="27" t="str">
+        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
+      </x:c>
+      <x:c r="E218" s="27" t="str">
+        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
+      </x:c>
+      <x:c r="F218" s="13" t="str">
+        <x:v>Native timeline/context menu pass</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8964,7 +8984,7 @@
         <x:v>apps/macos-studio/Sources/VideoOSStudio/TimelineViews.swift; apps/macos-studio/Sources/VideoOSStudio/FeedbackStatusBar.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectAudioWaveformMap.swift; apps/macos-studio/Sources/VideoOSStudioCore/StudioFeedbackSession.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectStudioPatchPromotionRunner.swift; runtime/eval/studio-patch-promoter.ts; scripts/promote-studio-patch.ts</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
-        <x:v>Timeline tracks, markers, MP4 waveforms through AVAssetReader, audio-file waveforms through AVAudioFile, cues, selection/context actions, pending operation summary, conflict detection, apply preview, promote replace/remove patches into planning artifacts, discard, and undo flow.</x:v>
+        <x:v>Timeline tracks, markers, MP4 waveforms through AVAssetReader, audio-file waveforms through AVAudioFile, audio/story cues, stable Timeline.* and FeedbackStatus.* AX identifiers, right-click context actions for approve/reject/swap/search/remove, pending operation summary, conflict detection, apply preview, promote replace/remove patches into planning artifacts, discard, and undo flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="48" customHeight="1">

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R50147e2fa6254f2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rc2bf5d19799b42cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R9808efb36a2d4adb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="Rd4207f5829704230"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R3d5e50cad6614dca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Reef68d17f9f34e89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R4e23e0978a0a46f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R679f567657464234"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R3540e636985b4a91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R4fa032c29c094a5a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -439,7 +439,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 15:32 JST</x:v>
+        <x:v>2026-06-23 15:45 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -487,7 +487,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build includes the US-053 Timeline/Feedback AX identifiers, the US-052 ProjectPanel compile/review identifiers plus roughCutCompileActivity label fix, the US-051 native local Source Analysis default, the US-047 Command Palette stale-search-field fix, the US-045 preview renderer duration fix, and the US-056 native Candidate Swap AX/testability fix. Focused TimelineDocument, ProjectAudioTimelineMap, ProjectAudioWaveformMap, StudioFeedbackSession, and CandidateBrowserDataSource tests passed 24/0; swift build --target VideoOSStudio passed; build_and_run.sh --verify rebuilt/applied the app from the repo root; git diff --check passed; and full swift test previously executed 229 tests with 0 failures.</x:v>
+        <x:v>Latest code build includes the US-054 visible FeedbackStatus.UndoButton, the US-053 Timeline/Feedback AX identifiers, the US-052 ProjectPanel compile/review identifiers plus roughCutCompileActivity label fix, the US-051 native local Source Analysis default, the US-047 Command Palette stale-search-field fix, the US-045 preview renderer duration fix, and the US-056 native Candidate Swap AX/testability fix. Focused US-054 Swift tests passed 21/0; studio-patch-promoter tests passed 5/0; npm run build passed; swift build --target VideoOSStudio passed; build_and_run.sh --verify rebuilt/applied the app from the repo root; git diff --check passed; and full swift test previously executed 229 tests with 0 failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-053 native loop verified Timeline marker/clip/audio cue identifiers and context menu actions on ax1-participant-voices-20260401. Native right-click Approve/Reject updated FeedbackStatus counts, Swap opened CandidateSwap.Title, Search opened Search Footage, and Discard returned all pending/approved/rejected/swapped counts to 0. CLI checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. The prior US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
+        <x:v>Latest US-054 native loop verified Studio feedback Apply &amp; Preview and Undo on a disposable project. Rejecting CLIP_001 staged one pending remove, Apply &amp; Preview wrote studio_patch_*.json plus patch_history backup/index, changed timeline hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e -&gt; 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, removed the only clip, reset pending counts, and enabled Promote/Undo. Clicking Undo restored CLIP_001, emptied history records, returned the hash to d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, disabled Undo/Promote, and the disposable project was deleted after Refresh Projects. Prior US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest native checks used computer-use element targeting: Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.Marker.*, Timeline.AudioCue.*, Timeline.ContextMenu.Approve/Reject/Swap/SearchReplacement, CandidateSwap.Title, Search Footage sheet, FeedbackStatus.PendingCount, and FeedbackStatus.DiscardButton. Prior ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Settings, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks remain recorded in Test Log.</x:v>
+        <x:v>Latest native checks used computer-use element targeting: ProjectShelf.us054-native-feedback-smoke-20260623, Timeline.Clip.V1.CLIP_001, Timeline.ContextMenu.Reject.V1.CLIP_001, FeedbackStatus.ApplyAndPreviewButton, FeedbackStatus.PromoteButton, FeedbackStatus.UndoButton, FeedbackStatus.DiscardButton, and RefreshProjectsButton. Prior Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Settings, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks remain recorded in Test Log.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1964,19 +1964,19 @@
         <x:v>As a native Studio editor, I can stage approve/reject/swap/note operations, detect conflicts, apply and preview them safely, promote applied patches, discard pending changes, or undo the last patch.</x:v>
       </x:c>
       <x:c r="D55" s="26" t="str">
-        <x:v>FeedbackStatusBar summarizes pending ops/conflicts/history; Timeline shortcuts stage approvals/rejections; StudioViewModel writes patch envelope, backs up timeline, compiles, records history, rolls back failure, highlights changed clips, promotes replace/remove patch ops into planning artifacts, and undoes.</x:v>
+        <x:v>FeedbackStatusBar summarizes pending ops/conflicts/history and exposes Apply &amp; Preview, Promote, Undo, and Discard controls; Timeline shortcuts stage approvals/rejections; StudioViewModel writes patch envelope, backs up timeline, compiles, records history, rolls back failure, highlights changed clips, promotes replace/remove patch ops into planning artifacts, and undoes.</x:v>
       </x:c>
       <x:c r="E55" s="26" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/FeedbackStatusBar.swift:4-63; apps/macos-studio/Sources/VideoOSStudio/ContentView.swift:810-816; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1633-1999; apps/macos-studio/Sources/VideoOSStudioCore/StudioFeedbackSession.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectStudioPatchPromotionRunner.swift; scripts/promote-studio-patch.ts; runtime/eval/studio-patch-promoter.ts</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/FeedbackStatusBar.swift:4-85; apps/macos-studio/Sources/VideoOSStudio/ContentView.swift:772-781,843-853; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1633-1999; apps/macos-studio/Sources/VideoOSStudioCore/StudioFeedbackSession.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectStudioPatchPromotionRunner.swift; scripts/promote-studio-patch.ts; runtime/eval/studio-patch-promoter.ts</x:v>
       </x:c>
       <x:c r="F55" s="26" t="str">
-        <x:v>Run StudioFeedbackSessionTests, ReviewPatchDocumentTests, PatchHistoryIndexTests, ProjectStudioPatchPromotionRunnerTests, studio-patch-promoter tests, TypeScript build, Swift build/test, build_and_run verify; manually stage/apply/undo one safe patch remains a visual pass.</x:v>
+        <x:v>Run StudioFeedbackSessionTests, ReviewPatchDocumentTests, PatchHistoryIndexTests, ProjectStudioPatchPromotionRunnerTests, studio-patch-promoter tests, TypeScript build, Swift build/test, build_and_run verify; stage/apply/undo one safe patch on a disposable native project and verify timeline hash/history cleanup.</x:v>
       </x:c>
       <x:c r="G55" s="26" t="str">
-        <x:v>Core/CLI pass after promote fix; native apply/undo visual pending</x:v>
+        <x:v>Native apply/undo pass; promote core/enable pass</x:v>
       </x:c>
       <x:c r="H55" s="11" t="str">
-        <x:v>Core patch/session/history behavior is covered. A new promote-studio-patch CLI now promotes replace_segment/remove_segment Studio patches into selects_candidates.yaml and edit_blueprint.yaml, Swift has a ProjectStudioPatchPromotionRunner, and the Promote button is only enabled when the latest applied patch has promotable operations. Native apply/undo visual loop is still not fully re-tested through UI automation.</x:v>
+        <x:v>Core patch/session/history behavior is covered. promote-studio-patch CLI promotes replace_segment/remove_segment Studio patches into selects_candidates.yaml and edit_blueprint.yaml, Swift has a ProjectStudioPatchPromotionRunner, and the Promote button is only enabled when the latest applied patch has promotable operations. Latest native pass added an explicit FeedbackStatus.UndoButton, copied the US-052 compile fixture to a disposable projects/us054-native-feedback-smoke-20260623 project, staged Reject on CLIP_001, clicked Apply &amp; Preview, observed Timeline updated. 1 clips changed with pending counts reset, timeline version=2 and clip count=0, studio_patch_*.json plus patch_history backup/index written, Promote and Undo enabled, then clicked Undo and observed Reverted to previous timeline, CLIP_001 restored, timeline hash returned to d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, history records emptied, and the disposable project was removed after Refresh Projects.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="48" customHeight="1">
@@ -3088,7 +3088,7 @@
         <x:v>Marked each macOS story with Core tests pass / UI pending or runtime pending instead of claiming Pass; next loop should run native manual/automation passes story by story and promote statuses only with evidence.</x:v>
       </x:c>
       <x:c r="H27" s="26" t="str">
-        <x:v>Current evidence: swift test passed 223 tests; build/run verify passed in the latest Viewer loop; US-045 has runtime/AVKit first-frame and latest-output evidence with visual confirmation pending, US-046 has project-switch runtime plus ProjectInitializer creation/failure contract tests but NSOpenPanel creation remains unpromoted, US-047 has native Command Palette keyboard/top-bar pass, US-048 has native Agent panel Check/Start/Stop lifecycle pass, US-049 has native read-only Status job plus approval prompt/rejection gate pass while approved write remains intentionally pending, US-050 has native Project tab readiness/action queue plus Copy-to-pasteboard pass while destructive Open/Start &amp; Run actions remain pending, US-051 has native local Source Analysis click evidence on a disposable one-source project, US-052 has native Compile Rough Cut and Apply Review Patch click evidence on a disposable project plus marker/index/library verification, and US-053 has native timeline marker/audio/waveform/context-menu approve/reject/swap/search evidence. Remaining macOS stories are explicitly not complete.</x:v>
+        <x:v>Current evidence: swift test passed 223 tests; build/run verify passed in the latest Viewer loop; US-045 has runtime/AVKit first-frame and latest-output evidence with visual confirmation pending, US-046 has project-switch runtime plus ProjectInitializer creation/failure contract tests but NSOpenPanel creation remains unpromoted, US-047 has native Command Palette keyboard/top-bar pass, US-048 has native Agent panel Check/Start/Stop lifecycle pass, US-049 has native read-only Status job plus approval prompt/rejection gate pass while approved write remains intentionally pending, US-050 has native Project tab readiness/action queue plus Copy-to-pasteboard pass while destructive Open/Start &amp; Run actions remain pending, US-051 has native local Source Analysis click evidence on a disposable one-source project, US-052 has native Compile Rough Cut and Apply Review Patch click evidence on a disposable project plus marker/index/library verification, US-053 has native timeline marker/audio/waveform/context-menu approve/reject/swap/search evidence, and US-054 has native disposable apply/undo evidence plus promote core/enable coverage. Remaining macOS stories are explicitly not complete.</x:v>
       </x:c>
       <x:c r="I27" s="11" t="str">
         <x:v>Open</x:v>
@@ -3433,13 +3433,13 @@
         <x:v>Phase 1 left Promote as a skeleton waiting for scripts/promote-studio-patch.ts, while the UI enabled the action based on patch history alone. An operator could apply a preview patch and believe it had been promoted, but a later full compile would still discard replace/remove decisions.</x:v>
       </x:c>
       <x:c r="G39" s="26" t="str">
-        <x:v>Added runtime/eval/studio-patch-promoter.ts and scripts/promote-studio-patch.ts to promote replace_segment/remove_segment ops into selects_candidates.yaml and edit_blueprint.yaml using patch history backups; added ProjectStudioPatchPromotionRunner; changed FeedbackStatusBar to enable Promote only when the latest patch is runnable and contains promotable ops.</x:v>
+        <x:v>Added runtime/eval/studio-patch-promoter.ts and scripts/promote-studio-patch.ts to promote replace_segment/remove_segment ops into selects_candidates.yaml and edit_blueprint.yaml using patch history backups; added ProjectStudioPatchPromotionRunner; changed FeedbackStatusBar to enable Promote only when the latest patch is runnable and contains promotable ops; added a visible Undo button so the native bar exposes the restore path without relying on hidden keyboard shortcuts.</x:v>
       </x:c>
       <x:c r="H39" s="26" t="str">
-        <x:v>studio-patch-promoter tests executed 5 tests with 0 failures, including file-level YAML mutation; npm run build passed; ProjectStudioPatchPromotionRunnerTests and US-054 feedback/history tests executed 21 Swift tests with 0 failures; full swift test passed 195 tests; swift build --target VideoOSStudio and ./script/build_and_run.sh --verify launched PID 49401 with no Studio patch/Promote error logs.</x:v>
+        <x:v>studio-patch-promoter tests executed 5 tests with 0 failures, including file-level YAML mutation; npm run build passed; latest ProjectStudioPatchPromotionRunnerTests and US-054 feedback/history tests executed 21 Swift tests with 0 failures; swift build --target VideoOSStudio and ./script/build_and_run.sh --verify passed; native disposable apply/undo pass showed Promote enabled after apply, Undo restored the original timeline hash, and recent logs had no Studio patch/Promote/crash/fatal matches.</x:v>
       </x:c>
       <x:c r="I39" s="11" t="str">
-        <x:v>Fixed; visual pending</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="48" customHeight="1">
@@ -8525,23 +8525,43 @@
       </x:c>
     </x:row>
     <x:row r="218" ht="48" customHeight="1">
-      <x:c r="A218" s="12" t="str">
+      <x:c r="A218" s="10" t="str">
         <x:v>TL-217</x:v>
       </x:c>
-      <x:c r="B218" s="27" t="str">
+      <x:c r="B218" s="26" t="str">
         <x:v>US-053</x:v>
       </x:c>
-      <x:c r="C218" s="27" t="str">
+      <x:c r="C218" s="26" t="str">
         <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
       </x:c>
-      <x:c r="D218" s="27" t="str">
+      <x:c r="D218" s="26" t="str">
         <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
       </x:c>
-      <x:c r="E218" s="27" t="str">
+      <x:c r="E218" s="26" t="str">
         <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
       </x:c>
-      <x:c r="F218" s="13" t="str">
+      <x:c r="F218" s="11" t="str">
         <x:v>Native timeline/context menu pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" ht="48" customHeight="1">
+      <x:c r="A219" s="12" t="str">
+        <x:v>TL-218</x:v>
+      </x:c>
+      <x:c r="B219" s="27" t="str">
+        <x:v>US-054</x:v>
+      </x:c>
+      <x:c r="C219" s="27" t="str">
+        <x:v>Native Studio feedback Apply and Undo</x:v>
+      </x:c>
+      <x:c r="D219" s="27" t="str">
+        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
+      </x:c>
+      <x:c r="E219" s="27" t="str">
+        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+      </x:c>
+      <x:c r="F219" s="13" t="str">
+        <x:v>Native apply/undo pass</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8981,10 +9001,10 @@
         <x:v>macOS Timeline and feedback</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/TimelineViews.swift; apps/macos-studio/Sources/VideoOSStudio/FeedbackStatusBar.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectAudioWaveformMap.swift; apps/macos-studio/Sources/VideoOSStudioCore/StudioFeedbackSession.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectStudioPatchPromotionRunner.swift; runtime/eval/studio-patch-promoter.ts; scripts/promote-studio-patch.ts</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/TimelineViews.swift; apps/macos-studio/Sources/VideoOSStudio/FeedbackStatusBar.swift; apps/macos-studio/Sources/VideoOSStudio/ContentView.swift:772-781,843-853; apps/macos-studio/Sources/VideoOSStudioCore/ProjectAudioWaveformMap.swift; apps/macos-studio/Sources/VideoOSStudioCore/StudioFeedbackSession.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectStudioPatchPromotionRunner.swift; runtime/eval/studio-patch-promoter.ts; scripts/promote-studio-patch.ts</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
-        <x:v>Timeline tracks, markers, MP4 waveforms through AVAssetReader, audio-file waveforms through AVAudioFile, audio/story cues, stable Timeline.* and FeedbackStatus.* AX identifiers, right-click context actions for approve/reject/swap/search/remove, pending operation summary, conflict detection, apply preview, promote replace/remove patches into planning artifacts, discard, and undo flow.</x:v>
+        <x:v>Timeline tracks, markers, MP4 waveforms through AVAssetReader, audio-file waveforms through AVAudioFile, audio/story cues, stable Timeline.* and FeedbackStatus.* AX identifiers, right-click context actions for approve/reject/swap/search/remove, pending operation summary, conflict detection, apply preview, promote replace/remove patches into planning artifacts, visible Undo button, discard, and backup-backed undo flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="48" customHeight="1">

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Reef68d17f9f34e89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R4e23e0978a0a46f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R679f567657464234"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R3540e636985b4a91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R4fa032c29c094a5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra7643ec7aec14448"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R5040a1af4ac44328"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Rece78bc9cd0b48bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R832469421b294a16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R052a3f4d096c4f2c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -439,7 +439,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 15:45 JST</x:v>
+        <x:v>2026-06-23 16:02 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -479,7 +479,7 @@
         <x:v>Issues tracked</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="220" customHeight="1">
@@ -487,7 +487,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build includes the US-054 visible FeedbackStatus.UndoButton, the US-053 Timeline/Feedback AX identifiers, the US-052 ProjectPanel compile/review identifiers plus roughCutCompileActivity label fix, the US-051 native local Source Analysis default, the US-047 Command Palette stale-search-field fix, the US-045 preview renderer duration fix, and the US-056 native Candidate Swap AX/testability fix. Focused US-054 Swift tests passed 21/0; studio-patch-promoter tests passed 5/0; npm run build passed; swift build --target VideoOSStudio passed; build_and_run.sh --verify rebuilt/applied the app from the repo root; git diff --check passed; and full swift test previously executed 229 tests with 0 failures.</x:v>
+        <x:v>Latest code build includes the US-057 FootageSearch.* leaf AX identifiers and first-beat default targeting, the US-054 visible FeedbackStatus.UndoButton, the US-053 Timeline/Feedback AX identifiers, the US-052 ProjectPanel compile/review identifiers plus roughCutCompileActivity label fix, the US-051 native local Source Analysis default, the US-047 Command Palette stale-search-field fix, the US-045 preview renderer duration fix, and the US-056 native Candidate Swap AX/testability fix. Focused US-057 Swift tests passed 15/0; footage-search CLI/audio Vitest passed 10/0; swift build --target VideoOSStudio passed; build_and_run.sh --verify rebuilt/applied the app from the repo root; recent log scan returned no Footage/fatal/crash matches; and full swift test previously executed 229 tests with 0 failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-054 native loop verified Studio feedback Apply &amp; Preview and Undo on a disposable project. Rejecting CLIP_001 staged one pending remove, Apply &amp; Preview wrote studio_patch_*.json plus patch_history backup/index, changed timeline hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e -&gt; 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, removed the only clip, reset pending counts, and enabled Promote/Undo. Clicking Undo restored CLIP_001, emptied history records, returned the hash to d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, disabled Undo/Promote, and the disposable project was deleted after Refresh Projects. Prior US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
+        <x:v>Latest US-057 native loop verified Footage Search from Command Palette on ax1-participant-voices-20260401. Text query AI returned Results 2 / fallback, exposed independent FootageSearch.ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs for two results, defaulted BeatPicker to b01, kept Use enabled, Preview on SEG_AST_76B05D86_0001 set the current-timeline preview status, Use on SEG_AST_610FB4A0_0001 staged one replace with 1 changes pending / 1 swapped, and Discard returned pending counts to zero. Prior US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest native checks used computer-use element targeting: ProjectShelf.us054-native-feedback-smoke-20260623, Timeline.Clip.V1.CLIP_001, Timeline.ContextMenu.Reject.V1.CLIP_001, FeedbackStatus.ApplyAndPreviewButton, FeedbackStatus.PromoteButton, FeedbackStatus.UndoButton, FeedbackStatus.DiscardButton, and RefreshProjectsButton. Prior Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Settings, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks remain recorded in Test Log.</x:v>
+        <x:v>Latest native checks used computer-use element targeting: CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.Title, FootageSearch.ModePicker, FootageSearch.QueryField, FootageSearch.SearchButton, FootageSearch.ResultSegment.SEG_AST_610FB4A0_0001, FootageSearch.PreviewButton.SEG_AST_76B05D86_0001, FootageSearch.BeatPicker.SEG_AST_610FB4A0_0001, FootageSearch.UseButton.SEG_AST_610FB4A0_0001, FeedbackStatus.PendingCount, and FeedbackStatus.DiscardButton. Prior Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Settings, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks remain recorded in Test Log.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2042,19 +2042,19 @@
         <x:v>As a native Studio editor, I can search footage by text, visual, audio, hybrid, or multimodal query, preview a result, choose a beat target, and stage it as a replacement.</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>FootageSearchView exposes mode picker, query/file anchors, result cards, per-channel score bars, Preview and Use actions; FootageSearchRunner invokes footage-search CLI and SearchResult builds a tested replace_segment operation whose with_candidate_ref remains a valid segment/candidate reference.</x:v>
+        <x:v>FootageSearchView exposes mode picker, query/file anchors, result count/status, result cards, per-channel score bars, Preview, beat picker, and Use actions with stable leaf AX identifiers; when no clip was selected before opening, it defaults the target beat to the first timeline beat so Use can stage a replacement immediately. FootageSearchRunner invokes footage-search CLI and SearchResult builds a tested replace_segment operation whose with_candidate_ref remains a valid segment/candidate reference.</x:v>
       </x:c>
       <x:c r="E58" s="26" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/FootageSearchView.swift:6-459,228-231; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:2029-2040; apps/macos-studio/Sources/VideoOSStudioCore/FootageSearchRunner.swift:4-114; apps/macos-studio/Tests/VideoOSStudioCoreTests/FootageSearchRunnerTests.swift:114-158; runtime/tools/footage-search-cli.ts:1-120</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/FootageSearchView.swift:6-533,44-48,144-205,246-277,338-413; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:2085-2109; apps/macos-studio/Sources/VideoOSStudioCore/FootageSearchRunner.swift:4-114; apps/macos-studio/Tests/VideoOSStudioCoreTests/FootageSearchRunnerTests.swift:114-158; runtime/tools/footage-search-cli.ts:1-120</x:v>
       </x:c>
       <x:c r="F58" s="26" t="str">
-        <x:v>Run FootageSearchRunnerTests and StudioFeedbackSessionTests; run footage-search CLI tests and audio-mode tests; smoke a real fixture search; build/run native app; complete native sheet visual click pass when capture/input harness is reliable.</x:v>
+        <x:v>Run FootageSearchRunnerTests and StudioFeedbackSessionTests; run footage-search CLI tests and audio-mode tests; smoke a real fixture search; build/run native app; open Footage Search from Command Palette, switch to text mode, query a project with fallback results, click Preview, click Use for a beat target, and confirm FeedbackStatus shows one swapped pending operation before Discard cleanup.</x:v>
       </x:c>
       <x:c r="G58" s="26" t="str">
-        <x:v>Core/CLI/runtime pass after staging-contract fix; native sheet visual pending</x:v>
+        <x:v>Native AX/pixel pass after sheet targetability fix</x:v>
       </x:c>
       <x:c r="H58" s="11" t="str">
-        <x:v>SearchResult now stages replace_segment with with_segment_id=segment_id, with_candidate_ref=segment_id, Footage Search mode in the reason, truncation, and StudioFeedbackSession validity coverage. clean-ui text query forest returned 3 runtime results, first SEG_0036 / AST_006. Native sheet click/visual confirmation remains pending under current AX/capture limitations.</x:v>
+        <x:v>SearchResult stages replace_segment with with_segment_id=segment_id, with_candidate_ref=segment_id, Footage Search mode in the reason, truncation, and StudioFeedbackSession validity coverage. clean-ui text query forest returned 3 runtime results, first SEG_0036 / AST_006. Latest native pass added FootageSearch.* identifiers and first-beat default target selection, relaunched VideoOSStudio PID 83156, opened Search Footage from Command Palette on ax1-participant-voices-20260401, switched to Text, queried AI, observed Results 2 / fallback, leaf IDs FootageSearch.ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* for SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001, clicked Preview on the in-timeline result, clicked Use on SEG_AST_610FB4A0_0001 with BeatPicker=b01, observed FeedbackStatus 1 changes pending / 1 swapped and status Previewing SEG_AST_76B05D86_0001 in the current timeline, then Discard returned 0 changes pending. 10m log scan returned no Footage/fatal/crash matches.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="48" customHeight="1">
@@ -3523,10 +3523,10 @@
         <x:v>Moved Footage Search payload construction into FootageSearchRunner.SearchResult.makeReplaceSegmentOperation(targetClipID:mode:), using segment_id as both with_segment_id and with_candidate_ref, preserving mode in the reason, and truncating long summaries.</x:v>
       </x:c>
       <x:c r="H42" s="26" t="str">
-        <x:v>FootageSearchRunnerTests now assert segment candidate refs, fallback/truncation, and Studio session validity; focused Swift tests executed 15 tests with 0 failures; footage-search CLI/audio Vitest executed 10 tests with 0 failures; clean-ui CLI smoke returned 3 forest results; build_and_run verify and full swift test 201 tests passed.</x:v>
+        <x:v>FootageSearchRunnerTests now assert segment candidate refs, fallback/truncation, and Studio session validity; focused Swift tests executed 15 tests with 0 failures; footage-search CLI/audio Vitest executed 10 tests with 0 failures; clean-ui CLI smoke returned 3 forest results; build_and_run verify and full swift test 201 tests passed. Latest native pass also clicked Preview and Use in the running app, observed 1 swapped pending operation, then Discard cleanup.</x:v>
       </x:c>
       <x:c r="I42" s="11" t="str">
-        <x:v>Fixed; native visual pending</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="48" customHeight="1">
@@ -4139,31 +4139,60 @@
       </x:c>
     </x:row>
     <x:row r="64" ht="48" customHeight="1">
-      <x:c r="A64" s="12" t="str">
+      <x:c r="A64" s="10" t="str">
         <x:v>ISS-063</x:v>
       </x:c>
-      <x:c r="B64" s="27" t="str">
+      <x:c r="B64" s="26" t="str">
         <x:v>US-047</x:v>
       </x:c>
-      <x:c r="C64" s="27" t="str">
+      <x:c r="C64" s="26" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="D64" s="27" t="str">
+      <x:c r="D64" s="26" t="str">
         <x:v>macOS UX/keyboard</x:v>
       </x:c>
-      <x:c r="E64" s="27" t="str">
+      <x:c r="E64" s="26" t="str">
         <x:v>Reopening Command Palette could keep stale text in the visible search field even though the Swift query state was reset before presenting.</x:v>
       </x:c>
-      <x:c r="F64" s="27" t="str">
+      <x:c r="F64" s="26" t="str">
         <x:v>The CommandPalettePanel reuses the same NSTextField/field editor between presentations. ContentView reset commandPaletteQuery to an empty string on open, but focusSearchField only made the field first responder and selected it; the AppKit field editor could still expose the previous composed value through AX and interfere with predictable keyboard/paste testing.</x:v>
       </x:c>
-      <x:c r="G64" s="27" t="str">
+      <x:c r="G64" s="26" t="str">
         <x:v>Changed focusSearchField to sync the NSTextField.stringValue and currentEditor string from parent.query before selecting the search text. This keeps the visible field and Swift binding aligned on every presentation.</x:v>
       </x:c>
-      <x:c r="H64" s="27" t="str">
+      <x:c r="H64" s="26" t="str">
         <x:v>After relaunch, Cmd-K opened a clean Command Palette search field. Setting AXValue to search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet; closing it returned to the main window with status Footage search opened; reopening and pressing Esc left only the Video OS Studio window. swift build --target VideoOSStudio, swift test --filter StudioCommandPaletteCommandTests 4/0, build_and_run.sh --verify, and git diff --check on ContentView.swift passed.</x:v>
       </x:c>
-      <x:c r="I64" s="13" t="str">
+      <x:c r="I64" s="11" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="48" customHeight="1">
+      <x:c r="A65" s="12" t="str">
+        <x:v>ISS-064</x:v>
+      </x:c>
+      <x:c r="B65" s="27" t="str">
+        <x:v>US-057</x:v>
+      </x:c>
+      <x:c r="C65" s="27" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="D65" s="27" t="str">
+        <x:v>macOS UX/testability</x:v>
+      </x:c>
+      <x:c r="E65" s="27" t="str">
+        <x:v>Footage Search results were visible, but result-card AX identifiers shadowed child Preview/BeatPicker/Use controls, and Command Palette opens could leave Use disabled because no clip-specific beat target was selected.</x:v>
+      </x:c>
+      <x:c r="F65" s="27" t="str">
+        <x:v>A parent FootageSearch.ResultCard identifier on the card container caused SwiftUI AX to report the thumbnail, text, Preview, beat picker, and Use button under the same ID. The global open path also initialized selectedBeatID to empty when no selected clip was available, so Use was disabled until the operator picked a beat manually.</x:v>
+      </x:c>
+      <x:c r="G65" s="27" t="str">
+        <x:v>Keep accessibility identifiers on leaf controls only, add FootageSearch.* identifiers for title/project/mode/query/search/path fields/status/result leaf controls, and initialize selectedBeatID from explicit initial beat, selected clip beat, or the first timeline beat.</x:v>
+      </x:c>
+      <x:c r="H65" s="27" t="str">
+        <x:v>After relaunch, Search Footage opened from Command Palette on ax1-participant-voices-20260401. Text query AI returned Results 2 / fallback; AX exposed FootageSearch.ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* independently; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on the in-timeline result set preview status, clicking Use on SEG_AST_610FB4A0_0001 staged 1 swapped pending operation, and Discard returned pending counts to zero. swift build --target VideoOSStudio, focused FootageSearchRunner/StudioFeedbackSession tests 15/0, footage-search Vitest 10/0, build_and_run --verify, and recent log scan passed.</x:v>
+      </x:c>
+      <x:c r="I65" s="13" t="str">
         <x:v>Fixed</x:v>
       </x:c>
     </x:row>
@@ -8545,23 +8574,43 @@
       </x:c>
     </x:row>
     <x:row r="219" ht="48" customHeight="1">
-      <x:c r="A219" s="12" t="str">
+      <x:c r="A219" s="10" t="str">
         <x:v>TL-218</x:v>
       </x:c>
-      <x:c r="B219" s="27" t="str">
+      <x:c r="B219" s="26" t="str">
         <x:v>US-054</x:v>
       </x:c>
-      <x:c r="C219" s="27" t="str">
+      <x:c r="C219" s="26" t="str">
         <x:v>Native Studio feedback Apply and Undo</x:v>
       </x:c>
-      <x:c r="D219" s="27" t="str">
+      <x:c r="D219" s="26" t="str">
         <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
       </x:c>
-      <x:c r="E219" s="27" t="str">
+      <x:c r="E219" s="26" t="str">
         <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
-      <x:c r="F219" s="13" t="str">
+      <x:c r="F219" s="11" t="str">
         <x:v>Native apply/undo pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" ht="48" customHeight="1">
+      <x:c r="A220" s="12" t="str">
+        <x:v>TL-219</x:v>
+      </x:c>
+      <x:c r="B220" s="27" t="str">
+        <x:v>US-057</x:v>
+      </x:c>
+      <x:c r="C220" s="27" t="str">
+        <x:v>Native Footage Search sheet and replacement staging</x:v>
+      </x:c>
+      <x:c r="D220" s="27" t="str">
+        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
+      </x:c>
+      <x:c r="E220" s="27" t="str">
+        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
+      </x:c>
+      <x:c r="F220" s="13" t="str">
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9034,10 +9083,10 @@
         <x:v>macOS Footage search</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/FootageSearchView.swift:6-459,228-231; apps/macos-studio/Sources/VideoOSStudioCore/FootageSearchRunner.swift:4-114; runtime/tools/footage-search-cli.ts:1-120; tests/footage-search-cli.test.ts; tests/footage-search-audio.test.ts</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/FootageSearchView.swift:6-533,44-48,144-205,246-277,338-413; apps/macos-studio/Sources/VideoOSStudioCore/FootageSearchRunner.swift:4-114; runtime/tools/footage-search-cli.ts:1-120; tests/footage-search-cli.test.ts; tests/footage-search-audio.test.ts</x:v>
       </x:c>
       <x:c r="C42" s="11" t="str">
-        <x:v>Text/visual/audio/hybrid/multimodal search controls, anchor file pickers, result score bars, preview, beat targeting, CLI-backed SearchResponse decoding, and tested replace_segment staging with segment_id candidate refs.</x:v>
+        <x:v>Text/visual/audio/hybrid/multimodal search controls, anchor file pickers, result/status display, first-beat default targeting, stable FootageSearch.* leaf AX identifiers, result score bars, preview, beat targeting, CLI-backed SearchResponse decoding, and tested replace_segment staging with segment_id candidate refs.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="48" customHeight="1">

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra7643ec7aec14448"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R5040a1af4ac44328"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Rece78bc9cd0b48bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R832469421b294a16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R052a3f4d096c4f2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb2f06df051b74a4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R568613d227414f98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Ra1121f00f05a43ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R1df6af649d4c4c9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Ree73dab6ee93449c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -439,7 +439,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 16:02 JST</x:v>
+        <x:v>2026-06-23 16:16 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -479,7 +479,7 @@
         <x:v>Issues tracked</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="220" customHeight="1">
@@ -487,7 +487,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build includes the US-057 FootageSearch.* leaf AX identifiers and first-beat default targeting, the US-054 visible FeedbackStatus.UndoButton, the US-053 Timeline/Feedback AX identifiers, the US-052 ProjectPanel compile/review identifiers plus roughCutCompileActivity label fix, the US-051 native local Source Analysis default, the US-047 Command Palette stale-search-field fix, the US-045 preview renderer duration fix, and the US-056 native Candidate Swap AX/testability fix. Focused US-057 Swift tests passed 15/0; footage-search CLI/audio Vitest passed 10/0; swift build --target VideoOSStudio passed; build_and_run.sh --verify rebuilt/applied the app from the repo root; recent log scan returned no Footage/fatal/crash matches; and full swift test previously executed 229 tests with 0 failures.</x:v>
+        <x:v>Latest code build includes Settings.TransportPicker and Settings.TransportDescription for US-066, the US-057 FootageSearch.* leaf AX identifiers and first-beat default targeting, the US-054 visible FeedbackStatus.UndoButton, the US-053 Timeline/Feedback AX identifiers, the US-052 ProjectPanel compile/review identifiers plus roughCutCompileActivity label fix, the US-051 native local Source Analysis default, the US-047 Command Palette stale-search-field fix, the US-045 preview renderer duration fix, and the US-056 native Candidate Swap AX/testability fix. Focused US-066 CodexAppServerProtocolTests passed 10/0; swift build --target VideoOSStudio passed; build_and_run.sh --verify rebuilt/applied the app from the repo root; and full swift test previously executed 229 tests with 0 failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-057 native loop verified Footage Search from Command Palette on ax1-participant-voices-20260401. Text query AI returned Results 2 / fallback, exposed independent FootageSearch.ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs for two results, defaulted BeatPicker to b01, kept Use enabled, Preview on SEG_AST_76B05D86_0001 set the current-timeline preview status, Use on SEG_AST_610FB4A0_0001 staged one replace with 1 changes pending / 1 swapped, and Discard returned pending counts to zero. Prior US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
+        <x:v>Latest US-066 native loop opened Settings, verified Settings.TransportPicker/Settings.TransportDescription in AX, switched Transport stdio -&gt; websocket -&gt; stdio, verified defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket then stdio, and deleted the test defaults key to restore the initial absent-key state. Prior US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest native checks used computer-use element targeting: CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.Title, FootageSearch.ModePicker, FootageSearch.QueryField, FootageSearch.SearchButton, FootageSearch.ResultSegment.SEG_AST_610FB4A0_0001, FootageSearch.PreviewButton.SEG_AST_76B05D86_0001, FootageSearch.BeatPicker.SEG_AST_610FB4A0_0001, FootageSearch.UseButton.SEG_AST_610FB4A0_0001, FeedbackStatus.PendingCount, and FeedbackStatus.DiscardButton. Prior Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Settings, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks remain recorded in Test Log.</x:v>
+        <x:v>Latest native checks used computer-use element targeting for Settings.TransportPicker and Settings.TransportDescription, plus picker menu options stdio, websocket, and unixSocket. Prior checks covered CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2279,16 +2279,16 @@
         <x:v>SettingsView persists preferred transport through CodexAppServerTransportPreferences; StudioViewModel resolves that preference for app-server check/start; VideoOSStudioApp builds app/studio/agent/transport/window menus; transport notifications drive StudioViewModel playback.</x:v>
       </x:c>
       <x:c r="E67" s="27" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/SettingsView.swift:6-56; apps/macos-studio/Sources/VideoOSStudio/VideoOSStudioApp.swift:365-579; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:132-136,989-1055; apps/macos-studio/Sources/VideoOSStudioCore/CodexAppServerTypes.swift:3-117; apps/macos-studio/Tests/VideoOSStudioCoreTests/CodexAppServerProtocolTests.swift:30-72</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/SettingsView.swift:6-58; apps/macos-studio/Sources/VideoOSStudio/VideoOSStudioApp.swift:365-579; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:132-136,989-1055; apps/macos-studio/Sources/VideoOSStudioCore/CodexAppServerTypes.swift:3-117; apps/macos-studio/Tests/VideoOSStudioCoreTests/CodexAppServerProtocolTests.swift:30-72</x:v>
       </x:c>
       <x:c r="F67" s="27" t="str">
         <x:v>Open Settings, switch transport picker, use menu/keyboard playback shortcuts, verify app-server check/start use the selected transport, and confirm playback state changes.</x:v>
       </x:c>
       <x:c r="G67" s="27" t="str">
-        <x:v>Runtime/menu/settings-window/pixel/inner-AX pass; picker mutation pending</x:v>
+        <x:v>Native Settings picker mutation pass</x:v>
       </x:c>
       <x:c r="H67" s="13" t="str">
-        <x:v>Coordinate-click runtime smoke advanced playhead from 00:00:00:00 to 00:00:00:15 and preserved Viewer/timeline sync. The preferred Codex transport setting now shares one storage key and launch-plan helper with StudioViewModel, so Check Codex App Server and Start Agent Session no longer ignore Settings. Settings transport option labels/description are now a Core contract consumed by SettingsView and covered by CodexAppServerProtocolTests. New build_and_run --verify launched VideoOSStudio PID 80422, menu click opened CGWindow name=Settings bounds=608x452, and AX listed Settings... plus Transport Play/Pause, Step Backward, and Step Forward menu items. Latest pass opened Settings from the app menu, captured outputs/.../us066-settings/settings-window-visible.png with the Settings window visibly over the Studio window, and recursive AX read Transport=stdio, Analysis Policy status=marlin enabled, VLM policy, Marlin Runtime=live runtime ready, Device=mps/ready, and dependency readiness rows. Focused CodexAppServerProtocolTests executed 10 tests with 0 failures; swift build and build_and_run --verify passed.</x:v>
+        <x:v>Coordinate-click runtime smoke advanced playhead from 00:00:00:00 to 00:00:00:15 and preserved Viewer/timeline sync. The preferred Codex transport setting now shares one storage key and launch-plan helper with StudioViewModel, so Check Codex App Server and Start Agent Session no longer ignore Settings. Settings transport option labels/description are now a Core contract consumed by SettingsView and covered by CodexAppServerProtocolTests. New build_and_run --verify launched VideoOSStudio PID 80422, menu click opened CGWindow name=Settings bounds=608x452, and AX listed Settings... plus Transport Play/Pause, Step Backward, and Step Forward menu items. Latest pass opened Settings from the app menu, captured outputs/.../us066-settings/settings-window-visible.png with the Settings window visibly over the Studio window, and recursive AX read Transport=stdio, Analysis Policy status=marlin enabled, VLM policy, Marlin Runtime=live runtime ready, Device=mps/ready, and dependency readiness rows. Current pass added Settings.TransportPicker and Settings.TransportDescription identifiers, used computer-use to switch Transport from stdio to websocket and back to stdio, verified defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket then stdio, deleted the test defaults key to restore the initial absent-key state, and reran CodexAppServerProtocolTests 10/0 plus swift build --target VideoOSStudio and build_and_run --verify.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4168,31 +4168,60 @@
       </x:c>
     </x:row>
     <x:row r="65" ht="48" customHeight="1">
-      <x:c r="A65" s="12" t="str">
+      <x:c r="A65" s="10" t="str">
         <x:v>ISS-064</x:v>
       </x:c>
-      <x:c r="B65" s="27" t="str">
+      <x:c r="B65" s="26" t="str">
         <x:v>US-057</x:v>
       </x:c>
-      <x:c r="C65" s="27" t="str">
+      <x:c r="C65" s="26" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="D65" s="27" t="str">
+      <x:c r="D65" s="26" t="str">
         <x:v>macOS UX/testability</x:v>
       </x:c>
-      <x:c r="E65" s="27" t="str">
+      <x:c r="E65" s="26" t="str">
         <x:v>Footage Search results were visible, but result-card AX identifiers shadowed child Preview/BeatPicker/Use controls, and Command Palette opens could leave Use disabled because no clip-specific beat target was selected.</x:v>
       </x:c>
-      <x:c r="F65" s="27" t="str">
+      <x:c r="F65" s="26" t="str">
         <x:v>A parent FootageSearch.ResultCard identifier on the card container caused SwiftUI AX to report the thumbnail, text, Preview, beat picker, and Use button under the same ID. The global open path also initialized selectedBeatID to empty when no selected clip was available, so Use was disabled until the operator picked a beat manually.</x:v>
       </x:c>
-      <x:c r="G65" s="27" t="str">
+      <x:c r="G65" s="26" t="str">
         <x:v>Keep accessibility identifiers on leaf controls only, add FootageSearch.* identifiers for title/project/mode/query/search/path fields/status/result leaf controls, and initialize selectedBeatID from explicit initial beat, selected clip beat, or the first timeline beat.</x:v>
       </x:c>
-      <x:c r="H65" s="27" t="str">
+      <x:c r="H65" s="26" t="str">
         <x:v>After relaunch, Search Footage opened from Command Palette on ax1-participant-voices-20260401. Text query AI returned Results 2 / fallback; AX exposed FootageSearch.ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* independently; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on the in-timeline result set preview status, clicking Use on SEG_AST_610FB4A0_0001 staged 1 swapped pending operation, and Discard returned pending counts to zero. swift build --target VideoOSStudio, focused FootageSearchRunner/StudioFeedbackSession tests 15/0, footage-search Vitest 10/0, build_and_run --verify, and recent log scan passed.</x:v>
       </x:c>
-      <x:c r="I65" s="13" t="str">
+      <x:c r="I65" s="11" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="48" customHeight="1">
+      <x:c r="A66" s="12" t="str">
+        <x:v>ISS-065</x:v>
+      </x:c>
+      <x:c r="B66" s="27" t="str">
+        <x:v>US-066</x:v>
+      </x:c>
+      <x:c r="C66" s="27" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="D66" s="27" t="str">
+        <x:v>macOS UX/testability</x:v>
+      </x:c>
+      <x:c r="E66" s="27" t="str">
+        <x:v>The Settings transport picker and explanatory text were visible, but lacked stable accessibility identifiers for repeatable native automation.</x:v>
+      </x:c>
+      <x:c r="F66" s="27" t="str">
+        <x:v>SettingsView rendered the Picker and description without leaf identifiers, so picker mutation proof depended on visible labels or coordinate-style targeting instead of a durable AX contract.</x:v>
+      </x:c>
+      <x:c r="G66" s="27" t="str">
+        <x:v>Added Settings.TransportPicker to the transport picker and Settings.TransportDescription to the description text, keeping the identifiers on leaf elements only.</x:v>
+      </x:c>
+      <x:c r="H66" s="27" t="str">
+        <x:v>Computer-use AX inspection exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker changed stdio to websocket, defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket, changing back returned stdio, and the test defaults key was deleted afterward. swift build --target VideoOSStudio, CodexAppServerProtocolTests 10/0, and build_and_run --verify passed.</x:v>
+      </x:c>
+      <x:c r="I66" s="13" t="str">
         <x:v>Fixed</x:v>
       </x:c>
     </x:row>
@@ -8594,23 +8623,43 @@
       </x:c>
     </x:row>
     <x:row r="220" ht="48" customHeight="1">
-      <x:c r="A220" s="12" t="str">
+      <x:c r="A220" s="10" t="str">
         <x:v>TL-219</x:v>
       </x:c>
-      <x:c r="B220" s="27" t="str">
+      <x:c r="B220" s="26" t="str">
         <x:v>US-057</x:v>
       </x:c>
-      <x:c r="C220" s="27" t="str">
+      <x:c r="C220" s="26" t="str">
         <x:v>Native Footage Search sheet and replacement staging</x:v>
       </x:c>
-      <x:c r="D220" s="27" t="str">
+      <x:c r="D220" s="26" t="str">
         <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
       </x:c>
-      <x:c r="E220" s="27" t="str">
+      <x:c r="E220" s="26" t="str">
         <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
       </x:c>
-      <x:c r="F220" s="13" t="str">
+      <x:c r="F220" s="11" t="str">
         <x:v>Native AX/pixel pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" ht="48" customHeight="1">
+      <x:c r="A221" s="12" t="str">
+        <x:v>TL-220</x:v>
+      </x:c>
+      <x:c r="B221" s="27" t="str">
+        <x:v>US-066</x:v>
+      </x:c>
+      <x:c r="C221" s="27" t="str">
+        <x:v>Native Settings transport picker mutation</x:v>
+      </x:c>
+      <x:c r="D221" s="27" t="str">
+        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
+      </x:c>
+      <x:c r="E221" s="27" t="str">
+        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
+      </x:c>
+      <x:c r="F221" s="13" t="str">
+        <x:v>Native Settings picker mutation pass</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9138,10 +9187,10 @@
         <x:v>macOS Settings and transport</x:v>
       </x:c>
       <x:c r="B47" s="27" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/SettingsView.swift:6-56; apps/macos-studio/Sources/VideoOSStudio/VideoOSStudioApp.swift:1-579; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:132-136,989-1055; apps/macos-studio/Sources/VideoOSStudioCore/CodexAppServerTypes.swift:3-117; apps/macos-studio/Tests/VideoOSStudioCoreTests/CodexAppServerProtocolTests.swift:30-72</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/SettingsView.swift:6-58; apps/macos-studio/Sources/VideoOSStudio/VideoOSStudioApp.swift:1-579; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:132-136,989-1055; apps/macos-studio/Sources/VideoOSStudioCore/CodexAppServerTypes.swift:3-117; apps/macos-studio/Tests/VideoOSStudioCoreTests/CodexAppServerProtocolTests.swift:30-72</x:v>
       </x:c>
       <x:c r="C47" s="13" t="str">
-        <x:v>Preferred Codex transport setting, shared UserDefaults-backed transport launch plan, Core-tested Settings transport option labels/description, analysis/Marlin policy display, app/studio/agent/transport menus, primary-display launch placement guard, and playback keyboard shortcuts.</x:v>
+        <x:v>Preferred Codex transport setting, shared UserDefaults-backed transport launch plan, Core-tested Settings transport option labels/description, stable Settings picker/description accessibility identifiers, analysis/Marlin policy display, app/studio/agent/transport menus, primary-display launch placement guard, and playback keyboard shortcuts.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb2f06df051b74a4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R568613d227414f98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Ra1121f00f05a43ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R1df6af649d4c4c9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Ree73dab6ee93449c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R6282d78dbcd742f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R93c63f060d414846"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R955fe60a97364275"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R3fdfe5a6aab44043"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R92b5c23446814c9d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -439,7 +439,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 16:16 JST</x:v>
+        <x:v>2026-06-23 16:25 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -479,7 +479,7 @@
         <x:v>Issues tracked</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="220" customHeight="1">
@@ -487,7 +487,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build includes Settings.TransportPicker and Settings.TransportDescription for US-066, the US-057 FootageSearch.* leaf AX identifiers and first-beat default targeting, the US-054 visible FeedbackStatus.UndoButton, the US-053 Timeline/Feedback AX identifiers, the US-052 ProjectPanel compile/review identifiers plus roughCutCompileActivity label fix, the US-051 native local Source Analysis default, the US-047 Command Palette stale-search-field fix, the US-045 preview renderer duration fix, and the US-056 native Candidate Swap AX/testability fix. Focused US-066 CodexAppServerProtocolTests passed 10/0; swift build --target VideoOSStudio passed; build_and_run.sh --verify rebuilt/applied the app from the repo root; and full swift test previously executed 229 tests with 0 failures.</x:v>
+        <x:v>Latest code build includes MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton for US-059, Settings.TransportPicker and Settings.TransportDescription for US-066, the US-057 FootageSearch.* leaf AX identifiers and first-beat default targeting, the US-054 visible FeedbackStatus.UndoButton, the US-053 Timeline/Feedback AX identifiers, the US-052 ProjectPanel compile/review identifiers plus roughCutCompileActivity label fix, the US-051 native local Source Analysis default, the US-047 Command Palette stale-search-field fix, the US-045 preview renderer duration fix, and the US-056 native Candidate Swap AX/testability fix. Focused US-059 ProjectMediaResolverTests passed 25/0; swift build --target VideoOSStudio passed; build_and_run.sh --verify rebuilt/applied the app from the repo root; and full swift test previously executed 229 tests with 0 failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-066 native loop opened Settings, verified Settings.TransportPicker/Settings.TransportDescription in AX, switched Transport stdio -&gt; websocket -&gt; stdio, verified defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket then stdio, and deleted the test defaults key to restore the initial absent-key state. Prior US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
+        <x:v>Latest US-059 native loop created a disposable media-relink project, verified MediaPanel relink controls through AX, opened and cancelled the Relink Missing Media NSOpenPanel, clicked Use Source Map Roots, observed 1 relinked file with 0 missing in the UI, confirmed source_map ready/relinkedSymlinks=1 through CLI and filesystem checks, deleted the disposable project/source root, and refreshed the app shelf. Prior US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest native checks used computer-use element targeting for Settings.TransportPicker and Settings.TransportDescription, plus picker menu options stdio, websocket, and unixSocket. Prior checks covered CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest native checks used computer-use element targeting for MediaPanel.MediaRelinkStatus, MediaPanel.RelinkMissingMediaButton, MediaPanel.UseSourceMapRootsButton, MediaPanel.ReplaceSyntheticMediaButton, ViewerDiagnosticActionButton, the Relink Missing Media NSOpenPanel, CancelButton, and ProjectShelf.us059-native-relink-smoke-20260623. Prior checks covered Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2094,19 +2094,19 @@
         <x:v>As a native Studio operator, I can audit media preview readiness, source-map coverage, broken paths, suggested roots, relink missing media, and explicitly replace generated synthetic placeholders with real source media.</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>MediaPanel renders preview readiness including synthetic preview count, source-map status, suggested roots, broken entries, relink plan/results, missing-media relink actions, and a separate Replace Synthetic Media action that passes includeSynthetic through StudioViewModel to ProjectMediaRelinker.</x:v>
+        <x:v>MediaPanel renders preview readiness including synthetic preview count, source-map status, suggested roots, broken entries, relink plan/results, missing-media relink actions, and a separate Replace Synthetic Media action that passes includeSynthetic through StudioViewModel to ProjectMediaRelinker. Relink status and the Relink Missing Media, Use Source Map Roots, and Replace Synthetic Media controls expose stable MediaPanel accessibility identifiers for native automation.</x:v>
       </x:c>
       <x:c r="E60" s="26" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:139-293; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:2213-2293; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMediaResolver.swift:130-151; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMediaRelinker.swift; apps/macos-studio/Sources/VideoOSStudioCLI/main.swift:1181-1278</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:139-300; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:2213-2293; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMediaResolver.swift:130-151; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMediaRelinker.swift; apps/macos-studio/Sources/VideoOSStudioCLI/main.swift:1181-1278</x:v>
       </x:c>
       <x:c r="F60" s="26" t="str">
-        <x:v>Run media resolver/source-map tests; run media status/source-map/relink checks on togakushi-camp and AX-1; run CLI synthetic replacement smoke; run full Swift regression and build/run verify; manually choose files through NSOpenPanel when capture/input is reliable.</x:v>
+        <x:v>Run media resolver/source-map tests; run media status/source-map/relink checks on togakushi-camp and AX-1; run CLI synthetic replacement smoke; run full Swift regression and build/run verify; open NSOpenPanel from Relink Missing Media, cancel safely, then run Use Source Map Roots on a disposable project and verify source_map/symlink output.</x:v>
       </x:c>
       <x:c r="G60" s="26" t="str">
-        <x:v>Core/CLI/runtime pass after native synthetic relink action fix; NSOpenPanel visual pending</x:v>
+        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
       </x:c>
       <x:c r="H60" s="11" t="str">
-        <x:v>MediaPanel now exposes Synthetic previews and a Replace Synthetic Media button that calls chooseAndRelinkSelectedProjectMedia(includeSynthetic: true). Default relink still ignores synthetic previews. togakushi-camp is now source map ready with 60/60 ready assets and 60 relinked symlinks; AX-1 remains source map ready with 2/2 ready assets; temp CLI smoke proved default no-op and --include-synthetic replacement. Full swift test passed 202 tests and build/run verify launched VideoOSStudio PID 42076.</x:v>
+        <x:v>MediaPanel now exposes Synthetic previews and a Replace Synthetic Media button that calls chooseAndRelinkSelectedProjectMedia(includeSynthetic: true). Default relink still ignores synthetic previews. togakushi-camp is now source map ready with 60/60 ready assets and 60 relinked symlinks; AX-1 remains source map ready with 2/2 ready assets; temp CLI smoke proved default no-op and --include-synthetic replacement. Current native pass added MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. On disposable projects/us059-native-relink-smoke-20260623, computer-use selected the project, verified ViewerDiagnosticActionButton reported 1 missing asset, confirmed MediaPanel Relink buttons enabled, opened the Relink Missing Media NSOpenPanel with the expected message and cancelled it, then clicked Use Source Map Roots. The UI changed to Relinked 1 files. 0 missing; 0 synthetic previews remain, Viewer changed from Source media unavailable to Move playhead onto a clip, media-status returned ready=1/missing=0, media-source-map-status returned source map ready coverage 1/1 and relinkedSymlinks=1, and source_map.json pointed to 02_media/relinked/AST_US059_RELINK-interview.mp4 -&gt; /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The disposable project and /tmp source root were removed and Refresh Projects removed it from the shelf. ProjectMediaResolverTests executed 25/0, swift build --target VideoOSStudio passed, diff check passed, and build_and_run --verify passed.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="48" customHeight="1">
@@ -4197,31 +4197,60 @@
       </x:c>
     </x:row>
     <x:row r="66" ht="48" customHeight="1">
-      <x:c r="A66" s="12" t="str">
+      <x:c r="A66" s="10" t="str">
         <x:v>ISS-065</x:v>
       </x:c>
-      <x:c r="B66" s="27" t="str">
+      <x:c r="B66" s="26" t="str">
         <x:v>US-066</x:v>
       </x:c>
-      <x:c r="C66" s="27" t="str">
+      <x:c r="C66" s="26" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="D66" s="27" t="str">
+      <x:c r="D66" s="26" t="str">
         <x:v>macOS UX/testability</x:v>
       </x:c>
-      <x:c r="E66" s="27" t="str">
+      <x:c r="E66" s="26" t="str">
         <x:v>The Settings transport picker and explanatory text were visible, but lacked stable accessibility identifiers for repeatable native automation.</x:v>
       </x:c>
-      <x:c r="F66" s="27" t="str">
+      <x:c r="F66" s="26" t="str">
         <x:v>SettingsView rendered the Picker and description without leaf identifiers, so picker mutation proof depended on visible labels or coordinate-style targeting instead of a durable AX contract.</x:v>
       </x:c>
-      <x:c r="G66" s="27" t="str">
+      <x:c r="G66" s="26" t="str">
         <x:v>Added Settings.TransportPicker to the transport picker and Settings.TransportDescription to the description text, keeping the identifiers on leaf elements only.</x:v>
       </x:c>
-      <x:c r="H66" s="27" t="str">
+      <x:c r="H66" s="26" t="str">
         <x:v>Computer-use AX inspection exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker changed stdio to websocket, defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket, changing back returned stdio, and the test defaults key was deleted afterward. swift build --target VideoOSStudio, CodexAppServerProtocolTests 10/0, and build_and_run --verify passed.</x:v>
       </x:c>
-      <x:c r="I66" s="13" t="str">
+      <x:c r="I66" s="11" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="48" customHeight="1">
+      <x:c r="A67" s="12" t="str">
+        <x:v>ISS-066</x:v>
+      </x:c>
+      <x:c r="B67" s="27" t="str">
+        <x:v>US-059</x:v>
+      </x:c>
+      <x:c r="C67" s="27" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="D67" s="27" t="str">
+        <x:v>macOS UX/testability</x:v>
+      </x:c>
+      <x:c r="E67" s="27" t="str">
+        <x:v>Media Relink controls were visible, but the status text and Relink/Use Source Map Roots/Replace Synthetic Media buttons did not have durable accessibility identifiers.</x:v>
+      </x:c>
+      <x:c r="F67" s="27" t="str">
+        <x:v>MediaPanel rendered these controls only by label. That made NSOpenPanel and source-map-root relink proof depend on localized text or positions rather than stable leaf identifiers.</x:v>
+      </x:c>
+      <x:c r="G67" s="27" t="str">
+        <x:v>Added MediaPanel.MediaRelinkStatus, MediaPanel.RelinkMissingMediaButton, MediaPanel.UseSourceMapRootsButton, and MediaPanel.ReplaceSyntheticMediaButton while keeping the identifiers on actionable leaf controls.</x:v>
+      </x:c>
+      <x:c r="H67" s="27" t="str">
+        <x:v>On a disposable us059-native-relink-smoke project, computer-use exposed all four identifiers, opened the Relink Missing Media NSOpenPanel, observed cancellation, clicked Use Source Map Roots, and saw MediaRelinkStatus change to Relinked 1 files with 0 missing. CLI media-status and media-source-map-status confirmed ready=1/missing=0, coverage 1/1, and one relinked symlink. ProjectMediaResolverTests 25/0, swift build --target VideoOSStudio, build_and_run --verify, and diff check passed.</x:v>
+      </x:c>
+      <x:c r="I67" s="13" t="str">
         <x:v>Fixed</x:v>
       </x:c>
     </x:row>
@@ -8643,23 +8672,43 @@
       </x:c>
     </x:row>
     <x:row r="221" ht="48" customHeight="1">
-      <x:c r="A221" s="12" t="str">
+      <x:c r="A221" s="10" t="str">
         <x:v>TL-220</x:v>
       </x:c>
-      <x:c r="B221" s="27" t="str">
+      <x:c r="B221" s="26" t="str">
         <x:v>US-066</x:v>
       </x:c>
-      <x:c r="C221" s="27" t="str">
+      <x:c r="C221" s="26" t="str">
         <x:v>Native Settings transport picker mutation</x:v>
       </x:c>
-      <x:c r="D221" s="27" t="str">
+      <x:c r="D221" s="26" t="str">
         <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
       </x:c>
-      <x:c r="E221" s="27" t="str">
+      <x:c r="E221" s="26" t="str">
         <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
       </x:c>
-      <x:c r="F221" s="13" t="str">
+      <x:c r="F221" s="11" t="str">
         <x:v>Native Settings picker mutation pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" ht="48" customHeight="1">
+      <x:c r="A222" s="12" t="str">
+        <x:v>TL-221</x:v>
+      </x:c>
+      <x:c r="B222" s="27" t="str">
+        <x:v>US-059</x:v>
+      </x:c>
+      <x:c r="C222" s="27" t="str">
+        <x:v>Native Media Relink buttons and source-map relink</x:v>
+      </x:c>
+      <x:c r="D222" s="27" t="str">
+        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
+      </x:c>
+      <x:c r="E222" s="27" t="str">
+        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
+      </x:c>
+      <x:c r="F222" s="13" t="str">
+        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9154,10 +9203,10 @@
         <x:v>macOS Media operations</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMediaResolver.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMediaRelinker.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMediaProxyPlanner.swift; apps/macos-studio/Sources/VideoOSStudioCLI/main.swift:1181-1278</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:21-642; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMediaResolver.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMediaRelinker.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMediaProxyPlanner.swift; apps/macos-studio/Sources/VideoOSStudioCLI/main.swift:1181-1278</x:v>
       </x:c>
       <x:c r="C44" s="11" t="str">
-        <x:v>Library readiness, media preview/source map, missing-media relink, explicit synthetic-to-real relink, synthetic demo media, smoke gates, proxy plans, render package, handoff, SQLite/RAG search.</x:v>
+        <x:v>Library readiness, media preview/source map, missing-media relink, explicit synthetic-to-real relink, stable MediaPanel Relink/Synthetic/Proxy/Render/Handoff/RAG accessibility identifiers, synthetic demo media, smoke gates, proxy plans, render package, handoff, SQLite/RAG search.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="48" customHeight="1">

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R6282d78dbcd742f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R93c63f060d414846"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R955fe60a97364275"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R3fdfe5a6aab44043"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R92b5c23446814c9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R266913a4af9e48e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R0992a9d3c40b4972"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Re142897a1af54709"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R53ae27900de5454a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R2b1e85e843ca49df"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -439,7 +439,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 16:25 JST</x:v>
+        <x:v>2026-06-23 16:35 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -479,7 +479,7 @@
         <x:v>Issues tracked</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="220" customHeight="1">
@@ -487,7 +487,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build includes MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton for US-059, Settings.TransportPicker and Settings.TransportDescription for US-066, the US-057 FootageSearch.* leaf AX identifiers and first-beat default targeting, the US-054 visible FeedbackStatus.UndoButton, the US-053 Timeline/Feedback AX identifiers, the US-052 ProjectPanel compile/review identifiers plus roughCutCompileActivity label fix, the US-051 native local Source Analysis default, the US-047 Command Palette stale-search-field fix, the US-045 preview renderer duration fix, and the US-056 native Candidate Swap AX/testability fix. Focused US-059 ProjectMediaResolverTests passed 25/0; swift build --target VideoOSStudio passed; build_and_run.sh --verify rebuilt/applied the app from the repo root; and full swift test previously executed 229 tests with 0 failures.</x:v>
+        <x:v>Latest code build includes MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.&lt;assetID&gt; for US-060, plus the prior US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix. Focused US-060 smoke/resolver tests passed 30/0; swift build --target VideoOSStudio passed; build_and_run.sh --verify rebuilt/applied the app from the repo root; and full swift test previously executed 229 tests with 0 failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-059 native loop created a disposable media-relink project, verified MediaPanel relink controls through AX, opened and cancelled the Relink Missing Media NSOpenPanel, clicked Use Source Map Roots, observed 1 relinked file with 0 missing in the UI, confirmed source_map ready/relinkedSymlinks=1 through CLI and filesystem checks, deleted the disposable project/source root, and refreshed the app shelf. Prior US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
+        <x:v>Latest US-060 native loop created disposable synthetic and proxy media projects, verified MediaPanel Synthetic/Proxy/Smoke controls through AX, clicked Build Demo Media, clicked Build Proxies, clicked Run Studio Smoke, confirmed UI status transitions, verified source_map coverage and proxy pending=0 through CLI, checked generated H.264/AAC media with ffprobe, and deleted the disposable projects. Prior US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest native checks used computer-use element targeting for MediaPanel.MediaRelinkStatus, MediaPanel.RelinkMissingMediaButton, MediaPanel.UseSourceMapRootsButton, MediaPanel.ReplaceSyntheticMediaButton, ViewerDiagnosticActionButton, the Relink Missing Media NSOpenPanel, CancelButton, and ProjectShelf.us059-native-relink-smoke-20260623. Prior checks covered Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest native checks used computer-use element targeting for ProjectShelf.us060-native-synthetic-smoke-20260623, ProjectShelf.us060-native-proxy-smoke-20260623, MediaPanel.SyntheticMediaStatus, MediaPanel.BuildDemoMediaButton, MediaPanel.StudioSyntheticSmokeStatus, MediaPanel.RunStudioSmokeButton, MediaPanel.StudioAcceptanceSmokeStatus, MediaPanel.RunAcceptanceSmokeButton, MediaPanel.MediaProxyOperationStatus, MediaPanel.BuildProxiesButton, MediaPanel.MediaProxyEmptyState, and MediaPanel.MediaProxyPlanItem.AST_US060_PROXY. Prior checks covered MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2120,19 +2120,19 @@
         <x:v>As a native Studio operator, I can build synthetic demo media, run synthetic/acceptance smoke tests, and build pending preview proxies for unsupported sources.</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>MediaPanel buttons call synthetic media builder, synthetic smoke, acceptance smoke, and media proxy builder; core planners produce ffmpeg/proxy commands and smoke summaries.</x:v>
+        <x:v>MediaPanel buttons call synthetic media builder, synthetic smoke, acceptance smoke, and media proxy builder; core planners produce ffmpeg/proxy commands and smoke summaries. The Synthetic/Proxy/Smoke status texts, action buttons, proxy empty state, and proxy plan rows expose stable MediaPanel accessibility identifiers for native verification.</x:v>
       </x:c>
       <x:c r="E61" s="26" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:294-407; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:2177-2210,2315-2405; apps/macos-studio/Sources/VideoOSStudioCore/ProjectSyntheticMediaBuilder.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMediaProxyPlanner.swift; apps/macos-studio/Sources/VideoOSStudioCLI/main.swift:1284-1379,2068-2140</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:333-453; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:2177-2210,2315-2405; apps/macos-studio/Sources/VideoOSStudioCore/ProjectSyntheticMediaBuilder.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMediaProxyPlanner.swift; apps/macos-studio/Sources/VideoOSStudioCLI/main.swift:1284-1379,2068-2140</x:v>
       </x:c>
       <x:c r="F61" s="26" t="str">
-        <x:v>Run synthetic/proxy/smoke tests; run studio-synthetic-smoke and studio-acceptance-smoke through CLI; run a temp unsupported-source proxy build; manually click Media tab smoke/proxy buttons when AX/capture input is reliable.</x:v>
+        <x:v>Run synthetic/proxy/smoke tests; run studio-synthetic-smoke and studio-acceptance-smoke through CLI; run a temp unsupported-source proxy build; click Media tab Build Demo Media, Build Proxies, and Run Studio Smoke through native AX controls.</x:v>
       </x:c>
       <x:c r="G61" s="26" t="str">
-        <x:v>Runtime/CLI pass; native Media button visual pending</x:v>
+        <x:v>Native synthetic/proxy/smoke button pass</x:v>
       </x:c>
       <x:c r="H61" s="11" t="str">
-        <x:v>AX-1 media-synthetic-plan reports synthetic media ready with 2 existing demo files and media-proxy-plan pending=0. studio-synthetic-smoke passed with source map ready, mediaReady=1, render packaged, packet verified, indexDocuments=5, studioScore=9/9. studio-acceptance-smoke passed Codex App Server handshake plus the same render/package/editor-packet loop. A temp camera.avi proxy smoke moved media-status from proxyNeeded=1 to proxy-video ready=1 after media-proxy-build created AST_PROXY_SMOKE.mp4. Focused Swift tests executed 16 tests with 0 failures; full swift test passed 202 tests; build_and_run verify launched VideoOSStudio PID 68107.</x:v>
+        <x:v>AX-1 media-synthetic-plan reports synthetic media ready with 2 existing demo files and media-proxy-plan pending=0. studio-synthetic-smoke passed with source map ready, mediaReady=1, render packaged, packet verified, indexDocuments=5, studioScore=9/9. studio-acceptance-smoke passed Codex App Server handshake plus the same render/package/editor-packet loop. A temp camera.avi proxy smoke moved media-status from proxyNeeded=1 to proxy-video ready=1 after media-proxy-build created AST_PROXY_SMOKE.mp4. Current native pass added stable MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.&lt;assetID&gt; identifiers. Computer-use selected us060-native-synthetic-smoke-20260623, clicked Build Demo Media, and saw Built 1, skipped 0, mapped 1; CLI returned ready=1/missing=0, source-map coverage 1/1, and ffprobe reported h264 1280x720 5.000000s. Computer-use selected us060-native-proxy-smoke-20260623, saw 1 preview proxies ready to build plus MediaProxyPlanItem.AST_US060_PROXY, clicked Build Proxies, and saw Built 1 preview proxies; CLI returned proxyPlans=0/pending=0 and ffprobe reported an H.264/AAC proxy. Run Studio Smoke was also clicked natively and returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused Swift tests executed 30 tests with 0 failures; swift build --target VideoOSStudio and build_and_run --verify passed.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="48" customHeight="1">
@@ -4226,31 +4226,60 @@
       </x:c>
     </x:row>
     <x:row r="67" ht="48" customHeight="1">
-      <x:c r="A67" s="12" t="str">
+      <x:c r="A67" s="10" t="str">
         <x:v>ISS-066</x:v>
       </x:c>
-      <x:c r="B67" s="27" t="str">
+      <x:c r="B67" s="26" t="str">
         <x:v>US-059</x:v>
       </x:c>
-      <x:c r="C67" s="27" t="str">
+      <x:c r="C67" s="26" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="D67" s="27" t="str">
+      <x:c r="D67" s="26" t="str">
         <x:v>macOS UX/testability</x:v>
       </x:c>
-      <x:c r="E67" s="27" t="str">
+      <x:c r="E67" s="26" t="str">
         <x:v>Media Relink controls were visible, but the status text and Relink/Use Source Map Roots/Replace Synthetic Media buttons did not have durable accessibility identifiers.</x:v>
       </x:c>
-      <x:c r="F67" s="27" t="str">
+      <x:c r="F67" s="26" t="str">
         <x:v>MediaPanel rendered these controls only by label. That made NSOpenPanel and source-map-root relink proof depend on localized text or positions rather than stable leaf identifiers.</x:v>
       </x:c>
-      <x:c r="G67" s="27" t="str">
+      <x:c r="G67" s="26" t="str">
         <x:v>Added MediaPanel.MediaRelinkStatus, MediaPanel.RelinkMissingMediaButton, MediaPanel.UseSourceMapRootsButton, and MediaPanel.ReplaceSyntheticMediaButton while keeping the identifiers on actionable leaf controls.</x:v>
       </x:c>
-      <x:c r="H67" s="27" t="str">
+      <x:c r="H67" s="26" t="str">
         <x:v>On a disposable us059-native-relink-smoke project, computer-use exposed all four identifiers, opened the Relink Missing Media NSOpenPanel, observed cancellation, clicked Use Source Map Roots, and saw MediaRelinkStatus change to Relinked 1 files with 0 missing. CLI media-status and media-source-map-status confirmed ready=1/missing=0, coverage 1/1, and one relinked symlink. ProjectMediaResolverTests 25/0, swift build --target VideoOSStudio, build_and_run --verify, and diff check passed.</x:v>
       </x:c>
-      <x:c r="I67" s="13" t="str">
+      <x:c r="I67" s="11" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="48" customHeight="1">
+      <x:c r="A68" s="12" t="str">
+        <x:v>ISS-067</x:v>
+      </x:c>
+      <x:c r="B68" s="27" t="str">
+        <x:v>US-060</x:v>
+      </x:c>
+      <x:c r="C68" s="27" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="D68" s="27" t="str">
+        <x:v>macOS UX/testability</x:v>
+      </x:c>
+      <x:c r="E68" s="27" t="str">
+        <x:v>Synthetic demo media, smoke, and proxy controls were runnable, but their MediaPanel controls could not be targeted repeatably by native automation.</x:v>
+      </x:c>
+      <x:c r="F68" s="27" t="str">
+        <x:v>The Synthetic Demo Media and Proxy Transcode Plan sections rendered status text, action buttons, proxy empty state, and proxy plan rows by visible text only. That made the final native verification depend on labels or panel position instead of durable leaf identifiers.</x:v>
+      </x:c>
+      <x:c r="G68" s="27" t="str">
+        <x:v>Added stable MediaPanel identifiers for synthetic status/build, studio smoke status/run, acceptance smoke status/run, proxy operation status/build, proxy empty state, and proxy plan items keyed by asset id.</x:v>
+      </x:c>
+      <x:c r="H68" s="27" t="str">
+        <x:v>Computer-use exposed the new identifiers, clicked Build Demo Media on us060-native-synthetic-smoke-20260623 and observed Built 1, skipped 0, mapped 1, clicked Build Proxies on us060-native-proxy-smoke-20260623 and observed Built 1 preview proxies, and clicked Run Studio Smoke until it reported Synthetic studio smoke passed. CLI media-status/source-map/proxy-plan and ffprobe confirmed ready media, coverage 1/1, pending=0, and valid H.264/AAC outputs. Focused Swift smoke/resolver tests 30/0, swift build --target VideoOSStudio, build_and_run --verify, and diff check passed.</x:v>
+      </x:c>
+      <x:c r="I68" s="13" t="str">
         <x:v>Fixed</x:v>
       </x:c>
     </x:row>
@@ -8692,23 +8721,43 @@
       </x:c>
     </x:row>
     <x:row r="222" ht="48" customHeight="1">
-      <x:c r="A222" s="12" t="str">
+      <x:c r="A222" s="10" t="str">
         <x:v>TL-221</x:v>
       </x:c>
-      <x:c r="B222" s="27" t="str">
+      <x:c r="B222" s="26" t="str">
         <x:v>US-059</x:v>
       </x:c>
-      <x:c r="C222" s="27" t="str">
+      <x:c r="C222" s="26" t="str">
         <x:v>Native Media Relink buttons and source-map relink</x:v>
       </x:c>
-      <x:c r="D222" s="27" t="str">
+      <x:c r="D222" s="26" t="str">
         <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
       </x:c>
-      <x:c r="E222" s="27" t="str">
+      <x:c r="E222" s="26" t="str">
         <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
       </x:c>
-      <x:c r="F222" s="13" t="str">
+      <x:c r="F222" s="11" t="str">
         <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" ht="48" customHeight="1">
+      <x:c r="A223" s="12" t="str">
+        <x:v>TL-222</x:v>
+      </x:c>
+      <x:c r="B223" s="27" t="str">
+        <x:v>US-060</x:v>
+      </x:c>
+      <x:c r="C223" s="27" t="str">
+        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
+      </x:c>
+      <x:c r="D223" s="27" t="str">
+        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
+      </x:c>
+      <x:c r="E223" s="27" t="str">
+        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
+      </x:c>
+      <x:c r="F223" s="13" t="str">
+        <x:v>Native synthetic/proxy/smoke button pass</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9206,7 +9255,7 @@
         <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:21-642; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMediaResolver.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMediaRelinker.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMediaProxyPlanner.swift; apps/macos-studio/Sources/VideoOSStudioCLI/main.swift:1181-1278</x:v>
       </x:c>
       <x:c r="C44" s="11" t="str">
-        <x:v>Library readiness, media preview/source map, missing-media relink, explicit synthetic-to-real relink, stable MediaPanel Relink/Synthetic/Proxy/Render/Handoff/RAG accessibility identifiers, synthetic demo media, smoke gates, proxy plans, render package, handoff, SQLite/RAG search.</x:v>
+        <x:v>Library readiness, media preview/source map, missing-media relink, explicit synthetic-to-real relink, stable MediaPanel Relink/Synthetic/Proxy/Smoke/Render/Handoff/RAG accessibility identifiers, synthetic demo media, smoke gates, proxy plans and proxy plan row IDs, render package, handoff, SQLite/RAG search.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="48" customHeight="1">

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R266913a4af9e48e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R0992a9d3c40b4972"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Re142897a1af54709"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R53ae27900de5454a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R2b1e85e843ca49df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5f5946456d034c61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rc687e53f810c4a20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Re53ce6700bc641a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R04b47cf067664435"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R376f4bf1edca4ee1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -479,7 +479,7 @@
         <x:v>Issues tracked</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="220" customHeight="1">
@@ -487,7 +487,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build includes MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.&lt;assetID&gt; for US-060, plus the prior US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix. Focused US-060 smoke/resolver tests passed 30/0; swift build --target VideoOSStudio passed; build_and_run.sh --verify rebuilt/applied the app from the repo root; and full swift test previously executed 229 tests with 0 failures.</x:v>
+        <x:v>Latest code build includes ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, ProjectInitializer.CancelButton, repo-root source-folder panel startup, and explicit Project creation status text for US-046, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix. Latest native build/run verified VideoOSStudio from the repo root.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-060 native loop created disposable synthetic and proxy media projects, verified MediaPanel Synthetic/Proxy/Smoke controls through AX, clicked Build Demo Media, clicked Build Proxies, clicked Run Studio Smoke, confirmed UI status transitions, verified source_map coverage and proxy pending=0 through CLI, checked generated H.264/AAC media with ffprobe, and deleted the disposable projects. Prior US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
+        <x:v>Latest US-046 native loop created disposable us046-native-create-20260623 from us046-native-source-20260623, verified New Project alert identifiers through AX, opened Choose Source Media Folder at the repo root, linked source media, confirmed ProjectShelf.us046-native-create-20260623 intent_pending, Project tab creation status, project_state.yaml intent_pending, 02_media/source symlink target, and H.264/AAC source media through ffprobe. Prior US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest native checks used computer-use element targeting for ProjectShelf.us060-native-synthetic-smoke-20260623, ProjectShelf.us060-native-proxy-smoke-20260623, MediaPanel.SyntheticMediaStatus, MediaPanel.BuildDemoMediaButton, MediaPanel.StudioSyntheticSmokeStatus, MediaPanel.RunStudioSmokeButton, MediaPanel.StudioAcceptanceSmokeStatus, MediaPanel.RunAcceptanceSmokeButton, MediaPanel.MediaProxyOperationStatus, MediaPanel.BuildProxiesButton, MediaPanel.MediaProxyEmptyState, and MediaPanel.MediaProxyPlanItem.AST_US060_PROXY. Prior checks covered MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest native checks used computer-use element targeting for ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, ProjectInitializer.CancelButton, OKButton/Link Source in the source-folder panel, ProjectShelf.us046-native-create-20260623, and Project tab Source Analysis/readiness text for the created project. Prior checks covered MediaPanel Synthetic/Proxy/Smoke controls, MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1756,19 +1756,19 @@
         <x:v>As a native Studio operator, I can refresh project state, create a project from a source folder, and switch between project shelves without losing the selected project context.</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>ProjectShelf exposes New Project, project state chips, and refresh; StudioViewModel scans projects, prompts for project id/source folder, initializes through ProjectInitializer, and reloads timeline/status. ProjectInitializer trims user-entered IDs, rejects reserved/invalid/existing projects, rejects missing source folders before running init-project, parses Next step output, reports subprocess failures, and reports missing project directories after a nominally successful run.</x:v>
+        <x:v>ProjectShelf exposes New Project, project state chips, and refresh; StudioViewModel scans projects, prompts for project id/source folder, initializes through ProjectInitializer, and reloads timeline/status. ProjectInitializer trims user-entered IDs, rejects reserved/invalid/existing projects, rejects missing source folders before running init-project, parses Next step output, reports subprocess failures, and reports missing project directories after a nominally successful run. The New Project alert exposes durable field/button identifiers, the source-folder panel starts from the repository root, and Project creation status is rendered as explicit inspectable text in the Project State section.</x:v>
       </x:c>
       <x:c r="E47" s="26" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/ContentView.swift:257-304; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:299-479; apps/macos-studio/Sources/VideoOSStudioCore/ProjectInitializer.swift:1-159; apps/macos-studio/Tests/VideoOSStudioCoreTests/ProjectInitializerTests.swift:1-118</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/ContentView.swift:257-304; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:299-479; apps/macos-studio/Sources/VideoOSStudio/ProjectInspectorViews.swift:6-31; apps/macos-studio/Sources/VideoOSStudioCore/ProjectInitializer.swift:1-159; apps/macos-studio/Tests/VideoOSStudioCoreTests/ProjectInitializerTests.swift:1-118</x:v>
       </x:c>
       <x:c r="F47" s="26" t="str">
         <x:v>Run project scanner/initializer tests, confirm command/menu wiring, then manually create/switch a project in native UI.</x:v>
       </x:c>
       <x:c r="G47" s="26" t="str">
-        <x:v>Project switch runtime plus Core creation-contract pass; NSOpenPanel visual pending</x:v>
+        <x:v>Native project creation and switch pass</x:v>
       </x:c>
       <x:c r="H47" s="11" t="str">
-        <x:v>AX/click smoke switched between ax1, fumoto-growth, and lively-alt-vol5; screenshots show the selected project reloads Viewer, timeline sequence, preview contract, and project chip. ProjectInitializerTests now execute 4 tests with 0 failures, covering trimmed user IDs, --source-dir command construction, reserved/invalid/existing projects, missing source folders, injected successful init with source symlink and Next step parsing, subprocess failure, and missing project directory after nominal success. Full swift test executed 222 tests with 0 failures and swift build --target VideoOSStudio passed. New Project NSOpenPanel visual creation remains unpromoted pending reliable UI capture/manual pass.</x:v>
+        <x:v>AX/click smoke switched between ax1, fumoto-growth, and lively-alt-vol5; screenshots show the selected project reloads Viewer, timeline sequence, preview contract, and project chip. Latest native pass clicked ProjectShelf.NewProject, confirmed ProjectInitializer.ProjectIDField plus ProjectInitializer.CreateButton/CancelButton, entered us046-native-create-20260623, and opened the Choose Source Media Folder NSOpenPanel from the repo root with message text naming 02_media/source and OKButton labelled Link Source. Selecting us046-native-source-20260623 created ProjectShelf.us046-native-create-20260623, selected that project, showed state intent_pending, Source Analysis ready for 1 linked source, and Project creation: Created us046-native-create-20260623 and linked source media. Filesystem verification showed project_state.yaml project_id=us046-native-create-20260623/current_state=intent_pending, 02_media/source symlinked to /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, and ffprobe reported h264 160x90 1.000000s plus AAC 1.000000s. ProjectInitializerTests cover trimmed IDs, --source-dir command construction, reserved/invalid/existing projects, missing source folders, successful init with source symlink and Next step parsing, subprocess failure, and missing project directory after nominal success.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="48" customHeight="1">
@@ -3088,7 +3088,7 @@
         <x:v>Marked each macOS story with Core tests pass / UI pending or runtime pending instead of claiming Pass; next loop should run native manual/automation passes story by story and promote statuses only with evidence.</x:v>
       </x:c>
       <x:c r="H27" s="26" t="str">
-        <x:v>Current evidence: swift test passed 223 tests; build/run verify passed in the latest Viewer loop; US-045 has runtime/AVKit first-frame and latest-output evidence with visual confirmation pending, US-046 has project-switch runtime plus ProjectInitializer creation/failure contract tests but NSOpenPanel creation remains unpromoted, US-047 has native Command Palette keyboard/top-bar pass, US-048 has native Agent panel Check/Start/Stop lifecycle pass, US-049 has native read-only Status job plus approval prompt/rejection gate pass while approved write remains intentionally pending, US-050 has native Project tab readiness/action queue plus Copy-to-pasteboard pass while destructive Open/Start &amp; Run actions remain pending, US-051 has native local Source Analysis click evidence on a disposable one-source project, US-052 has native Compile Rough Cut and Apply Review Patch click evidence on a disposable project plus marker/index/library verification, US-053 has native timeline marker/audio/waveform/context-menu approve/reject/swap/search evidence, and US-054 has native disposable apply/undo evidence plus promote core/enable coverage. Remaining macOS stories are explicitly not complete.</x:v>
+        <x:v>Current evidence: swift test passed 223 tests; build/run verify passed in the latest Viewer loop; US-045 has runtime/AVKit first-frame and latest-output evidence with visual confirmation pending, US-046 has project-switch runtime plus native New Project/NSOpenPanel creation and ProjectInitializer creation/failure contract tests, US-047 has native Command Palette keyboard/top-bar pass, US-048 has native Agent panel Check/Start/Stop lifecycle pass, US-049 has native read-only Status job plus approval prompt/rejection gate pass while approved write remains intentionally pending, US-050 has native Project tab readiness/action queue plus Copy-to-pasteboard pass while destructive Open/Start &amp; Run actions remain pending, US-051 has native local Source Analysis click evidence on a disposable one-source project, US-052 has native Compile Rough Cut and Apply Review Patch click evidence on a disposable project plus marker/index/library verification, US-053 has native timeline marker/audio/waveform/context-menu approve/reject/swap/search evidence, and US-054 has native disposable apply/undo evidence plus promote core/enable coverage. Remaining macOS stories are explicitly not complete.</x:v>
       </x:c>
       <x:c r="I27" s="11" t="str">
         <x:v>Open</x:v>
@@ -4255,31 +4255,60 @@
       </x:c>
     </x:row>
     <x:row r="68" ht="48" customHeight="1">
-      <x:c r="A68" s="12" t="str">
+      <x:c r="A68" s="10" t="str">
         <x:v>ISS-067</x:v>
       </x:c>
-      <x:c r="B68" s="27" t="str">
+      <x:c r="B68" s="26" t="str">
         <x:v>US-060</x:v>
       </x:c>
-      <x:c r="C68" s="27" t="str">
+      <x:c r="C68" s="26" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="D68" s="27" t="str">
+      <x:c r="D68" s="26" t="str">
         <x:v>macOS UX/testability</x:v>
       </x:c>
-      <x:c r="E68" s="27" t="str">
+      <x:c r="E68" s="26" t="str">
         <x:v>Synthetic demo media, smoke, and proxy controls were runnable, but their MediaPanel controls could not be targeted repeatably by native automation.</x:v>
       </x:c>
-      <x:c r="F68" s="27" t="str">
+      <x:c r="F68" s="26" t="str">
         <x:v>The Synthetic Demo Media and Proxy Transcode Plan sections rendered status text, action buttons, proxy empty state, and proxy plan rows by visible text only. That made the final native verification depend on labels or panel position instead of durable leaf identifiers.</x:v>
       </x:c>
-      <x:c r="G68" s="27" t="str">
+      <x:c r="G68" s="26" t="str">
         <x:v>Added stable MediaPanel identifiers for synthetic status/build, studio smoke status/run, acceptance smoke status/run, proxy operation status/build, proxy empty state, and proxy plan items keyed by asset id.</x:v>
       </x:c>
-      <x:c r="H68" s="27" t="str">
+      <x:c r="H68" s="26" t="str">
         <x:v>Computer-use exposed the new identifiers, clicked Build Demo Media on us060-native-synthetic-smoke-20260623 and observed Built 1, skipped 0, mapped 1, clicked Build Proxies on us060-native-proxy-smoke-20260623 and observed Built 1 preview proxies, and clicked Run Studio Smoke until it reported Synthetic studio smoke passed. CLI media-status/source-map/proxy-plan and ffprobe confirmed ready media, coverage 1/1, pending=0, and valid H.264/AAC outputs. Focused Swift smoke/resolver tests 30/0, swift build --target VideoOSStudio, build_and_run --verify, and diff check passed.</x:v>
       </x:c>
-      <x:c r="I68" s="13" t="str">
+      <x:c r="I68" s="11" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="48" customHeight="1">
+      <x:c r="A69" s="12" t="str">
+        <x:v>ISS-068</x:v>
+      </x:c>
+      <x:c r="B69" s="27" t="str">
+        <x:v>US-046</x:v>
+      </x:c>
+      <x:c r="C69" s="27" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="D69" s="27" t="str">
+        <x:v>macOS UX/testability</x:v>
+      </x:c>
+      <x:c r="E69" s="27" t="str">
+        <x:v>New Project creation could only be proven through visible labels and last Finder state, making the native NSOpenPanel path fragile.</x:v>
+      </x:c>
+      <x:c r="F69" s="27" t="str">
+        <x:v>The project ID alert used plain AppKit controls without stable accessibility identifiers, the source-folder panel inherited the user's last Finder location, and the Project creation row used LabeledContent that was easy to collapse in AX output.</x:v>
+      </x:c>
+      <x:c r="G69" s="27" t="str">
+        <x:v>Added ProjectInitializer.ProjectIDField/CreateButton/CancelButton, defaulted the source-folder NSOpenPanel to the repository root, and rendered Project creation as explicit status text in the Project State section.</x:v>
+      </x:c>
+      <x:c r="H69" s="27" t="str">
+        <x:v>Computer-use exposed the new alert identifiers, opened Choose Source Media Folder from the repo root, selected us046-native-source-20260623, and created us046-native-create-20260623. The shelf showed ProjectShelf.us046-native-create-20260623 intent_pending, the Project tab showed Project creation: Created us046-native-create-20260623 and linked source media, project_state.yaml recorded current_state=intent_pending, 02_media/source linked to the selected source folder, and ffprobe confirmed the linked H.264/AAC source clip.</x:v>
+      </x:c>
+      <x:c r="I69" s="13" t="str">
         <x:v>Fixed</x:v>
       </x:c>
     </x:row>
@@ -8741,23 +8770,43 @@
       </x:c>
     </x:row>
     <x:row r="223" ht="48" customHeight="1">
-      <x:c r="A223" s="12" t="str">
+      <x:c r="A223" s="10" t="str">
         <x:v>TL-222</x:v>
       </x:c>
-      <x:c r="B223" s="27" t="str">
+      <x:c r="B223" s="26" t="str">
         <x:v>US-060</x:v>
       </x:c>
-      <x:c r="C223" s="27" t="str">
+      <x:c r="C223" s="26" t="str">
         <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
       </x:c>
-      <x:c r="D223" s="27" t="str">
+      <x:c r="D223" s="26" t="str">
         <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
       </x:c>
-      <x:c r="E223" s="27" t="str">
+      <x:c r="E223" s="26" t="str">
         <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
       </x:c>
-      <x:c r="F223" s="13" t="str">
+      <x:c r="F223" s="11" t="str">
         <x:v>Native synthetic/proxy/smoke button pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="48" customHeight="1">
+      <x:c r="A224" s="12" t="str">
+        <x:v>TL-223</x:v>
+      </x:c>
+      <x:c r="B224" s="27" t="str">
+        <x:v>US-046</x:v>
+      </x:c>
+      <x:c r="C224" s="27" t="str">
+        <x:v>Native New Project from Source</x:v>
+      </x:c>
+      <x:c r="D224" s="27" t="str">
+        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
+      </x:c>
+      <x:c r="E224" s="27" t="str">
+        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
+      </x:c>
+      <x:c r="F224" s="13" t="str">
+        <x:v>Native project creation/NSOpenPanel pass</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9131,10 +9180,10 @@
         <x:v>macOS app shell and project shelf</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/ContentView.swift:5-125; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:299-479</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/ContentView.swift:5-125; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:299-479; apps/macos-studio/Sources/VideoOSStudio/ProjectInspectorViews.swift:6-31</x:v>
       </x:c>
       <x:c r="C33" s="11" t="str">
-        <x:v>Native shell wires top bar, project shelf, command palette, swap/search sheets, project scan, project creation, selection, and status refresh.</x:v>
+        <x:v>Native shell wires top bar, project shelf, command palette, swap/search sheets, project scan, project creation, selection, status refresh, stable New Project alert identifiers, repo-root source-folder panel start, and explicit Project creation status text.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="48" customHeight="1">

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5f5946456d034c61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rc687e53f810c4a20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Re53ce6700bc641a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R04b47cf067664435"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R376f4bf1edca4ee1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rbc5bfae1cbe14d22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rd287e3a23407496b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R9b3d092ea8b044fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R09e7eb3e7e344842"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R58dc1545115145e3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build includes ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, ProjectInitializer.CancelButton, repo-root source-folder panel startup, and explicit Project creation status text for US-046, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix. Latest native build/run verified VideoOSStudio from the repo root.</x:v>
+        <x:v>Latest code build includes ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, ProjectInitializer.CancelButton, repo-root source-folder panel startup, explicit Project creation status text for US-046, and MediaPanel.BuildAudioStoryGraphButton / MediaPanel.AudioStoryGraphCommandLine for US-062, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix. Latest native build/run verified VideoOSStudio from the repo root.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-046 native loop created disposable us046-native-create-20260623 from us046-native-source-20260623, verified New Project alert identifiers through AX, opened Choose Source Media Folder at the repo root, linked source media, confirmed ProjectShelf.us046-native-create-20260623 intent_pending, Project tab creation status, project_state.yaml intent_pending, 02_media/source symlink target, and H.264/AAC source media through ffprobe. Prior US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
+        <x:v>Latest US-062 native loop created disposable projects/us062-audio-story-smoke from the audio-story fixture with graph/index removed, clicked MediaPanel.BuildAudioStoryGraphButton, observed Building audio story graph... then Audio story graph built and indexed: 3 nodes / 7 docs, verified graph coverage ready, index-status searchDocuments=7, library-status ragReady=true/audioReady=true/audioStoryNodes=3, and removed the disposable project after Refresh Projects. Prior US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest native checks used computer-use element targeting for ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, ProjectInitializer.CancelButton, OKButton/Link Source in the source-folder panel, ProjectShelf.us046-native-create-20260623, and Project tab Source Analysis/readiness text for the created project. Prior checks covered MediaPanel Synthetic/Proxy/Smoke controls, MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest native checks used computer-use element targeting for ProjectShelf.us062-audio-story-smoke, MediaPanel.BuildAudioStoryGraphButton, and MediaPanel.AudioStoryGraphCommandLine; the visual state showed Story nodes 0 before the click, disabled Building Audio Graph during execution, and Story nodes 3 plus SQLite available 7 after completion. Prior checks covered ProjectShelf.NewProject, ProjectInitializer fields/buttons, source-folder panel Link Source, MediaPanel Synthetic/Proxy/Smoke controls, MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2178,13 +2178,13 @@
         <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:21-50; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:2623-2665; apps/macos-studio/Sources/VideoOSStudioCore/ProjectAudioStoryGraphRunPlan.swift; scripts/build-audio-story-graph.ts; runtime/artifacts/audio-story-project-builder.ts; runtime/artifacts/p2-audio-story-graph.ts; apps/macos-studio/Sources/VideoOSStudioCore/ProjectSQLiteIndex.swift:400-452</x:v>
       </x:c>
       <x:c r="F63" s="26" t="str">
-        <x:v>Run ProjectAudioStoryGraphRunPlanTests; run build-audio-story-graph dry-run and audio-story-run on a project with transcript, BGM, and audio-event artifacts; click native Studio &gt; Build Audio Story Graph; verify audio_story_graph.json mtime, SQLite search index refresh, library readiness, audio-map cues, build/test, and app relaunch.</x:v>
+        <x:v>Run ProjectAudioStoryGraphRunPlanTests; run build-audio-story-graph dry-run and audio-story-run on a project with transcript, BGM, and audio-event artifacts; click native MediaPanel Build Audio Story Graph; verify audio_story_graph.json contents, SQLite search index refresh, library readiness, audio-map cues, build/test, app relaunch, and cleanup of disposable projects.</x:v>
       </x:c>
       <x:c r="G63" s="26" t="str">
-        <x:v>Native menu/CLI/runtime pass; MediaPanel button AX ID added; pixel capture pending</x:v>
+        <x:v>Native MediaPanel audio graph pass</x:v>
       </x:c>
       <x:c r="H63" s="11" t="str">
-        <x:v>The outputs/019eee15.../us062-audio-story-smoke fixture still plans/runs successfully with 3 nodes, 1 edge, searchDocuments=7, and audioStoryNodes=3. A native Studio menu click on Build Audio Story Graph executed the same selected-project path for ax1-participant-voices-20260401: audio_story_graph.json and project_index.sqlite were both updated at 2026-06-23 08:11:59 JST, index-status reports 492 search documents, library-status reports audioReady=true and audioStoryNodes=239, and audio-map now surfaces audio-story cues. MediaPanel.BuildAudioStoryGraphButton and MediaPanel.AudioStoryGraphCommandLine accessibility identifiers were added. Focused ProjectAudioStoryGraphRunPlanTests/ProjectAudioTimelineMapTests/ProjectSQLiteIndexTests executed 6 tests with 0 failures, swift build --target VideoOSStudio passed, and build_and_run --verify relaunched VideoOSStudio PID 94629. Pixel screenshot capture remains unreliable in this desktop session.</x:v>
+        <x:v>The outputs/019eee15.../us062-audio-story-smoke fixture still plans/runs successfully with 3 nodes, 1 edge, searchDocuments=7, and audioStoryNodes=3. A native Studio menu click on Build Audio Story Graph executed the same selected-project path for ax1-participant-voices-20260401: audio_story_graph.json and project_index.sqlite were both updated at 2026-06-23 08:11:59 JST, index-status reports 492 search documents, library-status reports audioReady=true and audioStoryNodes=239, and audio-map now surfaces audio-story cues. Latest native MediaPanel pass selected a disposable projects/us062-audio-story-smoke project with no preexisting audio_story_graph.json or search index, exposed ProjectShelf.us062-audio-story-smoke, MediaPanel.BuildAudioStoryGraphButton, and MediaPanel.AudioStoryGraphCommandLine, clicked the button, observed disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id=us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; index-status reported searchDocuments=7; library-status reported ragReady=true, audioReady=true, audioStoryNodes=3; the disposable project was removed and Refresh Projects removed it from the shelf. Focused ProjectAudioStoryGraphRunPlanTests/ProjectAudioTimelineMapTests/ProjectSQLiteIndexTests executed 6 tests with 0 failures, swift build --target VideoOSStudio passed, and build_and_run --verify relaunched VideoOSStudio PID 94629.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="48" customHeight="1">
@@ -3807,16 +3807,16 @@
         <x:v>The Audio Story Graph action was runnable through menus and command palette, but the MediaPanel button had no stable automation identifier and direct button pixel proof remained blocked by the current AX window-list limitation.</x:v>
       </x:c>
       <x:c r="F52" s="26" t="str">
-        <x:v>MediaPanel rendered the button with only its localized label. In this desktop session CGWindow sees the app window, but System Events reports zero AX windows, so title/coordinate-based button confirmation is fragile even though the Studio menu action can execute.</x:v>
+        <x:v>MediaPanel rendered the button with only its localized label. Earlier System Events checks reported zero AX windows, so title/coordinate-based button confirmation was fragile even though the Studio menu action could execute.</x:v>
       </x:c>
       <x:c r="G52" s="26" t="str">
-        <x:v>Added MediaPanel.BuildAudioStoryGraphButton and MediaPanel.AudioStoryGraphCommandLine accessibility identifiers, then verified the native Studio menu action updates the selected project's audio_story_graph.json and SQLite index.</x:v>
+        <x:v>Added MediaPanel.BuildAudioStoryGraphButton and MediaPanel.AudioStoryGraphCommandLine accessibility identifiers, then verified the native MediaPanel button updates the selected project's audio_story_graph.json and SQLite index.</x:v>
       </x:c>
       <x:c r="H52" s="26" t="str">
-        <x:v>Native Studio &gt; Build Audio Story Graph updated ax1 audio_story_graph.json and project_index.sqlite at 2026-06-23 08:11:59 JST; index-status returned 492 search documents; library-status returned audioReady=true and audioStoryNodes=239; focused Swift tests/build/build_and_run passed.</x:v>
+        <x:v>Native MediaPanel click on disposable us062-audio-story-smoke changed the button to disabled Building Audio Graph, completed with Audio story graph built and indexed: 3 nodes / 7 docs, produced graph coverage ready, index-status searchDocuments=7, and library-status ragReady=true/audioReady=true/audioStoryNodes=3; the temporary project was removed after Refresh Projects.</x:v>
       </x:c>
       <x:c r="I52" s="11" t="str">
-        <x:v>Mitigated; pixel capture pending</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="48" customHeight="1">
@@ -8790,23 +8790,43 @@
       </x:c>
     </x:row>
     <x:row r="224" ht="48" customHeight="1">
-      <x:c r="A224" s="12" t="str">
+      <x:c r="A224" s="10" t="str">
         <x:v>TL-223</x:v>
       </x:c>
-      <x:c r="B224" s="27" t="str">
+      <x:c r="B224" s="26" t="str">
         <x:v>US-046</x:v>
       </x:c>
-      <x:c r="C224" s="27" t="str">
+      <x:c r="C224" s="26" t="str">
         <x:v>Native New Project from Source</x:v>
       </x:c>
-      <x:c r="D224" s="27" t="str">
+      <x:c r="D224" s="26" t="str">
         <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
       </x:c>
-      <x:c r="E224" s="27" t="str">
+      <x:c r="E224" s="26" t="str">
         <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
       </x:c>
-      <x:c r="F224" s="13" t="str">
+      <x:c r="F224" s="11" t="str">
         <x:v>Native project creation/NSOpenPanel pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" ht="48" customHeight="1">
+      <x:c r="A225" s="12" t="str">
+        <x:v>TL-224</x:v>
+      </x:c>
+      <x:c r="B225" s="27" t="str">
+        <x:v>US-062</x:v>
+      </x:c>
+      <x:c r="C225" s="27" t="str">
+        <x:v>Native MediaPanel Audio Story Graph button</x:v>
+      </x:c>
+      <x:c r="D225" s="27" t="str">
+        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
+      </x:c>
+      <x:c r="E225" s="27" t="str">
+        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+      </x:c>
+      <x:c r="F225" s="13" t="str">
+        <x:v>Native AX/UI/CLI pass</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rbc5bfae1cbe14d22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rd287e3a23407496b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R9b3d092ea8b044fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R09e7eb3e7e344842"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R58dc1545115145e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R78d307c819ac4698"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R86380b5aba2f4eae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R61b07d715d4d4307"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R5bea489a79924499"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R93f381c041da4d5d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build includes ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, ProjectInitializer.CancelButton, repo-root source-folder panel startup, explicit Project creation status text for US-046, and MediaPanel.BuildAudioStoryGraphButton / MediaPanel.AudioStoryGraphCommandLine for US-062, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix. Latest native build/run verified VideoOSStudio from the repo root.</x:v>
+        <x:v>Latest code build includes ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, ProjectInitializer.CancelButton, repo-root source-folder panel startup, explicit Project creation status text for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, and MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix. Latest native build/run verified VideoOSStudio from the repo root.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-062 native loop created disposable projects/us062-audio-story-smoke from the audio-story fixture with graph/index removed, clicked MediaPanel.BuildAudioStoryGraphButton, observed Building audio story graph... then Audio story graph built and indexed: 3 nodes / 7 docs, verified graph coverage ready, index-status searchDocuments=7, library-status ragReady=true/audioReady=true/audioStoryNodes=3, and removed the disposable project after Refresh Projects. Prior US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
+        <x:v>Latest US-063 native loop created disposable projects/us063-native-render-smoke-20260623 from a kept 1s synthetic studio smoke, clicked MediaPanel.RenderFinalPackageButton, observed Rendering and packaging final output... then Render packaged final output, verified render-status qaPassed=true / 7 checks / 0 failed / manifestCreatedAt=2026-06-23T08:20:57.186Z / publishedFinalVideo=true / finalMix=true, confirmed QA report passed=true, package manifest source_of_truth=nle_finishing, ffprobe h264 1280x720 duration=1.000000, library ready with mediaReady=true and indexDocuments=5, and removed the disposable project plus the new tmp smoke project after Refresh Projects. Prior US-062 Audio Story Graph, US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest native checks used computer-use element targeting for ProjectShelf.us062-audio-story-smoke, MediaPanel.BuildAudioStoryGraphButton, and MediaPanel.AudioStoryGraphCommandLine; the visual state showed Story nodes 0 before the click, disabled Building Audio Graph during execution, and Story nodes 3 plus SQLite available 7 after completion. Prior checks covered ProjectShelf.NewProject, ProjectInitializer fields/buttons, source-folder panel Link Source, MediaPanel Synthetic/Proxy/Smoke controls, MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest native checks used computer-use element targeting for ProjectShelf.us063-native-render-smoke-20260623, MediaPanel.RenderFinalPackageButton, and MediaPanel.RenderFinalPackageCommandLine; the visual state showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed before the click, disabled Rendering Final during execution, and Render packaged final output after completion. Prior checks covered ProjectShelf.us062-audio-story-smoke, MediaPanel.BuildAudioStoryGraphButton, ProjectShelf.NewProject, ProjectInitializer fields/buttons, source-folder panel Link Source, MediaPanel Synthetic/Proxy/Smoke controls, MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2204,13 +2204,13 @@
         <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:421-460; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:2746-2774; apps/macos-studio/Sources/VideoOSStudioCore/ProjectRenderRunner.swift:19-215; apps/macos-studio/Tests/VideoOSStudioCoreTests/ProjectRenderRunnerTests.swift; apps/macos-studio/Tests/VideoOSStudioCoreTests/ProjectRenderPackageStatusTests.swift; apps/macos-studio/Tests/VideoOSStudioCoreTests/ProjectPipelineGateStatusTests.swift</x:v>
       </x:c>
       <x:c r="F64" s="26" t="str">
-        <x:v>Run render package/runner tests; verify disabled render guard for missing inputs and invalid state; run one small packaged render path through videoos-studio-cli render-run; inspect package status and ffprobe final video; confirm MediaPanel.RenderFinalPackageButton and MediaPanel.RenderFinalPackageCommandLine are present in code; build and relaunch the native app.</x:v>
+        <x:v>Run render package/runner tests; verify disabled render guard for missing inputs and invalid state; run one small packaged render path through videoos-studio-cli render-run; inspect package status and ffprobe final video; click native MediaPanel Render Final Package on a disposable project; verify UI progress/completion, render status, QA report, manifest, final media, and cleanup.</x:v>
       </x:c>
       <x:c r="G64" s="26" t="str">
-        <x:v>Runtime/CLI pass after planner fix; native Render button AX identifiers added; pixel capture pending</x:v>
+        <x:v>Native Render button pass</x:v>
       </x:c>
       <x:c r="H64" s="11" t="str">
-        <x:v>ProjectRenderRunPlanner now checks creative_brief.yaml and edit_blueprint.yaml before Render canRun, preserving the worker's real prerequisites. For NLE-finishing projects it auto-populates supplied_final_path from 09_output/final.mp4 when present, so packaged projects can be revalidated instead of showing a runnable command that would fail. Focused Swift tests previously executed 17 tests with 0 failures across render runner/package status/synthetic smoke/acceptance/pipeline/readiness. A kept 1s synthetic project passed studio-synthetic-smoke, render-plan included supplied_final_path, render-run completed with qaPassed=true/packageManifest=true/qaReport=true, render-status reported render packaged with 7 QA checks and 0 failures, and ffprobe confirmed a 1.000000s H.264/AAC final.mp4 at 1280x720. Latest US-063 pass added MediaPanel.RenderFinalPackageButton and MediaPanel.RenderFinalPackageCommandLine accessibility identifiers. Focused render/package/pipeline/readiness/smoke tests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; git diff --check on MediaPanelViews.swift passed; build_and_run --verify relaunched VideoOSStudio PID 55448. System Events still reported 0 VideoOSStudio AX windows, so pixel/AX visual promotion remains pending.</x:v>
+        <x:v>ProjectRenderRunPlanner checks creative_brief.yaml and edit_blueprint.yaml before Render canRun, preserves the worker's real prerequisites, and auto-populates supplied_final_path from 09_output/final.mp4 for packaged NLE-finishing projects. A kept 1s synthetic project passed studio-synthetic-smoke, render-plan included supplied_final_path, render-run completed with qaPassed=true/packageManifest=true/qaReport=true, render-status reported render packaged with 7 QA checks and 0 failures, and ffprobe confirmed a 1.000000s H.264/AAC final.mp4 at 1280x720. Latest native pass copied that kept project to disposable projects/us063-native-render-smoke-20260623, exposed ProjectShelf.us063-native-render-smoke-20260623, MediaPanel.RenderFinalPackageButton, and MediaPanel.RenderFinalPackageCommandLine, saw status render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed with final video, QA report, manifest, and final mix existing, clicked Render Final Package, observed disabled Rendering Final plus Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, finalMix=true; QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe confirmed H.264 1280x720 duration=1.000000; library-status was library ready with mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and newly created tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="48" customHeight="1">
@@ -3697,10 +3697,10 @@
         <x:v>Added planner checks for creative brief and edit blueprint; surfaced missing creative brief/edit blueprint/supplied final readiness labels; detected source_of_truth_decision from project_state.yaml; and defaulted NLE-finishing packaged projects to use existing 09_output/final.mp4 as supplied_final_path.</x:v>
       </x:c>
       <x:c r="H48" s="26" t="str">
-        <x:v>ProjectRenderRunnerTests now cover missing worker inputs and packaged NLE final reuse; PipelineGateStatus fixture was aligned to real render inputs; focused Swift suite executed 17 tests with 0 failures; CLI render-plan on the kept synthetic project now includes supplied_final_path and render-run completed with qaPassed=true, packageManifest=true, qaReport=true.</x:v>
+        <x:v>Native MediaPanel Render Final Package on disposable us063-native-render-smoke-20260623 exposed the supplied_final_path command, ran from ready to render, showed Rendering Final during execution, completed with Render packaged final output, and render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true.</x:v>
       </x:c>
       <x:c r="I48" s="11" t="str">
-        <x:v>Fixed; native button visual pending</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="48" customHeight="1">
@@ -3862,19 +3862,19 @@
         <x:v>macOS UX/testability</x:v>
       </x:c>
       <x:c r="E54" s="26" t="str">
-        <x:v>The Render Final Package button could be inspected by label only, while this desktop session cannot reliably enumerate SwiftUI windows or capture pixels.</x:v>
+        <x:v>The Render Final Package button could be inspected by label only, while this desktop session could not reliably enumerate SwiftUI windows or capture pixels.</x:v>
       </x:c>
       <x:c r="F54" s="26" t="str">
-        <x:v>MediaPanel rendered the Render Final Package button and command-line text without stable accessibility identifiers. Since System Events currently reports 0 AX windows for VideoOSStudio, title/coordinate-based proof is too fragile to promote the native button path.</x:v>
+        <x:v>MediaPanel rendered the Render Final Package button and command-line text without stable accessibility identifiers. Earlier System Events checks reported 0 AX windows for VideoOSStudio, so title/coordinate-based proof was too fragile to promote the native button path.</x:v>
       </x:c>
       <x:c r="G54" s="26" t="str">
-        <x:v>Added MediaPanel.RenderFinalPackageButton and MediaPanel.RenderFinalPackageCommandLine accessibility identifiers using the existing MediaPanel naming pattern.</x:v>
+        <x:v>Added MediaPanel.RenderFinalPackageButton and MediaPanel.RenderFinalPackageCommandLine accessibility identifiers using the existing MediaPanel naming pattern, then verified the button through computer-use AX on a disposable render-ready project.</x:v>
       </x:c>
       <x:c r="H54" s="26" t="str">
-        <x:v>Focused render/package/pipeline/readiness/smoke Swift suite executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; git diff --check on MediaPanelViews.swift passed; build_and_run --verify relaunched VideoOSStudio PID 55448; app menus were visible while System Events still reported 0 AX windows.</x:v>
+        <x:v>Computer-use selected us063-native-render-smoke-20260623, exposed MediaPanel.RenderFinalPackageButton and MediaPanel.RenderFinalPackageCommandLine, clicked the button, observed disabled Rendering Final and Rendering and packaging final output..., then observed Render packaged final output with final video, QA report, manifest, and final mix exists. CLI/JQ/ffprobe confirmed render packaged, QA 7/0, manifest source_of_truth=nle_finishing, final media H.264 1280x720 1.000000s.</x:v>
       </x:c>
       <x:c r="I54" s="11" t="str">
-        <x:v>Mitigated; pixel capture pending</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="48" customHeight="1">
@@ -8810,22 +8810,42 @@
       </x:c>
     </x:row>
     <x:row r="225" ht="48" customHeight="1">
-      <x:c r="A225" s="12" t="str">
+      <x:c r="A225" s="10" t="str">
         <x:v>TL-224</x:v>
       </x:c>
-      <x:c r="B225" s="27" t="str">
+      <x:c r="B225" s="26" t="str">
         <x:v>US-062</x:v>
       </x:c>
-      <x:c r="C225" s="27" t="str">
+      <x:c r="C225" s="26" t="str">
         <x:v>Native MediaPanel Audio Story Graph button</x:v>
       </x:c>
-      <x:c r="D225" s="27" t="str">
+      <x:c r="D225" s="26" t="str">
         <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
       </x:c>
-      <x:c r="E225" s="27" t="str">
+      <x:c r="E225" s="26" t="str">
         <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
-      <x:c r="F225" s="13" t="str">
+      <x:c r="F225" s="11" t="str">
+        <x:v>Native AX/UI/CLI pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" ht="48" customHeight="1">
+      <x:c r="A226" s="12" t="str">
+        <x:v>TL-225</x:v>
+      </x:c>
+      <x:c r="B226" s="27" t="str">
+        <x:v>US-063</x:v>
+      </x:c>
+      <x:c r="C226" s="27" t="str">
+        <x:v>Native Render Final Package button</x:v>
+      </x:c>
+      <x:c r="D226" s="27" t="str">
+        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
+      </x:c>
+      <x:c r="E226" s="27" t="str">
+        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
+      </x:c>
+      <x:c r="F226" s="13" t="str">
         <x:v>Native AX/UI/CLI pass</x:v>
       </x:c>
     </x:row>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R78d307c819ac4698"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R86380b5aba2f4eae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R61b07d715d4d4307"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R5bea489a79924499"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R93f381c041da4d5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5598930707494e79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Raad911e0c45a49f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R53b3f56544674878"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="Ra7cae34f615144a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R58ccfe79fe9d45bc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build includes ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, ProjectInitializer.CancelButton, repo-root source-folder panel startup, explicit Project creation status text for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, and MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix. Latest native build/run verified VideoOSStudio from the repo root.</x:v>
+        <x:v>Latest code build includes ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, ProjectInitializer.CancelButton, repo-root source-folder panel startup, explicit Project creation status text for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix. Latest native build/run verified VideoOSStudio from the repo root.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-063 native loop created disposable projects/us063-native-render-smoke-20260623 from a kept 1s synthetic studio smoke, clicked MediaPanel.RenderFinalPackageButton, observed Rendering and packaging final output... then Render packaged final output, verified render-status qaPassed=true / 7 checks / 0 failed / manifestCreatedAt=2026-06-23T08:20:57.186Z / publishedFinalVideo=true / finalMix=true, confirmed QA report passed=true, package manifest source_of_truth=nle_finishing, ffprobe h264 1280x720 duration=1.000000, library ready with mediaReady=true and indexDocuments=5, and removed the disposable project plus the new tmp smoke project after Refresh Projects. Prior US-062 Audio Story Graph, US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
+        <x:v>Latest US-064 native loop created disposable handoff and final-media synthetic projects, clicked MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, observed packet verified / 6 of 6 files / final media included / final audio included / Exported packet with 7 files, verified Finder selected 09_output/editor_packet, confirmed handoff-packet-verify packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true, checked manifest entries for premiere_xml/editor_notes/review_report/review_patch/final_media/final_audio, ffprobed packet final media/audio, and removed the disposable projects plus the new tmp smoke project after Refresh Projects. Prior US-063 Render Final Package, US-062 Audio Story Graph, US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest native checks used computer-use element targeting for ProjectShelf.us063-native-render-smoke-20260623, MediaPanel.RenderFinalPackageButton, and MediaPanel.RenderFinalPackageCommandLine; the visual state showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed before the click, disabled Rendering Final during execution, and Render packaged final output after completion. Prior checks covered ProjectShelf.us062-audio-story-smoke, MediaPanel.BuildAudioStoryGraphButton, ProjectShelf.NewProject, ProjectInitializer fields/buttons, source-folder panel Link Source, MediaPanel Synthetic/Proxy/Smoke controls, MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest native checks used computer-use element targeting for ProjectShelf.us064-native-handoff-smoke-20260623, ProjectShelf.us064-native-packet-smoke-20260623, MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, MediaPanel.RevealEditorPacketButton, and MediaPanel.HandoffCommandLine; the visual/AX state showed packet missing before export, Exporting Premiere XML then Exported synthetic-studio-smoke_premiere.xml, Exporting editor packet then packet verified with final media/audio included, Reveal Packet status, and Finder selected 09_output/editor_packet. Prior checks covered ProjectShelf.us063-native-render-smoke-20260623, MediaPanel.RenderFinalPackageButton, ProjectShelf.us062-audio-story-smoke, MediaPanel.BuildAudioStoryGraphButton, ProjectShelf.NewProject, ProjectInitializer fields/buttons, source-folder panel Link Source, MediaPanel Synthetic/Proxy/Smoke controls, MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2230,13 +2230,13 @@
         <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:463-550; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:2668-2740; apps/macos-studio/Sources/VideoOSStudioCore/ProjectHandoffExport.swift; apps/macos-studio/Tests/VideoOSStudioCoreTests/ProjectHandoffExportTests.swift; apps/macos-studio/Tests/VideoOSStudioCoreTests/ProjectSyntheticHandoffSmokeTests.swift</x:v>
       </x:c>
       <x:c r="F65" s="26" t="str">
-        <x:v>Run ProjectHandoffExportTests; run handoff-status/export-premiere/packet-status/export-packet/packet-verify on a ready fixture; inspect manifest media files; confirm MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, MediaPanel.RevealEditorPacketButton, and MediaPanel.HandoffCommandLine exist in code; build and relaunch native app; native Reveal Packet/Finder visual confirmation remains separate.</x:v>
+        <x:v>Run ProjectHandoffExportTests; run handoff-status/export-premiere/packet-status/export-packet/packet-verify on a ready fixture; inspect manifest media files; click native MediaPanel Export Premiere XML, Export Editor Packet, and Reveal Packet on disposable projects; verify packet contents, final media/audio, Finder reveal selection, app refresh cleanup, build, and relaunch.</x:v>
       </x:c>
       <x:c r="G65" s="26" t="str">
-        <x:v>Runtime/CLI pass; native handoff AX identifiers added; Finder/pixel capture pending</x:v>
+        <x:v>Native Editor Handoff export/reveal pass</x:v>
       </x:c>
       <x:c r="H65" s="11" t="str">
-        <x:v>A kept 1s synthetic project reported handoff-status ready with source map ready, 1/1 coverage, mediaReady=1, mediaMissing=0, output synthetic-studio-smoke_premiere.xml, and packet ready without notes. handoff-export-premiere wrote XML with 1V+1A tracks and 2 clips. handoff-export-packet wrote 7 output files including XML, editor notes, review report, review patch, final_media-final.mp4, final_audio-final_mix.wav, and manifest.json. handoff-packet-verify reported packet verified, manifestFiles=6, existingFiles=6, missingFiles=0, mediaFiles=2, finalMedia=true, finalAudio=true. Focused Swift handoff/smoke suite previously passed 10 tests. Latest US-064 pass added MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, MediaPanel.RevealEditorPacketButton, and MediaPanel.HandoffCommandLine accessibility identifiers. Focused ProjectHandoffExportTests, ProjectSyntheticHandoffSmokeTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectLibraryReadinessStatusTests executed 13 tests with 0 failures; swift build --target VideoOSStudio passed; git diff --check on MediaPanelViews.swift passed; build_and_run --verify relaunched VideoOSStudio PID 76913. System Events listed the app menus but still reported 0 AX windows, so Finder/pixel visual promotion remains pending.</x:v>
+        <x:v>A kept 1s synthetic project reported handoff-status ready with source map ready, 1/1 coverage, mediaReady=1, mediaMissing=0, output synthetic-studio-smoke_premiere.xml, and packet ready without notes. handoff-export-premiere wrote XML with 1V+1A tracks and 2 clips. handoff-export-packet wrote 7 output files including XML, editor notes, review report, review patch, final_media-final.mp4, final_audio-final_mix.wav, and manifest.json. handoff-packet-verify reported packet verified, manifestFiles=6, existingFiles=6, missingFiles=0, mediaFiles=2, finalMedia=true, finalAudio=true. Latest native pass selected disposable ProjectShelf.us064-native-handoff-smoke-20260623 and confirmed MediaPanel.ExportPremiereXMLButton, ExportEditorPacketButton, RevealEditorPacketButton, and HandoffCommandLine through computer-use. It then selected final-media disposable ProjectShelf.us064-native-packet-smoke-20260623, whose MediaPanel showed packet ready without notes, review report included, review patch included, Preview/final media 2 files, and packet missing. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet changed status to Revealed editor packet in Finder, and Finder opened 09_output with editor_packet selected plus final.mp4 and synthetic-studio-smoke_premiere.xml visible. CLI handoff-packet-verify returned packet verified, manifestFiles=6, existingFiles=6, missingFiles=0, mediaFiles=2, finalMedia=true, finalAudio=true; jq confirmed manifest entries for premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe confirmed packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. The disposable projects and newly created tmp smoke project were removed, and Refresh Projects removed both us064 shelf entries.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="48" customHeight="1">
@@ -3900,10 +3900,10 @@
         <x:v>Added MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, MediaPanel.RevealEditorPacketButton, and MediaPanel.HandoffCommandLine identifiers using the existing MediaPanel naming pattern. editor_annotations.json remains a handoff artifact distinct from review_patch.json.</x:v>
       </x:c>
       <x:c r="H55" s="26" t="str">
-        <x:v>Focused handoff/library/smoke Swift suite executed 13 tests with 0 failures; swift build --target VideoOSStudio passed; git diff --check on MediaPanelViews.swift passed; build_and_run --verify relaunched VideoOSStudio PID 76913; app menus were visible while System Events still reported 0 AX windows.</x:v>
+        <x:v>Computer-use selected disposable us064-native-packet-smoke-20260623, exposed MediaPanel.ExportPremiereXMLButton, ExportEditorPacketButton, RevealEditorPacketButton, and HandoffCommandLine, clicked Export Premiere XML and Export Editor Packet, observed packet verified with 6/6 files plus final media/audio included, clicked Reveal Packet, and Finder selected 09_output/editor_packet. CLI/JQ/ffprobe confirmed manifest files, final media, and final audio, and cleanup removed the disposable projects from disk and shelf.</x:v>
       </x:c>
       <x:c r="I55" s="11" t="str">
-        <x:v>Mitigated; Finder/pixel capture pending</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="48" customHeight="1">
@@ -8830,23 +8830,43 @@
       </x:c>
     </x:row>
     <x:row r="226" ht="48" customHeight="1">
-      <x:c r="A226" s="12" t="str">
+      <x:c r="A226" s="10" t="str">
         <x:v>TL-225</x:v>
       </x:c>
-      <x:c r="B226" s="27" t="str">
+      <x:c r="B226" s="26" t="str">
         <x:v>US-063</x:v>
       </x:c>
-      <x:c r="C226" s="27" t="str">
+      <x:c r="C226" s="26" t="str">
         <x:v>Native Render Final Package button</x:v>
       </x:c>
-      <x:c r="D226" s="27" t="str">
+      <x:c r="D226" s="26" t="str">
         <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
       </x:c>
-      <x:c r="E226" s="27" t="str">
+      <x:c r="E226" s="26" t="str">
         <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
-      <x:c r="F226" s="13" t="str">
+      <x:c r="F226" s="11" t="str">
         <x:v>Native AX/UI/CLI pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" ht="48" customHeight="1">
+      <x:c r="A227" s="12" t="str">
+        <x:v>TL-226</x:v>
+      </x:c>
+      <x:c r="B227" s="27" t="str">
+        <x:v>US-064</x:v>
+      </x:c>
+      <x:c r="C227" s="27" t="str">
+        <x:v>Native Editor Handoff export and Finder reveal</x:v>
+      </x:c>
+      <x:c r="D227" s="27" t="str">
+        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
+      </x:c>
+      <x:c r="E227" s="27" t="str">
+        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
+      </x:c>
+      <x:c r="F227" s="13" t="str">
+        <x:v>Native AX/UI/Finder/CLI pass</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5598930707494e79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Raad911e0c45a49f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R53b3f56544674878"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="Ra7cae34f615144a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R58ccfe79fe9d45bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R8994f1798fb8464b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rf1bc61da807646a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R71705d7dd7de4937"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R36c5595879e64409"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Rb0facdded19740e5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-064 native loop created disposable handoff and final-media synthetic projects, clicked MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, observed packet verified / 6 of 6 files / final media included / final audio included / Exported packet with 7 files, verified Finder selected 09_output/editor_packet, confirmed handoff-packet-verify packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true, checked manifest entries for premiere_xml/editor_notes/review_report/review_patch/final_media/final_audio, ffprobed packet final media/audio, and removed the disposable projects plus the new tmp smoke project after Refresh Projects. Prior US-063 Render Final Package, US-062 Audio Story Graph, US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
+        <x:v>Latest US-055 native loop started a stdio Codex App Server session, selected CLP_0001 in the Clip inspector, pressed ClipInspector.AskCodexButton, observed NoteDraftEditor and HandoffInstructionDraftEditor populated with a live read-only proposal, captured /tmp/videoos-debug/us055-ask-codex-proposal-applied.png, and confirmed git status remained clean because Save Note was not pressed. Prior US-064 Editor Handoff export, US-063 Render Final Package, US-062 Audio Story Graph, US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-055 Save/Clear, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest native checks used computer-use element targeting for ProjectShelf.us064-native-handoff-smoke-20260623, ProjectShelf.us064-native-packet-smoke-20260623, MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, MediaPanel.RevealEditorPacketButton, and MediaPanel.HandoffCommandLine; the visual/AX state showed packet missing before export, Exporting Premiere XML then Exported synthetic-studio-smoke_premiere.xml, Exporting editor packet then packet verified with final media/audio included, Reveal Packet status, and Finder selected 09_output/editor_packet. Prior checks covered ProjectShelf.us063-native-render-smoke-20260623, MediaPanel.RenderFinalPackageButton, ProjectShelf.us062-audio-story-smoke, MediaPanel.BuildAudioStoryGraphButton, ProjectShelf.NewProject, ProjectInitializer fields/buttons, source-folder panel Link Source, MediaPanel Synthetic/Proxy/Smoke controls, MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest native checks used computer-use element targeting for Agent Start Agent Session, toolbar Clip, Timeline.Clip.V1.CLP_0001, ClipInspector.AskCodexButton, ClipInspector.NoteDraftEditor, ClipInspector.HandoffInstructionDraftEditor, and ClipInspector.EditorAnnotationStatus; the visual/AX state showed a live Codex proposal applied to draft for CLP_0001 with Save Note enabled but not pressed. Prior checks covered ProjectShelf.us064-native-handoff-smoke-20260623, ProjectShelf.us064-native-packet-smoke-20260623, MediaPanel.ExportPremiereXMLButton, ExportEditorPacketButton, RevealEditorPacketButton, ProjectShelf.us063-native-render-smoke-20260623, MediaPanel.RenderFinalPackageButton, ProjectShelf.us062-audio-story-smoke, MediaPanel.BuildAudioStoryGraphButton, ProjectShelf.NewProject, ProjectInitializer fields/buttons, source-folder panel Link Source, MediaPanel Synthetic/Proxy/Smoke controls, MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap, US-055 native Save/Clear, and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Live Ask Codex note proposal and visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1993,16 +1993,16 @@
         <x:v>ClipInspectorPanel renders selection/source/timeline/editorial intent, analysis evidence, transcripts, Marlin, audio evidence, note editors, and note action buttons; StudioViewModel persists ProjectEditorAnnotations; CLI exposes the same annotation status/add/clear/prompt contract for non-visual smoke coverage. The native note summary, draft editors, saved note fields, Ask Codex, Save, Clear, status, and no-selection state now expose stable ClipInspector identifiers.</x:v>
       </x:c>
       <x:c r="E56" s="26" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/ClipInspectorViews.swift:6-320; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:720-862; apps/macos-studio/Sources/VideoOSStudioCore/ProjectEditorAnnotations.swift; apps/macos-studio/Sources/VideoOSStudioCLI/main.swift:955-1035</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/ClipInspectorViews.swift:6-320; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:720-917; apps/macos-studio/Sources/VideoOSStudioCore/ProjectEditorAnnotations.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectEditorAnnotationProposal.swift; apps/macos-studio/Sources/VideoOSStudioCLI/main.swift:955-1035</x:v>
       </x:c>
       <x:c r="F56" s="26" t="str">
-        <x:v>Run annotation/evidence tests; save/clear a note through the same ProjectEditorAnnotationStore path and verify editor_annotations artifact; confirm ClipInspector accessibility identifiers are present in code and exposed in the running app after selecting a timeline clip; keep destructive native save/clear visual pass separate for a disposable or restored real-project project.</x:v>
+        <x:v>Run annotation/evidence/proposal tests; save/clear a note through the same ProjectEditorAnnotationStore path and verify editor_annotations artifact; confirm ClipInspector accessibility identifiers are present in code and exposed in the running app after selecting a timeline clip; start a read-only Codex App Server session, press Ask Codex, verify the proposal populates drafts, and do not press Save during the proposal check.</x:v>
       </x:c>
       <x:c r="G56" s="26" t="str">
-        <x:v>Core/CLI/runtime pass; native save/clear AX/pixel pass; live Ask Codex proposal pending</x:v>
+        <x:v>Native save/clear/Ask Codex proposal pass</x:v>
       </x:c>
       <x:c r="H56" s="11" t="str">
-        <x:v>ProjectEditorAnnotationsTests and ProjectEditorAnnotationProposalTests executed 5 tests with 0 failures. A /tmp clean-ui copy saved CLP_0001 to 07_handoff/editor_annotations.json, annotations-status reported 1 clip notes, clip-note-prompt emitted the read-only Codex prompt with existing note/handoff context, and clear returned notes=[]. ClipInspector now exposes EditorAnnotationSummary, NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, EditorAnnotationStatus, no-selection, and saved-note identifiers. Latest native pass on VideoOSStudio PID 94310 selected the Clip tab, selected the first V1 hero clip, set NoteDraftEditor and HandoffInstructionDraftEditor through AXValue, triggered Save Note, scrolled the right Clip Inspector to the Editor Note section, and observed 1 clip notes, Saved note for CLP_0001, saved handoff instruction text, and screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png. CLI annotations-status confirmed exists=true notes=1 and editor_annotations.json contained the note for CLP_0001. The same UI then triggered Clear and showed Cleared note for CLP_0001 plus 0 clip notes with screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png; CLI confirmed notes=0, then the temporary editor_annotations.json and empty 07_handoff directory were removed to restore the original no-annotations state. Ask Codex live note proposal remains unpromoted pending an approved/running agent session.</x:v>
+        <x:v>ProjectEditorAnnotationsTests and ProjectEditorAnnotationProposalTests executed 5 tests with 0 failures. A /tmp clean-ui copy saved CLP_0001 to 07_handoff/editor_annotations.json, annotations-status reported 1 clip notes, clip-note-prompt emitted the read-only Codex prompt with existing note/handoff context, and clear returned notes=[]. ClipInspector now exposes EditorAnnotationSummary, NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, EditorAnnotationStatus, no-selection, and saved-note identifiers. Native save/clear pass on VideoOSStudio PID 94310 selected the Clip tab, selected the first V1 hero clip, set NoteDraftEditor and HandoffInstructionDraftEditor through AXValue, triggered Save Note, observed 1 clip notes and Saved note for CLP_0001, verified editor_annotations.json, then triggered Clear and restored the original no-annotations state; screenshots /tmp/videoos-debug/us055-clip-note-saved-visible.png and /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible states. Latest live proposal pass on VideoOSStudio PID 30320 started a Codex App Server session over stdio, selected CLP_0001 in the Clip inspector, pressed ClipInspector.AskCodexButton, and observed NoteDraftEditor and HandoffInstructionDraftEditor populated with a Japanese proposal plus status Codex proposal applied to draft for CLP_0001. Save to write it. Screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the draft-applied state, and git status remained clean because Save was not pressed.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="48" customHeight="1">
@@ -3987,10 +3987,10 @@
         <x:v>Added ClipInspector.EditorAnnotationSummary, SavedNoteUpdatedAt, SavedHandoffInstruction, NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, EditorAnnotationStatus, and NoSelectionMessage identifiers.</x:v>
       </x:c>
       <x:c r="H58" s="26" t="str">
-        <x:v>rg confirmed the identifiers; focused annotation tests executed 5 tests with 0 failures; temporary clean-ui CLI smoke saved CLP_0001, generated a prompt with existing note context, cleared the note, and verified notes=[]; swift build --target VideoOSStudio and build_and_run --verify passed; AX exposed NoSelectionMessage before selection and note editor/button identifiers after selecting the first timeline clip.</x:v>
+        <x:v>rg confirmed the identifiers; focused annotation tests executed 5 tests with 0 failures; temporary clean-ui CLI smoke saved CLP_0001, generated a prompt with existing note context, cleared the note, and verified notes=[]; AX exposed NoSelectionMessage before selection and note editor/button identifiers after selecting the first timeline clip. Native Save/Clear was exercised through ClipInspector.NoteDraftEditor/HandoffInstructionDraftEditor/SaveNoteButton/ClearNoteButton with visible screenshots and filesystem verification. A live stdio Codex App Server session then pressed ClipInspector.AskCodexButton for CLP_0001 and populated both draft editors with a proposal without writing files.</x:v>
       </x:c>
       <x:c r="I58" s="11" t="str">
-        <x:v>Mitigated; pixel/save-click pending</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="48" customHeight="1">
@@ -8850,23 +8850,43 @@
       </x:c>
     </x:row>
     <x:row r="227" ht="48" customHeight="1">
-      <x:c r="A227" s="12" t="str">
+      <x:c r="A227" s="10" t="str">
         <x:v>TL-226</x:v>
       </x:c>
-      <x:c r="B227" s="27" t="str">
+      <x:c r="B227" s="26" t="str">
         <x:v>US-064</x:v>
       </x:c>
-      <x:c r="C227" s="27" t="str">
+      <x:c r="C227" s="26" t="str">
         <x:v>Native Editor Handoff export and Finder reveal</x:v>
       </x:c>
-      <x:c r="D227" s="27" t="str">
+      <x:c r="D227" s="26" t="str">
         <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
       </x:c>
-      <x:c r="E227" s="27" t="str">
+      <x:c r="E227" s="26" t="str">
         <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
       </x:c>
-      <x:c r="F227" s="13" t="str">
+      <x:c r="F227" s="11" t="str">
         <x:v>Native AX/UI/Finder/CLI pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" ht="48" customHeight="1">
+      <x:c r="A228" s="12" t="str">
+        <x:v>TL-227</x:v>
+      </x:c>
+      <x:c r="B228" s="27" t="str">
+        <x:v>US-055</x:v>
+      </x:c>
+      <x:c r="C228" s="27" t="str">
+        <x:v>Native Ask Codex editor-note proposal</x:v>
+      </x:c>
+      <x:c r="D228" s="27" t="str">
+        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
+      </x:c>
+      <x:c r="E228" s="27" t="str">
+        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
+      </x:c>
+      <x:c r="F228" s="13" t="str">
+        <x:v>Native read-only Codex proposal pass</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9317,10 +9337,10 @@
         <x:v>macOS Clip inspector</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/ClipInspectorViews.swift; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:720-862; apps/macos-studio/Sources/VideoOSStudioCore/ProjectEvidenceStore.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectEditorAnnotations.swift; apps/macos-studio/Sources/VideoOSStudioCLI/main.swift:955-1035</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/ClipInspectorViews.swift; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:720-917; apps/macos-studio/Sources/VideoOSStudioCore/ProjectEvidenceStore.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectEditorAnnotations.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectEditorAnnotationProposal.swift; apps/macos-studio/Sources/VideoOSStudioCLI/main.swift:955-1035</x:v>
       </x:c>
       <x:c r="C40" s="11" t="str">
-        <x:v>Selected clip source/timeline/intent, analysis evidence, transcript, Marlin/audio evidence, handoff notes, Codex note proposal, save/clear, stable ClipInspector AX identifiers, and CLI parity for annotation status/add/clear/prompt smoke tests.</x:v>
+        <x:v>Selected clip source/timeline/intent, analysis evidence, transcript, Marlin/audio evidence, handoff notes, read-only Codex note proposal, save/clear, stable ClipInspector AX identifiers, and CLI parity for annotation status/add/clear/prompt smoke tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="48" customHeight="1">

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R8994f1798fb8464b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rf1bc61da807646a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R71705d7dd7de4937"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R36c5595879e64409"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Rb0facdded19740e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R055aac4f891544ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R2214e8c153da49e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Re5ca421aec6740e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R78a477e122604c77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R4bb6467b80214f10"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-055 native loop started a stdio Codex App Server session, selected CLP_0001 in the Clip inspector, pressed ClipInspector.AskCodexButton, observed NoteDraftEditor and HandoffInstructionDraftEditor populated with a live read-only proposal, captured /tmp/videoos-debug/us055-ask-codex-proposal-applied.png, and confirmed git status remained clean because Save Note was not pressed. Prior US-064 Editor Handoff export, US-063 Render Final Package, US-062 Audio Story Graph, US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-055 Save/Clear, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
+        <x:v>Latest US-061 loop ran a live non-mock Marlin single-source completion on a /tmp lively-alt-vol5-derived fixture with requestTimeoutMs=900000 and VOS_MARLIN_PROXY_MAX_WIDTH=384; marlin-evaluate wrote marlin_events.json, marlin-status reported events=3/findResults=4/coverage=1.00/canPreferMarlin=true for the fixture, segments gained marlin_temporal_semantics peak provenance, index-rebuild produced 9 search documents, and git status stayed clean. Prior US-055 Ask Codex proposal, US-064 Editor Handoff export, US-063 Render Final Package, US-062 Audio Story Graph, US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-055 Save/Clear, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest native checks used computer-use element targeting for Agent Start Agent Session, toolbar Clip, Timeline.Clip.V1.CLP_0001, ClipInspector.AskCodexButton, ClipInspector.NoteDraftEditor, ClipInspector.HandoffInstructionDraftEditor, and ClipInspector.EditorAnnotationStatus; the visual/AX state showed a live Codex proposal applied to draft for CLP_0001 with Save Note enabled but not pressed. Prior checks covered ProjectShelf.us064-native-handoff-smoke-20260623, ProjectShelf.us064-native-packet-smoke-20260623, MediaPanel.ExportPremiereXMLButton, ExportEditorPacketButton, RevealEditorPacketButton, ProjectShelf.us063-native-render-smoke-20260623, MediaPanel.RenderFinalPackageButton, ProjectShelf.us062-audio-story-smoke, MediaPanel.BuildAudioStoryGraphButton, ProjectShelf.NewProject, ProjectInitializer fields/buttons, source-folder panel Link Source, MediaPanel Synthetic/Proxy/Smoke controls, MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest native visual check remains the US-055 computer-use pass for Agent Start Agent Session, toolbar Clip, Timeline.Clip.V1.CLP_0001, ClipInspector.AskCodexButton, ClipInspector.NoteDraftEditor, ClipInspector.HandoffInstructionDraftEditor, and ClipInspector.EditorAnnotationStatus. Latest US-061 live model check was CLI/runtime on /tmp because it intentionally avoided writing real project artifacts; prior Media tab AX checks already covered MediaPanel.MarlinEvaluationRecommendation, MarlinPreferenceRecommendation, MarlinQueueNextAction, MarlinRepresentativeNextAction, MarlinRepresentativeBucket.*, MarlinQueueItem.*, MarlinEvaluationRunStatus, RunMarlinEvaluationButton, ApplyMarlinPreferenceButton, MarlinEvaluationCommandLine, and MarlinEvaluationArtifactPath. Prior checks covered ProjectShelf.us064-native-handoff-smoke-20260623, ProjectShelf.us064-native-packet-smoke-20260623, MediaPanel.ExportPremiereXMLButton, ExportEditorPacketButton, RevealEditorPacketButton, ProjectShelf.us063-native-render-smoke-20260623, MediaPanel.RenderFinalPackageButton, ProjectShelf.us062-audio-story-smoke, MediaPanel.BuildAudioStoryGraphButton, ProjectShelf.NewProject, ProjectInitializer fields/buttons, source-folder panel Link Source, MediaPanel Synthetic/Proxy/Smoke controls, MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-061 is promoted for runtime/model/mock/native AX and a live non-mock single-source Marlin completion on a representative-source fixture; the full multi-source live batch and repo-level Marlin-first preference promotion remain pending evidence gates. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2152,13 +2152,13 @@
         <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:48-160; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1296-1325,2326-2481; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRuntimeStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinModelAccessStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationQueue.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRepresentativePlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationRunPlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinPreferenceDecision.swift</x:v>
       </x:c>
       <x:c r="F62" s="26" t="str">
-        <x:v>Run Marlin runtime/model/preference/queue/representative-plan/eval-plan/eval-run/status CLI checks, execute a tiny mock evaluation fixture, verify index refresh, verify Preference apply is blocked when gates fail, run Marlin focused Swift tests, confirm stable Marlin accessibility identifiers, and keep live representative completion pending until a long MPS run finishes.</x:v>
+        <x:v>Run Marlin runtime/model/preference/queue/representative-plan/eval-plan/eval-run/status CLI checks, execute a tiny mock evaluation fixture, verify index refresh, verify Preference apply is blocked when gates fail, run Marlin focused Swift tests, confirm stable Marlin accessibility identifiers, run at least one live non-mock representative-source completion, and leave full batch/preference promotion blocked until representative coverage and aggregate coverage gates pass.</x:v>
       </x:c>
       <x:c r="G62" s="26" t="str">
-        <x:v>Runtime/model/mock eval pass; Marlin AX identifiers added; live representative completion pending</x:v>
+        <x:v>Runtime/model/mock/native AX/live single-source pass; full batch preference gate pending</x:v>
       </x:c>
       <x:c r="H62" s="11" t="str">
-        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A live representative attempt selected lively-alt-vol5 because it covers the target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but the first caption request timed out after the fixed 300000ms default without writing marlin_events.json. The CLI/script path now supports --request-timeout-ms / --timeout-ms, dry-run shows 900000ms in the generated command, and focused TS/Swift tests pass. Latest pass added MediaPanel.MarlinEvaluationRecommendation, MarlinPreferenceRecommendation, MarlinQueueNextAction, MarlinRepresentativeNextAction, MarlinRepresentativeBucket.*, MarlinQueueItem.*, MarlinEvaluationRunStatus, RunMarlinEvaluationButton, ApplyMarlinPreferenceButton, MarlinEvaluationCommandLine, and MarlinEvaluationArtifactPath identifiers. Focused Marlin Swift tests executed 32 tests with 0 failures; swift build --target VideoOSStudio passed; diff check passed; build_and_run --verify relaunched the app. A long live completion run remains pending.</x:v>
+        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path now supports --request-timeout-ms / --timeout-ms, dry-run shows 900000ms in the generated command, and focused TS/Swift tests pass. Latest pass added MediaPanel.Marlin* identifiers and then ran a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4, with VOS_MARLIN_PROXY_MAX_WIDTH=384 and requestTimeoutMs=900000. marlin-evaluate completed with Mock=false, wrote marlin_events.json with inference_mode=live, model NemoStation/Marlin-2B, 1 asset, 3 events, and 4 find results; marlin-status reported candidate for preferred VLM, coverage=1.00, canPreferMarlin=true for the tmp fixture; segments.json gained marlin_temporal_semantics peak provenance and 3 interest points; index-rebuild produced 9 search documents. Full all-source representative run and repo-level preference promotion remain pending because the real repo gate still needs broader live coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="48" customHeight="1">
@@ -3784,10 +3784,10 @@
         <x:v>Added --request-timeout-ms and --timeout-ms to scripts/marlin-evaluate.ts, threaded requestTimeoutMs through ProjectMarlinEvaluationRunPlan and ProjectMarlinEvaluationRunner, surfaced it in marlin-eval-plan/marlin-eval-next/marlin-eval-run, and added a dry-run hint for slow MPS live runs.</x:v>
       </x:c>
       <x:c r="H51" s="26" t="str">
-        <x:v>npx vitest run tests/marlin-analysis-stage.test.ts passed 7 tests; swift test --filter ProjectMarlinEvaluationRunPlanTests passed 9 tests; marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 printed the timeout-bearing command; missing timeout value is rejected; marlin-eval-next dry-run prints requestTimeoutMs=900000.</x:v>
+        <x:v>npx vitest run tests/marlin-analysis-stage.test.ts passed 7 tests; swift test --filter ProjectMarlinEvaluationRunPlanTests passed 9 tests; marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 printed the timeout-bearing command; missing timeout value is rejected; marlin-eval-next dry-run prints requestTimeoutMs=900000. A live non-mock single-source run against a /tmp lively-alt-vol5-derived fixture completed with requestTimeoutMs=900000 and VOS_MARLIN_PROXY_MAX_WIDTH=384, wrote marlin_events.json, updated segments with marlin_temporal_semantics, and rebuilt an index with 9 search documents. The full 9-source representative batch remains intentionally pending.</x:v>
       </x:c>
       <x:c r="I51" s="11" t="str">
-        <x:v>Mitigated; live long-run pending</x:v>
+        <x:v>Mitigated; live single-source pass; full batch pending</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="48" customHeight="1">
@@ -8870,23 +8870,43 @@
       </x:c>
     </x:row>
     <x:row r="228" ht="48" customHeight="1">
-      <x:c r="A228" s="12" t="str">
+      <x:c r="A228" s="10" t="str">
         <x:v>TL-227</x:v>
       </x:c>
-      <x:c r="B228" s="27" t="str">
+      <x:c r="B228" s="26" t="str">
         <x:v>US-055</x:v>
       </x:c>
-      <x:c r="C228" s="27" t="str">
+      <x:c r="C228" s="26" t="str">
         <x:v>Native Ask Codex editor-note proposal</x:v>
       </x:c>
-      <x:c r="D228" s="27" t="str">
+      <x:c r="D228" s="26" t="str">
         <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
       </x:c>
-      <x:c r="E228" s="27" t="str">
+      <x:c r="E228" s="26" t="str">
         <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
       </x:c>
-      <x:c r="F228" s="13" t="str">
+      <x:c r="F228" s="11" t="str">
         <x:v>Native read-only Codex proposal pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" ht="48" customHeight="1">
+      <x:c r="A229" s="12" t="str">
+        <x:v>TL-228</x:v>
+      </x:c>
+      <x:c r="B229" s="27" t="str">
+        <x:v>US-061</x:v>
+      </x:c>
+      <x:c r="C229" s="27" t="str">
+        <x:v>Live Marlin single-source completion</x:v>
+      </x:c>
+      <x:c r="D229" s="27" t="str">
+        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
+      </x:c>
+      <x:c r="E229" s="27" t="str">
+        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
+      </x:c>
+      <x:c r="F229" s="13" t="str">
+        <x:v>Live single-source pass; full representative batch pending</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R055aac4f891544ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R2214e8c153da49e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Re5ca421aec6740e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R78a477e122604c77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R4bb6467b80214f10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R113da024f1ed459a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R34a6a473cf2b4d0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R11a812ee1e974cd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="Reed5ae96a68b4809"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Rfe484e6267bb4c80"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-061 loop ran a live non-mock Marlin single-source completion on a /tmp lively-alt-vol5-derived fixture with requestTimeoutMs=900000 and VOS_MARLIN_PROXY_MAX_WIDTH=384; marlin-evaluate wrote marlin_events.json, marlin-status reported events=3/findResults=4/coverage=1.00/canPreferMarlin=true for the fixture, segments gained marlin_temporal_semantics peak provenance, index-rebuild produced 9 search documents, and git status stayed clean. Prior US-055 Ask Codex proposal, US-064 Editor Handoff export, US-063 Render Final Package, US-062 Audio Story Graph, US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-055 Save/Clear, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
+        <x:v>Latest US-045 loop fresh-launched VideoOSStudio, selected ena-promo-ai, confirmed playback-contract exact / approvalGrade=true with hash f3bc3e6fef222e1a and media-status assets=89 ready=89 missing=0, captured /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and measured Viewer center near_black_pct=0.0000. Prior US-061 loop ran a live non-mock Marlin single-source completion on a /tmp lively-alt-vol5-derived fixture with requestTimeoutMs=900000 and VOS_MARLIN_PROXY_MAX_WIDTH=384; marlin-evaluate wrote marlin_events.json, marlin-status reported events=3/findResults=4/coverage=1.00/canPreferMarlin=true for the fixture, segments gained marlin_temporal_semantics peak provenance, index-rebuild produced 9 search documents, and git status stayed clean. Prior US-055 Ask Codex proposal, US-064 Editor Handoff export, US-063 Render Final Package, US-062 Audio Story Graph, US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-055 Save/Clear, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest native visual check remains the US-055 computer-use pass for Agent Start Agent Session, toolbar Clip, Timeline.Clip.V1.CLP_0001, ClipInspector.AskCodexButton, ClipInspector.NoteDraftEditor, ClipInspector.HandoffInstructionDraftEditor, and ClipInspector.EditorAnnotationStatus. Latest US-061 live model check was CLI/runtime on /tmp because it intentionally avoided writing real project artifacts; prior Media tab AX checks already covered MediaPanel.MarlinEvaluationRecommendation, MarlinPreferenceRecommendation, MarlinQueueNextAction, MarlinRepresentativeNextAction, MarlinRepresentativeBucket.*, MarlinQueueItem.*, MarlinEvaluationRunStatus, RunMarlinEvaluationButton, ApplyMarlinPreferenceButton, MarlinEvaluationCommandLine, and MarlinEvaluationArtifactPath. Prior checks covered ProjectShelf.us064-native-handoff-smoke-20260623, ProjectShelf.us064-native-packet-smoke-20260623, MediaPanel.ExportPremiereXMLButton, ExportEditorPacketButton, RevealEditorPacketButton, ProjectShelf.us063-native-render-smoke-20260623, MediaPanel.RenderFinalPackageButton, ProjectShelf.us062-audio-story-smoke, MediaPanel.BuildAudioStoryGraphButton, ProjectShelf.NewProject, ProjectInitializer fields/buttons, source-folder panel Link Source, MediaPanel Synthetic/Proxy/Smoke controls, MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest native visual check is the US-045 computer-use pass selecting ProjectShelf.ena-promo-ai and confirming a visible exact-preview Viewer frame: Support Playback contract Exact preview / preview-full.mp4, Timeline preview No audio, screenshot /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, Viewer center mean_rgb=(160.97,189.02,214.86), near_black_pct=0.0000. Prior native visual checks include the US-055 computer-use pass for Agent Start Agent Session, toolbar Clip, Timeline.Clip.V1.CLP_0001, ClipInspector.AskCodexButton, ClipInspector.NoteDraftEditor, ClipInspector.HandoffInstructionDraftEditor, and ClipInspector.EditorAnnotationStatus. Latest US-061 live model check was CLI/runtime on /tmp because it intentionally avoided writing real project artifacts; prior Media tab AX checks already covered MediaPanel.MarlinEvaluationRecommendation, MarlinPreferenceRecommendation, MarlinQueueNextAction, MarlinRepresentativeNextAction, MarlinRepresentativeBucket.*, MarlinQueueItem.*, MarlinEvaluationRunStatus, RunMarlinEvaluationButton, ApplyMarlinPreferenceButton, MarlinEvaluationCommandLine, and MarlinEvaluationArtifactPath. Prior checks covered ProjectShelf.us064-native-handoff-smoke-20260623, ProjectShelf.us064-native-packet-smoke-20260623, MediaPanel.ExportPremiereXMLButton, ExportEditorPacketButton, RevealEditorPacketButton, ProjectShelf.us063-native-render-smoke-20260623, MediaPanel.RenderFinalPackageButton, ProjectShelf.us062-audio-story-smoke, MediaPanel.BuildAudioStoryGraphButton, ProjectShelf.NewProject, ProjectInitializer fields/buttons, source-folder panel Link Source, MediaPanel Synthetic/Proxy/Smoke controls, MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -519,7 +519,7 @@
         <x:v>Latest US-045 fix/verification</x:v>
       </x:c>
       <x:c r="B13" s="19" t="str">
-        <x:v>ProjectMediaResolver still skips known-short timeline-preview candidates beyond their duration, and runtime/preview/segment-renderer.ts now clamps generated extracts to timeline_duration_frames/fps. Verification: ProjectMediaResolverTests 25/0, preview.test.ts 29/0, npm run build, build_and_run --verify, ffprobe 75.914714s for ena-promo-ai preview-full.mp4, playback-contract exact hash f3bc3e6fef222e1a, and computer-use Viewer evidence showing Exact preview / preview-full.mp4.</x:v>
+        <x:v>ProjectMediaResolver still skips known-short timeline-preview candidates beyond their duration, and runtime/preview/segment-renderer.ts now clamps generated extracts to timeline_duration_frames/fps. Verification: ProjectMediaResolverTests 25/0, preview.test.ts 29/0, npm run build, build_and_run --verify, ffprobe 75.914714s for ena-promo-ai preview-full.mp4, playback-contract exact hash f3bc3e6fef222e1a, and fresh computer-use Viewer evidence showing Exact preview / preview-full.mp4 with screenshot center near_black_pct=0.0000.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 now has native exact preview evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-061 is promoted for runtime/model/mock/native AX and a live non-mock single-source Marlin completion on a representative-source fixture; the full multi-source live batch and repo-level Marlin-first preference promotion remain pending evidence gates. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 now has native fresh-launch exact-preview pixel evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-061 is promoted for runtime/model/mock/native AX and a live non-mock single-source Marlin completion on a representative-source fixture; the full multi-source live batch and repo-level Marlin-first preference promotion remain pending evidence gates. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1739,10 +1739,10 @@
         <x:v>Launch VideoOSStudio, select ax1-participant-voices-20260401 and projects with missing or proxy-needed media, inspect D4887.MP4 in Viewer, compare timeline source time against synthetic, preview-editor, and real rendered media duration, confirm Source/Synthetic/Proxy/Missing/Timeline preview and nil-media diagnostics, run synthetic-to-real relink, confirm Viewer diagnostic action IDs and button wiring, compare ax1, ena-promo-ai, lively-alt-vol5, lively-talk-pv, and demo media readiness, verify exact/legacy/stale playback contracts, verify latest 09_output/*.mp4 fallback excludes raw sidecars and yields Timeline preview, verify short preview-editor files are skipped at later playheads, verify Program Viewer prefers an exact generated preview before a direct source clip, verify paused poster-frame generation for playable timeline previews, run Swift build/tests, inspect media readiness/logs, confirm ena-promo-ai direct media is nonblank and AVFoundation-playable, and capture visible screen evidence when screen capture is available.</x:v>
       </x:c>
       <x:c r="G46" s="26" t="str">
-        <x:v>Runtime/native player, timeline-preview priority, paused poster-frame, duration-aware short-preview fallback, and ena-promo-ai exact preview pass; AX-1 exact promotion still pending</x:v>
+        <x:v>Native Viewer pixel/exact preview pass; AX-1 exact promotion still pending</x:v>
       </x:c>
       <x:c r="H46" s="11" t="str">
-        <x:v>AX-1 resolves the first program clip to the real 331.335s D4887 source, ffmpeg extracted a nonblank interview frame at 14.88s, and AVFoundation/CoreMedia logs report ReadyForPlayback plus first video frame enqueued. The Viewer falls back to timeline preview artifacts, Web-era preview-editor files, rough-cut/final outputs, latest normal 09_output/*.mp4 rendered output, and packaged outputs when source media is offline. ProjectMediaResolver skips known-short timeline preview candidates when the current playhead exceeds their media duration. At 00:01:14, AX-1 no longer stays on the 8.007633s preview-editor-1775121573933.mp4; the Viewer subtitle changes to timeline-preview / ax1_promo_v5.mp4 and remains visually nonblack. ffprobe reports ax1_promo_v5.mp4 duration 75.000000. For ena-promo-ai, media-status returned assets=89 ready=89 missing=0, compile-run regenerated an exact timeline hash f3bc3e6fef222e1a, and preview-full generation exposed a renderer bug: the script reported 76.1s while ffprobe saw 93.581380s because source range duration exceeded timeline clip duration. runtime/preview/segment-renderer.ts now clamps extraction to timeline duration. After regeneration, ffprobe reports preview-full.mp4 duration 75.914714s for 76.083333s timeline content; playback-contract-status is exact; computer-use selected ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. ProjectMediaResolverTests executed 25 tests with 0 failures; preview.test.ts executed 29 tests with 0 failures; npm run build passed; build_and_run.sh --verify relaunched VideoOSStudio. AX-1 remains legacy_manifest rather than approval-grade exact preview.</x:v>
+        <x:v>AX-1 resolves the first program clip to the real 331.335s D4887 source, ffmpeg extracted a nonblank interview frame at 14.88s, and AVFoundation/CoreMedia logs report ReadyForPlayback plus first video frame enqueued. The Viewer falls back to timeline preview artifacts, Web-era preview-editor files, rough-cut/final outputs, latest normal 09_output/*.mp4 rendered output, and packaged outputs when source media is offline. ProjectMediaResolver skips known-short timeline preview candidates when the current playhead exceeds their media duration. At 00:01:14, AX-1 no longer stays on the 8.007633s preview-editor-1775121573933.mp4; the Viewer subtitle changes to timeline-preview / ax1_promo_v5.mp4 and remains visually nonblack. ffprobe reports ax1_promo_v5.mp4 duration 75.000000. For ena-promo-ai, media-status returned assets=89 ready=89 missing=0, compile-run regenerated an exact timeline hash f3bc3e6fef222e1a, and preview-full generation exposed a renderer bug: the script reported 76.1s while ffprobe saw 93.581380s because source range duration exceeded timeline clip duration. runtime/preview/segment-renderer.ts now clamps extraction to timeline duration. After regeneration, ffprobe reports preview-full.mp4 duration 75.914714s for 76.083333s timeline content; playback-contract-status is exact. Fresh launch retest on 2026-06-23 used computer-use to select ProjectShelf.ena-promo-ai; the Viewer showed Exact preview / preview-full.mp4 with visible video, screenshot /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png was 3.6M, and Pillow pixel stats for the Viewer center reported mean_rgb=(160.97,189.02,214.86) with near_black_pct=0.0000. ProjectMediaResolverTests executed 25 tests with 0 failures; preview.test.ts executed 29 tests with 0 failures; npm run build passed; build_and_run.sh --verify relaunched VideoOSStudio. AX-1 remains legacy_manifest rather than approval-grade exact preview.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="48" customHeight="1">
@@ -3320,10 +3320,10 @@
         <x:v>Replace the direct AVPlayerLayer NSView with AVKit AVPlayerView, keep the existing timeline sync and muted-video/audio-monitor split, and retain a separate visual/manual confirmation gate because this desktop session cannot capture the app window reliably.</x:v>
       </x:c>
       <x:c r="H35" s="26" t="str">
-        <x:v>swift build --product VideoOSStudio passed; ProjectMediaResolverTests and TimelineDocumentTests passed; ./script/build_and_run.sh --verify launched PID 77637; unified logs showed AVKit AVPlayerView setPlayer, ReadyForPlayback, and Did enqueue first frame. Full-screen capture was still black and screencapture -l returned could not create image from window.</x:v>
+        <x:v>swift build --product VideoOSStudio passed; ProjectMediaResolverTests and TimelineDocumentTests passed; ./script/build_and_run.sh --verify launched PID 77637; unified logs showed AVKit AVPlayerView setPlayer, ReadyForPlayback, and Did enqueue first frame. Later fresh-launch computer-use capture selected ena-promo-ai and the Viewer center measured near_black_pct=0.0000.</x:v>
       </x:c>
       <x:c r="I35" s="11" t="str">
-        <x:v>Mitigated; visual pending</x:v>
+        <x:v>Fixed; TL-229 native pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="48" customHeight="1">
@@ -3349,10 +3349,10 @@
         <x:v>Added ProjectMediaReference viewerModeLabel/viewerStartSeconds/viewerNeedsAttention, switched ViewerSurface and TransportBar to show Synthetic preview / Proxy preview / Missing media diagnostics, kept synthetic preview playback anchored at 0s, then added --include-synthetic relink so real media can replace generated placeholders.</x:v>
       </x:c>
       <x:c r="H36" s="26" t="str">
-        <x:v>ProjectMediaResolverTests cover direct source, proxy, synthetic viewer modes, synthetic viewerStartSeconds=0, and explicit synthetic replacement. AX-1 relink now points D4887/D4892 at real source media and current full swift test passed 192 tests.</x:v>
+        <x:v>ProjectMediaResolverTests cover direct source, proxy, synthetic viewer modes, synthetic viewerStartSeconds=0, and explicit synthetic replacement. AX-1 relink now points D4887/D4892 at real source media, and the later exact-preview pixel pass confirms Viewer mode/transport labels render with visible video.</x:v>
       </x:c>
       <x:c r="I36" s="11" t="str">
-        <x:v>Fixed; visual pending</x:v>
+        <x:v>Fixed; TL-229 native visual pass</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="48" customHeight="1">
@@ -3465,10 +3465,10 @@
         <x:v>Added ProjectMediaResolver.resolveTimelinePreview to prefer 05_timeline/previews/preview.json artifacts, then preview-full.mp4, in-range preview-first30s.mp4, and 09_output/rough-cut.mp4. StudioViewModel now falls back to that reference when program source video is not playback-ready, and Viewer labels/plays Timeline preview with audio fallback.</x:v>
       </x:c>
       <x:c r="H40" s="26" t="str">
-        <x:v>lively-talk-pv playback-contract-status returned state=exact while media-status returned ready=0 missing=21 and source-map brokenEntries=21; ProjectMediaResolverTests now cover exact preview artifact and rough-cut fallback; swift build --target VideoOSStudio passed; ./script/build_and_run.sh --verify launched PID 81756; full swift test executed 197 tests with 0 failures.</x:v>
+        <x:v>lively-talk-pv playback-contract-status returned state=exact while media-status returned ready=0 missing=21 and source-map brokenEntries=21; ProjectMediaResolverTests now cover exact preview artifact and rough-cut fallback; swift build --target VideoOSStudio passed; ./script/build_and_run.sh --verify launched PID 81756; full swift test executed 197 tests with 0 failures. TL-229 confirms the exact preview path displays visible pixels for ena-promo-ai.</x:v>
       </x:c>
       <x:c r="I40" s="11" t="str">
-        <x:v>Fixed; visual pending</x:v>
+        <x:v>Fixed; TL-229 native visual pass</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="48" customHeight="1">
@@ -3610,10 +3610,10 @@
         <x:v>Extended timeline preview resolution to include the latest preview-editor-*.mp4 before rendered fallbacks, then 09_output/final.mp4, 07_package/video/final.mp4, and 07_package/assembly.mp4. Marked these sources as Timeline preview so Viewer diagnostics stay consistent.</x:v>
       </x:c>
       <x:c r="H45" s="26" t="str">
-        <x:v>ffprobe confirmed AX-1 preview-editor-1775121573933.mp4 is playable H.264/AAC; ProjectMediaResolverTests now cover legacy editor preview, final render, and packaged assembly fallbacks; full swift test executed 205 tests with 0 failures; build_and_run verify launched VideoOSStudio PID 6717.</x:v>
+        <x:v>ffprobe confirmed AX-1 preview-editor-1775121573933.mp4 is playable H.264/AAC; ProjectMediaResolverTests now cover legacy editor preview, final render, and packaged assembly fallbacks; full swift test executed 205 tests with 0 failures; build_and_run verify launched VideoOSStudio PID 6717. Later TL-205 and TL-229 provide native pixel evidence for legacy duration fallback and exact preview playback.</x:v>
       </x:c>
       <x:c r="I45" s="11" t="str">
-        <x:v>Fixed; visual pending</x:v>
+        <x:v>Fixed; TL-229 native visual pass</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="48" customHeight="1">
@@ -3668,10 +3668,10 @@
         <x:v>Replaced the AVKit AVPlayerView wrapper with an explicit NSView containing AVPlayerLayer, set the layer to resizeAspect, laid it out to the container bounds without implicit animation, retained the muted-video plus separate audio-monitor split, and re-seeked after AVPlayerItem.status becomes ready.</x:v>
       </x:c>
       <x:c r="H47" s="26" t="str">
-        <x:v>swift build passed; swift test --filter ProjectMediaResolverTests executed 14 tests with 0 failures; ./script/build_and_run.sh --verify exited 0 and relaunched VideoOSStudio with an onscreen 1180x812 CGWindow. CLI monitor-status showed ax1 and lively-alt-vol5 program clips resolve to exists/video=ready while demo correctly reports missing source files.</x:v>
+        <x:v>swift build passed; swift test --filter ProjectMediaResolverTests executed 14 tests with 0 failures; ./script/build_and_run.sh --verify exited 0 and relaunched VideoOSStudio with an onscreen 1180x812 CGWindow. CLI monitor-status showed ax1 and lively-alt-vol5 program clips resolve to exists/video=ready while demo correctly reports missing source files. TL-229 fresh-launch pixel stats now confirm the explicit AVPlayerLayer path paints nonblack Viewer pixels.</x:v>
       </x:c>
       <x:c r="I47" s="11" t="str">
-        <x:v>Fixed; visual capture pending</x:v>
+        <x:v>Fixed; TL-229 native pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="48" customHeight="1">
@@ -3842,10 +3842,10 @@
         <x:v>Added ProjectMediaResolver.preferredProgramMedia, changed programMediaReference to prefer a playable timeline preview before source media, and made ViewerSurface use timeline-preview media for audio when the selected video media is a timeline preview.</x:v>
       </x:c>
       <x:c r="H53" s="26" t="str">
-        <x:v>ProjectMediaResolverTests executed 23 tests with 0 failures, including timeline-preview-before-source and source fallback coverage; swift build --target VideoOSStudio passed; git diff --check passed; build_and_run --verify relaunched VideoOSStudio PID 25435 with a visible 1180x812 CGWindow.</x:v>
+        <x:v>ProjectMediaResolverTests executed 23 tests with 0 failures, including timeline-preview-before-source and source fallback coverage; swift build --target VideoOSStudio passed; git diff --check passed; build_and_run --verify relaunched VideoOSStudio PID 25435 with a visible 1180x812 CGWindow. TL-229 shows the Program Viewer selecting exact preview / preview-full.mp4 and rendering nonblack pixels.</x:v>
       </x:c>
       <x:c r="I53" s="11" t="str">
-        <x:v>Mitigated; pixel capture pending</x:v>
+        <x:v>Fixed; TL-229 native pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="48" customHeight="1">
@@ -3929,10 +3929,10 @@
         <x:v>Added a poster CALayer above the AVPlayerLayer. The coordinator now generates an AVAssetImageGenerator frame asynchronously at the current Viewer start time, falls back to time zero, shows that poster while paused, and hides it during playback.</x:v>
       </x:c>
       <x:c r="H56" s="26" t="str">
-        <x:v>AVAssetImageGenerator generated a 1600x899 poster frame from projects/lively-talk-pv/09_output/rough-cut.mp4 at 1.5s; ProjectMediaResolverTests executed 23 tests with 0 failures; swift build --target VideoOSStudio passed; git diff --check on ViewerViews.swift passed; build_and_run --verify relaunched VideoOSStudio PID 31750 with a visible 1180x812 CGWindow.</x:v>
+        <x:v>AVAssetImageGenerator generated a 1600x899 poster frame from projects/lively-talk-pv/09_output/rough-cut.mp4 at 1.5s; ProjectMediaResolverTests executed 23 tests with 0 failures; swift build --target VideoOSStudio passed; git diff --check on ViewerViews.swift passed; build_and_run --verify relaunched VideoOSStudio PID 31750 with a visible 1180x812 CGWindow. TL-229 confirms the paused 00:00:00 exact-preview Viewer surface is nonblack on fresh launch.</x:v>
       </x:c>
       <x:c r="I56" s="11" t="str">
-        <x:v>Mitigated; pixel capture pending</x:v>
+        <x:v>Fixed; TL-229 paused-frame pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="48" customHeight="1">
@@ -4045,10 +4045,10 @@
         <x:v>Updated VideoOSStudioApp.ensureUsableMainWindowFrame so launch/reopen paths require enough visible area on the origin-zero primary display, while normal manual window moves can still stay on any usable display. The guard runs on launch and delayed focus retries.</x:v>
       </x:c>
       <x:c r="H60" s="26" t="str">
-        <x:v>After forcing the app window back to {-1920,-555}, build_and_run --verify relaunched VideoOSStudio PID 99006 and System Events/CGWindow both reported the corrected main-display frame at about {221,119} with size 1240x780. swift build --target VideoOSStudio, focused Marlin tests, and git diff --check passed.</x:v>
+        <x:v>After forcing the app window back to {-1920,-555}, build_and_run --verify relaunched VideoOSStudio PID 99006 and System Events/CGWindow both reported the corrected main-display frame at about {221,119} with size 1240x780. swift build --target VideoOSStudio, focused Marlin tests, and git diff --check passed. TL-229 fresh-launch evidence confirms the visible primary-display window shows nonblack Viewer pixels.</x:v>
       </x:c>
       <x:c r="I60" s="11" t="str">
-        <x:v>Mitigated; pixel Viewer capture still pending</x:v>
+        <x:v>Fixed; TL-229 fresh-launch pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="48" customHeight="1">
@@ -8890,23 +8890,43 @@
       </x:c>
     </x:row>
     <x:row r="229" ht="48" customHeight="1">
-      <x:c r="A229" s="12" t="str">
+      <x:c r="A229" s="10" t="str">
         <x:v>TL-228</x:v>
       </x:c>
-      <x:c r="B229" s="27" t="str">
+      <x:c r="B229" s="26" t="str">
         <x:v>US-061</x:v>
       </x:c>
-      <x:c r="C229" s="27" t="str">
+      <x:c r="C229" s="26" t="str">
         <x:v>Live Marlin single-source completion</x:v>
       </x:c>
-      <x:c r="D229" s="27" t="str">
+      <x:c r="D229" s="26" t="str">
         <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
       </x:c>
-      <x:c r="E229" s="27" t="str">
+      <x:c r="E229" s="26" t="str">
         <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
       </x:c>
-      <x:c r="F229" s="13" t="str">
+      <x:c r="F229" s="11" t="str">
         <x:v>Live single-source pass; full representative batch pending</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" ht="48" customHeight="1">
+      <x:c r="A230" s="12" t="str">
+        <x:v>TL-229</x:v>
+      </x:c>
+      <x:c r="B230" s="27" t="str">
+        <x:v>US-045</x:v>
+      </x:c>
+      <x:c r="C230" s="27" t="str">
+        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+      </x:c>
+      <x:c r="D230" s="27" t="str">
+        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+      </x:c>
+      <x:c r="E230" s="27" t="str">
+        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+      </x:c>
+      <x:c r="F230" s="13" t="str">
+        <x:v>Native fresh-launch pixel pass</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R113da024f1ed459a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R34a6a473cf2b4d0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R11a812ee1e974cd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="Reed5ae96a68b4809"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Rfe484e6267bb4c80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R123397fa397742fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R7fb2375d692b4c34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Rd9e7d816a4e545cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="Ra4af3d6e98f64d17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R4cf2b425d7a5477b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-045 loop fresh-launched VideoOSStudio, selected ena-promo-ai, confirmed playback-contract exact / approvalGrade=true with hash f3bc3e6fef222e1a and media-status assets=89 ready=89 missing=0, captured /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and measured Viewer center near_black_pct=0.0000. Prior US-061 loop ran a live non-mock Marlin single-source completion on a /tmp lively-alt-vol5-derived fixture with requestTimeoutMs=900000 and VOS_MARLIN_PROXY_MAX_WIDTH=384; marlin-evaluate wrote marlin_events.json, marlin-status reported events=3/findResults=4/coverage=1.00/canPreferMarlin=true for the fixture, segments gained marlin_temporal_semantics peak provenance, index-rebuild produced 9 search documents, and git status stayed clean. Prior US-055 Ask Codex proposal, US-064 Editor Handoff export, US-063 Render Final Package, US-062 Audio Story Graph, US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-055 Save/Clear, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
+        <x:v>Latest US-045 loop recompiled AX-1, changing playback-contract-status from legacy_manifest / approvalGrade=false to exact / approvalGrade=true with hash 171378fe2bfe3a7c, selected AX-1 in VideoOSStudio, captured /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and measured viewer_person_actual near_black_pct=0.0004. The preceding US-045 loop fresh-launched VideoOSStudio, selected ena-promo-ai, confirmed playback-contract exact / approvalGrade=true with hash f3bc3e6fef222e1a and media-status assets=89 ready=89 missing=0, captured /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and measured Viewer center near_black_pct=0.0000. Prior US-061 loop ran a live non-mock Marlin single-source completion on a /tmp lively-alt-vol5-derived fixture with requestTimeoutMs=900000 and VOS_MARLIN_PROXY_MAX_WIDTH=384; marlin-evaluate wrote marlin_events.json, marlin-status reported events=3/findResults=4/coverage=1.00/canPreferMarlin=true for the fixture, segments gained marlin_temporal_semantics peak provenance, index-rebuild produced 9 search documents, and git status stayed clean. Prior US-055 Ask Codex proposal, US-064 Editor Handoff export, US-063 Render Final Package, US-062 Audio Story Graph, US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-055 Save/Clear, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest native visual check is the US-045 computer-use pass selecting ProjectShelf.ena-promo-ai and confirming a visible exact-preview Viewer frame: Support Playback contract Exact preview / preview-full.mp4, Timeline preview No audio, screenshot /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, Viewer center mean_rgb=(160.97,189.02,214.86), near_black_pct=0.0000. Prior native visual checks include the US-055 computer-use pass for Agent Start Agent Session, toolbar Clip, Timeline.Clip.V1.CLP_0001, ClipInspector.AskCodexButton, ClipInspector.NoteDraftEditor, ClipInspector.HandoffInstructionDraftEditor, and ClipInspector.EditorAnnotationStatus. Latest US-061 live model check was CLI/runtime on /tmp because it intentionally avoided writing real project artifacts; prior Media tab AX checks already covered MediaPanel.MarlinEvaluationRecommendation, MarlinPreferenceRecommendation, MarlinQueueNextAction, MarlinRepresentativeNextAction, MarlinRepresentativeBucket.*, MarlinQueueItem.*, MarlinEvaluationRunStatus, RunMarlinEvaluationButton, ApplyMarlinPreferenceButton, MarlinEvaluationCommandLine, and MarlinEvaluationArtifactPath. Prior checks covered ProjectShelf.us064-native-handoff-smoke-20260623, ProjectShelf.us064-native-packet-smoke-20260623, MediaPanel.ExportPremiereXMLButton, ExportEditorPacketButton, RevealEditorPacketButton, ProjectShelf.us063-native-render-smoke-20260623, MediaPanel.RenderFinalPackageButton, ProjectShelf.us062-audio-story-smoke, MediaPanel.BuildAudioStoryGraphButton, ProjectShelf.NewProject, ProjectInitializer fields/buttons, source-folder panel Link Source, MediaPanel Synthetic/Proxy/Smoke controls, MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest native visual check is the US-045 computer-use pass selecting ProjectShelf.ax1-participant-voices-20260401 and confirming a visible exact-preview Viewer frame: Support Playback contract Exact preview / preview-editor-1775121573933.mp4, Timeline preview D4887.MP4, screenshot /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, viewer_person_actual mean_rgb=(144.62,141.42,149.8), near_black_pct=0.0004. The preceding native visual check selected ProjectShelf.ena-promo-ai and confirmed Support Playback contract Exact preview / preview-full.mp4, Timeline preview No audio, screenshot /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, Viewer center mean_rgb=(160.97,189.02,214.86), near_black_pct=0.0000. Prior native visual checks include the US-055 computer-use pass for Agent Start Agent Session, toolbar Clip, Timeline.Clip.V1.CLP_0001, ClipInspector.AskCodexButton, ClipInspector.NoteDraftEditor, ClipInspector.HandoffInstructionDraftEditor, and ClipInspector.EditorAnnotationStatus. Latest US-061 live model check was CLI/runtime on /tmp because it intentionally avoided writing real project artifacts; prior Media tab AX checks already covered MediaPanel.MarlinEvaluationRecommendation, MarlinPreferenceRecommendation, MarlinQueueNextAction, MarlinRepresentativeNextAction, MarlinRepresentativeBucket.*, MarlinQueueItem.*, MarlinEvaluationRunStatus, RunMarlinEvaluationButton, ApplyMarlinPreferenceButton, MarlinEvaluationCommandLine, and MarlinEvaluationArtifactPath. Prior checks covered ProjectShelf.us064-native-handoff-smoke-20260623, ProjectShelf.us064-native-packet-smoke-20260623, MediaPanel.ExportPremiereXMLButton, ExportEditorPacketButton, RevealEditorPacketButton, ProjectShelf.us063-native-render-smoke-20260623, MediaPanel.RenderFinalPackageButton, ProjectShelf.us062-audio-story-smoke, MediaPanel.BuildAudioStoryGraphButton, ProjectShelf.NewProject, ProjectInitializer fields/buttons, source-folder panel Link Source, MediaPanel Synthetic/Proxy/Smoke controls, MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -519,7 +519,7 @@
         <x:v>Latest US-045 fix/verification</x:v>
       </x:c>
       <x:c r="B13" s="19" t="str">
-        <x:v>ProjectMediaResolver still skips known-short timeline-preview candidates beyond their duration, and runtime/preview/segment-renderer.ts now clamps generated extracts to timeline_duration_frames/fps. Verification: ProjectMediaResolverTests 25/0, preview.test.ts 29/0, npm run build, build_and_run --verify, ffprobe 75.914714s for ena-promo-ai preview-full.mp4, playback-contract exact hash f3bc3e6fef222e1a, and fresh computer-use Viewer evidence showing Exact preview / preview-full.mp4 with screenshot center near_black_pct=0.0000.</x:v>
+        <x:v>ProjectMediaResolver still skips known-short timeline-preview candidates beyond their duration, and runtime/preview/segment-renderer.ts now clamps generated extracts to timeline_duration_frames/fps. Verification: ProjectMediaResolverTests 25/0, preview.test.ts 29/0, npm run build, build_and_run --verify, ffprobe 75.914714s for ena-promo-ai preview-full.mp4, ena playback-contract exact hash f3bc3e6fef222e1a, AX-1 playback-contract exact hash 171378fe2bfe3a7c, fresh computer-use Viewer evidence for ena-promo-ai with near_black_pct=0.0000, and fresh AX-1 Viewer evidence with viewer_person_actual near_black_pct=0.0004.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 now has native fresh-launch exact-preview pixel evidence on ena-promo-ai via preview-full.mp4, while AX-1 still reports legacy_manifest rather than approval-grade exact preview. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-061 is promoted for runtime/model/mock/native AX and a live non-mock single-source Marlin completion on a representative-source fixture; the full multi-source live batch and repo-level Marlin-first preference promotion remain pending evidence gates. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-061 is promoted for runtime/model/mock/native AX and a live non-mock single-source Marlin completion on a representative-source fixture; the full multi-source live batch and repo-level Marlin-first preference promotion remain pending evidence gates. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1739,10 +1739,10 @@
         <x:v>Launch VideoOSStudio, select ax1-participant-voices-20260401 and projects with missing or proxy-needed media, inspect D4887.MP4 in Viewer, compare timeline source time against synthetic, preview-editor, and real rendered media duration, confirm Source/Synthetic/Proxy/Missing/Timeline preview and nil-media diagnostics, run synthetic-to-real relink, confirm Viewer diagnostic action IDs and button wiring, compare ax1, ena-promo-ai, lively-alt-vol5, lively-talk-pv, and demo media readiness, verify exact/legacy/stale playback contracts, verify latest 09_output/*.mp4 fallback excludes raw sidecars and yields Timeline preview, verify short preview-editor files are skipped at later playheads, verify Program Viewer prefers an exact generated preview before a direct source clip, verify paused poster-frame generation for playable timeline previews, run Swift build/tests, inspect media readiness/logs, confirm ena-promo-ai direct media is nonblank and AVFoundation-playable, and capture visible screen evidence when screen capture is available.</x:v>
       </x:c>
       <x:c r="G46" s="26" t="str">
-        <x:v>Native Viewer pixel/exact preview pass; AX-1 exact promotion still pending</x:v>
+        <x:v>Native Viewer pixel/exact preview pass</x:v>
       </x:c>
       <x:c r="H46" s="11" t="str">
-        <x:v>AX-1 resolves the first program clip to the real 331.335s D4887 source, ffmpeg extracted a nonblank interview frame at 14.88s, and AVFoundation/CoreMedia logs report ReadyForPlayback plus first video frame enqueued. The Viewer falls back to timeline preview artifacts, Web-era preview-editor files, rough-cut/final outputs, latest normal 09_output/*.mp4 rendered output, and packaged outputs when source media is offline. ProjectMediaResolver skips known-short timeline preview candidates when the current playhead exceeds their media duration. At 00:01:14, AX-1 no longer stays on the 8.007633s preview-editor-1775121573933.mp4; the Viewer subtitle changes to timeline-preview / ax1_promo_v5.mp4 and remains visually nonblack. ffprobe reports ax1_promo_v5.mp4 duration 75.000000. For ena-promo-ai, media-status returned assets=89 ready=89 missing=0, compile-run regenerated an exact timeline hash f3bc3e6fef222e1a, and preview-full generation exposed a renderer bug: the script reported 76.1s while ffprobe saw 93.581380s because source range duration exceeded timeline clip duration. runtime/preview/segment-renderer.ts now clamps extraction to timeline duration. After regeneration, ffprobe reports preview-full.mp4 duration 75.914714s for 76.083333s timeline content; playback-contract-status is exact. Fresh launch retest on 2026-06-23 used computer-use to select ProjectShelf.ena-promo-ai; the Viewer showed Exact preview / preview-full.mp4 with visible video, screenshot /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png was 3.6M, and Pillow pixel stats for the Viewer center reported mean_rgb=(160.97,189.02,214.86) with near_black_pct=0.0000. ProjectMediaResolverTests executed 25 tests with 0 failures; preview.test.ts executed 29 tests with 0 failures; npm run build passed; build_and_run.sh --verify relaunched VideoOSStudio. AX-1 remains legacy_manifest rather than approval-grade exact preview.</x:v>
+        <x:v>AX-1 resolves the first program clip to the real 331.335s D4887 source, ffmpeg extracted a nonblank interview frame at 14.88s, and AVFoundation/CoreMedia logs report ReadyForPlayback plus first video frame enqueued. The Viewer falls back to timeline preview artifacts, Web-era preview-editor files, rough-cut/final outputs, latest normal 09_output/*.mp4 rendered output, and packaged outputs when source media is offline. ProjectMediaResolver skips known-short timeline preview candidates when the current playhead exceeds their media duration. At 00:01:14, AX-1 no longer stays on the 8.007633s preview-editor-1775121573933.mp4; the Viewer subtitle changes to timeline-preview / ax1_promo_v5.mp4 and remains visually nonblack. ffprobe reports ax1_promo_v5.mp4 duration 75.000000. For ena-promo-ai, media-status returned assets=89 ready=89 missing=0, compile-run regenerated an exact timeline hash f3bc3e6fef222e1a, and preview-full generation exposed a renderer bug: the script reported 76.1s while ffprobe saw 93.581380s because source range duration exceeded timeline clip duration. runtime/preview/segment-renderer.ts now clamps extraction to timeline duration. After regeneration, ffprobe reports preview-full.mp4 duration 75.914714s for 76.083333s timeline content; playback-contract-status is exact. Fresh launch retest on 2026-06-23 used computer-use to select ProjectShelf.ena-promo-ai; the Viewer showed Exact preview / preview-full.mp4 with visible video, screenshot /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png was 3.6M, and Pillow pixel stats for the Viewer center reported mean_rgb=(160.97,189.02,214.86) with near_black_pct=0.0000. AX-1 was then recompiled through videoos-studio-cli compile-run, changing playback-contract-status from legacy_manifest approvalGrade=false to exact approvalGrade=true with timelineHash=171378fe2bfe3a7c and manifestBaseTimelineHash=171378fe2bfe3a7c while leaving git status clean. Native AX-1 UI showed Exact preview / preview-editor-1775121573933.mp4 and Timeline preview D4887.MP4 with a visible interview frame; screenshot /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png was 3.5M, viewer_person_actual mean_rgb=(144.62,141.42,149.8), and near_black_pct=0.0004. ProjectMediaResolverTests executed 25 tests with 0 failures; preview.test.ts executed 29 tests with 0 failures; npm run build passed; build_and_run.sh --verify relaunched VideoOSStudio.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="48" customHeight="1">
@@ -8910,23 +8910,43 @@
       </x:c>
     </x:row>
     <x:row r="230" ht="48" customHeight="1">
-      <x:c r="A230" s="12" t="str">
+      <x:c r="A230" s="10" t="str">
         <x:v>TL-229</x:v>
       </x:c>
-      <x:c r="B230" s="27" t="str">
+      <x:c r="B230" s="26" t="str">
         <x:v>US-045</x:v>
       </x:c>
-      <x:c r="C230" s="27" t="str">
+      <x:c r="C230" s="26" t="str">
         <x:v>Native exact preview fresh-launch pixel pass</x:v>
       </x:c>
-      <x:c r="D230" s="27" t="str">
+      <x:c r="D230" s="26" t="str">
         <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
       </x:c>
-      <x:c r="E230" s="27" t="str">
+      <x:c r="E230" s="26" t="str">
         <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
       </x:c>
-      <x:c r="F230" s="13" t="str">
+      <x:c r="F230" s="11" t="str">
         <x:v>Native fresh-launch pixel pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" ht="48" customHeight="1">
+      <x:c r="A231" s="12" t="str">
+        <x:v>TL-230</x:v>
+      </x:c>
+      <x:c r="B231" s="27" t="str">
+        <x:v>US-045</x:v>
+      </x:c>
+      <x:c r="C231" s="27" t="str">
+        <x:v>AX-1 exact preview promotion and pixel pass</x:v>
+      </x:c>
+      <x:c r="D231" s="27" t="str">
+        <x:v>Run videoos-studio-cli compile-run on projects/ax1-participant-voices-20260401, confirm playback-contract-status, select ProjectShelf.ax1-participant-voices-20260401 in VideoOSStudio, capture /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and run Retina-coordinate pixel statistics on the Viewer region.</x:v>
+      </x:c>
+      <x:c r="E231" s="27" t="str">
+        <x:v>Before compile, playback-contract-status returned legacy_manifest and approvalGrade=false. compile-run completed with exitCode=0, timeline compiled, indexDocuments=492, and git status stayed clean. After compile, playback-contract-status returned state=exact, approvalGrade=true, timelineHash=171378fe2bfe3a7c, and manifestBaseTimelineHash=171378fe2bfe3a7c. Native Viewer showed Exact preview / preview-editor-1775121573933.mp4 and Timeline preview D4887.MP4 with a visible interview frame. Screenshot was 3.5M; viewer_person_actual mean_rgb=(144.62,141.42,149.8) and near_black_pct=0.0004, while left pillarbox near_black_pct=1.0000 as expected.</x:v>
+      </x:c>
+      <x:c r="F231" s="13" t="str">
+        <x:v>Native AX-1 exact/pixel pass</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R123397fa397742fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R7fb2375d692b4c34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Rd9e7d816a4e545cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="Ra4af3d6e98f64d17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R4cf2b425d7a5477b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R7b1005c622094fab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R8b952772061f446f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Rd5875a18fd134e0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R6b1141a8149f423a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Re13445cf9b144dd1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -439,7 +439,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 16:35 JST</x:v>
+        <x:v>2026-06-23 18:24 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -479,7 +479,7 @@
         <x:v>Issues tracked</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="220" customHeight="1">
@@ -487,7 +487,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build includes ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, ProjectInitializer.CancelButton, repo-root source-folder panel startup, explicit Project creation status text for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix. Latest native build/run verified VideoOSStudio from the repo root.</x:v>
+        <x:v>Latest code build includes ProjectPanel.ActionQueueStatus / ActionQueueCommand.&lt;id&gt; / ActionQueueRunButton.&lt;id&gt; / ActionQueueCopyButton.&lt;id&gt; for US-050, ProjectInitializer.ProjectIDField/CreateButton/CancelButton for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix. Latest native build/run verified VideoOSStudio from the repo root.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-045 loop recompiled AX-1, changing playback-contract-status from legacy_manifest / approvalGrade=false to exact / approvalGrade=true with hash 171378fe2bfe3a7c, selected AX-1 in VideoOSStudio, captured /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and measured viewer_person_actual near_black_pct=0.0004. The preceding US-045 loop fresh-launched VideoOSStudio, selected ena-promo-ai, confirmed playback-contract exact / approvalGrade=true with hash f3bc3e6fef222e1a and media-status assets=89 ready=89 missing=0, captured /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and measured Viewer center near_black_pct=0.0000. Prior US-061 loop ran a live non-mock Marlin single-source completion on a /tmp lively-alt-vol5-derived fixture with requestTimeoutMs=900000 and VOS_MARLIN_PROXY_MAX_WIDTH=384; marlin-evaluate wrote marlin_events.json, marlin-status reported events=3/findResults=4/coverage=1.00/canPreferMarlin=true for the fixture, segments gained marlin_temporal_semantics peak provenance, index-rebuild produced 9 search documents, and git status stayed clean. Prior US-055 Ask Codex proposal, US-064 Editor Handoff export, US-063 Render Final Package, US-062 Audio Story Graph, US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-055 Save/Clear, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-050 Project readiness/action queue, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
+        <x:v>Latest US-050 loop selected AX-1 in VideoOSStudio, confirmed action-scoped Action Queue AX identifiers, clicked ProjectPanel.ActionQueueRunButton.rough-cut-review, and observed Opening Codex approval gate for Review without approving writes or producing tracked project artifact changes. The preceding US-045 loop recompiled AX-1, changing playback-contract-status from legacy_manifest / approvalGrade=false to exact / approvalGrade=true with hash 171378fe2bfe3a7c, selected AX-1 in VideoOSStudio, captured /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and measured viewer_person_actual near_black_pct=0.0004. Prior US-061 loop ran a live non-mock Marlin single-source completion on a /tmp lively-alt-vol5-derived fixture with requestTimeoutMs=900000 and VOS_MARLIN_PROXY_MAX_WIDTH=384; marlin-evaluate wrote marlin_events.json, marlin-status reported events=3/findResults=4/coverage=1.00/canPreferMarlin=true for the fixture, segments gained marlin_temporal_semantics peak provenance, index-rebuild produced 9 search documents, and git status stayed clean. Prior US-055 Ask Codex proposal, US-064 Editor Handoff export, US-063 Render Final Package, US-062 Audio Story Graph, US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-055 Save/Clear, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest native visual check is the US-045 computer-use pass selecting ProjectShelf.ax1-participant-voices-20260401 and confirming a visible exact-preview Viewer frame: Support Playback contract Exact preview / preview-editor-1775121573933.mp4, Timeline preview D4887.MP4, screenshot /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, viewer_person_actual mean_rgb=(144.62,141.42,149.8), near_black_pct=0.0004. The preceding native visual check selected ProjectShelf.ena-promo-ai and confirmed Support Playback contract Exact preview / preview-full.mp4, Timeline preview No audio, screenshot /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, Viewer center mean_rgb=(160.97,189.02,214.86), near_black_pct=0.0000. Prior native visual checks include the US-055 computer-use pass for Agent Start Agent Session, toolbar Clip, Timeline.Clip.V1.CLP_0001, ClipInspector.AskCodexButton, ClipInspector.NoteDraftEditor, ClipInspector.HandoffInstructionDraftEditor, and ClipInspector.EditorAnnotationStatus. Latest US-061 live model check was CLI/runtime on /tmp because it intentionally avoided writing real project artifacts; prior Media tab AX checks already covered MediaPanel.MarlinEvaluationRecommendation, MarlinPreferenceRecommendation, MarlinQueueNextAction, MarlinRepresentativeNextAction, MarlinRepresentativeBucket.*, MarlinQueueItem.*, MarlinEvaluationRunStatus, RunMarlinEvaluationButton, ApplyMarlinPreferenceButton, MarlinEvaluationCommandLine, and MarlinEvaluationArtifactPath. Prior checks covered ProjectShelf.us064-native-handoff-smoke-20260623, ProjectShelf.us064-native-packet-smoke-20260623, MediaPanel.ExportPremiereXMLButton, ExportEditorPacketButton, RevealEditorPacketButton, ProjectShelf.us063-native-render-smoke-20260623, MediaPanel.RenderFinalPackageButton, ProjectShelf.us062-audio-story-smoke, MediaPanel.BuildAudioStoryGraphButton, ProjectShelf.NewProject, ProjectInitializer fields/buttons, source-folder panel Link Source, MediaPanel Synthetic/Proxy/Smoke controls, MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest native check is the US-050 computer-use pass selecting ProjectShelf.ax1-participant-voices-20260401, inspecting the Project tab Action Queue, confirming ProjectPanel.ActionQueueRunButton.rough-cut-review / CopyButton.rough-cut-review / RunButton.marlin-default / CopyButton.marlin-default, clicking rough-cut-review Start &amp; Run, and observing Opening Codex approval gate for Review with no approved write. The preceding native visual check selected AX-1 and confirmed a visible exact-preview Viewer frame: Support Playback contract Exact preview / preview-editor-1775121573933.mp4, Timeline preview D4887.MP4, screenshot /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, viewer_person_actual mean_rgb=(144.62,141.42,149.8), near_black_pct=0.0004. Prior native visual checks include the US-055 computer-use pass for Agent Start Agent Session, toolbar Clip, Timeline.Clip.V1.CLP_0001, ClipInspector.AskCodexButton, ClipInspector.NoteDraftEditor, ClipInspector.HandoffInstructionDraftEditor, and ClipInspector.EditorAnnotationStatus. Latest US-061 live model check was CLI/runtime on /tmp because it intentionally avoided writing real project artifacts; prior Media tab AX checks already covered MediaPanel.MarlinEvaluationRecommendation, MarlinPreferenceRecommendation, MarlinQueueNextAction, MarlinRepresentativeNextAction, MarlinRepresentativeBucket.*, MarlinQueueItem.*, MarlinEvaluationRunStatus, RunMarlinEvaluationButton, ApplyMarlinPreferenceButton, MarlinEvaluationCommandLine, and MarlinEvaluationArtifactPath. Prior checks covered ProjectShelf.us064-native-handoff-smoke-20260623, ProjectShelf.us064-native-packet-smoke-20260623, MediaPanel.ExportPremiereXMLButton, ExportEditorPacketButton, RevealEditorPacketButton, ProjectShelf.us063-native-render-smoke-20260623, MediaPanel.RenderFinalPackageButton, ProjectShelf.us062-audio-story-smoke, MediaPanel.BuildAudioStoryGraphButton, ProjectShelf.NewProject, ProjectInitializer fields/buttons, source-folder panel Link Source, MediaPanel Synthetic/Proxy/Smoke controls, MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility and Copy behavior; destructive Open/Start &amp; Run actions remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-061 is promoted for runtime/model/mock/native AX and a live non-mock single-source Marlin completion on a representative-source fixture; the full multi-source live batch and repo-level Marlin-first preference promotion remain pending evidence gates. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility, Copy behavior, stable action-scoped AX identifiers, and rough-cut-review Start &amp; Run stopping at the Codex approval gate; approved workspace-write review execution, Final render Open, and Marlin default Open remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-061 is promoted for runtime/model/mock/native AX and a live non-mock single-source Marlin completion on a representative-source fixture; the full multi-source live batch and repo-level Marlin-first preference promotion remain pending evidence gates. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1860,19 +1860,19 @@
         <x:v>As a native Studio operator, I can see goal coverage, readiness capabilities, pipeline gates, intent, alignment, review, and suggested next actions with runnable/copyable commands.</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>ProjectPanel renders all ProjectStudioGoalStatus and ProjectStudioReadinessStatus capabilities/actionQueue items, pipeline/library/planning/intent/review/source-analysis/compile sections, and delegates actions to StudioViewModel.</x:v>
+        <x:v>ProjectPanel renders all ProjectStudioGoalStatus and ProjectStudioReadinessStatus capabilities/actionQueue items, pipeline/library/planning/intent/review/source-analysis/compile sections, delegates actions to StudioViewModel, and exposes action-scoped status/command/run/copy accessibility identifiers.</x:v>
       </x:c>
       <x:c r="E51" s="26" t="str">
         <x:v>apps/macos-studio/Sources/VideoOSStudio/ProjectInspectorViews.swift:6-323; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1080-1304; apps/macos-studio/Sources/VideoOSStudioCore/ProjectStudioReadinessStatus.swift:148-347</x:v>
       </x:c>
       <x:c r="F51" s="26" t="str">
-        <x:v>Run studio-status, studio-action dry-runs, readiness/status tests, build/run verify, and a safe copy/blocked-action manual pass.</x:v>
+        <x:v>Run studio-status, studio-action dry-runs, readiness/status tests, build/run verify, a safe Copy pass, and one approval-gated Start &amp; Run pass that stops before approving writes.</x:v>
       </x:c>
       <x:c r="G51" s="26" t="str">
-        <x:v>Native readiness/action queue/copy pass; destructive runs pending</x:v>
+        <x:v>Native readiness/action queue/copy/approval-gate pass; approved writes pending</x:v>
       </x:c>
       <x:c r="H51" s="11" t="str">
-        <x:v>studio-status exposed capabilities and actionQueue for ax1 and fumoto-growth; studio-action dry-runs showed needs-search-root and codex-approval-required modes without executing writes; ProjectPanel now shows all capabilities/actions instead of truncating to 5. Latest native Project tab pass on ax1-participant-voices-20260401 showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent, Review, Source Analysis, and Rough Cut Compile; Studio Readiness reported 7/9 partially ready and exposed the action queue. Pressing Copy on the Marlin default gate updated the status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. ProjectStudioReadinessStatusTests and ProjectStudioGoalStatusTests executed 6 tests with 0 failures. Destructive Run/Open/Start &amp; Run actions remain intentionally unclicked.</x:v>
+        <x:v>studio-status exposed capabilities and actionQueue for ax1 and fumoto-growth; studio-action dry-runs showed needs-search-root and codex-approval-required modes without executing writes; ProjectPanel now shows all capabilities/actions instead of truncating to 5. Native Project tab passes on ax1-participant-voices-20260401 showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent, Review, Source Analysis, and Rough Cut Compile; Studio Readiness reported 7/9 partially ready and exposed the action queue. Pressing Copy on the Marlin default gate updated the status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. The latest pass added ProjectPanel.ActionQueueStatus, ActionQueueCommand.&lt;id&gt;, ActionQueueRunButton.&lt;id&gt;, and ActionQueueCopyButton.&lt;id&gt;; computer-use exposed rough-cut-review and marlin-default IDs, clicked rough-cut-review Start &amp; Run, then observed Opening Codex approval gate for Review without approving the workspace-write review job or producing tracked project artifact changes. ProjectStudioReadinessStatusTests and ProjectStudioGoalStatusTests executed 6 tests with 0 failures. Approved workspace-write review execution, Final render Open, and Marlin default Open remain intentionally pending operator approval.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="48" customHeight="1">
@@ -3088,7 +3088,7 @@
         <x:v>Marked each macOS story with Core tests pass / UI pending or runtime pending instead of claiming Pass; next loop should run native manual/automation passes story by story and promote statuses only with evidence.</x:v>
       </x:c>
       <x:c r="H27" s="26" t="str">
-        <x:v>Current evidence: swift test passed 223 tests; build/run verify passed in the latest Viewer loop; US-045 has runtime/AVKit first-frame and latest-output evidence with visual confirmation pending, US-046 has project-switch runtime plus native New Project/NSOpenPanel creation and ProjectInitializer creation/failure contract tests, US-047 has native Command Palette keyboard/top-bar pass, US-048 has native Agent panel Check/Start/Stop lifecycle pass, US-049 has native read-only Status job plus approval prompt/rejection gate pass while approved write remains intentionally pending, US-050 has native Project tab readiness/action queue plus Copy-to-pasteboard pass while destructive Open/Start &amp; Run actions remain pending, US-051 has native local Source Analysis click evidence on a disposable one-source project, US-052 has native Compile Rough Cut and Apply Review Patch click evidence on a disposable project plus marker/index/library verification, US-053 has native timeline marker/audio/waveform/context-menu approve/reject/swap/search evidence, and US-054 has native disposable apply/undo evidence plus promote core/enable coverage. Remaining macOS stories are explicitly not complete.</x:v>
+        <x:v>Current evidence: swift test passed 223 tests; build/run verify passed in the latest Viewer loop; US-045 has runtime/AVKit first-frame and latest-output evidence with visual confirmation pending, US-046 has project-switch runtime plus native New Project/NSOpenPanel creation and ProjectInitializer creation/failure contract tests, US-047 has native Command Palette keyboard/top-bar pass, US-048 has native Agent panel Check/Start/Stop lifecycle pass, US-049 has native read-only Status job plus approval prompt/rejection gate pass while approved write remains intentionally pending, US-050 has native Project tab readiness/action queue, Copy-to-pasteboard, stable action-scoped AX IDs, and rough-cut-review Start &amp; Run approval-gate pass while approved write/open actions remain pending, US-051 has native local Source Analysis click evidence on a disposable one-source project, US-052 has native Compile Rough Cut and Apply Review Patch click evidence on a disposable project plus marker/index/library verification, US-053 has native timeline marker/audio/waveform/context-menu approve/reject/swap/search evidence, and US-054 has native disposable apply/undo evidence plus promote core/enable coverage. Remaining macOS stories are explicitly not complete.</x:v>
       </x:c>
       <x:c r="I27" s="11" t="str">
         <x:v>Open</x:v>
@@ -4284,31 +4284,60 @@
       </x:c>
     </x:row>
     <x:row r="69" ht="48" customHeight="1">
-      <x:c r="A69" s="12" t="str">
+      <x:c r="A69" s="10" t="str">
         <x:v>ISS-068</x:v>
       </x:c>
-      <x:c r="B69" s="27" t="str">
+      <x:c r="B69" s="26" t="str">
         <x:v>US-046</x:v>
       </x:c>
-      <x:c r="C69" s="27" t="str">
+      <x:c r="C69" s="26" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="D69" s="27" t="str">
+      <x:c r="D69" s="26" t="str">
         <x:v>macOS UX/testability</x:v>
       </x:c>
-      <x:c r="E69" s="27" t="str">
+      <x:c r="E69" s="26" t="str">
         <x:v>New Project creation could only be proven through visible labels and last Finder state, making the native NSOpenPanel path fragile.</x:v>
       </x:c>
-      <x:c r="F69" s="27" t="str">
+      <x:c r="F69" s="26" t="str">
         <x:v>The project ID alert used plain AppKit controls without stable accessibility identifiers, the source-folder panel inherited the user's last Finder location, and the Project creation row used LabeledContent that was easy to collapse in AX output.</x:v>
       </x:c>
-      <x:c r="G69" s="27" t="str">
+      <x:c r="G69" s="26" t="str">
         <x:v>Added ProjectInitializer.ProjectIDField/CreateButton/CancelButton, defaulted the source-folder NSOpenPanel to the repository root, and rendered Project creation as explicit status text in the Project State section.</x:v>
       </x:c>
-      <x:c r="H69" s="27" t="str">
+      <x:c r="H69" s="26" t="str">
         <x:v>Computer-use exposed the new alert identifiers, opened Choose Source Media Folder from the repo root, selected us046-native-source-20260623, and created us046-native-create-20260623. The shelf showed ProjectShelf.us046-native-create-20260623 intent_pending, the Project tab showed Project creation: Created us046-native-create-20260623 and linked source media, project_state.yaml recorded current_state=intent_pending, 02_media/source linked to the selected source folder, and ffprobe confirmed the linked H.264/AAC source clip.</x:v>
       </x:c>
-      <x:c r="I69" s="13" t="str">
+      <x:c r="I69" s="11" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="48" customHeight="1">
+      <x:c r="A70" s="12" t="str">
+        <x:v>ISS-069</x:v>
+      </x:c>
+      <x:c r="B70" s="27" t="str">
+        <x:v>US-050</x:v>
+      </x:c>
+      <x:c r="C70" s="27" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="D70" s="27" t="str">
+        <x:v>macOS UX/testability</x:v>
+      </x:c>
+      <x:c r="E70" s="27" t="str">
+        <x:v>Action Queue Run/Copy actions were visible, but individual actions were not safely targetable through native automation.</x:v>
+      </x:c>
+      <x:c r="F70" s="27" t="str">
+        <x:v>The Action Queue status, command text, Run, and Copy leaf controls lacked action-scoped accessibility identifiers, so repeatable tests depended on labels or row position and risked pressing the wrong advisory or workspace-write action.</x:v>
+      </x:c>
+      <x:c r="G70" s="27" t="str">
+        <x:v>Added ProjectPanel.ActionQueueStatus, ProjectPanel.ActionQueueCommand.&lt;id&gt;, ProjectPanel.ActionQueueRunButton.&lt;id&gt;, and ProjectPanel.ActionQueueCopyButton.&lt;id&gt; on leaf controls.</x:v>
+      </x:c>
+      <x:c r="H70" s="27" t="str">
+        <x:v>computer-use exposed rough-cut-review and marlin-default Run/Copy identifiers; clicking ProjectPanel.ActionQueueRunButton.rough-cut-review changed the status from Starting Codex session for Review... to Opening Codex approval gate for Review. git status listed only the intentional ProjectInspectorViews.swift edit, and the AX-1 review folder still contained only human_notes.yaml. swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed.</x:v>
+      </x:c>
+      <x:c r="I70" s="13" t="str">
         <x:v>Fixed</x:v>
       </x:c>
     </x:row>
@@ -8930,23 +8959,43 @@
       </x:c>
     </x:row>
     <x:row r="231" ht="48" customHeight="1">
-      <x:c r="A231" s="12" t="str">
+      <x:c r="A231" s="10" t="str">
         <x:v>TL-230</x:v>
       </x:c>
-      <x:c r="B231" s="27" t="str">
+      <x:c r="B231" s="26" t="str">
         <x:v>US-045</x:v>
       </x:c>
-      <x:c r="C231" s="27" t="str">
+      <x:c r="C231" s="26" t="str">
         <x:v>AX-1 exact preview promotion and pixel pass</x:v>
       </x:c>
-      <x:c r="D231" s="27" t="str">
+      <x:c r="D231" s="26" t="str">
         <x:v>Run videoos-studio-cli compile-run on projects/ax1-participant-voices-20260401, confirm playback-contract-status, select ProjectShelf.ax1-participant-voices-20260401 in VideoOSStudio, capture /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and run Retina-coordinate pixel statistics on the Viewer region.</x:v>
       </x:c>
-      <x:c r="E231" s="27" t="str">
+      <x:c r="E231" s="26" t="str">
         <x:v>Before compile, playback-contract-status returned legacy_manifest and approvalGrade=false. compile-run completed with exitCode=0, timeline compiled, indexDocuments=492, and git status stayed clean. After compile, playback-contract-status returned state=exact, approvalGrade=true, timelineHash=171378fe2bfe3a7c, and manifestBaseTimelineHash=171378fe2bfe3a7c. Native Viewer showed Exact preview / preview-editor-1775121573933.mp4 and Timeline preview D4887.MP4 with a visible interview frame. Screenshot was 3.5M; viewer_person_actual mean_rgb=(144.62,141.42,149.8) and near_black_pct=0.0004, while left pillarbox near_black_pct=1.0000 as expected.</x:v>
       </x:c>
-      <x:c r="F231" s="13" t="str">
+      <x:c r="F231" s="11" t="str">
         <x:v>Native AX-1 exact/pixel pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" ht="48" customHeight="1">
+      <x:c r="A232" s="12" t="str">
+        <x:v>TL-231</x:v>
+      </x:c>
+      <x:c r="B232" s="27" t="str">
+        <x:v>US-050</x:v>
+      </x:c>
+      <x:c r="C232" s="27" t="str">
+        <x:v>Native Action Queue approval gate</x:v>
+      </x:c>
+      <x:c r="D232" s="27" t="str">
+        <x:v>Add ProjectPanel.ActionQueue* identifiers, relaunch VideoOSStudio, select AX-1 Project tab, inspect the Action Queue AX tree, click ProjectPanel.ActionQueueRunButton.rough-cut-review, and stop at the Codex approval gate without approving writes.</x:v>
+      </x:c>
+      <x:c r="E232" s="27" t="str">
+        <x:v>AX exposed ProjectPanel.ActionQueueRunButton.rough-cut-review, ProjectPanel.ActionQueueCopyButton.rough-cut-review, ProjectPanel.ActionQueueRunButton.marlin-default, and ProjectPanel.ActionQueueCopyButton.marlin-default. Clicking rough-cut-review changed the row to disabled Starting Codex session for Review..., then to Opening Codex approval gate for Review. ps showed a Codex app-server child under VideoOSStudio; git status listed only the intentional ProjectInspectorViews.swift edit, and projects/ax1-participant-voices-20260401/06_review still contained only human_notes.yaml.</x:v>
+      </x:c>
+      <x:c r="F232" s="13" t="str">
+        <x:v>Native approval-gate pass; write not approved</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R7b1005c622094fab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R8b952772061f446f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Rd5875a18fd134e0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R6b1141a8149f423a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Re13445cf9b144dd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R42178f5ca71f41ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rc454ec4e0df44931"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R059803872ac54527"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R16b1c0c4ad9d410d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R5ba7b0e7f7224c5f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -439,7 +439,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 18:24 JST</x:v>
+        <x:v>2026-06-23 18:42 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -479,7 +479,7 @@
         <x:v>Issues tracked</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="220" customHeight="1">
@@ -487,7 +487,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build includes ProjectPanel.ActionQueueStatus / ActionQueueCommand.&lt;id&gt; / ActionQueueRunButton.&lt;id&gt; / ActionQueueCopyButton.&lt;id&gt; for US-050, ProjectInitializer.ProjectIDField/CreateButton/CancelButton for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix. Latest native build/run verified VideoOSStudio from the repo root.</x:v>
+        <x:v>Latest code build replaces the inspector SwiftUI TabView with explicit InspectorTab.Agent/Project/Clip/Media/QA buttons for US-065, preserving the same Agent/Project/Clip/Media/QA panels while avoiding the segmented-control AXPress hang. The build also includes ProjectPanel.ActionQueueStatus / ActionQueueCommand.&lt;id&gt; / ActionQueueRunButton.&lt;id&gt; / ActionQueueCopyButton.&lt;id&gt; for US-050, ProjectInitializer.ProjectIDField/CreateButton/CancelButton for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix. Latest native build/run verified VideoOSStudio from the repo root.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-050 loop selected AX-1 in VideoOSStudio, confirmed action-scoped Action Queue AX identifiers, clicked ProjectPanel.ActionQueueRunButton.rough-cut-review, and observed Opening Codex approval gate for Review without approving writes or producing tracked project artifact changes. The preceding US-045 loop recompiled AX-1, changing playback-contract-status from legacy_manifest / approvalGrade=false to exact / approvalGrade=true with hash 171378fe2bfe3a7c, selected AX-1 in VideoOSStudio, captured /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and measured viewer_person_actual near_black_pct=0.0004. Prior US-061 loop ran a live non-mock Marlin single-source completion on a /tmp lively-alt-vol5-derived fixture with requestTimeoutMs=900000 and VOS_MARLIN_PROXY_MAX_WIDTH=384; marlin-evaluate wrote marlin_events.json, marlin-status reported events=3/findResults=4/coverage=1.00/canPreferMarlin=true for the fixture, segments gained marlin_temporal_semantics peak provenance, index-rebuild produced 9 search documents, and git status stayed clean. Prior US-055 Ask Codex proposal, US-064 Editor Handoff export, US-063 Render Final Package, US-062 Audio Story Graph, US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-055 Save/Clear, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and US-045 exact preview loops remain verified.</x:v>
+        <x:v>Latest US-065 loop first reproduced the old inspector TabView failure after RAG Add: clicking Agent through AX left PID 95918 around 98.8% CPU with sample evidence in NSSegmentedCell _performClick. After the InspectorTab.* fix, build_and_run --verify launched PID 9971; Computer Use selected Media, searched 参加, found 3 cited results, clicked Add RAG Context, selected Agent, and confirmed the prompt contained Material RAG context for query `参加` with all 3 citations while ps reported 0.0% CPU. The preceding US-050 loop selected AX-1 in VideoOSStudio, confirmed action-scoped Action Queue AX identifiers, clicked ProjectPanel.ActionQueueRunButton.rough-cut-review, and observed Opening Codex approval gate for Review without approving writes or producing tracked project artifact changes. Prior US-045, US-061, US-055 Ask Codex proposal, US-064 Editor Handoff export, US-063 Render Final Package, US-062 Audio Story Graph, US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-055 Save/Clear, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and exact preview loops remain verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest native check is the US-050 computer-use pass selecting ProjectShelf.ax1-participant-voices-20260401, inspecting the Project tab Action Queue, confirming ProjectPanel.ActionQueueRunButton.rough-cut-review / CopyButton.rough-cut-review / RunButton.marlin-default / CopyButton.marlin-default, clicking rough-cut-review Start &amp; Run, and observing Opening Codex approval gate for Review with no approved write. The preceding native visual check selected AX-1 and confirmed a visible exact-preview Viewer frame: Support Playback contract Exact preview / preview-editor-1775121573933.mp4, Timeline preview D4887.MP4, screenshot /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, viewer_person_actual mean_rgb=(144.62,141.42,149.8), near_black_pct=0.0004. Prior native visual checks include the US-055 computer-use pass for Agent Start Agent Session, toolbar Clip, Timeline.Clip.V1.CLP_0001, ClipInspector.AskCodexButton, ClipInspector.NoteDraftEditor, ClipInspector.HandoffInstructionDraftEditor, and ClipInspector.EditorAnnotationStatus. Latest US-061 live model check was CLI/runtime on /tmp because it intentionally avoided writing real project artifacts; prior Media tab AX checks already covered MediaPanel.MarlinEvaluationRecommendation, MarlinPreferenceRecommendation, MarlinQueueNextAction, MarlinRepresentativeNextAction, MarlinRepresentativeBucket.*, MarlinQueueItem.*, MarlinEvaluationRunStatus, RunMarlinEvaluationButton, ApplyMarlinPreferenceButton, MarlinEvaluationCommandLine, and MarlinEvaluationArtifactPath. Prior checks covered ProjectShelf.us064-native-handoff-smoke-20260623, ProjectShelf.us064-native-packet-smoke-20260623, MediaPanel.ExportPremiereXMLButton, ExportEditorPacketButton, RevealEditorPacketButton, ProjectShelf.us063-native-render-smoke-20260623, MediaPanel.RenderFinalPackageButton, ProjectShelf.us062-audio-story-smoke, MediaPanel.BuildAudioStoryGraphButton, ProjectShelf.NewProject, ProjectInitializer fields/buttons, source-folder panel Link Source, MediaPanel Synthetic/Proxy/Smoke controls, MediaPanel relink IDs, Settings.TransportPicker/Description, CommandPaletteButton, CommandPaletteSearchField, CommandPaletteItem.search-footage, FootageSearch.* result controls, FeedbackStatus.PendingCount/DiscardButton, Timeline clip/menu IDs, ProjectPanel compile/review, Source Analysis, Project tab readiness/copy, Agent Start/Run/Stop, Command Palette, ena-promo-ai exact preview, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, Media SQLite/RAG, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest native check is the US-065 computer-use pass selecting ProjectShelf.ax1-participant-voices-20260401, confirming InspectorTab.Agent/Project/Clip/Media/QA, selecting Media, searching 参加 in MediaPanel.IndexSearchField, observing Found 3 index results and 3 cited items ready for Codex prompt context, clicking MediaPanel.AddRAGContextButton, selecting InspectorTab.Agent, and confirming the Agent prompt contains Material RAG context for query `参加` with audio-story-node, segment, and transcript citations. The app stayed responsive after the Agent return and ps reported PID 9971 at 0.0% CPU. The preceding native check covered US-050 action-scoped Action Queue identifiers and rough-cut-review approval-gate behavior. Prior native visual checks include the US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-061 Marlin AX/readiness, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility, Copy behavior, stable action-scoped AX identifiers, and rough-cut-review Start &amp; Run stopping at the Codex approval gate; approved workspace-write review execution, Final render Open, and Marlin default Open remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-061 is promoted for runtime/model/mock/native AX and a live non-mock single-source Marlin completion on a representative-source fixture; the full multi-source live batch and repo-level Marlin-first preference promotion remain pending evidence gates. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility, Copy behavior, stable action-scoped AX identifiers, and rough-cut-review Start &amp; Run stopping at the Codex approval gate; approved workspace-write review execution, Final render Open, and Marlin default Open remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-065 is promoted for native SQLite/RAG Search/Add, cited Agent prompt insertion, and InspectorTab.* Agent/Media switching without AX hangs. US-061 is promoted for runtime/model/mock/native AX and a live non-mock single-source Marlin completion on a representative-source fixture; the full multi-source live batch and repo-level Marlin-first preference promotion remain pending evidence gates. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2250,19 +2250,19 @@
         <x:v>As a native Studio operator, I can rebuild the SQLite index, search transcripts/tags/Marlin/audio evidence, inspect cited results, and append the context pack to the Agent prompt.</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>MediaPanel SQLite Index and Search sections call rebuildSelectedProjectIndex, searchSelectedProjectIndex, and appendIndexContextToAgentPrompt; ProjectRAGContextPack formats cited prompt context, and VideoOSAgentJob injects non-empty cited packs into generated prompts. The native controls now expose stable MediaPanel identifiers for rebuild/search/add-context/status/summary/result rows so UI automation can target the path without title matching.</x:v>
+        <x:v>MediaPanel SQLite Index and Search sections call rebuildSelectedProjectIndex, searchSelectedProjectIndex, and appendIndexContextToAgentPrompt; ProjectRAGContextPack formats cited prompt context, and VideoOSAgentJob injects non-empty cited packs into generated prompts. The native controls now expose stable MediaPanel identifiers for rebuild/search/add-context/status/summary/result rows, and the inspector tab bar now exposes explicit InspectorTab.* buttons so UI automation can target the RAG path and return to Agent without segmented-control hangs.</x:v>
       </x:c>
       <x:c r="E66" s="26" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:554-627; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1540-1558,2735-2766; apps/macos-studio/Sources/VideoOSStudioCore/ProjectSQLiteIndex.swift:11-107; apps/macos-studio/Sources/VideoOSStudioCore/ProjectRAGContextPack.swift:16-35,95-106; apps/macos-studio/Sources/VideoOSStudioCore/VideoOSAgentJob.swift:313-421,481-483</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/AgentInspectorViews.swift:5-86; apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:554-627; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1540-1558,2735-2766; apps/macos-studio/Sources/VideoOSStudioCore/ProjectSQLiteIndex.swift:11-107; apps/macos-studio/Sources/VideoOSStudioCore/ProjectRAGContextPack.swift:16-35,95-106; apps/macos-studio/Sources/VideoOSStudioCore/VideoOSAgentJob.swift:313-421,481-483</x:v>
       </x:c>
       <x:c r="F66" s="26" t="str">
-        <x:v>Run SQLite/RAG tests; run studio synthetic smoke; rebuild/status the index; search a query; render index-context; generate an agent-prompt with --context-query; confirm MediaPanel RAG accessibility identifiers are present in code; confirm native MediaPanel Search and Add RAG Context through AX/pixel evidence on a selected project.</x:v>
+        <x:v>Run SQLite/RAG tests; run studio synthetic smoke; rebuild/status the index; search a query; render index-context; generate an agent-prompt with --context-query; confirm MediaPanel RAG accessibility identifiers are present in code; confirm native MediaPanel Search/Add RAG Context and Agent-tab return through AX on a selected project.</x:v>
       </x:c>
       <x:c r="G66" s="26" t="str">
-        <x:v>Runtime/CLI/native Search/Add pass</x:v>
+        <x:v>Native RAG/tab AX pass</x:v>
       </x:c>
       <x:c r="H66" s="11" t="str">
-        <x:v>Focused SQLite/RAG/readiness/agent/index-refresh Swift suite passed 38 tests after the MediaPanel identifier fix. A fresh 1s synthetic Studio project reported indexDocuments=5 and studioScore=9/9; index-rebuild produced 5 searchDocuments; index-status returned exists=true, searchDocuments=5, updatedAt=2026-06-23T00:10:46Z; index-search synthetic returned 4 results across segment, audio_story_node, marlin_event, and marlin_find. index-context emitted 4 prompt-ready citations with doc/asset/segment/time labels, and agent-prompt status --context-query=synthetic included those citations under a read-only write contract. Latest native pass on PID 99006 selected Media through the toolbar AX radio group, scrolled the MediaPanel to SQLite/Search with the right-pane AX scrollbar, focused the IndexSearchField, typed AI, returned 12 index results, enabled Add RAG Context, and pressing it changed the status to Added 12 cited RAG items to the Codex prompt. Screenshots captured /tmp/videoos-debug/us065-rag-focused-return.png and /tmp/videoos-debug/us065-rag-add-context.png. CLI index-context and agent-prompt with --context-query=AI emitted the same cited RAG context; media-status reconfirmed AX-1 ready=2/missing=0 and demo ready=0/missing=6.</x:v>
+        <x:v>Focused SQLite/RAG/readiness/agent/index-refresh Swift suite passed 38 tests after the MediaPanel identifier fix. A fresh 1s synthetic Studio project reported indexDocuments=5 and studioScore=9/9; index-rebuild produced 5 searchDocuments; index-status returned exists=true, searchDocuments=5, updatedAt=2026-06-23T00:10:46Z; index-search synthetic returned 4 results across segment, audio_story_node, marlin_event, and marlin_find. index-context emitted 4 prompt-ready citations with doc/asset/segment/time labels, and agent-prompt status --context-query=synthetic included those citations under a read-only write contract. Native pass on PID 99006 searched AI, returned 12 index results, enabled Add RAG Context, changed status to Added 12 cited RAG items to the Codex prompt, and screenshots captured /tmp/videoos-debug/us065-rag-focused-return.png and /tmp/videoos-debug/us065-rag-add-context.png. Latest native pass on PID 9971 exposed InspectorTab.Agent/Project/Clip/Media/QA, selected Media, searched 参加, returned 3 cited results across audio-story-node, segment, and transcript, clicked Add RAG Context, selected Agent, and confirmed the prompt contained Material RAG context for query `参加` with all 3 citations. ps reported 0.0% CPU after the Agent return.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="48" customHeight="1">
@@ -3958,10 +3958,10 @@
         <x:v>Added MediaPanel.IndexOperationStatus, MediaPanel.RebuildIndexButton, MediaPanel.IndexSearchField, MediaPanel.IndexSearchButton, MediaPanel.AddRAGContextButton, MediaPanel.IndexSearchEmptyState, MediaPanel.IndexContextSummary, and MediaPanel.IndexSearchResult.&lt;documentID&gt; identifiers, then verified the native Search/Add flow against AX-1.</x:v>
       </x:c>
       <x:c r="H57" s="26" t="str">
-        <x:v>rg confirmed the identifiers; focused SQLite/RAG/readiness/agent suite executed 38 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify exited 0; synthetic index/search/context/agent-prompt smoke passed with 5 docs and 4 cited results; latest native MediaPanel screenshot/AX pass searched AI, found 12 results, enabled Add RAG Context, and changed status to Added 12 cited RAG items to the Codex prompt.</x:v>
+        <x:v>rg confirmed the identifiers; focused SQLite/RAG/readiness/agent suite executed 38 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify exited 0; synthetic index/search/context/agent-prompt smoke passed with 5 docs and 4 cited results; latest native pass on PID 9971 selected InspectorTab.Media, searched 参加, found 3 cited results across audio-story-node, segment, and transcript, clicked Add RAG Context, then selected InspectorTab.Agent and confirmed the prompt contained Material RAG context for query `参加` with all 3 citations. The app stayed responsive and ps reported 0.0% CPU.</x:v>
       </x:c>
       <x:c r="I57" s="11" t="str">
-        <x:v>Mitigated; native RAG path verified</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="48" customHeight="1">
@@ -4313,31 +4313,60 @@
       </x:c>
     </x:row>
     <x:row r="70" ht="48" customHeight="1">
-      <x:c r="A70" s="12" t="str">
+      <x:c r="A70" s="10" t="str">
         <x:v>ISS-069</x:v>
       </x:c>
-      <x:c r="B70" s="27" t="str">
+      <x:c r="B70" s="26" t="str">
         <x:v>US-050</x:v>
       </x:c>
-      <x:c r="C70" s="27" t="str">
+      <x:c r="C70" s="26" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="D70" s="27" t="str">
+      <x:c r="D70" s="26" t="str">
         <x:v>macOS UX/testability</x:v>
       </x:c>
-      <x:c r="E70" s="27" t="str">
+      <x:c r="E70" s="26" t="str">
         <x:v>Action Queue Run/Copy actions were visible, but individual actions were not safely targetable through native automation.</x:v>
       </x:c>
-      <x:c r="F70" s="27" t="str">
+      <x:c r="F70" s="26" t="str">
         <x:v>The Action Queue status, command text, Run, and Copy leaf controls lacked action-scoped accessibility identifiers, so repeatable tests depended on labels or row position and risked pressing the wrong advisory or workspace-write action.</x:v>
       </x:c>
-      <x:c r="G70" s="27" t="str">
+      <x:c r="G70" s="26" t="str">
         <x:v>Added ProjectPanel.ActionQueueStatus, ProjectPanel.ActionQueueCommand.&lt;id&gt;, ProjectPanel.ActionQueueRunButton.&lt;id&gt;, and ProjectPanel.ActionQueueCopyButton.&lt;id&gt; on leaf controls.</x:v>
       </x:c>
-      <x:c r="H70" s="27" t="str">
+      <x:c r="H70" s="26" t="str">
         <x:v>computer-use exposed rough-cut-review and marlin-default Run/Copy identifiers; clicking ProjectPanel.ActionQueueRunButton.rough-cut-review changed the status from Starting Codex session for Review... to Opening Codex approval gate for Review. git status listed only the intentional ProjectInspectorViews.swift edit, and the AX-1 review folder still contained only human_notes.yaml. swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed.</x:v>
       </x:c>
-      <x:c r="I70" s="13" t="str">
+      <x:c r="I70" s="11" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="48" customHeight="1">
+      <x:c r="A71" s="12" t="str">
+        <x:v>ISS-070</x:v>
+      </x:c>
+      <x:c r="B71" s="27" t="str">
+        <x:v>US-065</x:v>
+      </x:c>
+      <x:c r="C71" s="27" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="D71" s="27" t="str">
+        <x:v>macOS UX/testability</x:v>
+      </x:c>
+      <x:c r="E71" s="27" t="str">
+        <x:v>Switching inspector tabs through Computer Use after adding RAG context could leave VideoOSStudio busy and unreachable to accessibility automation.</x:v>
+      </x:c>
+      <x:c r="F71" s="27" t="str">
+        <x:v>InspectorPanel used SwiftUI TabView, which exposed the tab strip as an AppKit NSSegmentedCell. In the RAG Search/Add flow, pressing the Agent segment entered the AX perform-action path and did not return, leaving Computer Use with noWindowsAvailable/timeouts and the app process around 98.8% CPU.</x:v>
+      </x:c>
+      <x:c r="G71" s="27" t="str">
+        <x:v>Replaced the inspector TabView with explicit SwiftUI Button tabs keyed as InspectorTab.Agent, InspectorTab.Project, InspectorTab.Clip, InspectorTab.Media, and InspectorTab.QA. The selected panel content is unchanged, but tab changes now avoid the segmented-cell AXPress path and expose stable tab identifiers.</x:v>
+      </x:c>
+      <x:c r="H71" s="27" t="str">
+        <x:v>Before the fix, PID 95918 stayed around 98.8% CPU and sample showed the main thread inside NSSegmentedCell _performClick after clicking Agent; /tmp/videoos-us065-rag-after-agent-click.png captured the app stuck on Media after Add RAG Context. After the fix, build_and_run --verify launched PID 9971; Computer Use exposed InspectorTab.* buttons, selected Media, searched 参加, added 3 cited RAG items, selected Agent, confirmed the prompt contained Material RAG context for query `参加`, and ps reported 0.0% CPU.</x:v>
+      </x:c>
+      <x:c r="I71" s="13" t="str">
         <x:v>Fixed</x:v>
       </x:c>
     </x:row>
@@ -8460,79 +8489,79 @@
     </x:row>
     <x:row r="206" ht="48" customHeight="1">
       <x:c r="A206" s="10" t="str">
-        <x:v>TL-205</x:v>
+        <x:v>TL-232</x:v>
       </x:c>
       <x:c r="B206" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-065</x:v>
       </x:c>
       <x:c r="C206" s="26" t="str">
-        <x:v>Native preview duration fallback</x:v>
+        <x:v>Native SQLite/RAG Search/Add and inspector tab AX fix</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
+        <x:v>Replace the inspector SwiftUI TabView with explicit InspectorTab.* buttons; relaunch VideoOSStudio; use InspectorTab.Media, search AX-1 SQLite index for 参加, click Add RAG Context, verify cited result IDs, click InspectorTab.Agent, and confirm AX remains responsive.</x:v>
       </x:c>
       <x:c r="E206" s="26" t="str">
-        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
+        <x:v>The pre-fix TabView path hung after RAG Add when AXPress clicked Agent, leaving PID 95918 around 98.8% CPU with sample evidence in NSSegmentedCell _performClick. After the explicit-button fix, build_and_run --verify launched PID 9971, Computer Use exposed InspectorTab.Agent/Project/Clip/Media/QA, Media search for 参加 returned 3 cited results (audio-story-node:UTTREF_TRI_AST_76B05D86_0005, segment:SEG_AST_76B05D86_0001, transcript:TR_AST_76B05D86:S1:19090251-31090251), Add changed status to Added 3 cited RAG items to the Codex prompt, Agent showed Material RAG context for query `参加` with all 3 citations, and ps reported 0.0% CPU.</x:v>
       </x:c>
       <x:c r="F206" s="11" t="str">
-        <x:v>Native pixel/runtime pass</x:v>
+        <x:v>Native RAG/tab AX pass</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="48" customHeight="1">
       <x:c r="A207" s="10" t="str">
-        <x:v>TL-206</x:v>
+        <x:v>TL-205</x:v>
       </x:c>
       <x:c r="B207" s="26" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C207" s="26" t="str">
-        <x:v>Native Clip Inspector save and clear</x:v>
+        <x:v>Native preview duration fallback</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
+        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
       </x:c>
       <x:c r="E207" s="26" t="str">
-        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
+        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F207" s="11" t="str">
-        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
+        <x:v>Native pixel/runtime pass</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="48" customHeight="1">
       <x:c r="A208" s="10" t="str">
-        <x:v>TL-207</x:v>
+        <x:v>TL-206</x:v>
       </x:c>
       <x:c r="B208" s="26" t="str">
-        <x:v>US-058</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C208" s="26" t="str">
-        <x:v>Native QA Dashboard issue jump</x:v>
+        <x:v>Native Clip Inspector save and clear</x:v>
       </x:c>
       <x:c r="D208" s="26" t="str">
-        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
+        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
       </x:c>
       <x:c r="E208" s="26" t="str">
-        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
+        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
       </x:c>
       <x:c r="F208" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="48" customHeight="1">
       <x:c r="A209" s="10" t="str">
-        <x:v>TL-208</x:v>
+        <x:v>TL-207</x:v>
       </x:c>
       <x:c r="B209" s="26" t="str">
-        <x:v>US-056</x:v>
+        <x:v>US-058</x:v>
       </x:c>
       <x:c r="C209" s="26" t="str">
-        <x:v>Native Candidate Swap sheet and staging</x:v>
+        <x:v>Native QA Dashboard issue jump</x:v>
       </x:c>
       <x:c r="D209" s="26" t="str">
-        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
+        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
       </x:c>
       <x:c r="E209" s="26" t="str">
-        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
+        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
       </x:c>
       <x:c r="F209" s="11" t="str">
         <x:v>Native AX/pixel pass</x:v>
@@ -8540,339 +8569,339 @@
     </x:row>
     <x:row r="210" ht="48" customHeight="1">
       <x:c r="A210" s="10" t="str">
-        <x:v>TL-209</x:v>
+        <x:v>TL-208</x:v>
       </x:c>
       <x:c r="B210" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-056</x:v>
       </x:c>
       <x:c r="C210" s="26" t="str">
-        <x:v>Native exact preview regeneration</x:v>
+        <x:v>Native Candidate Swap sheet and staging</x:v>
       </x:c>
       <x:c r="D210" s="26" t="str">
-        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
+        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
       </x:c>
       <x:c r="E210" s="26" t="str">
-        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
       </x:c>
       <x:c r="F210" s="11" t="str">
-        <x:v>Native exact preview pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="211" ht="48" customHeight="1">
       <x:c r="A211" s="10" t="str">
-        <x:v>TL-210</x:v>
+        <x:v>TL-209</x:v>
       </x:c>
       <x:c r="B211" s="26" t="str">
-        <x:v>US-047</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C211" s="26" t="str">
-        <x:v>Native Command Palette top-bar open/close</x:v>
+        <x:v>Native exact preview regeneration</x:v>
       </x:c>
       <x:c r="D211" s="26" t="str">
-        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
+        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
       </x:c>
       <x:c r="E211" s="26" t="str">
-        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
+        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F211" s="11" t="str">
-        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
+        <x:v>Native exact preview pass</x:v>
       </x:c>
     </x:row>
     <x:row r="212" ht="48" customHeight="1">
       <x:c r="A212" s="10" t="str">
-        <x:v>TL-211</x:v>
+        <x:v>TL-210</x:v>
       </x:c>
       <x:c r="B212" s="26" t="str">
         <x:v>US-047</x:v>
       </x:c>
       <x:c r="C212" s="26" t="str">
-        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
+        <x:v>Native Command Palette top-bar open/close</x:v>
       </x:c>
       <x:c r="D212" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
+        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
       </x:c>
       <x:c r="E212" s="26" t="str">
-        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
+        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
       </x:c>
       <x:c r="F212" s="11" t="str">
-        <x:v>Native keyboard/AX pass</x:v>
+        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
       </x:c>
     </x:row>
     <x:row r="213" ht="48" customHeight="1">
       <x:c r="A213" s="10" t="str">
-        <x:v>TL-212</x:v>
+        <x:v>TL-211</x:v>
       </x:c>
       <x:c r="B213" s="26" t="str">
-        <x:v>US-048</x:v>
+        <x:v>US-047</x:v>
       </x:c>
       <x:c r="C213" s="26" t="str">
-        <x:v>Native Agent panel session lifecycle</x:v>
+        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
       </x:c>
       <x:c r="D213" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
+        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
       </x:c>
       <x:c r="E213" s="26" t="str">
-        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
+        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
       </x:c>
       <x:c r="F213" s="11" t="str">
-        <x:v>Native AX/computer-use pass</x:v>
+        <x:v>Native keyboard/AX pass</x:v>
       </x:c>
     </x:row>
     <x:row r="214" ht="48" customHeight="1">
       <x:c r="A214" s="10" t="str">
-        <x:v>TL-213</x:v>
+        <x:v>TL-212</x:v>
       </x:c>
       <x:c r="B214" s="26" t="str">
-        <x:v>US-049</x:v>
+        <x:v>US-048</x:v>
       </x:c>
       <x:c r="C214" s="26" t="str">
-        <x:v>Native Status agent job read-only turn</x:v>
+        <x:v>Native Agent panel session lifecycle</x:v>
       </x:c>
       <x:c r="D214" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
       </x:c>
       <x:c r="E214" s="26" t="str">
-        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
+        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F214" s="11" t="str">
-        <x:v>Native read-only job pass; approved write pending</x:v>
+        <x:v>Native AX/computer-use pass</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="48" customHeight="1">
       <x:c r="A215" s="10" t="str">
-        <x:v>TL-214</x:v>
+        <x:v>TL-213</x:v>
       </x:c>
       <x:c r="B215" s="26" t="str">
-        <x:v>US-050</x:v>
+        <x:v>US-049</x:v>
       </x:c>
       <x:c r="C215" s="26" t="str">
-        <x:v>Native Project readiness/action queue Copy pass</x:v>
+        <x:v>Native Status agent job read-only turn</x:v>
       </x:c>
       <x:c r="D215" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
       </x:c>
       <x:c r="E215" s="26" t="str">
-        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
+        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F215" s="11" t="str">
-        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
+        <x:v>Native read-only job pass; approved write pending</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="48" customHeight="1">
       <x:c r="A216" s="10" t="str">
-        <x:v>TL-215</x:v>
+        <x:v>TL-214</x:v>
       </x:c>
       <x:c r="B216" s="26" t="str">
-        <x:v>US-051</x:v>
+        <x:v>US-050</x:v>
       </x:c>
       <x:c r="C216" s="26" t="str">
-        <x:v>Native local Source Analysis button</x:v>
+        <x:v>Native Project readiness/action queue Copy pass</x:v>
       </x:c>
       <x:c r="D216" s="26" t="str">
-        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
       </x:c>
       <x:c r="E216" s="26" t="str">
-        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
+        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
       </x:c>
       <x:c r="F216" s="11" t="str">
-        <x:v>Native local analysis pass</x:v>
+        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="48" customHeight="1">
       <x:c r="A217" s="10" t="str">
-        <x:v>TL-216</x:v>
+        <x:v>TL-215</x:v>
       </x:c>
       <x:c r="B217" s="26" t="str">
-        <x:v>US-052</x:v>
+        <x:v>US-051</x:v>
       </x:c>
       <x:c r="C217" s="26" t="str">
-        <x:v>Native Rough Cut and Review Patch buttons</x:v>
+        <x:v>Native local Source Analysis button</x:v>
       </x:c>
       <x:c r="D217" s="26" t="str">
-        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
+        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E217" s="26" t="str">
-        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
       </x:c>
       <x:c r="F217" s="11" t="str">
-        <x:v>Native compile/review patch pass</x:v>
+        <x:v>Native local analysis pass</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="48" customHeight="1">
       <x:c r="A218" s="10" t="str">
-        <x:v>TL-217</x:v>
+        <x:v>TL-216</x:v>
       </x:c>
       <x:c r="B218" s="26" t="str">
-        <x:v>US-053</x:v>
+        <x:v>US-052</x:v>
       </x:c>
       <x:c r="C218" s="26" t="str">
-        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
+        <x:v>Native Rough Cut and Review Patch buttons</x:v>
       </x:c>
       <x:c r="D218" s="26" t="str">
-        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
+        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E218" s="26" t="str">
-        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
+        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F218" s="11" t="str">
-        <x:v>Native timeline/context menu pass</x:v>
+        <x:v>Native compile/review patch pass</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="48" customHeight="1">
       <x:c r="A219" s="10" t="str">
-        <x:v>TL-218</x:v>
+        <x:v>TL-217</x:v>
       </x:c>
       <x:c r="B219" s="26" t="str">
-        <x:v>US-054</x:v>
+        <x:v>US-053</x:v>
       </x:c>
       <x:c r="C219" s="26" t="str">
-        <x:v>Native Studio feedback Apply and Undo</x:v>
+        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
       </x:c>
       <x:c r="D219" s="26" t="str">
-        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
+        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
       </x:c>
       <x:c r="E219" s="26" t="str">
-        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
       </x:c>
       <x:c r="F219" s="11" t="str">
-        <x:v>Native apply/undo pass</x:v>
+        <x:v>Native timeline/context menu pass</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="48" customHeight="1">
       <x:c r="A220" s="10" t="str">
-        <x:v>TL-219</x:v>
+        <x:v>TL-218</x:v>
       </x:c>
       <x:c r="B220" s="26" t="str">
-        <x:v>US-057</x:v>
+        <x:v>US-054</x:v>
       </x:c>
       <x:c r="C220" s="26" t="str">
-        <x:v>Native Footage Search sheet and replacement staging</x:v>
+        <x:v>Native Studio feedback Apply and Undo</x:v>
       </x:c>
       <x:c r="D220" s="26" t="str">
-        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
+        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E220" s="26" t="str">
-        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
+        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F220" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native apply/undo pass</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="48" customHeight="1">
       <x:c r="A221" s="10" t="str">
-        <x:v>TL-220</x:v>
+        <x:v>TL-219</x:v>
       </x:c>
       <x:c r="B221" s="26" t="str">
-        <x:v>US-066</x:v>
+        <x:v>US-057</x:v>
       </x:c>
       <x:c r="C221" s="26" t="str">
-        <x:v>Native Settings transport picker mutation</x:v>
+        <x:v>Native Footage Search sheet and replacement staging</x:v>
       </x:c>
       <x:c r="D221" s="26" t="str">
-        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
+        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
       </x:c>
       <x:c r="E221" s="26" t="str">
-        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
       </x:c>
       <x:c r="F221" s="11" t="str">
-        <x:v>Native Settings picker mutation pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="48" customHeight="1">
       <x:c r="A222" s="10" t="str">
-        <x:v>TL-221</x:v>
+        <x:v>TL-220</x:v>
       </x:c>
       <x:c r="B222" s="26" t="str">
-        <x:v>US-059</x:v>
+        <x:v>US-066</x:v>
       </x:c>
       <x:c r="C222" s="26" t="str">
-        <x:v>Native Media Relink buttons and source-map relink</x:v>
+        <x:v>Native Settings transport picker mutation</x:v>
       </x:c>
       <x:c r="D222" s="26" t="str">
-        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
+        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
       </x:c>
       <x:c r="E222" s="26" t="str">
-        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
+        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F222" s="11" t="str">
-        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
+        <x:v>Native Settings picker mutation pass</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="48" customHeight="1">
       <x:c r="A223" s="10" t="str">
-        <x:v>TL-222</x:v>
+        <x:v>TL-221</x:v>
       </x:c>
       <x:c r="B223" s="26" t="str">
-        <x:v>US-060</x:v>
+        <x:v>US-059</x:v>
       </x:c>
       <x:c r="C223" s="26" t="str">
-        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
+        <x:v>Native Media Relink buttons and source-map relink</x:v>
       </x:c>
       <x:c r="D223" s="26" t="str">
-        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
+        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
       </x:c>
       <x:c r="E223" s="26" t="str">
-        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
+        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
       </x:c>
       <x:c r="F223" s="11" t="str">
-        <x:v>Native synthetic/proxy/smoke button pass</x:v>
+        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="48" customHeight="1">
       <x:c r="A224" s="10" t="str">
-        <x:v>TL-223</x:v>
+        <x:v>TL-222</x:v>
       </x:c>
       <x:c r="B224" s="26" t="str">
-        <x:v>US-046</x:v>
+        <x:v>US-060</x:v>
       </x:c>
       <x:c r="C224" s="26" t="str">
-        <x:v>Native New Project from Source</x:v>
+        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
       </x:c>
       <x:c r="D224" s="26" t="str">
-        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
+        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
       </x:c>
       <x:c r="E224" s="26" t="str">
-        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
+        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
       </x:c>
       <x:c r="F224" s="11" t="str">
-        <x:v>Native project creation/NSOpenPanel pass</x:v>
+        <x:v>Native synthetic/proxy/smoke button pass</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="48" customHeight="1">
       <x:c r="A225" s="10" t="str">
-        <x:v>TL-224</x:v>
+        <x:v>TL-223</x:v>
       </x:c>
       <x:c r="B225" s="26" t="str">
-        <x:v>US-062</x:v>
+        <x:v>US-046</x:v>
       </x:c>
       <x:c r="C225" s="26" t="str">
-        <x:v>Native MediaPanel Audio Story Graph button</x:v>
+        <x:v>Native New Project from Source</x:v>
       </x:c>
       <x:c r="D225" s="26" t="str">
-        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
+        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
       </x:c>
       <x:c r="E225" s="26" t="str">
-        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
       </x:c>
       <x:c r="F225" s="11" t="str">
-        <x:v>Native AX/UI/CLI pass</x:v>
+        <x:v>Native project creation/NSOpenPanel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="48" customHeight="1">
       <x:c r="A226" s="10" t="str">
-        <x:v>TL-225</x:v>
+        <x:v>TL-224</x:v>
       </x:c>
       <x:c r="B226" s="26" t="str">
-        <x:v>US-063</x:v>
+        <x:v>US-062</x:v>
       </x:c>
       <x:c r="C226" s="26" t="str">
-        <x:v>Native Render Final Package button</x:v>
+        <x:v>Native MediaPanel Audio Story Graph button</x:v>
       </x:c>
       <x:c r="D226" s="26" t="str">
-        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
+        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E226" s="26" t="str">
-        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F226" s="11" t="str">
         <x:v>Native AX/UI/CLI pass</x:v>
@@ -8880,121 +8909,141 @@
     </x:row>
     <x:row r="227" ht="48" customHeight="1">
       <x:c r="A227" s="10" t="str">
-        <x:v>TL-226</x:v>
+        <x:v>TL-225</x:v>
       </x:c>
       <x:c r="B227" s="26" t="str">
-        <x:v>US-064</x:v>
+        <x:v>US-063</x:v>
       </x:c>
       <x:c r="C227" s="26" t="str">
-        <x:v>Native Editor Handoff export and Finder reveal</x:v>
+        <x:v>Native Render Final Package button</x:v>
       </x:c>
       <x:c r="D227" s="26" t="str">
-        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
+        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
       </x:c>
       <x:c r="E227" s="26" t="str">
-        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
+        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F227" s="11" t="str">
-        <x:v>Native AX/UI/Finder/CLI pass</x:v>
+        <x:v>Native AX/UI/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="48" customHeight="1">
       <x:c r="A228" s="10" t="str">
-        <x:v>TL-227</x:v>
+        <x:v>TL-226</x:v>
       </x:c>
       <x:c r="B228" s="26" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-064</x:v>
       </x:c>
       <x:c r="C228" s="26" t="str">
-        <x:v>Native Ask Codex editor-note proposal</x:v>
+        <x:v>Native Editor Handoff export and Finder reveal</x:v>
       </x:c>
       <x:c r="D228" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
+        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E228" s="26" t="str">
-        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
+        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
       </x:c>
       <x:c r="F228" s="11" t="str">
-        <x:v>Native read-only Codex proposal pass</x:v>
+        <x:v>Native AX/UI/Finder/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="48" customHeight="1">
       <x:c r="A229" s="10" t="str">
-        <x:v>TL-228</x:v>
+        <x:v>TL-227</x:v>
       </x:c>
       <x:c r="B229" s="26" t="str">
-        <x:v>US-061</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C229" s="26" t="str">
-        <x:v>Live Marlin single-source completion</x:v>
+        <x:v>Native Ask Codex editor-note proposal</x:v>
       </x:c>
       <x:c r="D229" s="26" t="str">
-        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
+        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
       </x:c>
       <x:c r="E229" s="26" t="str">
-        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
+        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
       </x:c>
       <x:c r="F229" s="11" t="str">
-        <x:v>Live single-source pass; full representative batch pending</x:v>
+        <x:v>Native read-only Codex proposal pass</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="48" customHeight="1">
       <x:c r="A230" s="10" t="str">
-        <x:v>TL-229</x:v>
+        <x:v>TL-228</x:v>
       </x:c>
       <x:c r="B230" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C230" s="26" t="str">
-        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+        <x:v>Live Marlin single-source completion</x:v>
       </x:c>
       <x:c r="D230" s="26" t="str">
-        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
       </x:c>
       <x:c r="E230" s="26" t="str">
-        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
       </x:c>
       <x:c r="F230" s="11" t="str">
-        <x:v>Native fresh-launch pixel pass</x:v>
+        <x:v>Live single-source pass; full representative batch pending</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="48" customHeight="1">
       <x:c r="A231" s="10" t="str">
-        <x:v>TL-230</x:v>
+        <x:v>TL-229</x:v>
       </x:c>
       <x:c r="B231" s="26" t="str">
         <x:v>US-045</x:v>
       </x:c>
       <x:c r="C231" s="26" t="str">
+        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+      </x:c>
+      <x:c r="D231" s="26" t="str">
+        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+      </x:c>
+      <x:c r="E231" s="26" t="str">
+        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+      </x:c>
+      <x:c r="F231" s="11" t="str">
+        <x:v>Native fresh-launch pixel pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" ht="48" customHeight="1">
+      <x:c r="A232" s="10" t="str">
+        <x:v>TL-230</x:v>
+      </x:c>
+      <x:c r="B232" s="26" t="str">
+        <x:v>US-045</x:v>
+      </x:c>
+      <x:c r="C232" s="26" t="str">
         <x:v>AX-1 exact preview promotion and pixel pass</x:v>
       </x:c>
-      <x:c r="D231" s="26" t="str">
+      <x:c r="D232" s="26" t="str">
         <x:v>Run videoos-studio-cli compile-run on projects/ax1-participant-voices-20260401, confirm playback-contract-status, select ProjectShelf.ax1-participant-voices-20260401 in VideoOSStudio, capture /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and run Retina-coordinate pixel statistics on the Viewer region.</x:v>
       </x:c>
-      <x:c r="E231" s="26" t="str">
+      <x:c r="E232" s="26" t="str">
         <x:v>Before compile, playback-contract-status returned legacy_manifest and approvalGrade=false. compile-run completed with exitCode=0, timeline compiled, indexDocuments=492, and git status stayed clean. After compile, playback-contract-status returned state=exact, approvalGrade=true, timelineHash=171378fe2bfe3a7c, and manifestBaseTimelineHash=171378fe2bfe3a7c. Native Viewer showed Exact preview / preview-editor-1775121573933.mp4 and Timeline preview D4887.MP4 with a visible interview frame. Screenshot was 3.5M; viewer_person_actual mean_rgb=(144.62,141.42,149.8) and near_black_pct=0.0004, while left pillarbox near_black_pct=1.0000 as expected.</x:v>
       </x:c>
-      <x:c r="F231" s="11" t="str">
+      <x:c r="F232" s="11" t="str">
         <x:v>Native AX-1 exact/pixel pass</x:v>
       </x:c>
     </x:row>
-    <x:row r="232" ht="48" customHeight="1">
-      <x:c r="A232" s="12" t="str">
+    <x:row r="233" ht="48" customHeight="1">
+      <x:c r="A233" s="12" t="str">
         <x:v>TL-231</x:v>
       </x:c>
-      <x:c r="B232" s="27" t="str">
+      <x:c r="B233" s="27" t="str">
         <x:v>US-050</x:v>
       </x:c>
-      <x:c r="C232" s="27" t="str">
+      <x:c r="C233" s="27" t="str">
         <x:v>Native Action Queue approval gate</x:v>
       </x:c>
-      <x:c r="D232" s="27" t="str">
+      <x:c r="D233" s="27" t="str">
         <x:v>Add ProjectPanel.ActionQueue* identifiers, relaunch VideoOSStudio, select AX-1 Project tab, inspect the Action Queue AX tree, click ProjectPanel.ActionQueueRunButton.rough-cut-review, and stop at the Codex approval gate without approving writes.</x:v>
       </x:c>
-      <x:c r="E232" s="27" t="str">
+      <x:c r="E233" s="27" t="str">
         <x:v>AX exposed ProjectPanel.ActionQueueRunButton.rough-cut-review, ProjectPanel.ActionQueueCopyButton.rough-cut-review, ProjectPanel.ActionQueueRunButton.marlin-default, and ProjectPanel.ActionQueueCopyButton.marlin-default. Clicking rough-cut-review changed the row to disabled Starting Codex session for Review..., then to Opening Codex approval gate for Review. ps showed a Codex app-server child under VideoOSStudio; git status listed only the intentional ProjectInspectorViews.swift edit, and projects/ax1-participant-voices-20260401/06_review still contained only human_notes.yaml.</x:v>
       </x:c>
-      <x:c r="F232" s="13" t="str">
+      <x:c r="F233" s="13" t="str">
         <x:v>Native approval-gate pass; write not approved</x:v>
       </x:c>
     </x:row>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R42178f5ca71f41ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rc454ec4e0df44931"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R059803872ac54527"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R16b1c0c4ad9d410d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R5ba7b0e7f7224c5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra11f5bae122a44c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R7272303ee7ba4cd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R4250cb3741a442ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R31a5deb299874f7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Ra11d324c517f465e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -439,7 +439,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 18:42 JST</x:v>
+        <x:v>2026-06-23 18:53 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -487,7 +487,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build replaces the inspector SwiftUI TabView with explicit InspectorTab.Agent/Project/Clip/Media/QA buttons for US-065, preserving the same Agent/Project/Clip/Media/QA panels while avoiding the segmented-control AXPress hang. The build also includes ProjectPanel.ActionQueueStatus / ActionQueueCommand.&lt;id&gt; / ActionQueueRunButton.&lt;id&gt; / ActionQueueCopyButton.&lt;id&gt; for US-050, ProjectInitializer.ProjectIDField/CreateButton/CancelButton for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix. Latest native build/run verified VideoOSStudio from the repo root.</x:v>
+        <x:v>Latest code build changes ProjectMarlinRuntimeStatusReader so optional Marlin dependency imports run in isolated child Python processes, avoiding the av+torchcodec duplicate AVFoundation warning while preserving the same module readiness contract. The previous build replaced the inspector SwiftUI TabView with explicit InspectorTab.Agent/Project/Clip/Media/QA buttons for US-065, preserving the same Agent/Project/Clip/Media/QA panels while avoiding the segmented-control AXPress hang. The build also includes ProjectPanel.ActionQueueStatus / ActionQueueCommand.&lt;id&gt; / ActionQueueRunButton.&lt;id&gt; / ActionQueueCopyButton.&lt;id&gt; for US-050, ProjectInitializer.ProjectIDField/CreateButton/CancelButton for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix. Latest native build verified VideoOSStudio from the repo root.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-065 loop first reproduced the old inspector TabView failure after RAG Add: clicking Agent through AX left PID 95918 around 98.8% CPU with sample evidence in NSSegmentedCell _performClick. After the InspectorTab.* fix, build_and_run --verify launched PID 9971; Computer Use selected Media, searched 参加, found 3 cited results, clicked Add RAG Context, selected Agent, and confirmed the prompt contained Material RAG context for query `参加` with all 3 citations while ps reported 0.0% CPU. The preceding US-050 loop selected AX-1 in VideoOSStudio, confirmed action-scoped Action Queue AX identifiers, clicked ProjectPanel.ActionQueueRunButton.rough-cut-review, and observed Opening Codex approval gate for Review without approving writes or producing tracked project artifact changes. Prior US-045, US-061, US-055 Ask Codex proposal, US-064 Editor Handoff export, US-063 Render Final Package, US-062 Audio Story Graph, US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-055 Save/Clear, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and exact preview loops remain verified.</x:v>
+        <x:v>Latest US-061 loop reproduced the duplicate AVFoundation warning with av+torchcodec in one Python process, confirmed av-only, torchcodec-only, and worker torch/transformers imports are clean, then verified the isolated child-process probe: marlin-runtime-status reports live runtime ready, resolvedDevice=mps, all required modules ready, and no stderr warning. ProjectMarlinRuntimeStatusTests executed 5 tests with 0 failures; swift build --target VideoOSStudio and git diff --check passed. The same pass audited US-046 through US-066 and closed the stale broad QA gap ISS-026 because all native macOS stories now have native pass statuses or explicit approval/preference gates. Prior US-065 RAG/Add/Agent-tab, US-050 approval gate, US-045 exact preview, US-061 live single-source, US-055 Ask Codex proposal, US-064 Editor Handoff export, US-063 Render Final Package, US-062 Audio Story Graph, US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-055 Save/Clear, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and exact preview loops remain verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest native check is the US-065 computer-use pass selecting ProjectShelf.ax1-participant-voices-20260401, confirming InspectorTab.Agent/Project/Clip/Media/QA, selecting Media, searching 参加 in MediaPanel.IndexSearchField, observing Found 3 index results and 3 cited items ready for Codex prompt context, clicking MediaPanel.AddRAGContextButton, selecting InspectorTab.Agent, and confirming the Agent prompt contains Material RAG context for query `参加` with audio-story-node, segment, and transcript citations. The app stayed responsive after the Agent return and ps reported PID 9971 at 0.0% CPU. The preceding native check covered US-050 action-scoped Action Queue identifiers and rough-cut-review approval-gate behavior. Prior native visual checks include the US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-061 Marlin AX/readiness, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest runtime/native check is the US-061 marlin-runtime-status pass after rebuilding the Swift core: status live runtime ready, resolvedDevice=mps, all modules ready, and no duplicate AVFoundation stderr warning. The previous native UI check selected ProjectShelf.ax1-participant-voices-20260401, confirmed InspectorTab.Agent/Project/Clip/Media/QA, selected Media, searched 参加 in MediaPanel.IndexSearchField, observed Found 3 index results and 3 cited items ready for Codex prompt context, clicked MediaPanel.AddRAGContextButton, selected InspectorTab.Agent, and confirmed the Agent prompt contains Material RAG context for query `参加` with audio-story-node, segment, and transcript citations. Prior native visual checks include the US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-061 Marlin AX/readiness, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -2158,7 +2158,7 @@
         <x:v>Runtime/model/mock/native AX/live single-source pass; full batch preference gate pending</x:v>
       </x:c>
       <x:c r="H62" s="11" t="str">
-        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path now supports --request-timeout-ms / --timeout-ms, dry-run shows 900000ms in the generated command, and focused TS/Swift tests pass. Latest pass added MediaPanel.Marlin* identifiers and then ran a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4, with VOS_MARLIN_PROXY_MAX_WIDTH=384 and requestTimeoutMs=900000. marlin-evaluate completed with Mock=false, wrote marlin_events.json with inference_mode=live, model NemoStation/Marlin-2B, 1 asset, 3 events, and 4 find results; marlin-status reported candidate for preferred VLM, coverage=1.00, canPreferMarlin=true for the tmp fixture; segments.json gained marlin_temporal_semantics peak provenance and 3 interest points; index-rebuild produced 9 search documents. Full all-source representative run and repo-level preference promotion remain pending because the real repo gate still needs broader live coverage.</x:v>
+        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. The runtime probe now imports dependency modules in isolated child processes, so the live marlin-runtime-status check no longer emits duplicate AVFoundation class warnings while still reporting every module ready. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path now supports --request-timeout-ms / --timeout-ms, dry-run shows 900000ms in the generated command, and focused TS/Swift tests pass. Latest pass added MediaPanel.Marlin* identifiers and then ran a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4, with VOS_MARLIN_PROXY_MAX_WIDTH=384 and requestTimeoutMs=900000. marlin-evaluate completed with Mock=false, wrote marlin_events.json with inference_mode=live, model NemoStation/Marlin-2B, 1 asset, 3 events, and 4 find results; marlin-status reported candidate for preferred VLM, coverage=1.00, canPreferMarlin=true for the tmp fixture; segments.json gained marlin_temporal_semantics peak provenance and 3 interest points; index-rebuild produced 9 search documents. Full all-source representative run and repo-level preference promotion remain pending because the real repo gate still needs broader live coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="48" customHeight="1">
@@ -3079,19 +3079,19 @@
         <x:v>QA gap</x:v>
       </x:c>
       <x:c r="E27" s="26" t="str">
-        <x:v>Most native macOS user stories are now code-mapped but not yet manually exercised end-to-end in the running app.</x:v>
+        <x:v>Most native macOS user stories were code-mapped but not yet manually exercised end-to-end in the running app.</x:v>
       </x:c>
       <x:c r="F27" s="26" t="str">
-        <x:v>Swift core tests cover many planners/data contracts, but the goal requires runtime UX/logistics testing for each user story, not just unit coverage.</x:v>
+        <x:v>Swift core tests covered many planners/data contracts, but the goal requires runtime UX/logistics testing for each user story, not just unit coverage.</x:v>
       </x:c>
       <x:c r="G27" s="26" t="str">
-        <x:v>Marked each macOS story with Core tests pass / UI pending or runtime pending instead of claiming Pass; next loop should run native manual/automation passes story by story and promote statuses only with evidence.</x:v>
+        <x:v>Ran the native manual/automation pass story by story, promoted each macOS story only when backed by native AX/pixel/CLI/file evidence, and left deliberately unapproved write operations and full Marlin representative promotion as explicit gates in their own story/issue rows.</x:v>
       </x:c>
       <x:c r="H27" s="26" t="str">
-        <x:v>Current evidence: swift test passed 223 tests; build/run verify passed in the latest Viewer loop; US-045 has runtime/AVKit first-frame and latest-output evidence with visual confirmation pending, US-046 has project-switch runtime plus native New Project/NSOpenPanel creation and ProjectInitializer creation/failure contract tests, US-047 has native Command Palette keyboard/top-bar pass, US-048 has native Agent panel Check/Start/Stop lifecycle pass, US-049 has native read-only Status job plus approval prompt/rejection gate pass while approved write remains intentionally pending, US-050 has native Project tab readiness/action queue, Copy-to-pasteboard, stable action-scoped AX IDs, and rough-cut-review Start &amp; Run approval-gate pass while approved write/open actions remain pending, US-051 has native local Source Analysis click evidence on a disposable one-source project, US-052 has native Compile Rough Cut and Apply Review Patch click evidence on a disposable project plus marker/index/library verification, US-053 has native timeline marker/audio/waveform/context-menu approve/reject/swap/search evidence, and US-054 has native disposable apply/undo evidence plus promote core/enable coverage. Remaining macOS stories are explicitly not complete.</x:v>
+        <x:v>Tracker audit now shows US-046 through US-066 all have native pass statuses or explicit approval/preference gates: project creation, Command Palette, Agent lifecycle/jobs, Project action queue, Source Analysis, compile/review patch, timeline actions, feedback apply/undo, Clip Inspector, Candidate Swap, Footage Search, QA jump, Media Relink, Synthetic/Proxy/Smoke, Marlin runtime/native/single-source, Audio Story Graph, Render Final, Editor Handoff, SQLite/RAG, and Settings picker. Remaining risk is no longer a broad QA gap; it is tracked specifically by ISS-050 for the full Marlin representative batch/preference gate and by approval-gated write actions in US-049/US-050.</x:v>
       </x:c>
       <x:c r="I27" s="11" t="str">
-        <x:v>Open</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="48" customHeight="1">
@@ -3630,19 +3630,19 @@
         <x:v>macOS runtime/logistics</x:v>
       </x:c>
       <x:c r="E46" s="26" t="str">
-        <x:v>Marlin runtime probe emits duplicate AVFoundation class warnings from Homebrew ffmpeg and PyAV bundled dylibs.</x:v>
+        <x:v>Marlin runtime probe emitted duplicate AVFoundation class warnings from Homebrew ffmpeg and PyAV bundled dylibs.</x:v>
       </x:c>
       <x:c r="F46" s="26" t="str">
-        <x:v>ProjectMarlinRuntimeStatusReader successfully imports the required modules, but the Python probe stderr reports AVFFrameReceiver and AVFAudioReceiver are implemented in both /opt/homebrew/Cellar/ffmpeg/8.0.1 and the PyAV wheel's bundled dylibs. The current status remains live runtime ready, but the warning itself says it may cause casting failures or crashes.</x:v>
+        <x:v>ProjectMarlinRuntimeStatusReader imported every optional module inside one Python process. Importing av and torchcodec together loads both PyAV bundled libavdevice and Homebrew ffmpeg libavdevice, which triggers ObjC duplicate AVFFrameReceiver/AVFAudioReceiver warnings even though the actual Marlin worker imports torch/transformers lazily and single-module imports are clean.</x:v>
       </x:c>
       <x:c r="G46" s="26" t="str">
-        <x:v>Document the warning as a non-blocking logistics issue for US-061. Before relying on long live Marlin batches, investigate environment isolation or library loading if the worker crashes. Do not block mock workflow QA or status display while runtime checks remain ready.</x:v>
+        <x:v>Changed the runtime probe to import each dependency in an isolated Python child process and aggregate stdout/stderr back into the same parser contract. This still verifies torch, transformers, torchcodec, qwen-vl-utils, av, pillow, and accelerate, but avoids co-loading av and torchcodec in the parent status process.</x:v>
       </x:c>
       <x:c r="H46" s="26" t="str">
-        <x:v>marlin-runtime-status returned live runtime ready with resolvedDevice=mps and all required modules ready, while stderr contained the duplicate AVFFrameReceiver/AVFAudioReceiver warning. marlin-model-access-status, mock eval-run, index rebuild, and focused tests still passed.</x:v>
+        <x:v>Before fix, marlin-runtime-status printed duplicate AVFFrameReceiver/AVFAudioReceiver warnings. Direct experiments showed av-only, torchcodec-only, and worker torch/transformers imports were clean, while av+torchcodec in one process reproduced the warning. After fix, .build/debug/videoos-studio-cli marlin-runtime-status reports live runtime ready, resolvedDevice=mps, all modules ready, and no stderr warning. ProjectMarlinRuntimeStatusTests 5/0, swift build --target VideoOSStudio, and git diff --check passed.</x:v>
       </x:c>
       <x:c r="I46" s="11" t="str">
-        <x:v>Open; non-blocking warning</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="48" customHeight="1">
@@ -8509,541 +8509,581 @@
     </x:row>
     <x:row r="207" ht="48" customHeight="1">
       <x:c r="A207" s="10" t="str">
-        <x:v>TL-205</x:v>
+        <x:v>TL-233</x:v>
       </x:c>
       <x:c r="B207" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-046-US-066</x:v>
       </x:c>
       <x:c r="C207" s="26" t="str">
-        <x:v>Native preview duration fallback</x:v>
+        <x:v>Native macOS story coverage audit</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
+        <x:v>Parse the canonical tracker for US-046 through US-066 story statuses, related issues, and latest test-log rows after the US-065 commit.</x:v>
       </x:c>
       <x:c r="E207" s="26" t="str">
-        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
+        <x:v>All US-046 through US-066 story rows now carry native pass statuses or explicit approval/preference gates. Related fixed issues cover project creation, Command Palette, Agent lifecycle/jobs, action queue, Source Analysis, compile/review patch, timeline actions, feedback apply/undo, Clip Inspector, Candidate Swap, Footage Search, QA jump, Media Relink, Synthetic/Proxy/Smoke, Marlin runtime/native/single-source, Audio Story Graph, Render Final, Editor Handoff, SQLite/RAG, and Settings picker. The stale broad QA issue ISS-026 is closed; remaining open scope is specific to US-061 full representative Marlin batch/preference gate and operator approval gates for workspace-write actions.</x:v>
       </x:c>
       <x:c r="F207" s="11" t="str">
-        <x:v>Native pixel/runtime pass</x:v>
+        <x:v>Coverage audit pass</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="48" customHeight="1">
       <x:c r="A208" s="10" t="str">
-        <x:v>TL-206</x:v>
+        <x:v>TL-234</x:v>
       </x:c>
       <x:c r="B208" s="26" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C208" s="26" t="str">
-        <x:v>Native Clip Inspector save and clear</x:v>
+        <x:v>Marlin runtime probe warning fix</x:v>
       </x:c>
       <x:c r="D208" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
+        <x:v>Verify the duplicate AVFoundation warning source, split ProjectMarlinRuntimeStatusReader dependency imports into isolated child Python processes, rebuild, rerun ProjectMarlinRuntimeStatusTests, and rerun marlin-runtime-status.</x:v>
       </x:c>
       <x:c r="E208" s="26" t="str">
-        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
+        <x:v>av-only, torchcodec-only, and worker torch/transformers imports were clean, while av+torchcodec in one Python process reproduced duplicate AVFFrameReceiver/AVFAudioReceiver warnings. After the isolated child-process probe fix, marlin-runtime-status reports live runtime ready, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, accelerate 1.13.0, and no stderr warning. ProjectMarlinRuntimeStatusTests executed 5 tests with 0 failures; swift build --target VideoOSStudio and git diff --check passed.</x:v>
       </x:c>
       <x:c r="F208" s="11" t="str">
-        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
+        <x:v>Runtime warning fixed</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="48" customHeight="1">
       <x:c r="A209" s="10" t="str">
-        <x:v>TL-207</x:v>
+        <x:v>TL-205</x:v>
       </x:c>
       <x:c r="B209" s="26" t="str">
-        <x:v>US-058</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C209" s="26" t="str">
-        <x:v>Native QA Dashboard issue jump</x:v>
+        <x:v>Native preview duration fallback</x:v>
       </x:c>
       <x:c r="D209" s="26" t="str">
-        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
+        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
       </x:c>
       <x:c r="E209" s="26" t="str">
-        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
+        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F209" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native pixel/runtime pass</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="48" customHeight="1">
       <x:c r="A210" s="10" t="str">
-        <x:v>TL-208</x:v>
+        <x:v>TL-206</x:v>
       </x:c>
       <x:c r="B210" s="26" t="str">
-        <x:v>US-056</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C210" s="26" t="str">
-        <x:v>Native Candidate Swap sheet and staging</x:v>
+        <x:v>Native Clip Inspector save and clear</x:v>
       </x:c>
       <x:c r="D210" s="26" t="str">
-        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
+        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
       </x:c>
       <x:c r="E210" s="26" t="str">
-        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
+        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
       </x:c>
       <x:c r="F210" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
       </x:c>
     </x:row>
     <x:row r="211" ht="48" customHeight="1">
       <x:c r="A211" s="10" t="str">
-        <x:v>TL-209</x:v>
+        <x:v>TL-207</x:v>
       </x:c>
       <x:c r="B211" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-058</x:v>
       </x:c>
       <x:c r="C211" s="26" t="str">
-        <x:v>Native exact preview regeneration</x:v>
+        <x:v>Native QA Dashboard issue jump</x:v>
       </x:c>
       <x:c r="D211" s="26" t="str">
-        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
+        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
       </x:c>
       <x:c r="E211" s="26" t="str">
-        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
+        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
       </x:c>
       <x:c r="F211" s="11" t="str">
-        <x:v>Native exact preview pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="212" ht="48" customHeight="1">
       <x:c r="A212" s="10" t="str">
-        <x:v>TL-210</x:v>
+        <x:v>TL-208</x:v>
       </x:c>
       <x:c r="B212" s="26" t="str">
-        <x:v>US-047</x:v>
+        <x:v>US-056</x:v>
       </x:c>
       <x:c r="C212" s="26" t="str">
-        <x:v>Native Command Palette top-bar open/close</x:v>
+        <x:v>Native Candidate Swap sheet and staging</x:v>
       </x:c>
       <x:c r="D212" s="26" t="str">
-        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
+        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
       </x:c>
       <x:c r="E212" s="26" t="str">
-        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
+        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
       </x:c>
       <x:c r="F212" s="11" t="str">
-        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="213" ht="48" customHeight="1">
       <x:c r="A213" s="10" t="str">
-        <x:v>TL-211</x:v>
+        <x:v>TL-209</x:v>
       </x:c>
       <x:c r="B213" s="26" t="str">
-        <x:v>US-047</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C213" s="26" t="str">
-        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
+        <x:v>Native exact preview regeneration</x:v>
       </x:c>
       <x:c r="D213" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
+        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
       </x:c>
       <x:c r="E213" s="26" t="str">
-        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
+        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F213" s="11" t="str">
-        <x:v>Native keyboard/AX pass</x:v>
+        <x:v>Native exact preview pass</x:v>
       </x:c>
     </x:row>
     <x:row r="214" ht="48" customHeight="1">
       <x:c r="A214" s="10" t="str">
-        <x:v>TL-212</x:v>
+        <x:v>TL-210</x:v>
       </x:c>
       <x:c r="B214" s="26" t="str">
-        <x:v>US-048</x:v>
+        <x:v>US-047</x:v>
       </x:c>
       <x:c r="C214" s="26" t="str">
-        <x:v>Native Agent panel session lifecycle</x:v>
+        <x:v>Native Command Palette top-bar open/close</x:v>
       </x:c>
       <x:c r="D214" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
+        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
       </x:c>
       <x:c r="E214" s="26" t="str">
-        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
+        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
       </x:c>
       <x:c r="F214" s="11" t="str">
-        <x:v>Native AX/computer-use pass</x:v>
+        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="48" customHeight="1">
       <x:c r="A215" s="10" t="str">
-        <x:v>TL-213</x:v>
+        <x:v>TL-211</x:v>
       </x:c>
       <x:c r="B215" s="26" t="str">
-        <x:v>US-049</x:v>
+        <x:v>US-047</x:v>
       </x:c>
       <x:c r="C215" s="26" t="str">
-        <x:v>Native Status agent job read-only turn</x:v>
+        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
       </x:c>
       <x:c r="D215" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
+        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
       </x:c>
       <x:c r="E215" s="26" t="str">
-        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
+        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
       </x:c>
       <x:c r="F215" s="11" t="str">
-        <x:v>Native read-only job pass; approved write pending</x:v>
+        <x:v>Native keyboard/AX pass</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="48" customHeight="1">
       <x:c r="A216" s="10" t="str">
-        <x:v>TL-214</x:v>
+        <x:v>TL-212</x:v>
       </x:c>
       <x:c r="B216" s="26" t="str">
-        <x:v>US-050</x:v>
+        <x:v>US-048</x:v>
       </x:c>
       <x:c r="C216" s="26" t="str">
-        <x:v>Native Project readiness/action queue Copy pass</x:v>
+        <x:v>Native Agent panel session lifecycle</x:v>
       </x:c>
       <x:c r="D216" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
       </x:c>
       <x:c r="E216" s="26" t="str">
-        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
+        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F216" s="11" t="str">
-        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
+        <x:v>Native AX/computer-use pass</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="48" customHeight="1">
       <x:c r="A217" s="10" t="str">
-        <x:v>TL-215</x:v>
+        <x:v>TL-213</x:v>
       </x:c>
       <x:c r="B217" s="26" t="str">
-        <x:v>US-051</x:v>
+        <x:v>US-049</x:v>
       </x:c>
       <x:c r="C217" s="26" t="str">
-        <x:v>Native local Source Analysis button</x:v>
+        <x:v>Native Status agent job read-only turn</x:v>
       </x:c>
       <x:c r="D217" s="26" t="str">
-        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
       </x:c>
       <x:c r="E217" s="26" t="str">
-        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
+        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F217" s="11" t="str">
-        <x:v>Native local analysis pass</x:v>
+        <x:v>Native read-only job pass; approved write pending</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="48" customHeight="1">
       <x:c r="A218" s="10" t="str">
-        <x:v>TL-216</x:v>
+        <x:v>TL-214</x:v>
       </x:c>
       <x:c r="B218" s="26" t="str">
-        <x:v>US-052</x:v>
+        <x:v>US-050</x:v>
       </x:c>
       <x:c r="C218" s="26" t="str">
-        <x:v>Native Rough Cut and Review Patch buttons</x:v>
+        <x:v>Native Project readiness/action queue Copy pass</x:v>
       </x:c>
       <x:c r="D218" s="26" t="str">
-        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
       </x:c>
       <x:c r="E218" s="26" t="str">
-        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
       </x:c>
       <x:c r="F218" s="11" t="str">
-        <x:v>Native compile/review patch pass</x:v>
+        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="48" customHeight="1">
       <x:c r="A219" s="10" t="str">
-        <x:v>TL-217</x:v>
+        <x:v>TL-215</x:v>
       </x:c>
       <x:c r="B219" s="26" t="str">
-        <x:v>US-053</x:v>
+        <x:v>US-051</x:v>
       </x:c>
       <x:c r="C219" s="26" t="str">
-        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
+        <x:v>Native local Source Analysis button</x:v>
       </x:c>
       <x:c r="D219" s="26" t="str">
-        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
+        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E219" s="26" t="str">
-        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
+        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
       </x:c>
       <x:c r="F219" s="11" t="str">
-        <x:v>Native timeline/context menu pass</x:v>
+        <x:v>Native local analysis pass</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="48" customHeight="1">
       <x:c r="A220" s="10" t="str">
-        <x:v>TL-218</x:v>
+        <x:v>TL-216</x:v>
       </x:c>
       <x:c r="B220" s="26" t="str">
-        <x:v>US-054</x:v>
+        <x:v>US-052</x:v>
       </x:c>
       <x:c r="C220" s="26" t="str">
-        <x:v>Native Studio feedback Apply and Undo</x:v>
+        <x:v>Native Rough Cut and Review Patch buttons</x:v>
       </x:c>
       <x:c r="D220" s="26" t="str">
-        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
+        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E220" s="26" t="str">
-        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F220" s="11" t="str">
-        <x:v>Native apply/undo pass</x:v>
+        <x:v>Native compile/review patch pass</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="48" customHeight="1">
       <x:c r="A221" s="10" t="str">
-        <x:v>TL-219</x:v>
+        <x:v>TL-217</x:v>
       </x:c>
       <x:c r="B221" s="26" t="str">
-        <x:v>US-057</x:v>
+        <x:v>US-053</x:v>
       </x:c>
       <x:c r="C221" s="26" t="str">
-        <x:v>Native Footage Search sheet and replacement staging</x:v>
+        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
       </x:c>
       <x:c r="D221" s="26" t="str">
-        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
+        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
       </x:c>
       <x:c r="E221" s="26" t="str">
-        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
+        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
       </x:c>
       <x:c r="F221" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native timeline/context menu pass</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="48" customHeight="1">
       <x:c r="A222" s="10" t="str">
-        <x:v>TL-220</x:v>
+        <x:v>TL-218</x:v>
       </x:c>
       <x:c r="B222" s="26" t="str">
-        <x:v>US-066</x:v>
+        <x:v>US-054</x:v>
       </x:c>
       <x:c r="C222" s="26" t="str">
-        <x:v>Native Settings transport picker mutation</x:v>
+        <x:v>Native Studio feedback Apply and Undo</x:v>
       </x:c>
       <x:c r="D222" s="26" t="str">
-        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
+        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E222" s="26" t="str">
-        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
+        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F222" s="11" t="str">
-        <x:v>Native Settings picker mutation pass</x:v>
+        <x:v>Native apply/undo pass</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="48" customHeight="1">
       <x:c r="A223" s="10" t="str">
-        <x:v>TL-221</x:v>
+        <x:v>TL-219</x:v>
       </x:c>
       <x:c r="B223" s="26" t="str">
-        <x:v>US-059</x:v>
+        <x:v>US-057</x:v>
       </x:c>
       <x:c r="C223" s="26" t="str">
-        <x:v>Native Media Relink buttons and source-map relink</x:v>
+        <x:v>Native Footage Search sheet and replacement staging</x:v>
       </x:c>
       <x:c r="D223" s="26" t="str">
-        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
+        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
       </x:c>
       <x:c r="E223" s="26" t="str">
-        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
+        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
       </x:c>
       <x:c r="F223" s="11" t="str">
-        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="48" customHeight="1">
       <x:c r="A224" s="10" t="str">
-        <x:v>TL-222</x:v>
+        <x:v>TL-220</x:v>
       </x:c>
       <x:c r="B224" s="26" t="str">
-        <x:v>US-060</x:v>
+        <x:v>US-066</x:v>
       </x:c>
       <x:c r="C224" s="26" t="str">
-        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
+        <x:v>Native Settings transport picker mutation</x:v>
       </x:c>
       <x:c r="D224" s="26" t="str">
-        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
+        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
       </x:c>
       <x:c r="E224" s="26" t="str">
-        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
+        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F224" s="11" t="str">
-        <x:v>Native synthetic/proxy/smoke button pass</x:v>
+        <x:v>Native Settings picker mutation pass</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="48" customHeight="1">
       <x:c r="A225" s="10" t="str">
-        <x:v>TL-223</x:v>
+        <x:v>TL-221</x:v>
       </x:c>
       <x:c r="B225" s="26" t="str">
-        <x:v>US-046</x:v>
+        <x:v>US-059</x:v>
       </x:c>
       <x:c r="C225" s="26" t="str">
-        <x:v>Native New Project from Source</x:v>
+        <x:v>Native Media Relink buttons and source-map relink</x:v>
       </x:c>
       <x:c r="D225" s="26" t="str">
-        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
+        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
       </x:c>
       <x:c r="E225" s="26" t="str">
-        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
+        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
       </x:c>
       <x:c r="F225" s="11" t="str">
-        <x:v>Native project creation/NSOpenPanel pass</x:v>
+        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="48" customHeight="1">
       <x:c r="A226" s="10" t="str">
-        <x:v>TL-224</x:v>
+        <x:v>TL-222</x:v>
       </x:c>
       <x:c r="B226" s="26" t="str">
-        <x:v>US-062</x:v>
+        <x:v>US-060</x:v>
       </x:c>
       <x:c r="C226" s="26" t="str">
-        <x:v>Native MediaPanel Audio Story Graph button</x:v>
+        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
       </x:c>
       <x:c r="D226" s="26" t="str">
-        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
+        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
       </x:c>
       <x:c r="E226" s="26" t="str">
-        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
       </x:c>
       <x:c r="F226" s="11" t="str">
-        <x:v>Native AX/UI/CLI pass</x:v>
+        <x:v>Native synthetic/proxy/smoke button pass</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="48" customHeight="1">
       <x:c r="A227" s="10" t="str">
-        <x:v>TL-225</x:v>
+        <x:v>TL-223</x:v>
       </x:c>
       <x:c r="B227" s="26" t="str">
-        <x:v>US-063</x:v>
+        <x:v>US-046</x:v>
       </x:c>
       <x:c r="C227" s="26" t="str">
-        <x:v>Native Render Final Package button</x:v>
+        <x:v>Native New Project from Source</x:v>
       </x:c>
       <x:c r="D227" s="26" t="str">
-        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
+        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
       </x:c>
       <x:c r="E227" s="26" t="str">
-        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
       </x:c>
       <x:c r="F227" s="11" t="str">
-        <x:v>Native AX/UI/CLI pass</x:v>
+        <x:v>Native project creation/NSOpenPanel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="48" customHeight="1">
       <x:c r="A228" s="10" t="str">
-        <x:v>TL-226</x:v>
+        <x:v>TL-224</x:v>
       </x:c>
       <x:c r="B228" s="26" t="str">
-        <x:v>US-064</x:v>
+        <x:v>US-062</x:v>
       </x:c>
       <x:c r="C228" s="26" t="str">
-        <x:v>Native Editor Handoff export and Finder reveal</x:v>
+        <x:v>Native MediaPanel Audio Story Graph button</x:v>
       </x:c>
       <x:c r="D228" s="26" t="str">
-        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
+        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E228" s="26" t="str">
-        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
+        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F228" s="11" t="str">
-        <x:v>Native AX/UI/Finder/CLI pass</x:v>
+        <x:v>Native AX/UI/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="48" customHeight="1">
       <x:c r="A229" s="10" t="str">
-        <x:v>TL-227</x:v>
+        <x:v>TL-225</x:v>
       </x:c>
       <x:c r="B229" s="26" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-063</x:v>
       </x:c>
       <x:c r="C229" s="26" t="str">
-        <x:v>Native Ask Codex editor-note proposal</x:v>
+        <x:v>Native Render Final Package button</x:v>
       </x:c>
       <x:c r="D229" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
+        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
       </x:c>
       <x:c r="E229" s="26" t="str">
-        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
+        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F229" s="11" t="str">
-        <x:v>Native read-only Codex proposal pass</x:v>
+        <x:v>Native AX/UI/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="48" customHeight="1">
       <x:c r="A230" s="10" t="str">
-        <x:v>TL-228</x:v>
+        <x:v>TL-226</x:v>
       </x:c>
       <x:c r="B230" s="26" t="str">
-        <x:v>US-061</x:v>
+        <x:v>US-064</x:v>
       </x:c>
       <x:c r="C230" s="26" t="str">
-        <x:v>Live Marlin single-source completion</x:v>
+        <x:v>Native Editor Handoff export and Finder reveal</x:v>
       </x:c>
       <x:c r="D230" s="26" t="str">
-        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
+        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E230" s="26" t="str">
-        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
+        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
       </x:c>
       <x:c r="F230" s="11" t="str">
-        <x:v>Live single-source pass; full representative batch pending</x:v>
+        <x:v>Native AX/UI/Finder/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="48" customHeight="1">
       <x:c r="A231" s="10" t="str">
-        <x:v>TL-229</x:v>
+        <x:v>TL-227</x:v>
       </x:c>
       <x:c r="B231" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C231" s="26" t="str">
-        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+        <x:v>Native Ask Codex editor-note proposal</x:v>
       </x:c>
       <x:c r="D231" s="26" t="str">
-        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
       </x:c>
       <x:c r="E231" s="26" t="str">
-        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
       </x:c>
       <x:c r="F231" s="11" t="str">
-        <x:v>Native fresh-launch pixel pass</x:v>
+        <x:v>Native read-only Codex proposal pass</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="48" customHeight="1">
       <x:c r="A232" s="10" t="str">
+        <x:v>TL-228</x:v>
+      </x:c>
+      <x:c r="B232" s="26" t="str">
+        <x:v>US-061</x:v>
+      </x:c>
+      <x:c r="C232" s="26" t="str">
+        <x:v>Live Marlin single-source completion</x:v>
+      </x:c>
+      <x:c r="D232" s="26" t="str">
+        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
+      </x:c>
+      <x:c r="E232" s="26" t="str">
+        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
+      </x:c>
+      <x:c r="F232" s="11" t="str">
+        <x:v>Live single-source pass; full representative batch pending</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" ht="48" customHeight="1">
+      <x:c r="A233" s="10" t="str">
+        <x:v>TL-229</x:v>
+      </x:c>
+      <x:c r="B233" s="26" t="str">
+        <x:v>US-045</x:v>
+      </x:c>
+      <x:c r="C233" s="26" t="str">
+        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+      </x:c>
+      <x:c r="D233" s="26" t="str">
+        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+      </x:c>
+      <x:c r="E233" s="26" t="str">
+        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+      </x:c>
+      <x:c r="F233" s="11" t="str">
+        <x:v>Native fresh-launch pixel pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" ht="48" customHeight="1">
+      <x:c r="A234" s="10" t="str">
         <x:v>TL-230</x:v>
       </x:c>
-      <x:c r="B232" s="26" t="str">
+      <x:c r="B234" s="26" t="str">
         <x:v>US-045</x:v>
       </x:c>
-      <x:c r="C232" s="26" t="str">
+      <x:c r="C234" s="26" t="str">
         <x:v>AX-1 exact preview promotion and pixel pass</x:v>
       </x:c>
-      <x:c r="D232" s="26" t="str">
+      <x:c r="D234" s="26" t="str">
         <x:v>Run videoos-studio-cli compile-run on projects/ax1-participant-voices-20260401, confirm playback-contract-status, select ProjectShelf.ax1-participant-voices-20260401 in VideoOSStudio, capture /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and run Retina-coordinate pixel statistics on the Viewer region.</x:v>
       </x:c>
-      <x:c r="E232" s="26" t="str">
+      <x:c r="E234" s="26" t="str">
         <x:v>Before compile, playback-contract-status returned legacy_manifest and approvalGrade=false. compile-run completed with exitCode=0, timeline compiled, indexDocuments=492, and git status stayed clean. After compile, playback-contract-status returned state=exact, approvalGrade=true, timelineHash=171378fe2bfe3a7c, and manifestBaseTimelineHash=171378fe2bfe3a7c. Native Viewer showed Exact preview / preview-editor-1775121573933.mp4 and Timeline preview D4887.MP4 with a visible interview frame. Screenshot was 3.5M; viewer_person_actual mean_rgb=(144.62,141.42,149.8) and near_black_pct=0.0004, while left pillarbox near_black_pct=1.0000 as expected.</x:v>
       </x:c>
-      <x:c r="F232" s="11" t="str">
+      <x:c r="F234" s="11" t="str">
         <x:v>Native AX-1 exact/pixel pass</x:v>
       </x:c>
     </x:row>
-    <x:row r="233" ht="48" customHeight="1">
-      <x:c r="A233" s="12" t="str">
+    <x:row r="235" ht="48" customHeight="1">
+      <x:c r="A235" s="12" t="str">
         <x:v>TL-231</x:v>
       </x:c>
-      <x:c r="B233" s="27" t="str">
+      <x:c r="B235" s="27" t="str">
         <x:v>US-050</x:v>
       </x:c>
-      <x:c r="C233" s="27" t="str">
+      <x:c r="C235" s="27" t="str">
         <x:v>Native Action Queue approval gate</x:v>
       </x:c>
-      <x:c r="D233" s="27" t="str">
+      <x:c r="D235" s="27" t="str">
         <x:v>Add ProjectPanel.ActionQueue* identifiers, relaunch VideoOSStudio, select AX-1 Project tab, inspect the Action Queue AX tree, click ProjectPanel.ActionQueueRunButton.rough-cut-review, and stop at the Codex approval gate without approving writes.</x:v>
       </x:c>
-      <x:c r="E233" s="27" t="str">
+      <x:c r="E235" s="27" t="str">
         <x:v>AX exposed ProjectPanel.ActionQueueRunButton.rough-cut-review, ProjectPanel.ActionQueueCopyButton.rough-cut-review, ProjectPanel.ActionQueueRunButton.marlin-default, and ProjectPanel.ActionQueueCopyButton.marlin-default. Clicking rough-cut-review changed the row to disabled Starting Codex session for Review..., then to Opening Codex approval gate for Review. ps showed a Codex app-server child under VideoOSStudio; git status listed only the intentional ProjectInspectorViews.swift edit, and projects/ax1-participant-voices-20260401/06_review still contained only human_notes.yaml.</x:v>
       </x:c>
-      <x:c r="F233" s="13" t="str">
+      <x:c r="F235" s="13" t="str">
         <x:v>Native approval-gate pass; write not approved</x:v>
       </x:c>
     </x:row>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra11f5bae122a44c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R7272303ee7ba4cd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R4250cb3741a442ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R31a5deb299874f7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Ra11d324c517f465e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R65d63d4c3df04629"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R425176be7927432e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R3b17f665144e4f6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R690e448556fa47ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R6f78ac45a62349aa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-061 loop reproduced the duplicate AVFoundation warning with av+torchcodec in one Python process, confirmed av-only, torchcodec-only, and worker torch/transformers imports are clean, then verified the isolated child-process probe: marlin-runtime-status reports live runtime ready, resolvedDevice=mps, all required modules ready, and no stderr warning. ProjectMarlinRuntimeStatusTests executed 5 tests with 0 failures; swift build --target VideoOSStudio and git diff --check passed. The same pass audited US-046 through US-066 and closed the stale broad QA gap ISS-026 because all native macOS stories now have native pass statuses or explicit approval/preference gates. Prior US-065 RAG/Add/Agent-tab, US-050 approval gate, US-045 exact preview, US-061 live single-source, US-055 Ask Codex proposal, US-064 Editor Handoff export, US-063 Render Final Package, US-062 Audio Story Graph, US-046 New Project, US-060 Synthetic/Proxy/Smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-055 Save/Clear, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, and exact preview loops remain verified.</x:v>
+        <x:v>Latest US-047 retest verified current Command Palette repeatability on VideoOSStudio PID 25505 after ./script/build_and_run.sh --verify: top-bar open exposed CommandPalettePanel/SearchField/CloseButton and stable CommandPaletteItem.* IDs, AXValue search footage filtered to CommandPaletteItem.search-footage, Return opened FootageSearch.Title, super+k opened the palette, and Escape dismissed it. This closes the stale ISS-027 mitigation because the current Computer Use path now proves top-bar, search, Return execution, Cmd-K, and Esc. Prior US-061 loop reproduced the duplicate AVFoundation warning with av+torchcodec in one Python process, confirmed av-only, torchcodec-only, and worker torch/transformers imports are clean, then verified the isolated child-process probe: marlin-runtime-status reports live runtime ready, resolvedDevice=mps, all required modules ready, and no stderr warning. ProjectMarlinRuntimeStatusTests executed 5 tests with 0 failures; swift build --target VideoOSStudio and git diff --check passed. The same pass audited US-046 through US-066 and closed the stale broad QA gap ISS-026 because all native macOS stories now have native pass statuses or explicit approval/preference gates.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest runtime/native check is the US-061 marlin-runtime-status pass after rebuilding the Swift core: status live runtime ready, resolvedDevice=mps, all modules ready, and no duplicate AVFoundation stderr warning. The previous native UI check selected ProjectShelf.ax1-participant-voices-20260401, confirmed InspectorTab.Agent/Project/Clip/Media/QA, selected Media, searched 参加 in MediaPanel.IndexSearchField, observed Found 3 index results and 3 cited items ready for Codex prompt context, clicked MediaPanel.AddRAGContextButton, selected InspectorTab.Agent, and confirmed the Agent prompt contains Material RAG context for query `参加` with audio-story-node, segment, and transcript citations. Prior native visual checks include the US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-061 Marlin AX/readiness, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, US-047 Command Palette, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest runtime/native check is the US-047 Command Palette computer-use pass on VideoOSStudio PID 25505: CommandPaletteButton opened CommandPalettePanel, search footage filtered to CommandPaletteItem.search-footage, Return opened the Footage Search sheet for ax1-participant-voices-20260401, closing it left FeedbackStatus Footage search opened, super+k opened the palette again, and Escape returned to VideoOSStudioMainWindow. Prior native checks include the US-061 marlin-runtime-status pass, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -1794,7 +1794,7 @@
         <x:v>Native Command Palette keyboard/top-bar pass</x:v>
       </x:c>
       <x:c r="H48" s="11" t="str">
-        <x:v>AX smoke verified Project, Media, and QA toolbar tabs; app menu opens a CGWindow-titled Command Palette panel. Command Palette commands use stable Core command IDs and deterministic accessibility identifiers instead of title-derived IDs, and search is covered by StudioCommandPaletteCommandTests for title, subtitle, keyword, multi-token, and play/pause state matching. computer-use clicked CommandPaletteButton element 10, opened CommandPalettePanel with CommandPaletteSearchField, CommandPaletteCloseButton, and command item IDs including refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph, then closed the panel through CommandPaletteCloseButton element 4. The latest fix syncs the reused NSTextField value from the cleared query before focusing, eliminating stale search text after reopening. On PID 24960, Cmd-K opened the palette, AXValue search footage filtered to only CommandPaletteItem.search-footage, Return opened the Search Footage sheet, closing the sheet left status Footage search opened, and Esc dismissed a reopened Command Palette. swift build --target VideoOSStudio, swift test --filter StudioCommandPaletteCommandTests 4/0, build_and_run.sh --verify, and git diff --check passed.</x:v>
+        <x:v>AX smoke verified Project, Media, and QA toolbar tabs; app menu opens a CGWindow-titled Command Palette panel. Command Palette commands use stable Core command IDs and deterministic accessibility identifiers instead of title-derived IDs, and search is covered by StudioCommandPaletteCommandTests for title, subtitle, keyword, multi-token, and play/pause state matching. computer-use clicked CommandPaletteButton element 10, opened CommandPalettePanel with CommandPaletteSearchField, CommandPaletteCloseButton, and command item IDs including refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph, then closed the panel through CommandPaletteCloseButton element 4. The latest fix syncs the reused NSTextField value from the cleared query before focusing, eliminating stale search text after reopening. On PID 24960, Cmd-K opened the palette, AXValue search footage filtered to only CommandPaletteItem.search-footage, Return opened the Search Footage sheet, closing the sheet left status Footage search opened, and Esc dismissed a reopened Command Palette. Fresh retest on PID 25505 repeated the current path: top-bar open, AXValue search footage, Return opened FootageSearch.Title, super+k opened CommandPalettePanel, and Escape dismissed it. swift build --target VideoOSStudio, swift test --filter StudioCommandPaletteCommandTests 4/0, build_and_run.sh --verify, and git diff --check passed.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="48" customHeight="1">
@@ -3108,19 +3108,19 @@
         <x:v>Accessibility/test logistics</x:v>
       </x:c>
       <x:c r="E28" s="26" t="str">
-        <x:v>Native Command Palette and some top-level controls are still not fully repeatable through macOS automation.</x:v>
+        <x:v>Native Command Palette and top-level controls previously were not fully repeatable through macOS automation.</x:v>
       </x:c>
       <x:c r="F28" s="26" t="str">
-        <x:v>The old SwiftUI sheet was unnamed and hard to observe as a stable macOS window; openCommandPalette also reused showMainWindow, whose delayed makeKeyAndOrderFront retries could steal focus back from the palette. Separately, this environment still fails to inject keyboard events into VideoOSStudio reliably.</x:v>
+        <x:v>The old SwiftUI sheet was unnamed and hard to observe as a stable macOS window; openCommandPalette also reused showMainWindow, whose delayed makeKeyAndOrderFront retries could steal focus back from the palette. Earlier keyboard injection paths also failed to provide repeatable Cmd-K/search/Return/Esc evidence.</x:v>
       </x:c>
       <x:c r="G28" s="26" t="str">
-        <x:v>Replaced the Command Palette sheet with a titled NSPanel/NSHostingController presenter, preserved the existing command view/actions, added a CommandPalettePanel identifier, added a close notification, prevented delayed main-window focus retries when opening the palette, focused the search NSTextField after panel display, added a local Cmd-K monitor, and made Return execute the first enabled filtered command.</x:v>
+        <x:v>Replaced the Command Palette sheet with a titled NSPanel/NSHostingController presenter, preserved the existing command view/actions, added a CommandPalettePanel identifier, added a close notification, prevented delayed main-window focus retries when opening the palette, focused and synchronized the search NSTextField after panel display, added a local Cmd-K monitor, and made Return execute the first enabled filtered command.</x:v>
       </x:c>
       <x:c r="H28" s="26" t="str">
-        <x:v>swift build --target VideoOSStudio passed; ./script/build_and_run.sh --verify passed; app menu Command Palette... produced a visible CGWindow named Command Palette. System Events, CGEvent tap, and postToPid keyboard injection still did not provide repeatable Cmd-K/search/Return/Esc evidence in this environment.</x:v>
+        <x:v>Fresh 2026-06-23 retest after ./script/build_and_run.sh --verify on VideoOSStudio PID 25505: CommandPaletteButton opened CommandPalettePanel with CommandPaletteSearchField and stable CommandPaletteItem.* IDs, AXValue search footage filtered to only CommandPaletteItem.search-footage, Return opened FootageSearch.Title for ax1-participant-voices-20260401, closing the sheet left FeedbackStatus Footage search opened, super+k reopened CommandPalettePanel, and Escape dismissed it back to VideoOSStudioMainWindow.</x:v>
       </x:c>
       <x:c r="I28" s="11" t="str">
-        <x:v>Mitigated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="48" customHeight="1">
@@ -8549,79 +8549,79 @@
     </x:row>
     <x:row r="209" ht="48" customHeight="1">
       <x:c r="A209" s="10" t="str">
-        <x:v>TL-205</x:v>
+        <x:v>TL-235</x:v>
       </x:c>
       <x:c r="B209" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-047</x:v>
       </x:c>
       <x:c r="C209" s="26" t="str">
-        <x:v>Native preview duration fallback</x:v>
+        <x:v>Fresh Command Palette repeatability retest</x:v>
       </x:c>
       <x:c r="D209" s="26" t="str">
-        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
+        <x:v>./script/build_and_run.sh --verify; computer-use top-bar open, AXValue search footage, Return execute, close Search Footage, super+k open, and Escape dismiss</x:v>
       </x:c>
       <x:c r="E209" s="26" t="str">
-        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
+        <x:v>VideoOSStudio PID 25505 exposed CommandPaletteButton element 10. Top-bar click opened CommandPalettePanel with CommandPaletteSearchField, CommandPaletteCloseButton, and stable command IDs. AXValue search footage filtered to only CommandPaletteItem.search-footage. Return opened FootageSearch.Title for ax1-participant-voices-20260401 and closing it left FeedbackStatus Footage search opened. super+k opened CommandPalettePanel again and Escape dismissed it back to VideoOSStudioMainWindow.</x:v>
       </x:c>
       <x:c r="F209" s="11" t="str">
-        <x:v>Native pixel/runtime pass</x:v>
+        <x:v>Native repeatability pass; ISS-027 fixed</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="48" customHeight="1">
       <x:c r="A210" s="10" t="str">
-        <x:v>TL-206</x:v>
+        <x:v>TL-205</x:v>
       </x:c>
       <x:c r="B210" s="26" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C210" s="26" t="str">
-        <x:v>Native Clip Inspector save and clear</x:v>
+        <x:v>Native preview duration fallback</x:v>
       </x:c>
       <x:c r="D210" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
+        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
       </x:c>
       <x:c r="E210" s="26" t="str">
-        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
+        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F210" s="11" t="str">
-        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
+        <x:v>Native pixel/runtime pass</x:v>
       </x:c>
     </x:row>
     <x:row r="211" ht="48" customHeight="1">
       <x:c r="A211" s="10" t="str">
-        <x:v>TL-207</x:v>
+        <x:v>TL-206</x:v>
       </x:c>
       <x:c r="B211" s="26" t="str">
-        <x:v>US-058</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C211" s="26" t="str">
-        <x:v>Native QA Dashboard issue jump</x:v>
+        <x:v>Native Clip Inspector save and clear</x:v>
       </x:c>
       <x:c r="D211" s="26" t="str">
-        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
+        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
       </x:c>
       <x:c r="E211" s="26" t="str">
-        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
+        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
       </x:c>
       <x:c r="F211" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
       </x:c>
     </x:row>
     <x:row r="212" ht="48" customHeight="1">
       <x:c r="A212" s="10" t="str">
-        <x:v>TL-208</x:v>
+        <x:v>TL-207</x:v>
       </x:c>
       <x:c r="B212" s="26" t="str">
-        <x:v>US-056</x:v>
+        <x:v>US-058</x:v>
       </x:c>
       <x:c r="C212" s="26" t="str">
-        <x:v>Native Candidate Swap sheet and staging</x:v>
+        <x:v>Native QA Dashboard issue jump</x:v>
       </x:c>
       <x:c r="D212" s="26" t="str">
-        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
+        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
       </x:c>
       <x:c r="E212" s="26" t="str">
-        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
+        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
       </x:c>
       <x:c r="F212" s="11" t="str">
         <x:v>Native AX/pixel pass</x:v>
@@ -8629,339 +8629,339 @@
     </x:row>
     <x:row r="213" ht="48" customHeight="1">
       <x:c r="A213" s="10" t="str">
-        <x:v>TL-209</x:v>
+        <x:v>TL-208</x:v>
       </x:c>
       <x:c r="B213" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-056</x:v>
       </x:c>
       <x:c r="C213" s="26" t="str">
-        <x:v>Native exact preview regeneration</x:v>
+        <x:v>Native Candidate Swap sheet and staging</x:v>
       </x:c>
       <x:c r="D213" s="26" t="str">
-        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
+        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
       </x:c>
       <x:c r="E213" s="26" t="str">
-        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
       </x:c>
       <x:c r="F213" s="11" t="str">
-        <x:v>Native exact preview pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="214" ht="48" customHeight="1">
       <x:c r="A214" s="10" t="str">
-        <x:v>TL-210</x:v>
+        <x:v>TL-209</x:v>
       </x:c>
       <x:c r="B214" s="26" t="str">
-        <x:v>US-047</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C214" s="26" t="str">
-        <x:v>Native Command Palette top-bar open/close</x:v>
+        <x:v>Native exact preview regeneration</x:v>
       </x:c>
       <x:c r="D214" s="26" t="str">
-        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
+        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
       </x:c>
       <x:c r="E214" s="26" t="str">
-        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
+        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F214" s="11" t="str">
-        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
+        <x:v>Native exact preview pass</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="48" customHeight="1">
       <x:c r="A215" s="10" t="str">
-        <x:v>TL-211</x:v>
+        <x:v>TL-210</x:v>
       </x:c>
       <x:c r="B215" s="26" t="str">
         <x:v>US-047</x:v>
       </x:c>
       <x:c r="C215" s="26" t="str">
-        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
+        <x:v>Native Command Palette top-bar open/close</x:v>
       </x:c>
       <x:c r="D215" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
+        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
       </x:c>
       <x:c r="E215" s="26" t="str">
-        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
+        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
       </x:c>
       <x:c r="F215" s="11" t="str">
-        <x:v>Native keyboard/AX pass</x:v>
+        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="48" customHeight="1">
       <x:c r="A216" s="10" t="str">
-        <x:v>TL-212</x:v>
+        <x:v>TL-211</x:v>
       </x:c>
       <x:c r="B216" s="26" t="str">
-        <x:v>US-048</x:v>
+        <x:v>US-047</x:v>
       </x:c>
       <x:c r="C216" s="26" t="str">
-        <x:v>Native Agent panel session lifecycle</x:v>
+        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
       </x:c>
       <x:c r="D216" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
+        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
       </x:c>
       <x:c r="E216" s="26" t="str">
-        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
+        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
       </x:c>
       <x:c r="F216" s="11" t="str">
-        <x:v>Native AX/computer-use pass</x:v>
+        <x:v>Native keyboard/AX pass</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="48" customHeight="1">
       <x:c r="A217" s="10" t="str">
-        <x:v>TL-213</x:v>
+        <x:v>TL-212</x:v>
       </x:c>
       <x:c r="B217" s="26" t="str">
-        <x:v>US-049</x:v>
+        <x:v>US-048</x:v>
       </x:c>
       <x:c r="C217" s="26" t="str">
-        <x:v>Native Status agent job read-only turn</x:v>
+        <x:v>Native Agent panel session lifecycle</x:v>
       </x:c>
       <x:c r="D217" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
       </x:c>
       <x:c r="E217" s="26" t="str">
-        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
+        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F217" s="11" t="str">
-        <x:v>Native read-only job pass; approved write pending</x:v>
+        <x:v>Native AX/computer-use pass</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="48" customHeight="1">
       <x:c r="A218" s="10" t="str">
-        <x:v>TL-214</x:v>
+        <x:v>TL-213</x:v>
       </x:c>
       <x:c r="B218" s="26" t="str">
-        <x:v>US-050</x:v>
+        <x:v>US-049</x:v>
       </x:c>
       <x:c r="C218" s="26" t="str">
-        <x:v>Native Project readiness/action queue Copy pass</x:v>
+        <x:v>Native Status agent job read-only turn</x:v>
       </x:c>
       <x:c r="D218" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
       </x:c>
       <x:c r="E218" s="26" t="str">
-        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
+        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F218" s="11" t="str">
-        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
+        <x:v>Native read-only job pass; approved write pending</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="48" customHeight="1">
       <x:c r="A219" s="10" t="str">
-        <x:v>TL-215</x:v>
+        <x:v>TL-214</x:v>
       </x:c>
       <x:c r="B219" s="26" t="str">
-        <x:v>US-051</x:v>
+        <x:v>US-050</x:v>
       </x:c>
       <x:c r="C219" s="26" t="str">
-        <x:v>Native local Source Analysis button</x:v>
+        <x:v>Native Project readiness/action queue Copy pass</x:v>
       </x:c>
       <x:c r="D219" s="26" t="str">
-        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
       </x:c>
       <x:c r="E219" s="26" t="str">
-        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
+        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
       </x:c>
       <x:c r="F219" s="11" t="str">
-        <x:v>Native local analysis pass</x:v>
+        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="48" customHeight="1">
       <x:c r="A220" s="10" t="str">
-        <x:v>TL-216</x:v>
+        <x:v>TL-215</x:v>
       </x:c>
       <x:c r="B220" s="26" t="str">
-        <x:v>US-052</x:v>
+        <x:v>US-051</x:v>
       </x:c>
       <x:c r="C220" s="26" t="str">
-        <x:v>Native Rough Cut and Review Patch buttons</x:v>
+        <x:v>Native local Source Analysis button</x:v>
       </x:c>
       <x:c r="D220" s="26" t="str">
-        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
+        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E220" s="26" t="str">
-        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
       </x:c>
       <x:c r="F220" s="11" t="str">
-        <x:v>Native compile/review patch pass</x:v>
+        <x:v>Native local analysis pass</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="48" customHeight="1">
       <x:c r="A221" s="10" t="str">
-        <x:v>TL-217</x:v>
+        <x:v>TL-216</x:v>
       </x:c>
       <x:c r="B221" s="26" t="str">
-        <x:v>US-053</x:v>
+        <x:v>US-052</x:v>
       </x:c>
       <x:c r="C221" s="26" t="str">
-        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
+        <x:v>Native Rough Cut and Review Patch buttons</x:v>
       </x:c>
       <x:c r="D221" s="26" t="str">
-        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
+        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E221" s="26" t="str">
-        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
+        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F221" s="11" t="str">
-        <x:v>Native timeline/context menu pass</x:v>
+        <x:v>Native compile/review patch pass</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="48" customHeight="1">
       <x:c r="A222" s="10" t="str">
-        <x:v>TL-218</x:v>
+        <x:v>TL-217</x:v>
       </x:c>
       <x:c r="B222" s="26" t="str">
-        <x:v>US-054</x:v>
+        <x:v>US-053</x:v>
       </x:c>
       <x:c r="C222" s="26" t="str">
-        <x:v>Native Studio feedback Apply and Undo</x:v>
+        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
       </x:c>
       <x:c r="D222" s="26" t="str">
-        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
+        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
       </x:c>
       <x:c r="E222" s="26" t="str">
-        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
       </x:c>
       <x:c r="F222" s="11" t="str">
-        <x:v>Native apply/undo pass</x:v>
+        <x:v>Native timeline/context menu pass</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="48" customHeight="1">
       <x:c r="A223" s="10" t="str">
-        <x:v>TL-219</x:v>
+        <x:v>TL-218</x:v>
       </x:c>
       <x:c r="B223" s="26" t="str">
-        <x:v>US-057</x:v>
+        <x:v>US-054</x:v>
       </x:c>
       <x:c r="C223" s="26" t="str">
-        <x:v>Native Footage Search sheet and replacement staging</x:v>
+        <x:v>Native Studio feedback Apply and Undo</x:v>
       </x:c>
       <x:c r="D223" s="26" t="str">
-        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
+        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E223" s="26" t="str">
-        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
+        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F223" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native apply/undo pass</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="48" customHeight="1">
       <x:c r="A224" s="10" t="str">
-        <x:v>TL-220</x:v>
+        <x:v>TL-219</x:v>
       </x:c>
       <x:c r="B224" s="26" t="str">
-        <x:v>US-066</x:v>
+        <x:v>US-057</x:v>
       </x:c>
       <x:c r="C224" s="26" t="str">
-        <x:v>Native Settings transport picker mutation</x:v>
+        <x:v>Native Footage Search sheet and replacement staging</x:v>
       </x:c>
       <x:c r="D224" s="26" t="str">
-        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
+        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
       </x:c>
       <x:c r="E224" s="26" t="str">
-        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
       </x:c>
       <x:c r="F224" s="11" t="str">
-        <x:v>Native Settings picker mutation pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="48" customHeight="1">
       <x:c r="A225" s="10" t="str">
-        <x:v>TL-221</x:v>
+        <x:v>TL-220</x:v>
       </x:c>
       <x:c r="B225" s="26" t="str">
-        <x:v>US-059</x:v>
+        <x:v>US-066</x:v>
       </x:c>
       <x:c r="C225" s="26" t="str">
-        <x:v>Native Media Relink buttons and source-map relink</x:v>
+        <x:v>Native Settings transport picker mutation</x:v>
       </x:c>
       <x:c r="D225" s="26" t="str">
-        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
+        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
       </x:c>
       <x:c r="E225" s="26" t="str">
-        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
+        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F225" s="11" t="str">
-        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
+        <x:v>Native Settings picker mutation pass</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="48" customHeight="1">
       <x:c r="A226" s="10" t="str">
-        <x:v>TL-222</x:v>
+        <x:v>TL-221</x:v>
       </x:c>
       <x:c r="B226" s="26" t="str">
-        <x:v>US-060</x:v>
+        <x:v>US-059</x:v>
       </x:c>
       <x:c r="C226" s="26" t="str">
-        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
+        <x:v>Native Media Relink buttons and source-map relink</x:v>
       </x:c>
       <x:c r="D226" s="26" t="str">
-        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
+        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
       </x:c>
       <x:c r="E226" s="26" t="str">
-        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
+        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
       </x:c>
       <x:c r="F226" s="11" t="str">
-        <x:v>Native synthetic/proxy/smoke button pass</x:v>
+        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="48" customHeight="1">
       <x:c r="A227" s="10" t="str">
-        <x:v>TL-223</x:v>
+        <x:v>TL-222</x:v>
       </x:c>
       <x:c r="B227" s="26" t="str">
-        <x:v>US-046</x:v>
+        <x:v>US-060</x:v>
       </x:c>
       <x:c r="C227" s="26" t="str">
-        <x:v>Native New Project from Source</x:v>
+        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
       </x:c>
       <x:c r="D227" s="26" t="str">
-        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
+        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
       </x:c>
       <x:c r="E227" s="26" t="str">
-        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
+        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
       </x:c>
       <x:c r="F227" s="11" t="str">
-        <x:v>Native project creation/NSOpenPanel pass</x:v>
+        <x:v>Native synthetic/proxy/smoke button pass</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="48" customHeight="1">
       <x:c r="A228" s="10" t="str">
-        <x:v>TL-224</x:v>
+        <x:v>TL-223</x:v>
       </x:c>
       <x:c r="B228" s="26" t="str">
-        <x:v>US-062</x:v>
+        <x:v>US-046</x:v>
       </x:c>
       <x:c r="C228" s="26" t="str">
-        <x:v>Native MediaPanel Audio Story Graph button</x:v>
+        <x:v>Native New Project from Source</x:v>
       </x:c>
       <x:c r="D228" s="26" t="str">
-        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
+        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
       </x:c>
       <x:c r="E228" s="26" t="str">
-        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
       </x:c>
       <x:c r="F228" s="11" t="str">
-        <x:v>Native AX/UI/CLI pass</x:v>
+        <x:v>Native project creation/NSOpenPanel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="48" customHeight="1">
       <x:c r="A229" s="10" t="str">
-        <x:v>TL-225</x:v>
+        <x:v>TL-224</x:v>
       </x:c>
       <x:c r="B229" s="26" t="str">
-        <x:v>US-063</x:v>
+        <x:v>US-062</x:v>
       </x:c>
       <x:c r="C229" s="26" t="str">
-        <x:v>Native Render Final Package button</x:v>
+        <x:v>Native MediaPanel Audio Story Graph button</x:v>
       </x:c>
       <x:c r="D229" s="26" t="str">
-        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
+        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E229" s="26" t="str">
-        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F229" s="11" t="str">
         <x:v>Native AX/UI/CLI pass</x:v>
@@ -8969,121 +8969,141 @@
     </x:row>
     <x:row r="230" ht="48" customHeight="1">
       <x:c r="A230" s="10" t="str">
-        <x:v>TL-226</x:v>
+        <x:v>TL-225</x:v>
       </x:c>
       <x:c r="B230" s="26" t="str">
-        <x:v>US-064</x:v>
+        <x:v>US-063</x:v>
       </x:c>
       <x:c r="C230" s="26" t="str">
-        <x:v>Native Editor Handoff export and Finder reveal</x:v>
+        <x:v>Native Render Final Package button</x:v>
       </x:c>
       <x:c r="D230" s="26" t="str">
-        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
+        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
       </x:c>
       <x:c r="E230" s="26" t="str">
-        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
+        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F230" s="11" t="str">
-        <x:v>Native AX/UI/Finder/CLI pass</x:v>
+        <x:v>Native AX/UI/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="48" customHeight="1">
       <x:c r="A231" s="10" t="str">
-        <x:v>TL-227</x:v>
+        <x:v>TL-226</x:v>
       </x:c>
       <x:c r="B231" s="26" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-064</x:v>
       </x:c>
       <x:c r="C231" s="26" t="str">
-        <x:v>Native Ask Codex editor-note proposal</x:v>
+        <x:v>Native Editor Handoff export and Finder reveal</x:v>
       </x:c>
       <x:c r="D231" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
+        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E231" s="26" t="str">
-        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
+        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
       </x:c>
       <x:c r="F231" s="11" t="str">
-        <x:v>Native read-only Codex proposal pass</x:v>
+        <x:v>Native AX/UI/Finder/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="48" customHeight="1">
       <x:c r="A232" s="10" t="str">
-        <x:v>TL-228</x:v>
+        <x:v>TL-227</x:v>
       </x:c>
       <x:c r="B232" s="26" t="str">
-        <x:v>US-061</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C232" s="26" t="str">
-        <x:v>Live Marlin single-source completion</x:v>
+        <x:v>Native Ask Codex editor-note proposal</x:v>
       </x:c>
       <x:c r="D232" s="26" t="str">
-        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
+        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
       </x:c>
       <x:c r="E232" s="26" t="str">
-        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
+        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
       </x:c>
       <x:c r="F232" s="11" t="str">
-        <x:v>Live single-source pass; full representative batch pending</x:v>
+        <x:v>Native read-only Codex proposal pass</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="48" customHeight="1">
       <x:c r="A233" s="10" t="str">
-        <x:v>TL-229</x:v>
+        <x:v>TL-228</x:v>
       </x:c>
       <x:c r="B233" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C233" s="26" t="str">
-        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+        <x:v>Live Marlin single-source completion</x:v>
       </x:c>
       <x:c r="D233" s="26" t="str">
-        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
       </x:c>
       <x:c r="E233" s="26" t="str">
-        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
       </x:c>
       <x:c r="F233" s="11" t="str">
-        <x:v>Native fresh-launch pixel pass</x:v>
+        <x:v>Live single-source pass; full representative batch pending</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="48" customHeight="1">
       <x:c r="A234" s="10" t="str">
-        <x:v>TL-230</x:v>
+        <x:v>TL-229</x:v>
       </x:c>
       <x:c r="B234" s="26" t="str">
         <x:v>US-045</x:v>
       </x:c>
       <x:c r="C234" s="26" t="str">
+        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+      </x:c>
+      <x:c r="D234" s="26" t="str">
+        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+      </x:c>
+      <x:c r="E234" s="26" t="str">
+        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+      </x:c>
+      <x:c r="F234" s="11" t="str">
+        <x:v>Native fresh-launch pixel pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" ht="48" customHeight="1">
+      <x:c r="A235" s="10" t="str">
+        <x:v>TL-230</x:v>
+      </x:c>
+      <x:c r="B235" s="26" t="str">
+        <x:v>US-045</x:v>
+      </x:c>
+      <x:c r="C235" s="26" t="str">
         <x:v>AX-1 exact preview promotion and pixel pass</x:v>
       </x:c>
-      <x:c r="D234" s="26" t="str">
+      <x:c r="D235" s="26" t="str">
         <x:v>Run videoos-studio-cli compile-run on projects/ax1-participant-voices-20260401, confirm playback-contract-status, select ProjectShelf.ax1-participant-voices-20260401 in VideoOSStudio, capture /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and run Retina-coordinate pixel statistics on the Viewer region.</x:v>
       </x:c>
-      <x:c r="E234" s="26" t="str">
+      <x:c r="E235" s="26" t="str">
         <x:v>Before compile, playback-contract-status returned legacy_manifest and approvalGrade=false. compile-run completed with exitCode=0, timeline compiled, indexDocuments=492, and git status stayed clean. After compile, playback-contract-status returned state=exact, approvalGrade=true, timelineHash=171378fe2bfe3a7c, and manifestBaseTimelineHash=171378fe2bfe3a7c. Native Viewer showed Exact preview / preview-editor-1775121573933.mp4 and Timeline preview D4887.MP4 with a visible interview frame. Screenshot was 3.5M; viewer_person_actual mean_rgb=(144.62,141.42,149.8) and near_black_pct=0.0004, while left pillarbox near_black_pct=1.0000 as expected.</x:v>
       </x:c>
-      <x:c r="F234" s="11" t="str">
+      <x:c r="F235" s="11" t="str">
         <x:v>Native AX-1 exact/pixel pass</x:v>
       </x:c>
     </x:row>
-    <x:row r="235" ht="48" customHeight="1">
-      <x:c r="A235" s="12" t="str">
+    <x:row r="236" ht="48" customHeight="1">
+      <x:c r="A236" s="12" t="str">
         <x:v>TL-231</x:v>
       </x:c>
-      <x:c r="B235" s="27" t="str">
+      <x:c r="B236" s="27" t="str">
         <x:v>US-050</x:v>
       </x:c>
-      <x:c r="C235" s="27" t="str">
+      <x:c r="C236" s="27" t="str">
         <x:v>Native Action Queue approval gate</x:v>
       </x:c>
-      <x:c r="D235" s="27" t="str">
+      <x:c r="D236" s="27" t="str">
         <x:v>Add ProjectPanel.ActionQueue* identifiers, relaunch VideoOSStudio, select AX-1 Project tab, inspect the Action Queue AX tree, click ProjectPanel.ActionQueueRunButton.rough-cut-review, and stop at the Codex approval gate without approving writes.</x:v>
       </x:c>
-      <x:c r="E235" s="27" t="str">
+      <x:c r="E236" s="27" t="str">
         <x:v>AX exposed ProjectPanel.ActionQueueRunButton.rough-cut-review, ProjectPanel.ActionQueueCopyButton.rough-cut-review, ProjectPanel.ActionQueueRunButton.marlin-default, and ProjectPanel.ActionQueueCopyButton.marlin-default. Clicking rough-cut-review changed the row to disabled Starting Codex session for Review..., then to Opening Codex approval gate for Review. ps showed a Codex app-server child under VideoOSStudio; git status listed only the intentional ProjectInspectorViews.swift edit, and projects/ax1-participant-voices-20260401/06_review still contained only human_notes.yaml.</x:v>
       </x:c>
-      <x:c r="F235" s="13" t="str">
+      <x:c r="F236" s="13" t="str">
         <x:v>Native approval-gate pass; write not approved</x:v>
       </x:c>
     </x:row>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R65d63d4c3df04629"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R425176be7927432e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R3b17f665144e4f6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R690e448556fa47ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R6f78ac45a62349aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rdddff3b394224f6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R6cdec73aedc7496f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R350da2fa3e7748a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R6fb6003f1a3e4ad5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Rca10793ca8b64489"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build changes ProjectMarlinRuntimeStatusReader so optional Marlin dependency imports run in isolated child Python processes, avoiding the av+torchcodec duplicate AVFoundation warning while preserving the same module readiness contract. The previous build replaced the inspector SwiftUI TabView with explicit InspectorTab.Agent/Project/Clip/Media/QA buttons for US-065, preserving the same Agent/Project/Clip/Media/QA panels while avoiding the segmented-control AXPress hang. The build also includes ProjectPanel.ActionQueueStatus / ActionQueueCommand.&lt;id&gt; / ActionQueueRunButton.&lt;id&gt; / ActionQueueCopyButton.&lt;id&gt; for US-050, ProjectInitializer.ProjectIDField/CreateButton/CancelButton for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix. Latest native build verified VideoOSStudio from the repo root.</x:v>
+        <x:v>Latest code build changes the Marlin evaluation path so runMarlinAnalysis writes per-asset checkpoints, scripts/marlin-evaluate.ts supports --max-sources and --skip-existing, and ProjectMarlinEvaluationRunPlan/Runner plus marlin-eval-plan/eval-next/eval-run pass those chunk controls through the macOS CLI/app path. swift build --target VideoOSStudioCLI passed. Prior native builds include ProjectMarlinRuntimeStatusReader isolated dependency probes, InspectorTab.Agent/Project/Clip/Media/QA buttons for US-065, ProjectPanel.ActionQueueStatus / ActionQueueCommand.&lt;id&gt; / ActionQueueRunButton.&lt;id&gt; / ActionQueueCopyButton.&lt;id&gt; for US-050, ProjectInitializer.ProjectIDField/CreateButton/CancelButton for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-047 retest verified current Command Palette repeatability on VideoOSStudio PID 25505 after ./script/build_and_run.sh --verify: top-bar open exposed CommandPalettePanel/SearchField/CloseButton and stable CommandPaletteItem.* IDs, AXValue search footage filtered to CommandPaletteItem.search-footage, Return opened FootageSearch.Title, super+k opened the palette, and Escape dismissed it. This closes the stale ISS-027 mitigation because the current Computer Use path now proves top-bar, search, Return execution, Cmd-K, and Esc. Prior US-061 loop reproduced the duplicate AVFoundation warning with av+torchcodec in one Python process, confirmed av-only, torchcodec-only, and worker torch/transformers imports are clean, then verified the isolated child-process probe: marlin-runtime-status reports live runtime ready, resolvedDevice=mps, all required modules ready, and no stderr warning. ProjectMarlinRuntimeStatusTests executed 5 tests with 0 failures; swift build --target VideoOSStudio and git diff --check passed. The same pass audited US-046 through US-066 and closed the stale broad QA gap ISS-026 because all native macOS stories now have native pass statuses or explicit approval/preference gates.</x:v>
+        <x:v>Latest US-061 pass verified resumable Marlin chunking: marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and the chunk options in the generated command; a /tmp lively-alt-vol5 mock chunk smoke ran two max-sources=1 passes, second with skip-existing, and accumulated 2 marlin_events items; all-existing skip-existing now returns sourceCount=0. Verification passed: npx vitest run tests/marlin-incremental-merge.test.ts tests/marlin-analysis-stage.test.ts 11/0, npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, and swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0. Prior US-047 retest verified current Command Palette repeatability on VideoOSStudio PID 25505 after ./script/build_and_run.sh --verify and closed ISS-027.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest runtime/native check is the US-047 Command Palette computer-use pass on VideoOSStudio PID 25505: CommandPaletteButton opened CommandPalettePanel, search footage filtered to CommandPaletteItem.search-footage, Return opened the Footage Search sheet for ax1-participant-voices-20260401, closing it left FeedbackStatus Footage search opened, super+k opened the palette again, and Escape returned to VideoOSStudioMainWindow. Prior native checks include the US-061 marlin-runtime-status pass, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest runtime/macOS CLI check is the US-061 Marlin resumable plan: .build/debug/videoos-studio-cli marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing returned ready/canRun=true/sourceCount=9, maxSources=1, skipExisting=true, and a command carrying --max-sources 1 --skip-existing before source URLs. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live single-source completion, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility, Copy behavior, stable action-scoped AX identifiers, and rough-cut-review Start &amp; Run stopping at the Codex approval gate; approved workspace-write review execution, Final render Open, and Marlin default Open remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-065 is promoted for native SQLite/RAG Search/Add, cited Agent prompt insertion, and InspectorTab.* Agent/Media switching without AX hangs. US-061 is promoted for runtime/model/mock/native AX and a live non-mock single-source Marlin completion on a representative-source fixture; the full multi-source live batch and repo-level Marlin-first preference promotion remain pending evidence gates. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility, Copy behavior, stable action-scoped AX identifiers, and rough-cut-review Start &amp; Run stopping at the Codex approval gate; approved workspace-write review execution, Final render Open, and Marlin default Open remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-065 is promoted for native SQLite/RAG Search/Add, cited Agent prompt insertion, and InspectorTab.* Agent/Media switching without AX hangs. US-061 is promoted for runtime/model/mock/native AX, live non-mock single-source Marlin completion on a representative-source fixture, and resumable checkpointed chunk controls; the full multi-source live representative batch and repo-level Marlin-first preference promotion remain pending evidence gates. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2146,19 +2146,19 @@
         <x:v>As a native Studio operator, I can inspect Marlin runtime/model access/coverage/queue, run project Marlin evaluation, and apply Marlin preference when evidence gates pass.</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>MediaPanel renders MarlinEvaluationStatus, runtime/model access, representative buckets, queue items, run plan, evaluation button, and Apply Marlin Preference button. Evaluation can run only when sources exist and runtime/model checks pass; mock artifacts are workflow QA only and must not count as Marlin preference evidence. The Marlin status, queue, representative buckets, run/apply buttons, command line, and artifact path now expose stable MediaPanel.Marlin* accessibility identifiers for native automation.</x:v>
+        <x:v>MediaPanel renders MarlinEvaluationStatus, runtime/model access, representative buckets, queue items, run plan, evaluation button, and Apply Marlin Preference button. Evaluation can run only when sources exist and runtime/model checks pass; mock artifacts are workflow QA only and must not count as Marlin preference evidence. The Marlin status, queue, representative buckets, run/apply buttons, command line, artifact path, and resumable chunk options now expose stable MediaPanel.Marlin*/CLI contracts for native automation.</x:v>
       </x:c>
       <x:c r="E62" s="26" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:48-160; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1296-1325,2326-2481; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRuntimeStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinModelAccessStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationQueue.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRepresentativePlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationRunPlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinPreferenceDecision.swift</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:48-160; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1296-1325,2326-2481; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRuntimeStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinModelAccessStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationQueue.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRepresentativePlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationRunPlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinPreferenceDecision.swift; runtime/pipeline/stages/marlin.ts; scripts/marlin-evaluate.ts</x:v>
       </x:c>
       <x:c r="F62" s="26" t="str">
-        <x:v>Run Marlin runtime/model/preference/queue/representative-plan/eval-plan/eval-run/status CLI checks, execute a tiny mock evaluation fixture, verify index refresh, verify Preference apply is blocked when gates fail, run Marlin focused Swift tests, confirm stable Marlin accessibility identifiers, run at least one live non-mock representative-source completion, and leave full batch/preference promotion blocked until representative coverage and aggregate coverage gates pass.</x:v>
+        <x:v>Run Marlin runtime/model/preference/queue/representative-plan/eval-plan/eval-run/status CLI checks, execute a tiny mock evaluation fixture, verify index refresh, verify Preference apply is blocked when gates fail, run Marlin focused Swift tests, confirm stable Marlin accessibility identifiers, run at least one live non-mock representative-source completion, verify resumable chunk/checkpoint behavior, and leave full batch/preference promotion blocked until representative coverage and aggregate coverage gates pass.</x:v>
       </x:c>
       <x:c r="G62" s="26" t="str">
-        <x:v>Runtime/model/mock/native AX/live single-source pass; full batch preference gate pending</x:v>
+        <x:v>Runtime/model/mock/native AX/live single-source/resumable chunk pass; full batch preference gate pending</x:v>
       </x:c>
       <x:c r="H62" s="11" t="str">
-        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. The runtime probe now imports dependency modules in isolated child processes, so the live marlin-runtime-status check no longer emits duplicate AVFoundation class warnings while still reporting every module ready. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path now supports --request-timeout-ms / --timeout-ms, dry-run shows 900000ms in the generated command, and focused TS/Swift tests pass. Latest pass added MediaPanel.Marlin* identifiers and then ran a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4, with VOS_MARLIN_PROXY_MAX_WIDTH=384 and requestTimeoutMs=900000. marlin-evaluate completed with Mock=false, wrote marlin_events.json with inference_mode=live, model NemoStation/Marlin-2B, 1 asset, 3 events, and 4 find results; marlin-status reported candidate for preferred VLM, coverage=1.00, canPreferMarlin=true for the tmp fixture; segments.json gained marlin_temporal_semantics peak provenance and 3 interest points; index-rebuild produced 9 search documents. Full all-source representative run and repo-level preference promotion remain pending because the real repo gate still needs broader live coverage.</x:v>
+        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. The runtime probe now imports dependency modules in isolated child processes, so the live marlin-runtime-status check no longer emits duplicate AVFoundation class warnings while still reporting every module ready. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path supports --request-timeout-ms / --timeout-ms, and a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4 completed with requestTimeoutMs=900000, wrote inference_mode=live Marlin events, updated segments with marlin_temporal_semantics, and rebuilt an index with 9 search documents. Current pass adds per-asset checkpoint writes in runMarlinAnalysis plus --max-sources and --skip-existing through marlin-evaluate, ProjectMarlinEvaluationRunPlan/Runner, marlin-eval-plan, marlin-eval-next, and marlin-eval-run. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and a command carrying those options before source URLs. A /tmp mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. All-existing skip-existing runs now return sourceCount=0 instead of a false failure. Focused verification passed: npx vitest run tests/marlin-incremental-merge.test.ts tests/marlin-analysis-stage.test.ts 11/0, npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, and swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0. Full all-source representative live run and repo-level preference promotion remain pending because the real repo gate still needs broader live coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="48" customHeight="1">
@@ -3778,16 +3778,16 @@
         <x:v>Live representative Marlin evaluation loaded the model but timed out before the first caption result and left no marlin_events.json artifact.</x:v>
       </x:c>
       <x:c r="F51" s="26" t="str">
-        <x:v>The local worker request timeout was fixed at the connector default of 300000ms unless VOS_MARLIN_REQUEST_TIMEOUT_MS was set manually; the native CLI plan/run path did not expose a per-run timeout for slow Apple Silicon live caption passes.</x:v>
+        <x:v>The local worker request timeout was fixed at the connector default of 300000ms unless VOS_MARLIN_REQUEST_TIMEOUT_MS was set manually; the native CLI plan/run path did not expose a per-run timeout for slow Apple Silicon live caption passes; and completed assets were only written after the whole asset loop finished, so a later source timeout could discard earlier completed captions.</x:v>
       </x:c>
       <x:c r="G51" s="26" t="str">
-        <x:v>Added --request-timeout-ms and --timeout-ms to scripts/marlin-evaluate.ts, threaded requestTimeoutMs through ProjectMarlinEvaluationRunPlan and ProjectMarlinEvaluationRunner, surfaced it in marlin-eval-plan/marlin-eval-next/marlin-eval-run, and added a dry-run hint for slow MPS live runs.</x:v>
+        <x:v>Added --request-timeout-ms and --timeout-ms to scripts/marlin-evaluate.ts, threaded requestTimeoutMs through ProjectMarlinEvaluationRunPlan and ProjectMarlinEvaluationRunner, surfaced it in marlin-eval-plan/marlin-eval-next/marlin-eval-run, added per-asset marlin_events checkpoint writes, and exposed --max-sources plus --skip-existing so representative coverage can be accumulated across bounded local runs.</x:v>
       </x:c>
       <x:c r="H51" s="26" t="str">
-        <x:v>npx vitest run tests/marlin-analysis-stage.test.ts passed 7 tests; swift test --filter ProjectMarlinEvaluationRunPlanTests passed 9 tests; marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 printed the timeout-bearing command; missing timeout value is rejected; marlin-eval-next dry-run prints requestTimeoutMs=900000. A live non-mock single-source run against a /tmp lively-alt-vol5-derived fixture completed with requestTimeoutMs=900000 and VOS_MARLIN_PROXY_MAX_WIDTH=384, wrote marlin_events.json, updated segments with marlin_temporal_semantics, and rebuilt an index with 9 search documents. The full 9-source representative batch remains intentionally pending.</x:v>
+        <x:v>npx vitest run tests/marlin-incremental-merge.test.ts tests/marlin-analysis-stage.test.ts passed 11 tests, including checkpoint-before-later-timeout and all-existing skip-existing no-op coverage; npx tsc --noEmit --pretty false and node --check scripts/marlin-evaluate.ts passed; swift build --target VideoOSStudioCLI passed; swift test --filter ProjectMarlinEvaluationRunPlanTests passed 11 tests. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and the chunk options in the generated command. A /tmp lively-alt-vol5 mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. A prior live non-mock single-source run against a /tmp lively-alt-vol5-derived fixture completed with requestTimeoutMs=900000 and wrote live Marlin events. The full 9-source representative live batch remains intentionally pending.</x:v>
       </x:c>
       <x:c r="I51" s="11" t="str">
-        <x:v>Mitigated; live single-source pass; full batch pending</x:v>
+        <x:v>Mitigated; resumable chunks; full batch pending</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="48" customHeight="1">
@@ -8569,79 +8569,79 @@
     </x:row>
     <x:row r="210" ht="48" customHeight="1">
       <x:c r="A210" s="10" t="str">
-        <x:v>TL-205</x:v>
+        <x:v>TL-236</x:v>
       </x:c>
       <x:c r="B210" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C210" s="26" t="str">
-        <x:v>Native preview duration fallback</x:v>
+        <x:v>Resumable Marlin chunk evaluation</x:v>
       </x:c>
       <x:c r="D210" s="26" t="str">
-        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
+        <x:v>Add per-asset Marlin artifact checkpoints and --max-sources/--skip-existing controls, dry-run lively-alt-vol5, run a tmp mock chunk smoke, and rerun focused TS/Swift checks.</x:v>
       </x:c>
       <x:c r="E210" s="26" t="str">
-        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
+        <x:v>runMarlinAnalysis now writes marlin_events.json after each completed asset and merges with existing artifacts, so completed assets survive a later source timeout. scripts/marlin-evaluate.ts supports --max-sources and --skip-existing; all-existing skip-existing runs complete with sourceCount=0. ProjectMarlinEvaluationRunPlan and ProjectMarlinEvaluationRunner pass those options through CLI/app paths. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1 and skipExisting=true. A /tmp lively-alt-vol5 mock chunk smoke ran two max-sources=1 passes, second with skip-existing, and accumulated 2 artifact items. Verification passed: npx vitest run tests/marlin-incremental-merge.test.ts tests/marlin-analysis-stage.test.ts 11/0, npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, and swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0.</x:v>
       </x:c>
       <x:c r="F210" s="11" t="str">
-        <x:v>Native pixel/runtime pass</x:v>
+        <x:v>Resumable chunk pass; full representative batch pending</x:v>
       </x:c>
     </x:row>
     <x:row r="211" ht="48" customHeight="1">
       <x:c r="A211" s="10" t="str">
-        <x:v>TL-206</x:v>
+        <x:v>TL-205</x:v>
       </x:c>
       <x:c r="B211" s="26" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C211" s="26" t="str">
-        <x:v>Native Clip Inspector save and clear</x:v>
+        <x:v>Native preview duration fallback</x:v>
       </x:c>
       <x:c r="D211" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
+        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
       </x:c>
       <x:c r="E211" s="26" t="str">
-        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
+        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F211" s="11" t="str">
-        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
+        <x:v>Native pixel/runtime pass</x:v>
       </x:c>
     </x:row>
     <x:row r="212" ht="48" customHeight="1">
       <x:c r="A212" s="10" t="str">
-        <x:v>TL-207</x:v>
+        <x:v>TL-206</x:v>
       </x:c>
       <x:c r="B212" s="26" t="str">
-        <x:v>US-058</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C212" s="26" t="str">
-        <x:v>Native QA Dashboard issue jump</x:v>
+        <x:v>Native Clip Inspector save and clear</x:v>
       </x:c>
       <x:c r="D212" s="26" t="str">
-        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
+        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
       </x:c>
       <x:c r="E212" s="26" t="str">
-        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
+        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
       </x:c>
       <x:c r="F212" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
       </x:c>
     </x:row>
     <x:row r="213" ht="48" customHeight="1">
       <x:c r="A213" s="10" t="str">
-        <x:v>TL-208</x:v>
+        <x:v>TL-207</x:v>
       </x:c>
       <x:c r="B213" s="26" t="str">
-        <x:v>US-056</x:v>
+        <x:v>US-058</x:v>
       </x:c>
       <x:c r="C213" s="26" t="str">
-        <x:v>Native Candidate Swap sheet and staging</x:v>
+        <x:v>Native QA Dashboard issue jump</x:v>
       </x:c>
       <x:c r="D213" s="26" t="str">
-        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
+        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
       </x:c>
       <x:c r="E213" s="26" t="str">
-        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
+        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
       </x:c>
       <x:c r="F213" s="11" t="str">
         <x:v>Native AX/pixel pass</x:v>
@@ -8649,339 +8649,339 @@
     </x:row>
     <x:row r="214" ht="48" customHeight="1">
       <x:c r="A214" s="10" t="str">
-        <x:v>TL-209</x:v>
+        <x:v>TL-208</x:v>
       </x:c>
       <x:c r="B214" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-056</x:v>
       </x:c>
       <x:c r="C214" s="26" t="str">
-        <x:v>Native exact preview regeneration</x:v>
+        <x:v>Native Candidate Swap sheet and staging</x:v>
       </x:c>
       <x:c r="D214" s="26" t="str">
-        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
+        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
       </x:c>
       <x:c r="E214" s="26" t="str">
-        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
       </x:c>
       <x:c r="F214" s="11" t="str">
-        <x:v>Native exact preview pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="48" customHeight="1">
       <x:c r="A215" s="10" t="str">
-        <x:v>TL-210</x:v>
+        <x:v>TL-209</x:v>
       </x:c>
       <x:c r="B215" s="26" t="str">
-        <x:v>US-047</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C215" s="26" t="str">
-        <x:v>Native Command Palette top-bar open/close</x:v>
+        <x:v>Native exact preview regeneration</x:v>
       </x:c>
       <x:c r="D215" s="26" t="str">
-        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
+        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
       </x:c>
       <x:c r="E215" s="26" t="str">
-        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
+        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F215" s="11" t="str">
-        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
+        <x:v>Native exact preview pass</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="48" customHeight="1">
       <x:c r="A216" s="10" t="str">
-        <x:v>TL-211</x:v>
+        <x:v>TL-210</x:v>
       </x:c>
       <x:c r="B216" s="26" t="str">
         <x:v>US-047</x:v>
       </x:c>
       <x:c r="C216" s="26" t="str">
-        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
+        <x:v>Native Command Palette top-bar open/close</x:v>
       </x:c>
       <x:c r="D216" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
+        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
       </x:c>
       <x:c r="E216" s="26" t="str">
-        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
+        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
       </x:c>
       <x:c r="F216" s="11" t="str">
-        <x:v>Native keyboard/AX pass</x:v>
+        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="48" customHeight="1">
       <x:c r="A217" s="10" t="str">
-        <x:v>TL-212</x:v>
+        <x:v>TL-211</x:v>
       </x:c>
       <x:c r="B217" s="26" t="str">
-        <x:v>US-048</x:v>
+        <x:v>US-047</x:v>
       </x:c>
       <x:c r="C217" s="26" t="str">
-        <x:v>Native Agent panel session lifecycle</x:v>
+        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
       </x:c>
       <x:c r="D217" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
+        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
       </x:c>
       <x:c r="E217" s="26" t="str">
-        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
+        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
       </x:c>
       <x:c r="F217" s="11" t="str">
-        <x:v>Native AX/computer-use pass</x:v>
+        <x:v>Native keyboard/AX pass</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="48" customHeight="1">
       <x:c r="A218" s="10" t="str">
-        <x:v>TL-213</x:v>
+        <x:v>TL-212</x:v>
       </x:c>
       <x:c r="B218" s="26" t="str">
-        <x:v>US-049</x:v>
+        <x:v>US-048</x:v>
       </x:c>
       <x:c r="C218" s="26" t="str">
-        <x:v>Native Status agent job read-only turn</x:v>
+        <x:v>Native Agent panel session lifecycle</x:v>
       </x:c>
       <x:c r="D218" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
       </x:c>
       <x:c r="E218" s="26" t="str">
-        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
+        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F218" s="11" t="str">
-        <x:v>Native read-only job pass; approved write pending</x:v>
+        <x:v>Native AX/computer-use pass</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="48" customHeight="1">
       <x:c r="A219" s="10" t="str">
-        <x:v>TL-214</x:v>
+        <x:v>TL-213</x:v>
       </x:c>
       <x:c r="B219" s="26" t="str">
-        <x:v>US-050</x:v>
+        <x:v>US-049</x:v>
       </x:c>
       <x:c r="C219" s="26" t="str">
-        <x:v>Native Project readiness/action queue Copy pass</x:v>
+        <x:v>Native Status agent job read-only turn</x:v>
       </x:c>
       <x:c r="D219" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
       </x:c>
       <x:c r="E219" s="26" t="str">
-        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
+        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F219" s="11" t="str">
-        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
+        <x:v>Native read-only job pass; approved write pending</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="48" customHeight="1">
       <x:c r="A220" s="10" t="str">
-        <x:v>TL-215</x:v>
+        <x:v>TL-214</x:v>
       </x:c>
       <x:c r="B220" s="26" t="str">
-        <x:v>US-051</x:v>
+        <x:v>US-050</x:v>
       </x:c>
       <x:c r="C220" s="26" t="str">
-        <x:v>Native local Source Analysis button</x:v>
+        <x:v>Native Project readiness/action queue Copy pass</x:v>
       </x:c>
       <x:c r="D220" s="26" t="str">
-        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
       </x:c>
       <x:c r="E220" s="26" t="str">
-        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
+        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
       </x:c>
       <x:c r="F220" s="11" t="str">
-        <x:v>Native local analysis pass</x:v>
+        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="48" customHeight="1">
       <x:c r="A221" s="10" t="str">
-        <x:v>TL-216</x:v>
+        <x:v>TL-215</x:v>
       </x:c>
       <x:c r="B221" s="26" t="str">
-        <x:v>US-052</x:v>
+        <x:v>US-051</x:v>
       </x:c>
       <x:c r="C221" s="26" t="str">
-        <x:v>Native Rough Cut and Review Patch buttons</x:v>
+        <x:v>Native local Source Analysis button</x:v>
       </x:c>
       <x:c r="D221" s="26" t="str">
-        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
+        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E221" s="26" t="str">
-        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
       </x:c>
       <x:c r="F221" s="11" t="str">
-        <x:v>Native compile/review patch pass</x:v>
+        <x:v>Native local analysis pass</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="48" customHeight="1">
       <x:c r="A222" s="10" t="str">
-        <x:v>TL-217</x:v>
+        <x:v>TL-216</x:v>
       </x:c>
       <x:c r="B222" s="26" t="str">
-        <x:v>US-053</x:v>
+        <x:v>US-052</x:v>
       </x:c>
       <x:c r="C222" s="26" t="str">
-        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
+        <x:v>Native Rough Cut and Review Patch buttons</x:v>
       </x:c>
       <x:c r="D222" s="26" t="str">
-        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
+        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E222" s="26" t="str">
-        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
+        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F222" s="11" t="str">
-        <x:v>Native timeline/context menu pass</x:v>
+        <x:v>Native compile/review patch pass</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="48" customHeight="1">
       <x:c r="A223" s="10" t="str">
-        <x:v>TL-218</x:v>
+        <x:v>TL-217</x:v>
       </x:c>
       <x:c r="B223" s="26" t="str">
-        <x:v>US-054</x:v>
+        <x:v>US-053</x:v>
       </x:c>
       <x:c r="C223" s="26" t="str">
-        <x:v>Native Studio feedback Apply and Undo</x:v>
+        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
       </x:c>
       <x:c r="D223" s="26" t="str">
-        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
+        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
       </x:c>
       <x:c r="E223" s="26" t="str">
-        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
       </x:c>
       <x:c r="F223" s="11" t="str">
-        <x:v>Native apply/undo pass</x:v>
+        <x:v>Native timeline/context menu pass</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="48" customHeight="1">
       <x:c r="A224" s="10" t="str">
-        <x:v>TL-219</x:v>
+        <x:v>TL-218</x:v>
       </x:c>
       <x:c r="B224" s="26" t="str">
-        <x:v>US-057</x:v>
+        <x:v>US-054</x:v>
       </x:c>
       <x:c r="C224" s="26" t="str">
-        <x:v>Native Footage Search sheet and replacement staging</x:v>
+        <x:v>Native Studio feedback Apply and Undo</x:v>
       </x:c>
       <x:c r="D224" s="26" t="str">
-        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
+        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E224" s="26" t="str">
-        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
+        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F224" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native apply/undo pass</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="48" customHeight="1">
       <x:c r="A225" s="10" t="str">
-        <x:v>TL-220</x:v>
+        <x:v>TL-219</x:v>
       </x:c>
       <x:c r="B225" s="26" t="str">
-        <x:v>US-066</x:v>
+        <x:v>US-057</x:v>
       </x:c>
       <x:c r="C225" s="26" t="str">
-        <x:v>Native Settings transport picker mutation</x:v>
+        <x:v>Native Footage Search sheet and replacement staging</x:v>
       </x:c>
       <x:c r="D225" s="26" t="str">
-        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
+        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
       </x:c>
       <x:c r="E225" s="26" t="str">
-        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
       </x:c>
       <x:c r="F225" s="11" t="str">
-        <x:v>Native Settings picker mutation pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="48" customHeight="1">
       <x:c r="A226" s="10" t="str">
-        <x:v>TL-221</x:v>
+        <x:v>TL-220</x:v>
       </x:c>
       <x:c r="B226" s="26" t="str">
-        <x:v>US-059</x:v>
+        <x:v>US-066</x:v>
       </x:c>
       <x:c r="C226" s="26" t="str">
-        <x:v>Native Media Relink buttons and source-map relink</x:v>
+        <x:v>Native Settings transport picker mutation</x:v>
       </x:c>
       <x:c r="D226" s="26" t="str">
-        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
+        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
       </x:c>
       <x:c r="E226" s="26" t="str">
-        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
+        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F226" s="11" t="str">
-        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
+        <x:v>Native Settings picker mutation pass</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="48" customHeight="1">
       <x:c r="A227" s="10" t="str">
-        <x:v>TL-222</x:v>
+        <x:v>TL-221</x:v>
       </x:c>
       <x:c r="B227" s="26" t="str">
-        <x:v>US-060</x:v>
+        <x:v>US-059</x:v>
       </x:c>
       <x:c r="C227" s="26" t="str">
-        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
+        <x:v>Native Media Relink buttons and source-map relink</x:v>
       </x:c>
       <x:c r="D227" s="26" t="str">
-        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
+        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
       </x:c>
       <x:c r="E227" s="26" t="str">
-        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
+        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
       </x:c>
       <x:c r="F227" s="11" t="str">
-        <x:v>Native synthetic/proxy/smoke button pass</x:v>
+        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="48" customHeight="1">
       <x:c r="A228" s="10" t="str">
-        <x:v>TL-223</x:v>
+        <x:v>TL-222</x:v>
       </x:c>
       <x:c r="B228" s="26" t="str">
-        <x:v>US-046</x:v>
+        <x:v>US-060</x:v>
       </x:c>
       <x:c r="C228" s="26" t="str">
-        <x:v>Native New Project from Source</x:v>
+        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
       </x:c>
       <x:c r="D228" s="26" t="str">
-        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
+        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
       </x:c>
       <x:c r="E228" s="26" t="str">
-        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
+        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
       </x:c>
       <x:c r="F228" s="11" t="str">
-        <x:v>Native project creation/NSOpenPanel pass</x:v>
+        <x:v>Native synthetic/proxy/smoke button pass</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="48" customHeight="1">
       <x:c r="A229" s="10" t="str">
-        <x:v>TL-224</x:v>
+        <x:v>TL-223</x:v>
       </x:c>
       <x:c r="B229" s="26" t="str">
-        <x:v>US-062</x:v>
+        <x:v>US-046</x:v>
       </x:c>
       <x:c r="C229" s="26" t="str">
-        <x:v>Native MediaPanel Audio Story Graph button</x:v>
+        <x:v>Native New Project from Source</x:v>
       </x:c>
       <x:c r="D229" s="26" t="str">
-        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
+        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
       </x:c>
       <x:c r="E229" s="26" t="str">
-        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
       </x:c>
       <x:c r="F229" s="11" t="str">
-        <x:v>Native AX/UI/CLI pass</x:v>
+        <x:v>Native project creation/NSOpenPanel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="48" customHeight="1">
       <x:c r="A230" s="10" t="str">
-        <x:v>TL-225</x:v>
+        <x:v>TL-224</x:v>
       </x:c>
       <x:c r="B230" s="26" t="str">
-        <x:v>US-063</x:v>
+        <x:v>US-062</x:v>
       </x:c>
       <x:c r="C230" s="26" t="str">
-        <x:v>Native Render Final Package button</x:v>
+        <x:v>Native MediaPanel Audio Story Graph button</x:v>
       </x:c>
       <x:c r="D230" s="26" t="str">
-        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
+        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E230" s="26" t="str">
-        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F230" s="11" t="str">
         <x:v>Native AX/UI/CLI pass</x:v>
@@ -8989,121 +8989,141 @@
     </x:row>
     <x:row r="231" ht="48" customHeight="1">
       <x:c r="A231" s="10" t="str">
-        <x:v>TL-226</x:v>
+        <x:v>TL-225</x:v>
       </x:c>
       <x:c r="B231" s="26" t="str">
-        <x:v>US-064</x:v>
+        <x:v>US-063</x:v>
       </x:c>
       <x:c r="C231" s="26" t="str">
-        <x:v>Native Editor Handoff export and Finder reveal</x:v>
+        <x:v>Native Render Final Package button</x:v>
       </x:c>
       <x:c r="D231" s="26" t="str">
-        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
+        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
       </x:c>
       <x:c r="E231" s="26" t="str">
-        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
+        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F231" s="11" t="str">
-        <x:v>Native AX/UI/Finder/CLI pass</x:v>
+        <x:v>Native AX/UI/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="48" customHeight="1">
       <x:c r="A232" s="10" t="str">
-        <x:v>TL-227</x:v>
+        <x:v>TL-226</x:v>
       </x:c>
       <x:c r="B232" s="26" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-064</x:v>
       </x:c>
       <x:c r="C232" s="26" t="str">
-        <x:v>Native Ask Codex editor-note proposal</x:v>
+        <x:v>Native Editor Handoff export and Finder reveal</x:v>
       </x:c>
       <x:c r="D232" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
+        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E232" s="26" t="str">
-        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
+        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
       </x:c>
       <x:c r="F232" s="11" t="str">
-        <x:v>Native read-only Codex proposal pass</x:v>
+        <x:v>Native AX/UI/Finder/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="48" customHeight="1">
       <x:c r="A233" s="10" t="str">
-        <x:v>TL-228</x:v>
+        <x:v>TL-227</x:v>
       </x:c>
       <x:c r="B233" s="26" t="str">
-        <x:v>US-061</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C233" s="26" t="str">
-        <x:v>Live Marlin single-source completion</x:v>
+        <x:v>Native Ask Codex editor-note proposal</x:v>
       </x:c>
       <x:c r="D233" s="26" t="str">
-        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
+        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
       </x:c>
       <x:c r="E233" s="26" t="str">
-        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
+        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
       </x:c>
       <x:c r="F233" s="11" t="str">
-        <x:v>Live single-source pass; full representative batch pending</x:v>
+        <x:v>Native read-only Codex proposal pass</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="48" customHeight="1">
       <x:c r="A234" s="10" t="str">
-        <x:v>TL-229</x:v>
+        <x:v>TL-228</x:v>
       </x:c>
       <x:c r="B234" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C234" s="26" t="str">
-        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+        <x:v>Live Marlin single-source completion</x:v>
       </x:c>
       <x:c r="D234" s="26" t="str">
-        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
       </x:c>
       <x:c r="E234" s="26" t="str">
-        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
       </x:c>
       <x:c r="F234" s="11" t="str">
-        <x:v>Native fresh-launch pixel pass</x:v>
+        <x:v>Live single-source pass; full representative batch pending</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="48" customHeight="1">
       <x:c r="A235" s="10" t="str">
-        <x:v>TL-230</x:v>
+        <x:v>TL-229</x:v>
       </x:c>
       <x:c r="B235" s="26" t="str">
         <x:v>US-045</x:v>
       </x:c>
       <x:c r="C235" s="26" t="str">
+        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+      </x:c>
+      <x:c r="D235" s="26" t="str">
+        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+      </x:c>
+      <x:c r="E235" s="26" t="str">
+        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+      </x:c>
+      <x:c r="F235" s="11" t="str">
+        <x:v>Native fresh-launch pixel pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="48" customHeight="1">
+      <x:c r="A236" s="10" t="str">
+        <x:v>TL-230</x:v>
+      </x:c>
+      <x:c r="B236" s="26" t="str">
+        <x:v>US-045</x:v>
+      </x:c>
+      <x:c r="C236" s="26" t="str">
         <x:v>AX-1 exact preview promotion and pixel pass</x:v>
       </x:c>
-      <x:c r="D235" s="26" t="str">
+      <x:c r="D236" s="26" t="str">
         <x:v>Run videoos-studio-cli compile-run on projects/ax1-participant-voices-20260401, confirm playback-contract-status, select ProjectShelf.ax1-participant-voices-20260401 in VideoOSStudio, capture /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and run Retina-coordinate pixel statistics on the Viewer region.</x:v>
       </x:c>
-      <x:c r="E235" s="26" t="str">
+      <x:c r="E236" s="26" t="str">
         <x:v>Before compile, playback-contract-status returned legacy_manifest and approvalGrade=false. compile-run completed with exitCode=0, timeline compiled, indexDocuments=492, and git status stayed clean. After compile, playback-contract-status returned state=exact, approvalGrade=true, timelineHash=171378fe2bfe3a7c, and manifestBaseTimelineHash=171378fe2bfe3a7c. Native Viewer showed Exact preview / preview-editor-1775121573933.mp4 and Timeline preview D4887.MP4 with a visible interview frame. Screenshot was 3.5M; viewer_person_actual mean_rgb=(144.62,141.42,149.8) and near_black_pct=0.0004, while left pillarbox near_black_pct=1.0000 as expected.</x:v>
       </x:c>
-      <x:c r="F235" s="11" t="str">
+      <x:c r="F236" s="11" t="str">
         <x:v>Native AX-1 exact/pixel pass</x:v>
       </x:c>
     </x:row>
-    <x:row r="236" ht="48" customHeight="1">
-      <x:c r="A236" s="12" t="str">
+    <x:row r="237" ht="48" customHeight="1">
+      <x:c r="A237" s="12" t="str">
         <x:v>TL-231</x:v>
       </x:c>
-      <x:c r="B236" s="27" t="str">
+      <x:c r="B237" s="27" t="str">
         <x:v>US-050</x:v>
       </x:c>
-      <x:c r="C236" s="27" t="str">
+      <x:c r="C237" s="27" t="str">
         <x:v>Native Action Queue approval gate</x:v>
       </x:c>
-      <x:c r="D236" s="27" t="str">
+      <x:c r="D237" s="27" t="str">
         <x:v>Add ProjectPanel.ActionQueue* identifiers, relaunch VideoOSStudio, select AX-1 Project tab, inspect the Action Queue AX tree, click ProjectPanel.ActionQueueRunButton.rough-cut-review, and stop at the Codex approval gate without approving writes.</x:v>
       </x:c>
-      <x:c r="E236" s="27" t="str">
+      <x:c r="E237" s="27" t="str">
         <x:v>AX exposed ProjectPanel.ActionQueueRunButton.rough-cut-review, ProjectPanel.ActionQueueCopyButton.rough-cut-review, ProjectPanel.ActionQueueRunButton.marlin-default, and ProjectPanel.ActionQueueCopyButton.marlin-default. Clicking rough-cut-review changed the row to disabled Starting Codex session for Review..., then to Opening Codex approval gate for Review. ps showed a Codex app-server child under VideoOSStudio; git status listed only the intentional ProjectInspectorViews.swift edit, and projects/ax1-participant-voices-20260401/06_review still contained only human_notes.yaml.</x:v>
       </x:c>
-      <x:c r="F236" s="13" t="str">
+      <x:c r="F237" s="13" t="str">
         <x:v>Native approval-gate pass; write not approved</x:v>
       </x:c>
     </x:row>
@@ -9610,10 +9630,10 @@
         <x:v>macOS Marlin and audio graph</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:21-160; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1296-1325,2326-2604; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRuntimeStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinModelAccessStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationQueue.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRepresentativePlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationRunPlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinPreferenceDecision.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectAudioStoryGraphRunPlan.swift; scripts/build-audio-story-graph.ts; runtime/artifacts/audio-story-project-builder.ts; runtime/artifacts/p2-audio-story-graph.ts; apps/macos-studio/Sources/VideoOSStudioCore/ProjectSQLiteIndex.swift:400-452</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:21-160; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1296-1325,2326-2604; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRuntimeStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinModelAccessStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationQueue.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRepresentativePlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationRunPlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinPreferenceDecision.swift; runtime/pipeline/stages/marlin.ts; scripts/marlin-evaluate.ts; apps/macos-studio/Sources/VideoOSStudioCore/ProjectAudioStoryGraphRunPlan.swift; scripts/build-audio-story-graph.ts; runtime/artifacts/audio-story-project-builder.ts; runtime/artifacts/p2-audio-story-graph.ts; apps/macos-studio/Sources/VideoOSStudioCore/ProjectSQLiteIndex.swift:400-452</x:v>
       </x:c>
       <x:c r="C45" s="11" t="str">
-        <x:v>Marlin runtime dependency checks, Hugging Face gated-model access checks, project evaluation status, representative queue/buckets, run-plan source selection, mock/live evaluation runner with SQLite index refresh, preference gate/apply guard, stable Marlin MediaPanel accessibility identifiers, and audio story graph command readiness/runtime execution. Audio story graph builds transcript utterance, audio event, and BGM music_section nodes, writes 03_analysis/audio_story_graph.json, and indexes audio_story_node search documents after success.</x:v>
+        <x:v>Marlin runtime dependency checks, Hugging Face gated-model access checks, project evaluation status, representative queue/buckets, run-plan source selection, mock/live evaluation runner with SQLite index refresh, resumable per-asset checkpointing, --max-sources/--skip-existing chunk controls, preference gate/apply guard, stable Marlin MediaPanel accessibility identifiers, and audio story graph command readiness/runtime execution. Audio story graph builds transcript utterance, audio event, and BGM music_section nodes, writes 03_analysis/audio_story_graph.json, and indexes audio_story_node search documents after success.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="48" customHeight="1">

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rdddff3b394224f6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R6cdec73aedc7496f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R350da2fa3e7748a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R6fb6003f1a3e4ad5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Rca10793ca8b64489"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R200a2e9ec4cf4239"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R38902b8e973b4fa4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R94ce5680c9f7438a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="Rfa40f7c83daa44f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Rbb93904782b442d1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -479,7 +479,7 @@
         <x:v>Issues tracked</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="220" customHeight="1">
@@ -487,7 +487,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build changes the Marlin evaluation path so runMarlinAnalysis writes per-asset checkpoints, scripts/marlin-evaluate.ts supports --max-sources and --skip-existing, and ProjectMarlinEvaluationRunPlan/Runner plus marlin-eval-plan/eval-next/eval-run pass those chunk controls through the macOS CLI/app path. swift build --target VideoOSStudioCLI passed. Prior native builds include ProjectMarlinRuntimeStatusReader isolated dependency probes, InspectorTab.Agent/Project/Clip/Media/QA buttons for US-065, ProjectPanel.ActionQueueStatus / ActionQueueCommand.&lt;id&gt; / ActionQueueRunButton.&lt;id&gt; / ActionQueueCopyButton.&lt;id&gt; for US-050, ProjectInitializer.ProjectIDField/CreateButton/CancelButton for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix.</x:v>
+        <x:v>Latest code build changes the Marlin evaluation input resolver so loadMarlinAssetInputs uses 02_media/source_map.json before indexed source fallbacks, preserving correct asset IDs when assets.json stores original camera filenames and operators pass linked media paths. The previous build made runMarlinAnalysis write per-asset checkpoints, added --max-sources/--skip-existing to scripts/marlin-evaluate.ts, and threaded those chunk controls through ProjectMarlinEvaluationRunPlan/Runner plus marlin-eval-plan/eval-next/eval-run. Prior native builds include ProjectMarlinRuntimeStatusReader isolated dependency probes, InspectorTab.Agent/Project/Clip/Media/QA buttons for US-065, ProjectPanel.ActionQueueStatus / ActionQueueCommand.&lt;id&gt; / ActionQueueRunButton.&lt;id&gt; / ActionQueueCopyButton.&lt;id&gt; for US-050, ProjectInitializer.ProjectIDField/CreateButton/CancelButton for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-061 pass verified resumable Marlin chunking: marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and the chunk options in the generated command; a /tmp lively-alt-vol5 mock chunk smoke ran two max-sources=1 passes, second with skip-existing, and accumulated 2 marlin_events items; all-existing skip-existing now returns sourceCount=0. Verification passed: npx vitest run tests/marlin-incremental-merge.test.ts tests/marlin-analysis-stage.test.ts 11/0, npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, and swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0. Prior US-047 retest verified current Command Palette repeatability on VideoOSStudio PID 25505 after ./script/build_and_run.sh --verify and closed ISS-027.</x:v>
+        <x:v>Latest US-061 pass verified source-map-aware Marlin chunks on the real lively-alt-vol5 project. npx vitest run tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts passed 12/0, npx tsc --noEmit --pretty false passed, and node --check scripts/marlin-evaluate.ts passed. Live non-mock runs with VOS_MARLIN_PROXY_MAX_WIDTH=384 and --request-timeout-ms 900000 completed for AST_5CAEC24E / 08-jun-a-man-and-a.mp4 and AST_25CDF4A5 / 06-jun-two-people-are.mp4. marlin_events.json has 2 assets, 13 events, and 8 find results; segments.json has Marlin summary/peak provenance for both; index-rebuild reports 2354 searchDocuments; marlin-status reports coverage=0.22 and canPreferMarlin=false; marlin-preference-status remains partially ready with lively-alt-vol5 at 2/9 peak segments. Prior US-047 retest verified current Command Palette repeatability and closed ISS-027.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest runtime/macOS CLI check is the US-061 Marlin resumable plan: .build/debug/videoos-studio-cli marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing returned ready/canRun=true/sourceCount=9, maxSources=1, skipExisting=true, and a command carrying --max-sources 1 --skip-existing before source URLs. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live single-source completion, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest runtime/macOS CLI check is the US-061 real-project Marlin chunk pass: live marlin-evaluate completed twice on lively-alt-vol5, index-rebuild succeeded, marlin-status reports 2 assets / 13 events / 8 find results / coverage=0.22 / canPreferMarlin=false, and marlin-preference-status keeps canPreferMarlinAsDefault=false. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live single-source completion, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility, Copy behavior, stable action-scoped AX identifiers, and rough-cut-review Start &amp; Run stopping at the Codex approval gate; approved workspace-write review execution, Final render Open, and Marlin default Open remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-065 is promoted for native SQLite/RAG Search/Add, cited Agent prompt insertion, and InspectorTab.* Agent/Media switching without AX hangs. US-061 is promoted for runtime/model/mock/native AX, live non-mock single-source Marlin completion on a representative-source fixture, and resumable checkpointed chunk controls; the full multi-source live representative batch and repo-level Marlin-first preference promotion remain pending evidence gates. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility, Copy behavior, stable action-scoped AX identifiers, and rough-cut-review Start &amp; Run stopping at the Codex approval gate; approved workspace-write review execution, Final render Open, and Marlin default Open remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-065 is promoted for native SQLite/RAG Search/Add, cited Agent prompt insertion, and InspectorTab.* Agent/Media switching without AX hangs. US-061 is promoted for runtime/model/mock/native AX, live non-mock representative chunks on lively-alt-vol5, source-map-aware chunk controls, and resumable checkpointed evaluation; the remaining 7/9 lively-alt-vol5 live sources and repo-level Marlin-first preference promotion remain pending evidence gates. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2146,19 +2146,19 @@
         <x:v>As a native Studio operator, I can inspect Marlin runtime/model access/coverage/queue, run project Marlin evaluation, and apply Marlin preference when evidence gates pass.</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>MediaPanel renders MarlinEvaluationStatus, runtime/model access, representative buckets, queue items, run plan, evaluation button, and Apply Marlin Preference button. Evaluation can run only when sources exist and runtime/model checks pass; mock artifacts are workflow QA only and must not count as Marlin preference evidence. The Marlin status, queue, representative buckets, run/apply buttons, command line, artifact path, and resumable chunk options now expose stable MediaPanel.Marlin*/CLI contracts for native automation.</x:v>
+        <x:v>MediaPanel renders MarlinEvaluationStatus, runtime/model access, representative buckets, queue items, run plan, evaluation button, and Apply Marlin Preference button. Evaluation can run only when sources exist and runtime/model checks pass; mock artifacts are workflow QA only and must not count as Marlin preference evidence. The Marlin status, queue, representative buckets, run/apply buttons, command line, artifact path, source-map-aware source selection, and resumable chunk options now expose stable MediaPanel.Marlin*/CLI contracts for native automation.</x:v>
       </x:c>
       <x:c r="E62" s="26" t="str">
         <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:48-160; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1296-1325,2326-2481; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRuntimeStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinModelAccessStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationQueue.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRepresentativePlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationRunPlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinPreferenceDecision.swift; runtime/pipeline/stages/marlin.ts; scripts/marlin-evaluate.ts</x:v>
       </x:c>
       <x:c r="F62" s="26" t="str">
-        <x:v>Run Marlin runtime/model/preference/queue/representative-plan/eval-plan/eval-run/status CLI checks, execute a tiny mock evaluation fixture, verify index refresh, verify Preference apply is blocked when gates fail, run Marlin focused Swift tests, confirm stable Marlin accessibility identifiers, run at least one live non-mock representative-source completion, verify resumable chunk/checkpoint behavior, and leave full batch/preference promotion blocked until representative coverage and aggregate coverage gates pass.</x:v>
+        <x:v>Run Marlin runtime/model/preference/queue/representative-plan/eval-plan/eval-run/status CLI checks, execute a tiny mock evaluation fixture, verify index refresh, verify Preference apply is blocked when gates fail, run Marlin focused Swift tests, confirm stable Marlin accessibility identifiers, run live non-mock representative-source chunks, verify source-map-aware chunk/checkpoint behavior, and leave full batch/preference promotion blocked until representative coverage and aggregate coverage gates pass.</x:v>
       </x:c>
       <x:c r="G62" s="26" t="str">
-        <x:v>Runtime/model/mock/native AX/live single-source/resumable chunk pass; full batch preference gate pending</x:v>
+        <x:v>Runtime/model/mock/native AX/live 2-source resumable pass; full batch preference gate pending</x:v>
       </x:c>
       <x:c r="H62" s="11" t="str">
-        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. The runtime probe now imports dependency modules in isolated child processes, so the live marlin-runtime-status check no longer emits duplicate AVFoundation class warnings while still reporting every module ready. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path supports --request-timeout-ms / --timeout-ms, and a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4 completed with requestTimeoutMs=900000, wrote inference_mode=live Marlin events, updated segments with marlin_temporal_semantics, and rebuilt an index with 9 search documents. Current pass adds per-asset checkpoint writes in runMarlinAnalysis plus --max-sources and --skip-existing through marlin-evaluate, ProjectMarlinEvaluationRunPlan/Runner, marlin-eval-plan, marlin-eval-next, and marlin-eval-run. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and a command carrying those options before source URLs. A /tmp mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. All-existing skip-existing runs now return sourceCount=0 instead of a false failure. Focused verification passed: npx vitest run tests/marlin-incremental-merge.test.ts tests/marlin-analysis-stage.test.ts 11/0, npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, and swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0. Full all-source representative live run and repo-level preference promotion remain pending because the real repo gate still needs broader live coverage.</x:v>
+        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. The runtime probe now imports dependency modules in isolated child processes, so the live marlin-runtime-status check no longer emits duplicate AVFoundation class warnings while still reporting every module ready. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path supports --request-timeout-ms / --timeout-ms, and a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4 completed with requestTimeoutMs=900000, wrote inference_mode=live Marlin events, updated segments with marlin_temporal_semantics, and rebuilt an index with 9 search documents. Current passes add per-asset checkpoint writes in runMarlinAnalysis plus --max-sources and --skip-existing through marlin-evaluate, ProjectMarlinEvaluationRunPlan/Runner, marlin-eval-plan, marlin-eval-next, and marlin-eval-run, then make loadMarlinAssetInputs source-map-aware so explicit linked filenames resolve to the correct asset_id when assets.json stores original camera filenames. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and a command carrying those options before source URLs. A /tmp mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. The real lively-alt-vol5 project now has live Marlin artifacts for AST_5CAEC24E / 08-jun-a-man-and-a.mp4 and AST_25CDF4A5 / 06-jun-two-people-are.mp4: marlin_events.json has 2 assets, 13 events, and 8 find results; segments.json has marlin_reporter summaries plus marlin_temporal_semantics provenance for both segments; index-rebuild produced 2354 search documents with 13 Marlin events and 8 Marlin find results. marlin-status reports coverage=0.22 and canPreferMarlin=false, while marlin-preference-status remains partially ready with lively-alt-vol5 at 2/9 peak segments and canPreferMarlinAsDefault=false. Focused verification passed: npx vitest run tests/marlin-incremental-merge.test.ts tests/marlin-analysis-stage.test.ts 12/0, npx tsc --noEmit --pretty false, and node --check scripts/marlin-evaluate.ts. Full all-source representative live run and repo-level preference promotion remain pending because the real repo gate still needs broader live coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="48" customHeight="1">
@@ -3784,10 +3784,10 @@
         <x:v>Added --request-timeout-ms and --timeout-ms to scripts/marlin-evaluate.ts, threaded requestTimeoutMs through ProjectMarlinEvaluationRunPlan and ProjectMarlinEvaluationRunner, surfaced it in marlin-eval-plan/marlin-eval-next/marlin-eval-run, added per-asset marlin_events checkpoint writes, and exposed --max-sources plus --skip-existing so representative coverage can be accumulated across bounded local runs.</x:v>
       </x:c>
       <x:c r="H51" s="26" t="str">
-        <x:v>npx vitest run tests/marlin-incremental-merge.test.ts tests/marlin-analysis-stage.test.ts passed 11 tests, including checkpoint-before-later-timeout and all-existing skip-existing no-op coverage; npx tsc --noEmit --pretty false and node --check scripts/marlin-evaluate.ts passed; swift build --target VideoOSStudioCLI passed; swift test --filter ProjectMarlinEvaluationRunPlanTests passed 11 tests. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and the chunk options in the generated command. A /tmp lively-alt-vol5 mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. A prior live non-mock single-source run against a /tmp lively-alt-vol5-derived fixture completed with requestTimeoutMs=900000 and wrote live Marlin events. The full 9-source representative live batch remains intentionally pending.</x:v>
+        <x:v>npx vitest run tests/marlin-incremental-merge.test.ts tests/marlin-analysis-stage.test.ts passed 12 tests, including checkpoint-before-later-timeout, source_map-aware explicit source selection, and all-existing skip-existing no-op coverage; npx tsc --noEmit --pretty false and node --check scripts/marlin-evaluate.ts passed. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and the chunk options in the generated command. A /tmp lively-alt-vol5 mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. The real lively-alt-vol5 project now has live non-mock Marlin evidence for AST_5CAEC24E and AST_25CDF4A5: 2 assets, 13 events, 8 find results, 2/9 Marlin peak segments, searchDocuments=2354 after index rebuild, and marlin-status coverage=0.22/canPreferMarlin=false. The full 9-source representative live batch remains intentionally pending.</x:v>
       </x:c>
       <x:c r="I51" s="11" t="str">
-        <x:v>Mitigated; resumable chunks; full batch pending</x:v>
+        <x:v>Mitigated; live 2/9 resumable chunks; full batch pending</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="48" customHeight="1">
@@ -3911,65 +3911,65 @@
         <x:v>ISS-055</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>macOS UX/playback</x:v>
+        <x:v>macOS runtime/logistics</x:v>
       </x:c>
       <x:c r="E56" s="26" t="str">
-        <x:v>A valid native Viewer media URL could still present as a black surface while playback was paused or before AVPlayerLayer painted its first frame.</x:v>
+        <x:v>Marlin explicit source selection could map a linked 02_media filename to the wrong asset when assets.json kept the original camera filename.</x:v>
       </x:c>
       <x:c r="F56" s="26" t="str">
-        <x:v>MediaVideoPlayer depended on AVPlayerLayer seek/ready callbacks to paint the initial still frame. In this desktop session screen capture is unreliable, but runtime evidence separated missing source media from a valid timeline preview path: lively-talk-pv source media is missing because /Volumes/DATA05 is unmounted, while 09_output/rough-cut.mp4 is a playable H.264 timeline preview.</x:v>
+        <x:v>loadMarlinAssetInputs resolved assets from assets.json source_locator, then filename basename, then sourceFiles by index. lively-alt-vol5 assets.json stores names such as D5053.MP4 while 02_media/source_map.json maps AST_5CAEC24E to the linked 08-jun-a-man-and-a.mp4 path, so passing only that linked source would previously select the first asset by indexed fallback.</x:v>
       </x:c>
       <x:c r="G56" s="26" t="str">
-        <x:v>Added a poster CALayer above the AVPlayerLayer. The coordinator now generates an AVAssetImageGenerator frame asynchronously at the current Viewer start time, falls back to time zero, shows that poster while paused, and hides it during playback.</x:v>
+        <x:v>Changed loadMarlinAssetInputs to load 02_media/source_map.json through the shared loadSourceMap helper and prefer source_map local_source_path/source_locator/link_path when assets.json omits source_locator.</x:v>
       </x:c>
       <x:c r="H56" s="26" t="str">
-        <x:v>AVAssetImageGenerator generated a 1600x899 poster frame from projects/lively-talk-pv/09_output/rough-cut.mp4 at 1.5s; ProjectMediaResolverTests executed 23 tests with 0 failures; swift build --target VideoOSStudio passed; git diff --check on ViewerViews.swift passed; build_and_run --verify relaunched VideoOSStudio PID 31750 with a visible 1180x812 CGWindow. TL-229 confirms the paused 00:00:00 exact-preview Viewer surface is nonblack on fresh launch.</x:v>
+        <x:v>The new marlin-analysis-stage test loads assets with original camera filenames plus a source_map and verifies that explicit 02_media/08-jun-a-man-and-a.mp4 selects AST_B rather than the first asset. A live lively-alt-vol5 run then wrote AST_5CAEC24E for 08-jun-a-man-and-a.mp4 and AST_25CDF4A5 for 06-jun-two-people-are.mp4, confirming the fixed mapping on the real project.</x:v>
       </x:c>
       <x:c r="I56" s="11" t="str">
-        <x:v>Fixed; TL-229 paused-frame pixel pass</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="48" customHeight="1">
       <x:c r="A57" s="10" t="str">
-        <x:v>ISS-056</x:v>
+        <x:v>ISS-055</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>US-065</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>macOS UX/testability</x:v>
+        <x:v>macOS UX/playback</x:v>
       </x:c>
       <x:c r="E57" s="26" t="str">
-        <x:v>SQLite/RAG native controls and result rows could be inspected only by label/content while this desktop session cannot enumerate SwiftUI windows or capture pixels.</x:v>
+        <x:v>A valid native Viewer media URL could still present as a black surface while playback was paused or before AVPlayerLayer painted its first frame.</x:v>
       </x:c>
       <x:c r="F57" s="26" t="str">
-        <x:v>MediaPanel rendered Rebuild Index, the search field/button, Add RAG Context, the empty state, the context summary, and result cards without stable accessibility identifiers. Earlier System Events windows were intermittent, so label/coordinate targeting was fragile until the MediaPanel could be targeted through the toolbar radio group and right-pane scroll area.</x:v>
+        <x:v>MediaVideoPlayer depended on AVPlayerLayer seek/ready callbacks to paint the initial still frame. In this desktop session screen capture is unreliable, but runtime evidence separated missing source media from a valid timeline preview path: lively-talk-pv source media is missing because /Volumes/DATA05 is unmounted, while 09_output/rough-cut.mp4 is a playable H.264 timeline preview.</x:v>
       </x:c>
       <x:c r="G57" s="26" t="str">
-        <x:v>Added MediaPanel.IndexOperationStatus, MediaPanel.RebuildIndexButton, MediaPanel.IndexSearchField, MediaPanel.IndexSearchButton, MediaPanel.AddRAGContextButton, MediaPanel.IndexSearchEmptyState, MediaPanel.IndexContextSummary, and MediaPanel.IndexSearchResult.&lt;documentID&gt; identifiers, then verified the native Search/Add flow against AX-1.</x:v>
+        <x:v>Added a poster CALayer above the AVPlayerLayer. The coordinator now generates an AVAssetImageGenerator frame asynchronously at the current Viewer start time, falls back to time zero, shows that poster while paused, and hides it during playback.</x:v>
       </x:c>
       <x:c r="H57" s="26" t="str">
-        <x:v>rg confirmed the identifiers; focused SQLite/RAG/readiness/agent suite executed 38 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify exited 0; synthetic index/search/context/agent-prompt smoke passed with 5 docs and 4 cited results; latest native pass on PID 9971 selected InspectorTab.Media, searched 参加, found 3 cited results across audio-story-node, segment, and transcript, clicked Add RAG Context, then selected InspectorTab.Agent and confirmed the prompt contained Material RAG context for query `参加` with all 3 citations. The app stayed responsive and ps reported 0.0% CPU.</x:v>
+        <x:v>AVAssetImageGenerator generated a 1600x899 poster frame from projects/lively-talk-pv/09_output/rough-cut.mp4 at 1.5s; ProjectMediaResolverTests executed 23 tests with 0 failures; swift build --target VideoOSStudio passed; git diff --check on ViewerViews.swift passed; build_and_run --verify relaunched VideoOSStudio PID 31750 with a visible 1180x812 CGWindow. TL-229 confirms the paused 00:00:00 exact-preview Viewer surface is nonblack on fresh launch.</x:v>
       </x:c>
       <x:c r="I57" s="11" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Fixed; TL-229 paused-frame pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="48" customHeight="1">
       <x:c r="A58" s="10" t="str">
-        <x:v>ISS-057</x:v>
+        <x:v>ISS-056</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-065</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
         <x:v>Medium</x:v>
@@ -3978,16 +3978,16 @@
         <x:v>macOS UX/testability</x:v>
       </x:c>
       <x:c r="E58" s="26" t="str">
-        <x:v>Clip Inspector note editors and Ask/Save/Clear controls could be inspected only by label/content, making the native editor-note workflow hard to automate safely.</x:v>
+        <x:v>SQLite/RAG native controls and result rows could be inspected only by label/content while this desktop session cannot enumerate SwiftUI windows or capture pixels.</x:v>
       </x:c>
       <x:c r="F58" s="26" t="str">
-        <x:v>ClipInspectorPanel rendered TextEditor fields and action buttons without stable accessibility identifiers. Earlier evidence relied on CLI parity because direct UI automation could not reliably target the note draft, handoff draft, or action buttons.</x:v>
+        <x:v>MediaPanel rendered Rebuild Index, the search field/button, Add RAG Context, the empty state, the context summary, and result cards without stable accessibility identifiers. Earlier System Events windows were intermittent, so label/coordinate targeting was fragile until the MediaPanel could be targeted through the toolbar radio group and right-pane scroll area.</x:v>
       </x:c>
       <x:c r="G58" s="26" t="str">
-        <x:v>Added ClipInspector.EditorAnnotationSummary, SavedNoteUpdatedAt, SavedHandoffInstruction, NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, EditorAnnotationStatus, and NoSelectionMessage identifiers.</x:v>
+        <x:v>Added MediaPanel.IndexOperationStatus, MediaPanel.RebuildIndexButton, MediaPanel.IndexSearchField, MediaPanel.IndexSearchButton, MediaPanel.AddRAGContextButton, MediaPanel.IndexSearchEmptyState, MediaPanel.IndexContextSummary, and MediaPanel.IndexSearchResult.&lt;documentID&gt; identifiers, then verified the native Search/Add flow against AX-1.</x:v>
       </x:c>
       <x:c r="H58" s="26" t="str">
-        <x:v>rg confirmed the identifiers; focused annotation tests executed 5 tests with 0 failures; temporary clean-ui CLI smoke saved CLP_0001, generated a prompt with existing note context, cleared the note, and verified notes=[]; AX exposed NoSelectionMessage before selection and note editor/button identifiers after selecting the first timeline clip. Native Save/Clear was exercised through ClipInspector.NoteDraftEditor/HandoffInstructionDraftEditor/SaveNoteButton/ClearNoteButton with visible screenshots and filesystem verification. A live stdio Codex App Server session then pressed ClipInspector.AskCodexButton for CLP_0001 and populated both draft editors with a proposal without writing files.</x:v>
+        <x:v>rg confirmed the identifiers; focused SQLite/RAG/readiness/agent suite executed 38 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify exited 0; synthetic index/search/context/agent-prompt smoke passed with 5 docs and 4 cited results; latest native pass on PID 9971 selected InspectorTab.Media, searched 参加, found 3 cited results across audio-story-node, segment, and transcript, clicked Add RAG Context, then selected InspectorTab.Agent and confirmed the prompt contained Material RAG context for query `参加` with all 3 citations. The app stayed responsive and ps reported 0.0% CPU.</x:v>
       </x:c>
       <x:c r="I58" s="11" t="str">
         <x:v>Fixed</x:v>
@@ -3995,10 +3995,10 @@
     </x:row>
     <x:row r="59" ht="48" customHeight="1">
       <x:c r="A59" s="10" t="str">
-        <x:v>ISS-058</x:v>
+        <x:v>ISS-057</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>US-058</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
         <x:v>Medium</x:v>
@@ -4007,16 +4007,16 @@
         <x:v>macOS UX/testability</x:v>
       </x:c>
       <x:c r="E59" s="26" t="str">
-        <x:v>QA Dashboard issue rows could remain unreachable in the native UI, so reviewers could see the score/radar but not reliably click a timestamped QA issue jump.</x:v>
+        <x:v>Clip Inspector note editors and Ask/Save/Clear controls could be inspected only by label/content, making the native editor-note workflow hard to automate safely.</x:v>
       </x:c>
       <x:c r="F59" s="26" t="str">
-        <x:v>The first mitigation added identifiers, but the issue list still used SwiftUI DisclosureGroup. In the running app, Iteration 1 exposed as AXDisclosureTriangle with no actions, AXDisclosing stayed 0, and issue jump buttons were not instantiated until the hidden group opened. A parent QADashboard.IssueGroup identifier also overrode child issue button identifiers after the first always-visible-row fix attempt.</x:v>
+        <x:v>ClipInspectorPanel rendered TextEditor fields and action buttons without stable accessibility identifiers. Earlier evidence relied on CLI parity because direct UI automation could not reliably target the note draft, handoff draft, or action buttons.</x:v>
       </x:c>
       <x:c r="G59" s="26" t="str">
-        <x:v>Replaced the issue DisclosureGroup with a direct VStack iteration header plus visible QAIssueRow buttons, moved the IssueGroup identifier to the header text, and preserved QADashboard.IssueJumpButton.&lt;issue_id&gt; on the button itself.</x:v>
+        <x:v>Added ClipInspector.EditorAnnotationSummary, SavedNoteUpdatedAt, SavedHandoffInstruction, NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, EditorAnnotationStatus, and NoSelectionMessage identifiers.</x:v>
       </x:c>
       <x:c r="H59" s="26" t="str">
-        <x:v>On PID 97663, QA tab for ena-promo-ai exposed QADashboard.BriefAlignmentRadar and QADashboard.IssueJumpButton.QAISSUE_16707063a988 / QAISSUE_2c0c06267ed5. AXPress on QAISSUE_16707063a988 moved the native Playhead from 00:00:00:00 to 00:00:17:12; /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows the visible issue rows and jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
+        <x:v>rg confirmed the identifiers; focused annotation tests executed 5 tests with 0 failures; temporary clean-ui CLI smoke saved CLP_0001, generated a prompt with existing note context, cleared the note, and verified notes=[]; AX exposed NoSelectionMessage before selection and note editor/button identifiers after selecting the first timeline clip. Native Save/Clear was exercised through ClipInspector.NoteDraftEditor/HandoffInstructionDraftEditor/SaveNoteButton/ClearNoteButton with visible screenshots and filesystem verification. A live stdio Codex App Server session then pressed ClipInspector.AskCodexButton for CLP_0001 and populated both draft editors with a proposal without writing files.</x:v>
       </x:c>
       <x:c r="I59" s="11" t="str">
         <x:v>Fixed</x:v>
@@ -4024,36 +4024,36 @@
     </x:row>
     <x:row r="60" ht="48" customHeight="1">
       <x:c r="A60" s="10" t="str">
-        <x:v>ISS-059</x:v>
+        <x:v>ISS-058</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-058</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>macOS logistics/window</x:v>
+        <x:v>macOS UX/testability</x:v>
       </x:c>
       <x:c r="E60" s="26" t="str">
-        <x:v>The running VideoOSStudio window could be off-screen, making the user think the native preview was not displaying.</x:v>
+        <x:v>QA Dashboard issue rows could remain unreachable in the native UI, so reviewers could see the score/radar but not reliably click a timestamped QA issue jump.</x:v>
       </x:c>
       <x:c r="F60" s="26" t="str">
-        <x:v>System Events reported the app window at {-1920,-555} while the desktop screenshot showed only Finder. After repositioning the window to {80,80}, the native Viewer showed the AX-1 timeline preview frame correctly. Separate data inspection showed demo/sample have timeline/assets but no playable source media or preview MP4s, so those projects legitimately show the no-media diagnostic. A follow-up found NSScreen.main can point at the off-screen/key-window display, so the previous usable-frame guard accepted the wrong display.</x:v>
+        <x:v>The first mitigation added identifiers, but the issue list still used SwiftUI DisclosureGroup. In the running app, Iteration 1 exposed as AXDisclosureTriangle with no actions, AXDisclosing stayed 0, and issue jump buttons were not instantiated until the hidden group opened. A parent QADashboard.IssueGroup identifier also overrode child issue button identifiers after the first always-visible-row fix attempt.</x:v>
       </x:c>
       <x:c r="G60" s="26" t="str">
-        <x:v>Updated VideoOSStudioApp.ensureUsableMainWindowFrame so launch/reopen paths require enough visible area on the origin-zero primary display, while normal manual window moves can still stay on any usable display. The guard runs on launch and delayed focus retries.</x:v>
+        <x:v>Replaced the issue DisclosureGroup with a direct VStack iteration header plus visible QAIssueRow buttons, moved the IssueGroup identifier to the header text, and preserved QADashboard.IssueJumpButton.&lt;issue_id&gt; on the button itself.</x:v>
       </x:c>
       <x:c r="H60" s="26" t="str">
-        <x:v>After forcing the app window back to {-1920,-555}, build_and_run --verify relaunched VideoOSStudio PID 99006 and System Events/CGWindow both reported the corrected main-display frame at about {221,119} with size 1240x780. swift build --target VideoOSStudio, focused Marlin tests, and git diff --check passed. TL-229 fresh-launch evidence confirms the visible primary-display window shows nonblack Viewer pixels.</x:v>
+        <x:v>On PID 97663, QA tab for ena-promo-ai exposed QADashboard.BriefAlignmentRadar and QADashboard.IssueJumpButton.QAISSUE_16707063a988 / QAISSUE_2c0c06267ed5. AXPress on QAISSUE_16707063a988 moved the native Playhead from 00:00:00:00 to 00:00:17:12; /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows the visible issue rows and jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
       </x:c>
       <x:c r="I60" s="11" t="str">
-        <x:v>Fixed; TL-229 fresh-launch pixel pass</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="48" customHeight="1">
       <x:c r="A61" s="10" t="str">
-        <x:v>ISS-060</x:v>
+        <x:v>ISS-059</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
         <x:v>US-045</x:v>
@@ -4062,48 +4062,48 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>macOS UX/playback</x:v>
+        <x:v>macOS logistics/window</x:v>
       </x:c>
       <x:c r="E61" s="26" t="str">
-        <x:v>At the end of the AX-1 timeline, the native Viewer could keep using the 8s preview-editor legacy MP4, causing a black or wrong preview even though a 75s rendered output existed.</x:v>
+        <x:v>The running VideoOSStudio window could be off-screen, making the user think the native preview was not displaying.</x:v>
       </x:c>
       <x:c r="F61" s="26" t="str">
-        <x:v>ProjectMediaResolver.resolveTimelinePreview picked the first existing timeline preview candidate without checking whether that media was long enough for the current playhead. The latest preview-editor-* file can be much shorter than the timeline and can mask rough-cut/final/latest-output fallbacks.</x:v>
+        <x:v>System Events reported the app window at {-1920,-555} while the desktop screenshot showed only Finder. After repositioning the window to {80,80}, the native Viewer showed the AX-1 timeline preview frame correctly. Separate data inspection showed demo/sample have timeline/assets but no playable source media or preview MP4s, so those projects legitimately show the no-media diagnostic. A follow-up found NSScreen.main can point at the off-screen/key-window display, so the previous usable-frame guard accepted the wrong display.</x:v>
       </x:c>
       <x:c r="G61" s="26" t="str">
-        <x:v>Added duration-aware filtering for timeline preview candidates. Known-short candidates are skipped after duration + 0.25s, while unknown-duration candidates remain usable to preserve older fallback behavior. Added an internal durationReader overload for deterministic tests.</x:v>
+        <x:v>Updated VideoOSStudioApp.ensureUsableMainWindowFrame so launch/reopen paths require enough visible area on the origin-zero primary display, while normal manual window moves can still stay on any usable display. The guard runs on launch and delayed focus retries.</x:v>
       </x:c>
       <x:c r="H61" s="26" t="str">
-        <x:v>ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; ./script/build_and_run.sh --verify relaunched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures; screenshot /tmp/videoos-debug/preview-fallback-end-menu-step.png shows 00:01:14 using timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 and preview-editor-1775121573933.mp4 duration 8.007633.</x:v>
+        <x:v>After forcing the app window back to {-1920,-555}, build_and_run --verify relaunched VideoOSStudio PID 99006 and System Events/CGWindow both reported the corrected main-display frame at about {221,119} with size 1240x780. swift build --target VideoOSStudio, focused Marlin tests, and git diff --check passed. TL-229 fresh-launch evidence confirms the visible primary-display window shows nonblack Viewer pixels.</x:v>
       </x:c>
       <x:c r="I61" s="11" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Fixed; TL-229 fresh-launch pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="48" customHeight="1">
       <x:c r="A62" s="10" t="str">
-        <x:v>ISS-061</x:v>
+        <x:v>ISS-060</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
-        <x:v>US-056</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>macOS UX/testability</x:v>
+        <x:v>macOS UX/playback</x:v>
       </x:c>
       <x:c r="E62" s="26" t="str">
-        <x:v>Candidate Swap leaf controls were present visually, but AX reported every sheet descendant as CandidateSwap.Sheet, hiding SearchForMoreButton and UseButton identifiers.</x:v>
+        <x:v>At the end of the AX-1 timeline, the native Viewer could keep using the 8s preview-editor legacy MP4, causing a black or wrong preview even though a 75s rendered output existed.</x:v>
       </x:c>
       <x:c r="F62" s="26" t="str">
-        <x:v>The root CandidateSwap sheet and parent panels carried accessibility identifiers. In SwiftUI this shadowed child AXIdentifier values, the same class of issue previously observed in grouped QA Dashboard rows.</x:v>
+        <x:v>ProjectMediaResolver.resolveTimelinePreview picked the first existing timeline preview candidate without checking whether that media was long enough for the current playhead. The latest preview-editor-* file can be much shorter than the timeline and can mask rough-cut/final/latest-output fallbacks.</x:v>
       </x:c>
       <x:c r="G62" s="26" t="str">
-        <x:v>Removed parent/container identifiers from the Candidate Swap root, current panel, alternatives panel/list, and candidate card container. Kept identifiers only on leaf title/subtitle/count/button/segment/empty/error elements so actionable controls expose their own stable AX IDs.</x:v>
+        <x:v>Added duration-aware filtering for timeline preview candidates. Known-short candidates are skipped after duration + 0.25s, while unknown-duration candidates remain usable to preserve older fallback behavior. Added an internal durationReader overload for deterministic tests.</x:v>
       </x:c>
       <x:c r="H62" s="26" t="str">
-        <x:v>After relaunch, AX exposed CandidateSwap.Title, CandidateSwap.Subtitle, CandidateSwap.CurrentClipHeader, CandidateSwap.AlternativeCount, CandidateSwap.SearchForMoreButton, CandidateSwap.CandidateSegment.*, and CandidateSwap.UseButton.* independently. On ena-promo-ai CLP_0002, AlternativeCount=21, Search for more opened FootageSearch, Use staged a swap and the status bar showed 1 swapped. swift build --target VideoOSStudio, focused Candidate/StudioFeedback tests, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
+        <x:v>ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; ./script/build_and_run.sh --verify relaunched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures; screenshot /tmp/videoos-debug/preview-fallback-end-menu-step.png shows 00:01:14 using timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 and preview-editor-1775121573933.mp4 duration 8.007633.</x:v>
       </x:c>
       <x:c r="I62" s="11" t="str">
         <x:v>Fixed</x:v>
@@ -4111,28 +4111,28 @@
     </x:row>
     <x:row r="63" ht="48" customHeight="1">
       <x:c r="A63" s="10" t="str">
-        <x:v>ISS-062</x:v>
+        <x:v>ISS-061</x:v>
       </x:c>
       <x:c r="B63" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-056</x:v>
       </x:c>
       <x:c r="C63" s="26" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="D63" s="26" t="str">
-        <x:v>Preview generation/playback contract</x:v>
+        <x:v>macOS UX/testability</x:v>
       </x:c>
       <x:c r="E63" s="26" t="str">
-        <x:v>The native Viewer could select preview-full.mp4 as an exact timeline preview, but the generated preview file could be longer than the compiled timeline and drift away from timeline intent.</x:v>
+        <x:v>Candidate Swap leaf controls were present visually, but AX reported every sheet descendant as CandidateSwap.Sheet, hiding SearchForMoreButton and UseButton identifiers.</x:v>
       </x:c>
       <x:c r="F63" s="26" t="str">
-        <x:v>runtime/preview/segment-renderer.ts extracted src_out_us - src_in_us for each source clip. Some source trim ranges are intentionally longer than timeline_duration_frames, so preview-segment.ts reported the timeline target duration while ffprobe showed a longer rendered MP4.</x:v>
+        <x:v>The root CandidateSwap sheet and parent panels carried accessibility identifiers. In SwiftUI this shadowed child AXIdentifier values, the same class of issue previously observed in grouped QA Dashboard rows.</x:v>
       </x:c>
       <x:c r="G63" s="26" t="str">
-        <x:v>Changed buildClipExtractArgs to accept a timeline-derived target duration, clamp it to the available source duration, and use clipTimelineDurationSec from timeline_duration_frames/fps during preview generation. Added unit and integration coverage for source ranges longer than timeline clips.</x:v>
+        <x:v>Removed parent/container identifiers from the Candidate Swap root, current panel, alternatives panel/list, and candidate card container. Kept identifiers only on leaf title/subtitle/count/button/segment/empty/error elements so actionable controls expose their own stable AX IDs.</x:v>
       </x:c>
       <x:c r="H63" s="26" t="str">
-        <x:v>Before fix, ena-promo-ai preview-segment.ts reported 76.1s but ffprobe showed preview-full.mp4 duration 93.581380s. After fix and regeneration, ffprobe reported 75.914714s for 76.083333s timeline content; playback-contract-status returned exact with timelineHash f3bc3e6fef222e1a; computer-use selected ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with a visible nonblack frame. npx vitest run tests/preview.test.ts passed 29 tests; npm run build passed; swift test --filter ProjectMediaResolverTests passed 25 tests.</x:v>
+        <x:v>After relaunch, AX exposed CandidateSwap.Title, CandidateSwap.Subtitle, CandidateSwap.CurrentClipHeader, CandidateSwap.AlternativeCount, CandidateSwap.SearchForMoreButton, CandidateSwap.CandidateSegment.*, and CandidateSwap.UseButton.* independently. On ena-promo-ai CLP_0002, AlternativeCount=21, Search for more opened FootageSearch, Use staged a swap and the status bar showed 1 swapped. swift build --target VideoOSStudio, focused Candidate/StudioFeedback tests, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
       </x:c>
       <x:c r="I63" s="11" t="str">
         <x:v>Fixed</x:v>
@@ -4140,28 +4140,28 @@
     </x:row>
     <x:row r="64" ht="48" customHeight="1">
       <x:c r="A64" s="10" t="str">
-        <x:v>ISS-063</x:v>
+        <x:v>ISS-062</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>US-047</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
-        <x:v>Medium</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>macOS UX/keyboard</x:v>
+        <x:v>Preview generation/playback contract</x:v>
       </x:c>
       <x:c r="E64" s="26" t="str">
-        <x:v>Reopening Command Palette could keep stale text in the visible search field even though the Swift query state was reset before presenting.</x:v>
+        <x:v>The native Viewer could select preview-full.mp4 as an exact timeline preview, but the generated preview file could be longer than the compiled timeline and drift away from timeline intent.</x:v>
       </x:c>
       <x:c r="F64" s="26" t="str">
-        <x:v>The CommandPalettePanel reuses the same NSTextField/field editor between presentations. ContentView reset commandPaletteQuery to an empty string on open, but focusSearchField only made the field first responder and selected it; the AppKit field editor could still expose the previous composed value through AX and interfere with predictable keyboard/paste testing.</x:v>
+        <x:v>runtime/preview/segment-renderer.ts extracted src_out_us - src_in_us for each source clip. Some source trim ranges are intentionally longer than timeline_duration_frames, so preview-segment.ts reported the timeline target duration while ffprobe showed a longer rendered MP4.</x:v>
       </x:c>
       <x:c r="G64" s="26" t="str">
-        <x:v>Changed focusSearchField to sync the NSTextField.stringValue and currentEditor string from parent.query before selecting the search text. This keeps the visible field and Swift binding aligned on every presentation.</x:v>
+        <x:v>Changed buildClipExtractArgs to accept a timeline-derived target duration, clamp it to the available source duration, and use clipTimelineDurationSec from timeline_duration_frames/fps during preview generation. Added unit and integration coverage for source ranges longer than timeline clips.</x:v>
       </x:c>
       <x:c r="H64" s="26" t="str">
-        <x:v>After relaunch, Cmd-K opened a clean Command Palette search field. Setting AXValue to search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet; closing it returned to the main window with status Footage search opened; reopening and pressing Esc left only the Video OS Studio window. swift build --target VideoOSStudio, swift test --filter StudioCommandPaletteCommandTests 4/0, build_and_run.sh --verify, and git diff --check on ContentView.swift passed.</x:v>
+        <x:v>Before fix, ena-promo-ai preview-segment.ts reported 76.1s but ffprobe showed preview-full.mp4 duration 93.581380s. After fix and regeneration, ffprobe reported 75.914714s for 76.083333s timeline content; playback-contract-status returned exact with timelineHash f3bc3e6fef222e1a; computer-use selected ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with a visible nonblack frame. npx vitest run tests/preview.test.ts passed 29 tests; npm run build passed; swift test --filter ProjectMediaResolverTests passed 25 tests.</x:v>
       </x:c>
       <x:c r="I64" s="11" t="str">
         <x:v>Fixed</x:v>
@@ -4169,28 +4169,28 @@
     </x:row>
     <x:row r="65" ht="48" customHeight="1">
       <x:c r="A65" s="10" t="str">
-        <x:v>ISS-064</x:v>
+        <x:v>ISS-063</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>US-057</x:v>
+        <x:v>US-047</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>macOS UX/testability</x:v>
+        <x:v>macOS UX/keyboard</x:v>
       </x:c>
       <x:c r="E65" s="26" t="str">
-        <x:v>Footage Search results were visible, but result-card AX identifiers shadowed child Preview/BeatPicker/Use controls, and Command Palette opens could leave Use disabled because no clip-specific beat target was selected.</x:v>
+        <x:v>Reopening Command Palette could keep stale text in the visible search field even though the Swift query state was reset before presenting.</x:v>
       </x:c>
       <x:c r="F65" s="26" t="str">
-        <x:v>A parent FootageSearch.ResultCard identifier on the card container caused SwiftUI AX to report the thumbnail, text, Preview, beat picker, and Use button under the same ID. The global open path also initialized selectedBeatID to empty when no selected clip was available, so Use was disabled until the operator picked a beat manually.</x:v>
+        <x:v>The CommandPalettePanel reuses the same NSTextField/field editor between presentations. ContentView reset commandPaletteQuery to an empty string on open, but focusSearchField only made the field first responder and selected it; the AppKit field editor could still expose the previous composed value through AX and interfere with predictable keyboard/paste testing.</x:v>
       </x:c>
       <x:c r="G65" s="26" t="str">
-        <x:v>Keep accessibility identifiers on leaf controls only, add FootageSearch.* identifiers for title/project/mode/query/search/path fields/status/result leaf controls, and initialize selectedBeatID from explicit initial beat, selected clip beat, or the first timeline beat.</x:v>
+        <x:v>Changed focusSearchField to sync the NSTextField.stringValue and currentEditor string from parent.query before selecting the search text. This keeps the visible field and Swift binding aligned on every presentation.</x:v>
       </x:c>
       <x:c r="H65" s="26" t="str">
-        <x:v>After relaunch, Search Footage opened from Command Palette on ax1-participant-voices-20260401. Text query AI returned Results 2 / fallback; AX exposed FootageSearch.ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* independently; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on the in-timeline result set preview status, clicking Use on SEG_AST_610FB4A0_0001 staged 1 swapped pending operation, and Discard returned pending counts to zero. swift build --target VideoOSStudio, focused FootageSearchRunner/StudioFeedbackSession tests 15/0, footage-search Vitest 10/0, build_and_run --verify, and recent log scan passed.</x:v>
+        <x:v>After relaunch, Cmd-K opened a clean Command Palette search field. Setting AXValue to search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet; closing it returned to the main window with status Footage search opened; reopening and pressing Esc left only the Video OS Studio window. swift build --target VideoOSStudio, swift test --filter StudioCommandPaletteCommandTests 4/0, build_and_run.sh --verify, and git diff --check on ContentView.swift passed.</x:v>
       </x:c>
       <x:c r="I65" s="11" t="str">
         <x:v>Fixed</x:v>
@@ -4198,28 +4198,28 @@
     </x:row>
     <x:row r="66" ht="48" customHeight="1">
       <x:c r="A66" s="10" t="str">
-        <x:v>ISS-065</x:v>
+        <x:v>ISS-064</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>US-066</x:v>
+        <x:v>US-057</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
-        <x:v>Low</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
         <x:v>macOS UX/testability</x:v>
       </x:c>
       <x:c r="E66" s="26" t="str">
-        <x:v>The Settings transport picker and explanatory text were visible, but lacked stable accessibility identifiers for repeatable native automation.</x:v>
+        <x:v>Footage Search results were visible, but result-card AX identifiers shadowed child Preview/BeatPicker/Use controls, and Command Palette opens could leave Use disabled because no clip-specific beat target was selected.</x:v>
       </x:c>
       <x:c r="F66" s="26" t="str">
-        <x:v>SettingsView rendered the Picker and description without leaf identifiers, so picker mutation proof depended on visible labels or coordinate-style targeting instead of a durable AX contract.</x:v>
+        <x:v>A parent FootageSearch.ResultCard identifier on the card container caused SwiftUI AX to report the thumbnail, text, Preview, beat picker, and Use button under the same ID. The global open path also initialized selectedBeatID to empty when no selected clip was available, so Use was disabled until the operator picked a beat manually.</x:v>
       </x:c>
       <x:c r="G66" s="26" t="str">
-        <x:v>Added Settings.TransportPicker to the transport picker and Settings.TransportDescription to the description text, keeping the identifiers on leaf elements only.</x:v>
+        <x:v>Keep accessibility identifiers on leaf controls only, add FootageSearch.* identifiers for title/project/mode/query/search/path fields/status/result leaf controls, and initialize selectedBeatID from explicit initial beat, selected clip beat, or the first timeline beat.</x:v>
       </x:c>
       <x:c r="H66" s="26" t="str">
-        <x:v>Computer-use AX inspection exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker changed stdio to websocket, defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket, changing back returned stdio, and the test defaults key was deleted afterward. swift build --target VideoOSStudio, CodexAppServerProtocolTests 10/0, and build_and_run --verify passed.</x:v>
+        <x:v>After relaunch, Search Footage opened from Command Palette on ax1-participant-voices-20260401. Text query AI returned Results 2 / fallback; AX exposed FootageSearch.ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* independently; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on the in-timeline result set preview status, clicking Use on SEG_AST_610FB4A0_0001 staged 1 swapped pending operation, and Discard returned pending counts to zero. swift build --target VideoOSStudio, focused FootageSearchRunner/StudioFeedbackSession tests 15/0, footage-search Vitest 10/0, build_and_run --verify, and recent log scan passed.</x:v>
       </x:c>
       <x:c r="I66" s="11" t="str">
         <x:v>Fixed</x:v>
@@ -4227,28 +4227,28 @@
     </x:row>
     <x:row r="67" ht="48" customHeight="1">
       <x:c r="A67" s="10" t="str">
-        <x:v>ISS-066</x:v>
+        <x:v>ISS-065</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>US-059</x:v>
+        <x:v>US-066</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
-        <x:v>Medium</x:v>
+        <x:v>Low</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
         <x:v>macOS UX/testability</x:v>
       </x:c>
       <x:c r="E67" s="26" t="str">
-        <x:v>Media Relink controls were visible, but the status text and Relink/Use Source Map Roots/Replace Synthetic Media buttons did not have durable accessibility identifiers.</x:v>
+        <x:v>The Settings transport picker and explanatory text were visible, but lacked stable accessibility identifiers for repeatable native automation.</x:v>
       </x:c>
       <x:c r="F67" s="26" t="str">
-        <x:v>MediaPanel rendered these controls only by label. That made NSOpenPanel and source-map-root relink proof depend on localized text or positions rather than stable leaf identifiers.</x:v>
+        <x:v>SettingsView rendered the Picker and description without leaf identifiers, so picker mutation proof depended on visible labels or coordinate-style targeting instead of a durable AX contract.</x:v>
       </x:c>
       <x:c r="G67" s="26" t="str">
-        <x:v>Added MediaPanel.MediaRelinkStatus, MediaPanel.RelinkMissingMediaButton, MediaPanel.UseSourceMapRootsButton, and MediaPanel.ReplaceSyntheticMediaButton while keeping the identifiers on actionable leaf controls.</x:v>
+        <x:v>Added Settings.TransportPicker to the transport picker and Settings.TransportDescription to the description text, keeping the identifiers on leaf elements only.</x:v>
       </x:c>
       <x:c r="H67" s="26" t="str">
-        <x:v>On a disposable us059-native-relink-smoke project, computer-use exposed all four identifiers, opened the Relink Missing Media NSOpenPanel, observed cancellation, clicked Use Source Map Roots, and saw MediaRelinkStatus change to Relinked 1 files with 0 missing. CLI media-status and media-source-map-status confirmed ready=1/missing=0, coverage 1/1, and one relinked symlink. ProjectMediaResolverTests 25/0, swift build --target VideoOSStudio, build_and_run --verify, and diff check passed.</x:v>
+        <x:v>Computer-use AX inspection exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker changed stdio to websocket, defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket, changing back returned stdio, and the test defaults key was deleted afterward. swift build --target VideoOSStudio, CodexAppServerProtocolTests 10/0, and build_and_run --verify passed.</x:v>
       </x:c>
       <x:c r="I67" s="11" t="str">
         <x:v>Fixed</x:v>
@@ -4256,10 +4256,10 @@
     </x:row>
     <x:row r="68" ht="48" customHeight="1">
       <x:c r="A68" s="10" t="str">
-        <x:v>ISS-067</x:v>
+        <x:v>ISS-066</x:v>
       </x:c>
       <x:c r="B68" s="26" t="str">
-        <x:v>US-060</x:v>
+        <x:v>US-059</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
         <x:v>Medium</x:v>
@@ -4268,16 +4268,16 @@
         <x:v>macOS UX/testability</x:v>
       </x:c>
       <x:c r="E68" s="26" t="str">
-        <x:v>Synthetic demo media, smoke, and proxy controls were runnable, but their MediaPanel controls could not be targeted repeatably by native automation.</x:v>
+        <x:v>Media Relink controls were visible, but the status text and Relink/Use Source Map Roots/Replace Synthetic Media buttons did not have durable accessibility identifiers.</x:v>
       </x:c>
       <x:c r="F68" s="26" t="str">
-        <x:v>The Synthetic Demo Media and Proxy Transcode Plan sections rendered status text, action buttons, proxy empty state, and proxy plan rows by visible text only. That made the final native verification depend on labels or panel position instead of durable leaf identifiers.</x:v>
+        <x:v>MediaPanel rendered these controls only by label. That made NSOpenPanel and source-map-root relink proof depend on localized text or positions rather than stable leaf identifiers.</x:v>
       </x:c>
       <x:c r="G68" s="26" t="str">
-        <x:v>Added stable MediaPanel identifiers for synthetic status/build, studio smoke status/run, acceptance smoke status/run, proxy operation status/build, proxy empty state, and proxy plan items keyed by asset id.</x:v>
+        <x:v>Added MediaPanel.MediaRelinkStatus, MediaPanel.RelinkMissingMediaButton, MediaPanel.UseSourceMapRootsButton, and MediaPanel.ReplaceSyntheticMediaButton while keeping the identifiers on actionable leaf controls.</x:v>
       </x:c>
       <x:c r="H68" s="26" t="str">
-        <x:v>Computer-use exposed the new identifiers, clicked Build Demo Media on us060-native-synthetic-smoke-20260623 and observed Built 1, skipped 0, mapped 1, clicked Build Proxies on us060-native-proxy-smoke-20260623 and observed Built 1 preview proxies, and clicked Run Studio Smoke until it reported Synthetic studio smoke passed. CLI media-status/source-map/proxy-plan and ffprobe confirmed ready media, coverage 1/1, pending=0, and valid H.264/AAC outputs. Focused Swift smoke/resolver tests 30/0, swift build --target VideoOSStudio, build_and_run --verify, and diff check passed.</x:v>
+        <x:v>On a disposable us059-native-relink-smoke project, computer-use exposed all four identifiers, opened the Relink Missing Media NSOpenPanel, observed cancellation, clicked Use Source Map Roots, and saw MediaRelinkStatus change to Relinked 1 files with 0 missing. CLI media-status and media-source-map-status confirmed ready=1/missing=0, coverage 1/1, and one relinked symlink. ProjectMediaResolverTests 25/0, swift build --target VideoOSStudio, build_and_run --verify, and diff check passed.</x:v>
       </x:c>
       <x:c r="I68" s="11" t="str">
         <x:v>Fixed</x:v>
@@ -4285,10 +4285,10 @@
     </x:row>
     <x:row r="69" ht="48" customHeight="1">
       <x:c r="A69" s="10" t="str">
-        <x:v>ISS-068</x:v>
+        <x:v>ISS-067</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>US-046</x:v>
+        <x:v>US-060</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
         <x:v>Medium</x:v>
@@ -4297,16 +4297,16 @@
         <x:v>macOS UX/testability</x:v>
       </x:c>
       <x:c r="E69" s="26" t="str">
-        <x:v>New Project creation could only be proven through visible labels and last Finder state, making the native NSOpenPanel path fragile.</x:v>
+        <x:v>Synthetic demo media, smoke, and proxy controls were runnable, but their MediaPanel controls could not be targeted repeatably by native automation.</x:v>
       </x:c>
       <x:c r="F69" s="26" t="str">
-        <x:v>The project ID alert used plain AppKit controls without stable accessibility identifiers, the source-folder panel inherited the user's last Finder location, and the Project creation row used LabeledContent that was easy to collapse in AX output.</x:v>
+        <x:v>The Synthetic Demo Media and Proxy Transcode Plan sections rendered status text, action buttons, proxy empty state, and proxy plan rows by visible text only. That made the final native verification depend on labels or panel position instead of durable leaf identifiers.</x:v>
       </x:c>
       <x:c r="G69" s="26" t="str">
-        <x:v>Added ProjectInitializer.ProjectIDField/CreateButton/CancelButton, defaulted the source-folder NSOpenPanel to the repository root, and rendered Project creation as explicit status text in the Project State section.</x:v>
+        <x:v>Added stable MediaPanel identifiers for synthetic status/build, studio smoke status/run, acceptance smoke status/run, proxy operation status/build, proxy empty state, and proxy plan items keyed by asset id.</x:v>
       </x:c>
       <x:c r="H69" s="26" t="str">
-        <x:v>Computer-use exposed the new alert identifiers, opened Choose Source Media Folder from the repo root, selected us046-native-source-20260623, and created us046-native-create-20260623. The shelf showed ProjectShelf.us046-native-create-20260623 intent_pending, the Project tab showed Project creation: Created us046-native-create-20260623 and linked source media, project_state.yaml recorded current_state=intent_pending, 02_media/source linked to the selected source folder, and ffprobe confirmed the linked H.264/AAC source clip.</x:v>
+        <x:v>Computer-use exposed the new identifiers, clicked Build Demo Media on us060-native-synthetic-smoke-20260623 and observed Built 1, skipped 0, mapped 1, clicked Build Proxies on us060-native-proxy-smoke-20260623 and observed Built 1 preview proxies, and clicked Run Studio Smoke until it reported Synthetic studio smoke passed. CLI media-status/source-map/proxy-plan and ffprobe confirmed ready media, coverage 1/1, pending=0, and valid H.264/AAC outputs. Focused Swift smoke/resolver tests 30/0, swift build --target VideoOSStudio, build_and_run --verify, and diff check passed.</x:v>
       </x:c>
       <x:c r="I69" s="11" t="str">
         <x:v>Fixed</x:v>
@@ -4314,10 +4314,10 @@
     </x:row>
     <x:row r="70" ht="48" customHeight="1">
       <x:c r="A70" s="10" t="str">
-        <x:v>ISS-069</x:v>
+        <x:v>ISS-068</x:v>
       </x:c>
       <x:c r="B70" s="26" t="str">
-        <x:v>US-050</x:v>
+        <x:v>US-046</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
         <x:v>Medium</x:v>
@@ -4326,47 +4326,76 @@
         <x:v>macOS UX/testability</x:v>
       </x:c>
       <x:c r="E70" s="26" t="str">
-        <x:v>Action Queue Run/Copy actions were visible, but individual actions were not safely targetable through native automation.</x:v>
+        <x:v>New Project creation could only be proven through visible labels and last Finder state, making the native NSOpenPanel path fragile.</x:v>
       </x:c>
       <x:c r="F70" s="26" t="str">
-        <x:v>The Action Queue status, command text, Run, and Copy leaf controls lacked action-scoped accessibility identifiers, so repeatable tests depended on labels or row position and risked pressing the wrong advisory or workspace-write action.</x:v>
+        <x:v>The project ID alert used plain AppKit controls without stable accessibility identifiers, the source-folder panel inherited the user's last Finder location, and the Project creation row used LabeledContent that was easy to collapse in AX output.</x:v>
       </x:c>
       <x:c r="G70" s="26" t="str">
-        <x:v>Added ProjectPanel.ActionQueueStatus, ProjectPanel.ActionQueueCommand.&lt;id&gt;, ProjectPanel.ActionQueueRunButton.&lt;id&gt;, and ProjectPanel.ActionQueueCopyButton.&lt;id&gt; on leaf controls.</x:v>
+        <x:v>Added ProjectInitializer.ProjectIDField/CreateButton/CancelButton, defaulted the source-folder NSOpenPanel to the repository root, and rendered Project creation as explicit status text in the Project State section.</x:v>
       </x:c>
       <x:c r="H70" s="26" t="str">
-        <x:v>computer-use exposed rough-cut-review and marlin-default Run/Copy identifiers; clicking ProjectPanel.ActionQueueRunButton.rough-cut-review changed the status from Starting Codex session for Review... to Opening Codex approval gate for Review. git status listed only the intentional ProjectInspectorViews.swift edit, and the AX-1 review folder still contained only human_notes.yaml. swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed.</x:v>
+        <x:v>Computer-use exposed the new alert identifiers, opened Choose Source Media Folder from the repo root, selected us046-native-source-20260623, and created us046-native-create-20260623. The shelf showed ProjectShelf.us046-native-create-20260623 intent_pending, the Project tab showed Project creation: Created us046-native-create-20260623 and linked source media, project_state.yaml recorded current_state=intent_pending, 02_media/source linked to the selected source folder, and ffprobe confirmed the linked H.264/AAC source clip.</x:v>
       </x:c>
       <x:c r="I70" s="11" t="str">
         <x:v>Fixed</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="48" customHeight="1">
-      <x:c r="A71" s="12" t="str">
+      <x:c r="A71" s="10" t="str">
+        <x:v>ISS-069</x:v>
+      </x:c>
+      <x:c r="B71" s="26" t="str">
+        <x:v>US-050</x:v>
+      </x:c>
+      <x:c r="C71" s="26" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="D71" s="26" t="str">
+        <x:v>macOS UX/testability</x:v>
+      </x:c>
+      <x:c r="E71" s="26" t="str">
+        <x:v>Action Queue Run/Copy actions were visible, but individual actions were not safely targetable through native automation.</x:v>
+      </x:c>
+      <x:c r="F71" s="26" t="str">
+        <x:v>The Action Queue status, command text, Run, and Copy leaf controls lacked action-scoped accessibility identifiers, so repeatable tests depended on labels or row position and risked pressing the wrong advisory or workspace-write action.</x:v>
+      </x:c>
+      <x:c r="G71" s="26" t="str">
+        <x:v>Added ProjectPanel.ActionQueueStatus, ProjectPanel.ActionQueueCommand.&lt;id&gt;, ProjectPanel.ActionQueueRunButton.&lt;id&gt;, and ProjectPanel.ActionQueueCopyButton.&lt;id&gt; on leaf controls.</x:v>
+      </x:c>
+      <x:c r="H71" s="26" t="str">
+        <x:v>computer-use exposed rough-cut-review and marlin-default Run/Copy identifiers; clicking ProjectPanel.ActionQueueRunButton.rough-cut-review changed the status from Starting Codex session for Review... to Opening Codex approval gate for Review. git status listed only the intentional ProjectInspectorViews.swift edit, and the AX-1 review folder still contained only human_notes.yaml. swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed.</x:v>
+      </x:c>
+      <x:c r="I71" s="11" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="48" customHeight="1">
+      <x:c r="A72" s="12" t="str">
         <x:v>ISS-070</x:v>
       </x:c>
-      <x:c r="B71" s="27" t="str">
+      <x:c r="B72" s="27" t="str">
         <x:v>US-065</x:v>
       </x:c>
-      <x:c r="C71" s="27" t="str">
+      <x:c r="C72" s="27" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="D71" s="27" t="str">
+      <x:c r="D72" s="27" t="str">
         <x:v>macOS UX/testability</x:v>
       </x:c>
-      <x:c r="E71" s="27" t="str">
+      <x:c r="E72" s="27" t="str">
         <x:v>Switching inspector tabs through Computer Use after adding RAG context could leave VideoOSStudio busy and unreachable to accessibility automation.</x:v>
       </x:c>
-      <x:c r="F71" s="27" t="str">
+      <x:c r="F72" s="27" t="str">
         <x:v>InspectorPanel used SwiftUI TabView, which exposed the tab strip as an AppKit NSSegmentedCell. In the RAG Search/Add flow, pressing the Agent segment entered the AX perform-action path and did not return, leaving Computer Use with noWindowsAvailable/timeouts and the app process around 98.8% CPU.</x:v>
       </x:c>
-      <x:c r="G71" s="27" t="str">
+      <x:c r="G72" s="27" t="str">
         <x:v>Replaced the inspector TabView with explicit SwiftUI Button tabs keyed as InspectorTab.Agent, InspectorTab.Project, InspectorTab.Clip, InspectorTab.Media, and InspectorTab.QA. The selected panel content is unchanged, but tab changes now avoid the segmented-cell AXPress path and expose stable tab identifiers.</x:v>
       </x:c>
-      <x:c r="H71" s="27" t="str">
+      <x:c r="H72" s="27" t="str">
         <x:v>Before the fix, PID 95918 stayed around 98.8% CPU and sample showed the main thread inside NSSegmentedCell _performClick after clicking Agent; /tmp/videoos-us065-rag-after-agent-click.png captured the app stuck on Media after Add RAG Context. After the fix, build_and_run --verify launched PID 9971; Computer Use exposed InspectorTab.* buttons, selected Media, searched 参加, added 3 cited RAG items, selected Agent, confirmed the prompt contained Material RAG context for query `参加`, and ps reported 0.0% CPU.</x:v>
       </x:c>
-      <x:c r="I71" s="13" t="str">
+      <x:c r="I72" s="13" t="str">
         <x:v>Fixed</x:v>
       </x:c>
     </x:row>
@@ -8589,79 +8618,79 @@
     </x:row>
     <x:row r="211" ht="48" customHeight="1">
       <x:c r="A211" s="10" t="str">
-        <x:v>TL-205</x:v>
+        <x:v>TL-237</x:v>
       </x:c>
       <x:c r="B211" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C211" s="26" t="str">
-        <x:v>Native preview duration fallback</x:v>
+        <x:v>Live Marlin chunks on lively-alt-vol5</x:v>
       </x:c>
       <x:c r="D211" s="26" t="str">
-        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
+        <x:v>Fix source_map-aware Marlin asset/source resolution, run live non-mock chunks for 08-jun-a-man-and-a.mp4 and 06-jun-two-people-are.mp4 on the real lively-alt-vol5 project, rebuild the SQLite index, and inspect preference status.</x:v>
       </x:c>
       <x:c r="E211" s="26" t="str">
-        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
+        <x:v>loadMarlinAssetInputs now uses 02_media/source_map.json before indexed source fallbacks, so linked source names map to the correct asset IDs when assets.json stores original camera filenames. npx vitest run tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts passed 12 tests, npx tsc --noEmit --pretty false passed, and node --check scripts/marlin-evaluate.ts passed. Live runs with VOS_MARLIN_PROXY_MAX_WIDTH=384 and --request-timeout-ms 900000 completed for AST_5CAEC24E / 08-jun-a-man-and-a.mp4 and AST_25CDF4A5 / 06-jun-two-people-are.mp4. marlin_events.json now has 2 assets, 13 events, and 8 find results; segments.json has marlin_reporter summary provenance and marlin_temporal_semantics peak provenance for both assets; index-rebuild reports 13 marlinEvents, 8 marlinFindResults, and 2354 searchDocuments. marlin-status reports coverage=0.22 and canPreferMarlin=false; marlin-preference-status remains partially ready with lively-alt-vol5 at 2/9 peak segments, so the default preference gate stays blocked.</x:v>
       </x:c>
       <x:c r="F211" s="11" t="str">
-        <x:v>Native pixel/runtime pass</x:v>
+        <x:v>Live 2/9 representative progress; preference gate pending</x:v>
       </x:c>
     </x:row>
     <x:row r="212" ht="48" customHeight="1">
       <x:c r="A212" s="10" t="str">
-        <x:v>TL-206</x:v>
+        <x:v>TL-205</x:v>
       </x:c>
       <x:c r="B212" s="26" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C212" s="26" t="str">
-        <x:v>Native Clip Inspector save and clear</x:v>
+        <x:v>Native preview duration fallback</x:v>
       </x:c>
       <x:c r="D212" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
+        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
       </x:c>
       <x:c r="E212" s="26" t="str">
-        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
+        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F212" s="11" t="str">
-        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
+        <x:v>Native pixel/runtime pass</x:v>
       </x:c>
     </x:row>
     <x:row r="213" ht="48" customHeight="1">
       <x:c r="A213" s="10" t="str">
-        <x:v>TL-207</x:v>
+        <x:v>TL-206</x:v>
       </x:c>
       <x:c r="B213" s="26" t="str">
-        <x:v>US-058</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C213" s="26" t="str">
-        <x:v>Native QA Dashboard issue jump</x:v>
+        <x:v>Native Clip Inspector save and clear</x:v>
       </x:c>
       <x:c r="D213" s="26" t="str">
-        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
+        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
       </x:c>
       <x:c r="E213" s="26" t="str">
-        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
+        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
       </x:c>
       <x:c r="F213" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
       </x:c>
     </x:row>
     <x:row r="214" ht="48" customHeight="1">
       <x:c r="A214" s="10" t="str">
-        <x:v>TL-208</x:v>
+        <x:v>TL-207</x:v>
       </x:c>
       <x:c r="B214" s="26" t="str">
-        <x:v>US-056</x:v>
+        <x:v>US-058</x:v>
       </x:c>
       <x:c r="C214" s="26" t="str">
-        <x:v>Native Candidate Swap sheet and staging</x:v>
+        <x:v>Native QA Dashboard issue jump</x:v>
       </x:c>
       <x:c r="D214" s="26" t="str">
-        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
+        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
       </x:c>
       <x:c r="E214" s="26" t="str">
-        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
+        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
       </x:c>
       <x:c r="F214" s="11" t="str">
         <x:v>Native AX/pixel pass</x:v>
@@ -8669,339 +8698,339 @@
     </x:row>
     <x:row r="215" ht="48" customHeight="1">
       <x:c r="A215" s="10" t="str">
-        <x:v>TL-209</x:v>
+        <x:v>TL-208</x:v>
       </x:c>
       <x:c r="B215" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-056</x:v>
       </x:c>
       <x:c r="C215" s="26" t="str">
-        <x:v>Native exact preview regeneration</x:v>
+        <x:v>Native Candidate Swap sheet and staging</x:v>
       </x:c>
       <x:c r="D215" s="26" t="str">
-        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
+        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
       </x:c>
       <x:c r="E215" s="26" t="str">
-        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
       </x:c>
       <x:c r="F215" s="11" t="str">
-        <x:v>Native exact preview pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="48" customHeight="1">
       <x:c r="A216" s="10" t="str">
-        <x:v>TL-210</x:v>
+        <x:v>TL-209</x:v>
       </x:c>
       <x:c r="B216" s="26" t="str">
-        <x:v>US-047</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C216" s="26" t="str">
-        <x:v>Native Command Palette top-bar open/close</x:v>
+        <x:v>Native exact preview regeneration</x:v>
       </x:c>
       <x:c r="D216" s="26" t="str">
-        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
+        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
       </x:c>
       <x:c r="E216" s="26" t="str">
-        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
+        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F216" s="11" t="str">
-        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
+        <x:v>Native exact preview pass</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="48" customHeight="1">
       <x:c r="A217" s="10" t="str">
-        <x:v>TL-211</x:v>
+        <x:v>TL-210</x:v>
       </x:c>
       <x:c r="B217" s="26" t="str">
         <x:v>US-047</x:v>
       </x:c>
       <x:c r="C217" s="26" t="str">
-        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
+        <x:v>Native Command Palette top-bar open/close</x:v>
       </x:c>
       <x:c r="D217" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
+        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
       </x:c>
       <x:c r="E217" s="26" t="str">
-        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
+        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
       </x:c>
       <x:c r="F217" s="11" t="str">
-        <x:v>Native keyboard/AX pass</x:v>
+        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="48" customHeight="1">
       <x:c r="A218" s="10" t="str">
-        <x:v>TL-212</x:v>
+        <x:v>TL-211</x:v>
       </x:c>
       <x:c r="B218" s="26" t="str">
-        <x:v>US-048</x:v>
+        <x:v>US-047</x:v>
       </x:c>
       <x:c r="C218" s="26" t="str">
-        <x:v>Native Agent panel session lifecycle</x:v>
+        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
       </x:c>
       <x:c r="D218" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
+        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
       </x:c>
       <x:c r="E218" s="26" t="str">
-        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
+        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
       </x:c>
       <x:c r="F218" s="11" t="str">
-        <x:v>Native AX/computer-use pass</x:v>
+        <x:v>Native keyboard/AX pass</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="48" customHeight="1">
       <x:c r="A219" s="10" t="str">
-        <x:v>TL-213</x:v>
+        <x:v>TL-212</x:v>
       </x:c>
       <x:c r="B219" s="26" t="str">
-        <x:v>US-049</x:v>
+        <x:v>US-048</x:v>
       </x:c>
       <x:c r="C219" s="26" t="str">
-        <x:v>Native Status agent job read-only turn</x:v>
+        <x:v>Native Agent panel session lifecycle</x:v>
       </x:c>
       <x:c r="D219" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
       </x:c>
       <x:c r="E219" s="26" t="str">
-        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
+        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F219" s="11" t="str">
-        <x:v>Native read-only job pass; approved write pending</x:v>
+        <x:v>Native AX/computer-use pass</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="48" customHeight="1">
       <x:c r="A220" s="10" t="str">
-        <x:v>TL-214</x:v>
+        <x:v>TL-213</x:v>
       </x:c>
       <x:c r="B220" s="26" t="str">
-        <x:v>US-050</x:v>
+        <x:v>US-049</x:v>
       </x:c>
       <x:c r="C220" s="26" t="str">
-        <x:v>Native Project readiness/action queue Copy pass</x:v>
+        <x:v>Native Status agent job read-only turn</x:v>
       </x:c>
       <x:c r="D220" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
       </x:c>
       <x:c r="E220" s="26" t="str">
-        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
+        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F220" s="11" t="str">
-        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
+        <x:v>Native read-only job pass; approved write pending</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="48" customHeight="1">
       <x:c r="A221" s="10" t="str">
-        <x:v>TL-215</x:v>
+        <x:v>TL-214</x:v>
       </x:c>
       <x:c r="B221" s="26" t="str">
-        <x:v>US-051</x:v>
+        <x:v>US-050</x:v>
       </x:c>
       <x:c r="C221" s="26" t="str">
-        <x:v>Native local Source Analysis button</x:v>
+        <x:v>Native Project readiness/action queue Copy pass</x:v>
       </x:c>
       <x:c r="D221" s="26" t="str">
-        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
       </x:c>
       <x:c r="E221" s="26" t="str">
-        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
+        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
       </x:c>
       <x:c r="F221" s="11" t="str">
-        <x:v>Native local analysis pass</x:v>
+        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="48" customHeight="1">
       <x:c r="A222" s="10" t="str">
-        <x:v>TL-216</x:v>
+        <x:v>TL-215</x:v>
       </x:c>
       <x:c r="B222" s="26" t="str">
-        <x:v>US-052</x:v>
+        <x:v>US-051</x:v>
       </x:c>
       <x:c r="C222" s="26" t="str">
-        <x:v>Native Rough Cut and Review Patch buttons</x:v>
+        <x:v>Native local Source Analysis button</x:v>
       </x:c>
       <x:c r="D222" s="26" t="str">
-        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
+        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E222" s="26" t="str">
-        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
       </x:c>
       <x:c r="F222" s="11" t="str">
-        <x:v>Native compile/review patch pass</x:v>
+        <x:v>Native local analysis pass</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="48" customHeight="1">
       <x:c r="A223" s="10" t="str">
-        <x:v>TL-217</x:v>
+        <x:v>TL-216</x:v>
       </x:c>
       <x:c r="B223" s="26" t="str">
-        <x:v>US-053</x:v>
+        <x:v>US-052</x:v>
       </x:c>
       <x:c r="C223" s="26" t="str">
-        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
+        <x:v>Native Rough Cut and Review Patch buttons</x:v>
       </x:c>
       <x:c r="D223" s="26" t="str">
-        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
+        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E223" s="26" t="str">
-        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
+        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F223" s="11" t="str">
-        <x:v>Native timeline/context menu pass</x:v>
+        <x:v>Native compile/review patch pass</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="48" customHeight="1">
       <x:c r="A224" s="10" t="str">
-        <x:v>TL-218</x:v>
+        <x:v>TL-217</x:v>
       </x:c>
       <x:c r="B224" s="26" t="str">
-        <x:v>US-054</x:v>
+        <x:v>US-053</x:v>
       </x:c>
       <x:c r="C224" s="26" t="str">
-        <x:v>Native Studio feedback Apply and Undo</x:v>
+        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
       </x:c>
       <x:c r="D224" s="26" t="str">
-        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
+        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
       </x:c>
       <x:c r="E224" s="26" t="str">
-        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
       </x:c>
       <x:c r="F224" s="11" t="str">
-        <x:v>Native apply/undo pass</x:v>
+        <x:v>Native timeline/context menu pass</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="48" customHeight="1">
       <x:c r="A225" s="10" t="str">
-        <x:v>TL-219</x:v>
+        <x:v>TL-218</x:v>
       </x:c>
       <x:c r="B225" s="26" t="str">
-        <x:v>US-057</x:v>
+        <x:v>US-054</x:v>
       </x:c>
       <x:c r="C225" s="26" t="str">
-        <x:v>Native Footage Search sheet and replacement staging</x:v>
+        <x:v>Native Studio feedback Apply and Undo</x:v>
       </x:c>
       <x:c r="D225" s="26" t="str">
-        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
+        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E225" s="26" t="str">
-        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
+        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F225" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native apply/undo pass</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="48" customHeight="1">
       <x:c r="A226" s="10" t="str">
-        <x:v>TL-220</x:v>
+        <x:v>TL-219</x:v>
       </x:c>
       <x:c r="B226" s="26" t="str">
-        <x:v>US-066</x:v>
+        <x:v>US-057</x:v>
       </x:c>
       <x:c r="C226" s="26" t="str">
-        <x:v>Native Settings transport picker mutation</x:v>
+        <x:v>Native Footage Search sheet and replacement staging</x:v>
       </x:c>
       <x:c r="D226" s="26" t="str">
-        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
+        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
       </x:c>
       <x:c r="E226" s="26" t="str">
-        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
       </x:c>
       <x:c r="F226" s="11" t="str">
-        <x:v>Native Settings picker mutation pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="48" customHeight="1">
       <x:c r="A227" s="10" t="str">
-        <x:v>TL-221</x:v>
+        <x:v>TL-220</x:v>
       </x:c>
       <x:c r="B227" s="26" t="str">
-        <x:v>US-059</x:v>
+        <x:v>US-066</x:v>
       </x:c>
       <x:c r="C227" s="26" t="str">
-        <x:v>Native Media Relink buttons and source-map relink</x:v>
+        <x:v>Native Settings transport picker mutation</x:v>
       </x:c>
       <x:c r="D227" s="26" t="str">
-        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
+        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
       </x:c>
       <x:c r="E227" s="26" t="str">
-        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
+        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F227" s="11" t="str">
-        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
+        <x:v>Native Settings picker mutation pass</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="48" customHeight="1">
       <x:c r="A228" s="10" t="str">
-        <x:v>TL-222</x:v>
+        <x:v>TL-221</x:v>
       </x:c>
       <x:c r="B228" s="26" t="str">
-        <x:v>US-060</x:v>
+        <x:v>US-059</x:v>
       </x:c>
       <x:c r="C228" s="26" t="str">
-        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
+        <x:v>Native Media Relink buttons and source-map relink</x:v>
       </x:c>
       <x:c r="D228" s="26" t="str">
-        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
+        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
       </x:c>
       <x:c r="E228" s="26" t="str">
-        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
+        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
       </x:c>
       <x:c r="F228" s="11" t="str">
-        <x:v>Native synthetic/proxy/smoke button pass</x:v>
+        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="48" customHeight="1">
       <x:c r="A229" s="10" t="str">
-        <x:v>TL-223</x:v>
+        <x:v>TL-222</x:v>
       </x:c>
       <x:c r="B229" s="26" t="str">
-        <x:v>US-046</x:v>
+        <x:v>US-060</x:v>
       </x:c>
       <x:c r="C229" s="26" t="str">
-        <x:v>Native New Project from Source</x:v>
+        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
       </x:c>
       <x:c r="D229" s="26" t="str">
-        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
+        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
       </x:c>
       <x:c r="E229" s="26" t="str">
-        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
+        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
       </x:c>
       <x:c r="F229" s="11" t="str">
-        <x:v>Native project creation/NSOpenPanel pass</x:v>
+        <x:v>Native synthetic/proxy/smoke button pass</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="48" customHeight="1">
       <x:c r="A230" s="10" t="str">
-        <x:v>TL-224</x:v>
+        <x:v>TL-223</x:v>
       </x:c>
       <x:c r="B230" s="26" t="str">
-        <x:v>US-062</x:v>
+        <x:v>US-046</x:v>
       </x:c>
       <x:c r="C230" s="26" t="str">
-        <x:v>Native MediaPanel Audio Story Graph button</x:v>
+        <x:v>Native New Project from Source</x:v>
       </x:c>
       <x:c r="D230" s="26" t="str">
-        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
+        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
       </x:c>
       <x:c r="E230" s="26" t="str">
-        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
       </x:c>
       <x:c r="F230" s="11" t="str">
-        <x:v>Native AX/UI/CLI pass</x:v>
+        <x:v>Native project creation/NSOpenPanel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="48" customHeight="1">
       <x:c r="A231" s="10" t="str">
-        <x:v>TL-225</x:v>
+        <x:v>TL-224</x:v>
       </x:c>
       <x:c r="B231" s="26" t="str">
-        <x:v>US-063</x:v>
+        <x:v>US-062</x:v>
       </x:c>
       <x:c r="C231" s="26" t="str">
-        <x:v>Native Render Final Package button</x:v>
+        <x:v>Native MediaPanel Audio Story Graph button</x:v>
       </x:c>
       <x:c r="D231" s="26" t="str">
-        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
+        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E231" s="26" t="str">
-        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F231" s="11" t="str">
         <x:v>Native AX/UI/CLI pass</x:v>
@@ -9009,121 +9038,141 @@
     </x:row>
     <x:row r="232" ht="48" customHeight="1">
       <x:c r="A232" s="10" t="str">
-        <x:v>TL-226</x:v>
+        <x:v>TL-225</x:v>
       </x:c>
       <x:c r="B232" s="26" t="str">
-        <x:v>US-064</x:v>
+        <x:v>US-063</x:v>
       </x:c>
       <x:c r="C232" s="26" t="str">
-        <x:v>Native Editor Handoff export and Finder reveal</x:v>
+        <x:v>Native Render Final Package button</x:v>
       </x:c>
       <x:c r="D232" s="26" t="str">
-        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
+        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
       </x:c>
       <x:c r="E232" s="26" t="str">
-        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
+        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F232" s="11" t="str">
-        <x:v>Native AX/UI/Finder/CLI pass</x:v>
+        <x:v>Native AX/UI/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="48" customHeight="1">
       <x:c r="A233" s="10" t="str">
-        <x:v>TL-227</x:v>
+        <x:v>TL-226</x:v>
       </x:c>
       <x:c r="B233" s="26" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-064</x:v>
       </x:c>
       <x:c r="C233" s="26" t="str">
-        <x:v>Native Ask Codex editor-note proposal</x:v>
+        <x:v>Native Editor Handoff export and Finder reveal</x:v>
       </x:c>
       <x:c r="D233" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
+        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E233" s="26" t="str">
-        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
+        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
       </x:c>
       <x:c r="F233" s="11" t="str">
-        <x:v>Native read-only Codex proposal pass</x:v>
+        <x:v>Native AX/UI/Finder/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="48" customHeight="1">
       <x:c r="A234" s="10" t="str">
-        <x:v>TL-228</x:v>
+        <x:v>TL-227</x:v>
       </x:c>
       <x:c r="B234" s="26" t="str">
-        <x:v>US-061</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C234" s="26" t="str">
-        <x:v>Live Marlin single-source completion</x:v>
+        <x:v>Native Ask Codex editor-note proposal</x:v>
       </x:c>
       <x:c r="D234" s="26" t="str">
-        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
+        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
       </x:c>
       <x:c r="E234" s="26" t="str">
-        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
+        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
       </x:c>
       <x:c r="F234" s="11" t="str">
-        <x:v>Live single-source pass; full representative batch pending</x:v>
+        <x:v>Native read-only Codex proposal pass</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="48" customHeight="1">
       <x:c r="A235" s="10" t="str">
-        <x:v>TL-229</x:v>
+        <x:v>TL-228</x:v>
       </x:c>
       <x:c r="B235" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C235" s="26" t="str">
-        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+        <x:v>Live Marlin single-source completion</x:v>
       </x:c>
       <x:c r="D235" s="26" t="str">
-        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
       </x:c>
       <x:c r="E235" s="26" t="str">
-        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
       </x:c>
       <x:c r="F235" s="11" t="str">
-        <x:v>Native fresh-launch pixel pass</x:v>
+        <x:v>Live single-source pass; full representative batch pending</x:v>
       </x:c>
     </x:row>
     <x:row r="236" ht="48" customHeight="1">
       <x:c r="A236" s="10" t="str">
-        <x:v>TL-230</x:v>
+        <x:v>TL-229</x:v>
       </x:c>
       <x:c r="B236" s="26" t="str">
         <x:v>US-045</x:v>
       </x:c>
       <x:c r="C236" s="26" t="str">
+        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+      </x:c>
+      <x:c r="D236" s="26" t="str">
+        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+      </x:c>
+      <x:c r="E236" s="26" t="str">
+        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+      </x:c>
+      <x:c r="F236" s="11" t="str">
+        <x:v>Native fresh-launch pixel pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" ht="48" customHeight="1">
+      <x:c r="A237" s="10" t="str">
+        <x:v>TL-230</x:v>
+      </x:c>
+      <x:c r="B237" s="26" t="str">
+        <x:v>US-045</x:v>
+      </x:c>
+      <x:c r="C237" s="26" t="str">
         <x:v>AX-1 exact preview promotion and pixel pass</x:v>
       </x:c>
-      <x:c r="D236" s="26" t="str">
+      <x:c r="D237" s="26" t="str">
         <x:v>Run videoos-studio-cli compile-run on projects/ax1-participant-voices-20260401, confirm playback-contract-status, select ProjectShelf.ax1-participant-voices-20260401 in VideoOSStudio, capture /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and run Retina-coordinate pixel statistics on the Viewer region.</x:v>
       </x:c>
-      <x:c r="E236" s="26" t="str">
+      <x:c r="E237" s="26" t="str">
         <x:v>Before compile, playback-contract-status returned legacy_manifest and approvalGrade=false. compile-run completed with exitCode=0, timeline compiled, indexDocuments=492, and git status stayed clean. After compile, playback-contract-status returned state=exact, approvalGrade=true, timelineHash=171378fe2bfe3a7c, and manifestBaseTimelineHash=171378fe2bfe3a7c. Native Viewer showed Exact preview / preview-editor-1775121573933.mp4 and Timeline preview D4887.MP4 with a visible interview frame. Screenshot was 3.5M; viewer_person_actual mean_rgb=(144.62,141.42,149.8) and near_black_pct=0.0004, while left pillarbox near_black_pct=1.0000 as expected.</x:v>
       </x:c>
-      <x:c r="F236" s="11" t="str">
+      <x:c r="F237" s="11" t="str">
         <x:v>Native AX-1 exact/pixel pass</x:v>
       </x:c>
     </x:row>
-    <x:row r="237" ht="48" customHeight="1">
-      <x:c r="A237" s="12" t="str">
+    <x:row r="238" ht="48" customHeight="1">
+      <x:c r="A238" s="12" t="str">
         <x:v>TL-231</x:v>
       </x:c>
-      <x:c r="B237" s="27" t="str">
+      <x:c r="B238" s="27" t="str">
         <x:v>US-050</x:v>
       </x:c>
-      <x:c r="C237" s="27" t="str">
+      <x:c r="C238" s="27" t="str">
         <x:v>Native Action Queue approval gate</x:v>
       </x:c>
-      <x:c r="D237" s="27" t="str">
+      <x:c r="D238" s="27" t="str">
         <x:v>Add ProjectPanel.ActionQueue* identifiers, relaunch VideoOSStudio, select AX-1 Project tab, inspect the Action Queue AX tree, click ProjectPanel.ActionQueueRunButton.rough-cut-review, and stop at the Codex approval gate without approving writes.</x:v>
       </x:c>
-      <x:c r="E237" s="27" t="str">
+      <x:c r="E238" s="27" t="str">
         <x:v>AX exposed ProjectPanel.ActionQueueRunButton.rough-cut-review, ProjectPanel.ActionQueueCopyButton.rough-cut-review, ProjectPanel.ActionQueueRunButton.marlin-default, and ProjectPanel.ActionQueueCopyButton.marlin-default. Clicking rough-cut-review changed the row to disabled Starting Codex session for Review..., then to Opening Codex approval gate for Review. ps showed a Codex app-server child under VideoOSStudio; git status listed only the intentional ProjectInspectorViews.swift edit, and projects/ax1-participant-voices-20260401/06_review still contained only human_notes.yaml.</x:v>
       </x:c>
-      <x:c r="F237" s="13" t="str">
+      <x:c r="F238" s="13" t="str">
         <x:v>Native approval-gate pass; write not approved</x:v>
       </x:c>
     </x:row>
@@ -9630,10 +9679,10 @@
         <x:v>macOS Marlin and audio graph</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:21-160; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1296-1325,2326-2604; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRuntimeStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinModelAccessStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationQueue.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRepresentativePlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationRunPlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinPreferenceDecision.swift; runtime/pipeline/stages/marlin.ts; scripts/marlin-evaluate.ts; apps/macos-studio/Sources/VideoOSStudioCore/ProjectAudioStoryGraphRunPlan.swift; scripts/build-audio-story-graph.ts; runtime/artifacts/audio-story-project-builder.ts; runtime/artifacts/p2-audio-story-graph.ts; apps/macos-studio/Sources/VideoOSStudioCore/ProjectSQLiteIndex.swift:400-452</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:21-160; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1296-1325,2326-2604; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRuntimeStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinModelAccessStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationQueue.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRepresentativePlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationRunPlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinPreferenceDecision.swift; runtime/pipeline/stages/marlin.ts; runtime/media/source-map.ts; scripts/marlin-evaluate.ts; apps/macos-studio/Sources/VideoOSStudioCore/ProjectAudioStoryGraphRunPlan.swift; scripts/build-audio-story-graph.ts; runtime/artifacts/audio-story-project-builder.ts; runtime/artifacts/p2-audio-story-graph.ts; apps/macos-studio/Sources/VideoOSStudioCore/ProjectSQLiteIndex.swift:400-452</x:v>
       </x:c>
       <x:c r="C45" s="11" t="str">
-        <x:v>Marlin runtime dependency checks, Hugging Face gated-model access checks, project evaluation status, representative queue/buckets, run-plan source selection, mock/live evaluation runner with SQLite index refresh, resumable per-asset checkpointing, --max-sources/--skip-existing chunk controls, preference gate/apply guard, stable Marlin MediaPanel accessibility identifiers, and audio story graph command readiness/runtime execution. Audio story graph builds transcript utterance, audio event, and BGM music_section nodes, writes 03_analysis/audio_story_graph.json, and indexes audio_story_node search documents after success.</x:v>
+        <x:v>Marlin runtime dependency checks, Hugging Face gated-model access checks, project evaluation status, representative queue/buckets, source-map-aware asset/source resolution, run-plan source selection, mock/live evaluation runner with SQLite index refresh, resumable per-asset checkpointing, --max-sources/--skip-existing chunk controls, preference gate/apply guard, stable Marlin MediaPanel accessibility identifiers, and audio story graph command readiness/runtime execution. Audio story graph builds transcript utterance, audio event, and BGM music_section nodes, writes 03_analysis/audio_story_graph.json, and indexes audio_story_node search documents after success.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="48" customHeight="1">

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R200a2e9ec4cf4239"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R38902b8e973b4fa4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R94ce5680c9f7438a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="Rfa40f7c83daa44f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Rbb93904782b442d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5f98742d35bc4fc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rb526ce3bf01e4e2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Rdab4f702d6b243f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R52183fc705304854"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R72c3b332f7dc497a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -439,7 +439,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 18:53 JST</x:v>
+        <x:v>2026-06-23 20:32 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -487,7 +487,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build changes the Marlin evaluation input resolver so loadMarlinAssetInputs uses 02_media/source_map.json before indexed source fallbacks, preserving correct asset IDs when assets.json stores original camera filenames and operators pass linked media paths. The previous build made runMarlinAnalysis write per-asset checkpoints, added --max-sources/--skip-existing to scripts/marlin-evaluate.ts, and threaded those chunk controls through ProjectMarlinEvaluationRunPlan/Runner plus marlin-eval-plan/eval-next/eval-run. Prior native builds include ProjectMarlinRuntimeStatusReader isolated dependency probes, InspectorTab.Agent/Project/Clip/Media/QA buttons for US-065, ProjectPanel.ActionQueueStatus / ActionQueueCommand.&lt;id&gt; / ActionQueueRunButton.&lt;id&gt; / ActionQueueCopyButton.&lt;id&gt; for US-050, ProjectInitializer.ProjectIDField/CreateButton/CancelButton for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix.</x:v>
+        <x:v>Latest code build adds Marlin --caption-only mode so long local chunks can skip find queries after captioning; the option is wired through runtime/pipeline/stages/marlin.ts, scripts/marlin-evaluate.ts, ProjectMarlinEvaluationRunPlan/Runner, and marlin-eval-plan/eval-next/eval-run. Prior US-061 builds changed loadMarlinAssetInputs to use 02_media/source_map.json before indexed source fallbacks, made runMarlinAnalysis write per-asset checkpoints, added --max-sources/--skip-existing to scripts/marlin-evaluate.ts, and threaded those chunk controls through the native CLI/app paths. Prior native builds include ProjectMarlinRuntimeStatusReader isolated dependency probes, InspectorTab.Agent/Project/Clip/Media/QA buttons for US-065, ProjectPanel.ActionQueueStatus / ActionQueueCommand.&lt;id&gt; / ActionQueueRunButton.&lt;id&gt; / ActionQueueCopyButton.&lt;id&gt; for US-050, ProjectInitializer.ProjectIDField/CreateButton/CancelButton for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-061 pass verified source-map-aware Marlin chunks on the real lively-alt-vol5 project. npx vitest run tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts passed 12/0, npx tsc --noEmit --pretty false passed, and node --check scripts/marlin-evaluate.ts passed. Live non-mock runs with VOS_MARLIN_PROXY_MAX_WIDTH=384 and --request-timeout-ms 900000 completed for AST_5CAEC24E / 08-jun-a-man-and-a.mp4 and AST_25CDF4A5 / 06-jun-two-people-are.mp4. marlin_events.json has 2 assets, 13 events, and 8 find results; segments.json has Marlin summary/peak provenance for both; index-rebuild reports 2354 searchDocuments; marlin-status reports coverage=0.22 and canPreferMarlin=false; marlin-preference-status remains partially ready with lively-alt-vol5 at 2/9 peak segments. Prior US-047 retest verified current Command Palette repeatability and closed ISS-027.</x:v>
+        <x:v>Latest US-061 pass verified caption-only Marlin chunks and documented the current long-source limit. npx vitest run tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts passed 13/0, npx tsc --noEmit --pretty false passed, node --check scripts/marlin-evaluate.ts passed, swift build --target VideoOSStudioCLI passed, swift test --filter ProjectMarlinEvaluationRunPlanTests passed 11/0, marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only printed captionOnly=true, and git diff --check passed. Live caption-only 02-jan-clip.mp4 built a 256px proxy but timed out after 900000ms for caption before writing a third artifact item. Existing live non-mock runs remain AST_5CAEC24E / 08-jun-a-man-and-a.mp4 and AST_25CDF4A5 / 06-jun-two-people-are.mp4 with 2 assets, 13 events, 8 find results, 2354 searchDocuments, coverage=0.22, and canPreferMarlin=false. Prior US-047 retest verified current Command Palette repeatability and closed ISS-027.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest runtime/macOS CLI check is the US-061 real-project Marlin chunk pass: live marlin-evaluate completed twice on lively-alt-vol5, index-rebuild succeeded, marlin-status reports 2 assets / 13 events / 8 find results / coverage=0.22 / canPreferMarlin=false, and marlin-preference-status keeps canPreferMarlinAsDefault=false. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live single-source completion, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest runtime/macOS CLI check is the US-061 caption-only long-source pass: marlin-eval-plan prints the caption-only command, live 02-jan-clip.mp4 built .marlin-proxy-cache/9d4fe6bfb20192e1-w256.mp4, then the Marlin worker timed out after 900000ms for caption; no worker process remained, git status stayed clean, marlin-status remained 2 assets / 13 events / 8 find results / coverage=0.22 / canPreferMarlin=false, and marlin-preference-status keeps canPreferMarlinAsDefault=false. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live single-source completion, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility, Copy behavior, stable action-scoped AX identifiers, and rough-cut-review Start &amp; Run stopping at the Codex approval gate; approved workspace-write review execution, Final render Open, and Marlin default Open remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-065 is promoted for native SQLite/RAG Search/Add, cited Agent prompt insertion, and InspectorTab.* Agent/Media switching without AX hangs. US-061 is promoted for runtime/model/mock/native AX, live non-mock representative chunks on lively-alt-vol5, source-map-aware chunk controls, and resumable checkpointed evaluation; the remaining 7/9 lively-alt-vol5 live sources and repo-level Marlin-first preference promotion remain pending evidence gates. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility, Copy behavior, stable action-scoped AX identifiers, and rough-cut-review Start &amp; Run stopping at the Codex approval gate; approved workspace-write review execution, Final render Open, and Marlin default Open remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-065 is promoted for native SQLite/RAG Search/Add, cited Agent prompt insertion, and InspectorTab.* Agent/Media switching without AX hangs. US-061 is promoted for runtime/model/mock/native AX, live non-mock representative chunks on lively-alt-vol5, source-map-aware chunk controls, resumable checkpointed evaluation, and caption-only CLI support; the remaining 7/9 lively-alt-vol5 live sources and repo-level Marlin-first preference promotion remain pending evidence gates because 02-jan-clip.mp4 still times out during local MPS caption even when find queries are skipped. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2146,19 +2146,19 @@
         <x:v>As a native Studio operator, I can inspect Marlin runtime/model access/coverage/queue, run project Marlin evaluation, and apply Marlin preference when evidence gates pass.</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>MediaPanel renders MarlinEvaluationStatus, runtime/model access, representative buckets, queue items, run plan, evaluation button, and Apply Marlin Preference button. Evaluation can run only when sources exist and runtime/model checks pass; mock artifacts are workflow QA only and must not count as Marlin preference evidence. The Marlin status, queue, representative buckets, run/apply buttons, command line, artifact path, source-map-aware source selection, and resumable chunk options now expose stable MediaPanel.Marlin*/CLI contracts for native automation.</x:v>
+        <x:v>MediaPanel renders MarlinEvaluationStatus, runtime/model access, representative buckets, queue items, run plan, evaluation button, and Apply Marlin Preference button. Evaluation can run only when sources exist and runtime/model checks pass; mock artifacts are workflow QA only and must not count as Marlin preference evidence. The Marlin status, queue, representative buckets, run/apply buttons, command line, artifact path, source-map-aware source selection, and resumable/caption-only chunk options now expose stable MediaPanel.Marlin*/CLI contracts for native automation.</x:v>
       </x:c>
       <x:c r="E62" s="26" t="str">
         <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:48-160; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1296-1325,2326-2481; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRuntimeStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinModelAccessStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationQueue.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRepresentativePlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationRunPlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinPreferenceDecision.swift; runtime/pipeline/stages/marlin.ts; scripts/marlin-evaluate.ts</x:v>
       </x:c>
       <x:c r="F62" s="26" t="str">
-        <x:v>Run Marlin runtime/model/preference/queue/representative-plan/eval-plan/eval-run/status CLI checks, execute a tiny mock evaluation fixture, verify index refresh, verify Preference apply is blocked when gates fail, run Marlin focused Swift tests, confirm stable Marlin accessibility identifiers, run live non-mock representative-source chunks, verify source-map-aware chunk/checkpoint behavior, and leave full batch/preference promotion blocked until representative coverage and aggregate coverage gates pass.</x:v>
+        <x:v>Run Marlin runtime/model/preference/queue/representative-plan/eval-plan/eval-run/status CLI checks, execute a tiny mock evaluation fixture, verify index refresh, verify Preference apply is blocked when gates fail, run Marlin focused Swift tests, confirm stable Marlin accessibility identifiers, run live non-mock representative-source chunks, verify source-map-aware chunk/checkpoint/caption-only behavior, and leave full batch/preference promotion blocked until representative coverage and aggregate coverage gates pass.</x:v>
       </x:c>
       <x:c r="G62" s="26" t="str">
-        <x:v>Runtime/model/mock/native AX/live 2-source resumable pass; full batch preference gate pending</x:v>
+        <x:v>Runtime/model/mock/native AX/live 2-source resumable pass; caption-only timeout documented; full batch preference gate pending</x:v>
       </x:c>
       <x:c r="H62" s="11" t="str">
-        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. The runtime probe now imports dependency modules in isolated child processes, so the live marlin-runtime-status check no longer emits duplicate AVFoundation class warnings while still reporting every module ready. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path supports --request-timeout-ms / --timeout-ms, and a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4 completed with requestTimeoutMs=900000, wrote inference_mode=live Marlin events, updated segments with marlin_temporal_semantics, and rebuilt an index with 9 search documents. Current passes add per-asset checkpoint writes in runMarlinAnalysis plus --max-sources and --skip-existing through marlin-evaluate, ProjectMarlinEvaluationRunPlan/Runner, marlin-eval-plan, marlin-eval-next, and marlin-eval-run, then make loadMarlinAssetInputs source-map-aware so explicit linked filenames resolve to the correct asset_id when assets.json stores original camera filenames. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and a command carrying those options before source URLs. A /tmp mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. The real lively-alt-vol5 project now has live Marlin artifacts for AST_5CAEC24E / 08-jun-a-man-and-a.mp4 and AST_25CDF4A5 / 06-jun-two-people-are.mp4: marlin_events.json has 2 assets, 13 events, and 8 find results; segments.json has marlin_reporter summaries plus marlin_temporal_semantics provenance for both segments; index-rebuild produced 2354 search documents with 13 Marlin events and 8 Marlin find results. marlin-status reports coverage=0.22 and canPreferMarlin=false, while marlin-preference-status remains partially ready with lively-alt-vol5 at 2/9 peak segments and canPreferMarlinAsDefault=false. Focused verification passed: npx vitest run tests/marlin-incremental-merge.test.ts tests/marlin-analysis-stage.test.ts 12/0, npx tsc --noEmit --pretty false, and node --check scripts/marlin-evaluate.ts. Full all-source representative live run and repo-level preference promotion remain pending because the real repo gate still needs broader live coverage.</x:v>
+        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. The runtime probe now imports dependency modules in isolated child processes, so the live marlin-runtime-status check no longer emits duplicate AVFoundation class warnings while still reporting every module ready. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path supports --request-timeout-ms / --timeout-ms, and a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4 completed with requestTimeoutMs=900000, wrote inference_mode=live Marlin events, updated segments with marlin_temporal_semantics, and rebuilt an index with 9 search documents. Current passes add per-asset checkpoint writes in runMarlinAnalysis plus --max-sources and --skip-existing through marlin-evaluate, ProjectMarlinEvaluationRunPlan/Runner, marlin-eval-plan, marlin-eval-next, and marlin-eval-run, then make loadMarlinAssetInputs source-map-aware so explicit linked filenames resolve to the correct asset_id when assets.json stores original camera filenames. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and a command carrying those options before source URLs. A /tmp mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. The real lively-alt-vol5 project now has live Marlin artifacts for AST_5CAEC24E / 08-jun-a-man-and-a.mp4 and AST_25CDF4A5 / 06-jun-two-people-are.mp4: marlin_events.json has 2 assets, 13 events, and 8 find results; segments.json has marlin_reporter summaries plus marlin_temporal_semantics provenance for both segments; index-rebuild produced 2354 search documents with 13 Marlin events and 8 Marlin find results. marlin-status reports coverage=0.22 and canPreferMarlin=false, while marlin-preference-status remains partially ready with lively-alt-vol5 at 2/9 peak segments and canPreferMarlinAsDefault=false. Latest code adds --caption-only through the TS stage, marlin-evaluate, native CLI plan/run paths, and ProjectMarlinEvaluationRunPlan/Runner; tests verify find queries are not invoked when captionOnly is true. Verification passed: npx vitest run tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts 13/0, npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0, marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only, and git diff --check. A live caption-only run on 02-jan-clip.mp4 with VOS_MARLIN_PROXY_MAX_WIDTH=256 built .marlin-proxy-cache/9d4fe6bfb20192e1-w256.mp4, then timed out after 900000ms for caption before writing new artifact items; no worker process remained, git status stayed clean, and marlin-status remained assets=2/events=13/findResults=8/coverage=0.22/canPreferMarlin=false. Full all-source representative live run and repo-level preference promotion remain pending because the real repo gate still needs broader live coverage and long-source local MPS caption is still too slow.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="48" customHeight="1">
@@ -3775,19 +3775,19 @@
         <x:v>macOS runtime/logistics</x:v>
       </x:c>
       <x:c r="E51" s="26" t="str">
-        <x:v>Live representative Marlin evaluation loaded the model but timed out before the first caption result and left no marlin_events.json artifact.</x:v>
+        <x:v>Live representative Marlin evaluation can accumulate short sources, but longer local MPS caption runs still time out before writing additional marlin_events evidence.</x:v>
       </x:c>
       <x:c r="F51" s="26" t="str">
-        <x:v>The local worker request timeout was fixed at the connector default of 300000ms unless VOS_MARLIN_REQUEST_TIMEOUT_MS was set manually; the native CLI plan/run path did not expose a per-run timeout for slow Apple Silicon live caption passes; and completed assets were only written after the whole asset loop finished, so a later source timeout could discard earlier completed captions.</x:v>
+        <x:v>The initial worker request timeout was fixed at the connector default of 300000ms unless VOS_MARLIN_REQUEST_TIMEOUT_MS was set manually; the native CLI plan/run path did not expose a per-run timeout for slow Apple Silicon live caption passes; completed assets were only written after the whole asset loop finished; and even caption-only long-source runs still spend the full 900000ms in the Marlin caption call on local MPS before returning.</x:v>
       </x:c>
       <x:c r="G51" s="26" t="str">
-        <x:v>Added --request-timeout-ms and --timeout-ms to scripts/marlin-evaluate.ts, threaded requestTimeoutMs through ProjectMarlinEvaluationRunPlan and ProjectMarlinEvaluationRunner, surfaced it in marlin-eval-plan/marlin-eval-next/marlin-eval-run, added per-asset marlin_events checkpoint writes, and exposed --max-sources plus --skip-existing so representative coverage can be accumulated across bounded local runs.</x:v>
+        <x:v>Added --request-timeout-ms and --timeout-ms to scripts/marlin-evaluate.ts, threaded requestTimeoutMs through ProjectMarlinEvaluationRunPlan and ProjectMarlinEvaluationRunner, surfaced it in marlin-eval-plan/marlin-eval-next/marlin-eval-run, added per-asset marlin_events checkpoint writes, exposed --max-sources plus --skip-existing so representative coverage can be accumulated across bounded local runs, and added --caption-only to skip find queries for long chunks.</x:v>
       </x:c>
       <x:c r="H51" s="26" t="str">
-        <x:v>npx vitest run tests/marlin-incremental-merge.test.ts tests/marlin-analysis-stage.test.ts passed 12 tests, including checkpoint-before-later-timeout, source_map-aware explicit source selection, and all-existing skip-existing no-op coverage; npx tsc --noEmit --pretty false and node --check scripts/marlin-evaluate.ts passed. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and the chunk options in the generated command. A /tmp lively-alt-vol5 mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. The real lively-alt-vol5 project now has live non-mock Marlin evidence for AST_5CAEC24E and AST_25CDF4A5: 2 assets, 13 events, 8 find results, 2/9 Marlin peak segments, searchDocuments=2354 after index rebuild, and marlin-status coverage=0.22/canPreferMarlin=false. The full 9-source representative live batch remains intentionally pending.</x:v>
+        <x:v>npx vitest run tests/marlin-incremental-merge.test.ts tests/marlin-analysis-stage.test.ts passed 13 tests, including checkpoint-before-later-timeout, source_map-aware explicit source selection, all-existing skip-existing no-op coverage, and caption-only find skipping; npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0, and git diff --check passed. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only printed captionOnly=true and the chunk options before source URLs. The real lively-alt-vol5 project has live non-mock Marlin evidence for AST_5CAEC24E and AST_25CDF4A5: 2 assets, 13 events, 8 find results, 2/9 Marlin peak segments, searchDocuments=2354 after index rebuild, and marlin-status coverage=0.22/canPreferMarlin=false. A live caption-only 02-jan-clip.mp4 run at proxy width 256 built the proxy cache, then timed out after 900000ms for caption before writing new artifact items, leaving coverage unchanged. The full 9-source representative live batch remains intentionally pending.</x:v>
       </x:c>
       <x:c r="I51" s="11" t="str">
-        <x:v>Mitigated; live 2/9 resumable chunks; full batch pending</x:v>
+        <x:v>Mitigated; live 2/9 resumable chunks; long-source MPS caption pending</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="48" customHeight="1">
@@ -8638,79 +8638,79 @@
     </x:row>
     <x:row r="212" ht="48" customHeight="1">
       <x:c r="A212" s="10" t="str">
-        <x:v>TL-205</x:v>
+        <x:v>TL-238</x:v>
       </x:c>
       <x:c r="B212" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C212" s="26" t="str">
-        <x:v>Native preview duration fallback</x:v>
+        <x:v>Caption-only Marlin chunk mode and long-source timeout</x:v>
       </x:c>
       <x:c r="D212" s="26" t="str">
-        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
+        <x:v>Add --caption-only through the TS Marlin stage, marlin-evaluate CLI, native CLI plan/run path, and ProjectMarlinEvaluationRunPlan/Runner; verify focused tests and run a live caption-only 02-jan-clip.mp4 chunk.</x:v>
       </x:c>
       <x:c r="E212" s="26" t="str">
-        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
+        <x:v>captionOnly skips Marlin find queries after captioning, and tests assert find is not called. Verification passed: npx vitest run tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts 13/0, npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0, .build/debug/videoos-studio-cli marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only, and git diff --check. Live run VOS_MARLIN_PROXY_MAX_WIDTH=256 npx tsx scripts/marlin-evaluate.ts --project projects/lively-alt-vol5 --repo-root &lt;repo&gt; --request-timeout-ms 900000 --max-sources=1 --skip-existing --caption-only &lt;02-jan-clip.mp4&gt; built .marlin-proxy-cache/9d4fe6bfb20192e1-w256.mp4, then failed with Marlin worker request timed out after 900000ms for caption before writing a third artifact item. No marlin worker remained, git status stayed clean, and marlin-status remained assets=2/events=13/findResults=8/coverage=0.22/canPreferMarlin=false.</x:v>
       </x:c>
       <x:c r="F212" s="11" t="str">
-        <x:v>Native pixel/runtime pass</x:v>
+        <x:v>Caption-only implemented; long-source MPS timeout documented</x:v>
       </x:c>
     </x:row>
     <x:row r="213" ht="48" customHeight="1">
       <x:c r="A213" s="10" t="str">
-        <x:v>TL-206</x:v>
+        <x:v>TL-205</x:v>
       </x:c>
       <x:c r="B213" s="26" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C213" s="26" t="str">
-        <x:v>Native Clip Inspector save and clear</x:v>
+        <x:v>Native preview duration fallback</x:v>
       </x:c>
       <x:c r="D213" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
+        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
       </x:c>
       <x:c r="E213" s="26" t="str">
-        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
+        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F213" s="11" t="str">
-        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
+        <x:v>Native pixel/runtime pass</x:v>
       </x:c>
     </x:row>
     <x:row r="214" ht="48" customHeight="1">
       <x:c r="A214" s="10" t="str">
-        <x:v>TL-207</x:v>
+        <x:v>TL-206</x:v>
       </x:c>
       <x:c r="B214" s="26" t="str">
-        <x:v>US-058</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C214" s="26" t="str">
-        <x:v>Native QA Dashboard issue jump</x:v>
+        <x:v>Native Clip Inspector save and clear</x:v>
       </x:c>
       <x:c r="D214" s="26" t="str">
-        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
+        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
       </x:c>
       <x:c r="E214" s="26" t="str">
-        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
+        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
       </x:c>
       <x:c r="F214" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="48" customHeight="1">
       <x:c r="A215" s="10" t="str">
-        <x:v>TL-208</x:v>
+        <x:v>TL-207</x:v>
       </x:c>
       <x:c r="B215" s="26" t="str">
-        <x:v>US-056</x:v>
+        <x:v>US-058</x:v>
       </x:c>
       <x:c r="C215" s="26" t="str">
-        <x:v>Native Candidate Swap sheet and staging</x:v>
+        <x:v>Native QA Dashboard issue jump</x:v>
       </x:c>
       <x:c r="D215" s="26" t="str">
-        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
+        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
       </x:c>
       <x:c r="E215" s="26" t="str">
-        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
+        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
       </x:c>
       <x:c r="F215" s="11" t="str">
         <x:v>Native AX/pixel pass</x:v>
@@ -8718,339 +8718,339 @@
     </x:row>
     <x:row r="216" ht="48" customHeight="1">
       <x:c r="A216" s="10" t="str">
-        <x:v>TL-209</x:v>
+        <x:v>TL-208</x:v>
       </x:c>
       <x:c r="B216" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-056</x:v>
       </x:c>
       <x:c r="C216" s="26" t="str">
-        <x:v>Native exact preview regeneration</x:v>
+        <x:v>Native Candidate Swap sheet and staging</x:v>
       </x:c>
       <x:c r="D216" s="26" t="str">
-        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
+        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
       </x:c>
       <x:c r="E216" s="26" t="str">
-        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
       </x:c>
       <x:c r="F216" s="11" t="str">
-        <x:v>Native exact preview pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="48" customHeight="1">
       <x:c r="A217" s="10" t="str">
-        <x:v>TL-210</x:v>
+        <x:v>TL-209</x:v>
       </x:c>
       <x:c r="B217" s="26" t="str">
-        <x:v>US-047</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C217" s="26" t="str">
-        <x:v>Native Command Palette top-bar open/close</x:v>
+        <x:v>Native exact preview regeneration</x:v>
       </x:c>
       <x:c r="D217" s="26" t="str">
-        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
+        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
       </x:c>
       <x:c r="E217" s="26" t="str">
-        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
+        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F217" s="11" t="str">
-        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
+        <x:v>Native exact preview pass</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="48" customHeight="1">
       <x:c r="A218" s="10" t="str">
-        <x:v>TL-211</x:v>
+        <x:v>TL-210</x:v>
       </x:c>
       <x:c r="B218" s="26" t="str">
         <x:v>US-047</x:v>
       </x:c>
       <x:c r="C218" s="26" t="str">
-        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
+        <x:v>Native Command Palette top-bar open/close</x:v>
       </x:c>
       <x:c r="D218" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
+        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
       </x:c>
       <x:c r="E218" s="26" t="str">
-        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
+        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
       </x:c>
       <x:c r="F218" s="11" t="str">
-        <x:v>Native keyboard/AX pass</x:v>
+        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="48" customHeight="1">
       <x:c r="A219" s="10" t="str">
-        <x:v>TL-212</x:v>
+        <x:v>TL-211</x:v>
       </x:c>
       <x:c r="B219" s="26" t="str">
-        <x:v>US-048</x:v>
+        <x:v>US-047</x:v>
       </x:c>
       <x:c r="C219" s="26" t="str">
-        <x:v>Native Agent panel session lifecycle</x:v>
+        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
       </x:c>
       <x:c r="D219" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
+        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
       </x:c>
       <x:c r="E219" s="26" t="str">
-        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
+        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
       </x:c>
       <x:c r="F219" s="11" t="str">
-        <x:v>Native AX/computer-use pass</x:v>
+        <x:v>Native keyboard/AX pass</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="48" customHeight="1">
       <x:c r="A220" s="10" t="str">
-        <x:v>TL-213</x:v>
+        <x:v>TL-212</x:v>
       </x:c>
       <x:c r="B220" s="26" t="str">
-        <x:v>US-049</x:v>
+        <x:v>US-048</x:v>
       </x:c>
       <x:c r="C220" s="26" t="str">
-        <x:v>Native Status agent job read-only turn</x:v>
+        <x:v>Native Agent panel session lifecycle</x:v>
       </x:c>
       <x:c r="D220" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
       </x:c>
       <x:c r="E220" s="26" t="str">
-        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
+        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F220" s="11" t="str">
-        <x:v>Native read-only job pass; approved write pending</x:v>
+        <x:v>Native AX/computer-use pass</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="48" customHeight="1">
       <x:c r="A221" s="10" t="str">
-        <x:v>TL-214</x:v>
+        <x:v>TL-213</x:v>
       </x:c>
       <x:c r="B221" s="26" t="str">
-        <x:v>US-050</x:v>
+        <x:v>US-049</x:v>
       </x:c>
       <x:c r="C221" s="26" t="str">
-        <x:v>Native Project readiness/action queue Copy pass</x:v>
+        <x:v>Native Status agent job read-only turn</x:v>
       </x:c>
       <x:c r="D221" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
       </x:c>
       <x:c r="E221" s="26" t="str">
-        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
+        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F221" s="11" t="str">
-        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
+        <x:v>Native read-only job pass; approved write pending</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="48" customHeight="1">
       <x:c r="A222" s="10" t="str">
-        <x:v>TL-215</x:v>
+        <x:v>TL-214</x:v>
       </x:c>
       <x:c r="B222" s="26" t="str">
-        <x:v>US-051</x:v>
+        <x:v>US-050</x:v>
       </x:c>
       <x:c r="C222" s="26" t="str">
-        <x:v>Native local Source Analysis button</x:v>
+        <x:v>Native Project readiness/action queue Copy pass</x:v>
       </x:c>
       <x:c r="D222" s="26" t="str">
-        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
       </x:c>
       <x:c r="E222" s="26" t="str">
-        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
+        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
       </x:c>
       <x:c r="F222" s="11" t="str">
-        <x:v>Native local analysis pass</x:v>
+        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="48" customHeight="1">
       <x:c r="A223" s="10" t="str">
-        <x:v>TL-216</x:v>
+        <x:v>TL-215</x:v>
       </x:c>
       <x:c r="B223" s="26" t="str">
-        <x:v>US-052</x:v>
+        <x:v>US-051</x:v>
       </x:c>
       <x:c r="C223" s="26" t="str">
-        <x:v>Native Rough Cut and Review Patch buttons</x:v>
+        <x:v>Native local Source Analysis button</x:v>
       </x:c>
       <x:c r="D223" s="26" t="str">
-        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
+        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E223" s="26" t="str">
-        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
       </x:c>
       <x:c r="F223" s="11" t="str">
-        <x:v>Native compile/review patch pass</x:v>
+        <x:v>Native local analysis pass</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="48" customHeight="1">
       <x:c r="A224" s="10" t="str">
-        <x:v>TL-217</x:v>
+        <x:v>TL-216</x:v>
       </x:c>
       <x:c r="B224" s="26" t="str">
-        <x:v>US-053</x:v>
+        <x:v>US-052</x:v>
       </x:c>
       <x:c r="C224" s="26" t="str">
-        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
+        <x:v>Native Rough Cut and Review Patch buttons</x:v>
       </x:c>
       <x:c r="D224" s="26" t="str">
-        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
+        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E224" s="26" t="str">
-        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
+        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F224" s="11" t="str">
-        <x:v>Native timeline/context menu pass</x:v>
+        <x:v>Native compile/review patch pass</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="48" customHeight="1">
       <x:c r="A225" s="10" t="str">
-        <x:v>TL-218</x:v>
+        <x:v>TL-217</x:v>
       </x:c>
       <x:c r="B225" s="26" t="str">
-        <x:v>US-054</x:v>
+        <x:v>US-053</x:v>
       </x:c>
       <x:c r="C225" s="26" t="str">
-        <x:v>Native Studio feedback Apply and Undo</x:v>
+        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
       </x:c>
       <x:c r="D225" s="26" t="str">
-        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
+        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
       </x:c>
       <x:c r="E225" s="26" t="str">
-        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
       </x:c>
       <x:c r="F225" s="11" t="str">
-        <x:v>Native apply/undo pass</x:v>
+        <x:v>Native timeline/context menu pass</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="48" customHeight="1">
       <x:c r="A226" s="10" t="str">
-        <x:v>TL-219</x:v>
+        <x:v>TL-218</x:v>
       </x:c>
       <x:c r="B226" s="26" t="str">
-        <x:v>US-057</x:v>
+        <x:v>US-054</x:v>
       </x:c>
       <x:c r="C226" s="26" t="str">
-        <x:v>Native Footage Search sheet and replacement staging</x:v>
+        <x:v>Native Studio feedback Apply and Undo</x:v>
       </x:c>
       <x:c r="D226" s="26" t="str">
-        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
+        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E226" s="26" t="str">
-        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
+        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F226" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native apply/undo pass</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="48" customHeight="1">
       <x:c r="A227" s="10" t="str">
-        <x:v>TL-220</x:v>
+        <x:v>TL-219</x:v>
       </x:c>
       <x:c r="B227" s="26" t="str">
-        <x:v>US-066</x:v>
+        <x:v>US-057</x:v>
       </x:c>
       <x:c r="C227" s="26" t="str">
-        <x:v>Native Settings transport picker mutation</x:v>
+        <x:v>Native Footage Search sheet and replacement staging</x:v>
       </x:c>
       <x:c r="D227" s="26" t="str">
-        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
+        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
       </x:c>
       <x:c r="E227" s="26" t="str">
-        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
       </x:c>
       <x:c r="F227" s="11" t="str">
-        <x:v>Native Settings picker mutation pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="48" customHeight="1">
       <x:c r="A228" s="10" t="str">
-        <x:v>TL-221</x:v>
+        <x:v>TL-220</x:v>
       </x:c>
       <x:c r="B228" s="26" t="str">
-        <x:v>US-059</x:v>
+        <x:v>US-066</x:v>
       </x:c>
       <x:c r="C228" s="26" t="str">
-        <x:v>Native Media Relink buttons and source-map relink</x:v>
+        <x:v>Native Settings transport picker mutation</x:v>
       </x:c>
       <x:c r="D228" s="26" t="str">
-        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
+        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
       </x:c>
       <x:c r="E228" s="26" t="str">
-        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
+        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F228" s="11" t="str">
-        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
+        <x:v>Native Settings picker mutation pass</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="48" customHeight="1">
       <x:c r="A229" s="10" t="str">
-        <x:v>TL-222</x:v>
+        <x:v>TL-221</x:v>
       </x:c>
       <x:c r="B229" s="26" t="str">
-        <x:v>US-060</x:v>
+        <x:v>US-059</x:v>
       </x:c>
       <x:c r="C229" s="26" t="str">
-        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
+        <x:v>Native Media Relink buttons and source-map relink</x:v>
       </x:c>
       <x:c r="D229" s="26" t="str">
-        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
+        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
       </x:c>
       <x:c r="E229" s="26" t="str">
-        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
+        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
       </x:c>
       <x:c r="F229" s="11" t="str">
-        <x:v>Native synthetic/proxy/smoke button pass</x:v>
+        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="48" customHeight="1">
       <x:c r="A230" s="10" t="str">
-        <x:v>TL-223</x:v>
+        <x:v>TL-222</x:v>
       </x:c>
       <x:c r="B230" s="26" t="str">
-        <x:v>US-046</x:v>
+        <x:v>US-060</x:v>
       </x:c>
       <x:c r="C230" s="26" t="str">
-        <x:v>Native New Project from Source</x:v>
+        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
       </x:c>
       <x:c r="D230" s="26" t="str">
-        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
+        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
       </x:c>
       <x:c r="E230" s="26" t="str">
-        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
+        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
       </x:c>
       <x:c r="F230" s="11" t="str">
-        <x:v>Native project creation/NSOpenPanel pass</x:v>
+        <x:v>Native synthetic/proxy/smoke button pass</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="48" customHeight="1">
       <x:c r="A231" s="10" t="str">
-        <x:v>TL-224</x:v>
+        <x:v>TL-223</x:v>
       </x:c>
       <x:c r="B231" s="26" t="str">
-        <x:v>US-062</x:v>
+        <x:v>US-046</x:v>
       </x:c>
       <x:c r="C231" s="26" t="str">
-        <x:v>Native MediaPanel Audio Story Graph button</x:v>
+        <x:v>Native New Project from Source</x:v>
       </x:c>
       <x:c r="D231" s="26" t="str">
-        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
+        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
       </x:c>
       <x:c r="E231" s="26" t="str">
-        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
       </x:c>
       <x:c r="F231" s="11" t="str">
-        <x:v>Native AX/UI/CLI pass</x:v>
+        <x:v>Native project creation/NSOpenPanel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="48" customHeight="1">
       <x:c r="A232" s="10" t="str">
-        <x:v>TL-225</x:v>
+        <x:v>TL-224</x:v>
       </x:c>
       <x:c r="B232" s="26" t="str">
-        <x:v>US-063</x:v>
+        <x:v>US-062</x:v>
       </x:c>
       <x:c r="C232" s="26" t="str">
-        <x:v>Native Render Final Package button</x:v>
+        <x:v>Native MediaPanel Audio Story Graph button</x:v>
       </x:c>
       <x:c r="D232" s="26" t="str">
-        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
+        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E232" s="26" t="str">
-        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F232" s="11" t="str">
         <x:v>Native AX/UI/CLI pass</x:v>
@@ -9058,121 +9058,141 @@
     </x:row>
     <x:row r="233" ht="48" customHeight="1">
       <x:c r="A233" s="10" t="str">
-        <x:v>TL-226</x:v>
+        <x:v>TL-225</x:v>
       </x:c>
       <x:c r="B233" s="26" t="str">
-        <x:v>US-064</x:v>
+        <x:v>US-063</x:v>
       </x:c>
       <x:c r="C233" s="26" t="str">
-        <x:v>Native Editor Handoff export and Finder reveal</x:v>
+        <x:v>Native Render Final Package button</x:v>
       </x:c>
       <x:c r="D233" s="26" t="str">
-        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
+        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
       </x:c>
       <x:c r="E233" s="26" t="str">
-        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
+        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F233" s="11" t="str">
-        <x:v>Native AX/UI/Finder/CLI pass</x:v>
+        <x:v>Native AX/UI/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="48" customHeight="1">
       <x:c r="A234" s="10" t="str">
-        <x:v>TL-227</x:v>
+        <x:v>TL-226</x:v>
       </x:c>
       <x:c r="B234" s="26" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-064</x:v>
       </x:c>
       <x:c r="C234" s="26" t="str">
-        <x:v>Native Ask Codex editor-note proposal</x:v>
+        <x:v>Native Editor Handoff export and Finder reveal</x:v>
       </x:c>
       <x:c r="D234" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
+        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E234" s="26" t="str">
-        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
+        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
       </x:c>
       <x:c r="F234" s="11" t="str">
-        <x:v>Native read-only Codex proposal pass</x:v>
+        <x:v>Native AX/UI/Finder/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="48" customHeight="1">
       <x:c r="A235" s="10" t="str">
-        <x:v>TL-228</x:v>
+        <x:v>TL-227</x:v>
       </x:c>
       <x:c r="B235" s="26" t="str">
-        <x:v>US-061</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C235" s="26" t="str">
-        <x:v>Live Marlin single-source completion</x:v>
+        <x:v>Native Ask Codex editor-note proposal</x:v>
       </x:c>
       <x:c r="D235" s="26" t="str">
-        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
+        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
       </x:c>
       <x:c r="E235" s="26" t="str">
-        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
+        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
       </x:c>
       <x:c r="F235" s="11" t="str">
-        <x:v>Live single-source pass; full representative batch pending</x:v>
+        <x:v>Native read-only Codex proposal pass</x:v>
       </x:c>
     </x:row>
     <x:row r="236" ht="48" customHeight="1">
       <x:c r="A236" s="10" t="str">
-        <x:v>TL-229</x:v>
+        <x:v>TL-228</x:v>
       </x:c>
       <x:c r="B236" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C236" s="26" t="str">
-        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+        <x:v>Live Marlin single-source completion</x:v>
       </x:c>
       <x:c r="D236" s="26" t="str">
-        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
       </x:c>
       <x:c r="E236" s="26" t="str">
-        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
       </x:c>
       <x:c r="F236" s="11" t="str">
-        <x:v>Native fresh-launch pixel pass</x:v>
+        <x:v>Live single-source pass; full representative batch pending</x:v>
       </x:c>
     </x:row>
     <x:row r="237" ht="48" customHeight="1">
       <x:c r="A237" s="10" t="str">
-        <x:v>TL-230</x:v>
+        <x:v>TL-229</x:v>
       </x:c>
       <x:c r="B237" s="26" t="str">
         <x:v>US-045</x:v>
       </x:c>
       <x:c r="C237" s="26" t="str">
+        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+      </x:c>
+      <x:c r="D237" s="26" t="str">
+        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+      </x:c>
+      <x:c r="E237" s="26" t="str">
+        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+      </x:c>
+      <x:c r="F237" s="11" t="str">
+        <x:v>Native fresh-launch pixel pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" ht="48" customHeight="1">
+      <x:c r="A238" s="10" t="str">
+        <x:v>TL-230</x:v>
+      </x:c>
+      <x:c r="B238" s="26" t="str">
+        <x:v>US-045</x:v>
+      </x:c>
+      <x:c r="C238" s="26" t="str">
         <x:v>AX-1 exact preview promotion and pixel pass</x:v>
       </x:c>
-      <x:c r="D237" s="26" t="str">
+      <x:c r="D238" s="26" t="str">
         <x:v>Run videoos-studio-cli compile-run on projects/ax1-participant-voices-20260401, confirm playback-contract-status, select ProjectShelf.ax1-participant-voices-20260401 in VideoOSStudio, capture /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and run Retina-coordinate pixel statistics on the Viewer region.</x:v>
       </x:c>
-      <x:c r="E237" s="26" t="str">
+      <x:c r="E238" s="26" t="str">
         <x:v>Before compile, playback-contract-status returned legacy_manifest and approvalGrade=false. compile-run completed with exitCode=0, timeline compiled, indexDocuments=492, and git status stayed clean. After compile, playback-contract-status returned state=exact, approvalGrade=true, timelineHash=171378fe2bfe3a7c, and manifestBaseTimelineHash=171378fe2bfe3a7c. Native Viewer showed Exact preview / preview-editor-1775121573933.mp4 and Timeline preview D4887.MP4 with a visible interview frame. Screenshot was 3.5M; viewer_person_actual mean_rgb=(144.62,141.42,149.8) and near_black_pct=0.0004, while left pillarbox near_black_pct=1.0000 as expected.</x:v>
       </x:c>
-      <x:c r="F237" s="11" t="str">
+      <x:c r="F238" s="11" t="str">
         <x:v>Native AX-1 exact/pixel pass</x:v>
       </x:c>
     </x:row>
-    <x:row r="238" ht="48" customHeight="1">
-      <x:c r="A238" s="12" t="str">
+    <x:row r="239" ht="48" customHeight="1">
+      <x:c r="A239" s="12" t="str">
         <x:v>TL-231</x:v>
       </x:c>
-      <x:c r="B238" s="27" t="str">
+      <x:c r="B239" s="27" t="str">
         <x:v>US-050</x:v>
       </x:c>
-      <x:c r="C238" s="27" t="str">
+      <x:c r="C239" s="27" t="str">
         <x:v>Native Action Queue approval gate</x:v>
       </x:c>
-      <x:c r="D238" s="27" t="str">
+      <x:c r="D239" s="27" t="str">
         <x:v>Add ProjectPanel.ActionQueue* identifiers, relaunch VideoOSStudio, select AX-1 Project tab, inspect the Action Queue AX tree, click ProjectPanel.ActionQueueRunButton.rough-cut-review, and stop at the Codex approval gate without approving writes.</x:v>
       </x:c>
-      <x:c r="E238" s="27" t="str">
+      <x:c r="E239" s="27" t="str">
         <x:v>AX exposed ProjectPanel.ActionQueueRunButton.rough-cut-review, ProjectPanel.ActionQueueCopyButton.rough-cut-review, ProjectPanel.ActionQueueRunButton.marlin-default, and ProjectPanel.ActionQueueCopyButton.marlin-default. Clicking rough-cut-review changed the row to disabled Starting Codex session for Review..., then to Opening Codex approval gate for Review. ps showed a Codex app-server child under VideoOSStudio; git status listed only the intentional ProjectInspectorViews.swift edit, and projects/ax1-participant-voices-20260401/06_review still contained only human_notes.yaml.</x:v>
       </x:c>
-      <x:c r="F238" s="13" t="str">
+      <x:c r="F239" s="13" t="str">
         <x:v>Native approval-gate pass; write not approved</x:v>
       </x:c>
     </x:row>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5f98742d35bc4fc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rb526ce3bf01e4e2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Rdab4f702d6b243f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R52183fc705304854"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R72c3b332f7dc497a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rbab9a9aa2138475f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rfa2c22da2b5f4c0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R0347fc9c079a4f7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="Raa1ca1f493c54b11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R6730e8d6cc734434"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -439,7 +439,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 20:32 JST</x:v>
+        <x:v>2026-06-23 20:54 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -487,7 +487,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build adds Marlin --caption-only mode so long local chunks can skip find queries after captioning; the option is wired through runtime/pipeline/stages/marlin.ts, scripts/marlin-evaluate.ts, ProjectMarlinEvaluationRunPlan/Runner, and marlin-eval-plan/eval-next/eval-run. Prior US-061 builds changed loadMarlinAssetInputs to use 02_media/source_map.json before indexed source fallbacks, made runMarlinAnalysis write per-asset checkpoints, added --max-sources/--skip-existing to scripts/marlin-evaluate.ts, and threaded those chunk controls through the native CLI/app paths. Prior native builds include ProjectMarlinRuntimeStatusReader isolated dependency probes, InspectorTab.Agent/Project/Clip/Media/QA buttons for US-065, ProjectPanel.ActionQueueStatus / ActionQueueCommand.&lt;id&gt; / ActionQueueRunButton.&lt;id&gt; / ActionQueueCopyButton.&lt;id&gt; for US-050, ProjectInitializer.ProjectIDField/CreateButton/CancelButton for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix.</x:v>
+        <x:v>Latest code build adds bounded Marlin range chunking for long local sources: --chunk-seconds, --chunk-overlap-seconds, and --max-chunks are wired through runtime/pipeline/stages/marlin.ts, scripts/marlin-evaluate.ts, ProjectMarlinEvaluationRunPlan/Runner, and marlin-eval-plan/eval-next/eval-run. The same path keeps --caption-only, source-map-aware source selection, per-asset/per-chunk checkpoints, --max-sources, and --skip-existing. Prior native builds include ProjectMarlinRuntimeStatusReader isolated dependency probes, InspectorTab.Agent/Project/Clip/Media/QA buttons for US-065, ProjectPanel.ActionQueueStatus / ActionQueueCommand.&lt;id&gt; / ActionQueueRunButton.&lt;id&gt; / ActionQueueCopyButton.&lt;id&gt; for US-050, ProjectInitializer.ProjectIDField/CreateButton/CancelButton for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-061 pass verified caption-only Marlin chunks and documented the current long-source limit. npx vitest run tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts passed 13/0, npx tsc --noEmit --pretty false passed, node --check scripts/marlin-evaluate.ts passed, swift build --target VideoOSStudioCLI passed, swift test --filter ProjectMarlinEvaluationRunPlanTests passed 11/0, marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only printed captionOnly=true, and git diff --check passed. Live caption-only 02-jan-clip.mp4 built a 256px proxy but timed out after 900000ms for caption before writing a third artifact item. Existing live non-mock runs remain AST_5CAEC24E / 08-jun-a-man-and-a.mp4 and AST_25CDF4A5 / 06-jun-two-people-are.mp4 with 2 assets, 13 events, 8 find results, 2354 searchDocuments, coverage=0.22, and canPreferMarlin=false. Prior US-047 retest verified current Command Palette repeatability and closed ISS-027.</x:v>
+        <x:v>Latest US-061 pass verified bounded caption-only Marlin range chunks. npx vitest run tests/marlin-normalize.test.ts tests/marlin-proxy.test.ts tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts passed 29/0, npx tsc --noEmit --pretty false passed, node --check scripts/marlin-evaluate.ts passed, swift build --target VideoOSStudioCLI passed, swift test --filter ProjectMarlinEvaluationRunPlanTests passed 11/0, marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=1 printed chunk options, and git diff --check passed. Live non-mock runs now cover AST_5CAEC24E / 08-jun-a-man-and-a.mp4, AST_25CDF4A5 / 06-jun-two-people-are.mp4, and AST_704DC85D / 02-jan-clip.mp4 first 30s range chunk, with 3 assets, 18 events, 8 find results, coverage=0.33, and canPreferMarlin=true for lively-alt-vol5. Repo-level canPreferMarlinAsDefault remains false pending broader coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest runtime/macOS CLI check is the US-061 caption-only long-source pass: marlin-eval-plan prints the caption-only command, live 02-jan-clip.mp4 built .marlin-proxy-cache/9d4fe6bfb20192e1-w256.mp4, then the Marlin worker timed out after 900000ms for caption; no worker process remained, git status stayed clean, marlin-status remained 2 assets / 13 events / 8 find results / coverage=0.22 / canPreferMarlin=false, and marlin-preference-status keeps canPreferMarlinAsDefault=false. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live single-source completion, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest runtime/macOS CLI check is the US-061 bounded range chunk pass: marlin-eval-plan prints the caption-only chunk command, live 02-jan-clip.mp4 created .marlin-proxy-cache/ranges/dd2959340fe6d155-0.000-30.000.mp4, completed, and appended AST_704DC85D with chunkIndices=[0]. marlin-status now reports 3 assets / 18 events / 8 find results / coverage=0.33 / canPreferMarlin=true for lively-alt-vol5; marlin-preference-status still keeps canPreferMarlinAsDefault=false because aggregate repo coverage remains 0.13 and only 5 projects are candidates. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live single-source completion, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility, Copy behavior, stable action-scoped AX identifiers, and rough-cut-review Start &amp; Run stopping at the Codex approval gate; approved workspace-write review execution, Final render Open, and Marlin default Open remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-065 is promoted for native SQLite/RAG Search/Add, cited Agent prompt insertion, and InspectorTab.* Agent/Media switching without AX hangs. US-061 is promoted for runtime/model/mock/native AX, live non-mock representative chunks on lively-alt-vol5, source-map-aware chunk controls, resumable checkpointed evaluation, and caption-only CLI support; the remaining 7/9 lively-alt-vol5 live sources and repo-level Marlin-first preference promotion remain pending evidence gates because 02-jan-clip.mp4 still times out during local MPS caption even when find queries are skipped. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility, Copy behavior, stable action-scoped AX identifiers, and rough-cut-review Start &amp; Run stopping at the Codex approval gate; approved workspace-write review execution, Final render Open, and Marlin default Open remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-065 is promoted for native SQLite/RAG Search/Add, cited Agent prompt insertion, and InspectorTab.* Agent/Media switching without AX hangs. US-061 is promoted for runtime/model/mock/native AX, live non-mock representative chunks on lively-alt-vol5, source-map-aware chunk controls, resumable checkpointed evaluation, caption-only CLI support, and bounded 30s range chunking that made 02-jan-clip.mp4 contribute a third live Marlin asset. The remaining 6/9 lively-alt-vol5 peak segments and repo-level Marlin-first preference promotion remain pending evidence gates. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2155,10 +2155,10 @@
         <x:v>Run Marlin runtime/model/preference/queue/representative-plan/eval-plan/eval-run/status CLI checks, execute a tiny mock evaluation fixture, verify index refresh, verify Preference apply is blocked when gates fail, run Marlin focused Swift tests, confirm stable Marlin accessibility identifiers, run live non-mock representative-source chunks, verify source-map-aware chunk/checkpoint/caption-only behavior, and leave full batch/preference promotion blocked until representative coverage and aggregate coverage gates pass.</x:v>
       </x:c>
       <x:c r="G62" s="26" t="str">
-        <x:v>Runtime/model/mock/native AX/live 2-source resumable pass; caption-only timeout documented; full batch preference gate pending</x:v>
+        <x:v>Runtime/model/mock/native AX/live 3-source range-chunk pass; full batch preference gate pending</x:v>
       </x:c>
       <x:c r="H62" s="11" t="str">
-        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. The runtime probe now imports dependency modules in isolated child processes, so the live marlin-runtime-status check no longer emits duplicate AVFoundation class warnings while still reporting every module ready. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path supports --request-timeout-ms / --timeout-ms, and a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4 completed with requestTimeoutMs=900000, wrote inference_mode=live Marlin events, updated segments with marlin_temporal_semantics, and rebuilt an index with 9 search documents. Current passes add per-asset checkpoint writes in runMarlinAnalysis plus --max-sources and --skip-existing through marlin-evaluate, ProjectMarlinEvaluationRunPlan/Runner, marlin-eval-plan, marlin-eval-next, and marlin-eval-run, then make loadMarlinAssetInputs source-map-aware so explicit linked filenames resolve to the correct asset_id when assets.json stores original camera filenames. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and a command carrying those options before source URLs. A /tmp mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. The real lively-alt-vol5 project now has live Marlin artifacts for AST_5CAEC24E / 08-jun-a-man-and-a.mp4 and AST_25CDF4A5 / 06-jun-two-people-are.mp4: marlin_events.json has 2 assets, 13 events, and 8 find results; segments.json has marlin_reporter summaries plus marlin_temporal_semantics provenance for both segments; index-rebuild produced 2354 search documents with 13 Marlin events and 8 Marlin find results. marlin-status reports coverage=0.22 and canPreferMarlin=false, while marlin-preference-status remains partially ready with lively-alt-vol5 at 2/9 peak segments and canPreferMarlinAsDefault=false. Latest code adds --caption-only through the TS stage, marlin-evaluate, native CLI plan/run paths, and ProjectMarlinEvaluationRunPlan/Runner; tests verify find queries are not invoked when captionOnly is true. Verification passed: npx vitest run tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts 13/0, npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0, marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only, and git diff --check. A live caption-only run on 02-jan-clip.mp4 with VOS_MARLIN_PROXY_MAX_WIDTH=256 built .marlin-proxy-cache/9d4fe6bfb20192e1-w256.mp4, then timed out after 900000ms for caption before writing new artifact items; no worker process remained, git status stayed clean, and marlin-status remained assets=2/events=13/findResults=8/coverage=0.22/canPreferMarlin=false. Full all-source representative live run and repo-level preference promotion remain pending because the real repo gate still needs broader live coverage and long-source local MPS caption is still too slow.</x:v>
+        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. The runtime probe now imports dependency modules in isolated child processes, so the live marlin-runtime-status check no longer emits duplicate AVFoundation class warnings while still reporting every module ready. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path supports --request-timeout-ms / --timeout-ms, and a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4 completed with requestTimeoutMs=900000, wrote inference_mode=live Marlin events, updated segments with marlin_temporal_semantics, and rebuilt an index with 9 search documents. Current passes add per-asset checkpoint writes in runMarlinAnalysis plus --max-sources and --skip-existing through marlin-evaluate, ProjectMarlinEvaluationRunPlan/Runner, marlin-eval-plan, marlin-eval-next, and marlin-eval-run, then make loadMarlinAssetInputs source-map-aware so explicit linked filenames resolve to the correct asset_id when assets.json stores original camera filenames. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and a command carrying those options before source URLs. A /tmp mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. The real lively-alt-vol5 project has live Marlin artifacts for AST_5CAEC24E / 08-jun-a-man-and-a.mp4, AST_25CDF4A5 / 06-jun-two-people-are.mp4, and AST_704DC85D / 02-jan-clip.mp4. The latest code adds --caption-only plus bounded range chunk controls (--chunk-seconds, --chunk-overlap-seconds, --max-chunks) through the TS stage, marlin-evaluate, native CLI plan/run paths, and ProjectMarlinEvaluationRunPlan/Runner; tests verify find queries are not invoked when captionOnly is true and chunk event IDs carry chunk metadata. Verification passed: npx vitest run tests/marlin-normalize.test.ts tests/marlin-proxy.test.ts tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts 29/0, npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0, marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=1, and git diff --check. A live range-chunk caption-only run on 02-jan-clip.mp4 with VOS_MARLIN_PROXY_MAX_WIDTH=256 created .marlin-proxy-cache/ranges/dd2959340fe6d155-0.000-30.000.mp4, completed, and appended AST_704DC85D with 5 events, chunkIndices=[0], and 0 find results. marlin-status now reports assets=3/events=18/findResults=8/segmentsWithMarlinPeak=3/coverage=0.33/canPreferMarlin=true, while repo-level marlin-preference-status remains partially ready with lively-alt-vol5 at 3/9 peak segments and canPreferMarlinAsDefault=false. Full all-source representative live run and repo-level preference promotion remain pending because the real repo gate still needs broader live coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="48" customHeight="1">
@@ -3775,19 +3775,19 @@
         <x:v>macOS runtime/logistics</x:v>
       </x:c>
       <x:c r="E51" s="26" t="str">
-        <x:v>Live representative Marlin evaluation can accumulate short sources, but longer local MPS caption runs still time out before writing additional marlin_events evidence.</x:v>
+        <x:v>Live representative Marlin evaluation can accumulate sources incrementally, but full-source local MPS caption runs are still too slow for broad unattended representative batches.</x:v>
       </x:c>
       <x:c r="F51" s="26" t="str">
-        <x:v>The initial worker request timeout was fixed at the connector default of 300000ms unless VOS_MARLIN_REQUEST_TIMEOUT_MS was set manually; the native CLI plan/run path did not expose a per-run timeout for slow Apple Silicon live caption passes; completed assets were only written after the whole asset loop finished; and even caption-only long-source runs still spend the full 900000ms in the Marlin caption call on local MPS before returning.</x:v>
+        <x:v>The initial worker request timeout was fixed at the connector default of 300000ms unless VOS_MARLIN_REQUEST_TIMEOUT_MS was set manually; the native CLI plan/run path did not expose a per-run timeout for slow Apple Silicon live caption passes; completed assets were only written after the whole asset loop finished; and caption-only still passed the full source/proxy into the Marlin caption call, so long clips could spend the entire 900000ms budget before returning.</x:v>
       </x:c>
       <x:c r="G51" s="26" t="str">
-        <x:v>Added --request-timeout-ms and --timeout-ms to scripts/marlin-evaluate.ts, threaded requestTimeoutMs through ProjectMarlinEvaluationRunPlan and ProjectMarlinEvaluationRunner, surfaced it in marlin-eval-plan/marlin-eval-next/marlin-eval-run, added per-asset marlin_events checkpoint writes, exposed --max-sources plus --skip-existing so representative coverage can be accumulated across bounded local runs, and added --caption-only to skip find queries for long chunks.</x:v>
+        <x:v>Added --request-timeout-ms and --timeout-ms to scripts/marlin-evaluate.ts, threaded requestTimeoutMs through ProjectMarlinEvaluationRunPlan and ProjectMarlinEvaluationRunner, surfaced it in marlin-eval-plan/marlin-eval-next/marlin-eval-run, added per-asset and per-chunk marlin_events checkpoint writes, exposed --max-sources plus --skip-existing so representative coverage can be accumulated across bounded local runs, added --caption-only to skip find queries for long chunks, and added --chunk-seconds/--chunk-overlap-seconds/--max-chunks so long sources are sliced into cached range proxies before captioning.</x:v>
       </x:c>
       <x:c r="H51" s="26" t="str">
-        <x:v>npx vitest run tests/marlin-incremental-merge.test.ts tests/marlin-analysis-stage.test.ts passed 13 tests, including checkpoint-before-later-timeout, source_map-aware explicit source selection, all-existing skip-existing no-op coverage, and caption-only find skipping; npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0, and git diff --check passed. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only printed captionOnly=true and the chunk options before source URLs. The real lively-alt-vol5 project has live non-mock Marlin evidence for AST_5CAEC24E and AST_25CDF4A5: 2 assets, 13 events, 8 find results, 2/9 Marlin peak segments, searchDocuments=2354 after index rebuild, and marlin-status coverage=0.22/canPreferMarlin=false. A live caption-only 02-jan-clip.mp4 run at proxy width 256 built the proxy cache, then timed out after 900000ms for caption before writing new artifact items, leaving coverage unchanged. The full 9-source representative live batch remains intentionally pending.</x:v>
+        <x:v>npx vitest run tests/marlin-normalize.test.ts tests/marlin-proxy.test.ts tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts passed 29 tests, including checkpoint-before-later-timeout, source_map-aware explicit source selection, all-existing skip-existing no-op coverage, caption-only find skipping, deterministic chunk boundaries, range proxy caching, and chunk event IDs; npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0, and git diff --check passed. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=1 printed the chunk options before source URLs. The real lively-alt-vol5 project has live non-mock Marlin evidence for AST_5CAEC24E, AST_25CDF4A5, and AST_704DC85D. The latest live 02-jan-clip.mp4 range run created .marlin-proxy-cache/ranges/dd2959340fe6d155-0.000-30.000.mp4, appended 5 chunk-indexed events, and raised marlin-status to 3 assets, 18 events, 8 find results, 3/9 Marlin peak segments, coverage=0.33, and canPreferMarlin=true. The full 9-source representative live batch and repo-level default preference remain intentionally pending broader evidence.</x:v>
       </x:c>
       <x:c r="I51" s="11" t="str">
-        <x:v>Mitigated; live 2/9 resumable chunks; long-source MPS caption pending</x:v>
+        <x:v>Mitigated; live 3/9 range chunks; repo preference gate pending</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="48" customHeight="1">
@@ -8644,16 +8644,16 @@
         <x:v>US-061</x:v>
       </x:c>
       <x:c r="C212" s="26" t="str">
-        <x:v>Caption-only Marlin chunk mode and long-source timeout</x:v>
+        <x:v>Caption-only bounded Marlin range chunks</x:v>
       </x:c>
       <x:c r="D212" s="26" t="str">
-        <x:v>Add --caption-only through the TS Marlin stage, marlin-evaluate CLI, native CLI plan/run path, and ProjectMarlinEvaluationRunPlan/Runner; verify focused tests and run a live caption-only 02-jan-clip.mp4 chunk.</x:v>
+        <x:v>Add --caption-only and bounded range chunk controls through the TS Marlin stage, marlin-evaluate CLI, native CLI plan/run path, and ProjectMarlinEvaluationRunPlan/Runner; verify focused tests and run a live 30s caption-only 02-jan-clip.mp4 range chunk.</x:v>
       </x:c>
       <x:c r="E212" s="26" t="str">
-        <x:v>captionOnly skips Marlin find queries after captioning, and tests assert find is not called. Verification passed: npx vitest run tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts 13/0, npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0, .build/debug/videoos-studio-cli marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only, and git diff --check. Live run VOS_MARLIN_PROXY_MAX_WIDTH=256 npx tsx scripts/marlin-evaluate.ts --project projects/lively-alt-vol5 --repo-root &lt;repo&gt; --request-timeout-ms 900000 --max-sources=1 --skip-existing --caption-only &lt;02-jan-clip.mp4&gt; built .marlin-proxy-cache/9d4fe6bfb20192e1-w256.mp4, then failed with Marlin worker request timed out after 900000ms for caption before writing a third artifact item. No marlin worker remained, git status stayed clean, and marlin-status remained assets=2/events=13/findResults=8/coverage=0.22/canPreferMarlin=false.</x:v>
+        <x:v>captionOnly skips Marlin find queries after captioning, chunk event IDs carry chunk metadata, and the runner can resume by completed chunk_index. Verification passed: npx vitest run tests/marlin-normalize.test.ts tests/marlin-proxy.test.ts tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts 29/0, npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0, .build/debug/videoos-studio-cli marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=1, and git diff --check. Live run VOS_MARLIN_PROXY_MAX_WIDTH=256 npx tsx scripts/marlin-evaluate.ts --project projects/lively-alt-vol5 --repo-root &lt;repo&gt; --request-timeout-ms 900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=1 &lt;02-jan-clip.mp4&gt; created .marlin-proxy-cache/ranges/dd2959340fe6d155-0.000-30.000.mp4 and completed. marlin_events.json now has AST_704DC85D / 02-jan-clip.mp4 with 5 events, chunkIndices=[0], and 0 find results; project marlin-status reports assets=3/events=18/findResults=8/coverage=0.33/canPreferMarlin=true. Repo marlin-preference-status remains partially ready with lively-alt-vol5 at 3/9 peak segments and canPreferMarlinAsDefault=false.</x:v>
       </x:c>
       <x:c r="F212" s="11" t="str">
-        <x:v>Caption-only implemented; long-source MPS timeout documented</x:v>
+        <x:v>Range chunk pass; repo preference gate pending</x:v>
       </x:c>
     </x:row>
     <x:row r="213" ht="48" customHeight="1">

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rbab9a9aa2138475f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rfa2c22da2b5f4c0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R0347fc9c079a4f7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="Raa1ca1f493c54b11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R6730e8d6cc734434"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R2640a1442cf94924"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R6ef50d727c544752"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R41c9d95ddfbe41fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R47636d119a1642cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R4687bd9be600466f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -439,7 +439,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 20:54 JST</x:v>
+        <x:v>2026-06-23 21:00 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-061 pass verified bounded caption-only Marlin range chunks. npx vitest run tests/marlin-normalize.test.ts tests/marlin-proxy.test.ts tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts passed 29/0, npx tsc --noEmit --pretty false passed, node --check scripts/marlin-evaluate.ts passed, swift build --target VideoOSStudioCLI passed, swift test --filter ProjectMarlinEvaluationRunPlanTests passed 11/0, marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=1 printed chunk options, and git diff --check passed. Live non-mock runs now cover AST_5CAEC24E / 08-jun-a-man-and-a.mp4, AST_25CDF4A5 / 06-jun-two-people-are.mp4, and AST_704DC85D / 02-jan-clip.mp4 first 30s range chunk, with 3 assets, 18 events, 8 find results, coverage=0.33, and canPreferMarlin=true for lively-alt-vol5. Repo-level canPreferMarlinAsDefault remains false pending broader coverage.</x:v>
+        <x:v>Latest US-061 pass advanced bounded caption-only Marlin range chunks on lively-alt-vol5. Prior implementation validation remains green: npx vitest run tests/marlin-normalize.test.ts tests/marlin-proxy.test.ts tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts passed 29/0, npx tsc --noEmit --pretty false passed, node --check scripts/marlin-evaluate.ts passed, swift build --target VideoOSStudioCLI passed, swift test --filter ProjectMarlinEvaluationRunPlanTests passed 11/0, and git diff --check passed. Live non-mock runs now cover AST_5CAEC24E / 08-jun-a-man-and-a.mp4, AST_25CDF4A5 / 06-jun-two-people-are.mp4, AST_704DC85D / 02-jan-clip.mp4 first 30s range chunk, and AST_09AE639A / 04-jan-clip.mp4 first two 30s range chunks. lively-alt-vol5 now has 4 assets, 29 events, 8 find results, coverage=0.44, and canPreferMarlin=true; index-rebuild reports 2370 searchDocuments. Repo-level canPreferMarlinAsDefault remains false pending broader coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest runtime/macOS CLI check is the US-061 bounded range chunk pass: marlin-eval-plan prints the caption-only chunk command, live 02-jan-clip.mp4 created .marlin-proxy-cache/ranges/dd2959340fe6d155-0.000-30.000.mp4, completed, and appended AST_704DC85D with chunkIndices=[0]. marlin-status now reports 3 assets / 18 events / 8 find results / coverage=0.33 / canPreferMarlin=true for lively-alt-vol5; marlin-preference-status still keeps canPreferMarlinAsDefault=false because aggregate repo coverage remains 0.13 and only 5 projects are candidates. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live single-source completion, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest runtime/macOS CLI check is the US-061 04-jan bounded range chunk pass: live 04-jan-clip.mp4 created .marlin-proxy-cache/ranges/0c9587769b484daa-0.000-30.000.mp4 and c038aafd7ae6116a-27.000-57.000.mp4, completed, and appended AST_09AE639A with chunkIndices=[0,1]. marlin-status now reports 4 assets / 29 events / 8 find results / coverage=0.44 / canPreferMarlin=true for lively-alt-vol5; marlin-preference-status still keeps canPreferMarlinAsDefault=false because aggregate repo coverage remains 0.13 and only 5 projects are candidates. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live single-source completion, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility, Copy behavior, stable action-scoped AX identifiers, and rough-cut-review Start &amp; Run stopping at the Codex approval gate; approved workspace-write review execution, Final render Open, and Marlin default Open remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-065 is promoted for native SQLite/RAG Search/Add, cited Agent prompt insertion, and InspectorTab.* Agent/Media switching without AX hangs. US-061 is promoted for runtime/model/mock/native AX, live non-mock representative chunks on lively-alt-vol5, source-map-aware chunk controls, resumable checkpointed evaluation, caption-only CLI support, and bounded 30s range chunking that made 02-jan-clip.mp4 contribute a third live Marlin asset. The remaining 6/9 lively-alt-vol5 peak segments and repo-level Marlin-first preference promotion remain pending evidence gates. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility, Copy behavior, stable action-scoped AX identifiers, and rough-cut-review Start &amp; Run stopping at the Codex approval gate; approved workspace-write review execution, Final render Open, and Marlin default Open remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-065 is promoted for native SQLite/RAG Search/Add, cited Agent prompt insertion, and InspectorTab.* Agent/Media switching without AX hangs. US-061 is promoted for runtime/model/mock/native AX, live non-mock representative chunks on lively-alt-vol5, source-map-aware chunk controls, resumable checkpointed evaluation, caption-only CLI support, and bounded 30s range chunking that made 02-jan-clip.mp4 and 04-jan-clip.mp4 contribute live Marlin assets. The remaining 5/9 lively-alt-vol5 peak segments and repo-level Marlin-first preference promotion remain pending evidence gates. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2155,10 +2155,10 @@
         <x:v>Run Marlin runtime/model/preference/queue/representative-plan/eval-plan/eval-run/status CLI checks, execute a tiny mock evaluation fixture, verify index refresh, verify Preference apply is blocked when gates fail, run Marlin focused Swift tests, confirm stable Marlin accessibility identifiers, run live non-mock representative-source chunks, verify source-map-aware chunk/checkpoint/caption-only behavior, and leave full batch/preference promotion blocked until representative coverage and aggregate coverage gates pass.</x:v>
       </x:c>
       <x:c r="G62" s="26" t="str">
-        <x:v>Runtime/model/mock/native AX/live 3-source range-chunk pass; full batch preference gate pending</x:v>
+        <x:v>Runtime/model/mock/native AX/live 4-source range-chunk pass; full batch preference gate pending</x:v>
       </x:c>
       <x:c r="H62" s="11" t="str">
-        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. The runtime probe now imports dependency modules in isolated child processes, so the live marlin-runtime-status check no longer emits duplicate AVFoundation class warnings while still reporting every module ready. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path supports --request-timeout-ms / --timeout-ms, and a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4 completed with requestTimeoutMs=900000, wrote inference_mode=live Marlin events, updated segments with marlin_temporal_semantics, and rebuilt an index with 9 search documents. Current passes add per-asset checkpoint writes in runMarlinAnalysis plus --max-sources and --skip-existing through marlin-evaluate, ProjectMarlinEvaluationRunPlan/Runner, marlin-eval-plan, marlin-eval-next, and marlin-eval-run, then make loadMarlinAssetInputs source-map-aware so explicit linked filenames resolve to the correct asset_id when assets.json stores original camera filenames. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and a command carrying those options before source URLs. A /tmp mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. The real lively-alt-vol5 project has live Marlin artifacts for AST_5CAEC24E / 08-jun-a-man-and-a.mp4, AST_25CDF4A5 / 06-jun-two-people-are.mp4, and AST_704DC85D / 02-jan-clip.mp4. The latest code adds --caption-only plus bounded range chunk controls (--chunk-seconds, --chunk-overlap-seconds, --max-chunks) through the TS stage, marlin-evaluate, native CLI plan/run paths, and ProjectMarlinEvaluationRunPlan/Runner; tests verify find queries are not invoked when captionOnly is true and chunk event IDs carry chunk metadata. Verification passed: npx vitest run tests/marlin-normalize.test.ts tests/marlin-proxy.test.ts tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts 29/0, npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0, marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=1, and git diff --check. A live range-chunk caption-only run on 02-jan-clip.mp4 with VOS_MARLIN_PROXY_MAX_WIDTH=256 created .marlin-proxy-cache/ranges/dd2959340fe6d155-0.000-30.000.mp4, completed, and appended AST_704DC85D with 5 events, chunkIndices=[0], and 0 find results. marlin-status now reports assets=3/events=18/findResults=8/segmentsWithMarlinPeak=3/coverage=0.33/canPreferMarlin=true, while repo-level marlin-preference-status remains partially ready with lively-alt-vol5 at 3/9 peak segments and canPreferMarlinAsDefault=false. Full all-source representative live run and repo-level preference promotion remain pending because the real repo gate still needs broader live coverage.</x:v>
+        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. The runtime probe now imports dependency modules in isolated child processes, so the live marlin-runtime-status check no longer emits duplicate AVFoundation class warnings while still reporting every module ready. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path supports --request-timeout-ms / --timeout-ms, and a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4 completed with requestTimeoutMs=900000, wrote inference_mode=live Marlin events, updated segments with marlin_temporal_semantics, and rebuilt an index with 9 search documents. Current passes add per-asset checkpoint writes in runMarlinAnalysis plus --max-sources and --skip-existing through marlin-evaluate, ProjectMarlinEvaluationRunPlan/Runner, marlin-eval-plan, marlin-eval-next, and marlin-eval-run, then make loadMarlinAssetInputs source-map-aware so explicit linked filenames resolve to the correct asset_id when assets.json stores original camera filenames. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and a command carrying those options before source URLs. A /tmp mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. The real lively-alt-vol5 project has live Marlin artifacts for AST_5CAEC24E / 08-jun-a-man-and-a.mp4, AST_25CDF4A5 / 06-jun-two-people-are.mp4, AST_704DC85D / 02-jan-clip.mp4, and AST_09AE639A / 04-jan-clip.mp4. The latest code adds --caption-only plus bounded range chunk controls (--chunk-seconds, --chunk-overlap-seconds, --max-chunks) through the TS stage, marlin-evaluate, native CLI plan/run paths, and ProjectMarlinEvaluationRunPlan/Runner; tests verify find queries are not invoked when captionOnly is true and chunk event IDs carry chunk metadata. Verification passed: npx vitest run tests/marlin-normalize.test.ts tests/marlin-proxy.test.ts tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts 29/0, npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0, marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=1, and git diff --check. Live range-chunk caption-only runs with VOS_MARLIN_PROXY_MAX_WIDTH=256 completed for 02-jan-clip.mp4 chunk 0 and 04-jan-clip.mp4 chunks 0-1. The latest 04-jan run created .marlin-proxy-cache/ranges/0c9587769b484daa-0.000-30.000.mp4 and c038aafd7ae6116a-27.000-57.000.mp4, appended AST_09AE639A with 11 events, chunkIndices=[0,1], and 0 find results, then index-rebuild reported 29 Marlin events, 8 Marlin find results, and 2370 search documents. marlin-status now reports assets=4/events=29/findResults=8/segmentsWithMarlinPeak=4/coverage=0.44/canPreferMarlin=true, while repo-level marlin-preference-status remains partially ready with lively-alt-vol5 at 4/9 peak segments and canPreferMarlinAsDefault=false. Full all-source representative live run and repo-level preference promotion remain pending because the real repo gate still needs broader live coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="48" customHeight="1">
@@ -3784,10 +3784,10 @@
         <x:v>Added --request-timeout-ms and --timeout-ms to scripts/marlin-evaluate.ts, threaded requestTimeoutMs through ProjectMarlinEvaluationRunPlan and ProjectMarlinEvaluationRunner, surfaced it in marlin-eval-plan/marlin-eval-next/marlin-eval-run, added per-asset and per-chunk marlin_events checkpoint writes, exposed --max-sources plus --skip-existing so representative coverage can be accumulated across bounded local runs, added --caption-only to skip find queries for long chunks, and added --chunk-seconds/--chunk-overlap-seconds/--max-chunks so long sources are sliced into cached range proxies before captioning.</x:v>
       </x:c>
       <x:c r="H51" s="26" t="str">
-        <x:v>npx vitest run tests/marlin-normalize.test.ts tests/marlin-proxy.test.ts tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts passed 29 tests, including checkpoint-before-later-timeout, source_map-aware explicit source selection, all-existing skip-existing no-op coverage, caption-only find skipping, deterministic chunk boundaries, range proxy caching, and chunk event IDs; npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0, and git diff --check passed. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=1 printed the chunk options before source URLs. The real lively-alt-vol5 project has live non-mock Marlin evidence for AST_5CAEC24E, AST_25CDF4A5, and AST_704DC85D. The latest live 02-jan-clip.mp4 range run created .marlin-proxy-cache/ranges/dd2959340fe6d155-0.000-30.000.mp4, appended 5 chunk-indexed events, and raised marlin-status to 3 assets, 18 events, 8 find results, 3/9 Marlin peak segments, coverage=0.33, and canPreferMarlin=true. The full 9-source representative live batch and repo-level default preference remain intentionally pending broader evidence.</x:v>
+        <x:v>npx vitest run tests/marlin-normalize.test.ts tests/marlin-proxy.test.ts tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts passed 29 tests, including checkpoint-before-later-timeout, source_map-aware explicit source selection, all-existing skip-existing no-op coverage, caption-only find skipping, deterministic chunk boundaries, range proxy caching, and chunk event IDs; npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0, and git diff --check passed. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=1 printed the chunk options before source URLs. The real lively-alt-vol5 project has live non-mock Marlin evidence for AST_5CAEC24E, AST_25CDF4A5, AST_704DC85D, and AST_09AE639A. The latest live 04-jan-clip.mp4 range run created two cached 30s range proxies, appended 11 chunk-indexed events, and raised marlin-status to 4 assets, 29 events, 8 find results, 4/9 Marlin peak segments, coverage=0.44, and canPreferMarlin=true. index-rebuild reported 29 Marlin events, 8 Marlin find results, and 2370 search documents. The full 9-source representative live batch and repo-level default preference remain intentionally pending broader evidence.</x:v>
       </x:c>
       <x:c r="I51" s="11" t="str">
-        <x:v>Mitigated; live 3/9 range chunks; repo preference gate pending</x:v>
+        <x:v>Mitigated; live 4/9 range chunks; repo preference gate pending</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="48" customHeight="1">
@@ -8658,79 +8658,79 @@
     </x:row>
     <x:row r="213" ht="48" customHeight="1">
       <x:c r="A213" s="10" t="str">
-        <x:v>TL-205</x:v>
+        <x:v>TL-239</x:v>
       </x:c>
       <x:c r="B213" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C213" s="26" t="str">
-        <x:v>Native preview duration fallback</x:v>
+        <x:v>Live Marlin 04-jan range chunks</x:v>
       </x:c>
       <x:c r="D213" s="26" t="str">
-        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
+        <x:v>Run the next lively-alt-vol5 source, 04-jan-clip.mp4, through bounded caption-only Marlin range chunks; rebuild the SQLite index; inspect project and repo preference status.</x:v>
       </x:c>
       <x:c r="E213" s="26" t="str">
-        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
+        <x:v>VOS_MARLIN_PROXY_MAX_WIDTH=256 npx tsx scripts/marlin-evaluate.ts --project projects/lively-alt-vol5 --repo-root &lt;repo&gt; --request-timeout-ms 900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=2 &lt;04-jan-clip.mp4&gt; completed. It created .marlin-proxy-cache/ranges/0c9587769b484daa-0.000-30.000.mp4 and c038aafd7ae6116a-27.000-57.000.mp4, then wrote AST_09AE639A / 02_media/04-jan-clip.mp4 with 11 events, chunkIndices=[0,1], and 0 find results. index-rebuild reported 2370 searchDocuments, 29 marlinEvents, and 8 marlinFindResults. marlin-status now reports assets=4/events=29/findResults=8/segmentsWithMarlinPeak=4/coverage=0.44/canPreferMarlin=true; marlin-preference-status remains partially ready with lively-alt-vol5 at 4/9 peak segments, aggregateCoverage=0.13, and canPreferMarlinAsDefault=false.</x:v>
       </x:c>
       <x:c r="F213" s="11" t="str">
-        <x:v>Native pixel/runtime pass</x:v>
+        <x:v>Live 4/9 representative progress; repo preference gate pending</x:v>
       </x:c>
     </x:row>
     <x:row r="214" ht="48" customHeight="1">
       <x:c r="A214" s="10" t="str">
-        <x:v>TL-206</x:v>
+        <x:v>TL-205</x:v>
       </x:c>
       <x:c r="B214" s="26" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C214" s="26" t="str">
-        <x:v>Native Clip Inspector save and clear</x:v>
+        <x:v>Native preview duration fallback</x:v>
       </x:c>
       <x:c r="D214" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
+        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
       </x:c>
       <x:c r="E214" s="26" t="str">
-        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
+        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F214" s="11" t="str">
-        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
+        <x:v>Native pixel/runtime pass</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="48" customHeight="1">
       <x:c r="A215" s="10" t="str">
-        <x:v>TL-207</x:v>
+        <x:v>TL-206</x:v>
       </x:c>
       <x:c r="B215" s="26" t="str">
-        <x:v>US-058</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C215" s="26" t="str">
-        <x:v>Native QA Dashboard issue jump</x:v>
+        <x:v>Native Clip Inspector save and clear</x:v>
       </x:c>
       <x:c r="D215" s="26" t="str">
-        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
+        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
       </x:c>
       <x:c r="E215" s="26" t="str">
-        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
+        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
       </x:c>
       <x:c r="F215" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="48" customHeight="1">
       <x:c r="A216" s="10" t="str">
-        <x:v>TL-208</x:v>
+        <x:v>TL-207</x:v>
       </x:c>
       <x:c r="B216" s="26" t="str">
-        <x:v>US-056</x:v>
+        <x:v>US-058</x:v>
       </x:c>
       <x:c r="C216" s="26" t="str">
-        <x:v>Native Candidate Swap sheet and staging</x:v>
+        <x:v>Native QA Dashboard issue jump</x:v>
       </x:c>
       <x:c r="D216" s="26" t="str">
-        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
+        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
       </x:c>
       <x:c r="E216" s="26" t="str">
-        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
+        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
       </x:c>
       <x:c r="F216" s="11" t="str">
         <x:v>Native AX/pixel pass</x:v>
@@ -8738,339 +8738,339 @@
     </x:row>
     <x:row r="217" ht="48" customHeight="1">
       <x:c r="A217" s="10" t="str">
-        <x:v>TL-209</x:v>
+        <x:v>TL-208</x:v>
       </x:c>
       <x:c r="B217" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-056</x:v>
       </x:c>
       <x:c r="C217" s="26" t="str">
-        <x:v>Native exact preview regeneration</x:v>
+        <x:v>Native Candidate Swap sheet and staging</x:v>
       </x:c>
       <x:c r="D217" s="26" t="str">
-        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
+        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
       </x:c>
       <x:c r="E217" s="26" t="str">
-        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
       </x:c>
       <x:c r="F217" s="11" t="str">
-        <x:v>Native exact preview pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="48" customHeight="1">
       <x:c r="A218" s="10" t="str">
-        <x:v>TL-210</x:v>
+        <x:v>TL-209</x:v>
       </x:c>
       <x:c r="B218" s="26" t="str">
-        <x:v>US-047</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C218" s="26" t="str">
-        <x:v>Native Command Palette top-bar open/close</x:v>
+        <x:v>Native exact preview regeneration</x:v>
       </x:c>
       <x:c r="D218" s="26" t="str">
-        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
+        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
       </x:c>
       <x:c r="E218" s="26" t="str">
-        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
+        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F218" s="11" t="str">
-        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
+        <x:v>Native exact preview pass</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="48" customHeight="1">
       <x:c r="A219" s="10" t="str">
-        <x:v>TL-211</x:v>
+        <x:v>TL-210</x:v>
       </x:c>
       <x:c r="B219" s="26" t="str">
         <x:v>US-047</x:v>
       </x:c>
       <x:c r="C219" s="26" t="str">
-        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
+        <x:v>Native Command Palette top-bar open/close</x:v>
       </x:c>
       <x:c r="D219" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
+        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
       </x:c>
       <x:c r="E219" s="26" t="str">
-        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
+        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
       </x:c>
       <x:c r="F219" s="11" t="str">
-        <x:v>Native keyboard/AX pass</x:v>
+        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="48" customHeight="1">
       <x:c r="A220" s="10" t="str">
-        <x:v>TL-212</x:v>
+        <x:v>TL-211</x:v>
       </x:c>
       <x:c r="B220" s="26" t="str">
-        <x:v>US-048</x:v>
+        <x:v>US-047</x:v>
       </x:c>
       <x:c r="C220" s="26" t="str">
-        <x:v>Native Agent panel session lifecycle</x:v>
+        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
       </x:c>
       <x:c r="D220" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
+        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
       </x:c>
       <x:c r="E220" s="26" t="str">
-        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
+        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
       </x:c>
       <x:c r="F220" s="11" t="str">
-        <x:v>Native AX/computer-use pass</x:v>
+        <x:v>Native keyboard/AX pass</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="48" customHeight="1">
       <x:c r="A221" s="10" t="str">
-        <x:v>TL-213</x:v>
+        <x:v>TL-212</x:v>
       </x:c>
       <x:c r="B221" s="26" t="str">
-        <x:v>US-049</x:v>
+        <x:v>US-048</x:v>
       </x:c>
       <x:c r="C221" s="26" t="str">
-        <x:v>Native Status agent job read-only turn</x:v>
+        <x:v>Native Agent panel session lifecycle</x:v>
       </x:c>
       <x:c r="D221" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
       </x:c>
       <x:c r="E221" s="26" t="str">
-        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
+        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F221" s="11" t="str">
-        <x:v>Native read-only job pass; approved write pending</x:v>
+        <x:v>Native AX/computer-use pass</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="48" customHeight="1">
       <x:c r="A222" s="10" t="str">
-        <x:v>TL-214</x:v>
+        <x:v>TL-213</x:v>
       </x:c>
       <x:c r="B222" s="26" t="str">
-        <x:v>US-050</x:v>
+        <x:v>US-049</x:v>
       </x:c>
       <x:c r="C222" s="26" t="str">
-        <x:v>Native Project readiness/action queue Copy pass</x:v>
+        <x:v>Native Status agent job read-only turn</x:v>
       </x:c>
       <x:c r="D222" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
       </x:c>
       <x:c r="E222" s="26" t="str">
-        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
+        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F222" s="11" t="str">
-        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
+        <x:v>Native read-only job pass; approved write pending</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="48" customHeight="1">
       <x:c r="A223" s="10" t="str">
-        <x:v>TL-215</x:v>
+        <x:v>TL-214</x:v>
       </x:c>
       <x:c r="B223" s="26" t="str">
-        <x:v>US-051</x:v>
+        <x:v>US-050</x:v>
       </x:c>
       <x:c r="C223" s="26" t="str">
-        <x:v>Native local Source Analysis button</x:v>
+        <x:v>Native Project readiness/action queue Copy pass</x:v>
       </x:c>
       <x:c r="D223" s="26" t="str">
-        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
       </x:c>
       <x:c r="E223" s="26" t="str">
-        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
+        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
       </x:c>
       <x:c r="F223" s="11" t="str">
-        <x:v>Native local analysis pass</x:v>
+        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="48" customHeight="1">
       <x:c r="A224" s="10" t="str">
-        <x:v>TL-216</x:v>
+        <x:v>TL-215</x:v>
       </x:c>
       <x:c r="B224" s="26" t="str">
-        <x:v>US-052</x:v>
+        <x:v>US-051</x:v>
       </x:c>
       <x:c r="C224" s="26" t="str">
-        <x:v>Native Rough Cut and Review Patch buttons</x:v>
+        <x:v>Native local Source Analysis button</x:v>
       </x:c>
       <x:c r="D224" s="26" t="str">
-        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
+        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E224" s="26" t="str">
-        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
       </x:c>
       <x:c r="F224" s="11" t="str">
-        <x:v>Native compile/review patch pass</x:v>
+        <x:v>Native local analysis pass</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="48" customHeight="1">
       <x:c r="A225" s="10" t="str">
-        <x:v>TL-217</x:v>
+        <x:v>TL-216</x:v>
       </x:c>
       <x:c r="B225" s="26" t="str">
-        <x:v>US-053</x:v>
+        <x:v>US-052</x:v>
       </x:c>
       <x:c r="C225" s="26" t="str">
-        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
+        <x:v>Native Rough Cut and Review Patch buttons</x:v>
       </x:c>
       <x:c r="D225" s="26" t="str">
-        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
+        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E225" s="26" t="str">
-        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
+        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F225" s="11" t="str">
-        <x:v>Native timeline/context menu pass</x:v>
+        <x:v>Native compile/review patch pass</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="48" customHeight="1">
       <x:c r="A226" s="10" t="str">
-        <x:v>TL-218</x:v>
+        <x:v>TL-217</x:v>
       </x:c>
       <x:c r="B226" s="26" t="str">
-        <x:v>US-054</x:v>
+        <x:v>US-053</x:v>
       </x:c>
       <x:c r="C226" s="26" t="str">
-        <x:v>Native Studio feedback Apply and Undo</x:v>
+        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
       </x:c>
       <x:c r="D226" s="26" t="str">
-        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
+        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
       </x:c>
       <x:c r="E226" s="26" t="str">
-        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
       </x:c>
       <x:c r="F226" s="11" t="str">
-        <x:v>Native apply/undo pass</x:v>
+        <x:v>Native timeline/context menu pass</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="48" customHeight="1">
       <x:c r="A227" s="10" t="str">
-        <x:v>TL-219</x:v>
+        <x:v>TL-218</x:v>
       </x:c>
       <x:c r="B227" s="26" t="str">
-        <x:v>US-057</x:v>
+        <x:v>US-054</x:v>
       </x:c>
       <x:c r="C227" s="26" t="str">
-        <x:v>Native Footage Search sheet and replacement staging</x:v>
+        <x:v>Native Studio feedback Apply and Undo</x:v>
       </x:c>
       <x:c r="D227" s="26" t="str">
-        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
+        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E227" s="26" t="str">
-        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
+        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F227" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native apply/undo pass</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="48" customHeight="1">
       <x:c r="A228" s="10" t="str">
-        <x:v>TL-220</x:v>
+        <x:v>TL-219</x:v>
       </x:c>
       <x:c r="B228" s="26" t="str">
-        <x:v>US-066</x:v>
+        <x:v>US-057</x:v>
       </x:c>
       <x:c r="C228" s="26" t="str">
-        <x:v>Native Settings transport picker mutation</x:v>
+        <x:v>Native Footage Search sheet and replacement staging</x:v>
       </x:c>
       <x:c r="D228" s="26" t="str">
-        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
+        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
       </x:c>
       <x:c r="E228" s="26" t="str">
-        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
       </x:c>
       <x:c r="F228" s="11" t="str">
-        <x:v>Native Settings picker mutation pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="48" customHeight="1">
       <x:c r="A229" s="10" t="str">
-        <x:v>TL-221</x:v>
+        <x:v>TL-220</x:v>
       </x:c>
       <x:c r="B229" s="26" t="str">
-        <x:v>US-059</x:v>
+        <x:v>US-066</x:v>
       </x:c>
       <x:c r="C229" s="26" t="str">
-        <x:v>Native Media Relink buttons and source-map relink</x:v>
+        <x:v>Native Settings transport picker mutation</x:v>
       </x:c>
       <x:c r="D229" s="26" t="str">
-        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
+        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
       </x:c>
       <x:c r="E229" s="26" t="str">
-        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
+        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F229" s="11" t="str">
-        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
+        <x:v>Native Settings picker mutation pass</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="48" customHeight="1">
       <x:c r="A230" s="10" t="str">
-        <x:v>TL-222</x:v>
+        <x:v>TL-221</x:v>
       </x:c>
       <x:c r="B230" s="26" t="str">
-        <x:v>US-060</x:v>
+        <x:v>US-059</x:v>
       </x:c>
       <x:c r="C230" s="26" t="str">
-        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
+        <x:v>Native Media Relink buttons and source-map relink</x:v>
       </x:c>
       <x:c r="D230" s="26" t="str">
-        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
+        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
       </x:c>
       <x:c r="E230" s="26" t="str">
-        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
+        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
       </x:c>
       <x:c r="F230" s="11" t="str">
-        <x:v>Native synthetic/proxy/smoke button pass</x:v>
+        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="48" customHeight="1">
       <x:c r="A231" s="10" t="str">
-        <x:v>TL-223</x:v>
+        <x:v>TL-222</x:v>
       </x:c>
       <x:c r="B231" s="26" t="str">
-        <x:v>US-046</x:v>
+        <x:v>US-060</x:v>
       </x:c>
       <x:c r="C231" s="26" t="str">
-        <x:v>Native New Project from Source</x:v>
+        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
       </x:c>
       <x:c r="D231" s="26" t="str">
-        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
+        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
       </x:c>
       <x:c r="E231" s="26" t="str">
-        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
+        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
       </x:c>
       <x:c r="F231" s="11" t="str">
-        <x:v>Native project creation/NSOpenPanel pass</x:v>
+        <x:v>Native synthetic/proxy/smoke button pass</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="48" customHeight="1">
       <x:c r="A232" s="10" t="str">
-        <x:v>TL-224</x:v>
+        <x:v>TL-223</x:v>
       </x:c>
       <x:c r="B232" s="26" t="str">
-        <x:v>US-062</x:v>
+        <x:v>US-046</x:v>
       </x:c>
       <x:c r="C232" s="26" t="str">
-        <x:v>Native MediaPanel Audio Story Graph button</x:v>
+        <x:v>Native New Project from Source</x:v>
       </x:c>
       <x:c r="D232" s="26" t="str">
-        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
+        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
       </x:c>
       <x:c r="E232" s="26" t="str">
-        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
       </x:c>
       <x:c r="F232" s="11" t="str">
-        <x:v>Native AX/UI/CLI pass</x:v>
+        <x:v>Native project creation/NSOpenPanel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="48" customHeight="1">
       <x:c r="A233" s="10" t="str">
-        <x:v>TL-225</x:v>
+        <x:v>TL-224</x:v>
       </x:c>
       <x:c r="B233" s="26" t="str">
-        <x:v>US-063</x:v>
+        <x:v>US-062</x:v>
       </x:c>
       <x:c r="C233" s="26" t="str">
-        <x:v>Native Render Final Package button</x:v>
+        <x:v>Native MediaPanel Audio Story Graph button</x:v>
       </x:c>
       <x:c r="D233" s="26" t="str">
-        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
+        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E233" s="26" t="str">
-        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F233" s="11" t="str">
         <x:v>Native AX/UI/CLI pass</x:v>
@@ -9078,121 +9078,141 @@
     </x:row>
     <x:row r="234" ht="48" customHeight="1">
       <x:c r="A234" s="10" t="str">
-        <x:v>TL-226</x:v>
+        <x:v>TL-225</x:v>
       </x:c>
       <x:c r="B234" s="26" t="str">
-        <x:v>US-064</x:v>
+        <x:v>US-063</x:v>
       </x:c>
       <x:c r="C234" s="26" t="str">
-        <x:v>Native Editor Handoff export and Finder reveal</x:v>
+        <x:v>Native Render Final Package button</x:v>
       </x:c>
       <x:c r="D234" s="26" t="str">
-        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
+        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
       </x:c>
       <x:c r="E234" s="26" t="str">
-        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
+        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F234" s="11" t="str">
-        <x:v>Native AX/UI/Finder/CLI pass</x:v>
+        <x:v>Native AX/UI/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="48" customHeight="1">
       <x:c r="A235" s="10" t="str">
-        <x:v>TL-227</x:v>
+        <x:v>TL-226</x:v>
       </x:c>
       <x:c r="B235" s="26" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-064</x:v>
       </x:c>
       <x:c r="C235" s="26" t="str">
-        <x:v>Native Ask Codex editor-note proposal</x:v>
+        <x:v>Native Editor Handoff export and Finder reveal</x:v>
       </x:c>
       <x:c r="D235" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
+        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E235" s="26" t="str">
-        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
+        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
       </x:c>
       <x:c r="F235" s="11" t="str">
-        <x:v>Native read-only Codex proposal pass</x:v>
+        <x:v>Native AX/UI/Finder/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="236" ht="48" customHeight="1">
       <x:c r="A236" s="10" t="str">
-        <x:v>TL-228</x:v>
+        <x:v>TL-227</x:v>
       </x:c>
       <x:c r="B236" s="26" t="str">
-        <x:v>US-061</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C236" s="26" t="str">
-        <x:v>Live Marlin single-source completion</x:v>
+        <x:v>Native Ask Codex editor-note proposal</x:v>
       </x:c>
       <x:c r="D236" s="26" t="str">
-        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
+        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
       </x:c>
       <x:c r="E236" s="26" t="str">
-        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
+        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
       </x:c>
       <x:c r="F236" s="11" t="str">
-        <x:v>Live single-source pass; full representative batch pending</x:v>
+        <x:v>Native read-only Codex proposal pass</x:v>
       </x:c>
     </x:row>
     <x:row r="237" ht="48" customHeight="1">
       <x:c r="A237" s="10" t="str">
-        <x:v>TL-229</x:v>
+        <x:v>TL-228</x:v>
       </x:c>
       <x:c r="B237" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C237" s="26" t="str">
-        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+        <x:v>Live Marlin single-source completion</x:v>
       </x:c>
       <x:c r="D237" s="26" t="str">
-        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
       </x:c>
       <x:c r="E237" s="26" t="str">
-        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
       </x:c>
       <x:c r="F237" s="11" t="str">
-        <x:v>Native fresh-launch pixel pass</x:v>
+        <x:v>Live single-source pass; full representative batch pending</x:v>
       </x:c>
     </x:row>
     <x:row r="238" ht="48" customHeight="1">
       <x:c r="A238" s="10" t="str">
-        <x:v>TL-230</x:v>
+        <x:v>TL-229</x:v>
       </x:c>
       <x:c r="B238" s="26" t="str">
         <x:v>US-045</x:v>
       </x:c>
       <x:c r="C238" s="26" t="str">
+        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+      </x:c>
+      <x:c r="D238" s="26" t="str">
+        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+      </x:c>
+      <x:c r="E238" s="26" t="str">
+        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+      </x:c>
+      <x:c r="F238" s="11" t="str">
+        <x:v>Native fresh-launch pixel pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" ht="48" customHeight="1">
+      <x:c r="A239" s="10" t="str">
+        <x:v>TL-230</x:v>
+      </x:c>
+      <x:c r="B239" s="26" t="str">
+        <x:v>US-045</x:v>
+      </x:c>
+      <x:c r="C239" s="26" t="str">
         <x:v>AX-1 exact preview promotion and pixel pass</x:v>
       </x:c>
-      <x:c r="D238" s="26" t="str">
+      <x:c r="D239" s="26" t="str">
         <x:v>Run videoos-studio-cli compile-run on projects/ax1-participant-voices-20260401, confirm playback-contract-status, select ProjectShelf.ax1-participant-voices-20260401 in VideoOSStudio, capture /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and run Retina-coordinate pixel statistics on the Viewer region.</x:v>
       </x:c>
-      <x:c r="E238" s="26" t="str">
+      <x:c r="E239" s="26" t="str">
         <x:v>Before compile, playback-contract-status returned legacy_manifest and approvalGrade=false. compile-run completed with exitCode=0, timeline compiled, indexDocuments=492, and git status stayed clean. After compile, playback-contract-status returned state=exact, approvalGrade=true, timelineHash=171378fe2bfe3a7c, and manifestBaseTimelineHash=171378fe2bfe3a7c. Native Viewer showed Exact preview / preview-editor-1775121573933.mp4 and Timeline preview D4887.MP4 with a visible interview frame. Screenshot was 3.5M; viewer_person_actual mean_rgb=(144.62,141.42,149.8) and near_black_pct=0.0004, while left pillarbox near_black_pct=1.0000 as expected.</x:v>
       </x:c>
-      <x:c r="F238" s="11" t="str">
+      <x:c r="F239" s="11" t="str">
         <x:v>Native AX-1 exact/pixel pass</x:v>
       </x:c>
     </x:row>
-    <x:row r="239" ht="48" customHeight="1">
-      <x:c r="A239" s="12" t="str">
+    <x:row r="240" ht="48" customHeight="1">
+      <x:c r="A240" s="12" t="str">
         <x:v>TL-231</x:v>
       </x:c>
-      <x:c r="B239" s="27" t="str">
+      <x:c r="B240" s="27" t="str">
         <x:v>US-050</x:v>
       </x:c>
-      <x:c r="C239" s="27" t="str">
+      <x:c r="C240" s="27" t="str">
         <x:v>Native Action Queue approval gate</x:v>
       </x:c>
-      <x:c r="D239" s="27" t="str">
+      <x:c r="D240" s="27" t="str">
         <x:v>Add ProjectPanel.ActionQueue* identifiers, relaunch VideoOSStudio, select AX-1 Project tab, inspect the Action Queue AX tree, click ProjectPanel.ActionQueueRunButton.rough-cut-review, and stop at the Codex approval gate without approving writes.</x:v>
       </x:c>
-      <x:c r="E239" s="27" t="str">
+      <x:c r="E240" s="27" t="str">
         <x:v>AX exposed ProjectPanel.ActionQueueRunButton.rough-cut-review, ProjectPanel.ActionQueueCopyButton.rough-cut-review, ProjectPanel.ActionQueueRunButton.marlin-default, and ProjectPanel.ActionQueueCopyButton.marlin-default. Clicking rough-cut-review changed the row to disabled Starting Codex session for Review..., then to Opening Codex approval gate for Review. ps showed a Codex app-server child under VideoOSStudio; git status listed only the intentional ProjectInspectorViews.swift edit, and projects/ax1-participant-voices-20260401/06_review still contained only human_notes.yaml.</x:v>
       </x:c>
-      <x:c r="F239" s="13" t="str">
+      <x:c r="F240" s="13" t="str">
         <x:v>Native approval-gate pass; write not approved</x:v>
       </x:c>
     </x:row>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R2640a1442cf94924"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R6ef50d727c544752"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R41c9d95ddfbe41fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R47636d119a1642cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R4687bd9be600466f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R05a6e5f86eff4234"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rc15c7786b88f425b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R962656ccb9d64bb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R9a18e121d17a4cf9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R8cd90eb3a0354bd8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -439,7 +439,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 21:00 JST</x:v>
+        <x:v>2026-06-23 21:15 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -495,7 +495,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-061 pass advanced bounded caption-only Marlin range chunks on lively-alt-vol5. Prior implementation validation remains green: npx vitest run tests/marlin-normalize.test.ts tests/marlin-proxy.test.ts tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts passed 29/0, npx tsc --noEmit --pretty false passed, node --check scripts/marlin-evaluate.ts passed, swift build --target VideoOSStudioCLI passed, swift test --filter ProjectMarlinEvaluationRunPlanTests passed 11/0, and git diff --check passed. Live non-mock runs now cover AST_5CAEC24E / 08-jun-a-man-and-a.mp4, AST_25CDF4A5 / 06-jun-two-people-are.mp4, AST_704DC85D / 02-jan-clip.mp4 first 30s range chunk, and AST_09AE639A / 04-jan-clip.mp4 first two 30s range chunks. lively-alt-vol5 now has 4 assets, 29 events, 8 find results, coverage=0.44, and canPreferMarlin=true; index-rebuild reports 2370 searchDocuments. Repo-level canPreferMarlinAsDefault remains false pending broader coverage.</x:v>
+        <x:v>Latest US-061 pass completed bounded caption-only Marlin range chunks for all 9 lively-alt-vol5 representative sources. Prior implementation validation remains green: npx vitest run tests/marlin-normalize.test.ts tests/marlin-proxy.test.ts tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts passed 29/0, npx tsc --noEmit --pretty false passed, node --check scripts/marlin-evaluate.ts passed, swift build --target VideoOSStudioCLI passed, swift test --filter ProjectMarlinEvaluationRunPlanTests passed 11/0, and git diff --check passed. Live non-mock runs now cover 08-jun, 06-jun, 02-jan, 04-jan, 03-jan, 07-jun, 05-jun, 01-jan, and 09-jun. lively-alt-vol5 now has 9 assets, 84 events, 8 find results, coverage=1.00, and canPreferMarlin=true; index-rebuild reports 2425 searchDocuments. Repo-level canPreferMarlinAsDefault remains false pending broader cross-project coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -503,7 +503,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest runtime/macOS CLI check is the US-061 04-jan bounded range chunk pass: live 04-jan-clip.mp4 created .marlin-proxy-cache/ranges/0c9587769b484daa-0.000-30.000.mp4 and c038aafd7ae6116a-27.000-57.000.mp4, completed, and appended AST_09AE639A with chunkIndices=[0,1]. marlin-status now reports 4 assets / 29 events / 8 find results / coverage=0.44 / canPreferMarlin=true for lively-alt-vol5; marlin-preference-status still keeps canPreferMarlinAsDefault=false because aggregate repo coverage remains 0.13 and only 5 projects are candidates. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live single-source completion, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest runtime/macOS CLI check is the US-061 9-source representative completion: marlin-status reports 9 assets / 84 events / 8 find results / coverage=1.00 / canPreferMarlin=true for lively-alt-vol5, and marlin-preference-status reports lively-alt-vol5 9/9 peak segments while the repo remains canPreferMarlinAsDefault=false because aggregateCoverage is 0.15 and other evaluated projects remain below gate. The final live pass added 03-jan, 07-jun, 05-jun, 01-jan, and 09-jun bounded chunks after the earlier 02-jan and 04-jan chunk passes. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live single-source completion, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -527,7 +527,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility, Copy behavior, stable action-scoped AX identifiers, and rough-cut-review Start &amp; Run stopping at the Codex approval gate; approved workspace-write review execution, Final render Open, and Marlin default Open remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-065 is promoted for native SQLite/RAG Search/Add, cited Agent prompt insertion, and InspectorTab.* Agent/Media switching without AX hangs. US-061 is promoted for runtime/model/mock/native AX, live non-mock representative chunks on lively-alt-vol5, source-map-aware chunk controls, resumable checkpointed evaluation, caption-only CLI support, and bounded 30s range chunking that made 02-jan-clip.mp4 and 04-jan-clip.mp4 contribute live Marlin assets. The remaining 5/9 lively-alt-vol5 peak segments and repo-level Marlin-first preference promotion remain pending evidence gates. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility, Copy behavior, stable action-scoped AX identifiers, and rough-cut-review Start &amp; Run stopping at the Codex approval gate; approved workspace-write review execution and Final render Open remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-065 is promoted for native SQLite/RAG Search/Add, cited Agent prompt insertion, and InspectorTab.* Agent/Media switching without AX hangs. US-061 is promoted for runtime/model/mock/native AX, live non-mock representative chunks on lively-alt-vol5, source-map-aware chunk controls, resumable checkpointed evaluation, caption-only CLI support, and bounded range chunking across all 9 lively-alt-vol5 representative sources; repo-level Marlin-first preference promotion remains pending because aggregate project coverage is still below gate. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2152,13 +2152,13 @@
         <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:48-160; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1296-1325,2326-2481; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRuntimeStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinModelAccessStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationQueue.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRepresentativePlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationRunPlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinPreferenceDecision.swift; runtime/pipeline/stages/marlin.ts; scripts/marlin-evaluate.ts</x:v>
       </x:c>
       <x:c r="F62" s="26" t="str">
-        <x:v>Run Marlin runtime/model/preference/queue/representative-plan/eval-plan/eval-run/status CLI checks, execute a tiny mock evaluation fixture, verify index refresh, verify Preference apply is blocked when gates fail, run Marlin focused Swift tests, confirm stable Marlin accessibility identifiers, run live non-mock representative-source chunks, verify source-map-aware chunk/checkpoint/caption-only behavior, and leave full batch/preference promotion blocked until representative coverage and aggregate coverage gates pass.</x:v>
+        <x:v>Run Marlin runtime/model/preference/queue/representative-plan/eval-plan/eval-run/status CLI checks, execute a tiny mock evaluation fixture, verify index refresh, verify Preference apply is blocked when gates fail, run Marlin focused Swift tests, confirm stable Marlin accessibility identifiers, run live non-mock representative-source chunks, verify source-map-aware chunk/checkpoint/caption-only behavior, and leave repo-level preference promotion blocked until aggregate evidence gates pass.</x:v>
       </x:c>
       <x:c r="G62" s="26" t="str">
-        <x:v>Runtime/model/mock/native AX/live 4-source range-chunk pass; full batch preference gate pending</x:v>
+        <x:v>Runtime/model/mock/native AX/live 9-source representative pass; repo preference gate pending</x:v>
       </x:c>
       <x:c r="H62" s="11" t="str">
-        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. The runtime probe now imports dependency modules in isolated child processes, so the live marlin-runtime-status check no longer emits duplicate AVFoundation class warnings while still reporting every module ready. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path supports --request-timeout-ms / --timeout-ms, and a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4 completed with requestTimeoutMs=900000, wrote inference_mode=live Marlin events, updated segments with marlin_temporal_semantics, and rebuilt an index with 9 search documents. Current passes add per-asset checkpoint writes in runMarlinAnalysis plus --max-sources and --skip-existing through marlin-evaluate, ProjectMarlinEvaluationRunPlan/Runner, marlin-eval-plan, marlin-eval-next, and marlin-eval-run, then make loadMarlinAssetInputs source-map-aware so explicit linked filenames resolve to the correct asset_id when assets.json stores original camera filenames. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and a command carrying those options before source URLs. A /tmp mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. The real lively-alt-vol5 project has live Marlin artifacts for AST_5CAEC24E / 08-jun-a-man-and-a.mp4, AST_25CDF4A5 / 06-jun-two-people-are.mp4, AST_704DC85D / 02-jan-clip.mp4, and AST_09AE639A / 04-jan-clip.mp4. The latest code adds --caption-only plus bounded range chunk controls (--chunk-seconds, --chunk-overlap-seconds, --max-chunks) through the TS stage, marlin-evaluate, native CLI plan/run paths, and ProjectMarlinEvaluationRunPlan/Runner; tests verify find queries are not invoked when captionOnly is true and chunk event IDs carry chunk metadata. Verification passed: npx vitest run tests/marlin-normalize.test.ts tests/marlin-proxy.test.ts tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts 29/0, npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0, marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=1, and git diff --check. Live range-chunk caption-only runs with VOS_MARLIN_PROXY_MAX_WIDTH=256 completed for 02-jan-clip.mp4 chunk 0 and 04-jan-clip.mp4 chunks 0-1. The latest 04-jan run created .marlin-proxy-cache/ranges/0c9587769b484daa-0.000-30.000.mp4 and c038aafd7ae6116a-27.000-57.000.mp4, appended AST_09AE639A with 11 events, chunkIndices=[0,1], and 0 find results, then index-rebuild reported 29 Marlin events, 8 Marlin find results, and 2370 search documents. marlin-status now reports assets=4/events=29/findResults=8/segmentsWithMarlinPeak=4/coverage=0.44/canPreferMarlin=true, while repo-level marlin-preference-status remains partially ready with lively-alt-vol5 at 4/9 peak segments and canPreferMarlinAsDefault=false. Full all-source representative live run and repo-level preference promotion remain pending because the real repo gate still needs broader live coverage.</x:v>
+        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. The runtime probe now imports dependency modules in isolated child processes, so the live marlin-runtime-status check no longer emits duplicate AVFoundation class warnings while still reporting every module ready. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path supports --request-timeout-ms / --timeout-ms, and a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4 completed with requestTimeoutMs=900000, wrote inference_mode=live Marlin events, updated segments with marlin_temporal_semantics, and rebuilt an index with 9 search documents. Current passes add per-asset checkpoint writes in runMarlinAnalysis plus --max-sources and --skip-existing through marlin-evaluate, ProjectMarlinEvaluationRunPlan/Runner, marlin-eval-plan, marlin-eval-next, and marlin-eval-run, then make loadMarlinAssetInputs source-map-aware so explicit linked filenames resolve to the correct asset_id when assets.json stores original camera filenames. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and a command carrying those options before source URLs. A /tmp mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. The latest code adds --caption-only plus bounded range chunk controls (--chunk-seconds, --chunk-overlap-seconds, --max-chunks) through the TS stage, marlin-evaluate, native CLI plan/run paths, and ProjectMarlinEvaluationRunPlan/Runner; tests verify find queries are not invoked when captionOnly is true and chunk event IDs carry chunk metadata. Verification passed: npx vitest run tests/marlin-normalize.test.ts tests/marlin-proxy.test.ts tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts 29/0, npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0, marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=1, and git diff --check. Live range-chunk caption-only runs with VOS_MARLIN_PROXY_MAX_WIDTH=256 completed for all 9 lively-alt-vol5 sources: existing full-source passes cover 08-jun-a-man-and-a.mp4 and 06-jun-two-people-are.mp4, while bounded chunk passes cover 02-jan-clip.mp4, 04-jan-clip.mp4, 03-jan-clip.mp4, 07-jun-clip.mp4, 05-jun-clip.mp4, 01-jan-clip.mp4, and 09-jun-clip.mp4. The final artifact has 9 items, 84 events, 8 find results, and chunked assets all carry chunkIndices [0] or [0,1]. index-rebuild reported 84 Marlin events, 8 Marlin find results, and 2425 search documents. marlin-status now reports assets=9/events=84/findResults=8/segmentsWithMarlinPeak=9/coverage=1.00/canPreferMarlin=true, while repo-level marlin-preference-status remains partially ready with lively-alt-vol5 at 9/9 peak segments, aggregateCoverage=0.15, and canPreferMarlinAsDefault=false. Repo-level preference promotion remains pending because other evaluated projects still lack enough Marlin-derived peak coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="48" customHeight="1">
@@ -3775,7 +3775,7 @@
         <x:v>macOS runtime/logistics</x:v>
       </x:c>
       <x:c r="E51" s="26" t="str">
-        <x:v>Live representative Marlin evaluation can accumulate sources incrementally, but full-source local MPS caption runs are still too slow for broad unattended representative batches.</x:v>
+        <x:v>Live representative Marlin evaluation can accumulate sources incrementally, but repo-level Marlin-first default promotion still needs broader coverage across other evaluated projects.</x:v>
       </x:c>
       <x:c r="F51" s="26" t="str">
         <x:v>The initial worker request timeout was fixed at the connector default of 300000ms unless VOS_MARLIN_REQUEST_TIMEOUT_MS was set manually; the native CLI plan/run path did not expose a per-run timeout for slow Apple Silicon live caption passes; completed assets were only written after the whole asset loop finished; and caption-only still passed the full source/proxy into the Marlin caption call, so long clips could spend the entire 900000ms budget before returning.</x:v>
@@ -3784,10 +3784,10 @@
         <x:v>Added --request-timeout-ms and --timeout-ms to scripts/marlin-evaluate.ts, threaded requestTimeoutMs through ProjectMarlinEvaluationRunPlan and ProjectMarlinEvaluationRunner, surfaced it in marlin-eval-plan/marlin-eval-next/marlin-eval-run, added per-asset and per-chunk marlin_events checkpoint writes, exposed --max-sources plus --skip-existing so representative coverage can be accumulated across bounded local runs, added --caption-only to skip find queries for long chunks, and added --chunk-seconds/--chunk-overlap-seconds/--max-chunks so long sources are sliced into cached range proxies before captioning.</x:v>
       </x:c>
       <x:c r="H51" s="26" t="str">
-        <x:v>npx vitest run tests/marlin-normalize.test.ts tests/marlin-proxy.test.ts tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts passed 29 tests, including checkpoint-before-later-timeout, source_map-aware explicit source selection, all-existing skip-existing no-op coverage, caption-only find skipping, deterministic chunk boundaries, range proxy caching, and chunk event IDs; npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0, and git diff --check passed. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=1 printed the chunk options before source URLs. The real lively-alt-vol5 project has live non-mock Marlin evidence for AST_5CAEC24E, AST_25CDF4A5, AST_704DC85D, and AST_09AE639A. The latest live 04-jan-clip.mp4 range run created two cached 30s range proxies, appended 11 chunk-indexed events, and raised marlin-status to 4 assets, 29 events, 8 find results, 4/9 Marlin peak segments, coverage=0.44, and canPreferMarlin=true. index-rebuild reported 29 Marlin events, 8 Marlin find results, and 2370 search documents. The full 9-source representative live batch and repo-level default preference remain intentionally pending broader evidence.</x:v>
+        <x:v>npx vitest run tests/marlin-normalize.test.ts tests/marlin-proxy.test.ts tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts passed 29 tests, including checkpoint-before-later-timeout, source_map-aware explicit source selection, all-existing skip-existing no-op coverage, caption-only find skipping, deterministic chunk boundaries, range proxy caching, and chunk event IDs; npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0, and git diff --check passed. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=1 printed the chunk options before source URLs. The real lively-alt-vol5 project now has live non-mock Marlin evidence for all 9 sources. Bounded caption-only runs completed for 03-jan, 07-jun, 05-jun, 01-jan, and 09-jun after the earlier 02-jan/04-jan passes, raising marlin-status to 9 assets, 84 events, 8 find results, 9/9 Marlin peak segments, coverage=1.00, and canPreferMarlin=true. index-rebuild reported 84 Marlin events, 8 Marlin find results, and 2425 search documents. Repo marlin-preference-status still reports canPreferMarlinAsDefault=false because aggregateCoverage=0.15 and other evaluated projects remain under the preference gate.</x:v>
       </x:c>
       <x:c r="I51" s="11" t="str">
-        <x:v>Mitigated; live 4/9 range chunks; repo preference gate pending</x:v>
+        <x:v>Mitigated; live 9/9 representative project; repo preference gate pending</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="48" customHeight="1">
@@ -8678,79 +8678,79 @@
     </x:row>
     <x:row r="214" ht="48" customHeight="1">
       <x:c r="A214" s="10" t="str">
-        <x:v>TL-205</x:v>
+        <x:v>TL-240</x:v>
       </x:c>
       <x:c r="B214" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C214" s="26" t="str">
-        <x:v>Native preview duration fallback</x:v>
+        <x:v>Live Marlin 9-source representative completion</x:v>
       </x:c>
       <x:c r="D214" s="26" t="str">
-        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
+        <x:v>Run bounded caption-only Marlin range chunks for the remaining lively-alt-vol5 sources, rebuild the SQLite index, and inspect project/repo preference status.</x:v>
       </x:c>
       <x:c r="E214" s="26" t="str">
-        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
+        <x:v>VOS_MARLIN_PROXY_MAX_WIDTH=256 npx tsx scripts/marlin-evaluate.ts completed for 03-jan-clip.mp4, 07-jun-clip.mp4, 05-jun-clip.mp4, 01-jan-clip.mp4, and 09-jun-clip.mp4 with --request-timeout-ms 900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=2. The final marlin_events.json has 9 items, 84 events, and 8 find results: full-source live items for 08-jun-a-man-and-a.mp4 and 06-jun-two-people-are.mp4, plus bounded chunked items for 02-jan, 04-jan, 03-jan, 07-jun, 05-jun, 01-jan, and 09-jun. index-rebuild reported 2425 searchDocuments, 84 marlinEvents, and 8 marlinFindResults. marlin-status reports assets=9/events=84/findResults=8/segmentsWithMarlinPeak=9/coverage=1.00/canPreferMarlin=true. marlin-preference-status remains partially ready because aggregateCoverage=0.15 and canPreferMarlinAsDefault=false even though lively-alt-vol5 is now 9/9.</x:v>
       </x:c>
       <x:c r="F214" s="11" t="str">
-        <x:v>Native pixel/runtime pass</x:v>
+        <x:v>Live 9/9 representative project pass; repo preference gate pending</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="48" customHeight="1">
       <x:c r="A215" s="10" t="str">
-        <x:v>TL-206</x:v>
+        <x:v>TL-205</x:v>
       </x:c>
       <x:c r="B215" s="26" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C215" s="26" t="str">
-        <x:v>Native Clip Inspector save and clear</x:v>
+        <x:v>Native preview duration fallback</x:v>
       </x:c>
       <x:c r="D215" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
+        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
       </x:c>
       <x:c r="E215" s="26" t="str">
-        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
+        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F215" s="11" t="str">
-        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
+        <x:v>Native pixel/runtime pass</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="48" customHeight="1">
       <x:c r="A216" s="10" t="str">
-        <x:v>TL-207</x:v>
+        <x:v>TL-206</x:v>
       </x:c>
       <x:c r="B216" s="26" t="str">
-        <x:v>US-058</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C216" s="26" t="str">
-        <x:v>Native QA Dashboard issue jump</x:v>
+        <x:v>Native Clip Inspector save and clear</x:v>
       </x:c>
       <x:c r="D216" s="26" t="str">
-        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
+        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
       </x:c>
       <x:c r="E216" s="26" t="str">
-        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
+        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
       </x:c>
       <x:c r="F216" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="48" customHeight="1">
       <x:c r="A217" s="10" t="str">
-        <x:v>TL-208</x:v>
+        <x:v>TL-207</x:v>
       </x:c>
       <x:c r="B217" s="26" t="str">
-        <x:v>US-056</x:v>
+        <x:v>US-058</x:v>
       </x:c>
       <x:c r="C217" s="26" t="str">
-        <x:v>Native Candidate Swap sheet and staging</x:v>
+        <x:v>Native QA Dashboard issue jump</x:v>
       </x:c>
       <x:c r="D217" s="26" t="str">
-        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
+        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
       </x:c>
       <x:c r="E217" s="26" t="str">
-        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
+        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
       </x:c>
       <x:c r="F217" s="11" t="str">
         <x:v>Native AX/pixel pass</x:v>
@@ -8758,339 +8758,339 @@
     </x:row>
     <x:row r="218" ht="48" customHeight="1">
       <x:c r="A218" s="10" t="str">
-        <x:v>TL-209</x:v>
+        <x:v>TL-208</x:v>
       </x:c>
       <x:c r="B218" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-056</x:v>
       </x:c>
       <x:c r="C218" s="26" t="str">
-        <x:v>Native exact preview regeneration</x:v>
+        <x:v>Native Candidate Swap sheet and staging</x:v>
       </x:c>
       <x:c r="D218" s="26" t="str">
-        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
+        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
       </x:c>
       <x:c r="E218" s="26" t="str">
-        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
       </x:c>
       <x:c r="F218" s="11" t="str">
-        <x:v>Native exact preview pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="48" customHeight="1">
       <x:c r="A219" s="10" t="str">
-        <x:v>TL-210</x:v>
+        <x:v>TL-209</x:v>
       </x:c>
       <x:c r="B219" s="26" t="str">
-        <x:v>US-047</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C219" s="26" t="str">
-        <x:v>Native Command Palette top-bar open/close</x:v>
+        <x:v>Native exact preview regeneration</x:v>
       </x:c>
       <x:c r="D219" s="26" t="str">
-        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
+        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
       </x:c>
       <x:c r="E219" s="26" t="str">
-        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
+        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F219" s="11" t="str">
-        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
+        <x:v>Native exact preview pass</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="48" customHeight="1">
       <x:c r="A220" s="10" t="str">
-        <x:v>TL-211</x:v>
+        <x:v>TL-210</x:v>
       </x:c>
       <x:c r="B220" s="26" t="str">
         <x:v>US-047</x:v>
       </x:c>
       <x:c r="C220" s="26" t="str">
-        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
+        <x:v>Native Command Palette top-bar open/close</x:v>
       </x:c>
       <x:c r="D220" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
+        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
       </x:c>
       <x:c r="E220" s="26" t="str">
-        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
+        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
       </x:c>
       <x:c r="F220" s="11" t="str">
-        <x:v>Native keyboard/AX pass</x:v>
+        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="48" customHeight="1">
       <x:c r="A221" s="10" t="str">
-        <x:v>TL-212</x:v>
+        <x:v>TL-211</x:v>
       </x:c>
       <x:c r="B221" s="26" t="str">
-        <x:v>US-048</x:v>
+        <x:v>US-047</x:v>
       </x:c>
       <x:c r="C221" s="26" t="str">
-        <x:v>Native Agent panel session lifecycle</x:v>
+        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
       </x:c>
       <x:c r="D221" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
+        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
       </x:c>
       <x:c r="E221" s="26" t="str">
-        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
+        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
       </x:c>
       <x:c r="F221" s="11" t="str">
-        <x:v>Native AX/computer-use pass</x:v>
+        <x:v>Native keyboard/AX pass</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="48" customHeight="1">
       <x:c r="A222" s="10" t="str">
-        <x:v>TL-213</x:v>
+        <x:v>TL-212</x:v>
       </x:c>
       <x:c r="B222" s="26" t="str">
-        <x:v>US-049</x:v>
+        <x:v>US-048</x:v>
       </x:c>
       <x:c r="C222" s="26" t="str">
-        <x:v>Native Status agent job read-only turn</x:v>
+        <x:v>Native Agent panel session lifecycle</x:v>
       </x:c>
       <x:c r="D222" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
       </x:c>
       <x:c r="E222" s="26" t="str">
-        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
+        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F222" s="11" t="str">
-        <x:v>Native read-only job pass; approved write pending</x:v>
+        <x:v>Native AX/computer-use pass</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="48" customHeight="1">
       <x:c r="A223" s="10" t="str">
-        <x:v>TL-214</x:v>
+        <x:v>TL-213</x:v>
       </x:c>
       <x:c r="B223" s="26" t="str">
-        <x:v>US-050</x:v>
+        <x:v>US-049</x:v>
       </x:c>
       <x:c r="C223" s="26" t="str">
-        <x:v>Native Project readiness/action queue Copy pass</x:v>
+        <x:v>Native Status agent job read-only turn</x:v>
       </x:c>
       <x:c r="D223" s="26" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
       </x:c>
       <x:c r="E223" s="26" t="str">
-        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
+        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F223" s="11" t="str">
-        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
+        <x:v>Native read-only job pass; approved write pending</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="48" customHeight="1">
       <x:c r="A224" s="10" t="str">
-        <x:v>TL-215</x:v>
+        <x:v>TL-214</x:v>
       </x:c>
       <x:c r="B224" s="26" t="str">
-        <x:v>US-051</x:v>
+        <x:v>US-050</x:v>
       </x:c>
       <x:c r="C224" s="26" t="str">
-        <x:v>Native local Source Analysis button</x:v>
+        <x:v>Native Project readiness/action queue Copy pass</x:v>
       </x:c>
       <x:c r="D224" s="26" t="str">
-        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
       </x:c>
       <x:c r="E224" s="26" t="str">
-        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
+        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
       </x:c>
       <x:c r="F224" s="11" t="str">
-        <x:v>Native local analysis pass</x:v>
+        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="48" customHeight="1">
       <x:c r="A225" s="10" t="str">
-        <x:v>TL-216</x:v>
+        <x:v>TL-215</x:v>
       </x:c>
       <x:c r="B225" s="26" t="str">
-        <x:v>US-052</x:v>
+        <x:v>US-051</x:v>
       </x:c>
       <x:c r="C225" s="26" t="str">
-        <x:v>Native Rough Cut and Review Patch buttons</x:v>
+        <x:v>Native local Source Analysis button</x:v>
       </x:c>
       <x:c r="D225" s="26" t="str">
-        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
+        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E225" s="26" t="str">
-        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
       </x:c>
       <x:c r="F225" s="11" t="str">
-        <x:v>Native compile/review patch pass</x:v>
+        <x:v>Native local analysis pass</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="48" customHeight="1">
       <x:c r="A226" s="10" t="str">
-        <x:v>TL-217</x:v>
+        <x:v>TL-216</x:v>
       </x:c>
       <x:c r="B226" s="26" t="str">
-        <x:v>US-053</x:v>
+        <x:v>US-052</x:v>
       </x:c>
       <x:c r="C226" s="26" t="str">
-        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
+        <x:v>Native Rough Cut and Review Patch buttons</x:v>
       </x:c>
       <x:c r="D226" s="26" t="str">
-        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
+        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E226" s="26" t="str">
-        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
+        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F226" s="11" t="str">
-        <x:v>Native timeline/context menu pass</x:v>
+        <x:v>Native compile/review patch pass</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="48" customHeight="1">
       <x:c r="A227" s="10" t="str">
-        <x:v>TL-218</x:v>
+        <x:v>TL-217</x:v>
       </x:c>
       <x:c r="B227" s="26" t="str">
-        <x:v>US-054</x:v>
+        <x:v>US-053</x:v>
       </x:c>
       <x:c r="C227" s="26" t="str">
-        <x:v>Native Studio feedback Apply and Undo</x:v>
+        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
       </x:c>
       <x:c r="D227" s="26" t="str">
-        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
+        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
       </x:c>
       <x:c r="E227" s="26" t="str">
-        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
       </x:c>
       <x:c r="F227" s="11" t="str">
-        <x:v>Native apply/undo pass</x:v>
+        <x:v>Native timeline/context menu pass</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="48" customHeight="1">
       <x:c r="A228" s="10" t="str">
-        <x:v>TL-219</x:v>
+        <x:v>TL-218</x:v>
       </x:c>
       <x:c r="B228" s="26" t="str">
-        <x:v>US-057</x:v>
+        <x:v>US-054</x:v>
       </x:c>
       <x:c r="C228" s="26" t="str">
-        <x:v>Native Footage Search sheet and replacement staging</x:v>
+        <x:v>Native Studio feedback Apply and Undo</x:v>
       </x:c>
       <x:c r="D228" s="26" t="str">
-        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
+        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E228" s="26" t="str">
-        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
+        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F228" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native apply/undo pass</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="48" customHeight="1">
       <x:c r="A229" s="10" t="str">
-        <x:v>TL-220</x:v>
+        <x:v>TL-219</x:v>
       </x:c>
       <x:c r="B229" s="26" t="str">
-        <x:v>US-066</x:v>
+        <x:v>US-057</x:v>
       </x:c>
       <x:c r="C229" s="26" t="str">
-        <x:v>Native Settings transport picker mutation</x:v>
+        <x:v>Native Footage Search sheet and replacement staging</x:v>
       </x:c>
       <x:c r="D229" s="26" t="str">
-        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
+        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
       </x:c>
       <x:c r="E229" s="26" t="str">
-        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
       </x:c>
       <x:c r="F229" s="11" t="str">
-        <x:v>Native Settings picker mutation pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="48" customHeight="1">
       <x:c r="A230" s="10" t="str">
-        <x:v>TL-221</x:v>
+        <x:v>TL-220</x:v>
       </x:c>
       <x:c r="B230" s="26" t="str">
-        <x:v>US-059</x:v>
+        <x:v>US-066</x:v>
       </x:c>
       <x:c r="C230" s="26" t="str">
-        <x:v>Native Media Relink buttons and source-map relink</x:v>
+        <x:v>Native Settings transport picker mutation</x:v>
       </x:c>
       <x:c r="D230" s="26" t="str">
-        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
+        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
       </x:c>
       <x:c r="E230" s="26" t="str">
-        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
+        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F230" s="11" t="str">
-        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
+        <x:v>Native Settings picker mutation pass</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="48" customHeight="1">
       <x:c r="A231" s="10" t="str">
-        <x:v>TL-222</x:v>
+        <x:v>TL-221</x:v>
       </x:c>
       <x:c r="B231" s="26" t="str">
-        <x:v>US-060</x:v>
+        <x:v>US-059</x:v>
       </x:c>
       <x:c r="C231" s="26" t="str">
-        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
+        <x:v>Native Media Relink buttons and source-map relink</x:v>
       </x:c>
       <x:c r="D231" s="26" t="str">
-        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
+        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
       </x:c>
       <x:c r="E231" s="26" t="str">
-        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
+        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
       </x:c>
       <x:c r="F231" s="11" t="str">
-        <x:v>Native synthetic/proxy/smoke button pass</x:v>
+        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="48" customHeight="1">
       <x:c r="A232" s="10" t="str">
-        <x:v>TL-223</x:v>
+        <x:v>TL-222</x:v>
       </x:c>
       <x:c r="B232" s="26" t="str">
-        <x:v>US-046</x:v>
+        <x:v>US-060</x:v>
       </x:c>
       <x:c r="C232" s="26" t="str">
-        <x:v>Native New Project from Source</x:v>
+        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
       </x:c>
       <x:c r="D232" s="26" t="str">
-        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
+        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
       </x:c>
       <x:c r="E232" s="26" t="str">
-        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
+        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
       </x:c>
       <x:c r="F232" s="11" t="str">
-        <x:v>Native project creation/NSOpenPanel pass</x:v>
+        <x:v>Native synthetic/proxy/smoke button pass</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="48" customHeight="1">
       <x:c r="A233" s="10" t="str">
-        <x:v>TL-224</x:v>
+        <x:v>TL-223</x:v>
       </x:c>
       <x:c r="B233" s="26" t="str">
-        <x:v>US-062</x:v>
+        <x:v>US-046</x:v>
       </x:c>
       <x:c r="C233" s="26" t="str">
-        <x:v>Native MediaPanel Audio Story Graph button</x:v>
+        <x:v>Native New Project from Source</x:v>
       </x:c>
       <x:c r="D233" s="26" t="str">
-        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
+        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
       </x:c>
       <x:c r="E233" s="26" t="str">
-        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
       </x:c>
       <x:c r="F233" s="11" t="str">
-        <x:v>Native AX/UI/CLI pass</x:v>
+        <x:v>Native project creation/NSOpenPanel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="48" customHeight="1">
       <x:c r="A234" s="10" t="str">
-        <x:v>TL-225</x:v>
+        <x:v>TL-224</x:v>
       </x:c>
       <x:c r="B234" s="26" t="str">
-        <x:v>US-063</x:v>
+        <x:v>US-062</x:v>
       </x:c>
       <x:c r="C234" s="26" t="str">
-        <x:v>Native Render Final Package button</x:v>
+        <x:v>Native MediaPanel Audio Story Graph button</x:v>
       </x:c>
       <x:c r="D234" s="26" t="str">
-        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
+        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E234" s="26" t="str">
-        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F234" s="11" t="str">
         <x:v>Native AX/UI/CLI pass</x:v>
@@ -9098,121 +9098,141 @@
     </x:row>
     <x:row r="235" ht="48" customHeight="1">
       <x:c r="A235" s="10" t="str">
-        <x:v>TL-226</x:v>
+        <x:v>TL-225</x:v>
       </x:c>
       <x:c r="B235" s="26" t="str">
-        <x:v>US-064</x:v>
+        <x:v>US-063</x:v>
       </x:c>
       <x:c r="C235" s="26" t="str">
-        <x:v>Native Editor Handoff export and Finder reveal</x:v>
+        <x:v>Native Render Final Package button</x:v>
       </x:c>
       <x:c r="D235" s="26" t="str">
-        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
+        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
       </x:c>
       <x:c r="E235" s="26" t="str">
-        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
+        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F235" s="11" t="str">
-        <x:v>Native AX/UI/Finder/CLI pass</x:v>
+        <x:v>Native AX/UI/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="236" ht="48" customHeight="1">
       <x:c r="A236" s="10" t="str">
-        <x:v>TL-227</x:v>
+        <x:v>TL-226</x:v>
       </x:c>
       <x:c r="B236" s="26" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-064</x:v>
       </x:c>
       <x:c r="C236" s="26" t="str">
-        <x:v>Native Ask Codex editor-note proposal</x:v>
+        <x:v>Native Editor Handoff export and Finder reveal</x:v>
       </x:c>
       <x:c r="D236" s="26" t="str">
-        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
+        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E236" s="26" t="str">
-        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
+        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
       </x:c>
       <x:c r="F236" s="11" t="str">
-        <x:v>Native read-only Codex proposal pass</x:v>
+        <x:v>Native AX/UI/Finder/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="237" ht="48" customHeight="1">
       <x:c r="A237" s="10" t="str">
-        <x:v>TL-228</x:v>
+        <x:v>TL-227</x:v>
       </x:c>
       <x:c r="B237" s="26" t="str">
-        <x:v>US-061</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C237" s="26" t="str">
-        <x:v>Live Marlin single-source completion</x:v>
+        <x:v>Native Ask Codex editor-note proposal</x:v>
       </x:c>
       <x:c r="D237" s="26" t="str">
-        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
+        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
       </x:c>
       <x:c r="E237" s="26" t="str">
-        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
+        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
       </x:c>
       <x:c r="F237" s="11" t="str">
-        <x:v>Live single-source pass; full representative batch pending</x:v>
+        <x:v>Native read-only Codex proposal pass</x:v>
       </x:c>
     </x:row>
     <x:row r="238" ht="48" customHeight="1">
       <x:c r="A238" s="10" t="str">
-        <x:v>TL-229</x:v>
+        <x:v>TL-228</x:v>
       </x:c>
       <x:c r="B238" s="26" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C238" s="26" t="str">
-        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+        <x:v>Live Marlin single-source completion</x:v>
       </x:c>
       <x:c r="D238" s="26" t="str">
-        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
       </x:c>
       <x:c r="E238" s="26" t="str">
-        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
       </x:c>
       <x:c r="F238" s="11" t="str">
-        <x:v>Native fresh-launch pixel pass</x:v>
+        <x:v>Live single-source pass; full representative batch pending</x:v>
       </x:c>
     </x:row>
     <x:row r="239" ht="48" customHeight="1">
       <x:c r="A239" s="10" t="str">
-        <x:v>TL-230</x:v>
+        <x:v>TL-229</x:v>
       </x:c>
       <x:c r="B239" s="26" t="str">
         <x:v>US-045</x:v>
       </x:c>
       <x:c r="C239" s="26" t="str">
+        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+      </x:c>
+      <x:c r="D239" s="26" t="str">
+        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+      </x:c>
+      <x:c r="E239" s="26" t="str">
+        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+      </x:c>
+      <x:c r="F239" s="11" t="str">
+        <x:v>Native fresh-launch pixel pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" ht="48" customHeight="1">
+      <x:c r="A240" s="10" t="str">
+        <x:v>TL-230</x:v>
+      </x:c>
+      <x:c r="B240" s="26" t="str">
+        <x:v>US-045</x:v>
+      </x:c>
+      <x:c r="C240" s="26" t="str">
         <x:v>AX-1 exact preview promotion and pixel pass</x:v>
       </x:c>
-      <x:c r="D239" s="26" t="str">
+      <x:c r="D240" s="26" t="str">
         <x:v>Run videoos-studio-cli compile-run on projects/ax1-participant-voices-20260401, confirm playback-contract-status, select ProjectShelf.ax1-participant-voices-20260401 in VideoOSStudio, capture /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and run Retina-coordinate pixel statistics on the Viewer region.</x:v>
       </x:c>
-      <x:c r="E239" s="26" t="str">
+      <x:c r="E240" s="26" t="str">
         <x:v>Before compile, playback-contract-status returned legacy_manifest and approvalGrade=false. compile-run completed with exitCode=0, timeline compiled, indexDocuments=492, and git status stayed clean. After compile, playback-contract-status returned state=exact, approvalGrade=true, timelineHash=171378fe2bfe3a7c, and manifestBaseTimelineHash=171378fe2bfe3a7c. Native Viewer showed Exact preview / preview-editor-1775121573933.mp4 and Timeline preview D4887.MP4 with a visible interview frame. Screenshot was 3.5M; viewer_person_actual mean_rgb=(144.62,141.42,149.8) and near_black_pct=0.0004, while left pillarbox near_black_pct=1.0000 as expected.</x:v>
       </x:c>
-      <x:c r="F239" s="11" t="str">
+      <x:c r="F240" s="11" t="str">
         <x:v>Native AX-1 exact/pixel pass</x:v>
       </x:c>
     </x:row>
-    <x:row r="240" ht="48" customHeight="1">
-      <x:c r="A240" s="12" t="str">
+    <x:row r="241" ht="48" customHeight="1">
+      <x:c r="A241" s="12" t="str">
         <x:v>TL-231</x:v>
       </x:c>
-      <x:c r="B240" s="27" t="str">
+      <x:c r="B241" s="27" t="str">
         <x:v>US-050</x:v>
       </x:c>
-      <x:c r="C240" s="27" t="str">
+      <x:c r="C241" s="27" t="str">
         <x:v>Native Action Queue approval gate</x:v>
       </x:c>
-      <x:c r="D240" s="27" t="str">
+      <x:c r="D241" s="27" t="str">
         <x:v>Add ProjectPanel.ActionQueue* identifiers, relaunch VideoOSStudio, select AX-1 Project tab, inspect the Action Queue AX tree, click ProjectPanel.ActionQueueRunButton.rough-cut-review, and stop at the Codex approval gate without approving writes.</x:v>
       </x:c>
-      <x:c r="E240" s="27" t="str">
+      <x:c r="E241" s="27" t="str">
         <x:v>AX exposed ProjectPanel.ActionQueueRunButton.rough-cut-review, ProjectPanel.ActionQueueCopyButton.rough-cut-review, ProjectPanel.ActionQueueRunButton.marlin-default, and ProjectPanel.ActionQueueCopyButton.marlin-default. Clicking rough-cut-review changed the row to disabled Starting Codex session for Review..., then to Opening Codex approval gate for Review. ps showed a Codex app-server child under VideoOSStudio; git status listed only the intentional ProjectInspectorViews.swift edit, and projects/ax1-participant-voices-20260401/06_review still contained only human_notes.yaml.</x:v>
       </x:c>
-      <x:c r="F240" s="13" t="str">
+      <x:c r="F241" s="13" t="str">
         <x:v>Native approval-gate pass; write not approved</x:v>
       </x:c>
     </x:row>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rf47556e99d334d0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R33719f10f55e41d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R485df4526a414575"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R6e731d4bac424bce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R2e9be4da83614b05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra6dcc9c353694c7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rac30d92325ae4a5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Rc97cc9d0c5b74bf9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R748de6aca7e947b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Re26a7e59bde34690"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,7 +433,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 21:32 JST</x:v>
+        <x:v>2026-06-23 21:47 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -473,7 +473,7 @@
         <x:v>Issues tracked</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="220" customHeight="1">
@@ -481,7 +481,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build adds bounded Marlin range chunking for long local sources: --chunk-seconds, --chunk-overlap-seconds, and --max-chunks are wired through runtime/pipeline/stages/marlin.ts, scripts/marlin-evaluate.ts, ProjectMarlinEvaluationRunPlan/Runner, and marlin-eval-plan/eval-next/eval-run. The same path keeps --caption-only, source-map-aware source selection, per-asset/per-chunk checkpoints, --max-sources, and --skip-existing. Prior native builds include ProjectMarlinRuntimeStatusReader isolated dependency probes, InspectorTab.Agent/Project/Clip/Media/QA buttons for US-065, ProjectPanel.ActionQueueStatus / ActionQueueCommand.&lt;id&gt; / ActionQueueRunButton.&lt;id&gt; / ActionQueueCopyButton.&lt;id&gt; for US-050, ProjectInitializer.ProjectIDField/CreateButton/CancelButton for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix.</x:v>
+        <x:v>Latest code build fixes resumable chunked Marlin progress when --skip-existing and --max-sources are combined: completed short no-chunk assets no longer consume the bounded run slot, so follow-up runs can advance to the next unevaluated source. Prior US-061 build work added bounded Marlin range chunking for long local sources: --chunk-seconds, --chunk-overlap-seconds, and --max-chunks are wired through runtime/pipeline/stages/marlin.ts, scripts/marlin-evaluate.ts, ProjectMarlinEvaluationRunPlan/Runner, and marlin-eval-plan/eval-next/eval-run. The same path keeps --caption-only, source-map-aware source selection, per-asset/per-chunk checkpoints, --max-sources, and --skip-existing. Prior native builds include ProjectMarlinRuntimeStatusReader isolated dependency probes, InspectorTab.Agent/Project/Clip/Media/QA buttons for US-065, ProjectPanel.ActionQueueStatus / ActionQueueCommand.&lt;id&gt; / ActionQueueRunButton.&lt;id&gt; / ActionQueueCopyButton.&lt;id&gt; for US-050, ProjectInitializer.ProjectIDField/CreateButton/CancelButton for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -489,7 +489,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-061 pass completed bounded caption-only Marlin range chunks for all 9 lively-alt-vol5 representative sources. Prior implementation validation remains green: npx vitest run tests/marlin-normalize.test.ts tests/marlin-proxy.test.ts tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts passed 29/0, npx tsc --noEmit --pretty false passed, node --check scripts/marlin-evaluate.ts passed, swift build --target VideoOSStudioCLI passed, swift test --filter ProjectMarlinEvaluationRunPlanTests passed 11/0, and git diff --check passed. Live non-mock runs now cover 08-jun, 06-jun, 02-jan, 04-jan, 03-jan, 07-jun, 05-jun, 01-jan, and 09-jun. lively-alt-vol5 now has 9 assets, 84 events, 8 find results, coverage=1.00, and canPreferMarlin=true; index-rebuild reports 2425 searchDocuments. Repo-level canPreferMarlinAsDefault remains false pending broader cross-project coverage.</x:v>
+        <x:v>Latest US-061 pass fixed and verified skip-existing chunk progress on togakushi-camp. npx vitest run tests/marlin-analysis-stage.test.ts passed 15/0, npx tsc --noEmit --pretty false passed, and live VOS_MARLIN_PROXY_MAX_WIDTH=256 marlin-eval-run togakushi-camp --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=2 advanced from completed T084 to AST_038AB86F / T001. The run rebuilt the index with searchDocuments=286 and marlinEvents=4; marlin-status reports togakushi-camp assets=2/events=4/segmentsWithMarlinPeak=2/coverage=0.03. Prior US-061 validation remains green for lively-alt-vol5 9-source representative chunks: 9 assets, 84 events, 8 find results, coverage=1.00, canPreferMarlin=true, and repo-level canPreferMarlinAsDefault remains false pending broader cross-project coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -497,7 +497,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest runtime/macOS CLI check is the US-061 9-source representative completion: marlin-status reports 9 assets / 84 events / 8 find results / coverage=1.00 / canPreferMarlin=true for lively-alt-vol5, and marlin-preference-status reports lively-alt-vol5 9/9 peak segments while the repo remains canPreferMarlinAsDefault=false because aggregateCoverage is 0.15 and other evaluated projects remain below gate. The final live pass added 03-jan, 07-jun, 05-jun, 01-jan, and 09-jun bounded chunks after the earlier 02-jan and 04-jan chunk passes. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live single-source completion, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest runtime/macOS CLI check is the US-061 togakushi-camp skip-existing chunk progress pass: VOS_MARLIN_PROXY_MAX_WIDTH=256 marlin-eval-run completed with indexRebuilt=true/searchDocuments=286 and added AST_038AB86F / NINJAV_S001_S001_T001.MOV after the already completed T084 source. marlin-status now reports assets=2/events=4/segmentsWithMarlinPeak=2/coverage=0.03 for togakushi-camp. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live representative completions, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -505,7 +505,7 @@
         <x:v>Latest US-061 follow-up</x:v>
       </x:c>
       <x:c r="B12" s="19" t="str">
-        <x:v>TL-241 adds a live togakushi-camp Marlin source and fixes two runtime blockers found during the run: duplicate transcript item IDs in SQLite index rebuild and degraded fallback peaks blocking Marlin temporal semantic materialization. Verification now shows togakushi-camp assets=1/events=3/segmentsWithMarlinPeak=1/coverage=0.02/searchDocuments=285; repo-level canPreferMarlinAsDefault remains false pending broader cross-project coverage.</x:v>
+        <x:v>TL-242 fixes the resumable chunked Marlin run path so --skip-existing --max-sources=1 no longer reselects completed short sources before advancing. Verification now shows togakushi-camp assets=2/events=4/segmentsWithMarlinPeak=2/coverage=0.03/searchDocuments=286 after adding AST_038AB86F / T001; repo-level canPreferMarlinAsDefault remains false pending broader cross-project coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="220" customHeight="1">
@@ -4431,31 +4431,60 @@
       </x:c>
     </x:row>
     <x:row r="74" ht="48" customHeight="1">
-      <x:c r="A74" s="12" t="str">
+      <x:c r="A74" s="10" t="str">
         <x:v>ISS-072</x:v>
       </x:c>
-      <x:c r="B74" s="25" t="str">
+      <x:c r="B74" s="24" t="str">
         <x:v>US-061</x:v>
       </x:c>
-      <x:c r="C74" s="25" t="str">
+      <x:c r="C74" s="24" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="D74" s="25" t="str">
+      <x:c r="D74" s="24" t="str">
         <x:v>Marlin materialization policy</x:v>
       </x:c>
-      <x:c r="E74" s="25" t="str">
+      <x:c r="E74" s="24" t="str">
         <x:v>Live Marlin events could remain invisible to preference coverage when an existing degraded fallback peak had fused_peak_score=1.</x:v>
       </x:c>
-      <x:c r="F74" s="25" t="str">
+      <x:c r="F74" s="24" t="str">
         <x:v>applyMarlinEventsToSegments only replaced existing peak_analysis when the current peak was absent, already Marlin-derived, or lower confidence than the new Marlin peak. Degraded fallback peaks use precision_mode=never and can carry fused_peak_score=1, so Marlin temporal semantics could update the summary/interest points but leave segmentsWithMarlinPeak at 0.</x:v>
       </x:c>
-      <x:c r="G74" s="25" t="str">
+      <x:c r="G74" s="24" t="str">
         <x:v>Treat degraded fallback peak_analysis as replaceable by Marlin temporal semantic peaks regardless of the degraded fused score.</x:v>
       </x:c>
-      <x:c r="H74" s="25" t="str">
+      <x:c r="H74" s="24" t="str">
         <x:v>marlin-analysis-stage now tests replacement of precision_mode=never degraded peaks. Re-running marlin-eval-run togakushi-camp completed and changed marlin-status from needs segment materialization to needs more footage evaluation with segmentsWithMarlinPeak=1, coverage=0.02, and index searchDocuments=285.</x:v>
       </x:c>
-      <x:c r="I74" s="13" t="str">
+      <x:c r="I74" s="11" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="48" customHeight="1">
+      <x:c r="A75" s="12" t="str">
+        <x:v>ISS-073</x:v>
+      </x:c>
+      <x:c r="B75" s="25" t="str">
+        <x:v>US-061</x:v>
+      </x:c>
+      <x:c r="C75" s="25" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="D75" s="25" t="str">
+        <x:v>Marlin resumability/logistics</x:v>
+      </x:c>
+      <x:c r="E75" s="25" t="str">
+        <x:v>Resumable chunked Marlin runs could repeatedly select a completed short source instead of advancing to the next unevaluated asset.</x:v>
+      </x:c>
+      <x:c r="F75" s="25" t="str">
+        <x:v>When chunking was enabled, selectMarlinAssetInputsForRun intentionally deferred skipExisting because resume state is per chunk. For short assets that do not produce chunks, --skip-existing --max-sources=1 still capped the run before runMarlinAnalysis could discover that the selected asset was already complete, so togakushi-camp kept presenting the completed T084 source instead of advancing to T001.</x:v>
+      </x:c>
+      <x:c r="G75" s="25" t="str">
+        <x:v>When chunking and skipExisting are both enabled, defer maxSources until an unfinished asset is actually evaluated; for short no-chunk assets, return null if an existing item already covers the asset.</x:v>
+      </x:c>
+      <x:c r="H75" s="25" t="str">
+        <x:v>marlin-analysis-stage now covers skip-existing with chunking across completed short assets. VOS_MARLIN_PROXY_MAX_WIDTH=256 marlin-eval-run togakushi-camp --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=2 advanced from AST_00725A11 / T084 to AST_038AB86F / T001, rebuilt the index, and raised togakushi-camp to assets=2/events=4/segmentsWithMarlinPeak=2/coverage=0.03/searchDocuments=286.</x:v>
+      </x:c>
+      <x:c r="I75" s="13" t="str">
         <x:v>Fixed</x:v>
       </x:c>
     </x:row>
@@ -8778,79 +8807,79 @@
     </x:row>
     <x:row r="216" ht="48" customHeight="1">
       <x:c r="A216" s="10" t="str">
-        <x:v>TL-205</x:v>
+        <x:v>TL-242</x:v>
       </x:c>
       <x:c r="B216" s="24" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C216" s="24" t="str">
-        <x:v>Native preview duration fallback</x:v>
+        <x:v>Togakushi Marlin skip-existing chunk progress</x:v>
       </x:c>
       <x:c r="D216" s="24" t="str">
-        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
+        <x:v>Fix and retest --skip-existing --max-sources=1 with chunk controls so completed short sources do not block the next unevaluated Togakushi source.</x:v>
       </x:c>
       <x:c r="E216" s="24" t="str">
-        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
+        <x:v>runtime/pipeline/stages/marlin.ts now defers maxSources until an unfinished asset is actually evaluated when chunking and skipExisting are both enabled, and skips already completed short no-chunk assets before whole-asset fallback. Verification passed: npx vitest run tests/marlin-analysis-stage.test.ts 15/0; npx tsc --noEmit --pretty false; VOS_MARLIN_PROXY_MAX_WIDTH=256 .build/debug/videoos-studio-cli marlin-eval-run togakushi-camp --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=2 completed with indexRebuilt=true/searchDocuments=286/marlinEvents=4. marlin-status now reports assets=2/events=4/segmentsWithMarlinPeak=2/coverage=0.03, with the new live source AST_038AB86F / NINJAV_S001_S001_T001.MOV.</x:v>
       </x:c>
       <x:c r="F216" s="11" t="str">
-        <x:v>Native pixel/runtime pass</x:v>
+        <x:v>Live 2/60 representative progress; skip-existing chunk fix verified</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="48" customHeight="1">
       <x:c r="A217" s="10" t="str">
-        <x:v>TL-206</x:v>
+        <x:v>TL-205</x:v>
       </x:c>
       <x:c r="B217" s="24" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C217" s="24" t="str">
-        <x:v>Native Clip Inspector save and clear</x:v>
+        <x:v>Native preview duration fallback</x:v>
       </x:c>
       <x:c r="D217" s="24" t="str">
-        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
+        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
       </x:c>
       <x:c r="E217" s="24" t="str">
-        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
+        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F217" s="11" t="str">
-        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
+        <x:v>Native pixel/runtime pass</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="48" customHeight="1">
       <x:c r="A218" s="10" t="str">
-        <x:v>TL-207</x:v>
+        <x:v>TL-206</x:v>
       </x:c>
       <x:c r="B218" s="24" t="str">
-        <x:v>US-058</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C218" s="24" t="str">
-        <x:v>Native QA Dashboard issue jump</x:v>
+        <x:v>Native Clip Inspector save and clear</x:v>
       </x:c>
       <x:c r="D218" s="24" t="str">
-        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
+        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
       </x:c>
       <x:c r="E218" s="24" t="str">
-        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
+        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
       </x:c>
       <x:c r="F218" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="48" customHeight="1">
       <x:c r="A219" s="10" t="str">
-        <x:v>TL-208</x:v>
+        <x:v>TL-207</x:v>
       </x:c>
       <x:c r="B219" s="24" t="str">
-        <x:v>US-056</x:v>
+        <x:v>US-058</x:v>
       </x:c>
       <x:c r="C219" s="24" t="str">
-        <x:v>Native Candidate Swap sheet and staging</x:v>
+        <x:v>Native QA Dashboard issue jump</x:v>
       </x:c>
       <x:c r="D219" s="24" t="str">
-        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
+        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
       </x:c>
       <x:c r="E219" s="24" t="str">
-        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
+        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
       </x:c>
       <x:c r="F219" s="11" t="str">
         <x:v>Native AX/pixel pass</x:v>
@@ -8858,339 +8887,339 @@
     </x:row>
     <x:row r="220" ht="48" customHeight="1">
       <x:c r="A220" s="10" t="str">
-        <x:v>TL-209</x:v>
+        <x:v>TL-208</x:v>
       </x:c>
       <x:c r="B220" s="24" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-056</x:v>
       </x:c>
       <x:c r="C220" s="24" t="str">
-        <x:v>Native exact preview regeneration</x:v>
+        <x:v>Native Candidate Swap sheet and staging</x:v>
       </x:c>
       <x:c r="D220" s="24" t="str">
-        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
+        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
       </x:c>
       <x:c r="E220" s="24" t="str">
-        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
       </x:c>
       <x:c r="F220" s="11" t="str">
-        <x:v>Native exact preview pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="48" customHeight="1">
       <x:c r="A221" s="10" t="str">
-        <x:v>TL-210</x:v>
+        <x:v>TL-209</x:v>
       </x:c>
       <x:c r="B221" s="24" t="str">
-        <x:v>US-047</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C221" s="24" t="str">
-        <x:v>Native Command Palette top-bar open/close</x:v>
+        <x:v>Native exact preview regeneration</x:v>
       </x:c>
       <x:c r="D221" s="24" t="str">
-        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
+        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
       </x:c>
       <x:c r="E221" s="24" t="str">
-        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
+        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F221" s="11" t="str">
-        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
+        <x:v>Native exact preview pass</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="48" customHeight="1">
       <x:c r="A222" s="10" t="str">
-        <x:v>TL-211</x:v>
+        <x:v>TL-210</x:v>
       </x:c>
       <x:c r="B222" s="24" t="str">
         <x:v>US-047</x:v>
       </x:c>
       <x:c r="C222" s="24" t="str">
-        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
+        <x:v>Native Command Palette top-bar open/close</x:v>
       </x:c>
       <x:c r="D222" s="24" t="str">
-        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
+        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
       </x:c>
       <x:c r="E222" s="24" t="str">
-        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
+        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
       </x:c>
       <x:c r="F222" s="11" t="str">
-        <x:v>Native keyboard/AX pass</x:v>
+        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="48" customHeight="1">
       <x:c r="A223" s="10" t="str">
-        <x:v>TL-212</x:v>
+        <x:v>TL-211</x:v>
       </x:c>
       <x:c r="B223" s="24" t="str">
-        <x:v>US-048</x:v>
+        <x:v>US-047</x:v>
       </x:c>
       <x:c r="C223" s="24" t="str">
-        <x:v>Native Agent panel session lifecycle</x:v>
+        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
       </x:c>
       <x:c r="D223" s="24" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
+        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
       </x:c>
       <x:c r="E223" s="24" t="str">
-        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
+        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
       </x:c>
       <x:c r="F223" s="11" t="str">
-        <x:v>Native AX/computer-use pass</x:v>
+        <x:v>Native keyboard/AX pass</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="48" customHeight="1">
       <x:c r="A224" s="10" t="str">
-        <x:v>TL-213</x:v>
+        <x:v>TL-212</x:v>
       </x:c>
       <x:c r="B224" s="24" t="str">
-        <x:v>US-049</x:v>
+        <x:v>US-048</x:v>
       </x:c>
       <x:c r="C224" s="24" t="str">
-        <x:v>Native Status agent job read-only turn</x:v>
+        <x:v>Native Agent panel session lifecycle</x:v>
       </x:c>
       <x:c r="D224" s="24" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
       </x:c>
       <x:c r="E224" s="24" t="str">
-        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
+        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F224" s="11" t="str">
-        <x:v>Native read-only job pass; approved write pending</x:v>
+        <x:v>Native AX/computer-use pass</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="48" customHeight="1">
       <x:c r="A225" s="10" t="str">
-        <x:v>TL-214</x:v>
+        <x:v>TL-213</x:v>
       </x:c>
       <x:c r="B225" s="24" t="str">
-        <x:v>US-050</x:v>
+        <x:v>US-049</x:v>
       </x:c>
       <x:c r="C225" s="24" t="str">
-        <x:v>Native Project readiness/action queue Copy pass</x:v>
+        <x:v>Native Status agent job read-only turn</x:v>
       </x:c>
       <x:c r="D225" s="24" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
       </x:c>
       <x:c r="E225" s="24" t="str">
-        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
+        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F225" s="11" t="str">
-        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
+        <x:v>Native read-only job pass; approved write pending</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="48" customHeight="1">
       <x:c r="A226" s="10" t="str">
-        <x:v>TL-215</x:v>
+        <x:v>TL-214</x:v>
       </x:c>
       <x:c r="B226" s="24" t="str">
-        <x:v>US-051</x:v>
+        <x:v>US-050</x:v>
       </x:c>
       <x:c r="C226" s="24" t="str">
-        <x:v>Native local Source Analysis button</x:v>
+        <x:v>Native Project readiness/action queue Copy pass</x:v>
       </x:c>
       <x:c r="D226" s="24" t="str">
-        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
       </x:c>
       <x:c r="E226" s="24" t="str">
-        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
+        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
       </x:c>
       <x:c r="F226" s="11" t="str">
-        <x:v>Native local analysis pass</x:v>
+        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="48" customHeight="1">
       <x:c r="A227" s="10" t="str">
-        <x:v>TL-216</x:v>
+        <x:v>TL-215</x:v>
       </x:c>
       <x:c r="B227" s="24" t="str">
-        <x:v>US-052</x:v>
+        <x:v>US-051</x:v>
       </x:c>
       <x:c r="C227" s="24" t="str">
-        <x:v>Native Rough Cut and Review Patch buttons</x:v>
+        <x:v>Native local Source Analysis button</x:v>
       </x:c>
       <x:c r="D227" s="24" t="str">
-        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
+        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E227" s="24" t="str">
-        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
       </x:c>
       <x:c r="F227" s="11" t="str">
-        <x:v>Native compile/review patch pass</x:v>
+        <x:v>Native local analysis pass</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="48" customHeight="1">
       <x:c r="A228" s="10" t="str">
-        <x:v>TL-217</x:v>
+        <x:v>TL-216</x:v>
       </x:c>
       <x:c r="B228" s="24" t="str">
-        <x:v>US-053</x:v>
+        <x:v>US-052</x:v>
       </x:c>
       <x:c r="C228" s="24" t="str">
-        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
+        <x:v>Native Rough Cut and Review Patch buttons</x:v>
       </x:c>
       <x:c r="D228" s="24" t="str">
-        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
+        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E228" s="24" t="str">
-        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
+        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F228" s="11" t="str">
-        <x:v>Native timeline/context menu pass</x:v>
+        <x:v>Native compile/review patch pass</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="48" customHeight="1">
       <x:c r="A229" s="10" t="str">
-        <x:v>TL-218</x:v>
+        <x:v>TL-217</x:v>
       </x:c>
       <x:c r="B229" s="24" t="str">
-        <x:v>US-054</x:v>
+        <x:v>US-053</x:v>
       </x:c>
       <x:c r="C229" s="24" t="str">
-        <x:v>Native Studio feedback Apply and Undo</x:v>
+        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
       </x:c>
       <x:c r="D229" s="24" t="str">
-        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
+        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
       </x:c>
       <x:c r="E229" s="24" t="str">
-        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
       </x:c>
       <x:c r="F229" s="11" t="str">
-        <x:v>Native apply/undo pass</x:v>
+        <x:v>Native timeline/context menu pass</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="48" customHeight="1">
       <x:c r="A230" s="10" t="str">
-        <x:v>TL-219</x:v>
+        <x:v>TL-218</x:v>
       </x:c>
       <x:c r="B230" s="24" t="str">
-        <x:v>US-057</x:v>
+        <x:v>US-054</x:v>
       </x:c>
       <x:c r="C230" s="24" t="str">
-        <x:v>Native Footage Search sheet and replacement staging</x:v>
+        <x:v>Native Studio feedback Apply and Undo</x:v>
       </x:c>
       <x:c r="D230" s="24" t="str">
-        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
+        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E230" s="24" t="str">
-        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
+        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F230" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native apply/undo pass</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="48" customHeight="1">
       <x:c r="A231" s="10" t="str">
-        <x:v>TL-220</x:v>
+        <x:v>TL-219</x:v>
       </x:c>
       <x:c r="B231" s="24" t="str">
-        <x:v>US-066</x:v>
+        <x:v>US-057</x:v>
       </x:c>
       <x:c r="C231" s="24" t="str">
-        <x:v>Native Settings transport picker mutation</x:v>
+        <x:v>Native Footage Search sheet and replacement staging</x:v>
       </x:c>
       <x:c r="D231" s="24" t="str">
-        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
+        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
       </x:c>
       <x:c r="E231" s="24" t="str">
-        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
       </x:c>
       <x:c r="F231" s="11" t="str">
-        <x:v>Native Settings picker mutation pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="48" customHeight="1">
       <x:c r="A232" s="10" t="str">
-        <x:v>TL-221</x:v>
+        <x:v>TL-220</x:v>
       </x:c>
       <x:c r="B232" s="24" t="str">
-        <x:v>US-059</x:v>
+        <x:v>US-066</x:v>
       </x:c>
       <x:c r="C232" s="24" t="str">
-        <x:v>Native Media Relink buttons and source-map relink</x:v>
+        <x:v>Native Settings transport picker mutation</x:v>
       </x:c>
       <x:c r="D232" s="24" t="str">
-        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
+        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
       </x:c>
       <x:c r="E232" s="24" t="str">
-        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
+        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F232" s="11" t="str">
-        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
+        <x:v>Native Settings picker mutation pass</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="48" customHeight="1">
       <x:c r="A233" s="10" t="str">
-        <x:v>TL-222</x:v>
+        <x:v>TL-221</x:v>
       </x:c>
       <x:c r="B233" s="24" t="str">
-        <x:v>US-060</x:v>
+        <x:v>US-059</x:v>
       </x:c>
       <x:c r="C233" s="24" t="str">
-        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
+        <x:v>Native Media Relink buttons and source-map relink</x:v>
       </x:c>
       <x:c r="D233" s="24" t="str">
-        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
+        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
       </x:c>
       <x:c r="E233" s="24" t="str">
-        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
+        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
       </x:c>
       <x:c r="F233" s="11" t="str">
-        <x:v>Native synthetic/proxy/smoke button pass</x:v>
+        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="48" customHeight="1">
       <x:c r="A234" s="10" t="str">
-        <x:v>TL-223</x:v>
+        <x:v>TL-222</x:v>
       </x:c>
       <x:c r="B234" s="24" t="str">
-        <x:v>US-046</x:v>
+        <x:v>US-060</x:v>
       </x:c>
       <x:c r="C234" s="24" t="str">
-        <x:v>Native New Project from Source</x:v>
+        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
       </x:c>
       <x:c r="D234" s="24" t="str">
-        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
+        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
       </x:c>
       <x:c r="E234" s="24" t="str">
-        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
+        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
       </x:c>
       <x:c r="F234" s="11" t="str">
-        <x:v>Native project creation/NSOpenPanel pass</x:v>
+        <x:v>Native synthetic/proxy/smoke button pass</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="48" customHeight="1">
       <x:c r="A235" s="10" t="str">
-        <x:v>TL-224</x:v>
+        <x:v>TL-223</x:v>
       </x:c>
       <x:c r="B235" s="24" t="str">
-        <x:v>US-062</x:v>
+        <x:v>US-046</x:v>
       </x:c>
       <x:c r="C235" s="24" t="str">
-        <x:v>Native MediaPanel Audio Story Graph button</x:v>
+        <x:v>Native New Project from Source</x:v>
       </x:c>
       <x:c r="D235" s="24" t="str">
-        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
+        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
       </x:c>
       <x:c r="E235" s="24" t="str">
-        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
       </x:c>
       <x:c r="F235" s="11" t="str">
-        <x:v>Native AX/UI/CLI pass</x:v>
+        <x:v>Native project creation/NSOpenPanel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="236" ht="48" customHeight="1">
       <x:c r="A236" s="10" t="str">
-        <x:v>TL-225</x:v>
+        <x:v>TL-224</x:v>
       </x:c>
       <x:c r="B236" s="24" t="str">
-        <x:v>US-063</x:v>
+        <x:v>US-062</x:v>
       </x:c>
       <x:c r="C236" s="24" t="str">
-        <x:v>Native Render Final Package button</x:v>
+        <x:v>Native MediaPanel Audio Story Graph button</x:v>
       </x:c>
       <x:c r="D236" s="24" t="str">
-        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
+        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E236" s="24" t="str">
-        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F236" s="11" t="str">
         <x:v>Native AX/UI/CLI pass</x:v>
@@ -9198,121 +9227,141 @@
     </x:row>
     <x:row r="237" ht="48" customHeight="1">
       <x:c r="A237" s="10" t="str">
-        <x:v>TL-226</x:v>
+        <x:v>TL-225</x:v>
       </x:c>
       <x:c r="B237" s="24" t="str">
-        <x:v>US-064</x:v>
+        <x:v>US-063</x:v>
       </x:c>
       <x:c r="C237" s="24" t="str">
-        <x:v>Native Editor Handoff export and Finder reveal</x:v>
+        <x:v>Native Render Final Package button</x:v>
       </x:c>
       <x:c r="D237" s="24" t="str">
-        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
+        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
       </x:c>
       <x:c r="E237" s="24" t="str">
-        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
+        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F237" s="11" t="str">
-        <x:v>Native AX/UI/Finder/CLI pass</x:v>
+        <x:v>Native AX/UI/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="238" ht="48" customHeight="1">
       <x:c r="A238" s="10" t="str">
-        <x:v>TL-227</x:v>
+        <x:v>TL-226</x:v>
       </x:c>
       <x:c r="B238" s="24" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-064</x:v>
       </x:c>
       <x:c r="C238" s="24" t="str">
-        <x:v>Native Ask Codex editor-note proposal</x:v>
+        <x:v>Native Editor Handoff export and Finder reveal</x:v>
       </x:c>
       <x:c r="D238" s="24" t="str">
-        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
+        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E238" s="24" t="str">
-        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
+        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
       </x:c>
       <x:c r="F238" s="11" t="str">
-        <x:v>Native read-only Codex proposal pass</x:v>
+        <x:v>Native AX/UI/Finder/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="239" ht="48" customHeight="1">
       <x:c r="A239" s="10" t="str">
-        <x:v>TL-228</x:v>
+        <x:v>TL-227</x:v>
       </x:c>
       <x:c r="B239" s="24" t="str">
-        <x:v>US-061</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C239" s="24" t="str">
-        <x:v>Live Marlin single-source completion</x:v>
+        <x:v>Native Ask Codex editor-note proposal</x:v>
       </x:c>
       <x:c r="D239" s="24" t="str">
-        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
+        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
       </x:c>
       <x:c r="E239" s="24" t="str">
-        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
+        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
       </x:c>
       <x:c r="F239" s="11" t="str">
-        <x:v>Live single-source pass; full representative batch pending</x:v>
+        <x:v>Native read-only Codex proposal pass</x:v>
       </x:c>
     </x:row>
     <x:row r="240" ht="48" customHeight="1">
       <x:c r="A240" s="10" t="str">
-        <x:v>TL-229</x:v>
+        <x:v>TL-228</x:v>
       </x:c>
       <x:c r="B240" s="24" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C240" s="24" t="str">
-        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+        <x:v>Live Marlin single-source completion</x:v>
       </x:c>
       <x:c r="D240" s="24" t="str">
-        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
       </x:c>
       <x:c r="E240" s="24" t="str">
-        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
       </x:c>
       <x:c r="F240" s="11" t="str">
-        <x:v>Native fresh-launch pixel pass</x:v>
+        <x:v>Live single-source pass; full representative batch pending</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="48" customHeight="1">
       <x:c r="A241" s="10" t="str">
-        <x:v>TL-230</x:v>
+        <x:v>TL-229</x:v>
       </x:c>
       <x:c r="B241" s="24" t="str">
         <x:v>US-045</x:v>
       </x:c>
       <x:c r="C241" s="24" t="str">
+        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+      </x:c>
+      <x:c r="D241" s="24" t="str">
+        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+      </x:c>
+      <x:c r="E241" s="24" t="str">
+        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+      </x:c>
+      <x:c r="F241" s="11" t="str">
+        <x:v>Native fresh-launch pixel pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" ht="48" customHeight="1">
+      <x:c r="A242" s="10" t="str">
+        <x:v>TL-230</x:v>
+      </x:c>
+      <x:c r="B242" s="24" t="str">
+        <x:v>US-045</x:v>
+      </x:c>
+      <x:c r="C242" s="24" t="str">
         <x:v>AX-1 exact preview promotion and pixel pass</x:v>
       </x:c>
-      <x:c r="D241" s="24" t="str">
+      <x:c r="D242" s="24" t="str">
         <x:v>Run videoos-studio-cli compile-run on projects/ax1-participant-voices-20260401, confirm playback-contract-status, select ProjectShelf.ax1-participant-voices-20260401 in VideoOSStudio, capture /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and run Retina-coordinate pixel statistics on the Viewer region.</x:v>
       </x:c>
-      <x:c r="E241" s="24" t="str">
+      <x:c r="E242" s="24" t="str">
         <x:v>Before compile, playback-contract-status returned legacy_manifest and approvalGrade=false. compile-run completed with exitCode=0, timeline compiled, indexDocuments=492, and git status stayed clean. After compile, playback-contract-status returned state=exact, approvalGrade=true, timelineHash=171378fe2bfe3a7c, and manifestBaseTimelineHash=171378fe2bfe3a7c. Native Viewer showed Exact preview / preview-editor-1775121573933.mp4 and Timeline preview D4887.MP4 with a visible interview frame. Screenshot was 3.5M; viewer_person_actual mean_rgb=(144.62,141.42,149.8) and near_black_pct=0.0004, while left pillarbox near_black_pct=1.0000 as expected.</x:v>
       </x:c>
-      <x:c r="F241" s="11" t="str">
+      <x:c r="F242" s="11" t="str">
         <x:v>Native AX-1 exact/pixel pass</x:v>
       </x:c>
     </x:row>
-    <x:row r="242" ht="48" customHeight="1">
-      <x:c r="A242" s="12" t="str">
+    <x:row r="243" ht="48" customHeight="1">
+      <x:c r="A243" s="12" t="str">
         <x:v>TL-231</x:v>
       </x:c>
-      <x:c r="B242" s="25" t="str">
+      <x:c r="B243" s="25" t="str">
         <x:v>US-050</x:v>
       </x:c>
-      <x:c r="C242" s="25" t="str">
+      <x:c r="C243" s="25" t="str">
         <x:v>Native Action Queue approval gate</x:v>
       </x:c>
-      <x:c r="D242" s="25" t="str">
+      <x:c r="D243" s="25" t="str">
         <x:v>Add ProjectPanel.ActionQueue* identifiers, relaunch VideoOSStudio, select AX-1 Project tab, inspect the Action Queue AX tree, click ProjectPanel.ActionQueueRunButton.rough-cut-review, and stop at the Codex approval gate without approving writes.</x:v>
       </x:c>
-      <x:c r="E242" s="25" t="str">
+      <x:c r="E243" s="25" t="str">
         <x:v>AX exposed ProjectPanel.ActionQueueRunButton.rough-cut-review, ProjectPanel.ActionQueueCopyButton.rough-cut-review, ProjectPanel.ActionQueueRunButton.marlin-default, and ProjectPanel.ActionQueueCopyButton.marlin-default. Clicking rough-cut-review changed the row to disabled Starting Codex session for Review..., then to Opening Codex approval gate for Review. ps showed a Codex app-server child under VideoOSStudio; git status listed only the intentional ProjectInspectorViews.swift edit, and projects/ax1-participant-voices-20260401/06_review still contained only human_notes.yaml.</x:v>
       </x:c>
-      <x:c r="F242" s="13" t="str">
+      <x:c r="F243" s="13" t="str">
         <x:v>Native approval-gate pass; write not approved</x:v>
       </x:c>
     </x:row>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra6dcc9c353694c7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rac30d92325ae4a5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Rc97cc9d0c5b74bf9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R748de6aca7e947b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Re26a7e59bde34690"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9b39550c98f14c71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R3497ad3ac3384e85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Rc66220cdddd54512"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R642f08917ade495f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Rec2ea8d925774623"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,7 +433,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 21:47 JST</x:v>
+        <x:v>2026-06-23 21:58 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -489,7 +489,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-061 pass fixed and verified skip-existing chunk progress on togakushi-camp. npx vitest run tests/marlin-analysis-stage.test.ts passed 15/0, npx tsc --noEmit --pretty false passed, and live VOS_MARLIN_PROXY_MAX_WIDTH=256 marlin-eval-run togakushi-camp --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=2 advanced from completed T084 to AST_038AB86F / T001. The run rebuilt the index with searchDocuments=286 and marlinEvents=4; marlin-status reports togakushi-camp assets=2/events=4/segmentsWithMarlinPeak=2/coverage=0.03. Prior US-061 validation remains green for lively-alt-vol5 9-source representative chunks: 9 assets, 84 events, 8 find results, coverage=1.00, canPreferMarlin=true, and repo-level canPreferMarlinAsDefault remains false pending broader cross-project coverage.</x:v>
+        <x:v>Latest US-061 pass ran the next resumable live Togakushi source after the skip-existing chunk fix. VOS_MARLIN_PROXY_MAX_WIDTH=256 marlin-eval-run togakushi-camp --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=2 advanced to AST_06D3223E / T056, rebuilt the index with searchDocuments=289 and marlinEvents=7, and marlin-status reports togakushi-camp assets=3/events=7/segmentsWithMarlinPeak=3/coverage=0.05. Prior validation remains green: npx vitest run tests/marlin-analysis-stage.test.ts 15/0, npx tsc --noEmit --pretty false, and lively-alt-vol5 9-source representative chunks at coverage=1.00/canPreferMarlin=true. Repo-level canPreferMarlinAsDefault remains false pending broader cross-project coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -497,7 +497,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest runtime/macOS CLI check is the US-061 togakushi-camp skip-existing chunk progress pass: VOS_MARLIN_PROXY_MAX_WIDTH=256 marlin-eval-run completed with indexRebuilt=true/searchDocuments=286 and added AST_038AB86F / NINJAV_S001_S001_T001.MOV after the already completed T084 source. marlin-status now reports assets=2/events=4/segmentsWithMarlinPeak=2/coverage=0.03 for togakushi-camp. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live representative completions, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest runtime/macOS CLI check is the US-061 Togakushi third-source progress pass: VOS_MARLIN_PROXY_MAX_WIDTH=256 marlin-eval-run completed with indexRebuilt=true/searchDocuments=289 and added AST_06D3223E / NINJAV_S001_S001_T056.MOV after the already completed T084 and T001 sources. marlin-status now reports assets=3/events=7/segmentsWithMarlinPeak=3/coverage=0.05 for togakushi-camp. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live representative completions, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -505,7 +505,7 @@
         <x:v>Latest US-061 follow-up</x:v>
       </x:c>
       <x:c r="B12" s="19" t="str">
-        <x:v>TL-242 fixes the resumable chunked Marlin run path so --skip-existing --max-sources=1 no longer reselects completed short sources before advancing. Verification now shows togakushi-camp assets=2/events=4/segmentsWithMarlinPeak=2/coverage=0.03/searchDocuments=286 after adding AST_038AB86F / T001; repo-level canPreferMarlinAsDefault remains false pending broader cross-project coverage.</x:v>
+        <x:v>TL-243 advances the resumable Togakushi Marlin batch to AST_06D3223E / T056 after the skip-existing chunk fix. Verification now shows togakushi-camp assets=3/events=7/segmentsWithMarlinPeak=3/coverage=0.05/searchDocuments=289; repo-level canPreferMarlinAsDefault remains false pending broader cross-project coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="220" customHeight="1">
@@ -8827,79 +8827,79 @@
     </x:row>
     <x:row r="217" ht="48" customHeight="1">
       <x:c r="A217" s="10" t="str">
-        <x:v>TL-205</x:v>
+        <x:v>TL-243</x:v>
       </x:c>
       <x:c r="B217" s="24" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C217" s="24" t="str">
-        <x:v>Native preview duration fallback</x:v>
+        <x:v>Togakushi Marlin third-source progress</x:v>
       </x:c>
       <x:c r="D217" s="24" t="str">
-        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
+        <x:v>Run the next resumable Togakushi Marlin source after the skip-existing chunk fix; rebuild the SQLite index; inspect project and repo preference status.</x:v>
       </x:c>
       <x:c r="E217" s="24" t="str">
-        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
+        <x:v>VOS_MARLIN_PROXY_MAX_WIDTH=256 .build/debug/videoos-studio-cli marlin-eval-run togakushi-camp --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=2 completed with indexRebuilt=true/searchDocuments=289/marlinEvents=7. The new source is AST_06D3223E / NINJAV_S001_S001_T056.MOV with 3 events. marlin-status now reports togakushi-camp assets=3/events=7/findResults=0/segmentsWithMarlinPeak=3/coverage=0.05/canPreferMarlin=false. marlin-preference-status remains partially ready with togakushi-camp at 3/60, aggregateCoverage=0.13, and canPreferMarlinAsDefault=false.</x:v>
       </x:c>
       <x:c r="F217" s="11" t="str">
-        <x:v>Native pixel/runtime pass</x:v>
+        <x:v>Live 3/60 representative progress; repo preference gate pending</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="48" customHeight="1">
       <x:c r="A218" s="10" t="str">
-        <x:v>TL-206</x:v>
+        <x:v>TL-205</x:v>
       </x:c>
       <x:c r="B218" s="24" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C218" s="24" t="str">
-        <x:v>Native Clip Inspector save and clear</x:v>
+        <x:v>Native preview duration fallback</x:v>
       </x:c>
       <x:c r="D218" s="24" t="str">
-        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
+        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
       </x:c>
       <x:c r="E218" s="24" t="str">
-        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
+        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F218" s="11" t="str">
-        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
+        <x:v>Native pixel/runtime pass</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="48" customHeight="1">
       <x:c r="A219" s="10" t="str">
-        <x:v>TL-207</x:v>
+        <x:v>TL-206</x:v>
       </x:c>
       <x:c r="B219" s="24" t="str">
-        <x:v>US-058</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C219" s="24" t="str">
-        <x:v>Native QA Dashboard issue jump</x:v>
+        <x:v>Native Clip Inspector save and clear</x:v>
       </x:c>
       <x:c r="D219" s="24" t="str">
-        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
+        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
       </x:c>
       <x:c r="E219" s="24" t="str">
-        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
+        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
       </x:c>
       <x:c r="F219" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="48" customHeight="1">
       <x:c r="A220" s="10" t="str">
-        <x:v>TL-208</x:v>
+        <x:v>TL-207</x:v>
       </x:c>
       <x:c r="B220" s="24" t="str">
-        <x:v>US-056</x:v>
+        <x:v>US-058</x:v>
       </x:c>
       <x:c r="C220" s="24" t="str">
-        <x:v>Native Candidate Swap sheet and staging</x:v>
+        <x:v>Native QA Dashboard issue jump</x:v>
       </x:c>
       <x:c r="D220" s="24" t="str">
-        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
+        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
       </x:c>
       <x:c r="E220" s="24" t="str">
-        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
+        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
       </x:c>
       <x:c r="F220" s="11" t="str">
         <x:v>Native AX/pixel pass</x:v>
@@ -8907,339 +8907,339 @@
     </x:row>
     <x:row r="221" ht="48" customHeight="1">
       <x:c r="A221" s="10" t="str">
-        <x:v>TL-209</x:v>
+        <x:v>TL-208</x:v>
       </x:c>
       <x:c r="B221" s="24" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-056</x:v>
       </x:c>
       <x:c r="C221" s="24" t="str">
-        <x:v>Native exact preview regeneration</x:v>
+        <x:v>Native Candidate Swap sheet and staging</x:v>
       </x:c>
       <x:c r="D221" s="24" t="str">
-        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
+        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
       </x:c>
       <x:c r="E221" s="24" t="str">
-        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
       </x:c>
       <x:c r="F221" s="11" t="str">
-        <x:v>Native exact preview pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="48" customHeight="1">
       <x:c r="A222" s="10" t="str">
-        <x:v>TL-210</x:v>
+        <x:v>TL-209</x:v>
       </x:c>
       <x:c r="B222" s="24" t="str">
-        <x:v>US-047</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C222" s="24" t="str">
-        <x:v>Native Command Palette top-bar open/close</x:v>
+        <x:v>Native exact preview regeneration</x:v>
       </x:c>
       <x:c r="D222" s="24" t="str">
-        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
+        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
       </x:c>
       <x:c r="E222" s="24" t="str">
-        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
+        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F222" s="11" t="str">
-        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
+        <x:v>Native exact preview pass</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="48" customHeight="1">
       <x:c r="A223" s="10" t="str">
-        <x:v>TL-211</x:v>
+        <x:v>TL-210</x:v>
       </x:c>
       <x:c r="B223" s="24" t="str">
         <x:v>US-047</x:v>
       </x:c>
       <x:c r="C223" s="24" t="str">
-        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
+        <x:v>Native Command Palette top-bar open/close</x:v>
       </x:c>
       <x:c r="D223" s="24" t="str">
-        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
+        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
       </x:c>
       <x:c r="E223" s="24" t="str">
-        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
+        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
       </x:c>
       <x:c r="F223" s="11" t="str">
-        <x:v>Native keyboard/AX pass</x:v>
+        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="48" customHeight="1">
       <x:c r="A224" s="10" t="str">
-        <x:v>TL-212</x:v>
+        <x:v>TL-211</x:v>
       </x:c>
       <x:c r="B224" s="24" t="str">
-        <x:v>US-048</x:v>
+        <x:v>US-047</x:v>
       </x:c>
       <x:c r="C224" s="24" t="str">
-        <x:v>Native Agent panel session lifecycle</x:v>
+        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
       </x:c>
       <x:c r="D224" s="24" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
+        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
       </x:c>
       <x:c r="E224" s="24" t="str">
-        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
+        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
       </x:c>
       <x:c r="F224" s="11" t="str">
-        <x:v>Native AX/computer-use pass</x:v>
+        <x:v>Native keyboard/AX pass</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="48" customHeight="1">
       <x:c r="A225" s="10" t="str">
-        <x:v>TL-213</x:v>
+        <x:v>TL-212</x:v>
       </x:c>
       <x:c r="B225" s="24" t="str">
-        <x:v>US-049</x:v>
+        <x:v>US-048</x:v>
       </x:c>
       <x:c r="C225" s="24" t="str">
-        <x:v>Native Status agent job read-only turn</x:v>
+        <x:v>Native Agent panel session lifecycle</x:v>
       </x:c>
       <x:c r="D225" s="24" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
       </x:c>
       <x:c r="E225" s="24" t="str">
-        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
+        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F225" s="11" t="str">
-        <x:v>Native read-only job pass; approved write pending</x:v>
+        <x:v>Native AX/computer-use pass</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="48" customHeight="1">
       <x:c r="A226" s="10" t="str">
-        <x:v>TL-214</x:v>
+        <x:v>TL-213</x:v>
       </x:c>
       <x:c r="B226" s="24" t="str">
-        <x:v>US-050</x:v>
+        <x:v>US-049</x:v>
       </x:c>
       <x:c r="C226" s="24" t="str">
-        <x:v>Native Project readiness/action queue Copy pass</x:v>
+        <x:v>Native Status agent job read-only turn</x:v>
       </x:c>
       <x:c r="D226" s="24" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
       </x:c>
       <x:c r="E226" s="24" t="str">
-        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
+        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F226" s="11" t="str">
-        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
+        <x:v>Native read-only job pass; approved write pending</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="48" customHeight="1">
       <x:c r="A227" s="10" t="str">
-        <x:v>TL-215</x:v>
+        <x:v>TL-214</x:v>
       </x:c>
       <x:c r="B227" s="24" t="str">
-        <x:v>US-051</x:v>
+        <x:v>US-050</x:v>
       </x:c>
       <x:c r="C227" s="24" t="str">
-        <x:v>Native local Source Analysis button</x:v>
+        <x:v>Native Project readiness/action queue Copy pass</x:v>
       </x:c>
       <x:c r="D227" s="24" t="str">
-        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
       </x:c>
       <x:c r="E227" s="24" t="str">
-        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
+        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
       </x:c>
       <x:c r="F227" s="11" t="str">
-        <x:v>Native local analysis pass</x:v>
+        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="48" customHeight="1">
       <x:c r="A228" s="10" t="str">
-        <x:v>TL-216</x:v>
+        <x:v>TL-215</x:v>
       </x:c>
       <x:c r="B228" s="24" t="str">
-        <x:v>US-052</x:v>
+        <x:v>US-051</x:v>
       </x:c>
       <x:c r="C228" s="24" t="str">
-        <x:v>Native Rough Cut and Review Patch buttons</x:v>
+        <x:v>Native local Source Analysis button</x:v>
       </x:c>
       <x:c r="D228" s="24" t="str">
-        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
+        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E228" s="24" t="str">
-        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
       </x:c>
       <x:c r="F228" s="11" t="str">
-        <x:v>Native compile/review patch pass</x:v>
+        <x:v>Native local analysis pass</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="48" customHeight="1">
       <x:c r="A229" s="10" t="str">
-        <x:v>TL-217</x:v>
+        <x:v>TL-216</x:v>
       </x:c>
       <x:c r="B229" s="24" t="str">
-        <x:v>US-053</x:v>
+        <x:v>US-052</x:v>
       </x:c>
       <x:c r="C229" s="24" t="str">
-        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
+        <x:v>Native Rough Cut and Review Patch buttons</x:v>
       </x:c>
       <x:c r="D229" s="24" t="str">
-        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
+        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E229" s="24" t="str">
-        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
+        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F229" s="11" t="str">
-        <x:v>Native timeline/context menu pass</x:v>
+        <x:v>Native compile/review patch pass</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="48" customHeight="1">
       <x:c r="A230" s="10" t="str">
-        <x:v>TL-218</x:v>
+        <x:v>TL-217</x:v>
       </x:c>
       <x:c r="B230" s="24" t="str">
-        <x:v>US-054</x:v>
+        <x:v>US-053</x:v>
       </x:c>
       <x:c r="C230" s="24" t="str">
-        <x:v>Native Studio feedback Apply and Undo</x:v>
+        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
       </x:c>
       <x:c r="D230" s="24" t="str">
-        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
+        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
       </x:c>
       <x:c r="E230" s="24" t="str">
-        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
       </x:c>
       <x:c r="F230" s="11" t="str">
-        <x:v>Native apply/undo pass</x:v>
+        <x:v>Native timeline/context menu pass</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="48" customHeight="1">
       <x:c r="A231" s="10" t="str">
-        <x:v>TL-219</x:v>
+        <x:v>TL-218</x:v>
       </x:c>
       <x:c r="B231" s="24" t="str">
-        <x:v>US-057</x:v>
+        <x:v>US-054</x:v>
       </x:c>
       <x:c r="C231" s="24" t="str">
-        <x:v>Native Footage Search sheet and replacement staging</x:v>
+        <x:v>Native Studio feedback Apply and Undo</x:v>
       </x:c>
       <x:c r="D231" s="24" t="str">
-        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
+        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E231" s="24" t="str">
-        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
+        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F231" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native apply/undo pass</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="48" customHeight="1">
       <x:c r="A232" s="10" t="str">
-        <x:v>TL-220</x:v>
+        <x:v>TL-219</x:v>
       </x:c>
       <x:c r="B232" s="24" t="str">
-        <x:v>US-066</x:v>
+        <x:v>US-057</x:v>
       </x:c>
       <x:c r="C232" s="24" t="str">
-        <x:v>Native Settings transport picker mutation</x:v>
+        <x:v>Native Footage Search sheet and replacement staging</x:v>
       </x:c>
       <x:c r="D232" s="24" t="str">
-        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
+        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
       </x:c>
       <x:c r="E232" s="24" t="str">
-        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
       </x:c>
       <x:c r="F232" s="11" t="str">
-        <x:v>Native Settings picker mutation pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="48" customHeight="1">
       <x:c r="A233" s="10" t="str">
-        <x:v>TL-221</x:v>
+        <x:v>TL-220</x:v>
       </x:c>
       <x:c r="B233" s="24" t="str">
-        <x:v>US-059</x:v>
+        <x:v>US-066</x:v>
       </x:c>
       <x:c r="C233" s="24" t="str">
-        <x:v>Native Media Relink buttons and source-map relink</x:v>
+        <x:v>Native Settings transport picker mutation</x:v>
       </x:c>
       <x:c r="D233" s="24" t="str">
-        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
+        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
       </x:c>
       <x:c r="E233" s="24" t="str">
-        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
+        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F233" s="11" t="str">
-        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
+        <x:v>Native Settings picker mutation pass</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="48" customHeight="1">
       <x:c r="A234" s="10" t="str">
-        <x:v>TL-222</x:v>
+        <x:v>TL-221</x:v>
       </x:c>
       <x:c r="B234" s="24" t="str">
-        <x:v>US-060</x:v>
+        <x:v>US-059</x:v>
       </x:c>
       <x:c r="C234" s="24" t="str">
-        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
+        <x:v>Native Media Relink buttons and source-map relink</x:v>
       </x:c>
       <x:c r="D234" s="24" t="str">
-        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
+        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
       </x:c>
       <x:c r="E234" s="24" t="str">
-        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
+        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
       </x:c>
       <x:c r="F234" s="11" t="str">
-        <x:v>Native synthetic/proxy/smoke button pass</x:v>
+        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="48" customHeight="1">
       <x:c r="A235" s="10" t="str">
-        <x:v>TL-223</x:v>
+        <x:v>TL-222</x:v>
       </x:c>
       <x:c r="B235" s="24" t="str">
-        <x:v>US-046</x:v>
+        <x:v>US-060</x:v>
       </x:c>
       <x:c r="C235" s="24" t="str">
-        <x:v>Native New Project from Source</x:v>
+        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
       </x:c>
       <x:c r="D235" s="24" t="str">
-        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
+        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
       </x:c>
       <x:c r="E235" s="24" t="str">
-        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
+        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
       </x:c>
       <x:c r="F235" s="11" t="str">
-        <x:v>Native project creation/NSOpenPanel pass</x:v>
+        <x:v>Native synthetic/proxy/smoke button pass</x:v>
       </x:c>
     </x:row>
     <x:row r="236" ht="48" customHeight="1">
       <x:c r="A236" s="10" t="str">
-        <x:v>TL-224</x:v>
+        <x:v>TL-223</x:v>
       </x:c>
       <x:c r="B236" s="24" t="str">
-        <x:v>US-062</x:v>
+        <x:v>US-046</x:v>
       </x:c>
       <x:c r="C236" s="24" t="str">
-        <x:v>Native MediaPanel Audio Story Graph button</x:v>
+        <x:v>Native New Project from Source</x:v>
       </x:c>
       <x:c r="D236" s="24" t="str">
-        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
+        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
       </x:c>
       <x:c r="E236" s="24" t="str">
-        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
       </x:c>
       <x:c r="F236" s="11" t="str">
-        <x:v>Native AX/UI/CLI pass</x:v>
+        <x:v>Native project creation/NSOpenPanel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="237" ht="48" customHeight="1">
       <x:c r="A237" s="10" t="str">
-        <x:v>TL-225</x:v>
+        <x:v>TL-224</x:v>
       </x:c>
       <x:c r="B237" s="24" t="str">
-        <x:v>US-063</x:v>
+        <x:v>US-062</x:v>
       </x:c>
       <x:c r="C237" s="24" t="str">
-        <x:v>Native Render Final Package button</x:v>
+        <x:v>Native MediaPanel Audio Story Graph button</x:v>
       </x:c>
       <x:c r="D237" s="24" t="str">
-        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
+        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E237" s="24" t="str">
-        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F237" s="11" t="str">
         <x:v>Native AX/UI/CLI pass</x:v>
@@ -9247,121 +9247,141 @@
     </x:row>
     <x:row r="238" ht="48" customHeight="1">
       <x:c r="A238" s="10" t="str">
-        <x:v>TL-226</x:v>
+        <x:v>TL-225</x:v>
       </x:c>
       <x:c r="B238" s="24" t="str">
-        <x:v>US-064</x:v>
+        <x:v>US-063</x:v>
       </x:c>
       <x:c r="C238" s="24" t="str">
-        <x:v>Native Editor Handoff export and Finder reveal</x:v>
+        <x:v>Native Render Final Package button</x:v>
       </x:c>
       <x:c r="D238" s="24" t="str">
-        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
+        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
       </x:c>
       <x:c r="E238" s="24" t="str">
-        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
+        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F238" s="11" t="str">
-        <x:v>Native AX/UI/Finder/CLI pass</x:v>
+        <x:v>Native AX/UI/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="239" ht="48" customHeight="1">
       <x:c r="A239" s="10" t="str">
-        <x:v>TL-227</x:v>
+        <x:v>TL-226</x:v>
       </x:c>
       <x:c r="B239" s="24" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-064</x:v>
       </x:c>
       <x:c r="C239" s="24" t="str">
-        <x:v>Native Ask Codex editor-note proposal</x:v>
+        <x:v>Native Editor Handoff export and Finder reveal</x:v>
       </x:c>
       <x:c r="D239" s="24" t="str">
-        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
+        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E239" s="24" t="str">
-        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
+        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
       </x:c>
       <x:c r="F239" s="11" t="str">
-        <x:v>Native read-only Codex proposal pass</x:v>
+        <x:v>Native AX/UI/Finder/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="240" ht="48" customHeight="1">
       <x:c r="A240" s="10" t="str">
-        <x:v>TL-228</x:v>
+        <x:v>TL-227</x:v>
       </x:c>
       <x:c r="B240" s="24" t="str">
-        <x:v>US-061</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C240" s="24" t="str">
-        <x:v>Live Marlin single-source completion</x:v>
+        <x:v>Native Ask Codex editor-note proposal</x:v>
       </x:c>
       <x:c r="D240" s="24" t="str">
-        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
+        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
       </x:c>
       <x:c r="E240" s="24" t="str">
-        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
+        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
       </x:c>
       <x:c r="F240" s="11" t="str">
-        <x:v>Live single-source pass; full representative batch pending</x:v>
+        <x:v>Native read-only Codex proposal pass</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="48" customHeight="1">
       <x:c r="A241" s="10" t="str">
-        <x:v>TL-229</x:v>
+        <x:v>TL-228</x:v>
       </x:c>
       <x:c r="B241" s="24" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C241" s="24" t="str">
-        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+        <x:v>Live Marlin single-source completion</x:v>
       </x:c>
       <x:c r="D241" s="24" t="str">
-        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
       </x:c>
       <x:c r="E241" s="24" t="str">
-        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
       </x:c>
       <x:c r="F241" s="11" t="str">
-        <x:v>Native fresh-launch pixel pass</x:v>
+        <x:v>Live single-source pass; full representative batch pending</x:v>
       </x:c>
     </x:row>
     <x:row r="242" ht="48" customHeight="1">
       <x:c r="A242" s="10" t="str">
-        <x:v>TL-230</x:v>
+        <x:v>TL-229</x:v>
       </x:c>
       <x:c r="B242" s="24" t="str">
         <x:v>US-045</x:v>
       </x:c>
       <x:c r="C242" s="24" t="str">
+        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+      </x:c>
+      <x:c r="D242" s="24" t="str">
+        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+      </x:c>
+      <x:c r="E242" s="24" t="str">
+        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+      </x:c>
+      <x:c r="F242" s="11" t="str">
+        <x:v>Native fresh-launch pixel pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" ht="48" customHeight="1">
+      <x:c r="A243" s="10" t="str">
+        <x:v>TL-230</x:v>
+      </x:c>
+      <x:c r="B243" s="24" t="str">
+        <x:v>US-045</x:v>
+      </x:c>
+      <x:c r="C243" s="24" t="str">
         <x:v>AX-1 exact preview promotion and pixel pass</x:v>
       </x:c>
-      <x:c r="D242" s="24" t="str">
+      <x:c r="D243" s="24" t="str">
         <x:v>Run videoos-studio-cli compile-run on projects/ax1-participant-voices-20260401, confirm playback-contract-status, select ProjectShelf.ax1-participant-voices-20260401 in VideoOSStudio, capture /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and run Retina-coordinate pixel statistics on the Viewer region.</x:v>
       </x:c>
-      <x:c r="E242" s="24" t="str">
+      <x:c r="E243" s="24" t="str">
         <x:v>Before compile, playback-contract-status returned legacy_manifest and approvalGrade=false. compile-run completed with exitCode=0, timeline compiled, indexDocuments=492, and git status stayed clean. After compile, playback-contract-status returned state=exact, approvalGrade=true, timelineHash=171378fe2bfe3a7c, and manifestBaseTimelineHash=171378fe2bfe3a7c. Native Viewer showed Exact preview / preview-editor-1775121573933.mp4 and Timeline preview D4887.MP4 with a visible interview frame. Screenshot was 3.5M; viewer_person_actual mean_rgb=(144.62,141.42,149.8) and near_black_pct=0.0004, while left pillarbox near_black_pct=1.0000 as expected.</x:v>
       </x:c>
-      <x:c r="F242" s="11" t="str">
+      <x:c r="F243" s="11" t="str">
         <x:v>Native AX-1 exact/pixel pass</x:v>
       </x:c>
     </x:row>
-    <x:row r="243" ht="48" customHeight="1">
-      <x:c r="A243" s="12" t="str">
+    <x:row r="244" ht="48" customHeight="1">
+      <x:c r="A244" s="12" t="str">
         <x:v>TL-231</x:v>
       </x:c>
-      <x:c r="B243" s="25" t="str">
+      <x:c r="B244" s="25" t="str">
         <x:v>US-050</x:v>
       </x:c>
-      <x:c r="C243" s="25" t="str">
+      <x:c r="C244" s="25" t="str">
         <x:v>Native Action Queue approval gate</x:v>
       </x:c>
-      <x:c r="D243" s="25" t="str">
+      <x:c r="D244" s="25" t="str">
         <x:v>Add ProjectPanel.ActionQueue* identifiers, relaunch VideoOSStudio, select AX-1 Project tab, inspect the Action Queue AX tree, click ProjectPanel.ActionQueueRunButton.rough-cut-review, and stop at the Codex approval gate without approving writes.</x:v>
       </x:c>
-      <x:c r="E243" s="25" t="str">
+      <x:c r="E244" s="25" t="str">
         <x:v>AX exposed ProjectPanel.ActionQueueRunButton.rough-cut-review, ProjectPanel.ActionQueueCopyButton.rough-cut-review, ProjectPanel.ActionQueueRunButton.marlin-default, and ProjectPanel.ActionQueueCopyButton.marlin-default. Clicking rough-cut-review changed the row to disabled Starting Codex session for Review..., then to Opening Codex approval gate for Review. ps showed a Codex app-server child under VideoOSStudio; git status listed only the intentional ProjectInspectorViews.swift edit, and projects/ax1-participant-voices-20260401/06_review still contained only human_notes.yaml.</x:v>
       </x:c>
-      <x:c r="F243" s="13" t="str">
+      <x:c r="F244" s="13" t="str">
         <x:v>Native approval-gate pass; write not approved</x:v>
       </x:c>
     </x:row>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9b39550c98f14c71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R3497ad3ac3384e85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Rc66220cdddd54512"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R642f08917ade495f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Rec2ea8d925774623"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rbf130fe827224b0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rcca903e2e0f74db5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Rc1eae7c812364c86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R98c2160205934aa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R7168049155284c25"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,7 +433,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 21:58 JST</x:v>
+        <x:v>2026-06-23 22:09 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -489,7 +489,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-061 pass ran the next resumable live Togakushi source after the skip-existing chunk fix. VOS_MARLIN_PROXY_MAX_WIDTH=256 marlin-eval-run togakushi-camp --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=2 advanced to AST_06D3223E / T056, rebuilt the index with searchDocuments=289 and marlinEvents=7, and marlin-status reports togakushi-camp assets=3/events=7/segmentsWithMarlinPeak=3/coverage=0.05. Prior validation remains green: npx vitest run tests/marlin-analysis-stage.test.ts 15/0, npx tsc --noEmit --pretty false, and lively-alt-vol5 9-source representative chunks at coverage=1.00/canPreferMarlin=true. Repo-level canPreferMarlinAsDefault remains false pending broader cross-project coverage.</x:v>
+        <x:v>Latest US-061 pass followed marlin-eval-next to rokutaro-graduation-20260319 and ran one bounded live caption-only source. swift build --target VideoOSStudioCLI passed, then VOS_MARLIN_PROXY_MAX_WIDTH=256 marlin-eval-run rokutaro-graduation-20260319 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=2 completed with indexRebuilt=true, searchDocuments=248, marlinEvents=1, and AST_73DD5497 / IMG_2911_still.mp4 materialized SEG_AST_73DD5497_0001 with marlin_temporal_semantics peak_analysis. Prior validation remains green: npx vitest run tests/marlin-analysis-stage.test.ts 15/0, npx tsc --noEmit --pretty false, and lively-alt-vol5 9-source representative chunks at coverage=1.00/canPreferMarlin=true. Repo-level canPreferMarlinAsDefault remains false pending broader cross-project coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -497,7 +497,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest runtime/macOS CLI check is the US-061 Togakushi third-source progress pass: VOS_MARLIN_PROXY_MAX_WIDTH=256 marlin-eval-run completed with indexRebuilt=true/searchDocuments=289 and added AST_06D3223E / NINJAV_S001_S001_T056.MOV after the already completed T084 and T001 sources. marlin-status now reports assets=3/events=7/segmentsWithMarlinPeak=3/coverage=0.05 for togakushi-camp. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live representative completions, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest runtime/macOS CLI check is the US-061 next-project Marlin progress pass: VOS_MARLIN_PROXY_MAX_WIDTH=256 marlin-eval-run completed with indexRebuilt=true/searchDocuments=248 and added AST_73DD5497 / IMG_2911_still.mp4 to rokutaro-graduation-20260319. marlin-status now reports that project assets=1/events=1/segmentsWithMarlinPeak=1/coverage=0.08, while marlin-preference-status reports evaluatedProjects=10, coveredSegments=48, aggregateCoverage=0.13, and canPreferMarlinAsDefault=false. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live representative completions, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -505,7 +505,7 @@
         <x:v>Latest US-061 follow-up</x:v>
       </x:c>
       <x:c r="B12" s="19" t="str">
-        <x:v>TL-243 advances the resumable Togakushi Marlin batch to AST_06D3223E / T056 after the skip-existing chunk fix. Verification now shows togakushi-camp assets=3/events=7/segmentsWithMarlinPeak=3/coverage=0.05/searchDocuments=289; repo-level canPreferMarlinAsDefault remains false pending broader cross-project coverage.</x:v>
+        <x:v>TL-244 advances the Marlin representative queue into rokutaro-graduation-20260319 via AST_73DD5497 / IMG_2911_still.mp4. Verification now shows rokutaro-graduation-20260319 assets=1/events=1/segmentsWithMarlinPeak=1/coverage=0.08/searchDocuments=248; repo-level canPreferMarlinAsDefault remains false pending broader cross-project coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="220" customHeight="1">
@@ -8847,79 +8847,79 @@
     </x:row>
     <x:row r="218" ht="48" customHeight="1">
       <x:c r="A218" s="10" t="str">
-        <x:v>TL-205</x:v>
+        <x:v>TL-244</x:v>
       </x:c>
       <x:c r="B218" s="24" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C218" s="24" t="str">
-        <x:v>Native preview duration fallback</x:v>
+        <x:v>Rokutaro graduation Marlin next-project progress</x:v>
       </x:c>
       <x:c r="D218" s="24" t="str">
-        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
+        <x:v>Run the next project returned by marlin-eval-next with one bounded live caption-only source; rebuild the SQLite index; inspect artifact, segment materialization, project status, and repo preference status.</x:v>
       </x:c>
       <x:c r="E218" s="24" t="str">
-        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
+        <x:v>swift build --target VideoOSStudioCLI passed. VOS_MARLIN_PROXY_MAX_WIDTH=256 .build/debug/videoos-studio-cli marlin-eval-run rokutaro-graduation-20260319 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=2 completed with indexRebuilt=true/searchDocuments=248/marlinEvents=1. The new live source is AST_73DD5497 / IMG_2911_still.mp4 with one event, SEG_AST_73DD5497_0001 gained marlin_temporal_semantics peak_analysis, and marlin-status reports assets=1/events=1/findResults=0/segmentsWithMarlinPeak=1/coverage=0.08/canPreferMarlin=false. marlin-preference-status now reports evaluatedProjects=10, coveredSegments=48, aggregateCoverage=0.13, and canPreferMarlinAsDefault=false.</x:v>
       </x:c>
       <x:c r="F218" s="11" t="str">
-        <x:v>Native pixel/runtime pass</x:v>
+        <x:v>Live next-project representative progress; repo preference gate pending</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="48" customHeight="1">
       <x:c r="A219" s="10" t="str">
-        <x:v>TL-206</x:v>
+        <x:v>TL-205</x:v>
       </x:c>
       <x:c r="B219" s="24" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C219" s="24" t="str">
-        <x:v>Native Clip Inspector save and clear</x:v>
+        <x:v>Native preview duration fallback</x:v>
       </x:c>
       <x:c r="D219" s="24" t="str">
-        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
+        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
       </x:c>
       <x:c r="E219" s="24" t="str">
-        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
+        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F219" s="11" t="str">
-        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
+        <x:v>Native pixel/runtime pass</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="48" customHeight="1">
       <x:c r="A220" s="10" t="str">
-        <x:v>TL-207</x:v>
+        <x:v>TL-206</x:v>
       </x:c>
       <x:c r="B220" s="24" t="str">
-        <x:v>US-058</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C220" s="24" t="str">
-        <x:v>Native QA Dashboard issue jump</x:v>
+        <x:v>Native Clip Inspector save and clear</x:v>
       </x:c>
       <x:c r="D220" s="24" t="str">
-        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
+        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
       </x:c>
       <x:c r="E220" s="24" t="str">
-        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
+        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
       </x:c>
       <x:c r="F220" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="48" customHeight="1">
       <x:c r="A221" s="10" t="str">
-        <x:v>TL-208</x:v>
+        <x:v>TL-207</x:v>
       </x:c>
       <x:c r="B221" s="24" t="str">
-        <x:v>US-056</x:v>
+        <x:v>US-058</x:v>
       </x:c>
       <x:c r="C221" s="24" t="str">
-        <x:v>Native Candidate Swap sheet and staging</x:v>
+        <x:v>Native QA Dashboard issue jump</x:v>
       </x:c>
       <x:c r="D221" s="24" t="str">
-        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
+        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
       </x:c>
       <x:c r="E221" s="24" t="str">
-        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
+        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
       </x:c>
       <x:c r="F221" s="11" t="str">
         <x:v>Native AX/pixel pass</x:v>
@@ -8927,339 +8927,339 @@
     </x:row>
     <x:row r="222" ht="48" customHeight="1">
       <x:c r="A222" s="10" t="str">
-        <x:v>TL-209</x:v>
+        <x:v>TL-208</x:v>
       </x:c>
       <x:c r="B222" s="24" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-056</x:v>
       </x:c>
       <x:c r="C222" s="24" t="str">
-        <x:v>Native exact preview regeneration</x:v>
+        <x:v>Native Candidate Swap sheet and staging</x:v>
       </x:c>
       <x:c r="D222" s="24" t="str">
-        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
+        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
       </x:c>
       <x:c r="E222" s="24" t="str">
-        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
       </x:c>
       <x:c r="F222" s="11" t="str">
-        <x:v>Native exact preview pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="48" customHeight="1">
       <x:c r="A223" s="10" t="str">
-        <x:v>TL-210</x:v>
+        <x:v>TL-209</x:v>
       </x:c>
       <x:c r="B223" s="24" t="str">
-        <x:v>US-047</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C223" s="24" t="str">
-        <x:v>Native Command Palette top-bar open/close</x:v>
+        <x:v>Native exact preview regeneration</x:v>
       </x:c>
       <x:c r="D223" s="24" t="str">
-        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
+        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
       </x:c>
       <x:c r="E223" s="24" t="str">
-        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
+        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F223" s="11" t="str">
-        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
+        <x:v>Native exact preview pass</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="48" customHeight="1">
       <x:c r="A224" s="10" t="str">
-        <x:v>TL-211</x:v>
+        <x:v>TL-210</x:v>
       </x:c>
       <x:c r="B224" s="24" t="str">
         <x:v>US-047</x:v>
       </x:c>
       <x:c r="C224" s="24" t="str">
-        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
+        <x:v>Native Command Palette top-bar open/close</x:v>
       </x:c>
       <x:c r="D224" s="24" t="str">
-        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
+        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
       </x:c>
       <x:c r="E224" s="24" t="str">
-        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
+        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
       </x:c>
       <x:c r="F224" s="11" t="str">
-        <x:v>Native keyboard/AX pass</x:v>
+        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="48" customHeight="1">
       <x:c r="A225" s="10" t="str">
-        <x:v>TL-212</x:v>
+        <x:v>TL-211</x:v>
       </x:c>
       <x:c r="B225" s="24" t="str">
-        <x:v>US-048</x:v>
+        <x:v>US-047</x:v>
       </x:c>
       <x:c r="C225" s="24" t="str">
-        <x:v>Native Agent panel session lifecycle</x:v>
+        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
       </x:c>
       <x:c r="D225" s="24" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
+        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
       </x:c>
       <x:c r="E225" s="24" t="str">
-        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
+        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
       </x:c>
       <x:c r="F225" s="11" t="str">
-        <x:v>Native AX/computer-use pass</x:v>
+        <x:v>Native keyboard/AX pass</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="48" customHeight="1">
       <x:c r="A226" s="10" t="str">
-        <x:v>TL-213</x:v>
+        <x:v>TL-212</x:v>
       </x:c>
       <x:c r="B226" s="24" t="str">
-        <x:v>US-049</x:v>
+        <x:v>US-048</x:v>
       </x:c>
       <x:c r="C226" s="24" t="str">
-        <x:v>Native Status agent job read-only turn</x:v>
+        <x:v>Native Agent panel session lifecycle</x:v>
       </x:c>
       <x:c r="D226" s="24" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
       </x:c>
       <x:c r="E226" s="24" t="str">
-        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
+        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F226" s="11" t="str">
-        <x:v>Native read-only job pass; approved write pending</x:v>
+        <x:v>Native AX/computer-use pass</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="48" customHeight="1">
       <x:c r="A227" s="10" t="str">
-        <x:v>TL-214</x:v>
+        <x:v>TL-213</x:v>
       </x:c>
       <x:c r="B227" s="24" t="str">
-        <x:v>US-050</x:v>
+        <x:v>US-049</x:v>
       </x:c>
       <x:c r="C227" s="24" t="str">
-        <x:v>Native Project readiness/action queue Copy pass</x:v>
+        <x:v>Native Status agent job read-only turn</x:v>
       </x:c>
       <x:c r="D227" s="24" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
       </x:c>
       <x:c r="E227" s="24" t="str">
-        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
+        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F227" s="11" t="str">
-        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
+        <x:v>Native read-only job pass; approved write pending</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="48" customHeight="1">
       <x:c r="A228" s="10" t="str">
-        <x:v>TL-215</x:v>
+        <x:v>TL-214</x:v>
       </x:c>
       <x:c r="B228" s="24" t="str">
-        <x:v>US-051</x:v>
+        <x:v>US-050</x:v>
       </x:c>
       <x:c r="C228" s="24" t="str">
-        <x:v>Native local Source Analysis button</x:v>
+        <x:v>Native Project readiness/action queue Copy pass</x:v>
       </x:c>
       <x:c r="D228" s="24" t="str">
-        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
       </x:c>
       <x:c r="E228" s="24" t="str">
-        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
+        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
       </x:c>
       <x:c r="F228" s="11" t="str">
-        <x:v>Native local analysis pass</x:v>
+        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="48" customHeight="1">
       <x:c r="A229" s="10" t="str">
-        <x:v>TL-216</x:v>
+        <x:v>TL-215</x:v>
       </x:c>
       <x:c r="B229" s="24" t="str">
-        <x:v>US-052</x:v>
+        <x:v>US-051</x:v>
       </x:c>
       <x:c r="C229" s="24" t="str">
-        <x:v>Native Rough Cut and Review Patch buttons</x:v>
+        <x:v>Native local Source Analysis button</x:v>
       </x:c>
       <x:c r="D229" s="24" t="str">
-        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
+        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E229" s="24" t="str">
-        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
       </x:c>
       <x:c r="F229" s="11" t="str">
-        <x:v>Native compile/review patch pass</x:v>
+        <x:v>Native local analysis pass</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="48" customHeight="1">
       <x:c r="A230" s="10" t="str">
-        <x:v>TL-217</x:v>
+        <x:v>TL-216</x:v>
       </x:c>
       <x:c r="B230" s="24" t="str">
-        <x:v>US-053</x:v>
+        <x:v>US-052</x:v>
       </x:c>
       <x:c r="C230" s="24" t="str">
-        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
+        <x:v>Native Rough Cut and Review Patch buttons</x:v>
       </x:c>
       <x:c r="D230" s="24" t="str">
-        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
+        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E230" s="24" t="str">
-        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
+        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F230" s="11" t="str">
-        <x:v>Native timeline/context menu pass</x:v>
+        <x:v>Native compile/review patch pass</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="48" customHeight="1">
       <x:c r="A231" s="10" t="str">
-        <x:v>TL-218</x:v>
+        <x:v>TL-217</x:v>
       </x:c>
       <x:c r="B231" s="24" t="str">
-        <x:v>US-054</x:v>
+        <x:v>US-053</x:v>
       </x:c>
       <x:c r="C231" s="24" t="str">
-        <x:v>Native Studio feedback Apply and Undo</x:v>
+        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
       </x:c>
       <x:c r="D231" s="24" t="str">
-        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
+        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
       </x:c>
       <x:c r="E231" s="24" t="str">
-        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
       </x:c>
       <x:c r="F231" s="11" t="str">
-        <x:v>Native apply/undo pass</x:v>
+        <x:v>Native timeline/context menu pass</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="48" customHeight="1">
       <x:c r="A232" s="10" t="str">
-        <x:v>TL-219</x:v>
+        <x:v>TL-218</x:v>
       </x:c>
       <x:c r="B232" s="24" t="str">
-        <x:v>US-057</x:v>
+        <x:v>US-054</x:v>
       </x:c>
       <x:c r="C232" s="24" t="str">
-        <x:v>Native Footage Search sheet and replacement staging</x:v>
+        <x:v>Native Studio feedback Apply and Undo</x:v>
       </x:c>
       <x:c r="D232" s="24" t="str">
-        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
+        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E232" s="24" t="str">
-        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
+        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F232" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native apply/undo pass</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="48" customHeight="1">
       <x:c r="A233" s="10" t="str">
-        <x:v>TL-220</x:v>
+        <x:v>TL-219</x:v>
       </x:c>
       <x:c r="B233" s="24" t="str">
-        <x:v>US-066</x:v>
+        <x:v>US-057</x:v>
       </x:c>
       <x:c r="C233" s="24" t="str">
-        <x:v>Native Settings transport picker mutation</x:v>
+        <x:v>Native Footage Search sheet and replacement staging</x:v>
       </x:c>
       <x:c r="D233" s="24" t="str">
-        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
+        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
       </x:c>
       <x:c r="E233" s="24" t="str">
-        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
       </x:c>
       <x:c r="F233" s="11" t="str">
-        <x:v>Native Settings picker mutation pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="48" customHeight="1">
       <x:c r="A234" s="10" t="str">
-        <x:v>TL-221</x:v>
+        <x:v>TL-220</x:v>
       </x:c>
       <x:c r="B234" s="24" t="str">
-        <x:v>US-059</x:v>
+        <x:v>US-066</x:v>
       </x:c>
       <x:c r="C234" s="24" t="str">
-        <x:v>Native Media Relink buttons and source-map relink</x:v>
+        <x:v>Native Settings transport picker mutation</x:v>
       </x:c>
       <x:c r="D234" s="24" t="str">
-        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
+        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
       </x:c>
       <x:c r="E234" s="24" t="str">
-        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
+        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F234" s="11" t="str">
-        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
+        <x:v>Native Settings picker mutation pass</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="48" customHeight="1">
       <x:c r="A235" s="10" t="str">
-        <x:v>TL-222</x:v>
+        <x:v>TL-221</x:v>
       </x:c>
       <x:c r="B235" s="24" t="str">
-        <x:v>US-060</x:v>
+        <x:v>US-059</x:v>
       </x:c>
       <x:c r="C235" s="24" t="str">
-        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
+        <x:v>Native Media Relink buttons and source-map relink</x:v>
       </x:c>
       <x:c r="D235" s="24" t="str">
-        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
+        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
       </x:c>
       <x:c r="E235" s="24" t="str">
-        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
+        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
       </x:c>
       <x:c r="F235" s="11" t="str">
-        <x:v>Native synthetic/proxy/smoke button pass</x:v>
+        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
       </x:c>
     </x:row>
     <x:row r="236" ht="48" customHeight="1">
       <x:c r="A236" s="10" t="str">
-        <x:v>TL-223</x:v>
+        <x:v>TL-222</x:v>
       </x:c>
       <x:c r="B236" s="24" t="str">
-        <x:v>US-046</x:v>
+        <x:v>US-060</x:v>
       </x:c>
       <x:c r="C236" s="24" t="str">
-        <x:v>Native New Project from Source</x:v>
+        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
       </x:c>
       <x:c r="D236" s="24" t="str">
-        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
+        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
       </x:c>
       <x:c r="E236" s="24" t="str">
-        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
+        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
       </x:c>
       <x:c r="F236" s="11" t="str">
-        <x:v>Native project creation/NSOpenPanel pass</x:v>
+        <x:v>Native synthetic/proxy/smoke button pass</x:v>
       </x:c>
     </x:row>
     <x:row r="237" ht="48" customHeight="1">
       <x:c r="A237" s="10" t="str">
-        <x:v>TL-224</x:v>
+        <x:v>TL-223</x:v>
       </x:c>
       <x:c r="B237" s="24" t="str">
-        <x:v>US-062</x:v>
+        <x:v>US-046</x:v>
       </x:c>
       <x:c r="C237" s="24" t="str">
-        <x:v>Native MediaPanel Audio Story Graph button</x:v>
+        <x:v>Native New Project from Source</x:v>
       </x:c>
       <x:c r="D237" s="24" t="str">
-        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
+        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
       </x:c>
       <x:c r="E237" s="24" t="str">
-        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
       </x:c>
       <x:c r="F237" s="11" t="str">
-        <x:v>Native AX/UI/CLI pass</x:v>
+        <x:v>Native project creation/NSOpenPanel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="238" ht="48" customHeight="1">
       <x:c r="A238" s="10" t="str">
-        <x:v>TL-225</x:v>
+        <x:v>TL-224</x:v>
       </x:c>
       <x:c r="B238" s="24" t="str">
-        <x:v>US-063</x:v>
+        <x:v>US-062</x:v>
       </x:c>
       <x:c r="C238" s="24" t="str">
-        <x:v>Native Render Final Package button</x:v>
+        <x:v>Native MediaPanel Audio Story Graph button</x:v>
       </x:c>
       <x:c r="D238" s="24" t="str">
-        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
+        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E238" s="24" t="str">
-        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F238" s="11" t="str">
         <x:v>Native AX/UI/CLI pass</x:v>
@@ -9267,121 +9267,141 @@
     </x:row>
     <x:row r="239" ht="48" customHeight="1">
       <x:c r="A239" s="10" t="str">
-        <x:v>TL-226</x:v>
+        <x:v>TL-225</x:v>
       </x:c>
       <x:c r="B239" s="24" t="str">
-        <x:v>US-064</x:v>
+        <x:v>US-063</x:v>
       </x:c>
       <x:c r="C239" s="24" t="str">
-        <x:v>Native Editor Handoff export and Finder reveal</x:v>
+        <x:v>Native Render Final Package button</x:v>
       </x:c>
       <x:c r="D239" s="24" t="str">
-        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
+        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
       </x:c>
       <x:c r="E239" s="24" t="str">
-        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
+        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F239" s="11" t="str">
-        <x:v>Native AX/UI/Finder/CLI pass</x:v>
+        <x:v>Native AX/UI/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="240" ht="48" customHeight="1">
       <x:c r="A240" s="10" t="str">
-        <x:v>TL-227</x:v>
+        <x:v>TL-226</x:v>
       </x:c>
       <x:c r="B240" s="24" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-064</x:v>
       </x:c>
       <x:c r="C240" s="24" t="str">
-        <x:v>Native Ask Codex editor-note proposal</x:v>
+        <x:v>Native Editor Handoff export and Finder reveal</x:v>
       </x:c>
       <x:c r="D240" s="24" t="str">
-        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
+        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E240" s="24" t="str">
-        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
+        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
       </x:c>
       <x:c r="F240" s="11" t="str">
-        <x:v>Native read-only Codex proposal pass</x:v>
+        <x:v>Native AX/UI/Finder/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="48" customHeight="1">
       <x:c r="A241" s="10" t="str">
-        <x:v>TL-228</x:v>
+        <x:v>TL-227</x:v>
       </x:c>
       <x:c r="B241" s="24" t="str">
-        <x:v>US-061</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C241" s="24" t="str">
-        <x:v>Live Marlin single-source completion</x:v>
+        <x:v>Native Ask Codex editor-note proposal</x:v>
       </x:c>
       <x:c r="D241" s="24" t="str">
-        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
+        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
       </x:c>
       <x:c r="E241" s="24" t="str">
-        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
+        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
       </x:c>
       <x:c r="F241" s="11" t="str">
-        <x:v>Live single-source pass; full representative batch pending</x:v>
+        <x:v>Native read-only Codex proposal pass</x:v>
       </x:c>
     </x:row>
     <x:row r="242" ht="48" customHeight="1">
       <x:c r="A242" s="10" t="str">
-        <x:v>TL-229</x:v>
+        <x:v>TL-228</x:v>
       </x:c>
       <x:c r="B242" s="24" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C242" s="24" t="str">
-        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+        <x:v>Live Marlin single-source completion</x:v>
       </x:c>
       <x:c r="D242" s="24" t="str">
-        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
       </x:c>
       <x:c r="E242" s="24" t="str">
-        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
       </x:c>
       <x:c r="F242" s="11" t="str">
-        <x:v>Native fresh-launch pixel pass</x:v>
+        <x:v>Live single-source pass; full representative batch pending</x:v>
       </x:c>
     </x:row>
     <x:row r="243" ht="48" customHeight="1">
       <x:c r="A243" s="10" t="str">
-        <x:v>TL-230</x:v>
+        <x:v>TL-229</x:v>
       </x:c>
       <x:c r="B243" s="24" t="str">
         <x:v>US-045</x:v>
       </x:c>
       <x:c r="C243" s="24" t="str">
+        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+      </x:c>
+      <x:c r="D243" s="24" t="str">
+        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+      </x:c>
+      <x:c r="E243" s="24" t="str">
+        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+      </x:c>
+      <x:c r="F243" s="11" t="str">
+        <x:v>Native fresh-launch pixel pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" ht="48" customHeight="1">
+      <x:c r="A244" s="10" t="str">
+        <x:v>TL-230</x:v>
+      </x:c>
+      <x:c r="B244" s="24" t="str">
+        <x:v>US-045</x:v>
+      </x:c>
+      <x:c r="C244" s="24" t="str">
         <x:v>AX-1 exact preview promotion and pixel pass</x:v>
       </x:c>
-      <x:c r="D243" s="24" t="str">
+      <x:c r="D244" s="24" t="str">
         <x:v>Run videoos-studio-cli compile-run on projects/ax1-participant-voices-20260401, confirm playback-contract-status, select ProjectShelf.ax1-participant-voices-20260401 in VideoOSStudio, capture /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and run Retina-coordinate pixel statistics on the Viewer region.</x:v>
       </x:c>
-      <x:c r="E243" s="24" t="str">
+      <x:c r="E244" s="24" t="str">
         <x:v>Before compile, playback-contract-status returned legacy_manifest and approvalGrade=false. compile-run completed with exitCode=0, timeline compiled, indexDocuments=492, and git status stayed clean. After compile, playback-contract-status returned state=exact, approvalGrade=true, timelineHash=171378fe2bfe3a7c, and manifestBaseTimelineHash=171378fe2bfe3a7c. Native Viewer showed Exact preview / preview-editor-1775121573933.mp4 and Timeline preview D4887.MP4 with a visible interview frame. Screenshot was 3.5M; viewer_person_actual mean_rgb=(144.62,141.42,149.8) and near_black_pct=0.0004, while left pillarbox near_black_pct=1.0000 as expected.</x:v>
       </x:c>
-      <x:c r="F243" s="11" t="str">
+      <x:c r="F244" s="11" t="str">
         <x:v>Native AX-1 exact/pixel pass</x:v>
       </x:c>
     </x:row>
-    <x:row r="244" ht="48" customHeight="1">
-      <x:c r="A244" s="12" t="str">
+    <x:row r="245" ht="48" customHeight="1">
+      <x:c r="A245" s="12" t="str">
         <x:v>TL-231</x:v>
       </x:c>
-      <x:c r="B244" s="25" t="str">
+      <x:c r="B245" s="25" t="str">
         <x:v>US-050</x:v>
       </x:c>
-      <x:c r="C244" s="25" t="str">
+      <x:c r="C245" s="25" t="str">
         <x:v>Native Action Queue approval gate</x:v>
       </x:c>
-      <x:c r="D244" s="25" t="str">
+      <x:c r="D245" s="25" t="str">
         <x:v>Add ProjectPanel.ActionQueue* identifiers, relaunch VideoOSStudio, select AX-1 Project tab, inspect the Action Queue AX tree, click ProjectPanel.ActionQueueRunButton.rough-cut-review, and stop at the Codex approval gate without approving writes.</x:v>
       </x:c>
-      <x:c r="E244" s="25" t="str">
+      <x:c r="E245" s="25" t="str">
         <x:v>AX exposed ProjectPanel.ActionQueueRunButton.rough-cut-review, ProjectPanel.ActionQueueCopyButton.rough-cut-review, ProjectPanel.ActionQueueRunButton.marlin-default, and ProjectPanel.ActionQueueCopyButton.marlin-default. Clicking rough-cut-review changed the row to disabled Starting Codex session for Review..., then to Opening Codex approval gate for Review. ps showed a Codex app-server child under VideoOSStudio; git status listed only the intentional ProjectInspectorViews.swift edit, and projects/ax1-participant-voices-20260401/06_review still contained only human_notes.yaml.</x:v>
       </x:c>
-      <x:c r="F244" s="13" t="str">
+      <x:c r="F245" s="13" t="str">
         <x:v>Native approval-gate pass; write not approved</x:v>
       </x:c>
     </x:row>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rbf130fe827224b0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rcca903e2e0f74db5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="Rc1eae7c812364c86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R98c2160205934aa6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R7168049155284c25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rd27bccac037c4579"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Ree6c7d5faba041d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R7be31abd0ecf4c2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R93524ad7603c4dbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Rf9ccb2d63e5f41b2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,7 +433,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 22:09 JST</x:v>
+        <x:v>2026-06-23 22:28 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -473,7 +473,7 @@
         <x:v>Issues tracked</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="220" customHeight="1">
@@ -481,7 +481,7 @@
         <x:v>Final build</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Latest code build fixes resumable chunked Marlin progress when --skip-existing and --max-sources are combined: completed short no-chunk assets no longer consume the bounded run slot, so follow-up runs can advance to the next unevaluated source. Prior US-061 build work added bounded Marlin range chunking for long local sources: --chunk-seconds, --chunk-overlap-seconds, and --max-chunks are wired through runtime/pipeline/stages/marlin.ts, scripts/marlin-evaluate.ts, ProjectMarlinEvaluationRunPlan/Runner, and marlin-eval-plan/eval-next/eval-run. The same path keeps --caption-only, source-map-aware source selection, per-asset/per-chunk checkpoints, --max-sources, and --skip-existing. Prior native builds include ProjectMarlinRuntimeStatusReader isolated dependency probes, InspectorTab.Agent/Project/Clip/Media/QA buttons for US-065, ProjectPanel.ActionQueueStatus / ActionQueueCommand.&lt;id&gt; / ActionQueueRunButton.&lt;id&gt; / ActionQueueCopyButton.&lt;id&gt; for US-050, ProjectInitializer.ProjectIDField/CreateButton/CancelButton for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix.</x:v>
+        <x:v>Latest code adds a Marlin materialization-only path for projects with existing 03_analysis/marlin_events.json but zero Marlin segment peaks. scripts/marlin-materialize.ts reapplies artifact evidence without model/runtime access; ProjectMarlinMaterializationPlanner/Runner, videoos-studio-cli marlin-materialize, Studio readiness/action routing, and ProjectMarlinEvaluationQueue now surface that fast action before long Marlin eval runs. Prior US-061 build work added bounded Marlin range chunking for long local sources: --chunk-seconds, --chunk-overlap-seconds, --max-chunks, --caption-only, source-map-aware source selection, per-asset/per-chunk checkpoints, --max-sources, and --skip-existing through runtime/pipeline/stages/marlin.ts, scripts/marlin-evaluate.ts, ProjectMarlinEvaluationRunPlan/Runner, and marlin-eval-plan/eval-next/eval-run. Prior native builds include ProjectMarlinRuntimeStatusReader isolated dependency probes, InspectorTab.Agent/Project/Clip/Media/QA buttons for US-065, ProjectPanel.ActionQueueStatus / ActionQueueCommand.&lt;id&gt; / ActionQueueRunButton.&lt;id&gt; / ActionQueueCopyButton.&lt;id&gt; for US-050, ProjectInitializer.ProjectIDField/CreateButton/CancelButton for US-046, MediaPanel.BuildAudioStoryGraphButton / AudioStoryGraphCommandLine for US-062, MediaPanel.RenderFinalPackageButton / RenderFinalPackageCommandLine for US-063, and MediaPanel.ExportPremiereXMLButton / ExportEditorPacketButton / RevealEditorPacketButton / HandoffCommandLine for US-064, plus the prior MediaPanel Synthetic/Proxy/Smoke IDs, US-059 relink IDs, Settings.TransportPicker/Description, US-057 FootageSearch.* leaf AX identifiers, US-054 FeedbackStatus.UndoButton, US-053 Timeline/Feedback AX identifiers, US-052 ProjectPanel compile/review identifiers, US-051 native local Source Analysis default, US-047 Command Palette stale-search-field fix, US-045 preview renderer duration fix, and US-056 Candidate Swap AX/testability fix.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="220" customHeight="1">
@@ -489,7 +489,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-061 pass followed marlin-eval-next to rokutaro-graduation-20260319 and ran one bounded live caption-only source. swift build --target VideoOSStudioCLI passed, then VOS_MARLIN_PROXY_MAX_WIDTH=256 marlin-eval-run rokutaro-graduation-20260319 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=2 completed with indexRebuilt=true, searchDocuments=248, marlinEvents=1, and AST_73DD5497 / IMG_2911_still.mp4 materialized SEG_AST_73DD5497_0001 with marlin_temporal_semantics peak_analysis. Prior validation remains green: npx vitest run tests/marlin-analysis-stage.test.ts 15/0, npx tsc --noEmit --pretty false, and lively-alt-vol5 9-source representative chunks at coverage=1.00/canPreferMarlin=true. Repo-level canPreferMarlinAsDefault remains false pending broader cross-project coverage.</x:v>
+        <x:v>Latest US-061 pass verified no-model materialization: npx vitest run tests/marlin-analysis-stage.test.ts passed 17/0, npx tsc --noEmit --pretty false passed, swift test --filter 'ProjectMarlinEvaluationRunPlanTests|ProjectMarlinEvaluationQueueTests|ProjectStudioReadinessStatusTests' passed 19/0, swift build --target VideoOSStudioCLI passed, and swift build --target VideoOSStudio passed. Before the live operation, marlin-status ena-promo reported needs segment materialization with 301 events, 89 segments, and 0 Marlin peaks; marlin-eval-queue nextAction correctly returned marlin-materialize ena-promo. Running .build/arm64-apple-macosx/debug/videoos-studio-cli marlin-materialize ena-promo completed Changed=true, Marlin peaks before=0, after=89, indexRebuilt=true, searchDocuments=479, marlinEvents=301. Afterward ena-promo and hard-linked ena-promo-ai report candidate coverage 89/89, queue advances to marlin-eval-run togakushi-camp, and repo-level canPreferMarlinAsDefault remains false pending broader cross-project coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -497,7 +497,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest runtime/macOS CLI check is the US-061 next-project Marlin progress pass: VOS_MARLIN_PROXY_MAX_WIDTH=256 marlin-eval-run completed with indexRebuilt=true/searchDocuments=248 and added AST_73DD5497 / IMG_2911_still.mp4 to rokutaro-graduation-20260319. marlin-status now reports that project assets=1/events=1/segmentsWithMarlinPeak=1/coverage=0.08, while marlin-preference-status reports evaluatedProjects=10, coveredSegments=48, aggregateCoverage=0.13, and canPreferMarlinAsDefault=false. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live representative completions, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest runtime/macOS CLI check is the US-061 materialization pass: marlin-status ena-promo changed from needs segment materialization to candidate for preferred VLM with assets=89/events=301/segmentsWithMarlinPeak=89/coverage=1.00/canPreferMarlin=true; ena-promo-ai reports the same because its segments.json has the same inode. marlin-preference-status now reports candidateProjects=7, coveredSegments=226, aggregateCoverage=0.61, and canPreferMarlinAsDefault=false. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live representative completions, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -505,7 +505,7 @@
         <x:v>Latest US-061 follow-up</x:v>
       </x:c>
       <x:c r="B12" s="19" t="str">
-        <x:v>TL-244 advances the Marlin representative queue into rokutaro-graduation-20260319 via AST_73DD5497 / IMG_2911_still.mp4. Verification now shows rokutaro-graduation-20260319 assets=1/events=1/segmentsWithMarlinPeak=1/coverage=0.08/searchDocuments=248; repo-level canPreferMarlinAsDefault remains false pending broader cross-project coverage.</x:v>
+        <x:v>TL-245 fixes the Marlin materialization UX/logistics gap and applies it to ena-promo. Verification now shows ena-promo assets=89/events=301/segmentsWithMarlinPeak=89/coverage=1.00/searchDocuments=479; ena-promo-ai shares the same segments.json inode and also reports 89/89. Repo-level canPreferMarlinAsDefault remains false pending broader evaluated-project coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="220" customHeight="1">
@@ -529,7 +529,7 @@
         <x:v>Remaining caveat</x:v>
       </x:c>
       <x:c r="B15" s="13" t="str">
-        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility, Copy behavior, stable action-scoped AX identifiers, and rough-cut-review Start &amp; Run stopping at the Codex approval gate; approved workspace-write review execution and Final render Open remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-065 is promoted for native SQLite/RAG Search/Add, cited Agent prompt insertion, and InspectorTab.* Agent/Media switching without AX hangs. US-061 is promoted for runtime/model/mock/native AX, live non-mock representative chunks on lively-alt-vol5, source-map-aware chunk controls, resumable checkpointed evaluation, caption-only CLI support, and bounded range chunking across all 9 lively-alt-vol5 representative sources; repo-level Marlin-first preference promotion remains pending because aggregate project coverage is still below gate. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
+        <x:v>US-045 is promoted for native exact-preview playback and pixel evidence on both ena-promo-ai via preview-full.mp4 and AX-1 via preview-editor-1775121573933.mp4 with exact playback-contract stamps. US-046 is promoted for native New Project alert, NSOpenPanel source-folder selection, project shelf selection, Project creation status, source symlink, and project_state verification on a disposable project. US-047 Command Palette is promoted for top-bar open/close, Cmd-K open, filtered Return execution, and Esc dismiss. US-048 Agent panel is promoted for Check/Start/Stop lifecycle. US-049 is promoted for native read-only Status job execution; approved workspace-write jobs remain intentionally pending operator approval. US-050 is promoted for Project readiness/action queue visibility, Copy behavior, stable action-scoped AX identifiers, and rough-cut-review Start &amp; Run stopping at the Codex approval gate; approved workspace-write review execution and Final render Open remain intentionally pending. US-051 is promoted for native local Source Analysis on a disposable project, but full external STT/VLM/Appraiser analysis remains a deliberate CLI/operator path. US-052 is promoted for native rough-cut compile and review_patch compile on a disposable project. US-053 is promoted for native timeline marker/audio/waveform inspection plus right-click approve/reject/swap/search actions. US-054 is promoted for native disposable apply/undo and promote-button enablement, while live promotion of a real editorial decision remains an operator-approved action. US-055 is promoted for native selection/evidence inspection, Save/Clear persistence and cleanup, and live read-only Ask Codex proposal drafting without pressing Save. US-065 is promoted for native SQLite/RAG Search/Add, cited Agent prompt insertion, and InspectorTab.* Agent/Media switching without AX hangs. US-061 is promoted for runtime/model/mock/native AX, live non-mock representative chunks on lively-alt-vol5, source-map-aware chunk controls, resumable checkpointed evaluation, caption-only CLI support, and bounded range chunking across all 9 lively-alt-vol5 representative sources; repo-level Marlin-first preference promotion remains pending because some evaluated projects still lack Marlin-derived peak coverage. US-057 is promoted for native text search, preview, beat targeting, replacement staging, and Discard cleanup. US-059 is promoted for native Media Relink status/buttons, NSOpenPanel open/cancel, source-map-root relink, source_map/symlink verification, and cleanup on a disposable project. US-060 is promoted for native synthetic demo media build, proxy build, and Studio synthetic smoke execution with CLI/ffprobe verification and cleanup on disposable projects; acceptance smoke remains covered by CLI/test gates. US-062 is promoted for native MediaPanel Build Audio Story Graph button execution, command-line visibility, graph/index/library verification, and cleanup on a disposable project. US-063 is promoted for native MediaPanel Render Final Package button execution, supplied_final_path command visibility, render-status/QA/manifest/final-media verification, and cleanup on a disposable project. US-064 is promoted for native MediaPanel Export Premiere XML, Export Editor Packet, Reveal Packet, Finder selection, manifest/final-media/final-audio verification, and cleanup on disposable projects. US-066 is promoted for Settings window inspection, transport picker mutation, defaults persistence, and defaults cleanup. US-056 Candidate Swap and US-058 radar/issues/jump remain promoted with native AX/pixel/file evidence. Visual/manual gaps for other native stories are unchanged unless specifically promoted in their story rows and Test Log entries.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2145,22 +2145,22 @@
         <x:v>macOS Marlin evaluation and preference policy</x:v>
       </x:c>
       <x:c r="C62" s="24" t="str">
-        <x:v>As a native Studio operator, I can inspect Marlin runtime/model access/coverage/queue, run project Marlin evaluation, and apply Marlin preference when evidence gates pass.</x:v>
+        <x:v>As a native Studio operator, I can inspect Marlin runtime/model access/coverage/queue, run project Marlin evaluation, materialize existing Marlin artifacts, and apply Marlin preference when evidence gates pass.</x:v>
       </x:c>
       <x:c r="D62" s="24" t="str">
-        <x:v>MediaPanel renders MarlinEvaluationStatus, runtime/model access, representative buckets, queue items, run plan, evaluation button, and Apply Marlin Preference button. Evaluation can run only when sources exist and runtime/model checks pass; mock artifacts are workflow QA only and must not count as Marlin preference evidence. The Marlin status, queue, representative buckets, run/apply buttons, command line, artifact path, source-map-aware source selection, and resumable/caption-only chunk options now expose stable MediaPanel.Marlin*/CLI contracts for native automation.</x:v>
+        <x:v>MediaPanel renders MarlinEvaluationStatus, runtime/model access, representative buckets, queue items, run plan, evaluation/materialization actions, and Apply Marlin Preference button. Evaluation can run only when sources exist and runtime/model checks pass; materialization can apply existing marlin_events.json without model access; mock artifacts are workflow QA only and must not count as Marlin preference evidence. The Marlin status, queue, representative buckets, run/materialize/apply buttons, command line, artifact path, source-map-aware source selection, and resumable/caption-only chunk options now expose stable MediaPanel.Marlin*/CLI contracts for native automation.</x:v>
       </x:c>
       <x:c r="E62" s="24" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:48-160; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1296-1325,2326-2481; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRuntimeStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinModelAccessStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationQueue.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRepresentativePlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationRunPlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinPreferenceDecision.swift; runtime/pipeline/stages/marlin.ts; scripts/marlin-evaluate.ts</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:48-160; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1296-1325,2508-2650; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRuntimeStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinModelAccessStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationQueue.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRepresentativePlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationRunPlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinPreferenceDecision.swift; runtime/pipeline/stages/marlin.ts; scripts/marlin-evaluate.ts; scripts/marlin-materialize.ts</x:v>
       </x:c>
       <x:c r="F62" s="24" t="str">
-        <x:v>Run Marlin runtime/model/preference/queue/representative-plan/eval-plan/eval-run/status CLI checks, execute a tiny mock evaluation fixture, verify index refresh, verify Preference apply is blocked when gates fail, run Marlin focused Swift tests, confirm stable Marlin accessibility identifiers, run live non-mock representative-source chunks, verify source-map-aware chunk/checkpoint/caption-only behavior, and leave repo-level preference promotion blocked until aggregate evidence gates pass.</x:v>
+        <x:v>Run Marlin runtime/model/preference/queue/representative-plan/eval-plan/eval-run/materialize/status CLI checks, execute a tiny mock evaluation fixture, verify index refresh, verify Preference apply is blocked when gates fail, run Marlin focused Swift tests, confirm stable Marlin accessibility identifiers, run live non-mock representative-source chunks, verify source-map-aware chunk/checkpoint/caption-only behavior, materialize existing artifacts without model access, and leave repo-level preference promotion blocked until aggregate evidence gates pass.</x:v>
       </x:c>
       <x:c r="G62" s="24" t="str">
-        <x:v>Runtime/model/mock/native AX/live 9-source representative pass; repo preference gate pending</x:v>
+        <x:v>Runtime/model/mock/native AX/live 9-source/materialization pass; repo preference gate pending</x:v>
       </x:c>
       <x:c r="H62" s="11" t="str">
-        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. The runtime probe now imports dependency modules in isolated child processes, so the live marlin-runtime-status check no longer emits duplicate AVFoundation class warnings while still reporting every module ready. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path supports --request-timeout-ms / --timeout-ms, and a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4 completed with requestTimeoutMs=900000, wrote inference_mode=live Marlin events, updated segments with marlin_temporal_semantics, and rebuilt an index with 9 search documents. Current passes add per-asset checkpoint writes in runMarlinAnalysis plus --max-sources and --skip-existing through marlin-evaluate, ProjectMarlinEvaluationRunPlan/Runner, marlin-eval-plan, marlin-eval-next, and marlin-eval-run, then make loadMarlinAssetInputs source-map-aware so explicit linked filenames resolve to the correct asset_id when assets.json stores original camera filenames. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and a command carrying those options before source URLs. A /tmp mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. The latest code adds --caption-only plus bounded range chunk controls (--chunk-seconds, --chunk-overlap-seconds, --max-chunks) through the TS stage, marlin-evaluate, native CLI plan/run paths, and ProjectMarlinEvaluationRunPlan/Runner; tests verify find queries are not invoked when captionOnly is true and chunk event IDs carry chunk metadata. Verification passed: npx vitest run tests/marlin-normalize.test.ts tests/marlin-proxy.test.ts tests/marlin-analysis-stage.test.ts tests/marlin-incremental-merge.test.ts 29/0, npx tsc --noEmit --pretty false, node --check scripts/marlin-evaluate.ts, swift build --target VideoOSStudioCLI, swift test --filter ProjectMarlinEvaluationRunPlanTests 11/0, marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=1, and git diff --check. Live range-chunk caption-only runs with VOS_MARLIN_PROXY_MAX_WIDTH=256 completed for all 9 lively-alt-vol5 sources: existing full-source passes cover 08-jun-a-man-and-a.mp4 and 06-jun-two-people-are.mp4, while bounded chunk passes cover 02-jan-clip.mp4, 04-jan-clip.mp4, 03-jan-clip.mp4, 07-jun-clip.mp4, 05-jun-clip.mp4, 01-jan-clip.mp4, and 09-jun-clip.mp4. The final artifact has 9 items, 84 events, 8 find results, and chunked assets all carry chunkIndices [0] or [0,1]. index-rebuild reported 84 Marlin events, 8 Marlin find results, and 2425 search documents. marlin-status now reports assets=9/events=84/findResults=8/segmentsWithMarlinPeak=9/coverage=1.00/canPreferMarlin=true, while repo-level marlin-preference-status remains partially ready with lively-alt-vol5 at 9/9 peak segments, aggregateCoverage=0.15, and canPreferMarlinAsDefault=false. Repo-level preference promotion remains pending because other evaluated projects still lack enough Marlin-derived peak coverage.</x:v>
+        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. The runtime probe now imports dependency modules in isolated child processes, so the live marlin-runtime-status check no longer emits duplicate AVFoundation class warnings while still reporting every module ready. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path supports --request-timeout-ms / --timeout-ms, and a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4 completed with requestTimeoutMs=900000, wrote inference_mode=live Marlin events, updated segments with marlin_temporal_semantics, and rebuilt an index with 9 search documents. Current passes add per-asset checkpoint writes in runMarlinAnalysis plus --max-sources and --skip-existing through marlin-evaluate, ProjectMarlinEvaluationRunPlan/Runner, marlin-eval-plan, marlin-eval-next, and marlin-eval-run, then make loadMarlinAssetInputs source-map-aware so explicit linked filenames resolve to the correct asset_id when assets.json stores original camera filenames. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and a command carrying those options before source URLs. A /tmp mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. The latest code adds --caption-only plus bounded range chunk controls (--chunk-seconds, --chunk-overlap-seconds, --max-chunks) through the TS stage, marlin-evaluate, native CLI plan/run paths, and ProjectMarlinEvaluationRunPlan/Runner; tests verify find queries are not invoked when captionOnly is true and chunk event IDs carry chunk metadata. The current materialization pass adds scripts/marlin-materialize.ts plus native CLI/Core/UI readiness routing so queue/readiness buttons run a no-model artifact materialization command when marlin_events.json exists but segments have no Marlin peaks. Verification passed: npx vitest run tests/marlin-analysis-stage.test.ts 17/0, npx tsc --noEmit --pretty false, swift build --target VideoOSStudioCLI, and swift test --filter 'ProjectMarlinEvaluationRunPlanTests|ProjectMarlinEvaluationQueueTests|ProjectStudioReadinessStatusTests' 19/0. Live materialization ran .build/arm64-apple-macosx/debug/videoos-studio-cli marlin-materialize ena-promo; it changed Marlin peaks from 0 to 89, rebuilt project_index.sqlite with searchDocuments=479/marlinEvents=301, and made ena-promo a candidate with coverage=1.00/canPreferMarlin=true. ena-promo-ai shares the same segments.json inode and now reports the same 89/89 candidate coverage. Repo-level marlin-preference-status improved to candidateProjects=7, coveredSegments=226, aggregateCoverage=0.61, but canPreferMarlinAsDefault remains false because other evaluated projects still need broader coverage or materialization.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="48" customHeight="1">
@@ -4460,31 +4460,60 @@
       </x:c>
     </x:row>
     <x:row r="75" ht="48" customHeight="1">
-      <x:c r="A75" s="12" t="str">
+      <x:c r="A75" s="10" t="str">
         <x:v>ISS-073</x:v>
       </x:c>
-      <x:c r="B75" s="25" t="str">
+      <x:c r="B75" s="24" t="str">
         <x:v>US-061</x:v>
       </x:c>
-      <x:c r="C75" s="25" t="str">
+      <x:c r="C75" s="24" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="D75" s="25" t="str">
+      <x:c r="D75" s="24" t="str">
         <x:v>Marlin resumability/logistics</x:v>
       </x:c>
-      <x:c r="E75" s="25" t="str">
+      <x:c r="E75" s="24" t="str">
         <x:v>Resumable chunked Marlin runs could repeatedly select a completed short source instead of advancing to the next unevaluated asset.</x:v>
       </x:c>
-      <x:c r="F75" s="25" t="str">
+      <x:c r="F75" s="24" t="str">
         <x:v>When chunking was enabled, selectMarlinAssetInputsForRun intentionally deferred skipExisting because resume state is per chunk. For short assets that do not produce chunks, --skip-existing --max-sources=1 still capped the run before runMarlinAnalysis could discover that the selected asset was already complete, so togakushi-camp kept presenting the completed T084 source instead of advancing to T001.</x:v>
       </x:c>
-      <x:c r="G75" s="25" t="str">
+      <x:c r="G75" s="24" t="str">
         <x:v>When chunking and skipExisting are both enabled, defer maxSources until an unfinished asset is actually evaluated; for short no-chunk assets, return null if an existing item already covers the asset.</x:v>
       </x:c>
-      <x:c r="H75" s="25" t="str">
+      <x:c r="H75" s="24" t="str">
         <x:v>marlin-analysis-stage now covers skip-existing with chunking across completed short assets. VOS_MARLIN_PROXY_MAX_WIDTH=256 marlin-eval-run togakushi-camp --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=2 advanced from AST_00725A11 / T084 to AST_038AB86F / T001, rebuilt the index, and raised togakushi-camp to assets=2/events=4/segmentsWithMarlinPeak=2/coverage=0.03/searchDocuments=286.</x:v>
       </x:c>
-      <x:c r="I75" s="13" t="str">
+      <x:c r="I75" s="11" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="48" customHeight="1">
+      <x:c r="A76" s="12" t="str">
+        <x:v>ISS-074</x:v>
+      </x:c>
+      <x:c r="B76" s="25" t="str">
+        <x:v>US-061</x:v>
+      </x:c>
+      <x:c r="C76" s="25" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="D76" s="25" t="str">
+        <x:v>Marlin materialization UX/logistics</x:v>
+      </x:c>
+      <x:c r="E76" s="25" t="str">
+        <x:v>Projects with existing live marlin_events.json but zero segment peaks were still routed to long Marlin evaluation commands instead of a fast materialization-only action.</x:v>
+      </x:c>
+      <x:c r="F76" s="25" t="str">
+        <x:v>ProjectMarlinEvaluationQueue and ProjectStudioReadinessStatus could detect needs segment materialization, but the recommended command/default action still pointed at marlin-eval-run or marlin-eval-next. There was no dedicated CLI/UI runner that reapplied existing artifact evidence without model/runtime access.</x:v>
+      </x:c>
+      <x:c r="G76" s="25" t="str">
+        <x:v>Add scripts/marlin-materialize.ts plus ProjectMarlinMaterializationPlanner/Runner, route CLI/studio-action/readiness/queue to marlin-materialize for needs segment materialization, and keep marlin-eval-next scoped to unevaluated runnable projects.</x:v>
+      </x:c>
+      <x:c r="H76" s="25" t="str">
+        <x:v>npx vitest run tests/marlin-analysis-stage.test.ts passed 17/0; Swift Marlin plan/queue/readiness tests passed 19/0; swift build --target VideoOSStudioCLI, swift build --target VideoOSStudio, and npx tsc --noEmit passed. marlin-materialize ena-promo changed Marlin peaks 0-&gt;89, rebuilt 479 search documents, and moved ena-promo/ena-promo-ai to candidate coverage 89/89.</x:v>
+      </x:c>
+      <x:c r="I76" s="13" t="str">
         <x:v>Fixed</x:v>
       </x:c>
     </x:row>
@@ -8867,79 +8896,79 @@
     </x:row>
     <x:row r="219" ht="48" customHeight="1">
       <x:c r="A219" s="10" t="str">
-        <x:v>TL-205</x:v>
+        <x:v>TL-245</x:v>
       </x:c>
       <x:c r="B219" s="24" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C219" s="24" t="str">
-        <x:v>Native preview duration fallback</x:v>
+        <x:v>Marlin materialization-only command and ena-promo application</x:v>
       </x:c>
       <x:c r="D219" s="24" t="str">
-        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
+        <x:v>Add and verify a no-model marlin-materialize path for existing artifacts; run it on ena-promo; inspect queue/status/preference outputs.</x:v>
       </x:c>
       <x:c r="E219" s="24" t="str">
-        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
+        <x:v>Added scripts/marlin-materialize.ts, ProjectMarlinMaterializationPlanner/Runner, CLI marlin-materialize, Studio readiness/action routing, and queue priority updates. npx vitest run tests/marlin-analysis-stage.test.ts passed 17/0; npx tsc --noEmit --pretty false passed; swift test --filter 'ProjectMarlinEvaluationRunPlanTests|ProjectMarlinEvaluationQueueTests|ProjectStudioReadinessStatusTests' passed 19/0; swift build --target VideoOSStudioCLI and swift build --target VideoOSStudio passed. Before materialization, ena-promo reported needs segment materialization with 301 events, 89 segments, and 0 Marlin peaks. marlin-materialize ena-promo completed Changed=true, Marlin peaks before=0, after=89, indexRebuilt=true, searchDocuments=479, marlinEvents=301. Afterward, ena-promo and hard-linked ena-promo-ai both report candidate for preferred VLM with coverage=1.00; queue nextAction advanced to marlin-eval-run togakushi-camp; repo preference status is still partially ready with candidateProjects=7, coveredSegments=226, aggregateCoverage=0.61, canPreferMarlinAsDefault=false.</x:v>
       </x:c>
       <x:c r="F219" s="11" t="str">
-        <x:v>Native pixel/runtime pass</x:v>
+        <x:v>Materialization UX fixed; repo preference gate pending</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="48" customHeight="1">
       <x:c r="A220" s="10" t="str">
-        <x:v>TL-206</x:v>
+        <x:v>TL-205</x:v>
       </x:c>
       <x:c r="B220" s="24" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C220" s="24" t="str">
-        <x:v>Native Clip Inspector save and clear</x:v>
+        <x:v>Native preview duration fallback</x:v>
       </x:c>
       <x:c r="D220" s="24" t="str">
-        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
+        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
       </x:c>
       <x:c r="E220" s="24" t="str">
-        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
+        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F220" s="11" t="str">
-        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
+        <x:v>Native pixel/runtime pass</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="48" customHeight="1">
       <x:c r="A221" s="10" t="str">
-        <x:v>TL-207</x:v>
+        <x:v>TL-206</x:v>
       </x:c>
       <x:c r="B221" s="24" t="str">
-        <x:v>US-058</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C221" s="24" t="str">
-        <x:v>Native QA Dashboard issue jump</x:v>
+        <x:v>Native Clip Inspector save and clear</x:v>
       </x:c>
       <x:c r="D221" s="24" t="str">
-        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
+        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
       </x:c>
       <x:c r="E221" s="24" t="str">
-        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
+        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
       </x:c>
       <x:c r="F221" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="48" customHeight="1">
       <x:c r="A222" s="10" t="str">
-        <x:v>TL-208</x:v>
+        <x:v>TL-207</x:v>
       </x:c>
       <x:c r="B222" s="24" t="str">
-        <x:v>US-056</x:v>
+        <x:v>US-058</x:v>
       </x:c>
       <x:c r="C222" s="24" t="str">
-        <x:v>Native Candidate Swap sheet and staging</x:v>
+        <x:v>Native QA Dashboard issue jump</x:v>
       </x:c>
       <x:c r="D222" s="24" t="str">
-        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
+        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
       </x:c>
       <x:c r="E222" s="24" t="str">
-        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
+        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
       </x:c>
       <x:c r="F222" s="11" t="str">
         <x:v>Native AX/pixel pass</x:v>
@@ -8947,339 +8976,339 @@
     </x:row>
     <x:row r="223" ht="48" customHeight="1">
       <x:c r="A223" s="10" t="str">
-        <x:v>TL-209</x:v>
+        <x:v>TL-208</x:v>
       </x:c>
       <x:c r="B223" s="24" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-056</x:v>
       </x:c>
       <x:c r="C223" s="24" t="str">
-        <x:v>Native exact preview regeneration</x:v>
+        <x:v>Native Candidate Swap sheet and staging</x:v>
       </x:c>
       <x:c r="D223" s="24" t="str">
-        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
+        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
       </x:c>
       <x:c r="E223" s="24" t="str">
-        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
       </x:c>
       <x:c r="F223" s="11" t="str">
-        <x:v>Native exact preview pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="48" customHeight="1">
       <x:c r="A224" s="10" t="str">
-        <x:v>TL-210</x:v>
+        <x:v>TL-209</x:v>
       </x:c>
       <x:c r="B224" s="24" t="str">
-        <x:v>US-047</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C224" s="24" t="str">
-        <x:v>Native Command Palette top-bar open/close</x:v>
+        <x:v>Native exact preview regeneration</x:v>
       </x:c>
       <x:c r="D224" s="24" t="str">
-        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
+        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
       </x:c>
       <x:c r="E224" s="24" t="str">
-        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
+        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F224" s="11" t="str">
-        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
+        <x:v>Native exact preview pass</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="48" customHeight="1">
       <x:c r="A225" s="10" t="str">
-        <x:v>TL-211</x:v>
+        <x:v>TL-210</x:v>
       </x:c>
       <x:c r="B225" s="24" t="str">
         <x:v>US-047</x:v>
       </x:c>
       <x:c r="C225" s="24" t="str">
-        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
+        <x:v>Native Command Palette top-bar open/close</x:v>
       </x:c>
       <x:c r="D225" s="24" t="str">
-        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
+        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
       </x:c>
       <x:c r="E225" s="24" t="str">
-        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
+        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
       </x:c>
       <x:c r="F225" s="11" t="str">
-        <x:v>Native keyboard/AX pass</x:v>
+        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="48" customHeight="1">
       <x:c r="A226" s="10" t="str">
-        <x:v>TL-212</x:v>
+        <x:v>TL-211</x:v>
       </x:c>
       <x:c r="B226" s="24" t="str">
-        <x:v>US-048</x:v>
+        <x:v>US-047</x:v>
       </x:c>
       <x:c r="C226" s="24" t="str">
-        <x:v>Native Agent panel session lifecycle</x:v>
+        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
       </x:c>
       <x:c r="D226" s="24" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
+        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
       </x:c>
       <x:c r="E226" s="24" t="str">
-        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
+        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
       </x:c>
       <x:c r="F226" s="11" t="str">
-        <x:v>Native AX/computer-use pass</x:v>
+        <x:v>Native keyboard/AX pass</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="48" customHeight="1">
       <x:c r="A227" s="10" t="str">
-        <x:v>TL-213</x:v>
+        <x:v>TL-212</x:v>
       </x:c>
       <x:c r="B227" s="24" t="str">
-        <x:v>US-049</x:v>
+        <x:v>US-048</x:v>
       </x:c>
       <x:c r="C227" s="24" t="str">
-        <x:v>Native Status agent job read-only turn</x:v>
+        <x:v>Native Agent panel session lifecycle</x:v>
       </x:c>
       <x:c r="D227" s="24" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
       </x:c>
       <x:c r="E227" s="24" t="str">
-        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
+        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F227" s="11" t="str">
-        <x:v>Native read-only job pass; approved write pending</x:v>
+        <x:v>Native AX/computer-use pass</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="48" customHeight="1">
       <x:c r="A228" s="10" t="str">
-        <x:v>TL-214</x:v>
+        <x:v>TL-213</x:v>
       </x:c>
       <x:c r="B228" s="24" t="str">
-        <x:v>US-050</x:v>
+        <x:v>US-049</x:v>
       </x:c>
       <x:c r="C228" s="24" t="str">
-        <x:v>Native Project readiness/action queue Copy pass</x:v>
+        <x:v>Native Status agent job read-only turn</x:v>
       </x:c>
       <x:c r="D228" s="24" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
       </x:c>
       <x:c r="E228" s="24" t="str">
-        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
+        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F228" s="11" t="str">
-        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
+        <x:v>Native read-only job pass; approved write pending</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="48" customHeight="1">
       <x:c r="A229" s="10" t="str">
-        <x:v>TL-215</x:v>
+        <x:v>TL-214</x:v>
       </x:c>
       <x:c r="B229" s="24" t="str">
-        <x:v>US-051</x:v>
+        <x:v>US-050</x:v>
       </x:c>
       <x:c r="C229" s="24" t="str">
-        <x:v>Native local Source Analysis button</x:v>
+        <x:v>Native Project readiness/action queue Copy pass</x:v>
       </x:c>
       <x:c r="D229" s="24" t="str">
-        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
       </x:c>
       <x:c r="E229" s="24" t="str">
-        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
+        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
       </x:c>
       <x:c r="F229" s="11" t="str">
-        <x:v>Native local analysis pass</x:v>
+        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="48" customHeight="1">
       <x:c r="A230" s="10" t="str">
-        <x:v>TL-216</x:v>
+        <x:v>TL-215</x:v>
       </x:c>
       <x:c r="B230" s="24" t="str">
-        <x:v>US-052</x:v>
+        <x:v>US-051</x:v>
       </x:c>
       <x:c r="C230" s="24" t="str">
-        <x:v>Native Rough Cut and Review Patch buttons</x:v>
+        <x:v>Native local Source Analysis button</x:v>
       </x:c>
       <x:c r="D230" s="24" t="str">
-        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
+        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E230" s="24" t="str">
-        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
       </x:c>
       <x:c r="F230" s="11" t="str">
-        <x:v>Native compile/review patch pass</x:v>
+        <x:v>Native local analysis pass</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="48" customHeight="1">
       <x:c r="A231" s="10" t="str">
-        <x:v>TL-217</x:v>
+        <x:v>TL-216</x:v>
       </x:c>
       <x:c r="B231" s="24" t="str">
-        <x:v>US-053</x:v>
+        <x:v>US-052</x:v>
       </x:c>
       <x:c r="C231" s="24" t="str">
-        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
+        <x:v>Native Rough Cut and Review Patch buttons</x:v>
       </x:c>
       <x:c r="D231" s="24" t="str">
-        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
+        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E231" s="24" t="str">
-        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
+        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F231" s="11" t="str">
-        <x:v>Native timeline/context menu pass</x:v>
+        <x:v>Native compile/review patch pass</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="48" customHeight="1">
       <x:c r="A232" s="10" t="str">
-        <x:v>TL-218</x:v>
+        <x:v>TL-217</x:v>
       </x:c>
       <x:c r="B232" s="24" t="str">
-        <x:v>US-054</x:v>
+        <x:v>US-053</x:v>
       </x:c>
       <x:c r="C232" s="24" t="str">
-        <x:v>Native Studio feedback Apply and Undo</x:v>
+        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
       </x:c>
       <x:c r="D232" s="24" t="str">
-        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
+        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
       </x:c>
       <x:c r="E232" s="24" t="str">
-        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
       </x:c>
       <x:c r="F232" s="11" t="str">
-        <x:v>Native apply/undo pass</x:v>
+        <x:v>Native timeline/context menu pass</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="48" customHeight="1">
       <x:c r="A233" s="10" t="str">
-        <x:v>TL-219</x:v>
+        <x:v>TL-218</x:v>
       </x:c>
       <x:c r="B233" s="24" t="str">
-        <x:v>US-057</x:v>
+        <x:v>US-054</x:v>
       </x:c>
       <x:c r="C233" s="24" t="str">
-        <x:v>Native Footage Search sheet and replacement staging</x:v>
+        <x:v>Native Studio feedback Apply and Undo</x:v>
       </x:c>
       <x:c r="D233" s="24" t="str">
-        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
+        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E233" s="24" t="str">
-        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
+        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F233" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native apply/undo pass</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="48" customHeight="1">
       <x:c r="A234" s="10" t="str">
-        <x:v>TL-220</x:v>
+        <x:v>TL-219</x:v>
       </x:c>
       <x:c r="B234" s="24" t="str">
-        <x:v>US-066</x:v>
+        <x:v>US-057</x:v>
       </x:c>
       <x:c r="C234" s="24" t="str">
-        <x:v>Native Settings transport picker mutation</x:v>
+        <x:v>Native Footage Search sheet and replacement staging</x:v>
       </x:c>
       <x:c r="D234" s="24" t="str">
-        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
+        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
       </x:c>
       <x:c r="E234" s="24" t="str">
-        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
       </x:c>
       <x:c r="F234" s="11" t="str">
-        <x:v>Native Settings picker mutation pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="48" customHeight="1">
       <x:c r="A235" s="10" t="str">
-        <x:v>TL-221</x:v>
+        <x:v>TL-220</x:v>
       </x:c>
       <x:c r="B235" s="24" t="str">
-        <x:v>US-059</x:v>
+        <x:v>US-066</x:v>
       </x:c>
       <x:c r="C235" s="24" t="str">
-        <x:v>Native Media Relink buttons and source-map relink</x:v>
+        <x:v>Native Settings transport picker mutation</x:v>
       </x:c>
       <x:c r="D235" s="24" t="str">
-        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
+        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
       </x:c>
       <x:c r="E235" s="24" t="str">
-        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
+        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F235" s="11" t="str">
-        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
+        <x:v>Native Settings picker mutation pass</x:v>
       </x:c>
     </x:row>
     <x:row r="236" ht="48" customHeight="1">
       <x:c r="A236" s="10" t="str">
-        <x:v>TL-222</x:v>
+        <x:v>TL-221</x:v>
       </x:c>
       <x:c r="B236" s="24" t="str">
-        <x:v>US-060</x:v>
+        <x:v>US-059</x:v>
       </x:c>
       <x:c r="C236" s="24" t="str">
-        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
+        <x:v>Native Media Relink buttons and source-map relink</x:v>
       </x:c>
       <x:c r="D236" s="24" t="str">
-        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
+        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
       </x:c>
       <x:c r="E236" s="24" t="str">
-        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
+        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
       </x:c>
       <x:c r="F236" s="11" t="str">
-        <x:v>Native synthetic/proxy/smoke button pass</x:v>
+        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
       </x:c>
     </x:row>
     <x:row r="237" ht="48" customHeight="1">
       <x:c r="A237" s="10" t="str">
-        <x:v>TL-223</x:v>
+        <x:v>TL-222</x:v>
       </x:c>
       <x:c r="B237" s="24" t="str">
-        <x:v>US-046</x:v>
+        <x:v>US-060</x:v>
       </x:c>
       <x:c r="C237" s="24" t="str">
-        <x:v>Native New Project from Source</x:v>
+        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
       </x:c>
       <x:c r="D237" s="24" t="str">
-        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
+        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
       </x:c>
       <x:c r="E237" s="24" t="str">
-        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
+        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
       </x:c>
       <x:c r="F237" s="11" t="str">
-        <x:v>Native project creation/NSOpenPanel pass</x:v>
+        <x:v>Native synthetic/proxy/smoke button pass</x:v>
       </x:c>
     </x:row>
     <x:row r="238" ht="48" customHeight="1">
       <x:c r="A238" s="10" t="str">
-        <x:v>TL-224</x:v>
+        <x:v>TL-223</x:v>
       </x:c>
       <x:c r="B238" s="24" t="str">
-        <x:v>US-062</x:v>
+        <x:v>US-046</x:v>
       </x:c>
       <x:c r="C238" s="24" t="str">
-        <x:v>Native MediaPanel Audio Story Graph button</x:v>
+        <x:v>Native New Project from Source</x:v>
       </x:c>
       <x:c r="D238" s="24" t="str">
-        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
+        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
       </x:c>
       <x:c r="E238" s="24" t="str">
-        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
       </x:c>
       <x:c r="F238" s="11" t="str">
-        <x:v>Native AX/UI/CLI pass</x:v>
+        <x:v>Native project creation/NSOpenPanel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="239" ht="48" customHeight="1">
       <x:c r="A239" s="10" t="str">
-        <x:v>TL-225</x:v>
+        <x:v>TL-224</x:v>
       </x:c>
       <x:c r="B239" s="24" t="str">
-        <x:v>US-063</x:v>
+        <x:v>US-062</x:v>
       </x:c>
       <x:c r="C239" s="24" t="str">
-        <x:v>Native Render Final Package button</x:v>
+        <x:v>Native MediaPanel Audio Story Graph button</x:v>
       </x:c>
       <x:c r="D239" s="24" t="str">
-        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
+        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E239" s="24" t="str">
-        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F239" s="11" t="str">
         <x:v>Native AX/UI/CLI pass</x:v>
@@ -9287,121 +9316,141 @@
     </x:row>
     <x:row r="240" ht="48" customHeight="1">
       <x:c r="A240" s="10" t="str">
-        <x:v>TL-226</x:v>
+        <x:v>TL-225</x:v>
       </x:c>
       <x:c r="B240" s="24" t="str">
-        <x:v>US-064</x:v>
+        <x:v>US-063</x:v>
       </x:c>
       <x:c r="C240" s="24" t="str">
-        <x:v>Native Editor Handoff export and Finder reveal</x:v>
+        <x:v>Native Render Final Package button</x:v>
       </x:c>
       <x:c r="D240" s="24" t="str">
-        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
+        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
       </x:c>
       <x:c r="E240" s="24" t="str">
-        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
+        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F240" s="11" t="str">
-        <x:v>Native AX/UI/Finder/CLI pass</x:v>
+        <x:v>Native AX/UI/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="48" customHeight="1">
       <x:c r="A241" s="10" t="str">
-        <x:v>TL-227</x:v>
+        <x:v>TL-226</x:v>
       </x:c>
       <x:c r="B241" s="24" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-064</x:v>
       </x:c>
       <x:c r="C241" s="24" t="str">
-        <x:v>Native Ask Codex editor-note proposal</x:v>
+        <x:v>Native Editor Handoff export and Finder reveal</x:v>
       </x:c>
       <x:c r="D241" s="24" t="str">
-        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
+        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E241" s="24" t="str">
-        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
+        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
       </x:c>
       <x:c r="F241" s="11" t="str">
-        <x:v>Native read-only Codex proposal pass</x:v>
+        <x:v>Native AX/UI/Finder/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="242" ht="48" customHeight="1">
       <x:c r="A242" s="10" t="str">
-        <x:v>TL-228</x:v>
+        <x:v>TL-227</x:v>
       </x:c>
       <x:c r="B242" s="24" t="str">
-        <x:v>US-061</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C242" s="24" t="str">
-        <x:v>Live Marlin single-source completion</x:v>
+        <x:v>Native Ask Codex editor-note proposal</x:v>
       </x:c>
       <x:c r="D242" s="24" t="str">
-        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
+        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
       </x:c>
       <x:c r="E242" s="24" t="str">
-        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
+        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
       </x:c>
       <x:c r="F242" s="11" t="str">
-        <x:v>Live single-source pass; full representative batch pending</x:v>
+        <x:v>Native read-only Codex proposal pass</x:v>
       </x:c>
     </x:row>
     <x:row r="243" ht="48" customHeight="1">
       <x:c r="A243" s="10" t="str">
-        <x:v>TL-229</x:v>
+        <x:v>TL-228</x:v>
       </x:c>
       <x:c r="B243" s="24" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C243" s="24" t="str">
-        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+        <x:v>Live Marlin single-source completion</x:v>
       </x:c>
       <x:c r="D243" s="24" t="str">
-        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
       </x:c>
       <x:c r="E243" s="24" t="str">
-        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
       </x:c>
       <x:c r="F243" s="11" t="str">
-        <x:v>Native fresh-launch pixel pass</x:v>
+        <x:v>Live single-source pass; full representative batch pending</x:v>
       </x:c>
     </x:row>
     <x:row r="244" ht="48" customHeight="1">
       <x:c r="A244" s="10" t="str">
-        <x:v>TL-230</x:v>
+        <x:v>TL-229</x:v>
       </x:c>
       <x:c r="B244" s="24" t="str">
         <x:v>US-045</x:v>
       </x:c>
       <x:c r="C244" s="24" t="str">
+        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+      </x:c>
+      <x:c r="D244" s="24" t="str">
+        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+      </x:c>
+      <x:c r="E244" s="24" t="str">
+        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+      </x:c>
+      <x:c r="F244" s="11" t="str">
+        <x:v>Native fresh-launch pixel pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" ht="48" customHeight="1">
+      <x:c r="A245" s="10" t="str">
+        <x:v>TL-230</x:v>
+      </x:c>
+      <x:c r="B245" s="24" t="str">
+        <x:v>US-045</x:v>
+      </x:c>
+      <x:c r="C245" s="24" t="str">
         <x:v>AX-1 exact preview promotion and pixel pass</x:v>
       </x:c>
-      <x:c r="D244" s="24" t="str">
+      <x:c r="D245" s="24" t="str">
         <x:v>Run videoos-studio-cli compile-run on projects/ax1-participant-voices-20260401, confirm playback-contract-status, select ProjectShelf.ax1-participant-voices-20260401 in VideoOSStudio, capture /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and run Retina-coordinate pixel statistics on the Viewer region.</x:v>
       </x:c>
-      <x:c r="E244" s="24" t="str">
+      <x:c r="E245" s="24" t="str">
         <x:v>Before compile, playback-contract-status returned legacy_manifest and approvalGrade=false. compile-run completed with exitCode=0, timeline compiled, indexDocuments=492, and git status stayed clean. After compile, playback-contract-status returned state=exact, approvalGrade=true, timelineHash=171378fe2bfe3a7c, and manifestBaseTimelineHash=171378fe2bfe3a7c. Native Viewer showed Exact preview / preview-editor-1775121573933.mp4 and Timeline preview D4887.MP4 with a visible interview frame. Screenshot was 3.5M; viewer_person_actual mean_rgb=(144.62,141.42,149.8) and near_black_pct=0.0004, while left pillarbox near_black_pct=1.0000 as expected.</x:v>
       </x:c>
-      <x:c r="F244" s="11" t="str">
+      <x:c r="F245" s="11" t="str">
         <x:v>Native AX-1 exact/pixel pass</x:v>
       </x:c>
     </x:row>
-    <x:row r="245" ht="48" customHeight="1">
-      <x:c r="A245" s="12" t="str">
+    <x:row r="246" ht="48" customHeight="1">
+      <x:c r="A246" s="12" t="str">
         <x:v>TL-231</x:v>
       </x:c>
-      <x:c r="B245" s="25" t="str">
+      <x:c r="B246" s="25" t="str">
         <x:v>US-050</x:v>
       </x:c>
-      <x:c r="C245" s="25" t="str">
+      <x:c r="C246" s="25" t="str">
         <x:v>Native Action Queue approval gate</x:v>
       </x:c>
-      <x:c r="D245" s="25" t="str">
+      <x:c r="D246" s="25" t="str">
         <x:v>Add ProjectPanel.ActionQueue* identifiers, relaunch VideoOSStudio, select AX-1 Project tab, inspect the Action Queue AX tree, click ProjectPanel.ActionQueueRunButton.rough-cut-review, and stop at the Codex approval gate without approving writes.</x:v>
       </x:c>
-      <x:c r="E245" s="25" t="str">
+      <x:c r="E246" s="25" t="str">
         <x:v>AX exposed ProjectPanel.ActionQueueRunButton.rough-cut-review, ProjectPanel.ActionQueueCopyButton.rough-cut-review, ProjectPanel.ActionQueueRunButton.marlin-default, and ProjectPanel.ActionQueueCopyButton.marlin-default. Clicking rough-cut-review changed the row to disabled Starting Codex session for Review..., then to Opening Codex approval gate for Review. ps showed a Codex app-server child under VideoOSStudio; git status listed only the intentional ProjectInspectorViews.swift edit, and projects/ax1-participant-voices-20260401/06_review still contained only human_notes.yaml.</x:v>
       </x:c>
-      <x:c r="F245" s="13" t="str">
+      <x:c r="F246" s="13" t="str">
         <x:v>Native approval-gate pass; write not approved</x:v>
       </x:c>
     </x:row>
@@ -9908,10 +9957,10 @@
         <x:v>macOS Marlin and audio graph</x:v>
       </x:c>
       <x:c r="B45" s="24" t="str">
-        <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:21-160; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1296-1325,2326-2604; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRuntimeStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinModelAccessStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationQueue.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRepresentativePlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationRunPlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinPreferenceDecision.swift; runtime/pipeline/stages/marlin.ts; runtime/media/source-map.ts; scripts/marlin-evaluate.ts; apps/macos-studio/Sources/VideoOSStudioCore/ProjectAudioStoryGraphRunPlan.swift; scripts/build-audio-story-graph.ts; runtime/artifacts/audio-story-project-builder.ts; runtime/artifacts/p2-audio-story-graph.ts; apps/macos-studio/Sources/VideoOSStudioCore/ProjectSQLiteIndex.swift:400-452</x:v>
+        <x:v>apps/macos-studio/Sources/VideoOSStudio/MediaPanelViews.swift:21-160; apps/macos-studio/Sources/VideoOSStudio/StudioViewModel.swift:1296-1325,2508-2650; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRuntimeStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinModelAccessStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationStatus.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationQueue.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinRepresentativePlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinEvaluationRunPlan.swift; apps/macos-studio/Sources/VideoOSStudioCore/ProjectMarlinPreferenceDecision.swift; runtime/pipeline/stages/marlin.ts; runtime/media/source-map.ts; scripts/marlin-evaluate.ts; scripts/marlin-materialize.ts; apps/macos-studio/Sources/VideoOSStudioCore/ProjectAudioStoryGraphRunPlan.swift; scripts/build-audio-story-graph.ts; runtime/artifacts/audio-story-project-builder.ts; runtime/artifacts/p2-audio-story-graph.ts; apps/macos-studio/Sources/VideoOSStudioCore/ProjectSQLiteIndex.swift:400-452</x:v>
       </x:c>
       <x:c r="C45" s="11" t="str">
-        <x:v>Marlin runtime dependency checks, Hugging Face gated-model access checks, project evaluation status, representative queue/buckets, source-map-aware asset/source resolution, run-plan source selection, mock/live evaluation runner with SQLite index refresh, resumable per-asset checkpointing, --max-sources/--skip-existing chunk controls, preference gate/apply guard, stable Marlin MediaPanel accessibility identifiers, and audio story graph command readiness/runtime execution. Audio story graph builds transcript utterance, audio event, and BGM music_section nodes, writes 03_analysis/audio_story_graph.json, and indexes audio_story_node search documents after success.</x:v>
+        <x:v>Marlin runtime dependency checks, Hugging Face gated-model access checks, project evaluation status, representative queue/buckets, source-map-aware asset/source resolution, run-plan source selection, no-model materialization for existing marlin_events.json, mock/live evaluation runner with SQLite index refresh, resumable per-asset checkpointing, --max-sources/--skip-existing chunk controls, preference gate/apply guard, stable Marlin MediaPanel accessibility identifiers, and audio story graph command readiness/runtime execution. Audio story graph builds transcript utterance, audio event, and BGM music_section nodes, writes 03_analysis/audio_story_graph.json, and indexes audio_story_node search documents after success.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="48" customHeight="1">

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rd27bccac037c4579"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Ree6c7d5faba041d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R7be31abd0ecf4c2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R93524ad7603c4dbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="Rf9ccb2d63e5f41b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Re6883ef438de49f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R4e32a42cf11f48b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R57cd63a4f3ef4457"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R3db72df175f94ae9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R856afb5e21ff4a00"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,7 +433,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 22:28 JST</x:v>
+        <x:v>2026-06-23 22:41 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -489,7 +489,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-061 pass verified no-model materialization: npx vitest run tests/marlin-analysis-stage.test.ts passed 17/0, npx tsc --noEmit --pretty false passed, swift test --filter 'ProjectMarlinEvaluationRunPlanTests|ProjectMarlinEvaluationQueueTests|ProjectStudioReadinessStatusTests' passed 19/0, swift build --target VideoOSStudioCLI passed, and swift build --target VideoOSStudio passed. Before the live operation, marlin-status ena-promo reported needs segment materialization with 301 events, 89 segments, and 0 Marlin peaks; marlin-eval-queue nextAction correctly returned marlin-materialize ena-promo. Running .build/arm64-apple-macosx/debug/videoos-studio-cli marlin-materialize ena-promo completed Changed=true, Marlin peaks before=0, after=89, indexRebuilt=true, searchDocuments=479, marlinEvents=301. Afterward ena-promo and hard-linked ena-promo-ai report candidate coverage 89/89, queue advances to marlin-eval-run togakushi-camp, and repo-level canPreferMarlinAsDefault remains false pending broader cross-project coverage.</x:v>
+        <x:v>Latest US-061 pass continued bounded live Togakushi coverage after the materialization fix. VOS_MARLIN_PROXY_MAX_WIDTH=256 .build/arm64-apple-macosx/debug/videoos-studio-cli marlin-eval-run togakushi-camp --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=2 completed with indexRebuilt=true, searchDocuments=295, marlinEvents=13, and marlinFindResults=0. Togakushi now has assets=4/events=13/segmentsWithMarlinPeak=4/coverage=0.07/canPreferMarlin=false; repo-level marlin-preference-status remains false pending broader cross-project coverage. The preceding materialization verification passed npx vitest run tests/marlin-analysis-stage.test.ts 17/0, npx tsc --noEmit --pretty false, swift test --filter 'ProjectMarlinEvaluationRunPlanTests|ProjectMarlinEvaluationQueueTests|ProjectStudioReadinessStatusTests' 19/0, swift build --target VideoOSStudioCLI, and swift build --target VideoOSStudio.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -497,7 +497,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest runtime/macOS CLI check is the US-061 materialization pass: marlin-status ena-promo changed from needs segment materialization to candidate for preferred VLM with assets=89/events=301/segmentsWithMarlinPeak=89/coverage=1.00/canPreferMarlin=true; ena-promo-ai reports the same because its segments.json has the same inode. marlin-preference-status now reports candidateProjects=7, coveredSegments=226, aggregateCoverage=0.61, and canPreferMarlinAsDefault=false. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status and live representative completions, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest runtime/macOS CLI check is the US-061 Togakushi fourth-source run: AST_08BC00DF / NINJAV_S001_S001_T071.MOV added 6 live events, marlin-status togakushi-camp reports assets=4/events=13/findResults=0/segmentsWithMarlinPeak=4/coverage=0.07/canPreferMarlin=false, and marlin-preference-status reports evaluatedProjects=10, candidateProjects=7, coveredSegments=227, aggregateCoverage=0.61, canPreferMarlinAsDefault=false. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status/materialization and live representative completions, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -505,7 +505,7 @@
         <x:v>Latest US-061 follow-up</x:v>
       </x:c>
       <x:c r="B12" s="19" t="str">
-        <x:v>TL-245 fixes the Marlin materialization UX/logistics gap and applies it to ena-promo. Verification now shows ena-promo assets=89/events=301/segmentsWithMarlinPeak=89/coverage=1.00/searchDocuments=479; ena-promo-ai shares the same segments.json inode and also reports 89/89. Repo-level canPreferMarlinAsDefault remains false pending broader evaluated-project coverage.</x:v>
+        <x:v>TL-246 extends Togakushi live Marlin coverage to a fourth source: AST_08BC00DF / NINJAV_S001_S001_T071.MOV added 6 events and raised the project to assets=4/events=13/segmentsWithMarlinPeak=4/coverage=0.07/searchDocuments=295. Repo-level canPreferMarlinAsDefault remains false pending broader evaluated-project coverage; TL-245 remains the materialization UX/logistics fix that moved ena-promo and ena-promo-ai to 89/89 coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="220" customHeight="1">
@@ -8916,79 +8916,79 @@
     </x:row>
     <x:row r="220" ht="48" customHeight="1">
       <x:c r="A220" s="10" t="str">
-        <x:v>TL-205</x:v>
+        <x:v>TL-246</x:v>
       </x:c>
       <x:c r="B220" s="24" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C220" s="24" t="str">
-        <x:v>Native preview duration fallback</x:v>
+        <x:v>Togakushi Marlin fourth-source progress</x:v>
       </x:c>
       <x:c r="D220" s="24" t="str">
-        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
+        <x:v>Run the next resumable Togakushi Marlin source through bounded live caption-only Marlin; inspect artifact, project status, and repo preference status.</x:v>
       </x:c>
       <x:c r="E220" s="24" t="str">
-        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
+        <x:v>VOS_MARLIN_PROXY_MAX_WIDTH=256 .build/arm64-apple-macosx/debug/videoos-studio-cli marlin-eval-run togakushi-camp --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=2 completed with indexRebuilt=true/searchDocuments=295/marlinEvents=13/marlinFindResults=0. The new source is AST_08BC00DF / NINJAV_S001_S001_T071.MOV with 6 events, raising togakushi-camp to assets=4/events=13/findResults=0/segmentsWithMarlinPeak=4/coverage=0.07/canPreferMarlin=false. marlin-preference-status remains partially ready with evaluatedProjects=10, candidateProjects=7, coveredSegments=227, aggregateCoverage=0.61, and canPreferMarlinAsDefault=false.</x:v>
       </x:c>
       <x:c r="F220" s="11" t="str">
-        <x:v>Native pixel/runtime pass</x:v>
+        <x:v>Live 4/60 representative progress; repo preference gate pending</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="48" customHeight="1">
       <x:c r="A221" s="10" t="str">
-        <x:v>TL-206</x:v>
+        <x:v>TL-205</x:v>
       </x:c>
       <x:c r="B221" s="24" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C221" s="24" t="str">
-        <x:v>Native Clip Inspector save and clear</x:v>
+        <x:v>Native preview duration fallback</x:v>
       </x:c>
       <x:c r="D221" s="24" t="str">
-        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
+        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
       </x:c>
       <x:c r="E221" s="24" t="str">
-        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
+        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F221" s="11" t="str">
-        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
+        <x:v>Native pixel/runtime pass</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="48" customHeight="1">
       <x:c r="A222" s="10" t="str">
-        <x:v>TL-207</x:v>
+        <x:v>TL-206</x:v>
       </x:c>
       <x:c r="B222" s="24" t="str">
-        <x:v>US-058</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C222" s="24" t="str">
-        <x:v>Native QA Dashboard issue jump</x:v>
+        <x:v>Native Clip Inspector save and clear</x:v>
       </x:c>
       <x:c r="D222" s="24" t="str">
-        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
+        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
       </x:c>
       <x:c r="E222" s="24" t="str">
-        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
+        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
       </x:c>
       <x:c r="F222" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="48" customHeight="1">
       <x:c r="A223" s="10" t="str">
-        <x:v>TL-208</x:v>
+        <x:v>TL-207</x:v>
       </x:c>
       <x:c r="B223" s="24" t="str">
-        <x:v>US-056</x:v>
+        <x:v>US-058</x:v>
       </x:c>
       <x:c r="C223" s="24" t="str">
-        <x:v>Native Candidate Swap sheet and staging</x:v>
+        <x:v>Native QA Dashboard issue jump</x:v>
       </x:c>
       <x:c r="D223" s="24" t="str">
-        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
+        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
       </x:c>
       <x:c r="E223" s="24" t="str">
-        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
+        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
       </x:c>
       <x:c r="F223" s="11" t="str">
         <x:v>Native AX/pixel pass</x:v>
@@ -8996,339 +8996,339 @@
     </x:row>
     <x:row r="224" ht="48" customHeight="1">
       <x:c r="A224" s="10" t="str">
-        <x:v>TL-209</x:v>
+        <x:v>TL-208</x:v>
       </x:c>
       <x:c r="B224" s="24" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-056</x:v>
       </x:c>
       <x:c r="C224" s="24" t="str">
-        <x:v>Native exact preview regeneration</x:v>
+        <x:v>Native Candidate Swap sheet and staging</x:v>
       </x:c>
       <x:c r="D224" s="24" t="str">
-        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
+        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
       </x:c>
       <x:c r="E224" s="24" t="str">
-        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
       </x:c>
       <x:c r="F224" s="11" t="str">
-        <x:v>Native exact preview pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="48" customHeight="1">
       <x:c r="A225" s="10" t="str">
-        <x:v>TL-210</x:v>
+        <x:v>TL-209</x:v>
       </x:c>
       <x:c r="B225" s="24" t="str">
-        <x:v>US-047</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C225" s="24" t="str">
-        <x:v>Native Command Palette top-bar open/close</x:v>
+        <x:v>Native exact preview regeneration</x:v>
       </x:c>
       <x:c r="D225" s="24" t="str">
-        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
+        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
       </x:c>
       <x:c r="E225" s="24" t="str">
-        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
+        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F225" s="11" t="str">
-        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
+        <x:v>Native exact preview pass</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="48" customHeight="1">
       <x:c r="A226" s="10" t="str">
-        <x:v>TL-211</x:v>
+        <x:v>TL-210</x:v>
       </x:c>
       <x:c r="B226" s="24" t="str">
         <x:v>US-047</x:v>
       </x:c>
       <x:c r="C226" s="24" t="str">
-        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
+        <x:v>Native Command Palette top-bar open/close</x:v>
       </x:c>
       <x:c r="D226" s="24" t="str">
-        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
+        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
       </x:c>
       <x:c r="E226" s="24" t="str">
-        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
+        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
       </x:c>
       <x:c r="F226" s="11" t="str">
-        <x:v>Native keyboard/AX pass</x:v>
+        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="48" customHeight="1">
       <x:c r="A227" s="10" t="str">
-        <x:v>TL-212</x:v>
+        <x:v>TL-211</x:v>
       </x:c>
       <x:c r="B227" s="24" t="str">
-        <x:v>US-048</x:v>
+        <x:v>US-047</x:v>
       </x:c>
       <x:c r="C227" s="24" t="str">
-        <x:v>Native Agent panel session lifecycle</x:v>
+        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
       </x:c>
       <x:c r="D227" s="24" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
+        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
       </x:c>
       <x:c r="E227" s="24" t="str">
-        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
+        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
       </x:c>
       <x:c r="F227" s="11" t="str">
-        <x:v>Native AX/computer-use pass</x:v>
+        <x:v>Native keyboard/AX pass</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="48" customHeight="1">
       <x:c r="A228" s="10" t="str">
-        <x:v>TL-213</x:v>
+        <x:v>TL-212</x:v>
       </x:c>
       <x:c r="B228" s="24" t="str">
-        <x:v>US-049</x:v>
+        <x:v>US-048</x:v>
       </x:c>
       <x:c r="C228" s="24" t="str">
-        <x:v>Native Status agent job read-only turn</x:v>
+        <x:v>Native Agent panel session lifecycle</x:v>
       </x:c>
       <x:c r="D228" s="24" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
       </x:c>
       <x:c r="E228" s="24" t="str">
-        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
+        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F228" s="11" t="str">
-        <x:v>Native read-only job pass; approved write pending</x:v>
+        <x:v>Native AX/computer-use pass</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="48" customHeight="1">
       <x:c r="A229" s="10" t="str">
-        <x:v>TL-214</x:v>
+        <x:v>TL-213</x:v>
       </x:c>
       <x:c r="B229" s="24" t="str">
-        <x:v>US-050</x:v>
+        <x:v>US-049</x:v>
       </x:c>
       <x:c r="C229" s="24" t="str">
-        <x:v>Native Project readiness/action queue Copy pass</x:v>
+        <x:v>Native Status agent job read-only turn</x:v>
       </x:c>
       <x:c r="D229" s="24" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
       </x:c>
       <x:c r="E229" s="24" t="str">
-        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
+        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F229" s="11" t="str">
-        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
+        <x:v>Native read-only job pass; approved write pending</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="48" customHeight="1">
       <x:c r="A230" s="10" t="str">
-        <x:v>TL-215</x:v>
+        <x:v>TL-214</x:v>
       </x:c>
       <x:c r="B230" s="24" t="str">
-        <x:v>US-051</x:v>
+        <x:v>US-050</x:v>
       </x:c>
       <x:c r="C230" s="24" t="str">
-        <x:v>Native local Source Analysis button</x:v>
+        <x:v>Native Project readiness/action queue Copy pass</x:v>
       </x:c>
       <x:c r="D230" s="24" t="str">
-        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
       </x:c>
       <x:c r="E230" s="24" t="str">
-        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
+        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
       </x:c>
       <x:c r="F230" s="11" t="str">
-        <x:v>Native local analysis pass</x:v>
+        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="48" customHeight="1">
       <x:c r="A231" s="10" t="str">
-        <x:v>TL-216</x:v>
+        <x:v>TL-215</x:v>
       </x:c>
       <x:c r="B231" s="24" t="str">
-        <x:v>US-052</x:v>
+        <x:v>US-051</x:v>
       </x:c>
       <x:c r="C231" s="24" t="str">
-        <x:v>Native Rough Cut and Review Patch buttons</x:v>
+        <x:v>Native local Source Analysis button</x:v>
       </x:c>
       <x:c r="D231" s="24" t="str">
-        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
+        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E231" s="24" t="str">
-        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
       </x:c>
       <x:c r="F231" s="11" t="str">
-        <x:v>Native compile/review patch pass</x:v>
+        <x:v>Native local analysis pass</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="48" customHeight="1">
       <x:c r="A232" s="10" t="str">
-        <x:v>TL-217</x:v>
+        <x:v>TL-216</x:v>
       </x:c>
       <x:c r="B232" s="24" t="str">
-        <x:v>US-053</x:v>
+        <x:v>US-052</x:v>
       </x:c>
       <x:c r="C232" s="24" t="str">
-        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
+        <x:v>Native Rough Cut and Review Patch buttons</x:v>
       </x:c>
       <x:c r="D232" s="24" t="str">
-        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
+        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E232" s="24" t="str">
-        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
+        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F232" s="11" t="str">
-        <x:v>Native timeline/context menu pass</x:v>
+        <x:v>Native compile/review patch pass</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="48" customHeight="1">
       <x:c r="A233" s="10" t="str">
-        <x:v>TL-218</x:v>
+        <x:v>TL-217</x:v>
       </x:c>
       <x:c r="B233" s="24" t="str">
-        <x:v>US-054</x:v>
+        <x:v>US-053</x:v>
       </x:c>
       <x:c r="C233" s="24" t="str">
-        <x:v>Native Studio feedback Apply and Undo</x:v>
+        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
       </x:c>
       <x:c r="D233" s="24" t="str">
-        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
+        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
       </x:c>
       <x:c r="E233" s="24" t="str">
-        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
       </x:c>
       <x:c r="F233" s="11" t="str">
-        <x:v>Native apply/undo pass</x:v>
+        <x:v>Native timeline/context menu pass</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="48" customHeight="1">
       <x:c r="A234" s="10" t="str">
-        <x:v>TL-219</x:v>
+        <x:v>TL-218</x:v>
       </x:c>
       <x:c r="B234" s="24" t="str">
-        <x:v>US-057</x:v>
+        <x:v>US-054</x:v>
       </x:c>
       <x:c r="C234" s="24" t="str">
-        <x:v>Native Footage Search sheet and replacement staging</x:v>
+        <x:v>Native Studio feedback Apply and Undo</x:v>
       </x:c>
       <x:c r="D234" s="24" t="str">
-        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
+        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E234" s="24" t="str">
-        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
+        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F234" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native apply/undo pass</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="48" customHeight="1">
       <x:c r="A235" s="10" t="str">
-        <x:v>TL-220</x:v>
+        <x:v>TL-219</x:v>
       </x:c>
       <x:c r="B235" s="24" t="str">
-        <x:v>US-066</x:v>
+        <x:v>US-057</x:v>
       </x:c>
       <x:c r="C235" s="24" t="str">
-        <x:v>Native Settings transport picker mutation</x:v>
+        <x:v>Native Footage Search sheet and replacement staging</x:v>
       </x:c>
       <x:c r="D235" s="24" t="str">
-        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
+        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
       </x:c>
       <x:c r="E235" s="24" t="str">
-        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
       </x:c>
       <x:c r="F235" s="11" t="str">
-        <x:v>Native Settings picker mutation pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="236" ht="48" customHeight="1">
       <x:c r="A236" s="10" t="str">
-        <x:v>TL-221</x:v>
+        <x:v>TL-220</x:v>
       </x:c>
       <x:c r="B236" s="24" t="str">
-        <x:v>US-059</x:v>
+        <x:v>US-066</x:v>
       </x:c>
       <x:c r="C236" s="24" t="str">
-        <x:v>Native Media Relink buttons and source-map relink</x:v>
+        <x:v>Native Settings transport picker mutation</x:v>
       </x:c>
       <x:c r="D236" s="24" t="str">
-        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
+        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
       </x:c>
       <x:c r="E236" s="24" t="str">
-        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
+        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F236" s="11" t="str">
-        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
+        <x:v>Native Settings picker mutation pass</x:v>
       </x:c>
     </x:row>
     <x:row r="237" ht="48" customHeight="1">
       <x:c r="A237" s="10" t="str">
-        <x:v>TL-222</x:v>
+        <x:v>TL-221</x:v>
       </x:c>
       <x:c r="B237" s="24" t="str">
-        <x:v>US-060</x:v>
+        <x:v>US-059</x:v>
       </x:c>
       <x:c r="C237" s="24" t="str">
-        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
+        <x:v>Native Media Relink buttons and source-map relink</x:v>
       </x:c>
       <x:c r="D237" s="24" t="str">
-        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
+        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
       </x:c>
       <x:c r="E237" s="24" t="str">
-        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
+        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
       </x:c>
       <x:c r="F237" s="11" t="str">
-        <x:v>Native synthetic/proxy/smoke button pass</x:v>
+        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
       </x:c>
     </x:row>
     <x:row r="238" ht="48" customHeight="1">
       <x:c r="A238" s="10" t="str">
-        <x:v>TL-223</x:v>
+        <x:v>TL-222</x:v>
       </x:c>
       <x:c r="B238" s="24" t="str">
-        <x:v>US-046</x:v>
+        <x:v>US-060</x:v>
       </x:c>
       <x:c r="C238" s="24" t="str">
-        <x:v>Native New Project from Source</x:v>
+        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
       </x:c>
       <x:c r="D238" s="24" t="str">
-        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
+        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
       </x:c>
       <x:c r="E238" s="24" t="str">
-        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
+        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
       </x:c>
       <x:c r="F238" s="11" t="str">
-        <x:v>Native project creation/NSOpenPanel pass</x:v>
+        <x:v>Native synthetic/proxy/smoke button pass</x:v>
       </x:c>
     </x:row>
     <x:row r="239" ht="48" customHeight="1">
       <x:c r="A239" s="10" t="str">
-        <x:v>TL-224</x:v>
+        <x:v>TL-223</x:v>
       </x:c>
       <x:c r="B239" s="24" t="str">
-        <x:v>US-062</x:v>
+        <x:v>US-046</x:v>
       </x:c>
       <x:c r="C239" s="24" t="str">
-        <x:v>Native MediaPanel Audio Story Graph button</x:v>
+        <x:v>Native New Project from Source</x:v>
       </x:c>
       <x:c r="D239" s="24" t="str">
-        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
+        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
       </x:c>
       <x:c r="E239" s="24" t="str">
-        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
       </x:c>
       <x:c r="F239" s="11" t="str">
-        <x:v>Native AX/UI/CLI pass</x:v>
+        <x:v>Native project creation/NSOpenPanel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="240" ht="48" customHeight="1">
       <x:c r="A240" s="10" t="str">
-        <x:v>TL-225</x:v>
+        <x:v>TL-224</x:v>
       </x:c>
       <x:c r="B240" s="24" t="str">
-        <x:v>US-063</x:v>
+        <x:v>US-062</x:v>
       </x:c>
       <x:c r="C240" s="24" t="str">
-        <x:v>Native Render Final Package button</x:v>
+        <x:v>Native MediaPanel Audio Story Graph button</x:v>
       </x:c>
       <x:c r="D240" s="24" t="str">
-        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
+        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E240" s="24" t="str">
-        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F240" s="11" t="str">
         <x:v>Native AX/UI/CLI pass</x:v>
@@ -9336,121 +9336,141 @@
     </x:row>
     <x:row r="241" ht="48" customHeight="1">
       <x:c r="A241" s="10" t="str">
-        <x:v>TL-226</x:v>
+        <x:v>TL-225</x:v>
       </x:c>
       <x:c r="B241" s="24" t="str">
-        <x:v>US-064</x:v>
+        <x:v>US-063</x:v>
       </x:c>
       <x:c r="C241" s="24" t="str">
-        <x:v>Native Editor Handoff export and Finder reveal</x:v>
+        <x:v>Native Render Final Package button</x:v>
       </x:c>
       <x:c r="D241" s="24" t="str">
-        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
+        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
       </x:c>
       <x:c r="E241" s="24" t="str">
-        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
+        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F241" s="11" t="str">
-        <x:v>Native AX/UI/Finder/CLI pass</x:v>
+        <x:v>Native AX/UI/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="242" ht="48" customHeight="1">
       <x:c r="A242" s="10" t="str">
-        <x:v>TL-227</x:v>
+        <x:v>TL-226</x:v>
       </x:c>
       <x:c r="B242" s="24" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-064</x:v>
       </x:c>
       <x:c r="C242" s="24" t="str">
-        <x:v>Native Ask Codex editor-note proposal</x:v>
+        <x:v>Native Editor Handoff export and Finder reveal</x:v>
       </x:c>
       <x:c r="D242" s="24" t="str">
-        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
+        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E242" s="24" t="str">
-        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
+        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
       </x:c>
       <x:c r="F242" s="11" t="str">
-        <x:v>Native read-only Codex proposal pass</x:v>
+        <x:v>Native AX/UI/Finder/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="243" ht="48" customHeight="1">
       <x:c r="A243" s="10" t="str">
-        <x:v>TL-228</x:v>
+        <x:v>TL-227</x:v>
       </x:c>
       <x:c r="B243" s="24" t="str">
-        <x:v>US-061</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C243" s="24" t="str">
-        <x:v>Live Marlin single-source completion</x:v>
+        <x:v>Native Ask Codex editor-note proposal</x:v>
       </x:c>
       <x:c r="D243" s="24" t="str">
-        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
+        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
       </x:c>
       <x:c r="E243" s="24" t="str">
-        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
+        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
       </x:c>
       <x:c r="F243" s="11" t="str">
-        <x:v>Live single-source pass; full representative batch pending</x:v>
+        <x:v>Native read-only Codex proposal pass</x:v>
       </x:c>
     </x:row>
     <x:row r="244" ht="48" customHeight="1">
       <x:c r="A244" s="10" t="str">
-        <x:v>TL-229</x:v>
+        <x:v>TL-228</x:v>
       </x:c>
       <x:c r="B244" s="24" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C244" s="24" t="str">
-        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+        <x:v>Live Marlin single-source completion</x:v>
       </x:c>
       <x:c r="D244" s="24" t="str">
-        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
       </x:c>
       <x:c r="E244" s="24" t="str">
-        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
       </x:c>
       <x:c r="F244" s="11" t="str">
-        <x:v>Native fresh-launch pixel pass</x:v>
+        <x:v>Live single-source pass; full representative batch pending</x:v>
       </x:c>
     </x:row>
     <x:row r="245" ht="48" customHeight="1">
       <x:c r="A245" s="10" t="str">
-        <x:v>TL-230</x:v>
+        <x:v>TL-229</x:v>
       </x:c>
       <x:c r="B245" s="24" t="str">
         <x:v>US-045</x:v>
       </x:c>
       <x:c r="C245" s="24" t="str">
+        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+      </x:c>
+      <x:c r="D245" s="24" t="str">
+        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+      </x:c>
+      <x:c r="E245" s="24" t="str">
+        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+      </x:c>
+      <x:c r="F245" s="11" t="str">
+        <x:v>Native fresh-launch pixel pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" ht="48" customHeight="1">
+      <x:c r="A246" s="10" t="str">
+        <x:v>TL-230</x:v>
+      </x:c>
+      <x:c r="B246" s="24" t="str">
+        <x:v>US-045</x:v>
+      </x:c>
+      <x:c r="C246" s="24" t="str">
         <x:v>AX-1 exact preview promotion and pixel pass</x:v>
       </x:c>
-      <x:c r="D245" s="24" t="str">
+      <x:c r="D246" s="24" t="str">
         <x:v>Run videoos-studio-cli compile-run on projects/ax1-participant-voices-20260401, confirm playback-contract-status, select ProjectShelf.ax1-participant-voices-20260401 in VideoOSStudio, capture /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and run Retina-coordinate pixel statistics on the Viewer region.</x:v>
       </x:c>
-      <x:c r="E245" s="24" t="str">
+      <x:c r="E246" s="24" t="str">
         <x:v>Before compile, playback-contract-status returned legacy_manifest and approvalGrade=false. compile-run completed with exitCode=0, timeline compiled, indexDocuments=492, and git status stayed clean. After compile, playback-contract-status returned state=exact, approvalGrade=true, timelineHash=171378fe2bfe3a7c, and manifestBaseTimelineHash=171378fe2bfe3a7c. Native Viewer showed Exact preview / preview-editor-1775121573933.mp4 and Timeline preview D4887.MP4 with a visible interview frame. Screenshot was 3.5M; viewer_person_actual mean_rgb=(144.62,141.42,149.8) and near_black_pct=0.0004, while left pillarbox near_black_pct=1.0000 as expected.</x:v>
       </x:c>
-      <x:c r="F245" s="11" t="str">
+      <x:c r="F246" s="11" t="str">
         <x:v>Native AX-1 exact/pixel pass</x:v>
       </x:c>
     </x:row>
-    <x:row r="246" ht="48" customHeight="1">
-      <x:c r="A246" s="12" t="str">
+    <x:row r="247" ht="48" customHeight="1">
+      <x:c r="A247" s="12" t="str">
         <x:v>TL-231</x:v>
       </x:c>
-      <x:c r="B246" s="25" t="str">
+      <x:c r="B247" s="25" t="str">
         <x:v>US-050</x:v>
       </x:c>
-      <x:c r="C246" s="25" t="str">
+      <x:c r="C247" s="25" t="str">
         <x:v>Native Action Queue approval gate</x:v>
       </x:c>
-      <x:c r="D246" s="25" t="str">
+      <x:c r="D247" s="25" t="str">
         <x:v>Add ProjectPanel.ActionQueue* identifiers, relaunch VideoOSStudio, select AX-1 Project tab, inspect the Action Queue AX tree, click ProjectPanel.ActionQueueRunButton.rough-cut-review, and stop at the Codex approval gate without approving writes.</x:v>
       </x:c>
-      <x:c r="E246" s="25" t="str">
+      <x:c r="E247" s="25" t="str">
         <x:v>AX exposed ProjectPanel.ActionQueueRunButton.rough-cut-review, ProjectPanel.ActionQueueCopyButton.rough-cut-review, ProjectPanel.ActionQueueRunButton.marlin-default, and ProjectPanel.ActionQueueCopyButton.marlin-default. Clicking rough-cut-review changed the row to disabled Starting Codex session for Review..., then to Opening Codex approval gate for Review. ps showed a Codex app-server child under VideoOSStudio; git status listed only the intentional ProjectInspectorViews.swift edit, and projects/ax1-participant-voices-20260401/06_review still contained only human_notes.yaml.</x:v>
       </x:c>
-      <x:c r="F246" s="13" t="str">
+      <x:c r="F247" s="13" t="str">
         <x:v>Native approval-gate pass; write not approved</x:v>
       </x:c>
     </x:row>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Re6883ef438de49f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="R4e32a42cf11f48b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R57cd63a4f3ef4457"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="R3db72df175f94ae9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R856afb5e21ff4a00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R429404c4fb354fd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rb5ea2a2d876748b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R5a3f8afc58a64387"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="Rf55aac97433b4592"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R6d384ab33dab4ff7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,7 +433,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>2026-06-23 22:41 JST</x:v>
+        <x:v>2026-06-23 22:48 JST</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -489,7 +489,7 @@
         <x:v>Final test</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Latest US-061 pass continued bounded live Togakushi coverage after the materialization fix. VOS_MARLIN_PROXY_MAX_WIDTH=256 .build/arm64-apple-macosx/debug/videoos-studio-cli marlin-eval-run togakushi-camp --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=2 completed with indexRebuilt=true, searchDocuments=295, marlinEvents=13, and marlinFindResults=0. Togakushi now has assets=4/events=13/segmentsWithMarlinPeak=4/coverage=0.07/canPreferMarlin=false; repo-level marlin-preference-status remains false pending broader cross-project coverage. The preceding materialization verification passed npx vitest run tests/marlin-analysis-stage.test.ts 17/0, npx tsc --noEmit --pretty false, swift test --filter 'ProjectMarlinEvaluationRunPlanTests|ProjectMarlinEvaluationQueueTests|ProjectStudioReadinessStatusTests' 19/0, swift build --target VideoOSStudioCLI, and swift build --target VideoOSStudio.</x:v>
+        <x:v>Latest US-061 pass continued bounded live Togakushi coverage after the materialization fix and verified the native CLI first. swift build --target VideoOSStudioCLI passed. VOS_MARLIN_PROXY_MAX_WIDTH=256 .build/arm64-apple-macosx/debug/videoos-studio-cli marlin-eval-run togakushi-camp --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=2 completed with indexRebuilt=true, searchDocuments=296, marlinEvents=14, and marlinFindResults=0. Togakushi now has assets=5/events=14/segmentsWithMarlinPeak=5/coverage=0.08/canPreferMarlin=false; repo-level marlin-preference-status remains false pending broader cross-project coverage. The preceding materialization verification passed npx vitest run tests/marlin-analysis-stage.test.ts 17/0, npx tsc --noEmit --pretty false, swift test --filter 'ProjectMarlinEvaluationRunPlanTests|ProjectMarlinEvaluationQueueTests|ProjectStudioReadinessStatusTests' 19/0, swift build --target VideoOSStudioCLI, and swift build --target VideoOSStudio.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="220" customHeight="1">
@@ -497,7 +497,7 @@
         <x:v>Browser/macOS check</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Latest runtime/macOS CLI check is the US-061 Togakushi fourth-source run: AST_08BC00DF / NINJAV_S001_S001_T071.MOV added 6 live events, marlin-status togakushi-camp reports assets=4/events=13/findResults=0/segmentsWithMarlinPeak=4/coverage=0.07/canPreferMarlin=false, and marlin-preference-status reports evaluatedProjects=10, candidateProjects=7, coveredSegments=227, aggregateCoverage=0.61, canPreferMarlinAsDefault=false. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status/materialization and live representative completions, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
+        <x:v>Latest runtime/macOS CLI check is the US-061 Togakushi fifth-source run: AST_0AD9FD1C / NINJAV_S001_S001_T035.MOV added 1 live event, marlin-status togakushi-camp reports assets=5/events=14/findResults=0/segmentsWithMarlinPeak=5/coverage=0.08/canPreferMarlin=false, and marlin-preference-status reports evaluatedProjects=10, candidateProjects=7, coveredSegments=228, aggregateCoverage=0.61, canPreferMarlinAsDefault=false. Prior native checks include the US-047 Command Palette computer-use pass, US-061 marlin-runtime-status/materialization and live representative completions, US-065 RAG/Add/Agent-tab, US-045 exact-preview Viewer pixel evidence, US-055 Ask Codex proposal, US-064 handoff, US-063 render, US-062 audio graph, US-046 New Project, US-060 synthetic/proxy/smoke, US-059 Media Relink, US-066 Settings picker, US-057 Footage Search, US-054 Apply/Undo, US-053 Timeline context menu, US-052 Rough Cut/Review Patch, US-051 Source Analysis, US-049 read-only Status job, US-048 Check/Start/Stop lifecycle, Candidate Swap, QA Dashboard issue-jump, Clip Inspector Save/Clear, diagnostics, relink/proxy/render/handoff, Marlin/audio graph, and Viewer readiness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="220" customHeight="1">
@@ -505,7 +505,7 @@
         <x:v>Latest US-061 follow-up</x:v>
       </x:c>
       <x:c r="B12" s="19" t="str">
-        <x:v>TL-246 extends Togakushi live Marlin coverage to a fourth source: AST_08BC00DF / NINJAV_S001_S001_T071.MOV added 6 events and raised the project to assets=4/events=13/segmentsWithMarlinPeak=4/coverage=0.07/searchDocuments=295. Repo-level canPreferMarlinAsDefault remains false pending broader evaluated-project coverage; TL-245 remains the materialization UX/logistics fix that moved ena-promo and ena-promo-ai to 89/89 coverage.</x:v>
+        <x:v>TL-247 extends Togakushi live Marlin coverage to a fifth source: AST_0AD9FD1C / NINJAV_S001_S001_T035.MOV added 1 event and raised the project to assets=5/events=14/segmentsWithMarlinPeak=5/coverage=0.08/searchDocuments=296. Repo-level canPreferMarlinAsDefault remains false pending broader evaluated-project coverage; TL-245 remains the materialization UX/logistics fix that moved ena-promo and ena-promo-ai to 89/89 coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="220" customHeight="1">
@@ -2157,10 +2157,10 @@
         <x:v>Run Marlin runtime/model/preference/queue/representative-plan/eval-plan/eval-run/materialize/status CLI checks, execute a tiny mock evaluation fixture, verify index refresh, verify Preference apply is blocked when gates fail, run Marlin focused Swift tests, confirm stable Marlin accessibility identifiers, run live non-mock representative-source chunks, verify source-map-aware chunk/checkpoint/caption-only behavior, materialize existing artifacts without model access, and leave repo-level preference promotion blocked until aggregate evidence gates pass.</x:v>
       </x:c>
       <x:c r="G62" s="24" t="str">
-        <x:v>Runtime/model/mock/native AX/live 9-source/materialization pass; repo preference gate pending</x:v>
+        <x:v>Runtime/model/mock/native AX/live 9-source/materialization/Togakushi 5-source pass; repo preference gate pending</x:v>
       </x:c>
       <x:c r="H62" s="11" t="str">
-        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. The runtime probe now imports dependency modules in isolated child processes, so the live marlin-runtime-status check no longer emits duplicate AVFoundation class warnings while still reporting every module ready. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path supports --request-timeout-ms / --timeout-ms, and a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4 completed with requestTimeoutMs=900000, wrote inference_mode=live Marlin events, updated segments with marlin_temporal_semantics, and rebuilt an index with 9 search documents. Current passes add per-asset checkpoint writes in runMarlinAnalysis plus --max-sources and --skip-existing through marlin-evaluate, ProjectMarlinEvaluationRunPlan/Runner, marlin-eval-plan, marlin-eval-next, and marlin-eval-run, then make loadMarlinAssetInputs source-map-aware so explicit linked filenames resolve to the correct asset_id when assets.json stores original camera filenames. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and a command carrying those options before source URLs. A /tmp mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. The latest code adds --caption-only plus bounded range chunk controls (--chunk-seconds, --chunk-overlap-seconds, --max-chunks) through the TS stage, marlin-evaluate, native CLI plan/run paths, and ProjectMarlinEvaluationRunPlan/Runner; tests verify find queries are not invoked when captionOnly is true and chunk event IDs carry chunk metadata. The current materialization pass adds scripts/marlin-materialize.ts plus native CLI/Core/UI readiness routing so queue/readiness buttons run a no-model artifact materialization command when marlin_events.json exists but segments have no Marlin peaks. Verification passed: npx vitest run tests/marlin-analysis-stage.test.ts 17/0, npx tsc --noEmit --pretty false, swift build --target VideoOSStudioCLI, and swift test --filter 'ProjectMarlinEvaluationRunPlanTests|ProjectMarlinEvaluationQueueTests|ProjectStudioReadinessStatusTests' 19/0. Live materialization ran .build/arm64-apple-macosx/debug/videoos-studio-cli marlin-materialize ena-promo; it changed Marlin peaks from 0 to 89, rebuilt project_index.sqlite with searchDocuments=479/marlinEvents=301, and made ena-promo a candidate with coverage=1.00/canPreferMarlin=true. ena-promo-ai shares the same segments.json inode and now reports the same 89/89 candidate coverage. Repo-level marlin-preference-status improved to candidateProjects=7, coveredSegments=226, aggregateCoverage=0.61, but canPreferMarlinAsDefault remains false because other evaluated projects still need broader coverage or materialization.</x:v>
+        <x:v>Current Apple Silicon runtime is ready with python/.venv-marlin/bin/python3, resolvedDevice=mps, torch 2.12.0, transformers 5.9.0, torchcodec 0.13.0, qwen-vl-utils 0.0.14, av 17.0.1, pillow 12.2.0, and accelerate 1.13.0. The runtime probe now imports dependency modules in isolated child processes, so the live marlin-runtime-status check no longer emits duplicate AVFoundation class warnings while still reporting every module ready. HF model access for NemoStation/Marlin-2B is ready. Repo preference status remains partially ready and canPreferMarlinAsDefault=false. A tiny outputs/us061-marlin-runtime-smoke fixture produced a mock marlin_events.json and rebuilt a SQLite index with 8 search documents; mock evidence is still excluded from preference promotion. A previous live representative attempt selected lively-alt-vol5 because it covers target buckets with 9 sources; the worker loaded NemoStation/Marlin-2B weights but timed out after the fixed 300000ms default before writing marlin_events.json. The CLI/script path supports --request-timeout-ms / --timeout-ms, and a live non-mock single-source completion against a /tmp fixture derived from lively-alt-vol5 AST_5CAEC24E / 08-jun-a-man-and-a.mp4 completed with requestTimeoutMs=900000, wrote inference_mode=live Marlin events, updated segments with marlin_temporal_semantics, and rebuilt an index with 9 search documents. Current passes add per-asset checkpoint writes in runMarlinAnalysis plus --max-sources and --skip-existing through marlin-evaluate, ProjectMarlinEvaluationRunPlan/Runner, marlin-eval-plan, marlin-eval-next, and marlin-eval-run, then make loadMarlinAssetInputs source-map-aware so explicit linked filenames resolve to the correct asset_id when assets.json stores original camera filenames. marlin-eval-plan lively-alt-vol5 --request-timeout-ms=900000 --max-sources=1 --skip-existing printed maxSources=1, skipExisting=true, and a command carrying those options before source URLs. A /tmp mock chunk smoke ran two max-sources=1 passes, the second with skip-existing, and accumulated 2 marlin_events items. The latest code adds --caption-only plus bounded range chunk controls (--chunk-seconds, --chunk-overlap-seconds, --max-chunks) through the TS stage, marlin-evaluate, native CLI plan/run paths, and ProjectMarlinEvaluationRunPlan/Runner; tests verify find queries are not invoked when captionOnly is true and chunk event IDs carry chunk metadata. The materialization pass adds scripts/marlin-materialize.ts plus native CLI/Core/UI readiness routing so queue/readiness buttons run a no-model artifact materialization command when marlin_events.json exists but segments have no Marlin peaks. Verification passed: npx vitest run tests/marlin-analysis-stage.test.ts 17/0, npx tsc --noEmit --pretty false, swift build --target VideoOSStudioCLI, and swift test --filter 'ProjectMarlinEvaluationRunPlanTests|ProjectMarlinEvaluationQueueTests|ProjectStudioReadinessStatusTests' 19/0. Live materialization ran .build/arm64-apple-macosx/debug/videoos-studio-cli marlin-materialize ena-promo; it changed Marlin peaks from 0 to 89, rebuilt project_index.sqlite with searchDocuments=479/marlinEvents=301, and made ena-promo a candidate with coverage=1.00/canPreferMarlin=true. ena-promo-ai shares the same segments.json inode and now reports the same 89/89 candidate coverage. The latest bounded Togakushi run advanced skip-existing evaluation to AST_0AD9FD1C / NINJAV_S001_S001_T035.MOV, raised togakushi-camp to assets=5/events=14/segmentsWithMarlinPeak=5/coverage=0.08/searchDocuments=296, and raised repo coveredSegments to 228 while canPreferMarlinAsDefault remains false because other evaluated projects still need broader coverage or materialization.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="48" customHeight="1">
@@ -8936,79 +8936,79 @@
     </x:row>
     <x:row r="221" ht="48" customHeight="1">
       <x:c r="A221" s="10" t="str">
-        <x:v>TL-205</x:v>
+        <x:v>TL-247</x:v>
       </x:c>
       <x:c r="B221" s="24" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C221" s="24" t="str">
-        <x:v>Native preview duration fallback</x:v>
+        <x:v>Togakushi Marlin fifth-source progress</x:v>
       </x:c>
       <x:c r="D221" s="24" t="str">
-        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
+        <x:v>Build the native CLI, rerun the next bounded skip-existing Togakushi Marlin source, and inspect artifact, project status, and repo preference status.</x:v>
       </x:c>
       <x:c r="E221" s="24" t="str">
-        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
+        <x:v>swift build --target VideoOSStudioCLI passed. Pre-run marlin-status togakushi-camp reported assets=4/events=13/segmentsWithMarlinPeak=4/coverage=0.07. VOS_MARLIN_PROXY_MAX_WIDTH=256 .build/arm64-apple-macosx/debug/videoos-studio-cli marlin-eval-run togakushi-camp --request-timeout-ms=900000 --max-sources=1 --skip-existing --caption-only --chunk-seconds=30 --chunk-overlap-seconds=3 --max-chunks=2 completed with indexRebuilt=true/searchDocuments=296/marlinEvents=14/marlinFindResults=0. The new source is AST_0AD9FD1C / NINJAV_S001_S001_T035.MOV with 1 event, raising togakushi-camp to assets=5/events=14/findResults=0/segmentsWithMarlinPeak=5/coverage=0.08/canPreferMarlin=false. marlin-preference-status remains partially ready with evaluatedProjects=10, candidateProjects=7, coveredSegments=228, aggregateCoverage=0.61, and canPreferMarlinAsDefault=false.</x:v>
       </x:c>
       <x:c r="F221" s="11" t="str">
-        <x:v>Native pixel/runtime pass</x:v>
+        <x:v>Live 5/60 representative progress; repo preference gate pending</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="48" customHeight="1">
       <x:c r="A222" s="10" t="str">
-        <x:v>TL-206</x:v>
+        <x:v>TL-205</x:v>
       </x:c>
       <x:c r="B222" s="24" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C222" s="24" t="str">
-        <x:v>Native Clip Inspector save and clear</x:v>
+        <x:v>Native preview duration fallback</x:v>
       </x:c>
       <x:c r="D222" s="24" t="str">
-        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
+        <x:v>Patch duration-aware timeline preview selection; relaunch native app; step AX-1 playhead to 00:01:14 via Transport &gt; Step Forward; capture screenshot and ffprobe selected outputs.</x:v>
       </x:c>
       <x:c r="E222" s="24" t="str">
-        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
+        <x:v>At 0s AX-1 still used preview-editor-1775121573933.mp4 as expected. At 00:01:14 the Viewer stayed visible and subtitle changed to timeline-preview / ax1_promo_v5.mp4; ffprobe reported ax1_promo_v5.mp4 duration 75.000000 while preview-editor is 8.007633. ProjectMediaResolverTests executed 25 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify launched VideoOSStudio PID 94310; full swift test executed 229 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F222" s="11" t="str">
-        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
+        <x:v>Native pixel/runtime pass</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="48" customHeight="1">
       <x:c r="A223" s="10" t="str">
-        <x:v>TL-207</x:v>
+        <x:v>TL-206</x:v>
       </x:c>
       <x:c r="B223" s="24" t="str">
-        <x:v>US-058</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C223" s="24" t="str">
-        <x:v>Native QA Dashboard issue jump</x:v>
+        <x:v>Native Clip Inspector save and clear</x:v>
       </x:c>
       <x:c r="D223" s="24" t="str">
-        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
+        <x:v>Use running VideoOSStudio PID 94310; select Clip tab; select first V1 hero clip; set ClipInspector.NoteDraftEditor and HandoffInstructionDraftEditor through AXValue; trigger Save Note; scroll the Clip Inspector to Editor Note; capture screenshot; verify annotations-status and editor_annotations.json; trigger Clear; capture screenshot; verify notes return to zero and restore original absent annotation artifact.</x:v>
       </x:c>
       <x:c r="E223" s="24" t="str">
-        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
+        <x:v>ClipInspector showed 1 clip notes, Saved note for CLP_0001, saved handoff text, and the saved note text after Save. annotations-status reported exists=true notes=1 and editor_annotations.json contained the CLP_0001 note. Screenshot /tmp/videoos-debug/us055-clip-note-saved-visible.png captured the visible saved Editor Note state. After Clear, ClipInspector showed Cleared note for CLP_0001 and 0 clip notes; annotations-status reported notes=0, screenshot /tmp/videoos-debug/us055-clip-note-cleared-visible.png captured the visible cleared Editor Note state, and the temporary editor_annotations.json plus empty 07_handoff directory were removed so annotations-status returned exists=false notes=0.</x:v>
       </x:c>
       <x:c r="F223" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native AX/pixel pass; live Ask Codex proposal pending</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="48" customHeight="1">
       <x:c r="A224" s="10" t="str">
-        <x:v>TL-208</x:v>
+        <x:v>TL-207</x:v>
       </x:c>
       <x:c r="B224" s="24" t="str">
-        <x:v>US-056</x:v>
+        <x:v>US-058</x:v>
       </x:c>
       <x:c r="C224" s="24" t="str">
-        <x:v>Native Candidate Swap sheet and staging</x:v>
+        <x:v>Native QA Dashboard issue jump</x:v>
       </x:c>
       <x:c r="D224" s="24" t="str">
-        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
+        <x:v>On VideoOSStudio PID 97663, select ena-promo-ai, open QA tab, scroll QADashboard.Panel to Issues, verify radar and issue jump buttons, press QADashboard.IssueJumpButton.QAISSUE_16707063a988, and capture screenshot.</x:v>
       </x:c>
       <x:c r="E224" s="24" t="str">
-        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
+        <x:v>Before the fix, Iteration 1 was an AXDisclosureTriangle with no actions and QADashboard.IssueJumpButton.* was missing. After replacing the DisclosureGroup with visible issue rows and moving the parent identifier to the header, AX exposed QADashboard.BriefAlignmentRadar plus QADashboard.IssueJumpButton.QAISSUE_16707063a988 and QAISSUE_2c0c06267ed5. Pressing QAISSUE_16707063a988 returned err=0 and changed Playhead from 00:00:00:00 to 00:00:17:12. Screenshot /tmp/videoos-debug/us058-qa-issues-jump-after-fix.png shows visible QA issues and the jumped playhead. swift build --target VideoOSStudio, swift test --filter QADashboardDocumentTests, git diff --check, and build_and_run --verify passed.</x:v>
       </x:c>
       <x:c r="F224" s="11" t="str">
         <x:v>Native AX/pixel pass</x:v>
@@ -9016,339 +9016,339 @@
     </x:row>
     <x:row r="225" ht="48" customHeight="1">
       <x:c r="A225" s="10" t="str">
-        <x:v>TL-209</x:v>
+        <x:v>TL-208</x:v>
       </x:c>
       <x:c r="B225" s="24" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-056</x:v>
       </x:c>
       <x:c r="C225" s="24" t="str">
-        <x:v>Native exact preview regeneration</x:v>
+        <x:v>Native Candidate Swap sheet and staging</x:v>
       </x:c>
       <x:c r="D225" s="24" t="str">
-        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
+        <x:v>On VideoOSStudio PID 97422, select ena-promo-ai, open Swap from the timeline context menu for b02 clip SEG_AST_B20ECEB1_0001, inspect CandidateSwap AX identifiers, press Search for more, reopen Swap, press the first Use button, then discard the staged operation.</x:v>
       </x:c>
       <x:c r="E225" s="24" t="str">
-        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial retest found every child AXIdentifier shadowed as CandidateSwap.Sheet. After removing parent/container identifiers, AX exposed CandidateSwap.Title, Subtitle, CurrentClipHeader, AlternativeCount=21, SearchForMoreButton, CandidateSegment.*, and UseButton.*. Search for more closed Candidate Swap and showed Search Footage plus Footage search opened for CLP_0002. Reopening Swap and pressing CandidateSwap.UseButton.cand_W_hrkTkvBjfH staged SEG_AST_6BE56C81_0001, closed the sheet, and showed 1 swapped; Discard returned 0 changes pending / 0 swapped. Screenshots: /tmp/videoos-debug/us056-candidate-swap-b02-sheet.png, /tmp/videoos-debug/us056-search-for-more-handoff.png, /tmp/videoos-debug/us056-candidate-swap-used-pending.png. Real ena-promo-ai candidate smoke returned 49 candidates; b02_discovery had 22 eligible candidates. swift build --target VideoOSStudio, focused CandidateBrowserDataSourceTests/StudioFeedbackSessionTests 15/0, git diff --check, build_and_run --verify, and full swift test 229/0 passed.</x:v>
       </x:c>
       <x:c r="F225" s="11" t="str">
-        <x:v>Native exact preview pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="48" customHeight="1">
       <x:c r="A226" s="10" t="str">
-        <x:v>TL-210</x:v>
+        <x:v>TL-209</x:v>
       </x:c>
       <x:c r="B226" s="24" t="str">
-        <x:v>US-047</x:v>
+        <x:v>US-045</x:v>
       </x:c>
       <x:c r="C226" s="24" t="str">
-        <x:v>Native Command Palette top-bar open/close</x:v>
+        <x:v>Native exact preview regeneration</x:v>
       </x:c>
       <x:c r="D226" s="24" t="str">
-        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
+        <x:v>Recompile ena-promo-ai, fix preview renderer duration source, regenerate preview-full.mp4, verify media duration and playback contract, relaunch the native app, and inspect the Viewer with computer-use.</x:v>
       </x:c>
       <x:c r="E226" s="24" t="str">
-        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
+        <x:v>Before fix, playback-contract-status was stale with timelineHash f0b574ea1ff7e541 versus manifestBaseTimelineHash 9096952b77dc9ae3, and preview-full.mp4 ffprobe duration was 93.581380s despite preview-segment.ts reporting 76.1s. After compile-run and renderer fix, playback-contract-status is exact with timelineHash f3bc3e6fef222e1a; preview-full.mp4 is H.264 1280x720 yuv420p with ffprobe duration 75.914714s for 76.083333s timeline content; computer-use clicked ProjectShelf.ena-promo-ai and Viewer showed Exact preview / preview-full.mp4 with visible video. npx vitest run tests/preview.test.ts passed 29 tests, npm run build passed, swift test --filter ProjectMediaResolverTests passed 25 tests, and build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F226" s="11" t="str">
-        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
+        <x:v>Native exact preview pass</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="48" customHeight="1">
       <x:c r="A227" s="10" t="str">
-        <x:v>TL-211</x:v>
+        <x:v>TL-210</x:v>
       </x:c>
       <x:c r="B227" s="24" t="str">
         <x:v>US-047</x:v>
       </x:c>
       <x:c r="C227" s="24" t="str">
-        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
+        <x:v>Native Command Palette top-bar open/close</x:v>
       </x:c>
       <x:c r="D227" s="24" t="str">
-        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
+        <x:v>Use computer-use on the running VideoOSStudio window, press CommandPaletteButton, inspect the Command Palette panel and item identifiers, then close it through the exposed close button.</x:v>
       </x:c>
       <x:c r="E227" s="24" t="str">
-        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
+        <x:v>CommandPaletteButton element 10 opened a separate CommandPalettePanel window with CommandPaletteSheet, CommandPaletteSearchField, CommandPaletteCloseButton, and stable command item IDs such as CommandPaletteItem.refresh-projects, new-project-from-source, check-codex-app-server, start-agent-session, compile-rough-cut, apply-review-patch, search-footage, rebuild-search-index, run-marlin-evaluation, and build-audio-story-graph. Pressing CommandPaletteCloseButton element 4 returned to the main VideoOSStudio window without disrupting ena-promo-ai exact preview.</x:v>
       </x:c>
       <x:c r="F227" s="11" t="str">
-        <x:v>Native keyboard/AX pass</x:v>
+        <x:v>Native AX/computer-use pass; keyboard execute pending</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="48" customHeight="1">
       <x:c r="A228" s="10" t="str">
-        <x:v>TL-212</x:v>
+        <x:v>TL-211</x:v>
       </x:c>
       <x:c r="B228" s="24" t="str">
-        <x:v>US-048</x:v>
+        <x:v>US-047</x:v>
       </x:c>
       <x:c r="C228" s="24" t="str">
-        <x:v>Native Agent panel session lifecycle</x:v>
+        <x:v>Native Command Palette keyboard execute and dismiss</x:v>
       </x:c>
       <x:c r="D228" s="24" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
+        <x:v>Use running VideoOSStudio PID 24960, clean stale Command Palette search field state, open Command Palette with Cmd-K, filter to Search Footage, execute with Return, close the Search Footage sheet, reopen Command Palette, and dismiss with Esc.</x:v>
       </x:c>
       <x:c r="E228" s="24" t="str">
-        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
+        <x:v>Initial retest confirmed Cmd-K opened CommandPalettePanel, but the reused NSTextField could retain stale AXValue せあrch across presentations. After syncing NSTextField/currentEditor from parent.query before focus, swift build --target VideoOSStudio and build_and_run.sh --verify passed. Cmd-K opened a clean search field; AXValue search footage filtered to only CommandPaletteItem.search-footage; Return opened the Search Footage sheet for ax1-participant-voices-20260401; closing the sheet returned to the main window with status Footage search opened; reopening the palette and pressing Esc left only the Video OS Studio window. StudioCommandPaletteCommandTests executed 4 tests with 0 failures and git diff --check on ContentView.swift passed.</x:v>
       </x:c>
       <x:c r="F228" s="11" t="str">
-        <x:v>Native AX/computer-use pass</x:v>
+        <x:v>Native keyboard/AX pass</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="48" customHeight="1">
       <x:c r="A229" s="10" t="str">
-        <x:v>TL-213</x:v>
+        <x:v>TL-212</x:v>
       </x:c>
       <x:c r="B229" s="24" t="str">
-        <x:v>US-049</x:v>
+        <x:v>US-048</x:v>
       </x:c>
       <x:c r="C229" s="24" t="str">
-        <x:v>Native Status agent job read-only turn</x:v>
+        <x:v>Native Agent panel session lifecycle</x:v>
       </x:c>
       <x:c r="D229" s="24" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; press Check Connection, Start Agent Session, and Stop Session; then run focused Codex App Server and command availability tests.</x:v>
       </x:c>
       <x:c r="E229" s="24" t="str">
-        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
+        <x:v>Initial Agent panel showed Status Unchecked, Check/Start enabled, and Stop disabled. Check Connection changed Status to Ready and detail to macos / Codex Desktop/0.140.0. Start Agent Session transitioned through Checking, then displayed Thread 019ef2ef-274b-7733-8833-b3583367fa20 and Model gpt-5.5, with Start disabled, Stop enabled, Run Job Turn enabled, and Run Read-Only Turn enabled. Stop Session cleared Thread/Model, reset Status to Unchecked, restored Start, disabled Stop, and set turn status to No active session. swift test --filter 'CodexAppServerProtocolTests|StudioCommandPaletteCommandTests' executed 14 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F229" s="11" t="str">
-        <x:v>Native read-only job pass; approved write pending</x:v>
+        <x:v>Native AX/computer-use pass</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="48" customHeight="1">
       <x:c r="A230" s="10" t="str">
-        <x:v>TL-214</x:v>
+        <x:v>TL-213</x:v>
       </x:c>
       <x:c r="B230" s="24" t="str">
-        <x:v>US-050</x:v>
+        <x:v>US-049</x:v>
       </x:c>
       <x:c r="C230" s="24" t="str">
-        <x:v>Native Project readiness/action queue Copy pass</x:v>
+        <x:v>Native Status agent job read-only turn</x:v>
       </x:c>
       <x:c r="D230" s="24" t="str">
-        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960; start a Codex session for ax1-participant-voices-20260401, keep Job=Status, press Run Job Turn, wait for completion, then stop the session and run focused agent job tests.</x:v>
       </x:c>
       <x:c r="E230" s="24" t="str">
-        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
+        <x:v>Start Agent Session created thread 019ef2f3-caf2-7f83-a0c6-daa5f0adde80 with model gpt-5.5. The Status job was selected, showed read-only / network off and the read-only approval summary, and Run Job Turn became enabled. Pressing it set Status to Turn running, then completed turn 019ef2f4-4356-7980-a833-320800815f2d with 214 events, 0 diffs, 0 contract warnings, and completed status in Turn Results. Stop Session cleared the active session and disabled Run Job Turn again. swift test --filter 'VideoOSAgentJobTests|VideoOSAgentJobReadinessTests' executed 13 tests with 0 failures.</x:v>
       </x:c>
       <x:c r="F230" s="11" t="str">
-        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
+        <x:v>Native read-only job pass; approved write pending</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="48" customHeight="1">
       <x:c r="A231" s="10" t="str">
-        <x:v>TL-215</x:v>
+        <x:v>TL-214</x:v>
       </x:c>
       <x:c r="B231" s="24" t="str">
-        <x:v>US-051</x:v>
+        <x:v>US-050</x:v>
       </x:c>
       <x:c r="C231" s="24" t="str">
-        <x:v>Native local Source Analysis button</x:v>
+        <x:v>Native Project readiness/action queue Copy pass</x:v>
       </x:c>
       <x:c r="D231" s="24" t="str">
-        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
+        <x:v>Use computer-use on running VideoOSStudio PID 24960 with ax1-participant-voices-20260401 selected; open the Project tab, inspect readiness/action queue sections, press a safe Copy button only, verify pasteboard content, and run focused Project readiness/goal tests.</x:v>
       </x:c>
       <x:c r="E231" s="24" t="str">
-        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
+        <x:v>Project tab showed State, Goal Coverage, Studio Readiness, Pipeline Gates, Planning, Intent Brief, Intent Alignment, Review, Source Analysis, and Rough Cut Compile. Studio Readiness reported ready to compile, 7/9 partially ready, 4/7 candidate projects, 3/3 representative buckets, and exposed queued Rough cut / review, Final render, and Marlin default gate actions. Pressing Copy on the Marlin default gate changed the action status to Copied command for Marlin default gate, and pbpaste returned swift run videoos-studio-cli marlin-eval-next --execute. swift test --filter 'ProjectStudioReadinessStatusTests|ProjectStudioGoalStatusTests' executed 6 tests with 0 failures. Destructive Open/Start &amp; Run actions were not clicked.</x:v>
       </x:c>
       <x:c r="F231" s="11" t="str">
-        <x:v>Native local analysis pass</x:v>
+        <x:v>Native copy/action queue pass; destructive runs pending</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="48" customHeight="1">
       <x:c r="A232" s="10" t="str">
-        <x:v>TL-216</x:v>
+        <x:v>TL-215</x:v>
       </x:c>
       <x:c r="B232" s="24" t="str">
-        <x:v>US-052</x:v>
+        <x:v>US-051</x:v>
       </x:c>
       <x:c r="C232" s="24" t="str">
-        <x:v>Native Rough Cut and Review Patch buttons</x:v>
+        <x:v>Native local Source Analysis button</x:v>
       </x:c>
       <x:c r="D232" s="24" t="str">
-        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
+        <x:v>Add native local analysis defaults, create a disposable projects/us051-native-analysis-smoke project with one MP4 source, relaunch VideoOSStudio, select the project, open Project tab, inspect Source Analysis command/status, click Run Source Analysis, verify generated artifacts/index, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E232" s="24" t="str">
-        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>ProjectPanel Source Analysis showed status ready, Sources 1, Skipped files 0, and command line with --skip-stt --skip-vlm --skip-diarize --skip-peak --skip-marlin --skip-appraiser --skip-media-link --skip-preflight --concurrency 1 --no-cache. Clicking ProjectPanel.RunSourceAnalysisButton changed it to disabled Analyzing Sources with status Analyzing 1 source files locally, then completed with Local analysis completed for 1 sources and Studio Readiness moved to ready for planning. File/CLI verification showed assets.json items=1, segments.json items=1, index-status searchDocuments=2, library-status ready for compile assets=1 segments=1 mediaReady=true ragReady=true, appraiser_frames absent, and source_map absent due skip-media-link. ProjectAnalysisRunnerTests executed 5 tests with 0 failures, swift build --target VideoOSStudio passed, build_and_run --verify passed, git diff --check passed, and the temporary project was removed.</x:v>
       </x:c>
       <x:c r="F232" s="11" t="str">
-        <x:v>Native compile/review patch pass</x:v>
+        <x:v>Native local analysis pass</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="48" customHeight="1">
       <x:c r="A233" s="10" t="str">
-        <x:v>TL-217</x:v>
+        <x:v>TL-216</x:v>
       </x:c>
       <x:c r="B233" s="24" t="str">
-        <x:v>US-053</x:v>
+        <x:v>US-052</x:v>
       </x:c>
       <x:c r="C233" s="24" t="str">
-        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
+        <x:v>Native Rough Cut and Review Patch buttons</x:v>
       </x:c>
       <x:c r="D233" s="24" t="str">
-        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
+        <x:v>Add ProjectPanel Rough Cut/Review Patch accessibility identifiers and compile-activity state, create a disposable projects/us052-native-compile-smoke copy from the US-052 smoke fixture, reset timeline.json to v001, relaunch VideoOSStudio, click Compile Rough Cut, click Apply Review Patch, verify timeline/index/library artifacts, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E233" s="24" t="str">
-        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
+        <x:v>ProjectPanel exposed ProjectPanel.CompileRoughCutButton, ProjectPanel.ApplyReviewPatchButton, ProjectPanel.RoughCutCompileStatus, and ProjectPanel.RoughCutCompileCommandLine. Clicking Compile Rough Cut changed only that button to disabled Compiling Rough Cut while Apply Review Patch stayed labeled Apply Review Patch, then completed with Rough cut compiled and timeline.json is ready and Viewer exact preview / 50s timeline. Clicking Apply Review Patch changed only that button to Applying Review Patch, command line included --patch review_patch.json, then completed with Review patch applied and timeline.json was recompiled. File/CLI verification showed timeline version=2, markerCount=6, US-052 smoke marker present at frame 12, index-status searchDocuments=253, library-status library ready / assets=2 / segments=2 / mediaReady=true / ragReady=true. ProjectRoughCutCompileRunnerTests, ReviewPatchDocumentTests, and ProjectAnalysisRunnerTests executed 16 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed; git diff --check passed; the temporary project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F233" s="11" t="str">
-        <x:v>Native timeline/context menu pass</x:v>
+        <x:v>Native compile/review patch pass</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="48" customHeight="1">
       <x:c r="A234" s="10" t="str">
-        <x:v>TL-218</x:v>
+        <x:v>TL-217</x:v>
       </x:c>
       <x:c r="B234" s="24" t="str">
-        <x:v>US-054</x:v>
+        <x:v>US-053</x:v>
       </x:c>
       <x:c r="C234" s="24" t="str">
-        <x:v>Native Studio feedback Apply and Undo</x:v>
+        <x:v>Native Timeline context menu and audio/waveform inspection</x:v>
       </x:c>
       <x:c r="D234" s="24" t="str">
-        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
+        <x:v>Add stable Timeline/Feedback accessibility identifiers, relaunch VideoOSStudio, inspect ax1-participant-voices-20260401 timeline markers/clips/audio cues, right-click clips to run Approve/Reject/Swap/Search, discard staged feedback, and rerun CLI/log checks.</x:v>
       </x:c>
       <x:c r="E234" s="24" t="str">
-        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 32295 exposed Timeline.Marker.*, Timeline.Clip.V1.CLP_0001, Timeline.Clip.V1.CLP_0002, Timeline.AudioCue.*, FeedbackStatus.*, and context menu IDs for Approve/Reject/Swap/SearchReplacement/Remove. Right-click CLP_0001 &gt; Approve changed status to 1 approved. Right-click CLP_0002 &gt; Reject changed status to 1 changes pending / 1 approved / 1 rejected. Right-click CLP_0001 &gt; Swap opened CandidateSwap.Title Swap: CLP_0001. Right-click CLP_0001 &gt; Search for replacement opened the Search Footage sheet. Discard returned 0 changes pending / 0 approved / 0 rejected / 0 swapped. CLI marker/audio/waveform checks returned 5 beat markers, 20 audio-story cues, and 7 A1 waveform overlays with 8 peaks each. Focused TimelineDocument/ProjectAudioTimelineMap/ProjectAudioWaveformMap/StudioFeedbackSession/CandidateBrowserDataSource tests executed 24 tests with 0 failures; swift build --target VideoOSStudio passed; build_and_run --verify passed from the repo root; git diff --check passed; latest 10m log scan returned no AVAudioFile/2003334207/ExtAudioFileOpenURL matches.</x:v>
       </x:c>
       <x:c r="F234" s="11" t="str">
-        <x:v>Native apply/undo pass</x:v>
+        <x:v>Native timeline/context menu pass</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="48" customHeight="1">
       <x:c r="A235" s="10" t="str">
-        <x:v>TL-219</x:v>
+        <x:v>TL-218</x:v>
       </x:c>
       <x:c r="B235" s="24" t="str">
-        <x:v>US-057</x:v>
+        <x:v>US-054</x:v>
       </x:c>
       <x:c r="C235" s="24" t="str">
-        <x:v>Native Footage Search sheet and replacement staging</x:v>
+        <x:v>Native Studio feedback Apply and Undo</x:v>
       </x:c>
       <x:c r="D235" s="24" t="str">
-        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
+        <x:v>Add a visible FeedbackStatus.UndoButton, create disposable projects/us054-native-feedback-smoke-20260623 from the US-052 compile fixture, reset timeline to v001, relaunch VideoOSStudio, stage Reject on CLIP_001, click Apply &amp; Preview, verify patch/history/timeline output, click Undo, verify timeline hash restoration, then remove the disposable project and refresh.</x:v>
       </x:c>
       <x:c r="E235" s="24" t="str">
-        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
+        <x:v>The disposable project planned canRun=true. Native UI exposed FeedbackStatus.UndoButton. Right-click CLIP_001 &gt; Reject changed status to 1 changes pending / 0 approved / 1 rejected. Apply &amp; Preview changed status to Applying Studio patch and refreshing preview, then Timeline updated. 1 clips changed; the timeline clip disappeared, duration became 0:00, pending/approved/rejected/swapped counts reset to 0, and Promote plus Undo became enabled. File checks showed timeline hash changed from d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e to 6b5b985bd5a7e9804e5ec442db2aa82364ad3fd5728550b0efff91261c435143, timeline version=2, totalClips=0, studio_patch_2026-06-23T06-42-27Z.json, patch_history/index.json, and timeline_backup_1.json. Clicking FeedbackStatus.UndoButton restored CLIP_001, status Reverted to previous timeline, hash d809bf06afc589294ac14c13245692f31c4788a07d9d975c923117f4c8bb012e, version=1.0, totalClips=1, and empty history records. Focused US-054 Swift tests executed 21/0; studio-patch-promoter tests executed 5/0; npm run build, swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed; 10m log scan returned no Studio patch/Promote/crash/fatal matches; the disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F235" s="11" t="str">
-        <x:v>Native AX/pixel pass</x:v>
+        <x:v>Native apply/undo pass</x:v>
       </x:c>
     </x:row>
     <x:row r="236" ht="48" customHeight="1">
       <x:c r="A236" s="10" t="str">
-        <x:v>TL-220</x:v>
+        <x:v>TL-219</x:v>
       </x:c>
       <x:c r="B236" s="24" t="str">
-        <x:v>US-066</x:v>
+        <x:v>US-057</x:v>
       </x:c>
       <x:c r="C236" s="24" t="str">
-        <x:v>Native Settings transport picker mutation</x:v>
+        <x:v>Native Footage Search sheet and replacement staging</x:v>
       </x:c>
       <x:c r="D236" s="24" t="str">
-        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
+        <x:v>Add FootageSearch leaf accessibility identifiers and first-beat default target selection, relaunch VideoOSStudio, open Search Footage from Command Palette, run a text search, inspect result controls, click Preview and Use, then discard the staged replacement.</x:v>
       </x:c>
       <x:c r="E236" s="24" t="str">
-        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
+        <x:v>Initial native retest returned Results 2 / fallback for ax1 text query AI, but every result child reported the parent FootageSearch.ResultCard ID and Use was disabled when opened from Command Palette without a selected clip. After the fix, VideoOSStudio PID 83156 exposed FootageSearch.Title, ProjectName, ModePicker, QueryField, SearchButton, VisualAnchor/AudioAnchor fields, ResultSegment.*, PreviewButton.*, BeatPicker.*, and UseButton.* leaf IDs. Text query AI returned SEG_AST_610FB4A0_0001 and SEG_AST_76B05D86_0001; BeatPicker defaulted to b01 and Use was enabled. Clicking Preview on SEG_AST_76B05D86_0001 set status Previewing SEG_AST_76B05D86_0001 in the current timeline. Clicking Use on SEG_AST_610FB4A0_0001 staged one replace, showing 1 changes pending / 1 swapped; Discard returned 0 changes pending. Focused Swift FootageSearchRunner/StudioFeedbackSession tests executed 15/0, footage-search CLI/audio Vitest executed 10/0, ax1 CLI text query AI returned 2 fallback results, swift build --target VideoOSStudio passed, build_and_run --verify passed, and recent log scan returned no Footage/fatal/crash matches.</x:v>
       </x:c>
       <x:c r="F236" s="11" t="str">
-        <x:v>Native Settings picker mutation pass</x:v>
+        <x:v>Native AX/pixel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="237" ht="48" customHeight="1">
       <x:c r="A237" s="10" t="str">
-        <x:v>TL-221</x:v>
+        <x:v>TL-220</x:v>
       </x:c>
       <x:c r="B237" s="24" t="str">
-        <x:v>US-059</x:v>
+        <x:v>US-066</x:v>
       </x:c>
       <x:c r="C237" s="24" t="str">
-        <x:v>Native Media Relink buttons and source-map relink</x:v>
+        <x:v>Native Settings transport picker mutation</x:v>
       </x:c>
       <x:c r="D237" s="24" t="str">
-        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
+        <x:v>Add Settings transport leaf accessibility identifiers, relaunch VideoOSStudio, open Settings, mutate the Transport picker, verify UserDefaults persistence, restore the original defaults state, and run focused transport tests/build.</x:v>
       </x:c>
       <x:c r="E237" s="24" t="str">
-        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
+        <x:v>VideoOSStudio PID 26200 Settings window exposed Settings.TransportPicker value stdio and Settings.TransportDescription. Clicking the picker exposed stdio, websocket, and unixSocket options; selecting websocket changed the picker value and defaults read com.videoos.studio videoOSStudioPreferredTransport returned websocket. Selecting stdio changed the picker back and defaults returned stdio; defaults delete restored the initial absent key. CodexAppServerProtocolTests executed 10 tests with 0 failures, swift build --target VideoOSStudio passed, and ./script/build_and_run.sh --verify passed.</x:v>
       </x:c>
       <x:c r="F237" s="11" t="str">
-        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
+        <x:v>Native Settings picker mutation pass</x:v>
       </x:c>
     </x:row>
     <x:row r="238" ht="48" customHeight="1">
       <x:c r="A238" s="10" t="str">
-        <x:v>TL-222</x:v>
+        <x:v>TL-221</x:v>
       </x:c>
       <x:c r="B238" s="24" t="str">
-        <x:v>US-060</x:v>
+        <x:v>US-059</x:v>
       </x:c>
       <x:c r="C238" s="24" t="str">
-        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
+        <x:v>Native Media Relink buttons and source-map relink</x:v>
       </x:c>
       <x:c r="D238" s="24" t="str">
-        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
+        <x:v>Add MediaPanel relink leaf accessibility identifiers, create a disposable us059-native-relink-smoke project with one missing source-map path and one matching source under the suggested root, relaunch VideoOSStudio, verify NSOpenPanel open/cancel, click Use Source Map Roots, inspect UI and filesystem results, then remove the disposable project and source root.</x:v>
       </x:c>
       <x:c r="E238" s="24" t="str">
-        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
+        <x:v>VideoOSStudio PID 51840 exposed MediaPanel.MediaRelinkStatus, RelinkMissingMediaButton, UseSourceMapRootsButton, and ReplaceSyntheticMediaButton. The disposable project initially showed Source media unavailable, 1 missing media files need relink, Relink Missing Media enabled, Use Source Map Roots enabled, and Replace Synthetic Media disabled. Clicking Relink Missing Media opened an NSOpenPanel titled Relink Missing Media with the expected message; Cancel returned MediaRelinkStatus to Relink cancelled. Clicking Use Source Map Roots changed the Viewer diagnostic to Move playhead onto a clip and MediaRelinkStatus to Relinked 1 files. 0 missing; 0 synthetic previews remain. CLI media-status returned ready=1/missing=0; media-source-map-status returned source map ready, coverage 1/1, relinkedSymlinks=1; source_map.json wrote 02_media/relinked/AST_US059_RELINK-interview.mp4 pointing at /private/tmp/videoos-us059-source-root-20260623/real/interview.mp4. The temporary project and /tmp source root were removed and Refresh Projects removed the shelf item.</x:v>
       </x:c>
       <x:c r="F238" s="11" t="str">
-        <x:v>Native synthetic/proxy/smoke button pass</x:v>
+        <x:v>Native relink AX/NSOpenPanel/source-map pass</x:v>
       </x:c>
     </x:row>
     <x:row r="239" ht="48" customHeight="1">
       <x:c r="A239" s="10" t="str">
-        <x:v>TL-223</x:v>
+        <x:v>TL-222</x:v>
       </x:c>
       <x:c r="B239" s="24" t="str">
-        <x:v>US-046</x:v>
+        <x:v>US-060</x:v>
       </x:c>
       <x:c r="C239" s="24" t="str">
-        <x:v>Native New Project from Source</x:v>
+        <x:v>Native Synthetic/Proxy/Smoke Media buttons</x:v>
       </x:c>
       <x:c r="D239" s="24" t="str">
-        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
+        <x:v>Add MediaPanel synthetic/proxy/smoke leaf accessibility identifiers, create disposable us060-native-synthetic-smoke-20260623 and us060-native-proxy-smoke-20260623 projects, relaunch VideoOSStudio, click Build Demo Media, Build Proxies, and Run Studio Smoke, then verify generated media through CLI and ffprobe.</x:v>
       </x:c>
       <x:c r="E239" s="24" t="str">
-        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
+        <x:v>VideoOSStudio PID 9023 exposed MediaPanel.SyntheticMediaStatus, BuildDemoMediaButton, StudioSyntheticSmokeStatus, RunStudioSmokeButton, StudioAcceptanceSmokeStatus, RunAcceptanceSmokeButton, MediaProxyOperationStatus, BuildProxiesButton, MediaProxyEmptyState, and MediaProxyPlanItem.AST_US060_PROXY. Build Demo Media changed the synthetic project status to Built 1, skipped 0, mapped 1; media-status returned ready=1/missing=0 and media-source-map-status returned coverage 1/1; ffprobe reported h264 1280x720 5.000000s plus AAC. Build Proxies changed proxy status to Built 1 preview proxies, disabled Build Proxies, and showed the empty state; media-status returned ready=1/missing=0/proxyNeeded=0, media-proxy-plan returned proxyPlans=0/pending=0, and ffprobe reported an H.264/AAC proxy. Run Studio Smoke returned Synthetic studio smoke passed with render packaged, packet media=2, score=9/9. Focused ProjectSyntheticMediaBuilderTests, ProjectMediaResolverTests, ProjectStudioSyntheticSmokeTests, ProjectStudioAcceptanceSmokeTests, and ProjectSyntheticHandoffSmokeTests executed 30 tests with 0 failures; swift build --target VideoOSStudio, build_and_run --verify, and git diff --check passed. The disposable projects were removed after verification.</x:v>
       </x:c>
       <x:c r="F239" s="11" t="str">
-        <x:v>Native project creation/NSOpenPanel pass</x:v>
+        <x:v>Native synthetic/proxy/smoke button pass</x:v>
       </x:c>
     </x:row>
     <x:row r="240" ht="48" customHeight="1">
       <x:c r="A240" s="10" t="str">
-        <x:v>TL-224</x:v>
+        <x:v>TL-223</x:v>
       </x:c>
       <x:c r="B240" s="24" t="str">
-        <x:v>US-062</x:v>
+        <x:v>US-046</x:v>
       </x:c>
       <x:c r="C240" s="24" t="str">
-        <x:v>Native MediaPanel Audio Story Graph button</x:v>
+        <x:v>Native New Project from Source</x:v>
       </x:c>
       <x:c r="D240" s="24" t="str">
-        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
+        <x:v>Add New Project alert identifiers and repo-root source-folder panel default, create a disposable us046-native-create-20260623 project from us046-native-source-20260623 in the running macOS app, inspect the shelf/Project tab, and verify project_state plus linked media on disk.</x:v>
       </x:c>
       <x:c r="E240" s="24" t="str">
-        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>VideoOSStudio PID 4587 exposed ProjectShelf.NewProject, ProjectInitializer.ProjectIDField, ProjectInitializer.CreateButton, and ProjectInitializer.CancelButton. Creating us046-native-create-20260623 opened Choose Source Media Folder at the repo root with us046-native-source-20260623 selectable and OKButton labelled Link Source. After clicking Link Source, ProjectShelf.us046-native-create-20260623 appeared with intent_pending, the Project tab showed Source Analysis ready for 1 linked source and Project creation: Created us046-native-create-20260623 and linked source media. File checks showed project_state.yaml project_id us046-native-create-20260623/current_state intent_pending, 02_media/source -&gt; /Users/mocchalera/Dev/video-os-v2-spec/us046-native-source-20260623, ffprobe h264 160x90 1.000000s, and ffprobe aac 1.000000s.</x:v>
       </x:c>
       <x:c r="F240" s="11" t="str">
-        <x:v>Native AX/UI/CLI pass</x:v>
+        <x:v>Native project creation/NSOpenPanel pass</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="48" customHeight="1">
       <x:c r="A241" s="10" t="str">
-        <x:v>TL-225</x:v>
+        <x:v>TL-224</x:v>
       </x:c>
       <x:c r="B241" s="24" t="str">
-        <x:v>US-063</x:v>
+        <x:v>US-062</x:v>
       </x:c>
       <x:c r="C241" s="24" t="str">
-        <x:v>Native Render Final Package button</x:v>
+        <x:v>Native MediaPanel Audio Story Graph button</x:v>
       </x:c>
       <x:c r="D241" s="24" t="str">
-        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
+        <x:v>Create disposable projects/us062-audio-story-smoke from the US-062 fixture with audio_story_graph.json and search index removed, select it in VideoOSStudio, click MediaPanel.BuildAudioStoryGraphButton, inspect UI completion, verify generated graph/index/library output, then remove the disposable project and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E241" s="24" t="str">
-        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
+        <x:v>Before the click, the disposable project showed ProjectShelf.us062-audio-story-smoke media_analyzed, Audio signals 0 / Story nodes 0 / Run ready, command line npx tsx scripts/build-audio-story-graph.ts .../projects/us062-audio-story-smoke, no audio_story_graph.json, and no search/project_index.sqlite. Clicking MediaPanel.BuildAudioStoryGraphButton changed it to disabled Building Audio Graph with Building audio story graph..., then completed with Audio story graph built and indexed: 3 nodes / 7 docs and SQLite status available 7 / Index refreshed after audio story graph: 3 audio nodes. jq verified project_id us062-audio-story-smoke, nodes=3, edges=1, coverage_status=ready; videoos-studio-cli index-status returned exists=true/searchDocuments=7/updatedAt=2026-06-23T08:11:56Z; library-status returned ragReady=true/indexDocuments=7/audioReady=true/audioStoryNodes=3. The disposable project was removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F241" s="11" t="str">
         <x:v>Native AX/UI/CLI pass</x:v>
@@ -9356,121 +9356,141 @@
     </x:row>
     <x:row r="242" ht="48" customHeight="1">
       <x:c r="A242" s="10" t="str">
-        <x:v>TL-226</x:v>
+        <x:v>TL-225</x:v>
       </x:c>
       <x:c r="B242" s="24" t="str">
-        <x:v>US-064</x:v>
+        <x:v>US-063</x:v>
       </x:c>
       <x:c r="C242" s="24" t="str">
-        <x:v>Native Editor Handoff export and Finder reveal</x:v>
+        <x:v>Native Render Final Package button</x:v>
       </x:c>
       <x:c r="D242" s="24" t="str">
-        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
+        <x:v>Run studio-synthetic-smoke --duration=1 --keep, copy the kept project to disposable projects/us063-native-render-smoke-20260623, select it in VideoOSStudio, click MediaPanel.RenderFinalPackageButton, inspect UI progress/completion, verify render status, QA report, manifest, final media, library status, and cleanup.</x:v>
       </x:c>
       <x:c r="E242" s="24" t="str">
-        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
+        <x:v>The disposable project appeared as ProjectShelf.us063-native-render-smoke-20260623 packaged. MediaPanel showed render packaged / ready to render / passed / nle_finishing / 7 total / 0 failed, final video / QA report / manifest / final mix exists, MediaPanel.RenderFinalPackageButton enabled, and MediaPanel.RenderFinalPackageCommandLine containing supplied_final_path to 09_output/final.mp4. Clicking the button changed it to disabled Rendering Final with Rendering and packaging final output..., then completed with Render packaged final output. render-status returned qaPassed=true, qaChecks=7, qaFailedChecks=0, manifestCreatedAt=2026-06-23T08:20:57.186Z, publishedFinalVideo=true, packageManifest=true, qaReport=true, finalMix=true. QA report passed=true with 7 checks and 0 failed; package_manifest source_of_truth=nle_finishing; ffprobe reported h264 1280x720 duration=1.000000; library-status returned library ready, mediaReady=true, ragReady=true, indexDocuments=5. The disposable project and new tmp smoke project were removed and Refresh Projects removed it from the shelf.</x:v>
       </x:c>
       <x:c r="F242" s="11" t="str">
-        <x:v>Native AX/UI/Finder/CLI pass</x:v>
+        <x:v>Native AX/UI/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="243" ht="48" customHeight="1">
       <x:c r="A243" s="10" t="str">
-        <x:v>TL-227</x:v>
+        <x:v>TL-226</x:v>
       </x:c>
       <x:c r="B243" s="24" t="str">
-        <x:v>US-055</x:v>
+        <x:v>US-064</x:v>
       </x:c>
       <x:c r="C243" s="24" t="str">
-        <x:v>Native Ask Codex editor-note proposal</x:v>
+        <x:v>Native Editor Handoff export and Finder reveal</x:v>
       </x:c>
       <x:c r="D243" s="24" t="str">
-        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
+        <x:v>Create disposable handoff and final-media synthetic projects, select them in VideoOSStudio, click MediaPanel.ExportPremiereXMLButton, MediaPanel.ExportEditorPacketButton, and MediaPanel.RevealEditorPacketButton, verify Finder selection and packet contents, then remove the disposable projects and refresh the shelf.</x:v>
       </x:c>
       <x:c r="E243" s="24" t="str">
-        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
+        <x:v>The basic us064-native-handoff-smoke-20260623 fixture confirmed the native buttons and Finder reveal path: Export Premiere XML completed, Export Editor Packet produced a 3-file notes/XML packet, Reveal Packet changed the status to Revealed editor packet in Finder, and Finder selected 09_output/editor_packet. The final-media us064-native-packet-smoke-20260623 fixture started with packet missing but review report included, review patch included, and Preview/final media 2 files. Clicking Export Premiere XML showed Exporting Premiere XML... then Exported synthetic-studio-smoke_premiere.xml. Clicking Export Editor Packet showed Exporting editor packet... then packet verified, 6/6 files, final media included, final audio included, and Exported packet with 7 files. Clicking Reveal Packet showed Revealed editor packet in Finder, and Finder selected editor_packet in 09_output next to final.mp4 and synthetic-studio-smoke_premiere.xml. handoff-packet-verify returned packet verified with manifestFiles=6/existingFiles=6/missingFiles=0/mediaFiles=2/finalMedia=true/finalAudio=true; jq listed premiere_xml, editor_notes, review_report, review_patch, final_media, and final_audio; ffprobe reported packet final_media H.264 1280x720 duration=1.000000 and final_audio pcm_s16le 44100Hz mono. Both disposable projects and the new tmp smoke project were removed, and Refresh Projects removed the us064 shelf entries.</x:v>
       </x:c>
       <x:c r="F243" s="11" t="str">
-        <x:v>Native read-only Codex proposal pass</x:v>
+        <x:v>Native AX/UI/Finder/CLI pass</x:v>
       </x:c>
     </x:row>
     <x:row r="244" ht="48" customHeight="1">
       <x:c r="A244" s="10" t="str">
-        <x:v>TL-228</x:v>
+        <x:v>TL-227</x:v>
       </x:c>
       <x:c r="B244" s="24" t="str">
-        <x:v>US-061</x:v>
+        <x:v>US-055</x:v>
       </x:c>
       <x:c r="C244" s="24" t="str">
-        <x:v>Live Marlin single-source completion</x:v>
+        <x:v>Native Ask Codex editor-note proposal</x:v>
       </x:c>
       <x:c r="D244" s="24" t="str">
-        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
+        <x:v>Use running VideoOSStudio PID 30320 with ax1-participant-voices-20260401 selected; start a stdio Codex App Server session; open the Clip tab; select Timeline.Clip.V1.CLP_0001; press ClipInspector.AskCodexButton; verify the read-only proposal populates draft editors; do not press Save; confirm git status stays clean.</x:v>
       </x:c>
       <x:c r="E244" s="24" t="str">
-        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
+        <x:v>Start Agent Session reached Ready with thread 019ef3a9-251a-70a0-afd7-f83b121af6d0 and model gpt-5.5. The Clip inspector initially exposed ClipInspector.NoSelectionMessage, then after selecting CLP_0001 exposed ClipInspector.NoteDraftEditor, HandoffInstructionDraftEditor, AskCodexButton, SaveNoteButton, ClearNoteButton, and EditorAnnotationStatus. Pressing Ask Codex changed status to Codex is proposing an editor note..., then completed with Codex proposal applied to draft for CLP_0001. Save to write it. NoteDraftEditor was populated with AIへの危機感と参加理由が率直に語られ... and HandoffInstructionDraftEditor with 話者の「正直AIについては危機感」を軸に残し... . Save Note became enabled but was not pressed, Clear stayed disabled, screenshot /tmp/videoos-debug/us055-ask-codex-proposal-applied.png captured the visible draft-applied state, and git status --short remained empty.</x:v>
       </x:c>
       <x:c r="F244" s="11" t="str">
-        <x:v>Live single-source pass; full representative batch pending</x:v>
+        <x:v>Native read-only Codex proposal pass</x:v>
       </x:c>
     </x:row>
     <x:row r="245" ht="48" customHeight="1">
       <x:c r="A245" s="10" t="str">
-        <x:v>TL-229</x:v>
+        <x:v>TL-228</x:v>
       </x:c>
       <x:c r="B245" s="24" t="str">
-        <x:v>US-045</x:v>
+        <x:v>US-061</x:v>
       </x:c>
       <x:c r="C245" s="24" t="str">
-        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+        <x:v>Live Marlin single-source completion</x:v>
       </x:c>
       <x:c r="D245" s="24" t="str">
-        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+        <x:v>Create /tmp/videoos-us061-live-one-source-20260623175610 with lively-alt-vol5 asset AST_5CAEC24E and its matching segment, run VOS_MARLIN_PROXY_MAX_WIDTH=384 npx tsx scripts/marlin-evaluate.ts --project &lt;tmp&gt; --repo-root &lt;repo&gt; --request-timeout-ms 900000 &lt;08-jun-a-man-and-a.mp4&gt;, inspect marlin-status and artifact JSON, then rebuild the SQLite index.</x:v>
       </x:c>
       <x:c r="E245" s="24" t="str">
-        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+        <x:v>The 10.515s 4K source was proxied to .marlin-proxy-cache/9c710360b51ba8d0-w384.mp4. marlin-evaluate completed with Output /tmp/videoos-us061-live-one-source-20260623175610/03_analysis/marlin_events.json, Sources 1, Model NemoStation/Marlin-2B, Mock false. marlin-status reported candidate for preferred VLM with artifactModel NemoStation/Marlin-2B, assets=1, events=3, findResults=4, segmentsWithMarlinPeak=1, coverage=1.00, canPreferMarlin=true. Artifact JSON reported inference_mode=live and asset_id AST_5CAEC24E; segments.json gained peak_analysis.provenance.precision_mode=marlin_temporal_semantics and 3 interest points. index-rebuild succeeded and index-status reported searchDocuments=9. git status stayed clean because all live outputs were under /tmp.</x:v>
       </x:c>
       <x:c r="F245" s="11" t="str">
-        <x:v>Native fresh-launch pixel pass</x:v>
+        <x:v>Live single-source pass; full representative batch pending</x:v>
       </x:c>
     </x:row>
     <x:row r="246" ht="48" customHeight="1">
       <x:c r="A246" s="10" t="str">
-        <x:v>TL-230</x:v>
+        <x:v>TL-229</x:v>
       </x:c>
       <x:c r="B246" s="24" t="str">
         <x:v>US-045</x:v>
       </x:c>
       <x:c r="C246" s="24" t="str">
+        <x:v>Native exact preview fresh-launch pixel pass</x:v>
+      </x:c>
+      <x:c r="D246" s="24" t="str">
+        <x:v>Fresh launch with ./script/build_and_run.sh --verify, select ProjectShelf.ena-promo-ai in the running macOS app via computer-use, inspect playback/media contracts, capture /tmp/videoos-debug/us045-ena-exact-preview-visible-20260623.png, and run Pillow pixel statistics on the Viewer region.</x:v>
+      </x:c>
+      <x:c r="E246" s="24" t="str">
+        <x:v>VideoOSStudio launched on the primary display, initially showed a nonblank AX-1 Viewer frame, then selecting ena-promo-ai showed Support Playback contract: Exact preview / preview-full.mp4 and Playhead 00:00:00:00 Timeline preview No audio. playback-contract-status returned state=exact approvalGrade=true hash f3bc3e6fef222e1a, media-status returned assets=89 ready=89 missing=0 proxyNeeded=0. Screenshot was 3.6M; Viewer center mean_rgb=(160.97,189.02,214.86) and near_black_pct=0.0000.</x:v>
+      </x:c>
+      <x:c r="F246" s="11" t="str">
+        <x:v>Native fresh-launch pixel pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" ht="48" customHeight="1">
+      <x:c r="A247" s="10" t="str">
+        <x:v>TL-230</x:v>
+      </x:c>
+      <x:c r="B247" s="24" t="str">
+        <x:v>US-045</x:v>
+      </x:c>
+      <x:c r="C247" s="24" t="str">
         <x:v>AX-1 exact preview promotion and pixel pass</x:v>
       </x:c>
-      <x:c r="D246" s="24" t="str">
+      <x:c r="D247" s="24" t="str">
         <x:v>Run videoos-studio-cli compile-run on projects/ax1-participant-voices-20260401, confirm playback-contract-status, select ProjectShelf.ax1-participant-voices-20260401 in VideoOSStudio, capture /tmp/videoos-debug/us045-ax1-exact-preview-visible-20260623.png, and run Retina-coordinate pixel statistics on the Viewer region.</x:v>
       </x:c>
-      <x:c r="E246" s="24" t="str">
+      <x:c r="E247" s="24" t="str">
         <x:v>Before compile, playback-contract-status returned legacy_manifest and approvalGrade=false. compile-run completed with exitCode=0, timeline compiled, indexDocuments=492, and git status stayed clean. After compile, playback-contract-status returned state=exact, approvalGrade=true, timelineHash=171378fe2bfe3a7c, and manifestBaseTimelineHash=171378fe2bfe3a7c. Native Viewer showed Exact preview / preview-editor-1775121573933.mp4 and Timeline preview D4887.MP4 with a visible interview frame. Screenshot was 3.5M; viewer_person_actual mean_rgb=(144.62,141.42,149.8) and near_black_pct=0.0004, while left pillarbox near_black_pct=1.0000 as expected.</x:v>
       </x:c>
-      <x:c r="F246" s="11" t="str">
+      <x:c r="F247" s="11" t="str">
         <x:v>Native AX-1 exact/pixel pass</x:v>
       </x:c>
     </x:row>
-    <x:row r="247" ht="48" customHeight="1">
-      <x:c r="A247" s="12" t="str">
+    <x:row r="248" ht="48" customHeight="1">
+      <x:c r="A248" s="12" t="str">
         <x:v>TL-231</x:v>
       </x:c>
-      <x:c r="B247" s="25" t="str">
+      <x:c r="B248" s="25" t="str">
         <x:v>US-050</x:v>
       </x:c>
-      <x:c r="C247" s="25" t="str">
+      <x:c r="C248" s="25" t="str">
         <x:v>Native Action Queue approval gate</x:v>
       </x:c>
-      <x:c r="D247" s="25" t="str">
+      <x:c r="D248" s="25" t="str">
         <x:v>Add ProjectPanel.ActionQueue* identifiers, relaunch VideoOSStudio, select AX-1 Project tab, inspect the Action Queue AX tree, click ProjectPanel.ActionQueueRunButton.rough-cut-review, and stop at the Codex approval gate without approving writes.</x:v>
       </x:c>
-      <x:c r="E247" s="25" t="str">
+      <x:c r="E248" s="25" t="str">
         <x:v>AX exposed ProjectPanel.ActionQueueRunButton.rough-cut-review, ProjectPanel.ActionQueueCopyButton.rough-cut-review, ProjectPanel.ActionQueueRunButton.marlin-default, and ProjectPanel.ActionQueueCopyButton.marlin-default. Clicking rough-cut-review changed the row to disabled Starting Codex session for Review..., then to Opening Codex approval gate for Review. ps showed a Codex app-server child under VideoOSStudio; git status listed only the intentional ProjectInspectorViews.swift edit, and projects/ax1-participant-voices-20260401/06_review still contained only human_notes.yaml.</x:v>
       </x:c>
-      <x:c r="F247" s="13" t="str">
+      <x:c r="F248" s="13" t="str">
         <x:v>Native approval-gate pass; write not approved</x:v>
       </x:c>
     </x:row>

--- a/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
+++ b/outputs/019eee15-26e2-7cd0-b070-cb96ee4ee5ed/video-os-v2-feature-status.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R429404c4fb354fd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" r:id="Rb5ea2a2d876748b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="3" r:id="R5a3f8afc58a64387"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="4" r:id="Rf55aac97433b4592"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Map" sheetId="5" r:id="R6d384ab33dab4ff7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R85689df6f47e4bc5"/>
+    <x:she